--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="152">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -51,6 +51,9 @@
   <si>
     <t>R2 Outcome (color code
 cell background)</t>
+  </si>
+  <si>
+    <t>Implies working perfectly</t>
   </si>
   <si>
     <t>Role Based Login</t>
@@ -67,6 +70,9 @@
     <t>Successful authentication and redirection to user dashboard</t>
   </si>
   <si>
+    <t>Implies not part of this Release</t>
+  </si>
+  <si>
     <t>Admin login with valid CAS credentials</t>
   </si>
   <si>
@@ -78,6 +84,9 @@
     <t>Successful authentication and redirection to dashboard</t>
   </si>
   <si>
+    <t>Implies not a bug but a warning</t>
+  </si>
+  <si>
     <t>Login with invalid credentials</t>
   </si>
   <si>
@@ -87,6 +96,9 @@
   </si>
   <si>
     <t>Login fails and error message is displayed</t>
+  </si>
+  <si>
+    <t>Its a bug and needs to be fixed</t>
   </si>
   <si>
     <t>View Available Rooms</t>
@@ -513,7 +525,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -544,6 +556,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <sz val="10.0"/>
+      <color rgb="FF00FF00"/>
+      <name val="Arial"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
@@ -560,12 +577,42 @@
       <name val="Arimo"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="lightGray"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00FF00"/>
+        <bgColor rgb="FF00FF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF000000"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor rgb="FFFF0000"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -723,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="62">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -746,14 +793,27 @@
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
+    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
@@ -764,26 +824,30 @@
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
+    <xf borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
@@ -800,7 +864,7 @@
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -818,7 +882,7 @@
     <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -857,19 +921,19 @@
     <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="2" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1109,7 +1173,9 @@
     <col customWidth="1" min="7" max="7" width="17.25"/>
     <col customWidth="1" min="8" max="8" width="17.75"/>
     <col customWidth="1" min="9" max="9" width="15.25"/>
-    <col customWidth="1" min="10" max="26" width="8.88"/>
+    <col customWidth="1" min="10" max="11" width="8.88"/>
+    <col customWidth="1" min="12" max="12" width="40.25"/>
+    <col customWidth="1" min="13" max="26" width="8.88"/>
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
@@ -1152,8 +1218,10 @@
         <v>9</v>
       </c>
       <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="K2" s="8"/>
+      <c r="L2" s="9" t="s">
+        <v>11</v>
+      </c>
       <c r="M2" s="7"/>
       <c r="N2" s="7"/>
       <c r="O2" s="7"/>
@@ -1170,5590 +1238,5602 @@
       <c r="Z2" s="7"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="8">
+      <c r="A3" s="10">
         <v>1.0</v>
       </c>
-      <c r="B3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="9" t="s">
+      <c r="B3" s="11" t="s">
         <v>12</v>
       </c>
-      <c r="D3" s="9" t="s">
+      <c r="C3" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="F3" s="10"/>
-      <c r="G3" s="10"/>
-      <c r="H3" s="10"/>
-      <c r="I3" s="10"/>
+      <c r="E3" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="F3" s="12"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="12"/>
+      <c r="I3" s="13"/>
+      <c r="K3" s="14"/>
+      <c r="L3" s="15" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="11">
+      <c r="A4" s="16">
         <f t="shared" ref="A4:A12" si="1">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="9" t="s">
+      <c r="B4" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="17" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
+      <c r="D4" s="11" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="F4" s="18"/>
+      <c r="G4" s="18"/>
+      <c r="H4" s="18"/>
+      <c r="I4" s="18"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="15" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="11">
+      <c r="A5" s="16">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="B5" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
+      <c r="B5" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C5" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E5" s="17" t="s">
+        <v>23</v>
+      </c>
+      <c r="F5" s="18"/>
+      <c r="G5" s="18"/>
+      <c r="H5" s="18"/>
+      <c r="I5" s="18"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="15" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="11">
+      <c r="A6" s="16">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B6" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D6" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="E6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
+      <c r="B6" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C6" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>27</v>
+      </c>
+      <c r="E6" s="17" t="s">
+        <v>28</v>
+      </c>
+      <c r="F6" s="18"/>
+      <c r="G6" s="18"/>
+      <c r="H6" s="18"/>
+      <c r="I6" s="18"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="11">
+      <c r="A7" s="16">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D7" s="12" t="s">
+      <c r="B7" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="E7" s="12" t="s">
+      <c r="C7" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="F7" s="13"/>
-      <c r="G7" s="13"/>
-      <c r="H7" s="13"/>
-      <c r="I7" s="13"/>
+      <c r="D7" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="17" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="18"/>
+      <c r="G7" s="18"/>
+      <c r="H7" s="18"/>
+      <c r="I7" s="18"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="11">
+      <c r="A8" s="16">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B8" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D8" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="E8" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" s="13"/>
-      <c r="G8" s="13"/>
-      <c r="H8" s="13"/>
-      <c r="I8" s="13"/>
+      <c r="B8" s="17" t="s">
+        <v>25</v>
+      </c>
+      <c r="C8" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D8" s="17" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8" s="17" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="18"/>
+      <c r="G8" s="18"/>
+      <c r="H8" s="18"/>
+      <c r="I8" s="18"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="11">
+      <c r="A9" s="16">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B9" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D9" s="12" t="s">
+      <c r="B9" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="E9" s="12" t="s">
-        <v>32</v>
-      </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="13"/>
-      <c r="H9" s="13"/>
-      <c r="I9" s="13"/>
+      <c r="D9" s="17" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9" s="17" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9" s="18"/>
+      <c r="G9" s="18"/>
+      <c r="H9" s="18"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="11">
+      <c r="A10" s="16">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B10" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="E10" s="12" t="s">
+      <c r="B10" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="F10" s="13"/>
-      <c r="G10" s="13"/>
-      <c r="H10" s="13"/>
-      <c r="I10" s="13"/>
+      <c r="C10" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="D10" s="17" t="s">
+        <v>37</v>
+      </c>
+      <c r="E10" s="17" t="s">
+        <v>38</v>
+      </c>
+      <c r="F10" s="18"/>
+      <c r="G10" s="18"/>
+      <c r="H10" s="18"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="11">
+      <c r="A11" s="16">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B11" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="F11" s="13"/>
-      <c r="G11" s="13"/>
-      <c r="H11" s="13"/>
-      <c r="I11" s="13"/>
+      <c r="B11" s="17" t="s">
+        <v>39</v>
+      </c>
+      <c r="C11" s="17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D11" s="17" t="s">
+        <v>41</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>42</v>
+      </c>
+      <c r="F11" s="18"/>
+      <c r="G11" s="18"/>
+      <c r="H11" s="18"/>
+      <c r="I11" s="18"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="11">
+      <c r="A12" s="16">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B12" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="13"/>
-      <c r="G12" s="13"/>
-      <c r="H12" s="13"/>
-      <c r="I12" s="13"/>
+      <c r="C12" s="17" t="s">
+        <v>43</v>
+      </c>
+      <c r="D12" s="17" t="s">
+        <v>44</v>
+      </c>
+      <c r="E12" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="F12" s="18"/>
+      <c r="G12" s="18"/>
+      <c r="H12" s="18"/>
+      <c r="I12" s="18"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="A13" s="16"/>
+      <c r="B13" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="E13" s="12" t="s">
+      <c r="C13" s="17" t="s">
         <v>43</v>
       </c>
-      <c r="F13" s="13"/>
-      <c r="G13" s="13"/>
-      <c r="H13" s="13"/>
-      <c r="I13" s="13"/>
+      <c r="D13" s="17" t="s">
+        <v>46</v>
+      </c>
+      <c r="E13" s="17" t="s">
+        <v>47</v>
+      </c>
+      <c r="F13" s="18"/>
+      <c r="G13" s="18"/>
+      <c r="H13" s="18"/>
+      <c r="I13" s="18"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="11">
+      <c r="A14" s="16">
         <f>A12+1</f>
         <v>11</v>
       </c>
-      <c r="B14" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="F14" s="13"/>
-      <c r="G14" s="13"/>
-      <c r="H14" s="13"/>
-      <c r="I14" s="13"/>
+      <c r="B14" s="17" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D14" s="17" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" s="17" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="18"/>
+      <c r="G14" s="18"/>
+      <c r="H14" s="18"/>
+      <c r="I14" s="18"/>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="11">
+      <c r="A15" s="16">
         <f t="shared" ref="A15:A33" si="2">A14+1</f>
         <v>12</v>
       </c>
-      <c r="B15" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>51</v>
-      </c>
-      <c r="F15" s="13"/>
-      <c r="G15" s="13"/>
-      <c r="H15" s="13"/>
-      <c r="I15" s="13"/>
+      <c r="B15" s="17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C15" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D15" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E15" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="18"/>
+      <c r="G15" s="18"/>
+      <c r="H15" s="18"/>
+      <c r="I15" s="18"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="11">
+      <c r="A16" s="16">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B16" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="C16" s="12" t="s">
+      <c r="B16" s="17" t="s">
         <v>52</v>
       </c>
-      <c r="D16" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>53</v>
-      </c>
-      <c r="F16" s="13"/>
-      <c r="G16" s="13"/>
-      <c r="H16" s="13"/>
-      <c r="I16" s="13"/>
+      <c r="C16" s="17" t="s">
+        <v>56</v>
+      </c>
+      <c r="D16" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="E16" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F16" s="18"/>
+      <c r="G16" s="18"/>
+      <c r="H16" s="18"/>
+      <c r="I16" s="18"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="11">
+      <c r="A17" s="16">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="B17" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="E17" s="12" t="s">
-        <v>56</v>
-      </c>
-      <c r="F17" s="13"/>
-      <c r="G17" s="13"/>
-      <c r="H17" s="13"/>
-      <c r="I17" s="13"/>
+      <c r="B17" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C17" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="D17" s="17" t="s">
+        <v>59</v>
+      </c>
+      <c r="E17" s="17" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="18"/>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18"/>
+      <c r="I17" s="18"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="11">
+      <c r="A18" s="16">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B18" s="12" t="s">
-        <v>57</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="E18" s="12" t="s">
-        <v>60</v>
-      </c>
-      <c r="F18" s="13"/>
-      <c r="G18" s="13"/>
-      <c r="H18" s="13"/>
-      <c r="I18" s="13"/>
+      <c r="B18" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C18" s="17" t="s">
+        <v>62</v>
+      </c>
+      <c r="D18" s="17" t="s">
+        <v>63</v>
+      </c>
+      <c r="E18" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="F18" s="18"/>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18"/>
+      <c r="I18" s="18"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="11">
+      <c r="A19" s="16">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="B19" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>62</v>
-      </c>
-      <c r="D19" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E19" s="12" t="s">
-        <v>64</v>
-      </c>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
+      <c r="B19" s="17" t="s">
+        <v>65</v>
+      </c>
+      <c r="C19" s="17" t="s">
+        <v>66</v>
+      </c>
+      <c r="D19" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E19" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="F19" s="18"/>
+      <c r="G19" s="18"/>
+      <c r="H19" s="18"/>
+      <c r="I19" s="18"/>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="11">
+      <c r="A20" s="16">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="B20" s="12" t="s">
-        <v>61</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="B20" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D20" s="12" t="s">
-        <v>63</v>
-      </c>
-      <c r="E20" s="12" t="s">
-        <v>66</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
-      <c r="H20" s="13"/>
-      <c r="I20" s="13"/>
+      <c r="C20" s="17" t="s">
+        <v>69</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>70</v>
+      </c>
+      <c r="F20" s="18"/>
+      <c r="G20" s="18"/>
+      <c r="H20" s="18"/>
+      <c r="I20" s="18"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="11">
+      <c r="A21" s="16">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="B21" s="12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="D21" s="12" t="s">
-        <v>69</v>
-      </c>
-      <c r="E21" s="12" t="s">
-        <v>70</v>
-      </c>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
+      <c r="B21" s="17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C21" s="17" t="s">
+        <v>72</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>73</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F21" s="18"/>
+      <c r="G21" s="18"/>
+      <c r="H21" s="18"/>
+      <c r="I21" s="18"/>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="11">
+      <c r="A22" s="16">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="B22" s="12" t="s">
-        <v>71</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>72</v>
-      </c>
-      <c r="D22" s="12" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="12" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="13"/>
-      <c r="G22" s="13"/>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13"/>
+      <c r="B22" s="17" t="s">
+        <v>75</v>
+      </c>
+      <c r="C22" s="17" t="s">
+        <v>76</v>
+      </c>
+      <c r="D22" s="17" t="s">
+        <v>77</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>78</v>
+      </c>
+      <c r="F22" s="18"/>
+      <c r="G22" s="18"/>
+      <c r="H22" s="18"/>
+      <c r="I22" s="18"/>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="11">
+      <c r="A23" s="16">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="B23" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D23" s="12" t="s">
-        <v>76</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>77</v>
-      </c>
-      <c r="F23" s="13"/>
-      <c r="G23" s="13"/>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13"/>
+      <c r="B23" s="17" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D23" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="17" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="18"/>
+      <c r="G23" s="18"/>
+      <c r="H23" s="18"/>
+      <c r="I23" s="18"/>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="11">
+      <c r="A24" s="16">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="B24" s="12" t="s">
-        <v>75</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="E24" s="12" t="s">
+      <c r="B24" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="F24" s="13"/>
-      <c r="G24" s="13"/>
-      <c r="H24" s="13"/>
-      <c r="I24" s="13"/>
+      <c r="C24" s="17" t="s">
+        <v>49</v>
+      </c>
+      <c r="D24" s="17" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="17" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="18"/>
+      <c r="G24" s="18"/>
+      <c r="H24" s="18"/>
+      <c r="I24" s="18"/>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="11">
+      <c r="A25" s="16">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B25" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D25" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="E25" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="F25" s="13"/>
-      <c r="G25" s="13"/>
-      <c r="H25" s="13"/>
-      <c r="I25" s="13"/>
+      <c r="B25" s="17" t="s">
+        <v>84</v>
+      </c>
+      <c r="C25" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25" s="17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="17" t="s">
+        <v>86</v>
+      </c>
+      <c r="F25" s="18"/>
+      <c r="G25" s="18"/>
+      <c r="H25" s="18"/>
+      <c r="I25" s="18"/>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="11">
+      <c r="A26" s="16">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="14" t="s">
-        <v>83</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>84</v>
-      </c>
-      <c r="D26" s="12" t="s">
-        <v>85</v>
-      </c>
-      <c r="E26" s="12" t="s">
-        <v>86</v>
-      </c>
-      <c r="F26" s="13"/>
-      <c r="G26" s="13"/>
-      <c r="H26" s="13"/>
-      <c r="I26" s="13"/>
+      <c r="B26" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="C26" s="17" t="s">
+        <v>88</v>
+      </c>
+      <c r="D26" s="17" t="s">
+        <v>89</v>
+      </c>
+      <c r="E26" s="17" t="s">
+        <v>90</v>
+      </c>
+      <c r="F26" s="18"/>
+      <c r="G26" s="18"/>
+      <c r="H26" s="18"/>
+      <c r="I26" s="18"/>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="11">
+      <c r="A27" s="16">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B27" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="12" t="s">
+      <c r="B27" s="17" t="s">
         <v>87</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>88</v>
-      </c>
-      <c r="F27" s="13"/>
-      <c r="G27" s="13"/>
-      <c r="H27" s="13"/>
-      <c r="I27" s="13"/>
+      <c r="C27" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D27" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="E27" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="F27" s="18"/>
+      <c r="G27" s="18"/>
+      <c r="H27" s="18"/>
+      <c r="I27" s="18"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="11">
+      <c r="A28" s="16">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B28" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="D28" s="12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E28" s="12" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="13"/>
-      <c r="G28" s="13"/>
-      <c r="H28" s="13"/>
-      <c r="I28" s="13"/>
+      <c r="B28" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C28" s="17" t="s">
+        <v>26</v>
+      </c>
+      <c r="D28" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="E28" s="17" t="s">
+        <v>94</v>
+      </c>
+      <c r="F28" s="18"/>
+      <c r="G28" s="18"/>
+      <c r="H28" s="18"/>
+      <c r="I28" s="18"/>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="11">
+      <c r="A29" s="16">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B29" s="13"/>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
-      <c r="G29" s="13"/>
-      <c r="H29" s="13"/>
-      <c r="I29" s="13"/>
+      <c r="B29" s="18"/>
+      <c r="C29" s="18"/>
+      <c r="D29" s="18"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="18"/>
+      <c r="G29" s="18"/>
+      <c r="H29" s="18"/>
+      <c r="I29" s="18"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="11">
+      <c r="A30" s="16">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B30" s="13"/>
-      <c r="C30" s="15"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="13"/>
-      <c r="H30" s="13"/>
-      <c r="I30" s="13"/>
+      <c r="B30" s="18"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="18"/>
+      <c r="E30" s="18"/>
+      <c r="F30" s="18"/>
+      <c r="G30" s="18"/>
+      <c r="H30" s="18"/>
+      <c r="I30" s="18"/>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="11">
+      <c r="A31" s="16">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B31" s="13"/>
-      <c r="C31" s="15"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
-      <c r="G31" s="13"/>
-      <c r="H31" s="13"/>
-      <c r="I31" s="13"/>
+      <c r="B31" s="18"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="18"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="18"/>
+      <c r="G31" s="18"/>
+      <c r="H31" s="18"/>
+      <c r="I31" s="18"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="11">
+      <c r="A32" s="16">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B32" s="13"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="13"/>
-      <c r="F32" s="13"/>
-      <c r="G32" s="13"/>
-      <c r="H32" s="13"/>
-      <c r="I32" s="13"/>
+      <c r="B32" s="18"/>
+      <c r="C32" s="18"/>
+      <c r="D32" s="18"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="18"/>
+      <c r="G32" s="18"/>
+      <c r="H32" s="18"/>
+      <c r="I32" s="18"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="11">
+      <c r="A33" s="16">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B33" s="13"/>
-      <c r="C33" s="13"/>
-      <c r="D33" s="13"/>
-      <c r="E33" s="13"/>
-      <c r="F33" s="13"/>
-      <c r="G33" s="13"/>
-      <c r="H33" s="13"/>
-      <c r="I33" s="13"/>
+      <c r="B33" s="18"/>
+      <c r="C33" s="18"/>
+      <c r="D33" s="18"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="18"/>
+      <c r="G33" s="18"/>
+      <c r="H33" s="18"/>
+      <c r="I33" s="18"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="16"/>
-      <c r="B34" s="16"/>
-      <c r="C34" s="16"/>
+      <c r="A34" s="23"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="23"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="16"/>
-      <c r="B35" s="16"/>
-      <c r="C35" s="16"/>
+      <c r="A35" s="23"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="16"/>
-      <c r="B36" s="16"/>
-      <c r="C36" s="16"/>
+      <c r="A36" s="23"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="16"/>
-      <c r="B37" s="16"/>
-      <c r="C37" s="16"/>
+      <c r="A37" s="23"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="23"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="16"/>
-      <c r="B38" s="16"/>
-      <c r="C38" s="16"/>
-      <c r="K38" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="Q38" s="17"/>
-      <c r="R38" s="17"/>
-      <c r="S38" s="17"/>
-      <c r="T38" s="17"/>
+      <c r="A38" s="23"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="23"/>
+      <c r="K38" s="24" t="s">
+        <v>95</v>
+      </c>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="16"/>
-      <c r="B39" s="16"/>
-      <c r="C39" s="16"/>
-      <c r="K39" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="Q39" s="17"/>
-      <c r="R39" s="17"/>
-      <c r="S39" s="17"/>
-      <c r="T39" s="17"/>
+      <c r="A39" s="23"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="23"/>
+      <c r="K39" s="24" t="s">
+        <v>96</v>
+      </c>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="24"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="16"/>
-      <c r="B40" s="16"/>
-      <c r="C40" s="16"/>
-      <c r="K40" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="Q40" s="17"/>
-      <c r="R40" s="17"/>
-      <c r="S40" s="17"/>
-      <c r="T40" s="17"/>
+      <c r="A40" s="23"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="23"/>
+      <c r="K40" s="24" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="16"/>
-      <c r="B41" s="16"/>
-      <c r="C41" s="16"/>
-      <c r="K41" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="Q41" s="17"/>
-      <c r="R41" s="17"/>
-      <c r="S41" s="17"/>
-      <c r="T41" s="17"/>
+      <c r="A41" s="23"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="23"/>
+      <c r="K41" s="24" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q41" s="24"/>
+      <c r="R41" s="24"/>
+      <c r="S41" s="24"/>
+      <c r="T41" s="24"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="16"/>
-      <c r="B42" s="16"/>
-      <c r="C42" s="16"/>
-      <c r="K42" s="17" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q42" s="17"/>
-      <c r="R42" s="17"/>
-      <c r="S42" s="17"/>
-      <c r="T42" s="17"/>
+      <c r="A42" s="23"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="23"/>
+      <c r="K42" s="24" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q42" s="24"/>
+      <c r="R42" s="24"/>
+      <c r="S42" s="24"/>
+      <c r="T42" s="24"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="16"/>
-      <c r="B43" s="16"/>
-      <c r="C43" s="16"/>
-      <c r="K43" s="17" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q43" s="17"/>
-      <c r="R43" s="17"/>
-      <c r="S43" s="17"/>
-      <c r="T43" s="17"/>
+      <c r="A43" s="23"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="23"/>
+      <c r="K43" s="24" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q43" s="24"/>
+      <c r="R43" s="24"/>
+      <c r="S43" s="24"/>
+      <c r="T43" s="24"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="16"/>
-      <c r="B44" s="16"/>
-      <c r="C44" s="16"/>
-      <c r="K44" s="17"/>
-      <c r="R44" s="17"/>
-      <c r="S44" s="17"/>
-      <c r="T44" s="17"/>
+      <c r="A44" s="23"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="23"/>
+      <c r="K44" s="24"/>
+      <c r="R44" s="24"/>
+      <c r="S44" s="24"/>
+      <c r="T44" s="24"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="16"/>
-      <c r="B45" s="16"/>
-      <c r="C45" s="16"/>
-      <c r="K45" s="17"/>
-      <c r="R45" s="17"/>
-      <c r="S45" s="17"/>
-      <c r="T45" s="17"/>
+      <c r="A45" s="23"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="23"/>
+      <c r="K45" s="24"/>
+      <c r="R45" s="24"/>
+      <c r="S45" s="24"/>
+      <c r="T45" s="24"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="16"/>
-      <c r="B46" s="16"/>
-      <c r="C46" s="16"/>
-      <c r="K46" s="17"/>
-      <c r="R46" s="17"/>
-      <c r="S46" s="17"/>
-      <c r="T46" s="17"/>
+      <c r="A46" s="23"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="23"/>
+      <c r="K46" s="24"/>
+      <c r="R46" s="24"/>
+      <c r="S46" s="24"/>
+      <c r="T46" s="24"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="16"/>
-      <c r="B47" s="16"/>
-      <c r="C47" s="16"/>
-      <c r="K47" s="17"/>
-      <c r="R47" s="17"/>
-      <c r="S47" s="17"/>
-      <c r="T47" s="17"/>
+      <c r="A47" s="23"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="23"/>
+      <c r="K47" s="24"/>
+      <c r="R47" s="24"/>
+      <c r="S47" s="24"/>
+      <c r="T47" s="24"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="16"/>
-      <c r="B48" s="16"/>
-      <c r="C48" s="16"/>
-      <c r="K48" s="17"/>
-      <c r="L48" s="17"/>
-      <c r="M48" s="17"/>
-      <c r="N48" s="17"/>
-      <c r="O48" s="17"/>
-      <c r="P48" s="17"/>
-      <c r="Q48" s="17"/>
-      <c r="R48" s="17"/>
-      <c r="S48" s="17"/>
-      <c r="T48" s="17"/>
+      <c r="A48" s="23"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="23"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="24"/>
+      <c r="Q48" s="24"/>
+      <c r="R48" s="24"/>
+      <c r="S48" s="24"/>
+      <c r="T48" s="24"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="16"/>
-      <c r="B49" s="16"/>
-      <c r="C49" s="16"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
-      <c r="N49" s="17"/>
-      <c r="O49" s="17"/>
-      <c r="P49" s="17"/>
-      <c r="Q49" s="17"/>
-      <c r="R49" s="17"/>
-      <c r="S49" s="17"/>
-      <c r="T49" s="17"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="23"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="24"/>
+      <c r="Q49" s="24"/>
+      <c r="R49" s="24"/>
+      <c r="S49" s="24"/>
+      <c r="T49" s="24"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="16"/>
-      <c r="B50" s="16"/>
-      <c r="C50" s="16"/>
-      <c r="K50" s="17"/>
-      <c r="L50" s="17"/>
-      <c r="M50" s="17"/>
-      <c r="N50" s="17"/>
-      <c r="O50" s="17"/>
-      <c r="P50" s="17"/>
-      <c r="Q50" s="17"/>
-      <c r="R50" s="17"/>
-      <c r="S50" s="17"/>
-      <c r="T50" s="17"/>
+      <c r="A50" s="23"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="23"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
+      <c r="N50" s="24"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="24"/>
+      <c r="Q50" s="24"/>
+      <c r="R50" s="24"/>
+      <c r="S50" s="24"/>
+      <c r="T50" s="24"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="16"/>
-      <c r="B51" s="16"/>
-      <c r="C51" s="16"/>
-      <c r="K51" s="17"/>
-      <c r="L51" s="17"/>
-      <c r="M51" s="17"/>
-      <c r="N51" s="17"/>
-      <c r="O51" s="17"/>
-      <c r="P51" s="17"/>
-      <c r="Q51" s="17"/>
-      <c r="R51" s="17"/>
-      <c r="S51" s="17"/>
-      <c r="T51" s="17"/>
+      <c r="A51" s="23"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+      <c r="N51" s="24"/>
+      <c r="O51" s="24"/>
+      <c r="P51" s="24"/>
+      <c r="Q51" s="24"/>
+      <c r="R51" s="24"/>
+      <c r="S51" s="24"/>
+      <c r="T51" s="24"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="16"/>
-      <c r="B52" s="16"/>
-      <c r="C52" s="16"/>
-      <c r="K52" s="17"/>
-      <c r="L52" s="17"/>
-      <c r="M52" s="17"/>
-      <c r="N52" s="17"/>
-      <c r="O52" s="17"/>
-      <c r="P52" s="17"/>
-      <c r="Q52" s="17"/>
-      <c r="R52" s="17"/>
-      <c r="S52" s="17"/>
-      <c r="T52" s="17"/>
+      <c r="A52" s="23"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="24"/>
+      <c r="T52" s="24"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="16"/>
-      <c r="B53" s="16"/>
-      <c r="C53" s="16"/>
+      <c r="A53" s="23"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="23"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="16"/>
-      <c r="B54" s="16"/>
-      <c r="C54" s="16"/>
+      <c r="A54" s="23"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="23"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="16"/>
-      <c r="B55" s="16"/>
-      <c r="C55" s="16"/>
+      <c r="A55" s="23"/>
+      <c r="B55" s="23"/>
+      <c r="C55" s="23"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="16"/>
-      <c r="B56" s="16"/>
-      <c r="C56" s="16"/>
+      <c r="A56" s="23"/>
+      <c r="B56" s="23"/>
+      <c r="C56" s="23"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="16"/>
-      <c r="B57" s="16"/>
-      <c r="C57" s="16"/>
+      <c r="A57" s="23"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="23"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="16"/>
-      <c r="B58" s="16"/>
-      <c r="C58" s="16"/>
+      <c r="A58" s="23"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="23"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="16"/>
-      <c r="B59" s="16"/>
-      <c r="C59" s="16"/>
+      <c r="A59" s="23"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="23"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="16"/>
-      <c r="B60" s="16"/>
-      <c r="C60" s="16"/>
+      <c r="A60" s="23"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="23"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="16"/>
-      <c r="B61" s="16"/>
-      <c r="C61" s="16"/>
+      <c r="A61" s="23"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="23"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="16"/>
-      <c r="B62" s="16"/>
-      <c r="C62" s="16"/>
+      <c r="A62" s="23"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="23"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="16"/>
-      <c r="B63" s="16"/>
-      <c r="C63" s="16"/>
+      <c r="A63" s="23"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="23"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="16"/>
-      <c r="B64" s="16"/>
-      <c r="C64" s="16"/>
+      <c r="A64" s="23"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="16"/>
-      <c r="B65" s="16"/>
-      <c r="C65" s="16"/>
+      <c r="A65" s="23"/>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="16"/>
-      <c r="B66" s="16"/>
-      <c r="C66" s="16"/>
+      <c r="A66" s="23"/>
+      <c r="B66" s="23"/>
+      <c r="C66" s="23"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="16"/>
-      <c r="B67" s="16"/>
-      <c r="C67" s="16"/>
+      <c r="A67" s="23"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="23"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="16"/>
-      <c r="B68" s="16"/>
-      <c r="C68" s="16"/>
+      <c r="A68" s="23"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="23"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="16"/>
-      <c r="B69" s="16"/>
-      <c r="C69" s="16"/>
+      <c r="A69" s="23"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="23"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="16"/>
-      <c r="B70" s="16"/>
-      <c r="C70" s="16"/>
+      <c r="A70" s="23"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="23"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="16"/>
-      <c r="B71" s="16"/>
-      <c r="C71" s="16"/>
+      <c r="A71" s="23"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="23"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="16"/>
-      <c r="B72" s="16"/>
-      <c r="C72" s="16"/>
+      <c r="A72" s="23"/>
+      <c r="B72" s="23"/>
+      <c r="C72" s="23"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="16"/>
-      <c r="B73" s="16"/>
-      <c r="C73" s="16"/>
+      <c r="A73" s="23"/>
+      <c r="B73" s="23"/>
+      <c r="C73" s="23"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="16"/>
-      <c r="B74" s="16"/>
-      <c r="C74" s="16"/>
+      <c r="A74" s="23"/>
+      <c r="B74" s="23"/>
+      <c r="C74" s="23"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="16"/>
-      <c r="B75" s="16"/>
-      <c r="C75" s="16"/>
+      <c r="A75" s="23"/>
+      <c r="B75" s="23"/>
+      <c r="C75" s="23"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="16"/>
-      <c r="B76" s="16"/>
-      <c r="C76" s="16"/>
+      <c r="A76" s="23"/>
+      <c r="B76" s="23"/>
+      <c r="C76" s="23"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="16"/>
-      <c r="B77" s="16"/>
-      <c r="C77" s="16"/>
+      <c r="A77" s="23"/>
+      <c r="B77" s="23"/>
+      <c r="C77" s="23"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="16"/>
-      <c r="B78" s="16"/>
-      <c r="C78" s="16"/>
+      <c r="A78" s="23"/>
+      <c r="B78" s="23"/>
+      <c r="C78" s="23"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="16"/>
-      <c r="B79" s="16"/>
-      <c r="C79" s="16"/>
+      <c r="A79" s="23"/>
+      <c r="B79" s="23"/>
+      <c r="C79" s="23"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="16"/>
-      <c r="B80" s="16"/>
-      <c r="C80" s="16"/>
+      <c r="A80" s="23"/>
+      <c r="B80" s="23"/>
+      <c r="C80" s="23"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="16"/>
-      <c r="B81" s="16"/>
-      <c r="C81" s="16"/>
+      <c r="A81" s="23"/>
+      <c r="B81" s="23"/>
+      <c r="C81" s="23"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="16"/>
-      <c r="B82" s="16"/>
-      <c r="C82" s="16"/>
+      <c r="A82" s="23"/>
+      <c r="B82" s="23"/>
+      <c r="C82" s="23"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="16"/>
-      <c r="B83" s="16"/>
-      <c r="C83" s="16"/>
+      <c r="A83" s="23"/>
+      <c r="B83" s="23"/>
+      <c r="C83" s="23"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="16"/>
-      <c r="B84" s="16"/>
-      <c r="C84" s="16"/>
+      <c r="A84" s="23"/>
+      <c r="B84" s="23"/>
+      <c r="C84" s="23"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="16"/>
-      <c r="B85" s="16"/>
-      <c r="C85" s="16"/>
+      <c r="A85" s="23"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="23"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="16"/>
-      <c r="B86" s="16"/>
-      <c r="C86" s="16"/>
+      <c r="A86" s="23"/>
+      <c r="B86" s="23"/>
+      <c r="C86" s="23"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="16"/>
-      <c r="B87" s="16"/>
-      <c r="C87" s="16"/>
+      <c r="A87" s="23"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="23"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="16"/>
-      <c r="B88" s="16"/>
-      <c r="C88" s="16"/>
+      <c r="A88" s="23"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="23"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="16"/>
-      <c r="B89" s="16"/>
-      <c r="C89" s="16"/>
+      <c r="A89" s="23"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="23"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="16"/>
-      <c r="B90" s="16"/>
-      <c r="C90" s="16"/>
+      <c r="A90" s="23"/>
+      <c r="B90" s="23"/>
+      <c r="C90" s="23"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="16"/>
-      <c r="B91" s="16"/>
-      <c r="C91" s="16"/>
+      <c r="A91" s="23"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="23"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="16"/>
-      <c r="B92" s="16"/>
-      <c r="C92" s="16"/>
+      <c r="A92" s="23"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="23"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="16"/>
-      <c r="B93" s="16"/>
-      <c r="C93" s="16"/>
+      <c r="A93" s="23"/>
+      <c r="B93" s="23"/>
+      <c r="C93" s="23"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="16"/>
-      <c r="B94" s="16"/>
-      <c r="C94" s="16"/>
+      <c r="A94" s="23"/>
+      <c r="B94" s="23"/>
+      <c r="C94" s="23"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="16"/>
-      <c r="B95" s="16"/>
-      <c r="C95" s="16"/>
+      <c r="A95" s="23"/>
+      <c r="B95" s="23"/>
+      <c r="C95" s="23"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="16"/>
-      <c r="B96" s="16"/>
-      <c r="C96" s="16"/>
+      <c r="A96" s="23"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="23"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="16"/>
-      <c r="B97" s="16"/>
-      <c r="C97" s="16"/>
+      <c r="A97" s="23"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="23"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="A98" s="16"/>
-      <c r="B98" s="16"/>
-      <c r="C98" s="16"/>
+      <c r="A98" s="23"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="23"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="A99" s="16"/>
-      <c r="B99" s="16"/>
-      <c r="C99" s="16"/>
+      <c r="A99" s="23"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="23"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="A100" s="16"/>
-      <c r="B100" s="16"/>
-      <c r="C100" s="16"/>
+      <c r="A100" s="23"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="23"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="A101" s="16"/>
-      <c r="B101" s="16"/>
-      <c r="C101" s="16"/>
+      <c r="A101" s="23"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="23"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="A102" s="16"/>
-      <c r="B102" s="16"/>
-      <c r="C102" s="16"/>
+      <c r="A102" s="23"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="23"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="A103" s="16"/>
-      <c r="B103" s="16"/>
-      <c r="C103" s="16"/>
+      <c r="A103" s="23"/>
+      <c r="B103" s="23"/>
+      <c r="C103" s="23"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" s="16"/>
-      <c r="B104" s="16"/>
-      <c r="C104" s="16"/>
+      <c r="A104" s="23"/>
+      <c r="B104" s="23"/>
+      <c r="C104" s="23"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="16"/>
-      <c r="B105" s="16"/>
-      <c r="C105" s="16"/>
+      <c r="A105" s="23"/>
+      <c r="B105" s="23"/>
+      <c r="C105" s="23"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="16"/>
-      <c r="B106" s="16"/>
-      <c r="C106" s="16"/>
+      <c r="A106" s="23"/>
+      <c r="B106" s="23"/>
+      <c r="C106" s="23"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="16"/>
-      <c r="B107" s="16"/>
-      <c r="C107" s="16"/>
+      <c r="A107" s="23"/>
+      <c r="B107" s="23"/>
+      <c r="C107" s="23"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="16"/>
-      <c r="B108" s="16"/>
-      <c r="C108" s="16"/>
+      <c r="A108" s="23"/>
+      <c r="B108" s="23"/>
+      <c r="C108" s="23"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="16"/>
-      <c r="B109" s="16"/>
-      <c r="C109" s="16"/>
+      <c r="A109" s="23"/>
+      <c r="B109" s="23"/>
+      <c r="C109" s="23"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="16"/>
-      <c r="B110" s="16"/>
-      <c r="C110" s="16"/>
+      <c r="A110" s="23"/>
+      <c r="B110" s="23"/>
+      <c r="C110" s="23"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="16"/>
-      <c r="B111" s="16"/>
-      <c r="C111" s="16"/>
+      <c r="A111" s="23"/>
+      <c r="B111" s="23"/>
+      <c r="C111" s="23"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="A112" s="16"/>
-      <c r="B112" s="16"/>
-      <c r="C112" s="16"/>
+      <c r="A112" s="23"/>
+      <c r="B112" s="23"/>
+      <c r="C112" s="23"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="A113" s="16"/>
-      <c r="B113" s="16"/>
-      <c r="C113" s="16"/>
+      <c r="A113" s="23"/>
+      <c r="B113" s="23"/>
+      <c r="C113" s="23"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="16"/>
-      <c r="B114" s="16"/>
-      <c r="C114" s="16"/>
+      <c r="A114" s="23"/>
+      <c r="B114" s="23"/>
+      <c r="C114" s="23"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="16"/>
-      <c r="B115" s="16"/>
-      <c r="C115" s="16"/>
+      <c r="A115" s="23"/>
+      <c r="B115" s="23"/>
+      <c r="C115" s="23"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="16"/>
-      <c r="B116" s="16"/>
-      <c r="C116" s="16"/>
+      <c r="A116" s="23"/>
+      <c r="B116" s="23"/>
+      <c r="C116" s="23"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="A117" s="16"/>
-      <c r="B117" s="16"/>
-      <c r="C117" s="16"/>
+      <c r="A117" s="23"/>
+      <c r="B117" s="23"/>
+      <c r="C117" s="23"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="A118" s="16"/>
-      <c r="B118" s="16"/>
-      <c r="C118" s="16"/>
+      <c r="A118" s="23"/>
+      <c r="B118" s="23"/>
+      <c r="C118" s="23"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="16"/>
-      <c r="B119" s="16"/>
-      <c r="C119" s="16"/>
+      <c r="A119" s="23"/>
+      <c r="B119" s="23"/>
+      <c r="C119" s="23"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="A120" s="16"/>
-      <c r="B120" s="16"/>
-      <c r="C120" s="16"/>
+      <c r="A120" s="23"/>
+      <c r="B120" s="23"/>
+      <c r="C120" s="23"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="A121" s="16"/>
-      <c r="B121" s="16"/>
-      <c r="C121" s="16"/>
+      <c r="A121" s="23"/>
+      <c r="B121" s="23"/>
+      <c r="C121" s="23"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="A122" s="16"/>
-      <c r="B122" s="16"/>
-      <c r="C122" s="16"/>
+      <c r="A122" s="23"/>
+      <c r="B122" s="23"/>
+      <c r="C122" s="23"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="A123" s="16"/>
-      <c r="B123" s="16"/>
-      <c r="C123" s="16"/>
+      <c r="A123" s="23"/>
+      <c r="B123" s="23"/>
+      <c r="C123" s="23"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="A124" s="16"/>
-      <c r="B124" s="16"/>
-      <c r="C124" s="16"/>
+      <c r="A124" s="23"/>
+      <c r="B124" s="23"/>
+      <c r="C124" s="23"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="A125" s="16"/>
-      <c r="B125" s="16"/>
-      <c r="C125" s="16"/>
+      <c r="A125" s="23"/>
+      <c r="B125" s="23"/>
+      <c r="C125" s="23"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="A126" s="16"/>
-      <c r="B126" s="16"/>
-      <c r="C126" s="16"/>
+      <c r="A126" s="23"/>
+      <c r="B126" s="23"/>
+      <c r="C126" s="23"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="16"/>
-      <c r="B127" s="16"/>
-      <c r="C127" s="16"/>
+      <c r="A127" s="23"/>
+      <c r="B127" s="23"/>
+      <c r="C127" s="23"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="16"/>
-      <c r="B128" s="16"/>
-      <c r="C128" s="16"/>
+      <c r="A128" s="23"/>
+      <c r="B128" s="23"/>
+      <c r="C128" s="23"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="A129" s="16"/>
-      <c r="B129" s="16"/>
-      <c r="C129" s="16"/>
+      <c r="A129" s="23"/>
+      <c r="B129" s="23"/>
+      <c r="C129" s="23"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="A130" s="16"/>
-      <c r="B130" s="16"/>
-      <c r="C130" s="16"/>
+      <c r="A130" s="23"/>
+      <c r="B130" s="23"/>
+      <c r="C130" s="23"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="A131" s="16"/>
-      <c r="B131" s="16"/>
-      <c r="C131" s="16"/>
+      <c r="A131" s="23"/>
+      <c r="B131" s="23"/>
+      <c r="C131" s="23"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="A132" s="16"/>
-      <c r="B132" s="16"/>
-      <c r="C132" s="16"/>
+      <c r="A132" s="23"/>
+      <c r="B132" s="23"/>
+      <c r="C132" s="23"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="A133" s="16"/>
-      <c r="B133" s="16"/>
-      <c r="C133" s="16"/>
+      <c r="A133" s="23"/>
+      <c r="B133" s="23"/>
+      <c r="C133" s="23"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="A134" s="16"/>
-      <c r="B134" s="16"/>
-      <c r="C134" s="16"/>
+      <c r="A134" s="23"/>
+      <c r="B134" s="23"/>
+      <c r="C134" s="23"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="A135" s="16"/>
-      <c r="B135" s="16"/>
-      <c r="C135" s="16"/>
+      <c r="A135" s="23"/>
+      <c r="B135" s="23"/>
+      <c r="C135" s="23"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="A136" s="16"/>
-      <c r="B136" s="16"/>
-      <c r="C136" s="16"/>
+      <c r="A136" s="23"/>
+      <c r="B136" s="23"/>
+      <c r="C136" s="23"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="A137" s="16"/>
-      <c r="B137" s="16"/>
-      <c r="C137" s="16"/>
+      <c r="A137" s="23"/>
+      <c r="B137" s="23"/>
+      <c r="C137" s="23"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="A138" s="16"/>
-      <c r="B138" s="16"/>
-      <c r="C138" s="16"/>
+      <c r="A138" s="23"/>
+      <c r="B138" s="23"/>
+      <c r="C138" s="23"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="A139" s="16"/>
-      <c r="B139" s="16"/>
-      <c r="C139" s="16"/>
+      <c r="A139" s="23"/>
+      <c r="B139" s="23"/>
+      <c r="C139" s="23"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="A140" s="16"/>
-      <c r="B140" s="16"/>
-      <c r="C140" s="16"/>
+      <c r="A140" s="23"/>
+      <c r="B140" s="23"/>
+      <c r="C140" s="23"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="A141" s="16"/>
-      <c r="B141" s="16"/>
-      <c r="C141" s="16"/>
+      <c r="A141" s="23"/>
+      <c r="B141" s="23"/>
+      <c r="C141" s="23"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="A142" s="16"/>
-      <c r="B142" s="16"/>
-      <c r="C142" s="16"/>
+      <c r="A142" s="23"/>
+      <c r="B142" s="23"/>
+      <c r="C142" s="23"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="A143" s="16"/>
-      <c r="B143" s="16"/>
-      <c r="C143" s="16"/>
+      <c r="A143" s="23"/>
+      <c r="B143" s="23"/>
+      <c r="C143" s="23"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="A144" s="16"/>
-      <c r="B144" s="16"/>
-      <c r="C144" s="16"/>
+      <c r="A144" s="23"/>
+      <c r="B144" s="23"/>
+      <c r="C144" s="23"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="A145" s="16"/>
-      <c r="B145" s="16"/>
-      <c r="C145" s="16"/>
+      <c r="A145" s="23"/>
+      <c r="B145" s="23"/>
+      <c r="C145" s="23"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="A146" s="16"/>
-      <c r="B146" s="16"/>
-      <c r="C146" s="16"/>
+      <c r="A146" s="23"/>
+      <c r="B146" s="23"/>
+      <c r="C146" s="23"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="A147" s="16"/>
-      <c r="B147" s="16"/>
-      <c r="C147" s="16"/>
+      <c r="A147" s="23"/>
+      <c r="B147" s="23"/>
+      <c r="C147" s="23"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="16"/>
-      <c r="B148" s="16"/>
-      <c r="C148" s="16"/>
+      <c r="A148" s="23"/>
+      <c r="B148" s="23"/>
+      <c r="C148" s="23"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="A149" s="16"/>
-      <c r="B149" s="16"/>
-      <c r="C149" s="16"/>
+      <c r="A149" s="23"/>
+      <c r="B149" s="23"/>
+      <c r="C149" s="23"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="A150" s="16"/>
-      <c r="B150" s="16"/>
-      <c r="C150" s="16"/>
+      <c r="A150" s="23"/>
+      <c r="B150" s="23"/>
+      <c r="C150" s="23"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="A151" s="16"/>
-      <c r="B151" s="16"/>
-      <c r="C151" s="16"/>
+      <c r="A151" s="23"/>
+      <c r="B151" s="23"/>
+      <c r="C151" s="23"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="A152" s="16"/>
-      <c r="B152" s="16"/>
-      <c r="C152" s="16"/>
+      <c r="A152" s="23"/>
+      <c r="B152" s="23"/>
+      <c r="C152" s="23"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="A153" s="16"/>
-      <c r="B153" s="16"/>
-      <c r="C153" s="16"/>
+      <c r="A153" s="23"/>
+      <c r="B153" s="23"/>
+      <c r="C153" s="23"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="A154" s="16"/>
-      <c r="B154" s="16"/>
-      <c r="C154" s="16"/>
+      <c r="A154" s="23"/>
+      <c r="B154" s="23"/>
+      <c r="C154" s="23"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="A155" s="16"/>
-      <c r="B155" s="16"/>
-      <c r="C155" s="16"/>
+      <c r="A155" s="23"/>
+      <c r="B155" s="23"/>
+      <c r="C155" s="23"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="A156" s="16"/>
-      <c r="B156" s="16"/>
-      <c r="C156" s="16"/>
+      <c r="A156" s="23"/>
+      <c r="B156" s="23"/>
+      <c r="C156" s="23"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="A157" s="16"/>
-      <c r="B157" s="16"/>
-      <c r="C157" s="16"/>
+      <c r="A157" s="23"/>
+      <c r="B157" s="23"/>
+      <c r="C157" s="23"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="A158" s="16"/>
-      <c r="B158" s="16"/>
-      <c r="C158" s="16"/>
+      <c r="A158" s="23"/>
+      <c r="B158" s="23"/>
+      <c r="C158" s="23"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="A159" s="16"/>
-      <c r="B159" s="16"/>
-      <c r="C159" s="16"/>
+      <c r="A159" s="23"/>
+      <c r="B159" s="23"/>
+      <c r="C159" s="23"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="A160" s="16"/>
-      <c r="B160" s="16"/>
-      <c r="C160" s="16"/>
+      <c r="A160" s="23"/>
+      <c r="B160" s="23"/>
+      <c r="C160" s="23"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="A161" s="16"/>
-      <c r="B161" s="16"/>
-      <c r="C161" s="16"/>
+      <c r="A161" s="23"/>
+      <c r="B161" s="23"/>
+      <c r="C161" s="23"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="A162" s="16"/>
-      <c r="B162" s="16"/>
-      <c r="C162" s="16"/>
+      <c r="A162" s="23"/>
+      <c r="B162" s="23"/>
+      <c r="C162" s="23"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="A163" s="16"/>
-      <c r="B163" s="16"/>
-      <c r="C163" s="16"/>
+      <c r="A163" s="23"/>
+      <c r="B163" s="23"/>
+      <c r="C163" s="23"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="A164" s="16"/>
-      <c r="B164" s="16"/>
-      <c r="C164" s="16"/>
+      <c r="A164" s="23"/>
+      <c r="B164" s="23"/>
+      <c r="C164" s="23"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="A165" s="16"/>
-      <c r="B165" s="16"/>
-      <c r="C165" s="16"/>
+      <c r="A165" s="23"/>
+      <c r="B165" s="23"/>
+      <c r="C165" s="23"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="A166" s="16"/>
-      <c r="B166" s="16"/>
-      <c r="C166" s="16"/>
+      <c r="A166" s="23"/>
+      <c r="B166" s="23"/>
+      <c r="C166" s="23"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="A167" s="16"/>
-      <c r="B167" s="16"/>
-      <c r="C167" s="16"/>
+      <c r="A167" s="23"/>
+      <c r="B167" s="23"/>
+      <c r="C167" s="23"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="16"/>
-      <c r="B168" s="16"/>
-      <c r="C168" s="16"/>
+      <c r="A168" s="23"/>
+      <c r="B168" s="23"/>
+      <c r="C168" s="23"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="A169" s="16"/>
-      <c r="B169" s="16"/>
-      <c r="C169" s="16"/>
+      <c r="A169" s="23"/>
+      <c r="B169" s="23"/>
+      <c r="C169" s="23"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="A170" s="16"/>
-      <c r="B170" s="16"/>
-      <c r="C170" s="16"/>
+      <c r="A170" s="23"/>
+      <c r="B170" s="23"/>
+      <c r="C170" s="23"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="A171" s="16"/>
-      <c r="B171" s="16"/>
-      <c r="C171" s="16"/>
+      <c r="A171" s="23"/>
+      <c r="B171" s="23"/>
+      <c r="C171" s="23"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="A172" s="16"/>
-      <c r="B172" s="16"/>
-      <c r="C172" s="16"/>
+      <c r="A172" s="23"/>
+      <c r="B172" s="23"/>
+      <c r="C172" s="23"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="A173" s="16"/>
-      <c r="B173" s="16"/>
-      <c r="C173" s="16"/>
+      <c r="A173" s="23"/>
+      <c r="B173" s="23"/>
+      <c r="C173" s="23"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="A174" s="16"/>
-      <c r="B174" s="16"/>
-      <c r="C174" s="16"/>
+      <c r="A174" s="23"/>
+      <c r="B174" s="23"/>
+      <c r="C174" s="23"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="A175" s="16"/>
-      <c r="B175" s="16"/>
-      <c r="C175" s="16"/>
+      <c r="A175" s="23"/>
+      <c r="B175" s="23"/>
+      <c r="C175" s="23"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="A176" s="16"/>
-      <c r="B176" s="16"/>
-      <c r="C176" s="16"/>
+      <c r="A176" s="23"/>
+      <c r="B176" s="23"/>
+      <c r="C176" s="23"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="A177" s="16"/>
-      <c r="B177" s="16"/>
-      <c r="C177" s="16"/>
+      <c r="A177" s="23"/>
+      <c r="B177" s="23"/>
+      <c r="C177" s="23"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="16"/>
-      <c r="B178" s="16"/>
-      <c r="C178" s="16"/>
+      <c r="A178" s="23"/>
+      <c r="B178" s="23"/>
+      <c r="C178" s="23"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="A179" s="16"/>
-      <c r="B179" s="16"/>
-      <c r="C179" s="16"/>
+      <c r="A179" s="23"/>
+      <c r="B179" s="23"/>
+      <c r="C179" s="23"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="A180" s="16"/>
-      <c r="B180" s="16"/>
-      <c r="C180" s="16"/>
+      <c r="A180" s="23"/>
+      <c r="B180" s="23"/>
+      <c r="C180" s="23"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="A181" s="16"/>
-      <c r="B181" s="16"/>
-      <c r="C181" s="16"/>
+      <c r="A181" s="23"/>
+      <c r="B181" s="23"/>
+      <c r="C181" s="23"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="A182" s="16"/>
-      <c r="B182" s="16"/>
-      <c r="C182" s="16"/>
+      <c r="A182" s="23"/>
+      <c r="B182" s="23"/>
+      <c r="C182" s="23"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="A183" s="16"/>
-      <c r="B183" s="16"/>
-      <c r="C183" s="16"/>
+      <c r="A183" s="23"/>
+      <c r="B183" s="23"/>
+      <c r="C183" s="23"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="A184" s="16"/>
-      <c r="B184" s="16"/>
-      <c r="C184" s="16"/>
+      <c r="A184" s="23"/>
+      <c r="B184" s="23"/>
+      <c r="C184" s="23"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="A185" s="16"/>
-      <c r="B185" s="16"/>
-      <c r="C185" s="16"/>
+      <c r="A185" s="23"/>
+      <c r="B185" s="23"/>
+      <c r="C185" s="23"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="A186" s="16"/>
-      <c r="B186" s="16"/>
-      <c r="C186" s="16"/>
+      <c r="A186" s="23"/>
+      <c r="B186" s="23"/>
+      <c r="C186" s="23"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="A187" s="16"/>
-      <c r="B187" s="16"/>
-      <c r="C187" s="16"/>
+      <c r="A187" s="23"/>
+      <c r="B187" s="23"/>
+      <c r="C187" s="23"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="16"/>
-      <c r="B188" s="16"/>
-      <c r="C188" s="16"/>
+      <c r="A188" s="23"/>
+      <c r="B188" s="23"/>
+      <c r="C188" s="23"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="A189" s="16"/>
-      <c r="B189" s="16"/>
-      <c r="C189" s="16"/>
+      <c r="A189" s="23"/>
+      <c r="B189" s="23"/>
+      <c r="C189" s="23"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="A190" s="16"/>
-      <c r="B190" s="16"/>
-      <c r="C190" s="16"/>
+      <c r="A190" s="23"/>
+      <c r="B190" s="23"/>
+      <c r="C190" s="23"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="A191" s="16"/>
-      <c r="B191" s="16"/>
-      <c r="C191" s="16"/>
+      <c r="A191" s="23"/>
+      <c r="B191" s="23"/>
+      <c r="C191" s="23"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="A192" s="16"/>
-      <c r="B192" s="16"/>
-      <c r="C192" s="16"/>
+      <c r="A192" s="23"/>
+      <c r="B192" s="23"/>
+      <c r="C192" s="23"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="A193" s="16"/>
-      <c r="B193" s="16"/>
-      <c r="C193" s="16"/>
+      <c r="A193" s="23"/>
+      <c r="B193" s="23"/>
+      <c r="C193" s="23"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="A194" s="16"/>
-      <c r="B194" s="16"/>
-      <c r="C194" s="16"/>
+      <c r="A194" s="23"/>
+      <c r="B194" s="23"/>
+      <c r="C194" s="23"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="A195" s="16"/>
-      <c r="B195" s="16"/>
-      <c r="C195" s="16"/>
+      <c r="A195" s="23"/>
+      <c r="B195" s="23"/>
+      <c r="C195" s="23"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="A196" s="16"/>
-      <c r="B196" s="16"/>
-      <c r="C196" s="16"/>
+      <c r="A196" s="23"/>
+      <c r="B196" s="23"/>
+      <c r="C196" s="23"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="A197" s="16"/>
-      <c r="B197" s="16"/>
-      <c r="C197" s="16"/>
+      <c r="A197" s="23"/>
+      <c r="B197" s="23"/>
+      <c r="C197" s="23"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="A198" s="16"/>
-      <c r="B198" s="16"/>
-      <c r="C198" s="16"/>
+      <c r="A198" s="23"/>
+      <c r="B198" s="23"/>
+      <c r="C198" s="23"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="A199" s="16"/>
-      <c r="B199" s="16"/>
-      <c r="C199" s="16"/>
+      <c r="A199" s="23"/>
+      <c r="B199" s="23"/>
+      <c r="C199" s="23"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="A200" s="16"/>
-      <c r="B200" s="16"/>
-      <c r="C200" s="16"/>
+      <c r="A200" s="23"/>
+      <c r="B200" s="23"/>
+      <c r="C200" s="23"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="A201" s="16"/>
-      <c r="B201" s="16"/>
-      <c r="C201" s="16"/>
+      <c r="A201" s="23"/>
+      <c r="B201" s="23"/>
+      <c r="C201" s="23"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="A202" s="16"/>
-      <c r="B202" s="16"/>
-      <c r="C202" s="16"/>
+      <c r="A202" s="23"/>
+      <c r="B202" s="23"/>
+      <c r="C202" s="23"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="A203" s="16"/>
-      <c r="B203" s="16"/>
-      <c r="C203" s="16"/>
+      <c r="A203" s="23"/>
+      <c r="B203" s="23"/>
+      <c r="C203" s="23"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="A204" s="16"/>
-      <c r="B204" s="16"/>
-      <c r="C204" s="16"/>
+      <c r="A204" s="23"/>
+      <c r="B204" s="23"/>
+      <c r="C204" s="23"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="A205" s="16"/>
-      <c r="B205" s="16"/>
-      <c r="C205" s="16"/>
+      <c r="A205" s="23"/>
+      <c r="B205" s="23"/>
+      <c r="C205" s="23"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="A206" s="16"/>
-      <c r="B206" s="16"/>
-      <c r="C206" s="16"/>
+      <c r="A206" s="23"/>
+      <c r="B206" s="23"/>
+      <c r="C206" s="23"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="A207" s="16"/>
-      <c r="B207" s="16"/>
-      <c r="C207" s="16"/>
+      <c r="A207" s="23"/>
+      <c r="B207" s="23"/>
+      <c r="C207" s="23"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="16"/>
-      <c r="B208" s="16"/>
-      <c r="C208" s="16"/>
+      <c r="A208" s="23"/>
+      <c r="B208" s="23"/>
+      <c r="C208" s="23"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="A209" s="16"/>
-      <c r="B209" s="16"/>
-      <c r="C209" s="16"/>
+      <c r="A209" s="23"/>
+      <c r="B209" s="23"/>
+      <c r="C209" s="23"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="A210" s="16"/>
-      <c r="B210" s="16"/>
-      <c r="C210" s="16"/>
+      <c r="A210" s="23"/>
+      <c r="B210" s="23"/>
+      <c r="C210" s="23"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="A211" s="16"/>
-      <c r="B211" s="16"/>
-      <c r="C211" s="16"/>
+      <c r="A211" s="23"/>
+      <c r="B211" s="23"/>
+      <c r="C211" s="23"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="A212" s="16"/>
-      <c r="B212" s="16"/>
-      <c r="C212" s="16"/>
+      <c r="A212" s="23"/>
+      <c r="B212" s="23"/>
+      <c r="C212" s="23"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="A213" s="16"/>
-      <c r="B213" s="16"/>
-      <c r="C213" s="16"/>
+      <c r="A213" s="23"/>
+      <c r="B213" s="23"/>
+      <c r="C213" s="23"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="A214" s="16"/>
-      <c r="B214" s="16"/>
-      <c r="C214" s="16"/>
+      <c r="A214" s="23"/>
+      <c r="B214" s="23"/>
+      <c r="C214" s="23"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="A215" s="16"/>
-      <c r="B215" s="16"/>
-      <c r="C215" s="16"/>
+      <c r="A215" s="23"/>
+      <c r="B215" s="23"/>
+      <c r="C215" s="23"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="A216" s="16"/>
-      <c r="B216" s="16"/>
-      <c r="C216" s="16"/>
+      <c r="A216" s="23"/>
+      <c r="B216" s="23"/>
+      <c r="C216" s="23"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="A217" s="16"/>
-      <c r="B217" s="16"/>
-      <c r="C217" s="16"/>
+      <c r="A217" s="23"/>
+      <c r="B217" s="23"/>
+      <c r="C217" s="23"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="A218" s="16"/>
-      <c r="B218" s="16"/>
-      <c r="C218" s="16"/>
+      <c r="A218" s="23"/>
+      <c r="B218" s="23"/>
+      <c r="C218" s="23"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="A219" s="16"/>
-      <c r="B219" s="16"/>
-      <c r="C219" s="16"/>
+      <c r="A219" s="23"/>
+      <c r="B219" s="23"/>
+      <c r="C219" s="23"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="A220" s="16"/>
-      <c r="B220" s="16"/>
-      <c r="C220" s="16"/>
+      <c r="A220" s="23"/>
+      <c r="B220" s="23"/>
+      <c r="C220" s="23"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="A221" s="16"/>
-      <c r="B221" s="16"/>
-      <c r="C221" s="16"/>
+      <c r="A221" s="23"/>
+      <c r="B221" s="23"/>
+      <c r="C221" s="23"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="A222" s="16"/>
-      <c r="B222" s="16"/>
-      <c r="C222" s="16"/>
+      <c r="A222" s="23"/>
+      <c r="B222" s="23"/>
+      <c r="C222" s="23"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="A223" s="16"/>
-      <c r="B223" s="16"/>
-      <c r="C223" s="16"/>
+      <c r="A223" s="23"/>
+      <c r="B223" s="23"/>
+      <c r="C223" s="23"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="A224" s="16"/>
-      <c r="B224" s="16"/>
-      <c r="C224" s="16"/>
+      <c r="A224" s="23"/>
+      <c r="B224" s="23"/>
+      <c r="C224" s="23"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="A225" s="16"/>
-      <c r="B225" s="16"/>
-      <c r="C225" s="16"/>
+      <c r="A225" s="23"/>
+      <c r="B225" s="23"/>
+      <c r="C225" s="23"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="16"/>
-      <c r="B226" s="16"/>
-      <c r="C226" s="16"/>
+      <c r="A226" s="23"/>
+      <c r="B226" s="23"/>
+      <c r="C226" s="23"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="16"/>
-      <c r="B227" s="16"/>
-      <c r="C227" s="16"/>
+      <c r="A227" s="23"/>
+      <c r="B227" s="23"/>
+      <c r="C227" s="23"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="16"/>
-      <c r="B228" s="16"/>
-      <c r="C228" s="16"/>
+      <c r="A228" s="23"/>
+      <c r="B228" s="23"/>
+      <c r="C228" s="23"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="16"/>
-      <c r="B229" s="16"/>
-      <c r="C229" s="16"/>
+      <c r="A229" s="23"/>
+      <c r="B229" s="23"/>
+      <c r="C229" s="23"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="16"/>
-      <c r="B230" s="16"/>
-      <c r="C230" s="16"/>
+      <c r="A230" s="23"/>
+      <c r="B230" s="23"/>
+      <c r="C230" s="23"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="A231" s="16"/>
-      <c r="B231" s="16"/>
-      <c r="C231" s="16"/>
+      <c r="A231" s="23"/>
+      <c r="B231" s="23"/>
+      <c r="C231" s="23"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="A232" s="16"/>
-      <c r="B232" s="16"/>
-      <c r="C232" s="16"/>
+      <c r="A232" s="23"/>
+      <c r="B232" s="23"/>
+      <c r="C232" s="23"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="A233" s="16"/>
-      <c r="B233" s="16"/>
-      <c r="C233" s="16"/>
+      <c r="A233" s="23"/>
+      <c r="B233" s="23"/>
+      <c r="C233" s="23"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="A234" s="16"/>
-      <c r="B234" s="16"/>
-      <c r="C234" s="16"/>
+      <c r="A234" s="23"/>
+      <c r="B234" s="23"/>
+      <c r="C234" s="23"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="A235" s="16"/>
-      <c r="B235" s="16"/>
-      <c r="C235" s="16"/>
+      <c r="A235" s="23"/>
+      <c r="B235" s="23"/>
+      <c r="C235" s="23"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="A236" s="16"/>
-      <c r="B236" s="16"/>
-      <c r="C236" s="16"/>
+      <c r="A236" s="23"/>
+      <c r="B236" s="23"/>
+      <c r="C236" s="23"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="A237" s="16"/>
-      <c r="B237" s="16"/>
-      <c r="C237" s="16"/>
+      <c r="A237" s="23"/>
+      <c r="B237" s="23"/>
+      <c r="C237" s="23"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="A238" s="16"/>
-      <c r="B238" s="16"/>
-      <c r="C238" s="16"/>
+      <c r="A238" s="23"/>
+      <c r="B238" s="23"/>
+      <c r="C238" s="23"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="A239" s="16"/>
-      <c r="B239" s="16"/>
-      <c r="C239" s="16"/>
+      <c r="A239" s="23"/>
+      <c r="B239" s="23"/>
+      <c r="C239" s="23"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="A240" s="16"/>
-      <c r="B240" s="16"/>
-      <c r="C240" s="16"/>
+      <c r="A240" s="23"/>
+      <c r="B240" s="23"/>
+      <c r="C240" s="23"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="A241" s="16"/>
-      <c r="B241" s="16"/>
-      <c r="C241" s="16"/>
+      <c r="A241" s="23"/>
+      <c r="B241" s="23"/>
+      <c r="C241" s="23"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="A242" s="16"/>
-      <c r="B242" s="16"/>
-      <c r="C242" s="16"/>
+      <c r="A242" s="23"/>
+      <c r="B242" s="23"/>
+      <c r="C242" s="23"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="A243" s="16"/>
-      <c r="B243" s="16"/>
-      <c r="C243" s="16"/>
+      <c r="A243" s="23"/>
+      <c r="B243" s="23"/>
+      <c r="C243" s="23"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="A244" s="16"/>
-      <c r="B244" s="16"/>
-      <c r="C244" s="16"/>
+      <c r="A244" s="23"/>
+      <c r="B244" s="23"/>
+      <c r="C244" s="23"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="A245" s="16"/>
-      <c r="B245" s="16"/>
-      <c r="C245" s="16"/>
+      <c r="A245" s="23"/>
+      <c r="B245" s="23"/>
+      <c r="C245" s="23"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="A246" s="16"/>
-      <c r="B246" s="16"/>
-      <c r="C246" s="16"/>
+      <c r="A246" s="23"/>
+      <c r="B246" s="23"/>
+      <c r="C246" s="23"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="A247" s="16"/>
-      <c r="B247" s="16"/>
-      <c r="C247" s="16"/>
+      <c r="A247" s="23"/>
+      <c r="B247" s="23"/>
+      <c r="C247" s="23"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="16"/>
-      <c r="B248" s="16"/>
-      <c r="C248" s="16"/>
+      <c r="A248" s="23"/>
+      <c r="B248" s="23"/>
+      <c r="C248" s="23"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="A249" s="16"/>
-      <c r="B249" s="16"/>
-      <c r="C249" s="16"/>
+      <c r="A249" s="23"/>
+      <c r="B249" s="23"/>
+      <c r="C249" s="23"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="A250" s="16"/>
-      <c r="B250" s="16"/>
-      <c r="C250" s="16"/>
+      <c r="A250" s="23"/>
+      <c r="B250" s="23"/>
+      <c r="C250" s="23"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="A251" s="16"/>
-      <c r="B251" s="16"/>
-      <c r="C251" s="16"/>
+      <c r="A251" s="23"/>
+      <c r="B251" s="23"/>
+      <c r="C251" s="23"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="A252" s="16"/>
-      <c r="B252" s="16"/>
-      <c r="C252" s="16"/>
+      <c r="A252" s="23"/>
+      <c r="B252" s="23"/>
+      <c r="C252" s="23"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="A253" s="16"/>
-      <c r="B253" s="16"/>
-      <c r="C253" s="16"/>
+      <c r="A253" s="23"/>
+      <c r="B253" s="23"/>
+      <c r="C253" s="23"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="A254" s="16"/>
-      <c r="B254" s="16"/>
-      <c r="C254" s="16"/>
+      <c r="A254" s="23"/>
+      <c r="B254" s="23"/>
+      <c r="C254" s="23"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="A255" s="16"/>
-      <c r="B255" s="16"/>
-      <c r="C255" s="16"/>
+      <c r="A255" s="23"/>
+      <c r="B255" s="23"/>
+      <c r="C255" s="23"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="A256" s="16"/>
-      <c r="B256" s="16"/>
-      <c r="C256" s="16"/>
+      <c r="A256" s="23"/>
+      <c r="B256" s="23"/>
+      <c r="C256" s="23"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="A257" s="16"/>
-      <c r="B257" s="16"/>
-      <c r="C257" s="16"/>
+      <c r="A257" s="23"/>
+      <c r="B257" s="23"/>
+      <c r="C257" s="23"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="A258" s="16"/>
-      <c r="B258" s="16"/>
-      <c r="C258" s="16"/>
+      <c r="A258" s="23"/>
+      <c r="B258" s="23"/>
+      <c r="C258" s="23"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="A259" s="16"/>
-      <c r="B259" s="16"/>
-      <c r="C259" s="16"/>
+      <c r="A259" s="23"/>
+      <c r="B259" s="23"/>
+      <c r="C259" s="23"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="A260" s="16"/>
-      <c r="B260" s="16"/>
-      <c r="C260" s="16"/>
+      <c r="A260" s="23"/>
+      <c r="B260" s="23"/>
+      <c r="C260" s="23"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="A261" s="16"/>
-      <c r="B261" s="16"/>
-      <c r="C261" s="16"/>
+      <c r="A261" s="23"/>
+      <c r="B261" s="23"/>
+      <c r="C261" s="23"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="A262" s="16"/>
-      <c r="B262" s="16"/>
-      <c r="C262" s="16"/>
+      <c r="A262" s="23"/>
+      <c r="B262" s="23"/>
+      <c r="C262" s="23"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="A263" s="16"/>
-      <c r="B263" s="16"/>
-      <c r="C263" s="16"/>
+      <c r="A263" s="23"/>
+      <c r="B263" s="23"/>
+      <c r="C263" s="23"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="A264" s="16"/>
-      <c r="B264" s="16"/>
-      <c r="C264" s="16"/>
+      <c r="A264" s="23"/>
+      <c r="B264" s="23"/>
+      <c r="C264" s="23"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="A265" s="16"/>
-      <c r="B265" s="16"/>
-      <c r="C265" s="16"/>
+      <c r="A265" s="23"/>
+      <c r="B265" s="23"/>
+      <c r="C265" s="23"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="A266" s="16"/>
-      <c r="B266" s="16"/>
-      <c r="C266" s="16"/>
+      <c r="A266" s="23"/>
+      <c r="B266" s="23"/>
+      <c r="C266" s="23"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="A267" s="16"/>
-      <c r="B267" s="16"/>
-      <c r="C267" s="16"/>
+      <c r="A267" s="23"/>
+      <c r="B267" s="23"/>
+      <c r="C267" s="23"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="16"/>
-      <c r="B268" s="16"/>
-      <c r="C268" s="16"/>
+      <c r="A268" s="23"/>
+      <c r="B268" s="23"/>
+      <c r="C268" s="23"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="A269" s="16"/>
-      <c r="B269" s="16"/>
-      <c r="C269" s="16"/>
+      <c r="A269" s="23"/>
+      <c r="B269" s="23"/>
+      <c r="C269" s="23"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="A270" s="16"/>
-      <c r="B270" s="16"/>
-      <c r="C270" s="16"/>
+      <c r="A270" s="23"/>
+      <c r="B270" s="23"/>
+      <c r="C270" s="23"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="A271" s="16"/>
-      <c r="B271" s="16"/>
-      <c r="C271" s="16"/>
+      <c r="A271" s="23"/>
+      <c r="B271" s="23"/>
+      <c r="C271" s="23"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="A272" s="16"/>
-      <c r="B272" s="16"/>
-      <c r="C272" s="16"/>
+      <c r="A272" s="23"/>
+      <c r="B272" s="23"/>
+      <c r="C272" s="23"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="A273" s="16"/>
-      <c r="B273" s="16"/>
-      <c r="C273" s="16"/>
+      <c r="A273" s="23"/>
+      <c r="B273" s="23"/>
+      <c r="C273" s="23"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="A274" s="16"/>
-      <c r="B274" s="16"/>
-      <c r="C274" s="16"/>
+      <c r="A274" s="23"/>
+      <c r="B274" s="23"/>
+      <c r="C274" s="23"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="A275" s="16"/>
-      <c r="B275" s="16"/>
-      <c r="C275" s="16"/>
+      <c r="A275" s="23"/>
+      <c r="B275" s="23"/>
+      <c r="C275" s="23"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="A276" s="16"/>
-      <c r="B276" s="16"/>
-      <c r="C276" s="16"/>
+      <c r="A276" s="23"/>
+      <c r="B276" s="23"/>
+      <c r="C276" s="23"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="A277" s="16"/>
-      <c r="B277" s="16"/>
-      <c r="C277" s="16"/>
+      <c r="A277" s="23"/>
+      <c r="B277" s="23"/>
+      <c r="C277" s="23"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="A278" s="16"/>
-      <c r="B278" s="16"/>
-      <c r="C278" s="16"/>
+      <c r="A278" s="23"/>
+      <c r="B278" s="23"/>
+      <c r="C278" s="23"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="A279" s="16"/>
-      <c r="B279" s="16"/>
-      <c r="C279" s="16"/>
+      <c r="A279" s="23"/>
+      <c r="B279" s="23"/>
+      <c r="C279" s="23"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="A280" s="16"/>
-      <c r="B280" s="16"/>
-      <c r="C280" s="16"/>
+      <c r="A280" s="23"/>
+      <c r="B280" s="23"/>
+      <c r="C280" s="23"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="A281" s="16"/>
-      <c r="B281" s="16"/>
-      <c r="C281" s="16"/>
+      <c r="A281" s="23"/>
+      <c r="B281" s="23"/>
+      <c r="C281" s="23"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="A282" s="16"/>
-      <c r="B282" s="16"/>
-      <c r="C282" s="16"/>
+      <c r="A282" s="23"/>
+      <c r="B282" s="23"/>
+      <c r="C282" s="23"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="A283" s="16"/>
-      <c r="B283" s="16"/>
-      <c r="C283" s="16"/>
+      <c r="A283" s="23"/>
+      <c r="B283" s="23"/>
+      <c r="C283" s="23"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="A284" s="16"/>
-      <c r="B284" s="16"/>
-      <c r="C284" s="16"/>
+      <c r="A284" s="23"/>
+      <c r="B284" s="23"/>
+      <c r="C284" s="23"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="A285" s="16"/>
-      <c r="B285" s="16"/>
-      <c r="C285" s="16"/>
+      <c r="A285" s="23"/>
+      <c r="B285" s="23"/>
+      <c r="C285" s="23"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="A286" s="16"/>
-      <c r="B286" s="16"/>
-      <c r="C286" s="16"/>
+      <c r="A286" s="23"/>
+      <c r="B286" s="23"/>
+      <c r="C286" s="23"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="A287" s="16"/>
-      <c r="B287" s="16"/>
-      <c r="C287" s="16"/>
+      <c r="A287" s="23"/>
+      <c r="B287" s="23"/>
+      <c r="C287" s="23"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="16"/>
-      <c r="B288" s="16"/>
-      <c r="C288" s="16"/>
+      <c r="A288" s="23"/>
+      <c r="B288" s="23"/>
+      <c r="C288" s="23"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="A289" s="16"/>
-      <c r="B289" s="16"/>
-      <c r="C289" s="16"/>
+      <c r="A289" s="23"/>
+      <c r="B289" s="23"/>
+      <c r="C289" s="23"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="A290" s="16"/>
-      <c r="B290" s="16"/>
-      <c r="C290" s="16"/>
+      <c r="A290" s="23"/>
+      <c r="B290" s="23"/>
+      <c r="C290" s="23"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="A291" s="16"/>
-      <c r="B291" s="16"/>
-      <c r="C291" s="16"/>
+      <c r="A291" s="23"/>
+      <c r="B291" s="23"/>
+      <c r="C291" s="23"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="A292" s="16"/>
-      <c r="B292" s="16"/>
-      <c r="C292" s="16"/>
+      <c r="A292" s="23"/>
+      <c r="B292" s="23"/>
+      <c r="C292" s="23"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="A293" s="16"/>
-      <c r="B293" s="16"/>
-      <c r="C293" s="16"/>
+      <c r="A293" s="23"/>
+      <c r="B293" s="23"/>
+      <c r="C293" s="23"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="A294" s="16"/>
-      <c r="B294" s="16"/>
-      <c r="C294" s="16"/>
+      <c r="A294" s="23"/>
+      <c r="B294" s="23"/>
+      <c r="C294" s="23"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="A295" s="16"/>
-      <c r="B295" s="16"/>
-      <c r="C295" s="16"/>
+      <c r="A295" s="23"/>
+      <c r="B295" s="23"/>
+      <c r="C295" s="23"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="A296" s="16"/>
-      <c r="B296" s="16"/>
-      <c r="C296" s="16"/>
+      <c r="A296" s="23"/>
+      <c r="B296" s="23"/>
+      <c r="C296" s="23"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="A297" s="16"/>
-      <c r="B297" s="16"/>
-      <c r="C297" s="16"/>
+      <c r="A297" s="23"/>
+      <c r="B297" s="23"/>
+      <c r="C297" s="23"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="A298" s="16"/>
-      <c r="B298" s="16"/>
-      <c r="C298" s="16"/>
+      <c r="A298" s="23"/>
+      <c r="B298" s="23"/>
+      <c r="C298" s="23"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="A299" s="16"/>
-      <c r="B299" s="16"/>
-      <c r="C299" s="16"/>
+      <c r="A299" s="23"/>
+      <c r="B299" s="23"/>
+      <c r="C299" s="23"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="A300" s="16"/>
-      <c r="B300" s="16"/>
-      <c r="C300" s="16"/>
+      <c r="A300" s="23"/>
+      <c r="B300" s="23"/>
+      <c r="C300" s="23"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="A301" s="16"/>
-      <c r="B301" s="16"/>
-      <c r="C301" s="16"/>
+      <c r="A301" s="23"/>
+      <c r="B301" s="23"/>
+      <c r="C301" s="23"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="A302" s="16"/>
-      <c r="B302" s="16"/>
-      <c r="C302" s="16"/>
+      <c r="A302" s="23"/>
+      <c r="B302" s="23"/>
+      <c r="C302" s="23"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="A303" s="16"/>
-      <c r="B303" s="16"/>
-      <c r="C303" s="16"/>
+      <c r="A303" s="23"/>
+      <c r="B303" s="23"/>
+      <c r="C303" s="23"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="A304" s="16"/>
-      <c r="B304" s="16"/>
-      <c r="C304" s="16"/>
+      <c r="A304" s="23"/>
+      <c r="B304" s="23"/>
+      <c r="C304" s="23"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="A305" s="16"/>
-      <c r="B305" s="16"/>
-      <c r="C305" s="16"/>
+      <c r="A305" s="23"/>
+      <c r="B305" s="23"/>
+      <c r="C305" s="23"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="A306" s="16"/>
-      <c r="B306" s="16"/>
-      <c r="C306" s="16"/>
+      <c r="A306" s="23"/>
+      <c r="B306" s="23"/>
+      <c r="C306" s="23"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="A307" s="16"/>
-      <c r="B307" s="16"/>
-      <c r="C307" s="16"/>
+      <c r="A307" s="23"/>
+      <c r="B307" s="23"/>
+      <c r="C307" s="23"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="16"/>
-      <c r="B308" s="16"/>
-      <c r="C308" s="16"/>
+      <c r="A308" s="23"/>
+      <c r="B308" s="23"/>
+      <c r="C308" s="23"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="A309" s="16"/>
-      <c r="B309" s="16"/>
-      <c r="C309" s="16"/>
+      <c r="A309" s="23"/>
+      <c r="B309" s="23"/>
+      <c r="C309" s="23"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="A310" s="16"/>
-      <c r="B310" s="16"/>
-      <c r="C310" s="16"/>
+      <c r="A310" s="23"/>
+      <c r="B310" s="23"/>
+      <c r="C310" s="23"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="A311" s="16"/>
-      <c r="B311" s="16"/>
-      <c r="C311" s="16"/>
+      <c r="A311" s="23"/>
+      <c r="B311" s="23"/>
+      <c r="C311" s="23"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="A312" s="16"/>
-      <c r="B312" s="16"/>
-      <c r="C312" s="16"/>
+      <c r="A312" s="23"/>
+      <c r="B312" s="23"/>
+      <c r="C312" s="23"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="A313" s="16"/>
-      <c r="B313" s="16"/>
-      <c r="C313" s="16"/>
+      <c r="A313" s="23"/>
+      <c r="B313" s="23"/>
+      <c r="C313" s="23"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="A314" s="16"/>
-      <c r="B314" s="16"/>
-      <c r="C314" s="16"/>
+      <c r="A314" s="23"/>
+      <c r="B314" s="23"/>
+      <c r="C314" s="23"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="A315" s="16"/>
-      <c r="B315" s="16"/>
-      <c r="C315" s="16"/>
+      <c r="A315" s="23"/>
+      <c r="B315" s="23"/>
+      <c r="C315" s="23"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="A316" s="16"/>
-      <c r="B316" s="16"/>
-      <c r="C316" s="16"/>
+      <c r="A316" s="23"/>
+      <c r="B316" s="23"/>
+      <c r="C316" s="23"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="A317" s="16"/>
-      <c r="B317" s="16"/>
-      <c r="C317" s="16"/>
+      <c r="A317" s="23"/>
+      <c r="B317" s="23"/>
+      <c r="C317" s="23"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="A318" s="16"/>
-      <c r="B318" s="16"/>
-      <c r="C318" s="16"/>
+      <c r="A318" s="23"/>
+      <c r="B318" s="23"/>
+      <c r="C318" s="23"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="A319" s="16"/>
-      <c r="B319" s="16"/>
-      <c r="C319" s="16"/>
+      <c r="A319" s="23"/>
+      <c r="B319" s="23"/>
+      <c r="C319" s="23"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="A320" s="16"/>
-      <c r="B320" s="16"/>
-      <c r="C320" s="16"/>
+      <c r="A320" s="23"/>
+      <c r="B320" s="23"/>
+      <c r="C320" s="23"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="A321" s="16"/>
-      <c r="B321" s="16"/>
-      <c r="C321" s="16"/>
+      <c r="A321" s="23"/>
+      <c r="B321" s="23"/>
+      <c r="C321" s="23"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="A322" s="16"/>
-      <c r="B322" s="16"/>
-      <c r="C322" s="16"/>
+      <c r="A322" s="23"/>
+      <c r="B322" s="23"/>
+      <c r="C322" s="23"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="A323" s="16"/>
-      <c r="B323" s="16"/>
-      <c r="C323" s="16"/>
+      <c r="A323" s="23"/>
+      <c r="B323" s="23"/>
+      <c r="C323" s="23"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="A324" s="16"/>
-      <c r="B324" s="16"/>
-      <c r="C324" s="16"/>
+      <c r="A324" s="23"/>
+      <c r="B324" s="23"/>
+      <c r="C324" s="23"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="A325" s="16"/>
-      <c r="B325" s="16"/>
-      <c r="C325" s="16"/>
+      <c r="A325" s="23"/>
+      <c r="B325" s="23"/>
+      <c r="C325" s="23"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="A326" s="16"/>
-      <c r="B326" s="16"/>
-      <c r="C326" s="16"/>
+      <c r="A326" s="23"/>
+      <c r="B326" s="23"/>
+      <c r="C326" s="23"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="A327" s="16"/>
-      <c r="B327" s="16"/>
-      <c r="C327" s="16"/>
+      <c r="A327" s="23"/>
+      <c r="B327" s="23"/>
+      <c r="C327" s="23"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="16"/>
-      <c r="B328" s="16"/>
-      <c r="C328" s="16"/>
+      <c r="A328" s="23"/>
+      <c r="B328" s="23"/>
+      <c r="C328" s="23"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="A329" s="16"/>
-      <c r="B329" s="16"/>
-      <c r="C329" s="16"/>
+      <c r="A329" s="23"/>
+      <c r="B329" s="23"/>
+      <c r="C329" s="23"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="A330" s="16"/>
-      <c r="B330" s="16"/>
-      <c r="C330" s="16"/>
+      <c r="A330" s="23"/>
+      <c r="B330" s="23"/>
+      <c r="C330" s="23"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="A331" s="16"/>
-      <c r="B331" s="16"/>
-      <c r="C331" s="16"/>
+      <c r="A331" s="23"/>
+      <c r="B331" s="23"/>
+      <c r="C331" s="23"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="A332" s="16"/>
-      <c r="B332" s="16"/>
-      <c r="C332" s="16"/>
+      <c r="A332" s="23"/>
+      <c r="B332" s="23"/>
+      <c r="C332" s="23"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="A333" s="16"/>
-      <c r="B333" s="16"/>
-      <c r="C333" s="16"/>
+      <c r="A333" s="23"/>
+      <c r="B333" s="23"/>
+      <c r="C333" s="23"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="A334" s="16"/>
-      <c r="B334" s="16"/>
-      <c r="C334" s="16"/>
+      <c r="A334" s="23"/>
+      <c r="B334" s="23"/>
+      <c r="C334" s="23"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="A335" s="16"/>
-      <c r="B335" s="16"/>
-      <c r="C335" s="16"/>
+      <c r="A335" s="23"/>
+      <c r="B335" s="23"/>
+      <c r="C335" s="23"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="A336" s="16"/>
-      <c r="B336" s="16"/>
-      <c r="C336" s="16"/>
+      <c r="A336" s="23"/>
+      <c r="B336" s="23"/>
+      <c r="C336" s="23"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="A337" s="16"/>
-      <c r="B337" s="16"/>
-      <c r="C337" s="16"/>
+      <c r="A337" s="23"/>
+      <c r="B337" s="23"/>
+      <c r="C337" s="23"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="A338" s="16"/>
-      <c r="B338" s="16"/>
-      <c r="C338" s="16"/>
+      <c r="A338" s="23"/>
+      <c r="B338" s="23"/>
+      <c r="C338" s="23"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="A339" s="16"/>
-      <c r="B339" s="16"/>
-      <c r="C339" s="16"/>
+      <c r="A339" s="23"/>
+      <c r="B339" s="23"/>
+      <c r="C339" s="23"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="A340" s="16"/>
-      <c r="B340" s="16"/>
-      <c r="C340" s="16"/>
+      <c r="A340" s="23"/>
+      <c r="B340" s="23"/>
+      <c r="C340" s="23"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="A341" s="16"/>
-      <c r="B341" s="16"/>
-      <c r="C341" s="16"/>
+      <c r="A341" s="23"/>
+      <c r="B341" s="23"/>
+      <c r="C341" s="23"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="A342" s="16"/>
-      <c r="B342" s="16"/>
-      <c r="C342" s="16"/>
+      <c r="A342" s="23"/>
+      <c r="B342" s="23"/>
+      <c r="C342" s="23"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="A343" s="16"/>
-      <c r="B343" s="16"/>
-      <c r="C343" s="16"/>
+      <c r="A343" s="23"/>
+      <c r="B343" s="23"/>
+      <c r="C343" s="23"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="A344" s="16"/>
-      <c r="B344" s="16"/>
-      <c r="C344" s="16"/>
+      <c r="A344" s="23"/>
+      <c r="B344" s="23"/>
+      <c r="C344" s="23"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="A345" s="16"/>
-      <c r="B345" s="16"/>
-      <c r="C345" s="16"/>
+      <c r="A345" s="23"/>
+      <c r="B345" s="23"/>
+      <c r="C345" s="23"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="A346" s="16"/>
-      <c r="B346" s="16"/>
-      <c r="C346" s="16"/>
+      <c r="A346" s="23"/>
+      <c r="B346" s="23"/>
+      <c r="C346" s="23"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="A347" s="16"/>
-      <c r="B347" s="16"/>
-      <c r="C347" s="16"/>
+      <c r="A347" s="23"/>
+      <c r="B347" s="23"/>
+      <c r="C347" s="23"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="16"/>
-      <c r="B348" s="16"/>
-      <c r="C348" s="16"/>
+      <c r="A348" s="23"/>
+      <c r="B348" s="23"/>
+      <c r="C348" s="23"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="A349" s="16"/>
-      <c r="B349" s="16"/>
-      <c r="C349" s="16"/>
+      <c r="A349" s="23"/>
+      <c r="B349" s="23"/>
+      <c r="C349" s="23"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="A350" s="16"/>
-      <c r="B350" s="16"/>
-      <c r="C350" s="16"/>
+      <c r="A350" s="23"/>
+      <c r="B350" s="23"/>
+      <c r="C350" s="23"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="A351" s="16"/>
-      <c r="B351" s="16"/>
-      <c r="C351" s="16"/>
+      <c r="A351" s="23"/>
+      <c r="B351" s="23"/>
+      <c r="C351" s="23"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="A352" s="16"/>
-      <c r="B352" s="16"/>
-      <c r="C352" s="16"/>
+      <c r="A352" s="23"/>
+      <c r="B352" s="23"/>
+      <c r="C352" s="23"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="A353" s="16"/>
-      <c r="B353" s="16"/>
-      <c r="C353" s="16"/>
+      <c r="A353" s="23"/>
+      <c r="B353" s="23"/>
+      <c r="C353" s="23"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="A354" s="16"/>
-      <c r="B354" s="16"/>
-      <c r="C354" s="16"/>
+      <c r="A354" s="23"/>
+      <c r="B354" s="23"/>
+      <c r="C354" s="23"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="A355" s="16"/>
-      <c r="B355" s="16"/>
-      <c r="C355" s="16"/>
+      <c r="A355" s="23"/>
+      <c r="B355" s="23"/>
+      <c r="C355" s="23"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="A356" s="16"/>
-      <c r="B356" s="16"/>
-      <c r="C356" s="16"/>
+      <c r="A356" s="23"/>
+      <c r="B356" s="23"/>
+      <c r="C356" s="23"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="A357" s="16"/>
-      <c r="B357" s="16"/>
-      <c r="C357" s="16"/>
+      <c r="A357" s="23"/>
+      <c r="B357" s="23"/>
+      <c r="C357" s="23"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="A358" s="16"/>
-      <c r="B358" s="16"/>
-      <c r="C358" s="16"/>
+      <c r="A358" s="23"/>
+      <c r="B358" s="23"/>
+      <c r="C358" s="23"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="A359" s="16"/>
-      <c r="B359" s="16"/>
-      <c r="C359" s="16"/>
+      <c r="A359" s="23"/>
+      <c r="B359" s="23"/>
+      <c r="C359" s="23"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="A360" s="16"/>
-      <c r="B360" s="16"/>
-      <c r="C360" s="16"/>
+      <c r="A360" s="23"/>
+      <c r="B360" s="23"/>
+      <c r="C360" s="23"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="A361" s="16"/>
-      <c r="B361" s="16"/>
-      <c r="C361" s="16"/>
+      <c r="A361" s="23"/>
+      <c r="B361" s="23"/>
+      <c r="C361" s="23"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="A362" s="16"/>
-      <c r="B362" s="16"/>
-      <c r="C362" s="16"/>
+      <c r="A362" s="23"/>
+      <c r="B362" s="23"/>
+      <c r="C362" s="23"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="A363" s="16"/>
-      <c r="B363" s="16"/>
-      <c r="C363" s="16"/>
+      <c r="A363" s="23"/>
+      <c r="B363" s="23"/>
+      <c r="C363" s="23"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="A364" s="16"/>
-      <c r="B364" s="16"/>
-      <c r="C364" s="16"/>
+      <c r="A364" s="23"/>
+      <c r="B364" s="23"/>
+      <c r="C364" s="23"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="A365" s="16"/>
-      <c r="B365" s="16"/>
-      <c r="C365" s="16"/>
+      <c r="A365" s="23"/>
+      <c r="B365" s="23"/>
+      <c r="C365" s="23"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="A366" s="16"/>
-      <c r="B366" s="16"/>
-      <c r="C366" s="16"/>
+      <c r="A366" s="23"/>
+      <c r="B366" s="23"/>
+      <c r="C366" s="23"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="A367" s="16"/>
-      <c r="B367" s="16"/>
-      <c r="C367" s="16"/>
+      <c r="A367" s="23"/>
+      <c r="B367" s="23"/>
+      <c r="C367" s="23"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="16"/>
-      <c r="B368" s="16"/>
-      <c r="C368" s="16"/>
+      <c r="A368" s="23"/>
+      <c r="B368" s="23"/>
+      <c r="C368" s="23"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="A369" s="16"/>
-      <c r="B369" s="16"/>
-      <c r="C369" s="16"/>
+      <c r="A369" s="23"/>
+      <c r="B369" s="23"/>
+      <c r="C369" s="23"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="A370" s="16"/>
-      <c r="B370" s="16"/>
-      <c r="C370" s="16"/>
+      <c r="A370" s="23"/>
+      <c r="B370" s="23"/>
+      <c r="C370" s="23"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="A371" s="16"/>
-      <c r="B371" s="16"/>
-      <c r="C371" s="16"/>
+      <c r="A371" s="23"/>
+      <c r="B371" s="23"/>
+      <c r="C371" s="23"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="A372" s="16"/>
-      <c r="B372" s="16"/>
-      <c r="C372" s="16"/>
+      <c r="A372" s="23"/>
+      <c r="B372" s="23"/>
+      <c r="C372" s="23"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="A373" s="16"/>
-      <c r="B373" s="16"/>
-      <c r="C373" s="16"/>
+      <c r="A373" s="23"/>
+      <c r="B373" s="23"/>
+      <c r="C373" s="23"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="A374" s="16"/>
-      <c r="B374" s="16"/>
-      <c r="C374" s="16"/>
+      <c r="A374" s="23"/>
+      <c r="B374" s="23"/>
+      <c r="C374" s="23"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="A375" s="16"/>
-      <c r="B375" s="16"/>
-      <c r="C375" s="16"/>
+      <c r="A375" s="23"/>
+      <c r="B375" s="23"/>
+      <c r="C375" s="23"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="A376" s="16"/>
-      <c r="B376" s="16"/>
-      <c r="C376" s="16"/>
+      <c r="A376" s="23"/>
+      <c r="B376" s="23"/>
+      <c r="C376" s="23"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="A377" s="16"/>
-      <c r="B377" s="16"/>
-      <c r="C377" s="16"/>
+      <c r="A377" s="23"/>
+      <c r="B377" s="23"/>
+      <c r="C377" s="23"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="A378" s="16"/>
-      <c r="B378" s="16"/>
-      <c r="C378" s="16"/>
+      <c r="A378" s="23"/>
+      <c r="B378" s="23"/>
+      <c r="C378" s="23"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="A379" s="16"/>
-      <c r="B379" s="16"/>
-      <c r="C379" s="16"/>
+      <c r="A379" s="23"/>
+      <c r="B379" s="23"/>
+      <c r="C379" s="23"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="A380" s="16"/>
-      <c r="B380" s="16"/>
-      <c r="C380" s="16"/>
+      <c r="A380" s="23"/>
+      <c r="B380" s="23"/>
+      <c r="C380" s="23"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="A381" s="16"/>
-      <c r="B381" s="16"/>
-      <c r="C381" s="16"/>
+      <c r="A381" s="23"/>
+      <c r="B381" s="23"/>
+      <c r="C381" s="23"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="A382" s="16"/>
-      <c r="B382" s="16"/>
-      <c r="C382" s="16"/>
+      <c r="A382" s="23"/>
+      <c r="B382" s="23"/>
+      <c r="C382" s="23"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="A383" s="16"/>
-      <c r="B383" s="16"/>
-      <c r="C383" s="16"/>
+      <c r="A383" s="23"/>
+      <c r="B383" s="23"/>
+      <c r="C383" s="23"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="A384" s="16"/>
-      <c r="B384" s="16"/>
-      <c r="C384" s="16"/>
+      <c r="A384" s="23"/>
+      <c r="B384" s="23"/>
+      <c r="C384" s="23"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="A385" s="16"/>
-      <c r="B385" s="16"/>
-      <c r="C385" s="16"/>
+      <c r="A385" s="23"/>
+      <c r="B385" s="23"/>
+      <c r="C385" s="23"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="A386" s="16"/>
-      <c r="B386" s="16"/>
-      <c r="C386" s="16"/>
+      <c r="A386" s="23"/>
+      <c r="B386" s="23"/>
+      <c r="C386" s="23"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="A387" s="16"/>
-      <c r="B387" s="16"/>
-      <c r="C387" s="16"/>
+      <c r="A387" s="23"/>
+      <c r="B387" s="23"/>
+      <c r="C387" s="23"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="A388" s="16"/>
-      <c r="B388" s="16"/>
-      <c r="C388" s="16"/>
+      <c r="A388" s="23"/>
+      <c r="B388" s="23"/>
+      <c r="C388" s="23"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="A389" s="16"/>
-      <c r="B389" s="16"/>
-      <c r="C389" s="16"/>
+      <c r="A389" s="23"/>
+      <c r="B389" s="23"/>
+      <c r="C389" s="23"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="A390" s="16"/>
-      <c r="B390" s="16"/>
-      <c r="C390" s="16"/>
+      <c r="A390" s="23"/>
+      <c r="B390" s="23"/>
+      <c r="C390" s="23"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="A391" s="16"/>
-      <c r="B391" s="16"/>
-      <c r="C391" s="16"/>
+      <c r="A391" s="23"/>
+      <c r="B391" s="23"/>
+      <c r="C391" s="23"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="A392" s="16"/>
-      <c r="B392" s="16"/>
-      <c r="C392" s="16"/>
+      <c r="A392" s="23"/>
+      <c r="B392" s="23"/>
+      <c r="C392" s="23"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="A393" s="16"/>
-      <c r="B393" s="16"/>
-      <c r="C393" s="16"/>
+      <c r="A393" s="23"/>
+      <c r="B393" s="23"/>
+      <c r="C393" s="23"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="A394" s="16"/>
-      <c r="B394" s="16"/>
-      <c r="C394" s="16"/>
+      <c r="A394" s="23"/>
+      <c r="B394" s="23"/>
+      <c r="C394" s="23"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="A395" s="16"/>
-      <c r="B395" s="16"/>
-      <c r="C395" s="16"/>
+      <c r="A395" s="23"/>
+      <c r="B395" s="23"/>
+      <c r="C395" s="23"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="A396" s="16"/>
-      <c r="B396" s="16"/>
-      <c r="C396" s="16"/>
+      <c r="A396" s="23"/>
+      <c r="B396" s="23"/>
+      <c r="C396" s="23"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="A397" s="16"/>
-      <c r="B397" s="16"/>
-      <c r="C397" s="16"/>
+      <c r="A397" s="23"/>
+      <c r="B397" s="23"/>
+      <c r="C397" s="23"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="A398" s="16"/>
-      <c r="B398" s="16"/>
-      <c r="C398" s="16"/>
+      <c r="A398" s="23"/>
+      <c r="B398" s="23"/>
+      <c r="C398" s="23"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="A399" s="16"/>
-      <c r="B399" s="16"/>
-      <c r="C399" s="16"/>
+      <c r="A399" s="23"/>
+      <c r="B399" s="23"/>
+      <c r="C399" s="23"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="A400" s="16"/>
-      <c r="B400" s="16"/>
-      <c r="C400" s="16"/>
+      <c r="A400" s="23"/>
+      <c r="B400" s="23"/>
+      <c r="C400" s="23"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="A401" s="16"/>
-      <c r="B401" s="16"/>
-      <c r="C401" s="16"/>
+      <c r="A401" s="23"/>
+      <c r="B401" s="23"/>
+      <c r="C401" s="23"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="A402" s="16"/>
-      <c r="B402" s="16"/>
-      <c r="C402" s="16"/>
+      <c r="A402" s="23"/>
+      <c r="B402" s="23"/>
+      <c r="C402" s="23"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="A403" s="16"/>
-      <c r="B403" s="16"/>
-      <c r="C403" s="16"/>
+      <c r="A403" s="23"/>
+      <c r="B403" s="23"/>
+      <c r="C403" s="23"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="A404" s="16"/>
-      <c r="B404" s="16"/>
-      <c r="C404" s="16"/>
+      <c r="A404" s="23"/>
+      <c r="B404" s="23"/>
+      <c r="C404" s="23"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="A405" s="16"/>
-      <c r="B405" s="16"/>
-      <c r="C405" s="16"/>
+      <c r="A405" s="23"/>
+      <c r="B405" s="23"/>
+      <c r="C405" s="23"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="A406" s="16"/>
-      <c r="B406" s="16"/>
-      <c r="C406" s="16"/>
+      <c r="A406" s="23"/>
+      <c r="B406" s="23"/>
+      <c r="C406" s="23"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="A407" s="16"/>
-      <c r="B407" s="16"/>
-      <c r="C407" s="16"/>
+      <c r="A407" s="23"/>
+      <c r="B407" s="23"/>
+      <c r="C407" s="23"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="A408" s="16"/>
-      <c r="B408" s="16"/>
-      <c r="C408" s="16"/>
+      <c r="A408" s="23"/>
+      <c r="B408" s="23"/>
+      <c r="C408" s="23"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="A409" s="16"/>
-      <c r="B409" s="16"/>
-      <c r="C409" s="16"/>
+      <c r="A409" s="23"/>
+      <c r="B409" s="23"/>
+      <c r="C409" s="23"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="A410" s="16"/>
-      <c r="B410" s="16"/>
-      <c r="C410" s="16"/>
+      <c r="A410" s="23"/>
+      <c r="B410" s="23"/>
+      <c r="C410" s="23"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="A411" s="16"/>
-      <c r="B411" s="16"/>
-      <c r="C411" s="16"/>
+      <c r="A411" s="23"/>
+      <c r="B411" s="23"/>
+      <c r="C411" s="23"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="A412" s="16"/>
-      <c r="B412" s="16"/>
-      <c r="C412" s="16"/>
+      <c r="A412" s="23"/>
+      <c r="B412" s="23"/>
+      <c r="C412" s="23"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="A413" s="16"/>
-      <c r="B413" s="16"/>
-      <c r="C413" s="16"/>
+      <c r="A413" s="23"/>
+      <c r="B413" s="23"/>
+      <c r="C413" s="23"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="A414" s="16"/>
-      <c r="B414" s="16"/>
-      <c r="C414" s="16"/>
+      <c r="A414" s="23"/>
+      <c r="B414" s="23"/>
+      <c r="C414" s="23"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="A415" s="16"/>
-      <c r="B415" s="16"/>
-      <c r="C415" s="16"/>
+      <c r="A415" s="23"/>
+      <c r="B415" s="23"/>
+      <c r="C415" s="23"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="A416" s="16"/>
-      <c r="B416" s="16"/>
-      <c r="C416" s="16"/>
+      <c r="A416" s="23"/>
+      <c r="B416" s="23"/>
+      <c r="C416" s="23"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="A417" s="16"/>
-      <c r="B417" s="16"/>
-      <c r="C417" s="16"/>
+      <c r="A417" s="23"/>
+      <c r="B417" s="23"/>
+      <c r="C417" s="23"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="A418" s="16"/>
-      <c r="B418" s="16"/>
-      <c r="C418" s="16"/>
+      <c r="A418" s="23"/>
+      <c r="B418" s="23"/>
+      <c r="C418" s="23"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="A419" s="16"/>
-      <c r="B419" s="16"/>
-      <c r="C419" s="16"/>
+      <c r="A419" s="23"/>
+      <c r="B419" s="23"/>
+      <c r="C419" s="23"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="A420" s="16"/>
-      <c r="B420" s="16"/>
-      <c r="C420" s="16"/>
+      <c r="A420" s="23"/>
+      <c r="B420" s="23"/>
+      <c r="C420" s="23"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="A421" s="16"/>
-      <c r="B421" s="16"/>
-      <c r="C421" s="16"/>
+      <c r="A421" s="23"/>
+      <c r="B421" s="23"/>
+      <c r="C421" s="23"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="A422" s="16"/>
-      <c r="B422" s="16"/>
-      <c r="C422" s="16"/>
+      <c r="A422" s="23"/>
+      <c r="B422" s="23"/>
+      <c r="C422" s="23"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="A423" s="16"/>
-      <c r="B423" s="16"/>
-      <c r="C423" s="16"/>
+      <c r="A423" s="23"/>
+      <c r="B423" s="23"/>
+      <c r="C423" s="23"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="A424" s="16"/>
-      <c r="B424" s="16"/>
-      <c r="C424" s="16"/>
+      <c r="A424" s="23"/>
+      <c r="B424" s="23"/>
+      <c r="C424" s="23"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="A425" s="16"/>
-      <c r="B425" s="16"/>
-      <c r="C425" s="16"/>
+      <c r="A425" s="23"/>
+      <c r="B425" s="23"/>
+      <c r="C425" s="23"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="A426" s="16"/>
-      <c r="B426" s="16"/>
-      <c r="C426" s="16"/>
+      <c r="A426" s="23"/>
+      <c r="B426" s="23"/>
+      <c r="C426" s="23"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="A427" s="16"/>
-      <c r="B427" s="16"/>
-      <c r="C427" s="16"/>
+      <c r="A427" s="23"/>
+      <c r="B427" s="23"/>
+      <c r="C427" s="23"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="A428" s="16"/>
-      <c r="B428" s="16"/>
-      <c r="C428" s="16"/>
+      <c r="A428" s="23"/>
+      <c r="B428" s="23"/>
+      <c r="C428" s="23"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="A429" s="16"/>
-      <c r="B429" s="16"/>
-      <c r="C429" s="16"/>
+      <c r="A429" s="23"/>
+      <c r="B429" s="23"/>
+      <c r="C429" s="23"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="A430" s="16"/>
-      <c r="B430" s="16"/>
-      <c r="C430" s="16"/>
+      <c r="A430" s="23"/>
+      <c r="B430" s="23"/>
+      <c r="C430" s="23"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="A431" s="16"/>
-      <c r="B431" s="16"/>
-      <c r="C431" s="16"/>
+      <c r="A431" s="23"/>
+      <c r="B431" s="23"/>
+      <c r="C431" s="23"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="A432" s="16"/>
-      <c r="B432" s="16"/>
-      <c r="C432" s="16"/>
+      <c r="A432" s="23"/>
+      <c r="B432" s="23"/>
+      <c r="C432" s="23"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="A433" s="16"/>
-      <c r="B433" s="16"/>
-      <c r="C433" s="16"/>
+      <c r="A433" s="23"/>
+      <c r="B433" s="23"/>
+      <c r="C433" s="23"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="A434" s="16"/>
-      <c r="B434" s="16"/>
-      <c r="C434" s="16"/>
+      <c r="A434" s="23"/>
+      <c r="B434" s="23"/>
+      <c r="C434" s="23"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="16"/>
-      <c r="B435" s="16"/>
-      <c r="C435" s="16"/>
+      <c r="A435" s="23"/>
+      <c r="B435" s="23"/>
+      <c r="C435" s="23"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="16"/>
-      <c r="B436" s="16"/>
-      <c r="C436" s="16"/>
+      <c r="A436" s="23"/>
+      <c r="B436" s="23"/>
+      <c r="C436" s="23"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="16"/>
-      <c r="B437" s="16"/>
-      <c r="C437" s="16"/>
+      <c r="A437" s="23"/>
+      <c r="B437" s="23"/>
+      <c r="C437" s="23"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="16"/>
-      <c r="B438" s="16"/>
-      <c r="C438" s="16"/>
+      <c r="A438" s="23"/>
+      <c r="B438" s="23"/>
+      <c r="C438" s="23"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="16"/>
-      <c r="B439" s="16"/>
-      <c r="C439" s="16"/>
+      <c r="A439" s="23"/>
+      <c r="B439" s="23"/>
+      <c r="C439" s="23"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="16"/>
-      <c r="B440" s="16"/>
-      <c r="C440" s="16"/>
+      <c r="A440" s="23"/>
+      <c r="B440" s="23"/>
+      <c r="C440" s="23"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="A441" s="16"/>
-      <c r="B441" s="16"/>
-      <c r="C441" s="16"/>
+      <c r="A441" s="23"/>
+      <c r="B441" s="23"/>
+      <c r="C441" s="23"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="A442" s="16"/>
-      <c r="B442" s="16"/>
-      <c r="C442" s="16"/>
+      <c r="A442" s="23"/>
+      <c r="B442" s="23"/>
+      <c r="C442" s="23"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="16"/>
-      <c r="B443" s="16"/>
-      <c r="C443" s="16"/>
+      <c r="A443" s="23"/>
+      <c r="B443" s="23"/>
+      <c r="C443" s="23"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="16"/>
-      <c r="B444" s="16"/>
-      <c r="C444" s="16"/>
+      <c r="A444" s="23"/>
+      <c r="B444" s="23"/>
+      <c r="C444" s="23"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="16"/>
-      <c r="B445" s="16"/>
-      <c r="C445" s="16"/>
+      <c r="A445" s="23"/>
+      <c r="B445" s="23"/>
+      <c r="C445" s="23"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="16"/>
-      <c r="B446" s="16"/>
-      <c r="C446" s="16"/>
+      <c r="A446" s="23"/>
+      <c r="B446" s="23"/>
+      <c r="C446" s="23"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="A447" s="16"/>
-      <c r="B447" s="16"/>
-      <c r="C447" s="16"/>
+      <c r="A447" s="23"/>
+      <c r="B447" s="23"/>
+      <c r="C447" s="23"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="A448" s="16"/>
-      <c r="B448" s="16"/>
-      <c r="C448" s="16"/>
+      <c r="A448" s="23"/>
+      <c r="B448" s="23"/>
+      <c r="C448" s="23"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="A449" s="16"/>
-      <c r="B449" s="16"/>
-      <c r="C449" s="16"/>
+      <c r="A449" s="23"/>
+      <c r="B449" s="23"/>
+      <c r="C449" s="23"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="A450" s="16"/>
-      <c r="B450" s="16"/>
-      <c r="C450" s="16"/>
+      <c r="A450" s="23"/>
+      <c r="B450" s="23"/>
+      <c r="C450" s="23"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="A451" s="16"/>
-      <c r="B451" s="16"/>
-      <c r="C451" s="16"/>
+      <c r="A451" s="23"/>
+      <c r="B451" s="23"/>
+      <c r="C451" s="23"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="A452" s="16"/>
-      <c r="B452" s="16"/>
-      <c r="C452" s="16"/>
+      <c r="A452" s="23"/>
+      <c r="B452" s="23"/>
+      <c r="C452" s="23"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="16"/>
-      <c r="B453" s="16"/>
-      <c r="C453" s="16"/>
+      <c r="A453" s="23"/>
+      <c r="B453" s="23"/>
+      <c r="C453" s="23"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="16"/>
-      <c r="B454" s="16"/>
-      <c r="C454" s="16"/>
+      <c r="A454" s="23"/>
+      <c r="B454" s="23"/>
+      <c r="C454" s="23"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="16"/>
-      <c r="B455" s="16"/>
-      <c r="C455" s="16"/>
+      <c r="A455" s="23"/>
+      <c r="B455" s="23"/>
+      <c r="C455" s="23"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="16"/>
-      <c r="B456" s="16"/>
-      <c r="C456" s="16"/>
+      <c r="A456" s="23"/>
+      <c r="B456" s="23"/>
+      <c r="C456" s="23"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="A457" s="16"/>
-      <c r="B457" s="16"/>
-      <c r="C457" s="16"/>
+      <c r="A457" s="23"/>
+      <c r="B457" s="23"/>
+      <c r="C457" s="23"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="A458" s="16"/>
-      <c r="B458" s="16"/>
-      <c r="C458" s="16"/>
+      <c r="A458" s="23"/>
+      <c r="B458" s="23"/>
+      <c r="C458" s="23"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="A459" s="16"/>
-      <c r="B459" s="16"/>
-      <c r="C459" s="16"/>
+      <c r="A459" s="23"/>
+      <c r="B459" s="23"/>
+      <c r="C459" s="23"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="A460" s="16"/>
-      <c r="B460" s="16"/>
-      <c r="C460" s="16"/>
+      <c r="A460" s="23"/>
+      <c r="B460" s="23"/>
+      <c r="C460" s="23"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="A461" s="16"/>
-      <c r="B461" s="16"/>
-      <c r="C461" s="16"/>
+      <c r="A461" s="23"/>
+      <c r="B461" s="23"/>
+      <c r="C461" s="23"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="A462" s="16"/>
-      <c r="B462" s="16"/>
-      <c r="C462" s="16"/>
+      <c r="A462" s="23"/>
+      <c r="B462" s="23"/>
+      <c r="C462" s="23"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="A463" s="16"/>
-      <c r="B463" s="16"/>
-      <c r="C463" s="16"/>
+      <c r="A463" s="23"/>
+      <c r="B463" s="23"/>
+      <c r="C463" s="23"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="A464" s="16"/>
-      <c r="B464" s="16"/>
-      <c r="C464" s="16"/>
+      <c r="A464" s="23"/>
+      <c r="B464" s="23"/>
+      <c r="C464" s="23"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="A465" s="16"/>
-      <c r="B465" s="16"/>
-      <c r="C465" s="16"/>
+      <c r="A465" s="23"/>
+      <c r="B465" s="23"/>
+      <c r="C465" s="23"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="A466" s="16"/>
-      <c r="B466" s="16"/>
-      <c r="C466" s="16"/>
+      <c r="A466" s="23"/>
+      <c r="B466" s="23"/>
+      <c r="C466" s="23"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="A467" s="16"/>
-      <c r="B467" s="16"/>
-      <c r="C467" s="16"/>
+      <c r="A467" s="23"/>
+      <c r="B467" s="23"/>
+      <c r="C467" s="23"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="A468" s="16"/>
-      <c r="B468" s="16"/>
-      <c r="C468" s="16"/>
+      <c r="A468" s="23"/>
+      <c r="B468" s="23"/>
+      <c r="C468" s="23"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="A469" s="16"/>
-      <c r="B469" s="16"/>
-      <c r="C469" s="16"/>
+      <c r="A469" s="23"/>
+      <c r="B469" s="23"/>
+      <c r="C469" s="23"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="A470" s="16"/>
-      <c r="B470" s="16"/>
-      <c r="C470" s="16"/>
+      <c r="A470" s="23"/>
+      <c r="B470" s="23"/>
+      <c r="C470" s="23"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="A471" s="16"/>
-      <c r="B471" s="16"/>
-      <c r="C471" s="16"/>
+      <c r="A471" s="23"/>
+      <c r="B471" s="23"/>
+      <c r="C471" s="23"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="A472" s="16"/>
-      <c r="B472" s="16"/>
-      <c r="C472" s="16"/>
+      <c r="A472" s="23"/>
+      <c r="B472" s="23"/>
+      <c r="C472" s="23"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="A473" s="16"/>
-      <c r="B473" s="16"/>
-      <c r="C473" s="16"/>
+      <c r="A473" s="23"/>
+      <c r="B473" s="23"/>
+      <c r="C473" s="23"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="A474" s="16"/>
-      <c r="B474" s="16"/>
-      <c r="C474" s="16"/>
+      <c r="A474" s="23"/>
+      <c r="B474" s="23"/>
+      <c r="C474" s="23"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="A475" s="16"/>
-      <c r="B475" s="16"/>
-      <c r="C475" s="16"/>
+      <c r="A475" s="23"/>
+      <c r="B475" s="23"/>
+      <c r="C475" s="23"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="A476" s="16"/>
-      <c r="B476" s="16"/>
-      <c r="C476" s="16"/>
+      <c r="A476" s="23"/>
+      <c r="B476" s="23"/>
+      <c r="C476" s="23"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="A477" s="16"/>
-      <c r="B477" s="16"/>
-      <c r="C477" s="16"/>
+      <c r="A477" s="23"/>
+      <c r="B477" s="23"/>
+      <c r="C477" s="23"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="A478" s="16"/>
-      <c r="B478" s="16"/>
-      <c r="C478" s="16"/>
+      <c r="A478" s="23"/>
+      <c r="B478" s="23"/>
+      <c r="C478" s="23"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="A479" s="16"/>
-      <c r="B479" s="16"/>
-      <c r="C479" s="16"/>
+      <c r="A479" s="23"/>
+      <c r="B479" s="23"/>
+      <c r="C479" s="23"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="A480" s="16"/>
-      <c r="B480" s="16"/>
-      <c r="C480" s="16"/>
+      <c r="A480" s="23"/>
+      <c r="B480" s="23"/>
+      <c r="C480" s="23"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="A481" s="16"/>
-      <c r="B481" s="16"/>
-      <c r="C481" s="16"/>
+      <c r="A481" s="23"/>
+      <c r="B481" s="23"/>
+      <c r="C481" s="23"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="A482" s="16"/>
-      <c r="B482" s="16"/>
-      <c r="C482" s="16"/>
+      <c r="A482" s="23"/>
+      <c r="B482" s="23"/>
+      <c r="C482" s="23"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="A483" s="16"/>
-      <c r="B483" s="16"/>
-      <c r="C483" s="16"/>
+      <c r="A483" s="23"/>
+      <c r="B483" s="23"/>
+      <c r="C483" s="23"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="A484" s="16"/>
-      <c r="B484" s="16"/>
-      <c r="C484" s="16"/>
+      <c r="A484" s="23"/>
+      <c r="B484" s="23"/>
+      <c r="C484" s="23"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="A485" s="16"/>
-      <c r="B485" s="16"/>
-      <c r="C485" s="16"/>
+      <c r="A485" s="23"/>
+      <c r="B485" s="23"/>
+      <c r="C485" s="23"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="A486" s="16"/>
-      <c r="B486" s="16"/>
-      <c r="C486" s="16"/>
+      <c r="A486" s="23"/>
+      <c r="B486" s="23"/>
+      <c r="C486" s="23"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="A487" s="16"/>
-      <c r="B487" s="16"/>
-      <c r="C487" s="16"/>
+      <c r="A487" s="23"/>
+      <c r="B487" s="23"/>
+      <c r="C487" s="23"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="A488" s="16"/>
-      <c r="B488" s="16"/>
-      <c r="C488" s="16"/>
+      <c r="A488" s="23"/>
+      <c r="B488" s="23"/>
+      <c r="C488" s="23"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="A489" s="16"/>
-      <c r="B489" s="16"/>
-      <c r="C489" s="16"/>
+      <c r="A489" s="23"/>
+      <c r="B489" s="23"/>
+      <c r="C489" s="23"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="A490" s="16"/>
-      <c r="B490" s="16"/>
-      <c r="C490" s="16"/>
+      <c r="A490" s="23"/>
+      <c r="B490" s="23"/>
+      <c r="C490" s="23"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="A491" s="16"/>
-      <c r="B491" s="16"/>
-      <c r="C491" s="16"/>
+      <c r="A491" s="23"/>
+      <c r="B491" s="23"/>
+      <c r="C491" s="23"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="A492" s="16"/>
-      <c r="B492" s="16"/>
-      <c r="C492" s="16"/>
+      <c r="A492" s="23"/>
+      <c r="B492" s="23"/>
+      <c r="C492" s="23"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="A493" s="16"/>
-      <c r="B493" s="16"/>
-      <c r="C493" s="16"/>
+      <c r="A493" s="23"/>
+      <c r="B493" s="23"/>
+      <c r="C493" s="23"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="A494" s="16"/>
-      <c r="B494" s="16"/>
-      <c r="C494" s="16"/>
+      <c r="A494" s="23"/>
+      <c r="B494" s="23"/>
+      <c r="C494" s="23"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="A495" s="16"/>
-      <c r="B495" s="16"/>
-      <c r="C495" s="16"/>
+      <c r="A495" s="23"/>
+      <c r="B495" s="23"/>
+      <c r="C495" s="23"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="A496" s="16"/>
-      <c r="B496" s="16"/>
-      <c r="C496" s="16"/>
+      <c r="A496" s="23"/>
+      <c r="B496" s="23"/>
+      <c r="C496" s="23"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="A497" s="16"/>
-      <c r="B497" s="16"/>
-      <c r="C497" s="16"/>
+      <c r="A497" s="23"/>
+      <c r="B497" s="23"/>
+      <c r="C497" s="23"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="A498" s="16"/>
-      <c r="B498" s="16"/>
-      <c r="C498" s="16"/>
+      <c r="A498" s="23"/>
+      <c r="B498" s="23"/>
+      <c r="C498" s="23"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="A499" s="16"/>
-      <c r="B499" s="16"/>
-      <c r="C499" s="16"/>
+      <c r="A499" s="23"/>
+      <c r="B499" s="23"/>
+      <c r="C499" s="23"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="A500" s="16"/>
-      <c r="B500" s="16"/>
-      <c r="C500" s="16"/>
+      <c r="A500" s="23"/>
+      <c r="B500" s="23"/>
+      <c r="C500" s="23"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="A501" s="16"/>
-      <c r="B501" s="16"/>
-      <c r="C501" s="16"/>
+      <c r="A501" s="23"/>
+      <c r="B501" s="23"/>
+      <c r="C501" s="23"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="A502" s="16"/>
-      <c r="B502" s="16"/>
-      <c r="C502" s="16"/>
+      <c r="A502" s="23"/>
+      <c r="B502" s="23"/>
+      <c r="C502" s="23"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="A503" s="16"/>
-      <c r="B503" s="16"/>
-      <c r="C503" s="16"/>
+      <c r="A503" s="23"/>
+      <c r="B503" s="23"/>
+      <c r="C503" s="23"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="A504" s="16"/>
-      <c r="B504" s="16"/>
-      <c r="C504" s="16"/>
+      <c r="A504" s="23"/>
+      <c r="B504" s="23"/>
+      <c r="C504" s="23"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="A505" s="16"/>
-      <c r="B505" s="16"/>
-      <c r="C505" s="16"/>
+      <c r="A505" s="23"/>
+      <c r="B505" s="23"/>
+      <c r="C505" s="23"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="A506" s="16"/>
-      <c r="B506" s="16"/>
-      <c r="C506" s="16"/>
+      <c r="A506" s="23"/>
+      <c r="B506" s="23"/>
+      <c r="C506" s="23"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="A507" s="16"/>
-      <c r="B507" s="16"/>
-      <c r="C507" s="16"/>
+      <c r="A507" s="23"/>
+      <c r="B507" s="23"/>
+      <c r="C507" s="23"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="A508" s="16"/>
-      <c r="B508" s="16"/>
-      <c r="C508" s="16"/>
+      <c r="A508" s="23"/>
+      <c r="B508" s="23"/>
+      <c r="C508" s="23"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="A509" s="16"/>
-      <c r="B509" s="16"/>
-      <c r="C509" s="16"/>
+      <c r="A509" s="23"/>
+      <c r="B509" s="23"/>
+      <c r="C509" s="23"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="A510" s="16"/>
-      <c r="B510" s="16"/>
-      <c r="C510" s="16"/>
+      <c r="A510" s="23"/>
+      <c r="B510" s="23"/>
+      <c r="C510" s="23"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="A511" s="16"/>
-      <c r="B511" s="16"/>
-      <c r="C511" s="16"/>
+      <c r="A511" s="23"/>
+      <c r="B511" s="23"/>
+      <c r="C511" s="23"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="A512" s="16"/>
-      <c r="B512" s="16"/>
-      <c r="C512" s="16"/>
+      <c r="A512" s="23"/>
+      <c r="B512" s="23"/>
+      <c r="C512" s="23"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="A513" s="16"/>
-      <c r="B513" s="16"/>
-      <c r="C513" s="16"/>
+      <c r="A513" s="23"/>
+      <c r="B513" s="23"/>
+      <c r="C513" s="23"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="A514" s="16"/>
-      <c r="B514" s="16"/>
-      <c r="C514" s="16"/>
+      <c r="A514" s="23"/>
+      <c r="B514" s="23"/>
+      <c r="C514" s="23"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="A515" s="16"/>
-      <c r="B515" s="16"/>
-      <c r="C515" s="16"/>
+      <c r="A515" s="23"/>
+      <c r="B515" s="23"/>
+      <c r="C515" s="23"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="A516" s="16"/>
-      <c r="B516" s="16"/>
-      <c r="C516" s="16"/>
+      <c r="A516" s="23"/>
+      <c r="B516" s="23"/>
+      <c r="C516" s="23"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="A517" s="16"/>
-      <c r="B517" s="16"/>
-      <c r="C517" s="16"/>
+      <c r="A517" s="23"/>
+      <c r="B517" s="23"/>
+      <c r="C517" s="23"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="A518" s="16"/>
-      <c r="B518" s="16"/>
-      <c r="C518" s="16"/>
+      <c r="A518" s="23"/>
+      <c r="B518" s="23"/>
+      <c r="C518" s="23"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="A519" s="16"/>
-      <c r="B519" s="16"/>
-      <c r="C519" s="16"/>
+      <c r="A519" s="23"/>
+      <c r="B519" s="23"/>
+      <c r="C519" s="23"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="A520" s="16"/>
-      <c r="B520" s="16"/>
-      <c r="C520" s="16"/>
+      <c r="A520" s="23"/>
+      <c r="B520" s="23"/>
+      <c r="C520" s="23"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="A521" s="16"/>
-      <c r="B521" s="16"/>
-      <c r="C521" s="16"/>
+      <c r="A521" s="23"/>
+      <c r="B521" s="23"/>
+      <c r="C521" s="23"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="A522" s="16"/>
-      <c r="B522" s="16"/>
-      <c r="C522" s="16"/>
+      <c r="A522" s="23"/>
+      <c r="B522" s="23"/>
+      <c r="C522" s="23"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="A523" s="16"/>
-      <c r="B523" s="16"/>
-      <c r="C523" s="16"/>
+      <c r="A523" s="23"/>
+      <c r="B523" s="23"/>
+      <c r="C523" s="23"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="A524" s="16"/>
-      <c r="B524" s="16"/>
-      <c r="C524" s="16"/>
+      <c r="A524" s="23"/>
+      <c r="B524" s="23"/>
+      <c r="C524" s="23"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="A525" s="16"/>
-      <c r="B525" s="16"/>
-      <c r="C525" s="16"/>
+      <c r="A525" s="23"/>
+      <c r="B525" s="23"/>
+      <c r="C525" s="23"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="A526" s="16"/>
-      <c r="B526" s="16"/>
-      <c r="C526" s="16"/>
+      <c r="A526" s="23"/>
+      <c r="B526" s="23"/>
+      <c r="C526" s="23"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="A527" s="16"/>
-      <c r="B527" s="16"/>
-      <c r="C527" s="16"/>
+      <c r="A527" s="23"/>
+      <c r="B527" s="23"/>
+      <c r="C527" s="23"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="A528" s="16"/>
-      <c r="B528" s="16"/>
-      <c r="C528" s="16"/>
+      <c r="A528" s="23"/>
+      <c r="B528" s="23"/>
+      <c r="C528" s="23"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="A529" s="16"/>
-      <c r="B529" s="16"/>
-      <c r="C529" s="16"/>
+      <c r="A529" s="23"/>
+      <c r="B529" s="23"/>
+      <c r="C529" s="23"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="A530" s="16"/>
-      <c r="B530" s="16"/>
-      <c r="C530" s="16"/>
+      <c r="A530" s="23"/>
+      <c r="B530" s="23"/>
+      <c r="C530" s="23"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="A531" s="16"/>
-      <c r="B531" s="16"/>
-      <c r="C531" s="16"/>
+      <c r="A531" s="23"/>
+      <c r="B531" s="23"/>
+      <c r="C531" s="23"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="A532" s="16"/>
-      <c r="B532" s="16"/>
-      <c r="C532" s="16"/>
+      <c r="A532" s="23"/>
+      <c r="B532" s="23"/>
+      <c r="C532" s="23"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="A533" s="16"/>
-      <c r="B533" s="16"/>
-      <c r="C533" s="16"/>
+      <c r="A533" s="23"/>
+      <c r="B533" s="23"/>
+      <c r="C533" s="23"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="A534" s="16"/>
-      <c r="B534" s="16"/>
-      <c r="C534" s="16"/>
+      <c r="A534" s="23"/>
+      <c r="B534" s="23"/>
+      <c r="C534" s="23"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="A535" s="16"/>
-      <c r="B535" s="16"/>
-      <c r="C535" s="16"/>
+      <c r="A535" s="23"/>
+      <c r="B535" s="23"/>
+      <c r="C535" s="23"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="A536" s="16"/>
-      <c r="B536" s="16"/>
-      <c r="C536" s="16"/>
+      <c r="A536" s="23"/>
+      <c r="B536" s="23"/>
+      <c r="C536" s="23"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="A537" s="16"/>
-      <c r="B537" s="16"/>
-      <c r="C537" s="16"/>
+      <c r="A537" s="23"/>
+      <c r="B537" s="23"/>
+      <c r="C537" s="23"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="A538" s="16"/>
-      <c r="B538" s="16"/>
-      <c r="C538" s="16"/>
+      <c r="A538" s="23"/>
+      <c r="B538" s="23"/>
+      <c r="C538" s="23"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="A539" s="16"/>
-      <c r="B539" s="16"/>
-      <c r="C539" s="16"/>
+      <c r="A539" s="23"/>
+      <c r="B539" s="23"/>
+      <c r="C539" s="23"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="A540" s="16"/>
-      <c r="B540" s="16"/>
-      <c r="C540" s="16"/>
+      <c r="A540" s="23"/>
+      <c r="B540" s="23"/>
+      <c r="C540" s="23"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="A541" s="16"/>
-      <c r="B541" s="16"/>
-      <c r="C541" s="16"/>
+      <c r="A541" s="23"/>
+      <c r="B541" s="23"/>
+      <c r="C541" s="23"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="A542" s="16"/>
-      <c r="B542" s="16"/>
-      <c r="C542" s="16"/>
+      <c r="A542" s="23"/>
+      <c r="B542" s="23"/>
+      <c r="C542" s="23"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="A543" s="16"/>
-      <c r="B543" s="16"/>
-      <c r="C543" s="16"/>
+      <c r="A543" s="23"/>
+      <c r="B543" s="23"/>
+      <c r="C543" s="23"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="A544" s="16"/>
-      <c r="B544" s="16"/>
-      <c r="C544" s="16"/>
+      <c r="A544" s="23"/>
+      <c r="B544" s="23"/>
+      <c r="C544" s="23"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="A545" s="16"/>
-      <c r="B545" s="16"/>
-      <c r="C545" s="16"/>
+      <c r="A545" s="23"/>
+      <c r="B545" s="23"/>
+      <c r="C545" s="23"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="A546" s="16"/>
-      <c r="B546" s="16"/>
-      <c r="C546" s="16"/>
+      <c r="A546" s="23"/>
+      <c r="B546" s="23"/>
+      <c r="C546" s="23"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="A547" s="16"/>
-      <c r="B547" s="16"/>
-      <c r="C547" s="16"/>
+      <c r="A547" s="23"/>
+      <c r="B547" s="23"/>
+      <c r="C547" s="23"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="A548" s="16"/>
-      <c r="B548" s="16"/>
-      <c r="C548" s="16"/>
+      <c r="A548" s="23"/>
+      <c r="B548" s="23"/>
+      <c r="C548" s="23"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="A549" s="16"/>
-      <c r="B549" s="16"/>
-      <c r="C549" s="16"/>
+      <c r="A549" s="23"/>
+      <c r="B549" s="23"/>
+      <c r="C549" s="23"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="A550" s="16"/>
-      <c r="B550" s="16"/>
-      <c r="C550" s="16"/>
+      <c r="A550" s="23"/>
+      <c r="B550" s="23"/>
+      <c r="C550" s="23"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="A551" s="16"/>
-      <c r="B551" s="16"/>
-      <c r="C551" s="16"/>
+      <c r="A551" s="23"/>
+      <c r="B551" s="23"/>
+      <c r="C551" s="23"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="A552" s="16"/>
-      <c r="B552" s="16"/>
-      <c r="C552" s="16"/>
+      <c r="A552" s="23"/>
+      <c r="B552" s="23"/>
+      <c r="C552" s="23"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="A553" s="16"/>
-      <c r="B553" s="16"/>
-      <c r="C553" s="16"/>
+      <c r="A553" s="23"/>
+      <c r="B553" s="23"/>
+      <c r="C553" s="23"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="A554" s="16"/>
-      <c r="B554" s="16"/>
-      <c r="C554" s="16"/>
+      <c r="A554" s="23"/>
+      <c r="B554" s="23"/>
+      <c r="C554" s="23"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="A555" s="16"/>
-      <c r="B555" s="16"/>
-      <c r="C555" s="16"/>
+      <c r="A555" s="23"/>
+      <c r="B555" s="23"/>
+      <c r="C555" s="23"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="A556" s="16"/>
-      <c r="B556" s="16"/>
-      <c r="C556" s="16"/>
+      <c r="A556" s="23"/>
+      <c r="B556" s="23"/>
+      <c r="C556" s="23"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="A557" s="16"/>
-      <c r="B557" s="16"/>
-      <c r="C557" s="16"/>
+      <c r="A557" s="23"/>
+      <c r="B557" s="23"/>
+      <c r="C557" s="23"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="A558" s="16"/>
-      <c r="B558" s="16"/>
-      <c r="C558" s="16"/>
+      <c r="A558" s="23"/>
+      <c r="B558" s="23"/>
+      <c r="C558" s="23"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="A559" s="16"/>
-      <c r="B559" s="16"/>
-      <c r="C559" s="16"/>
+      <c r="A559" s="23"/>
+      <c r="B559" s="23"/>
+      <c r="C559" s="23"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="A560" s="16"/>
-      <c r="B560" s="16"/>
-      <c r="C560" s="16"/>
+      <c r="A560" s="23"/>
+      <c r="B560" s="23"/>
+      <c r="C560" s="23"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="A561" s="16"/>
-      <c r="B561" s="16"/>
-      <c r="C561" s="16"/>
+      <c r="A561" s="23"/>
+      <c r="B561" s="23"/>
+      <c r="C561" s="23"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="A562" s="16"/>
-      <c r="B562" s="16"/>
-      <c r="C562" s="16"/>
+      <c r="A562" s="23"/>
+      <c r="B562" s="23"/>
+      <c r="C562" s="23"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="A563" s="16"/>
-      <c r="B563" s="16"/>
-      <c r="C563" s="16"/>
+      <c r="A563" s="23"/>
+      <c r="B563" s="23"/>
+      <c r="C563" s="23"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="A564" s="16"/>
-      <c r="B564" s="16"/>
-      <c r="C564" s="16"/>
+      <c r="A564" s="23"/>
+      <c r="B564" s="23"/>
+      <c r="C564" s="23"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="A565" s="16"/>
-      <c r="B565" s="16"/>
-      <c r="C565" s="16"/>
+      <c r="A565" s="23"/>
+      <c r="B565" s="23"/>
+      <c r="C565" s="23"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="A566" s="16"/>
-      <c r="B566" s="16"/>
-      <c r="C566" s="16"/>
+      <c r="A566" s="23"/>
+      <c r="B566" s="23"/>
+      <c r="C566" s="23"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="A567" s="16"/>
-      <c r="B567" s="16"/>
-      <c r="C567" s="16"/>
+      <c r="A567" s="23"/>
+      <c r="B567" s="23"/>
+      <c r="C567" s="23"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="A568" s="16"/>
-      <c r="B568" s="16"/>
-      <c r="C568" s="16"/>
+      <c r="A568" s="23"/>
+      <c r="B568" s="23"/>
+      <c r="C568" s="23"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="A569" s="16"/>
-      <c r="B569" s="16"/>
-      <c r="C569" s="16"/>
+      <c r="A569" s="23"/>
+      <c r="B569" s="23"/>
+      <c r="C569" s="23"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="A570" s="16"/>
-      <c r="B570" s="16"/>
-      <c r="C570" s="16"/>
+      <c r="A570" s="23"/>
+      <c r="B570" s="23"/>
+      <c r="C570" s="23"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="A571" s="16"/>
-      <c r="B571" s="16"/>
-      <c r="C571" s="16"/>
+      <c r="A571" s="23"/>
+      <c r="B571" s="23"/>
+      <c r="C571" s="23"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="A572" s="16"/>
-      <c r="B572" s="16"/>
-      <c r="C572" s="16"/>
+      <c r="A572" s="23"/>
+      <c r="B572" s="23"/>
+      <c r="C572" s="23"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="A573" s="16"/>
-      <c r="B573" s="16"/>
-      <c r="C573" s="16"/>
+      <c r="A573" s="23"/>
+      <c r="B573" s="23"/>
+      <c r="C573" s="23"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="A574" s="16"/>
-      <c r="B574" s="16"/>
-      <c r="C574" s="16"/>
+      <c r="A574" s="23"/>
+      <c r="B574" s="23"/>
+      <c r="C574" s="23"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="A575" s="16"/>
-      <c r="B575" s="16"/>
-      <c r="C575" s="16"/>
+      <c r="A575" s="23"/>
+      <c r="B575" s="23"/>
+      <c r="C575" s="23"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="A576" s="16"/>
-      <c r="B576" s="16"/>
-      <c r="C576" s="16"/>
+      <c r="A576" s="23"/>
+      <c r="B576" s="23"/>
+      <c r="C576" s="23"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="A577" s="16"/>
-      <c r="B577" s="16"/>
-      <c r="C577" s="16"/>
+      <c r="A577" s="23"/>
+      <c r="B577" s="23"/>
+      <c r="C577" s="23"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="A578" s="16"/>
-      <c r="B578" s="16"/>
-      <c r="C578" s="16"/>
+      <c r="A578" s="23"/>
+      <c r="B578" s="23"/>
+      <c r="C578" s="23"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="A579" s="16"/>
-      <c r="B579" s="16"/>
-      <c r="C579" s="16"/>
+      <c r="A579" s="23"/>
+      <c r="B579" s="23"/>
+      <c r="C579" s="23"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="A580" s="16"/>
-      <c r="B580" s="16"/>
-      <c r="C580" s="16"/>
+      <c r="A580" s="23"/>
+      <c r="B580" s="23"/>
+      <c r="C580" s="23"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="A581" s="16"/>
-      <c r="B581" s="16"/>
-      <c r="C581" s="16"/>
+      <c r="A581" s="23"/>
+      <c r="B581" s="23"/>
+      <c r="C581" s="23"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="A582" s="16"/>
-      <c r="B582" s="16"/>
-      <c r="C582" s="16"/>
+      <c r="A582" s="23"/>
+      <c r="B582" s="23"/>
+      <c r="C582" s="23"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="A583" s="16"/>
-      <c r="B583" s="16"/>
-      <c r="C583" s="16"/>
+      <c r="A583" s="23"/>
+      <c r="B583" s="23"/>
+      <c r="C583" s="23"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="A584" s="16"/>
-      <c r="B584" s="16"/>
-      <c r="C584" s="16"/>
+      <c r="A584" s="23"/>
+      <c r="B584" s="23"/>
+      <c r="C584" s="23"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="A585" s="16"/>
-      <c r="B585" s="16"/>
-      <c r="C585" s="16"/>
+      <c r="A585" s="23"/>
+      <c r="B585" s="23"/>
+      <c r="C585" s="23"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="A586" s="16"/>
-      <c r="B586" s="16"/>
-      <c r="C586" s="16"/>
+      <c r="A586" s="23"/>
+      <c r="B586" s="23"/>
+      <c r="C586" s="23"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="A587" s="16"/>
-      <c r="B587" s="16"/>
-      <c r="C587" s="16"/>
+      <c r="A587" s="23"/>
+      <c r="B587" s="23"/>
+      <c r="C587" s="23"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="A588" s="16"/>
-      <c r="B588" s="16"/>
-      <c r="C588" s="16"/>
+      <c r="A588" s="23"/>
+      <c r="B588" s="23"/>
+      <c r="C588" s="23"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="A589" s="16"/>
-      <c r="B589" s="16"/>
-      <c r="C589" s="16"/>
+      <c r="A589" s="23"/>
+      <c r="B589" s="23"/>
+      <c r="C589" s="23"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="A590" s="16"/>
-      <c r="B590" s="16"/>
-      <c r="C590" s="16"/>
+      <c r="A590" s="23"/>
+      <c r="B590" s="23"/>
+      <c r="C590" s="23"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="A591" s="16"/>
-      <c r="B591" s="16"/>
-      <c r="C591" s="16"/>
+      <c r="A591" s="23"/>
+      <c r="B591" s="23"/>
+      <c r="C591" s="23"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="A592" s="16"/>
-      <c r="B592" s="16"/>
-      <c r="C592" s="16"/>
+      <c r="A592" s="23"/>
+      <c r="B592" s="23"/>
+      <c r="C592" s="23"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="A593" s="16"/>
-      <c r="B593" s="16"/>
-      <c r="C593" s="16"/>
+      <c r="A593" s="23"/>
+      <c r="B593" s="23"/>
+      <c r="C593" s="23"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="A594" s="16"/>
-      <c r="B594" s="16"/>
-      <c r="C594" s="16"/>
+      <c r="A594" s="23"/>
+      <c r="B594" s="23"/>
+      <c r="C594" s="23"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="A595" s="16"/>
-      <c r="B595" s="16"/>
-      <c r="C595" s="16"/>
+      <c r="A595" s="23"/>
+      <c r="B595" s="23"/>
+      <c r="C595" s="23"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="A596" s="16"/>
-      <c r="B596" s="16"/>
-      <c r="C596" s="16"/>
+      <c r="A596" s="23"/>
+      <c r="B596" s="23"/>
+      <c r="C596" s="23"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="A597" s="16"/>
-      <c r="B597" s="16"/>
-      <c r="C597" s="16"/>
+      <c r="A597" s="23"/>
+      <c r="B597" s="23"/>
+      <c r="C597" s="23"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="A598" s="16"/>
-      <c r="B598" s="16"/>
-      <c r="C598" s="16"/>
+      <c r="A598" s="23"/>
+      <c r="B598" s="23"/>
+      <c r="C598" s="23"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="A599" s="16"/>
-      <c r="B599" s="16"/>
-      <c r="C599" s="16"/>
+      <c r="A599" s="23"/>
+      <c r="B599" s="23"/>
+      <c r="C599" s="23"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="A600" s="16"/>
-      <c r="B600" s="16"/>
-      <c r="C600" s="16"/>
+      <c r="A600" s="23"/>
+      <c r="B600" s="23"/>
+      <c r="C600" s="23"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="A601" s="16"/>
-      <c r="B601" s="16"/>
-      <c r="C601" s="16"/>
+      <c r="A601" s="23"/>
+      <c r="B601" s="23"/>
+      <c r="C601" s="23"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="A602" s="16"/>
-      <c r="B602" s="16"/>
-      <c r="C602" s="16"/>
+      <c r="A602" s="23"/>
+      <c r="B602" s="23"/>
+      <c r="C602" s="23"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="A603" s="16"/>
-      <c r="B603" s="16"/>
-      <c r="C603" s="16"/>
+      <c r="A603" s="23"/>
+      <c r="B603" s="23"/>
+      <c r="C603" s="23"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="A604" s="16"/>
-      <c r="B604" s="16"/>
-      <c r="C604" s="16"/>
+      <c r="A604" s="23"/>
+      <c r="B604" s="23"/>
+      <c r="C604" s="23"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="A605" s="16"/>
-      <c r="B605" s="16"/>
-      <c r="C605" s="16"/>
+      <c r="A605" s="23"/>
+      <c r="B605" s="23"/>
+      <c r="C605" s="23"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="A606" s="16"/>
-      <c r="B606" s="16"/>
-      <c r="C606" s="16"/>
+      <c r="A606" s="23"/>
+      <c r="B606" s="23"/>
+      <c r="C606" s="23"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="A607" s="16"/>
-      <c r="B607" s="16"/>
-      <c r="C607" s="16"/>
+      <c r="A607" s="23"/>
+      <c r="B607" s="23"/>
+      <c r="C607" s="23"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="A608" s="16"/>
-      <c r="B608" s="16"/>
-      <c r="C608" s="16"/>
+      <c r="A608" s="23"/>
+      <c r="B608" s="23"/>
+      <c r="C608" s="23"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="A609" s="16"/>
-      <c r="B609" s="16"/>
-      <c r="C609" s="16"/>
+      <c r="A609" s="23"/>
+      <c r="B609" s="23"/>
+      <c r="C609" s="23"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="A610" s="16"/>
-      <c r="B610" s="16"/>
-      <c r="C610" s="16"/>
+      <c r="A610" s="23"/>
+      <c r="B610" s="23"/>
+      <c r="C610" s="23"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="A611" s="16"/>
-      <c r="B611" s="16"/>
-      <c r="C611" s="16"/>
+      <c r="A611" s="23"/>
+      <c r="B611" s="23"/>
+      <c r="C611" s="23"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="A612" s="16"/>
-      <c r="B612" s="16"/>
-      <c r="C612" s="16"/>
+      <c r="A612" s="23"/>
+      <c r="B612" s="23"/>
+      <c r="C612" s="23"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="A613" s="16"/>
-      <c r="B613" s="16"/>
-      <c r="C613" s="16"/>
+      <c r="A613" s="23"/>
+      <c r="B613" s="23"/>
+      <c r="C613" s="23"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="A614" s="16"/>
-      <c r="B614" s="16"/>
-      <c r="C614" s="16"/>
+      <c r="A614" s="23"/>
+      <c r="B614" s="23"/>
+      <c r="C614" s="23"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="A615" s="16"/>
-      <c r="B615" s="16"/>
-      <c r="C615" s="16"/>
+      <c r="A615" s="23"/>
+      <c r="B615" s="23"/>
+      <c r="C615" s="23"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="A616" s="16"/>
-      <c r="B616" s="16"/>
-      <c r="C616" s="16"/>
+      <c r="A616" s="23"/>
+      <c r="B616" s="23"/>
+      <c r="C616" s="23"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="A617" s="16"/>
-      <c r="B617" s="16"/>
-      <c r="C617" s="16"/>
+      <c r="A617" s="23"/>
+      <c r="B617" s="23"/>
+      <c r="C617" s="23"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="A618" s="16"/>
-      <c r="B618" s="16"/>
-      <c r="C618" s="16"/>
+      <c r="A618" s="23"/>
+      <c r="B618" s="23"/>
+      <c r="C618" s="23"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="A619" s="16"/>
-      <c r="B619" s="16"/>
-      <c r="C619" s="16"/>
+      <c r="A619" s="23"/>
+      <c r="B619" s="23"/>
+      <c r="C619" s="23"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="A620" s="16"/>
-      <c r="B620" s="16"/>
-      <c r="C620" s="16"/>
+      <c r="A620" s="23"/>
+      <c r="B620" s="23"/>
+      <c r="C620" s="23"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="A621" s="16"/>
-      <c r="B621" s="16"/>
-      <c r="C621" s="16"/>
+      <c r="A621" s="23"/>
+      <c r="B621" s="23"/>
+      <c r="C621" s="23"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="A622" s="16"/>
-      <c r="B622" s="16"/>
-      <c r="C622" s="16"/>
+      <c r="A622" s="23"/>
+      <c r="B622" s="23"/>
+      <c r="C622" s="23"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="A623" s="16"/>
-      <c r="B623" s="16"/>
-      <c r="C623" s="16"/>
+      <c r="A623" s="23"/>
+      <c r="B623" s="23"/>
+      <c r="C623" s="23"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="A624" s="16"/>
-      <c r="B624" s="16"/>
-      <c r="C624" s="16"/>
+      <c r="A624" s="23"/>
+      <c r="B624" s="23"/>
+      <c r="C624" s="23"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="A625" s="16"/>
-      <c r="B625" s="16"/>
-      <c r="C625" s="16"/>
+      <c r="A625" s="23"/>
+      <c r="B625" s="23"/>
+      <c r="C625" s="23"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="A626" s="16"/>
-      <c r="B626" s="16"/>
-      <c r="C626" s="16"/>
+      <c r="A626" s="23"/>
+      <c r="B626" s="23"/>
+      <c r="C626" s="23"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="A627" s="16"/>
-      <c r="B627" s="16"/>
-      <c r="C627" s="16"/>
+      <c r="A627" s="23"/>
+      <c r="B627" s="23"/>
+      <c r="C627" s="23"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="A628" s="16"/>
-      <c r="B628" s="16"/>
-      <c r="C628" s="16"/>
+      <c r="A628" s="23"/>
+      <c r="B628" s="23"/>
+      <c r="C628" s="23"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="A629" s="16"/>
-      <c r="B629" s="16"/>
-      <c r="C629" s="16"/>
+      <c r="A629" s="23"/>
+      <c r="B629" s="23"/>
+      <c r="C629" s="23"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="A630" s="16"/>
-      <c r="B630" s="16"/>
-      <c r="C630" s="16"/>
+      <c r="A630" s="23"/>
+      <c r="B630" s="23"/>
+      <c r="C630" s="23"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="A631" s="16"/>
-      <c r="B631" s="16"/>
-      <c r="C631" s="16"/>
+      <c r="A631" s="23"/>
+      <c r="B631" s="23"/>
+      <c r="C631" s="23"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="A632" s="16"/>
-      <c r="B632" s="16"/>
-      <c r="C632" s="16"/>
+      <c r="A632" s="23"/>
+      <c r="B632" s="23"/>
+      <c r="C632" s="23"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="A633" s="16"/>
-      <c r="B633" s="16"/>
-      <c r="C633" s="16"/>
+      <c r="A633" s="23"/>
+      <c r="B633" s="23"/>
+      <c r="C633" s="23"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="A634" s="16"/>
-      <c r="B634" s="16"/>
-      <c r="C634" s="16"/>
+      <c r="A634" s="23"/>
+      <c r="B634" s="23"/>
+      <c r="C634" s="23"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="A635" s="16"/>
-      <c r="B635" s="16"/>
-      <c r="C635" s="16"/>
+      <c r="A635" s="23"/>
+      <c r="B635" s="23"/>
+      <c r="C635" s="23"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="A636" s="16"/>
-      <c r="B636" s="16"/>
-      <c r="C636" s="16"/>
+      <c r="A636" s="23"/>
+      <c r="B636" s="23"/>
+      <c r="C636" s="23"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="A637" s="16"/>
-      <c r="B637" s="16"/>
-      <c r="C637" s="16"/>
+      <c r="A637" s="23"/>
+      <c r="B637" s="23"/>
+      <c r="C637" s="23"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="A638" s="16"/>
-      <c r="B638" s="16"/>
-      <c r="C638" s="16"/>
+      <c r="A638" s="23"/>
+      <c r="B638" s="23"/>
+      <c r="C638" s="23"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="A639" s="16"/>
-      <c r="B639" s="16"/>
-      <c r="C639" s="16"/>
+      <c r="A639" s="23"/>
+      <c r="B639" s="23"/>
+      <c r="C639" s="23"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="A640" s="16"/>
-      <c r="B640" s="16"/>
-      <c r="C640" s="16"/>
+      <c r="A640" s="23"/>
+      <c r="B640" s="23"/>
+      <c r="C640" s="23"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="A641" s="16"/>
-      <c r="B641" s="16"/>
-      <c r="C641" s="16"/>
+      <c r="A641" s="23"/>
+      <c r="B641" s="23"/>
+      <c r="C641" s="23"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="A642" s="16"/>
-      <c r="B642" s="16"/>
-      <c r="C642" s="16"/>
+      <c r="A642" s="23"/>
+      <c r="B642" s="23"/>
+      <c r="C642" s="23"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="A643" s="16"/>
-      <c r="B643" s="16"/>
-      <c r="C643" s="16"/>
+      <c r="A643" s="23"/>
+      <c r="B643" s="23"/>
+      <c r="C643" s="23"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="A644" s="16"/>
-      <c r="B644" s="16"/>
-      <c r="C644" s="16"/>
+      <c r="A644" s="23"/>
+      <c r="B644" s="23"/>
+      <c r="C644" s="23"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="A645" s="16"/>
-      <c r="B645" s="16"/>
-      <c r="C645" s="16"/>
+      <c r="A645" s="23"/>
+      <c r="B645" s="23"/>
+      <c r="C645" s="23"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="A646" s="16"/>
-      <c r="B646" s="16"/>
-      <c r="C646" s="16"/>
+      <c r="A646" s="23"/>
+      <c r="B646" s="23"/>
+      <c r="C646" s="23"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="A647" s="16"/>
-      <c r="B647" s="16"/>
-      <c r="C647" s="16"/>
+      <c r="A647" s="23"/>
+      <c r="B647" s="23"/>
+      <c r="C647" s="23"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="A648" s="16"/>
-      <c r="B648" s="16"/>
-      <c r="C648" s="16"/>
+      <c r="A648" s="23"/>
+      <c r="B648" s="23"/>
+      <c r="C648" s="23"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="A649" s="16"/>
-      <c r="B649" s="16"/>
-      <c r="C649" s="16"/>
+      <c r="A649" s="23"/>
+      <c r="B649" s="23"/>
+      <c r="C649" s="23"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="A650" s="16"/>
-      <c r="B650" s="16"/>
-      <c r="C650" s="16"/>
+      <c r="A650" s="23"/>
+      <c r="B650" s="23"/>
+      <c r="C650" s="23"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="A651" s="16"/>
-      <c r="B651" s="16"/>
-      <c r="C651" s="16"/>
+      <c r="A651" s="23"/>
+      <c r="B651" s="23"/>
+      <c r="C651" s="23"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="A652" s="16"/>
-      <c r="B652" s="16"/>
-      <c r="C652" s="16"/>
+      <c r="A652" s="23"/>
+      <c r="B652" s="23"/>
+      <c r="C652" s="23"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="A653" s="16"/>
-      <c r="B653" s="16"/>
-      <c r="C653" s="16"/>
+      <c r="A653" s="23"/>
+      <c r="B653" s="23"/>
+      <c r="C653" s="23"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="A654" s="16"/>
-      <c r="B654" s="16"/>
-      <c r="C654" s="16"/>
+      <c r="A654" s="23"/>
+      <c r="B654" s="23"/>
+      <c r="C654" s="23"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="A655" s="16"/>
-      <c r="B655" s="16"/>
-      <c r="C655" s="16"/>
+      <c r="A655" s="23"/>
+      <c r="B655" s="23"/>
+      <c r="C655" s="23"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="A656" s="16"/>
-      <c r="B656" s="16"/>
-      <c r="C656" s="16"/>
+      <c r="A656" s="23"/>
+      <c r="B656" s="23"/>
+      <c r="C656" s="23"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="A657" s="16"/>
-      <c r="B657" s="16"/>
-      <c r="C657" s="16"/>
+      <c r="A657" s="23"/>
+      <c r="B657" s="23"/>
+      <c r="C657" s="23"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="A658" s="16"/>
-      <c r="B658" s="16"/>
-      <c r="C658" s="16"/>
+      <c r="A658" s="23"/>
+      <c r="B658" s="23"/>
+      <c r="C658" s="23"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="A659" s="16"/>
-      <c r="B659" s="16"/>
-      <c r="C659" s="16"/>
+      <c r="A659" s="23"/>
+      <c r="B659" s="23"/>
+      <c r="C659" s="23"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="A660" s="16"/>
-      <c r="B660" s="16"/>
-      <c r="C660" s="16"/>
+      <c r="A660" s="23"/>
+      <c r="B660" s="23"/>
+      <c r="C660" s="23"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="A661" s="16"/>
-      <c r="B661" s="16"/>
-      <c r="C661" s="16"/>
+      <c r="A661" s="23"/>
+      <c r="B661" s="23"/>
+      <c r="C661" s="23"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="A662" s="16"/>
-      <c r="B662" s="16"/>
-      <c r="C662" s="16"/>
+      <c r="A662" s="23"/>
+      <c r="B662" s="23"/>
+      <c r="C662" s="23"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="A663" s="16"/>
-      <c r="B663" s="16"/>
-      <c r="C663" s="16"/>
+      <c r="A663" s="23"/>
+      <c r="B663" s="23"/>
+      <c r="C663" s="23"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="A664" s="16"/>
-      <c r="B664" s="16"/>
-      <c r="C664" s="16"/>
+      <c r="A664" s="23"/>
+      <c r="B664" s="23"/>
+      <c r="C664" s="23"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="A665" s="16"/>
-      <c r="B665" s="16"/>
-      <c r="C665" s="16"/>
+      <c r="A665" s="23"/>
+      <c r="B665" s="23"/>
+      <c r="C665" s="23"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="A666" s="16"/>
-      <c r="B666" s="16"/>
-      <c r="C666" s="16"/>
+      <c r="A666" s="23"/>
+      <c r="B666" s="23"/>
+      <c r="C666" s="23"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="A667" s="16"/>
-      <c r="B667" s="16"/>
-      <c r="C667" s="16"/>
+      <c r="A667" s="23"/>
+      <c r="B667" s="23"/>
+      <c r="C667" s="23"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="A668" s="16"/>
-      <c r="B668" s="16"/>
-      <c r="C668" s="16"/>
+      <c r="A668" s="23"/>
+      <c r="B668" s="23"/>
+      <c r="C668" s="23"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="A669" s="16"/>
-      <c r="B669" s="16"/>
-      <c r="C669" s="16"/>
+      <c r="A669" s="23"/>
+      <c r="B669" s="23"/>
+      <c r="C669" s="23"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="A670" s="16"/>
-      <c r="B670" s="16"/>
-      <c r="C670" s="16"/>
+      <c r="A670" s="23"/>
+      <c r="B670" s="23"/>
+      <c r="C670" s="23"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="A671" s="16"/>
-      <c r="B671" s="16"/>
-      <c r="C671" s="16"/>
+      <c r="A671" s="23"/>
+      <c r="B671" s="23"/>
+      <c r="C671" s="23"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="A672" s="16"/>
-      <c r="B672" s="16"/>
-      <c r="C672" s="16"/>
+      <c r="A672" s="23"/>
+      <c r="B672" s="23"/>
+      <c r="C672" s="23"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="A673" s="16"/>
-      <c r="B673" s="16"/>
-      <c r="C673" s="16"/>
+      <c r="A673" s="23"/>
+      <c r="B673" s="23"/>
+      <c r="C673" s="23"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="A674" s="16"/>
-      <c r="B674" s="16"/>
-      <c r="C674" s="16"/>
+      <c r="A674" s="23"/>
+      <c r="B674" s="23"/>
+      <c r="C674" s="23"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="A675" s="16"/>
-      <c r="B675" s="16"/>
-      <c r="C675" s="16"/>
+      <c r="A675" s="23"/>
+      <c r="B675" s="23"/>
+      <c r="C675" s="23"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="A676" s="16"/>
-      <c r="B676" s="16"/>
-      <c r="C676" s="16"/>
+      <c r="A676" s="23"/>
+      <c r="B676" s="23"/>
+      <c r="C676" s="23"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="A677" s="16"/>
-      <c r="B677" s="16"/>
-      <c r="C677" s="16"/>
+      <c r="A677" s="23"/>
+      <c r="B677" s="23"/>
+      <c r="C677" s="23"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="A678" s="16"/>
-      <c r="B678" s="16"/>
-      <c r="C678" s="16"/>
+      <c r="A678" s="23"/>
+      <c r="B678" s="23"/>
+      <c r="C678" s="23"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="A679" s="16"/>
-      <c r="B679" s="16"/>
-      <c r="C679" s="16"/>
+      <c r="A679" s="23"/>
+      <c r="B679" s="23"/>
+      <c r="C679" s="23"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="A680" s="16"/>
-      <c r="B680" s="16"/>
-      <c r="C680" s="16"/>
+      <c r="A680" s="23"/>
+      <c r="B680" s="23"/>
+      <c r="C680" s="23"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="A681" s="16"/>
-      <c r="B681" s="16"/>
-      <c r="C681" s="16"/>
+      <c r="A681" s="23"/>
+      <c r="B681" s="23"/>
+      <c r="C681" s="23"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="A682" s="16"/>
-      <c r="B682" s="16"/>
-      <c r="C682" s="16"/>
+      <c r="A682" s="23"/>
+      <c r="B682" s="23"/>
+      <c r="C682" s="23"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="A683" s="16"/>
-      <c r="B683" s="16"/>
-      <c r="C683" s="16"/>
+      <c r="A683" s="23"/>
+      <c r="B683" s="23"/>
+      <c r="C683" s="23"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="A684" s="16"/>
-      <c r="B684" s="16"/>
-      <c r="C684" s="16"/>
+      <c r="A684" s="23"/>
+      <c r="B684" s="23"/>
+      <c r="C684" s="23"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="A685" s="16"/>
-      <c r="B685" s="16"/>
-      <c r="C685" s="16"/>
+      <c r="A685" s="23"/>
+      <c r="B685" s="23"/>
+      <c r="C685" s="23"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="A686" s="16"/>
-      <c r="B686" s="16"/>
-      <c r="C686" s="16"/>
+      <c r="A686" s="23"/>
+      <c r="B686" s="23"/>
+      <c r="C686" s="23"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="A687" s="16"/>
-      <c r="B687" s="16"/>
-      <c r="C687" s="16"/>
+      <c r="A687" s="23"/>
+      <c r="B687" s="23"/>
+      <c r="C687" s="23"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="A688" s="16"/>
-      <c r="B688" s="16"/>
-      <c r="C688" s="16"/>
+      <c r="A688" s="23"/>
+      <c r="B688" s="23"/>
+      <c r="C688" s="23"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="A689" s="16"/>
-      <c r="B689" s="16"/>
-      <c r="C689" s="16"/>
+      <c r="A689" s="23"/>
+      <c r="B689" s="23"/>
+      <c r="C689" s="23"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="A690" s="16"/>
-      <c r="B690" s="16"/>
-      <c r="C690" s="16"/>
+      <c r="A690" s="23"/>
+      <c r="B690" s="23"/>
+      <c r="C690" s="23"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="A691" s="16"/>
-      <c r="B691" s="16"/>
-      <c r="C691" s="16"/>
+      <c r="A691" s="23"/>
+      <c r="B691" s="23"/>
+      <c r="C691" s="23"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="A692" s="16"/>
-      <c r="B692" s="16"/>
-      <c r="C692" s="16"/>
+      <c r="A692" s="23"/>
+      <c r="B692" s="23"/>
+      <c r="C692" s="23"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="A693" s="16"/>
-      <c r="B693" s="16"/>
-      <c r="C693" s="16"/>
+      <c r="A693" s="23"/>
+      <c r="B693" s="23"/>
+      <c r="C693" s="23"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="A694" s="16"/>
-      <c r="B694" s="16"/>
-      <c r="C694" s="16"/>
+      <c r="A694" s="23"/>
+      <c r="B694" s="23"/>
+      <c r="C694" s="23"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="A695" s="16"/>
-      <c r="B695" s="16"/>
-      <c r="C695" s="16"/>
+      <c r="A695" s="23"/>
+      <c r="B695" s="23"/>
+      <c r="C695" s="23"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="A696" s="16"/>
-      <c r="B696" s="16"/>
-      <c r="C696" s="16"/>
+      <c r="A696" s="23"/>
+      <c r="B696" s="23"/>
+      <c r="C696" s="23"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="A697" s="16"/>
-      <c r="B697" s="16"/>
-      <c r="C697" s="16"/>
+      <c r="A697" s="23"/>
+      <c r="B697" s="23"/>
+      <c r="C697" s="23"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="A698" s="16"/>
-      <c r="B698" s="16"/>
-      <c r="C698" s="16"/>
+      <c r="A698" s="23"/>
+      <c r="B698" s="23"/>
+      <c r="C698" s="23"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="A699" s="16"/>
-      <c r="B699" s="16"/>
-      <c r="C699" s="16"/>
+      <c r="A699" s="23"/>
+      <c r="B699" s="23"/>
+      <c r="C699" s="23"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="A700" s="16"/>
-      <c r="B700" s="16"/>
-      <c r="C700" s="16"/>
+      <c r="A700" s="23"/>
+      <c r="B700" s="23"/>
+      <c r="C700" s="23"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="A701" s="16"/>
-      <c r="B701" s="16"/>
-      <c r="C701" s="16"/>
+      <c r="A701" s="23"/>
+      <c r="B701" s="23"/>
+      <c r="C701" s="23"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="A702" s="16"/>
-      <c r="B702" s="16"/>
-      <c r="C702" s="16"/>
+      <c r="A702" s="23"/>
+      <c r="B702" s="23"/>
+      <c r="C702" s="23"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="A703" s="16"/>
-      <c r="B703" s="16"/>
-      <c r="C703" s="16"/>
+      <c r="A703" s="23"/>
+      <c r="B703" s="23"/>
+      <c r="C703" s="23"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="A704" s="16"/>
-      <c r="B704" s="16"/>
-      <c r="C704" s="16"/>
+      <c r="A704" s="23"/>
+      <c r="B704" s="23"/>
+      <c r="C704" s="23"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="A705" s="16"/>
-      <c r="B705" s="16"/>
-      <c r="C705" s="16"/>
+      <c r="A705" s="23"/>
+      <c r="B705" s="23"/>
+      <c r="C705" s="23"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="A706" s="16"/>
-      <c r="B706" s="16"/>
-      <c r="C706" s="16"/>
+      <c r="A706" s="23"/>
+      <c r="B706" s="23"/>
+      <c r="C706" s="23"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="A707" s="16"/>
-      <c r="B707" s="16"/>
-      <c r="C707" s="16"/>
+      <c r="A707" s="23"/>
+      <c r="B707" s="23"/>
+      <c r="C707" s="23"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="16"/>
-      <c r="B708" s="16"/>
-      <c r="C708" s="16"/>
+      <c r="A708" s="23"/>
+      <c r="B708" s="23"/>
+      <c r="C708" s="23"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="A709" s="16"/>
-      <c r="B709" s="16"/>
-      <c r="C709" s="16"/>
+      <c r="A709" s="23"/>
+      <c r="B709" s="23"/>
+      <c r="C709" s="23"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="A710" s="16"/>
-      <c r="B710" s="16"/>
-      <c r="C710" s="16"/>
+      <c r="A710" s="23"/>
+      <c r="B710" s="23"/>
+      <c r="C710" s="23"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="A711" s="16"/>
-      <c r="B711" s="16"/>
-      <c r="C711" s="16"/>
+      <c r="A711" s="23"/>
+      <c r="B711" s="23"/>
+      <c r="C711" s="23"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="A712" s="16"/>
-      <c r="B712" s="16"/>
-      <c r="C712" s="16"/>
+      <c r="A712" s="23"/>
+      <c r="B712" s="23"/>
+      <c r="C712" s="23"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="A713" s="16"/>
-      <c r="B713" s="16"/>
-      <c r="C713" s="16"/>
+      <c r="A713" s="23"/>
+      <c r="B713" s="23"/>
+      <c r="C713" s="23"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="A714" s="16"/>
-      <c r="B714" s="16"/>
-      <c r="C714" s="16"/>
+      <c r="A714" s="23"/>
+      <c r="B714" s="23"/>
+      <c r="C714" s="23"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="A715" s="16"/>
-      <c r="B715" s="16"/>
-      <c r="C715" s="16"/>
+      <c r="A715" s="23"/>
+      <c r="B715" s="23"/>
+      <c r="C715" s="23"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="A716" s="16"/>
-      <c r="B716" s="16"/>
-      <c r="C716" s="16"/>
+      <c r="A716" s="23"/>
+      <c r="B716" s="23"/>
+      <c r="C716" s="23"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="A717" s="16"/>
-      <c r="B717" s="16"/>
-      <c r="C717" s="16"/>
+      <c r="A717" s="23"/>
+      <c r="B717" s="23"/>
+      <c r="C717" s="23"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="A718" s="16"/>
-      <c r="B718" s="16"/>
-      <c r="C718" s="16"/>
+      <c r="A718" s="23"/>
+      <c r="B718" s="23"/>
+      <c r="C718" s="23"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="A719" s="16"/>
-      <c r="B719" s="16"/>
-      <c r="C719" s="16"/>
+      <c r="A719" s="23"/>
+      <c r="B719" s="23"/>
+      <c r="C719" s="23"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="A720" s="16"/>
-      <c r="B720" s="16"/>
-      <c r="C720" s="16"/>
+      <c r="A720" s="23"/>
+      <c r="B720" s="23"/>
+      <c r="C720" s="23"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="A721" s="16"/>
-      <c r="B721" s="16"/>
-      <c r="C721" s="16"/>
+      <c r="A721" s="23"/>
+      <c r="B721" s="23"/>
+      <c r="C721" s="23"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="A722" s="16"/>
-      <c r="B722" s="16"/>
-      <c r="C722" s="16"/>
+      <c r="A722" s="23"/>
+      <c r="B722" s="23"/>
+      <c r="C722" s="23"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="A723" s="16"/>
-      <c r="B723" s="16"/>
-      <c r="C723" s="16"/>
+      <c r="A723" s="23"/>
+      <c r="B723" s="23"/>
+      <c r="C723" s="23"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="A724" s="16"/>
-      <c r="B724" s="16"/>
-      <c r="C724" s="16"/>
+      <c r="A724" s="23"/>
+      <c r="B724" s="23"/>
+      <c r="C724" s="23"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="A725" s="16"/>
-      <c r="B725" s="16"/>
-      <c r="C725" s="16"/>
+      <c r="A725" s="23"/>
+      <c r="B725" s="23"/>
+      <c r="C725" s="23"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="A726" s="16"/>
-      <c r="B726" s="16"/>
-      <c r="C726" s="16"/>
+      <c r="A726" s="23"/>
+      <c r="B726" s="23"/>
+      <c r="C726" s="23"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="A727" s="16"/>
-      <c r="B727" s="16"/>
-      <c r="C727" s="16"/>
+      <c r="A727" s="23"/>
+      <c r="B727" s="23"/>
+      <c r="C727" s="23"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="A728" s="16"/>
-      <c r="B728" s="16"/>
-      <c r="C728" s="16"/>
+      <c r="A728" s="23"/>
+      <c r="B728" s="23"/>
+      <c r="C728" s="23"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="A729" s="16"/>
-      <c r="B729" s="16"/>
-      <c r="C729" s="16"/>
+      <c r="A729" s="23"/>
+      <c r="B729" s="23"/>
+      <c r="C729" s="23"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="A730" s="16"/>
-      <c r="B730" s="16"/>
-      <c r="C730" s="16"/>
+      <c r="A730" s="23"/>
+      <c r="B730" s="23"/>
+      <c r="C730" s="23"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="A731" s="16"/>
-      <c r="B731" s="16"/>
-      <c r="C731" s="16"/>
+      <c r="A731" s="23"/>
+      <c r="B731" s="23"/>
+      <c r="C731" s="23"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="A732" s="16"/>
-      <c r="B732" s="16"/>
-      <c r="C732" s="16"/>
+      <c r="A732" s="23"/>
+      <c r="B732" s="23"/>
+      <c r="C732" s="23"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="A733" s="16"/>
-      <c r="B733" s="16"/>
-      <c r="C733" s="16"/>
+      <c r="A733" s="23"/>
+      <c r="B733" s="23"/>
+      <c r="C733" s="23"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="A734" s="16"/>
-      <c r="B734" s="16"/>
-      <c r="C734" s="16"/>
+      <c r="A734" s="23"/>
+      <c r="B734" s="23"/>
+      <c r="C734" s="23"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="A735" s="16"/>
-      <c r="B735" s="16"/>
-      <c r="C735" s="16"/>
+      <c r="A735" s="23"/>
+      <c r="B735" s="23"/>
+      <c r="C735" s="23"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="A736" s="16"/>
-      <c r="B736" s="16"/>
-      <c r="C736" s="16"/>
+      <c r="A736" s="23"/>
+      <c r="B736" s="23"/>
+      <c r="C736" s="23"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="A737" s="16"/>
-      <c r="B737" s="16"/>
-      <c r="C737" s="16"/>
+      <c r="A737" s="23"/>
+      <c r="B737" s="23"/>
+      <c r="C737" s="23"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="A738" s="16"/>
-      <c r="B738" s="16"/>
-      <c r="C738" s="16"/>
+      <c r="A738" s="23"/>
+      <c r="B738" s="23"/>
+      <c r="C738" s="23"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="A739" s="16"/>
-      <c r="B739" s="16"/>
-      <c r="C739" s="16"/>
+      <c r="A739" s="23"/>
+      <c r="B739" s="23"/>
+      <c r="C739" s="23"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="A740" s="16"/>
-      <c r="B740" s="16"/>
-      <c r="C740" s="16"/>
+      <c r="A740" s="23"/>
+      <c r="B740" s="23"/>
+      <c r="C740" s="23"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="A741" s="16"/>
-      <c r="B741" s="16"/>
-      <c r="C741" s="16"/>
+      <c r="A741" s="23"/>
+      <c r="B741" s="23"/>
+      <c r="C741" s="23"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="A742" s="16"/>
-      <c r="B742" s="16"/>
-      <c r="C742" s="16"/>
+      <c r="A742" s="23"/>
+      <c r="B742" s="23"/>
+      <c r="C742" s="23"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="A743" s="16"/>
-      <c r="B743" s="16"/>
-      <c r="C743" s="16"/>
+      <c r="A743" s="23"/>
+      <c r="B743" s="23"/>
+      <c r="C743" s="23"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="A744" s="16"/>
-      <c r="B744" s="16"/>
-      <c r="C744" s="16"/>
+      <c r="A744" s="23"/>
+      <c r="B744" s="23"/>
+      <c r="C744" s="23"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="A745" s="16"/>
-      <c r="B745" s="16"/>
-      <c r="C745" s="16"/>
+      <c r="A745" s="23"/>
+      <c r="B745" s="23"/>
+      <c r="C745" s="23"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="A746" s="16"/>
-      <c r="B746" s="16"/>
-      <c r="C746" s="16"/>
+      <c r="A746" s="23"/>
+      <c r="B746" s="23"/>
+      <c r="C746" s="23"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="A747" s="16"/>
-      <c r="B747" s="16"/>
-      <c r="C747" s="16"/>
+      <c r="A747" s="23"/>
+      <c r="B747" s="23"/>
+      <c r="C747" s="23"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="A748" s="16"/>
-      <c r="B748" s="16"/>
-      <c r="C748" s="16"/>
+      <c r="A748" s="23"/>
+      <c r="B748" s="23"/>
+      <c r="C748" s="23"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="A749" s="16"/>
-      <c r="B749" s="16"/>
-      <c r="C749" s="16"/>
+      <c r="A749" s="23"/>
+      <c r="B749" s="23"/>
+      <c r="C749" s="23"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="A750" s="16"/>
-      <c r="B750" s="16"/>
-      <c r="C750" s="16"/>
+      <c r="A750" s="23"/>
+      <c r="B750" s="23"/>
+      <c r="C750" s="23"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="A751" s="16"/>
-      <c r="B751" s="16"/>
-      <c r="C751" s="16"/>
+      <c r="A751" s="23"/>
+      <c r="B751" s="23"/>
+      <c r="C751" s="23"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="A752" s="16"/>
-      <c r="B752" s="16"/>
-      <c r="C752" s="16"/>
+      <c r="A752" s="23"/>
+      <c r="B752" s="23"/>
+      <c r="C752" s="23"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="A753" s="16"/>
-      <c r="B753" s="16"/>
-      <c r="C753" s="16"/>
+      <c r="A753" s="23"/>
+      <c r="B753" s="23"/>
+      <c r="C753" s="23"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="A754" s="16"/>
-      <c r="B754" s="16"/>
-      <c r="C754" s="16"/>
+      <c r="A754" s="23"/>
+      <c r="B754" s="23"/>
+      <c r="C754" s="23"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="A755" s="16"/>
-      <c r="B755" s="16"/>
-      <c r="C755" s="16"/>
+      <c r="A755" s="23"/>
+      <c r="B755" s="23"/>
+      <c r="C755" s="23"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="A756" s="16"/>
-      <c r="B756" s="16"/>
-      <c r="C756" s="16"/>
+      <c r="A756" s="23"/>
+      <c r="B756" s="23"/>
+      <c r="C756" s="23"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="A757" s="16"/>
-      <c r="B757" s="16"/>
-      <c r="C757" s="16"/>
+      <c r="A757" s="23"/>
+      <c r="B757" s="23"/>
+      <c r="C757" s="23"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="A758" s="16"/>
-      <c r="B758" s="16"/>
-      <c r="C758" s="16"/>
+      <c r="A758" s="23"/>
+      <c r="B758" s="23"/>
+      <c r="C758" s="23"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="A759" s="16"/>
-      <c r="B759" s="16"/>
-      <c r="C759" s="16"/>
+      <c r="A759" s="23"/>
+      <c r="B759" s="23"/>
+      <c r="C759" s="23"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="A760" s="16"/>
-      <c r="B760" s="16"/>
-      <c r="C760" s="16"/>
+      <c r="A760" s="23"/>
+      <c r="B760" s="23"/>
+      <c r="C760" s="23"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="A761" s="16"/>
-      <c r="B761" s="16"/>
-      <c r="C761" s="16"/>
+      <c r="A761" s="23"/>
+      <c r="B761" s="23"/>
+      <c r="C761" s="23"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="A762" s="16"/>
-      <c r="B762" s="16"/>
-      <c r="C762" s="16"/>
+      <c r="A762" s="23"/>
+      <c r="B762" s="23"/>
+      <c r="C762" s="23"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="A763" s="16"/>
-      <c r="B763" s="16"/>
-      <c r="C763" s="16"/>
+      <c r="A763" s="23"/>
+      <c r="B763" s="23"/>
+      <c r="C763" s="23"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="A764" s="16"/>
-      <c r="B764" s="16"/>
-      <c r="C764" s="16"/>
+      <c r="A764" s="23"/>
+      <c r="B764" s="23"/>
+      <c r="C764" s="23"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="A765" s="16"/>
-      <c r="B765" s="16"/>
-      <c r="C765" s="16"/>
+      <c r="A765" s="23"/>
+      <c r="B765" s="23"/>
+      <c r="C765" s="23"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="A766" s="16"/>
-      <c r="B766" s="16"/>
-      <c r="C766" s="16"/>
+      <c r="A766" s="23"/>
+      <c r="B766" s="23"/>
+      <c r="C766" s="23"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="A767" s="16"/>
-      <c r="B767" s="16"/>
-      <c r="C767" s="16"/>
+      <c r="A767" s="23"/>
+      <c r="B767" s="23"/>
+      <c r="C767" s="23"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="A768" s="16"/>
-      <c r="B768" s="16"/>
-      <c r="C768" s="16"/>
+      <c r="A768" s="23"/>
+      <c r="B768" s="23"/>
+      <c r="C768" s="23"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="A769" s="16"/>
-      <c r="B769" s="16"/>
-      <c r="C769" s="16"/>
+      <c r="A769" s="23"/>
+      <c r="B769" s="23"/>
+      <c r="C769" s="23"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="A770" s="16"/>
-      <c r="B770" s="16"/>
-      <c r="C770" s="16"/>
+      <c r="A770" s="23"/>
+      <c r="B770" s="23"/>
+      <c r="C770" s="23"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="A771" s="16"/>
-      <c r="B771" s="16"/>
-      <c r="C771" s="16"/>
+      <c r="A771" s="23"/>
+      <c r="B771" s="23"/>
+      <c r="C771" s="23"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="A772" s="16"/>
-      <c r="B772" s="16"/>
-      <c r="C772" s="16"/>
+      <c r="A772" s="23"/>
+      <c r="B772" s="23"/>
+      <c r="C772" s="23"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="A773" s="16"/>
-      <c r="B773" s="16"/>
-      <c r="C773" s="16"/>
+      <c r="A773" s="23"/>
+      <c r="B773" s="23"/>
+      <c r="C773" s="23"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="A774" s="16"/>
-      <c r="B774" s="16"/>
-      <c r="C774" s="16"/>
+      <c r="A774" s="23"/>
+      <c r="B774" s="23"/>
+      <c r="C774" s="23"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="A775" s="16"/>
-      <c r="B775" s="16"/>
-      <c r="C775" s="16"/>
+      <c r="A775" s="23"/>
+      <c r="B775" s="23"/>
+      <c r="C775" s="23"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="A776" s="16"/>
-      <c r="B776" s="16"/>
-      <c r="C776" s="16"/>
+      <c r="A776" s="23"/>
+      <c r="B776" s="23"/>
+      <c r="C776" s="23"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="A777" s="16"/>
-      <c r="B777" s="16"/>
-      <c r="C777" s="16"/>
+      <c r="A777" s="23"/>
+      <c r="B777" s="23"/>
+      <c r="C777" s="23"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="A778" s="16"/>
-      <c r="B778" s="16"/>
-      <c r="C778" s="16"/>
+      <c r="A778" s="23"/>
+      <c r="B778" s="23"/>
+      <c r="C778" s="23"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="A779" s="16"/>
-      <c r="B779" s="16"/>
-      <c r="C779" s="16"/>
+      <c r="A779" s="23"/>
+      <c r="B779" s="23"/>
+      <c r="C779" s="23"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="A780" s="16"/>
-      <c r="B780" s="16"/>
-      <c r="C780" s="16"/>
+      <c r="A780" s="23"/>
+      <c r="B780" s="23"/>
+      <c r="C780" s="23"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="A781" s="16"/>
-      <c r="B781" s="16"/>
-      <c r="C781" s="16"/>
+      <c r="A781" s="23"/>
+      <c r="B781" s="23"/>
+      <c r="C781" s="23"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="A782" s="16"/>
-      <c r="B782" s="16"/>
-      <c r="C782" s="16"/>
+      <c r="A782" s="23"/>
+      <c r="B782" s="23"/>
+      <c r="C782" s="23"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="A783" s="16"/>
-      <c r="B783" s="16"/>
-      <c r="C783" s="16"/>
+      <c r="A783" s="23"/>
+      <c r="B783" s="23"/>
+      <c r="C783" s="23"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="A784" s="16"/>
-      <c r="B784" s="16"/>
-      <c r="C784" s="16"/>
+      <c r="A784" s="23"/>
+      <c r="B784" s="23"/>
+      <c r="C784" s="23"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="A785" s="16"/>
-      <c r="B785" s="16"/>
-      <c r="C785" s="16"/>
+      <c r="A785" s="23"/>
+      <c r="B785" s="23"/>
+      <c r="C785" s="23"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="A786" s="16"/>
-      <c r="B786" s="16"/>
-      <c r="C786" s="16"/>
+      <c r="A786" s="23"/>
+      <c r="B786" s="23"/>
+      <c r="C786" s="23"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="A787" s="16"/>
-      <c r="B787" s="16"/>
-      <c r="C787" s="16"/>
+      <c r="A787" s="23"/>
+      <c r="B787" s="23"/>
+      <c r="C787" s="23"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="A788" s="16"/>
-      <c r="B788" s="16"/>
-      <c r="C788" s="16"/>
+      <c r="A788" s="23"/>
+      <c r="B788" s="23"/>
+      <c r="C788" s="23"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="A789" s="16"/>
-      <c r="B789" s="16"/>
-      <c r="C789" s="16"/>
+      <c r="A789" s="23"/>
+      <c r="B789" s="23"/>
+      <c r="C789" s="23"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="A790" s="16"/>
-      <c r="B790" s="16"/>
-      <c r="C790" s="16"/>
+      <c r="A790" s="23"/>
+      <c r="B790" s="23"/>
+      <c r="C790" s="23"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="A791" s="16"/>
-      <c r="B791" s="16"/>
-      <c r="C791" s="16"/>
+      <c r="A791" s="23"/>
+      <c r="B791" s="23"/>
+      <c r="C791" s="23"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="A792" s="16"/>
-      <c r="B792" s="16"/>
-      <c r="C792" s="16"/>
+      <c r="A792" s="23"/>
+      <c r="B792" s="23"/>
+      <c r="C792" s="23"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="A793" s="16"/>
-      <c r="B793" s="16"/>
-      <c r="C793" s="16"/>
+      <c r="A793" s="23"/>
+      <c r="B793" s="23"/>
+      <c r="C793" s="23"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="A794" s="16"/>
-      <c r="B794" s="16"/>
-      <c r="C794" s="16"/>
+      <c r="A794" s="23"/>
+      <c r="B794" s="23"/>
+      <c r="C794" s="23"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="A795" s="16"/>
-      <c r="B795" s="16"/>
-      <c r="C795" s="16"/>
+      <c r="A795" s="23"/>
+      <c r="B795" s="23"/>
+      <c r="C795" s="23"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="A796" s="16"/>
-      <c r="B796" s="16"/>
-      <c r="C796" s="16"/>
+      <c r="A796" s="23"/>
+      <c r="B796" s="23"/>
+      <c r="C796" s="23"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="A797" s="16"/>
-      <c r="B797" s="16"/>
-      <c r="C797" s="16"/>
+      <c r="A797" s="23"/>
+      <c r="B797" s="23"/>
+      <c r="C797" s="23"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="A798" s="16"/>
-      <c r="B798" s="16"/>
-      <c r="C798" s="16"/>
+      <c r="A798" s="23"/>
+      <c r="B798" s="23"/>
+      <c r="C798" s="23"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="A799" s="16"/>
-      <c r="B799" s="16"/>
-      <c r="C799" s="16"/>
+      <c r="A799" s="23"/>
+      <c r="B799" s="23"/>
+      <c r="C799" s="23"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="A800" s="16"/>
-      <c r="B800" s="16"/>
-      <c r="C800" s="16"/>
+      <c r="A800" s="23"/>
+      <c r="B800" s="23"/>
+      <c r="C800" s="23"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="A801" s="16"/>
-      <c r="B801" s="16"/>
-      <c r="C801" s="16"/>
+      <c r="A801" s="23"/>
+      <c r="B801" s="23"/>
+      <c r="C801" s="23"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="A802" s="16"/>
-      <c r="B802" s="16"/>
-      <c r="C802" s="16"/>
+      <c r="A802" s="23"/>
+      <c r="B802" s="23"/>
+      <c r="C802" s="23"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="A803" s="16"/>
-      <c r="B803" s="16"/>
-      <c r="C803" s="16"/>
+      <c r="A803" s="23"/>
+      <c r="B803" s="23"/>
+      <c r="C803" s="23"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="A804" s="16"/>
-      <c r="B804" s="16"/>
-      <c r="C804" s="16"/>
+      <c r="A804" s="23"/>
+      <c r="B804" s="23"/>
+      <c r="C804" s="23"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="A805" s="16"/>
-      <c r="B805" s="16"/>
-      <c r="C805" s="16"/>
+      <c r="A805" s="23"/>
+      <c r="B805" s="23"/>
+      <c r="C805" s="23"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="A806" s="16"/>
-      <c r="B806" s="16"/>
-      <c r="C806" s="16"/>
+      <c r="A806" s="23"/>
+      <c r="B806" s="23"/>
+      <c r="C806" s="23"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="A807" s="16"/>
-      <c r="B807" s="16"/>
-      <c r="C807" s="16"/>
+      <c r="A807" s="23"/>
+      <c r="B807" s="23"/>
+      <c r="C807" s="23"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="A808" s="16"/>
-      <c r="B808" s="16"/>
-      <c r="C808" s="16"/>
+      <c r="A808" s="23"/>
+      <c r="B808" s="23"/>
+      <c r="C808" s="23"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="A809" s="16"/>
-      <c r="B809" s="16"/>
-      <c r="C809" s="16"/>
+      <c r="A809" s="23"/>
+      <c r="B809" s="23"/>
+      <c r="C809" s="23"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="A810" s="16"/>
-      <c r="B810" s="16"/>
-      <c r="C810" s="16"/>
+      <c r="A810" s="23"/>
+      <c r="B810" s="23"/>
+      <c r="C810" s="23"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="A811" s="16"/>
-      <c r="B811" s="16"/>
-      <c r="C811" s="16"/>
+      <c r="A811" s="23"/>
+      <c r="B811" s="23"/>
+      <c r="C811" s="23"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="A812" s="16"/>
-      <c r="B812" s="16"/>
-      <c r="C812" s="16"/>
+      <c r="A812" s="23"/>
+      <c r="B812" s="23"/>
+      <c r="C812" s="23"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="A813" s="16"/>
-      <c r="B813" s="16"/>
-      <c r="C813" s="16"/>
+      <c r="A813" s="23"/>
+      <c r="B813" s="23"/>
+      <c r="C813" s="23"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="A814" s="16"/>
-      <c r="B814" s="16"/>
-      <c r="C814" s="16"/>
+      <c r="A814" s="23"/>
+      <c r="B814" s="23"/>
+      <c r="C814" s="23"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="A815" s="16"/>
-      <c r="B815" s="16"/>
-      <c r="C815" s="16"/>
+      <c r="A815" s="23"/>
+      <c r="B815" s="23"/>
+      <c r="C815" s="23"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="A816" s="16"/>
-      <c r="B816" s="16"/>
-      <c r="C816" s="16"/>
+      <c r="A816" s="23"/>
+      <c r="B816" s="23"/>
+      <c r="C816" s="23"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="A817" s="16"/>
-      <c r="B817" s="16"/>
-      <c r="C817" s="16"/>
+      <c r="A817" s="23"/>
+      <c r="B817" s="23"/>
+      <c r="C817" s="23"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="A818" s="16"/>
-      <c r="B818" s="16"/>
-      <c r="C818" s="16"/>
+      <c r="A818" s="23"/>
+      <c r="B818" s="23"/>
+      <c r="C818" s="23"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="A819" s="16"/>
-      <c r="B819" s="16"/>
-      <c r="C819" s="16"/>
+      <c r="A819" s="23"/>
+      <c r="B819" s="23"/>
+      <c r="C819" s="23"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="A820" s="16"/>
-      <c r="B820" s="16"/>
-      <c r="C820" s="16"/>
+      <c r="A820" s="23"/>
+      <c r="B820" s="23"/>
+      <c r="C820" s="23"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="A821" s="16"/>
-      <c r="B821" s="16"/>
-      <c r="C821" s="16"/>
+      <c r="A821" s="23"/>
+      <c r="B821" s="23"/>
+      <c r="C821" s="23"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="A822" s="16"/>
-      <c r="B822" s="16"/>
-      <c r="C822" s="16"/>
+      <c r="A822" s="23"/>
+      <c r="B822" s="23"/>
+      <c r="C822" s="23"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="A823" s="16"/>
-      <c r="B823" s="16"/>
-      <c r="C823" s="16"/>
+      <c r="A823" s="23"/>
+      <c r="B823" s="23"/>
+      <c r="C823" s="23"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="A824" s="16"/>
-      <c r="B824" s="16"/>
-      <c r="C824" s="16"/>
+      <c r="A824" s="23"/>
+      <c r="B824" s="23"/>
+      <c r="C824" s="23"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="A825" s="16"/>
-      <c r="B825" s="16"/>
-      <c r="C825" s="16"/>
+      <c r="A825" s="23"/>
+      <c r="B825" s="23"/>
+      <c r="C825" s="23"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="A826" s="16"/>
-      <c r="B826" s="16"/>
-      <c r="C826" s="16"/>
+      <c r="A826" s="23"/>
+      <c r="B826" s="23"/>
+      <c r="C826" s="23"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="A827" s="16"/>
-      <c r="B827" s="16"/>
-      <c r="C827" s="16"/>
+      <c r="A827" s="23"/>
+      <c r="B827" s="23"/>
+      <c r="C827" s="23"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="A828" s="16"/>
-      <c r="B828" s="16"/>
-      <c r="C828" s="16"/>
+      <c r="A828" s="23"/>
+      <c r="B828" s="23"/>
+      <c r="C828" s="23"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="A829" s="16"/>
-      <c r="B829" s="16"/>
-      <c r="C829" s="16"/>
+      <c r="A829" s="23"/>
+      <c r="B829" s="23"/>
+      <c r="C829" s="23"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="A830" s="16"/>
-      <c r="B830" s="16"/>
-      <c r="C830" s="16"/>
+      <c r="A830" s="23"/>
+      <c r="B830" s="23"/>
+      <c r="C830" s="23"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="A831" s="16"/>
-      <c r="B831" s="16"/>
-      <c r="C831" s="16"/>
+      <c r="A831" s="23"/>
+      <c r="B831" s="23"/>
+      <c r="C831" s="23"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="A832" s="16"/>
-      <c r="B832" s="16"/>
-      <c r="C832" s="16"/>
+      <c r="A832" s="23"/>
+      <c r="B832" s="23"/>
+      <c r="C832" s="23"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="A833" s="16"/>
-      <c r="B833" s="16"/>
-      <c r="C833" s="16"/>
+      <c r="A833" s="23"/>
+      <c r="B833" s="23"/>
+      <c r="C833" s="23"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="A834" s="16"/>
-      <c r="B834" s="16"/>
-      <c r="C834" s="16"/>
+      <c r="A834" s="23"/>
+      <c r="B834" s="23"/>
+      <c r="C834" s="23"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="A835" s="16"/>
-      <c r="B835" s="16"/>
-      <c r="C835" s="16"/>
+      <c r="A835" s="23"/>
+      <c r="B835" s="23"/>
+      <c r="C835" s="23"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="A836" s="16"/>
-      <c r="B836" s="16"/>
-      <c r="C836" s="16"/>
+      <c r="A836" s="23"/>
+      <c r="B836" s="23"/>
+      <c r="C836" s="23"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="A837" s="16"/>
-      <c r="B837" s="16"/>
-      <c r="C837" s="16"/>
+      <c r="A837" s="23"/>
+      <c r="B837" s="23"/>
+      <c r="C837" s="23"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="A838" s="16"/>
-      <c r="B838" s="16"/>
-      <c r="C838" s="16"/>
+      <c r="A838" s="23"/>
+      <c r="B838" s="23"/>
+      <c r="C838" s="23"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="A839" s="16"/>
-      <c r="B839" s="16"/>
-      <c r="C839" s="16"/>
+      <c r="A839" s="23"/>
+      <c r="B839" s="23"/>
+      <c r="C839" s="23"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="A840" s="16"/>
-      <c r="B840" s="16"/>
-      <c r="C840" s="16"/>
+      <c r="A840" s="23"/>
+      <c r="B840" s="23"/>
+      <c r="C840" s="23"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="A841" s="16"/>
-      <c r="B841" s="16"/>
-      <c r="C841" s="16"/>
+      <c r="A841" s="23"/>
+      <c r="B841" s="23"/>
+      <c r="C841" s="23"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="A842" s="16"/>
-      <c r="B842" s="16"/>
-      <c r="C842" s="16"/>
+      <c r="A842" s="23"/>
+      <c r="B842" s="23"/>
+      <c r="C842" s="23"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="A843" s="16"/>
-      <c r="B843" s="16"/>
-      <c r="C843" s="16"/>
+      <c r="A843" s="23"/>
+      <c r="B843" s="23"/>
+      <c r="C843" s="23"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="A844" s="16"/>
-      <c r="B844" s="16"/>
-      <c r="C844" s="16"/>
+      <c r="A844" s="23"/>
+      <c r="B844" s="23"/>
+      <c r="C844" s="23"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="A845" s="16"/>
-      <c r="B845" s="16"/>
-      <c r="C845" s="16"/>
+      <c r="A845" s="23"/>
+      <c r="B845" s="23"/>
+      <c r="C845" s="23"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="A846" s="16"/>
-      <c r="B846" s="16"/>
-      <c r="C846" s="16"/>
+      <c r="A846" s="23"/>
+      <c r="B846" s="23"/>
+      <c r="C846" s="23"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="A847" s="16"/>
-      <c r="B847" s="16"/>
-      <c r="C847" s="16"/>
+      <c r="A847" s="23"/>
+      <c r="B847" s="23"/>
+      <c r="C847" s="23"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="A848" s="16"/>
-      <c r="B848" s="16"/>
-      <c r="C848" s="16"/>
+      <c r="A848" s="23"/>
+      <c r="B848" s="23"/>
+      <c r="C848" s="23"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="A849" s="16"/>
-      <c r="B849" s="16"/>
-      <c r="C849" s="16"/>
+      <c r="A849" s="23"/>
+      <c r="B849" s="23"/>
+      <c r="C849" s="23"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="A850" s="16"/>
-      <c r="B850" s="16"/>
-      <c r="C850" s="16"/>
+      <c r="A850" s="23"/>
+      <c r="B850" s="23"/>
+      <c r="C850" s="23"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="A851" s="16"/>
-      <c r="B851" s="16"/>
-      <c r="C851" s="16"/>
+      <c r="A851" s="23"/>
+      <c r="B851" s="23"/>
+      <c r="C851" s="23"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="A852" s="16"/>
-      <c r="B852" s="16"/>
-      <c r="C852" s="16"/>
+      <c r="A852" s="23"/>
+      <c r="B852" s="23"/>
+      <c r="C852" s="23"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="A853" s="16"/>
-      <c r="B853" s="16"/>
-      <c r="C853" s="16"/>
+      <c r="A853" s="23"/>
+      <c r="B853" s="23"/>
+      <c r="C853" s="23"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="A854" s="16"/>
-      <c r="B854" s="16"/>
-      <c r="C854" s="16"/>
+      <c r="A854" s="23"/>
+      <c r="B854" s="23"/>
+      <c r="C854" s="23"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="A855" s="16"/>
-      <c r="B855" s="16"/>
-      <c r="C855" s="16"/>
+      <c r="A855" s="23"/>
+      <c r="B855" s="23"/>
+      <c r="C855" s="23"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="A856" s="16"/>
-      <c r="B856" s="16"/>
-      <c r="C856" s="16"/>
+      <c r="A856" s="23"/>
+      <c r="B856" s="23"/>
+      <c r="C856" s="23"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="A857" s="16"/>
-      <c r="B857" s="16"/>
-      <c r="C857" s="16"/>
+      <c r="A857" s="23"/>
+      <c r="B857" s="23"/>
+      <c r="C857" s="23"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="A858" s="16"/>
-      <c r="B858" s="16"/>
-      <c r="C858" s="16"/>
+      <c r="A858" s="23"/>
+      <c r="B858" s="23"/>
+      <c r="C858" s="23"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="A859" s="16"/>
-      <c r="B859" s="16"/>
-      <c r="C859" s="16"/>
+      <c r="A859" s="23"/>
+      <c r="B859" s="23"/>
+      <c r="C859" s="23"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="A860" s="16"/>
-      <c r="B860" s="16"/>
-      <c r="C860" s="16"/>
+      <c r="A860" s="23"/>
+      <c r="B860" s="23"/>
+      <c r="C860" s="23"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="A861" s="16"/>
-      <c r="B861" s="16"/>
-      <c r="C861" s="16"/>
+      <c r="A861" s="23"/>
+      <c r="B861" s="23"/>
+      <c r="C861" s="23"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="A862" s="16"/>
-      <c r="B862" s="16"/>
-      <c r="C862" s="16"/>
+      <c r="A862" s="23"/>
+      <c r="B862" s="23"/>
+      <c r="C862" s="23"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="A863" s="16"/>
-      <c r="B863" s="16"/>
-      <c r="C863" s="16"/>
+      <c r="A863" s="23"/>
+      <c r="B863" s="23"/>
+      <c r="C863" s="23"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="A864" s="16"/>
-      <c r="B864" s="16"/>
-      <c r="C864" s="16"/>
+      <c r="A864" s="23"/>
+      <c r="B864" s="23"/>
+      <c r="C864" s="23"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="A865" s="16"/>
-      <c r="B865" s="16"/>
-      <c r="C865" s="16"/>
+      <c r="A865" s="23"/>
+      <c r="B865" s="23"/>
+      <c r="C865" s="23"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="A866" s="16"/>
-      <c r="B866" s="16"/>
-      <c r="C866" s="16"/>
+      <c r="A866" s="23"/>
+      <c r="B866" s="23"/>
+      <c r="C866" s="23"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="A867" s="16"/>
-      <c r="B867" s="16"/>
-      <c r="C867" s="16"/>
+      <c r="A867" s="23"/>
+      <c r="B867" s="23"/>
+      <c r="C867" s="23"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="A868" s="16"/>
-      <c r="B868" s="16"/>
-      <c r="C868" s="16"/>
+      <c r="A868" s="23"/>
+      <c r="B868" s="23"/>
+      <c r="C868" s="23"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="A869" s="16"/>
-      <c r="B869" s="16"/>
-      <c r="C869" s="16"/>
+      <c r="A869" s="23"/>
+      <c r="B869" s="23"/>
+      <c r="C869" s="23"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="A870" s="16"/>
-      <c r="B870" s="16"/>
-      <c r="C870" s="16"/>
+      <c r="A870" s="23"/>
+      <c r="B870" s="23"/>
+      <c r="C870" s="23"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="16"/>
-      <c r="B871" s="16"/>
-      <c r="C871" s="16"/>
+      <c r="A871" s="23"/>
+      <c r="B871" s="23"/>
+      <c r="C871" s="23"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="A872" s="16"/>
-      <c r="B872" s="16"/>
-      <c r="C872" s="16"/>
+      <c r="A872" s="23"/>
+      <c r="B872" s="23"/>
+      <c r="C872" s="23"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="A873" s="16"/>
-      <c r="B873" s="16"/>
-      <c r="C873" s="16"/>
+      <c r="A873" s="23"/>
+      <c r="B873" s="23"/>
+      <c r="C873" s="23"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="A874" s="16"/>
-      <c r="B874" s="16"/>
-      <c r="C874" s="16"/>
+      <c r="A874" s="23"/>
+      <c r="B874" s="23"/>
+      <c r="C874" s="23"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="A875" s="16"/>
-      <c r="B875" s="16"/>
-      <c r="C875" s="16"/>
+      <c r="A875" s="23"/>
+      <c r="B875" s="23"/>
+      <c r="C875" s="23"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="16"/>
-      <c r="B876" s="16"/>
-      <c r="C876" s="16"/>
+      <c r="A876" s="23"/>
+      <c r="B876" s="23"/>
+      <c r="C876" s="23"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="A877" s="16"/>
-      <c r="B877" s="16"/>
-      <c r="C877" s="16"/>
+      <c r="A877" s="23"/>
+      <c r="B877" s="23"/>
+      <c r="C877" s="23"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="A878" s="16"/>
-      <c r="B878" s="16"/>
-      <c r="C878" s="16"/>
+      <c r="A878" s="23"/>
+      <c r="B878" s="23"/>
+      <c r="C878" s="23"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="A879" s="16"/>
-      <c r="B879" s="16"/>
-      <c r="C879" s="16"/>
+      <c r="A879" s="23"/>
+      <c r="B879" s="23"/>
+      <c r="C879" s="23"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="A880" s="16"/>
-      <c r="B880" s="16"/>
-      <c r="C880" s="16"/>
+      <c r="A880" s="23"/>
+      <c r="B880" s="23"/>
+      <c r="C880" s="23"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="A881" s="16"/>
-      <c r="B881" s="16"/>
-      <c r="C881" s="16"/>
+      <c r="A881" s="23"/>
+      <c r="B881" s="23"/>
+      <c r="C881" s="23"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="A882" s="16"/>
-      <c r="B882" s="16"/>
-      <c r="C882" s="16"/>
+      <c r="A882" s="23"/>
+      <c r="B882" s="23"/>
+      <c r="C882" s="23"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="A883" s="16"/>
-      <c r="B883" s="16"/>
-      <c r="C883" s="16"/>
+      <c r="A883" s="23"/>
+      <c r="B883" s="23"/>
+      <c r="C883" s="23"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="A884" s="16"/>
-      <c r="B884" s="16"/>
-      <c r="C884" s="16"/>
+      <c r="A884" s="23"/>
+      <c r="B884" s="23"/>
+      <c r="C884" s="23"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="A885" s="16"/>
-      <c r="B885" s="16"/>
-      <c r="C885" s="16"/>
+      <c r="A885" s="23"/>
+      <c r="B885" s="23"/>
+      <c r="C885" s="23"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="A886" s="16"/>
-      <c r="B886" s="16"/>
-      <c r="C886" s="16"/>
+      <c r="A886" s="23"/>
+      <c r="B886" s="23"/>
+      <c r="C886" s="23"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="A887" s="16"/>
-      <c r="B887" s="16"/>
-      <c r="C887" s="16"/>
+      <c r="A887" s="23"/>
+      <c r="B887" s="23"/>
+      <c r="C887" s="23"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="A888" s="16"/>
-      <c r="B888" s="16"/>
-      <c r="C888" s="16"/>
+      <c r="A888" s="23"/>
+      <c r="B888" s="23"/>
+      <c r="C888" s="23"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="A889" s="16"/>
-      <c r="B889" s="16"/>
-      <c r="C889" s="16"/>
+      <c r="A889" s="23"/>
+      <c r="B889" s="23"/>
+      <c r="C889" s="23"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="A890" s="16"/>
-      <c r="B890" s="16"/>
-      <c r="C890" s="16"/>
+      <c r="A890" s="23"/>
+      <c r="B890" s="23"/>
+      <c r="C890" s="23"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="A891" s="16"/>
-      <c r="B891" s="16"/>
-      <c r="C891" s="16"/>
+      <c r="A891" s="23"/>
+      <c r="B891" s="23"/>
+      <c r="C891" s="23"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="A892" s="16"/>
-      <c r="B892" s="16"/>
-      <c r="C892" s="16"/>
+      <c r="A892" s="23"/>
+      <c r="B892" s="23"/>
+      <c r="C892" s="23"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="A893" s="16"/>
-      <c r="B893" s="16"/>
-      <c r="C893" s="16"/>
+      <c r="A893" s="23"/>
+      <c r="B893" s="23"/>
+      <c r="C893" s="23"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="A894" s="16"/>
-      <c r="B894" s="16"/>
-      <c r="C894" s="16"/>
+      <c r="A894" s="23"/>
+      <c r="B894" s="23"/>
+      <c r="C894" s="23"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="A895" s="16"/>
-      <c r="B895" s="16"/>
-      <c r="C895" s="16"/>
+      <c r="A895" s="23"/>
+      <c r="B895" s="23"/>
+      <c r="C895" s="23"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="A896" s="16"/>
-      <c r="B896" s="16"/>
-      <c r="C896" s="16"/>
+      <c r="A896" s="23"/>
+      <c r="B896" s="23"/>
+      <c r="C896" s="23"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="A897" s="16"/>
-      <c r="B897" s="16"/>
-      <c r="C897" s="16"/>
+      <c r="A897" s="23"/>
+      <c r="B897" s="23"/>
+      <c r="C897" s="23"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="A898" s="16"/>
-      <c r="B898" s="16"/>
-      <c r="C898" s="16"/>
+      <c r="A898" s="23"/>
+      <c r="B898" s="23"/>
+      <c r="C898" s="23"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="A899" s="16"/>
-      <c r="B899" s="16"/>
-      <c r="C899" s="16"/>
+      <c r="A899" s="23"/>
+      <c r="B899" s="23"/>
+      <c r="C899" s="23"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="A900" s="16"/>
-      <c r="B900" s="16"/>
-      <c r="C900" s="16"/>
+      <c r="A900" s="23"/>
+      <c r="B900" s="23"/>
+      <c r="C900" s="23"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="A901" s="16"/>
-      <c r="B901" s="16"/>
-      <c r="C901" s="16"/>
+      <c r="A901" s="23"/>
+      <c r="B901" s="23"/>
+      <c r="C901" s="23"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="A902" s="16"/>
-      <c r="B902" s="16"/>
-      <c r="C902" s="16"/>
+      <c r="A902" s="23"/>
+      <c r="B902" s="23"/>
+      <c r="C902" s="23"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="A903" s="16"/>
-      <c r="B903" s="16"/>
-      <c r="C903" s="16"/>
+      <c r="A903" s="23"/>
+      <c r="B903" s="23"/>
+      <c r="C903" s="23"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="A904" s="16"/>
-      <c r="B904" s="16"/>
-      <c r="C904" s="16"/>
+      <c r="A904" s="23"/>
+      <c r="B904" s="23"/>
+      <c r="C904" s="23"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="A905" s="16"/>
-      <c r="B905" s="16"/>
-      <c r="C905" s="16"/>
+      <c r="A905" s="23"/>
+      <c r="B905" s="23"/>
+      <c r="C905" s="23"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="A906" s="16"/>
-      <c r="B906" s="16"/>
-      <c r="C906" s="16"/>
+      <c r="A906" s="23"/>
+      <c r="B906" s="23"/>
+      <c r="C906" s="23"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="A907" s="16"/>
-      <c r="B907" s="16"/>
-      <c r="C907" s="16"/>
+      <c r="A907" s="23"/>
+      <c r="B907" s="23"/>
+      <c r="C907" s="23"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="A908" s="16"/>
-      <c r="B908" s="16"/>
-      <c r="C908" s="16"/>
+      <c r="A908" s="23"/>
+      <c r="B908" s="23"/>
+      <c r="C908" s="23"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="A909" s="16"/>
-      <c r="B909" s="16"/>
-      <c r="C909" s="16"/>
+      <c r="A909" s="23"/>
+      <c r="B909" s="23"/>
+      <c r="C909" s="23"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="A910" s="16"/>
-      <c r="B910" s="16"/>
-      <c r="C910" s="16"/>
+      <c r="A910" s="23"/>
+      <c r="B910" s="23"/>
+      <c r="C910" s="23"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="A911" s="16"/>
-      <c r="B911" s="16"/>
-      <c r="C911" s="16"/>
+      <c r="A911" s="23"/>
+      <c r="B911" s="23"/>
+      <c r="C911" s="23"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="A912" s="16"/>
-      <c r="B912" s="16"/>
-      <c r="C912" s="16"/>
+      <c r="A912" s="23"/>
+      <c r="B912" s="23"/>
+      <c r="C912" s="23"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="A913" s="16"/>
-      <c r="B913" s="16"/>
-      <c r="C913" s="16"/>
+      <c r="A913" s="23"/>
+      <c r="B913" s="23"/>
+      <c r="C913" s="23"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="A914" s="16"/>
-      <c r="B914" s="16"/>
-      <c r="C914" s="16"/>
+      <c r="A914" s="23"/>
+      <c r="B914" s="23"/>
+      <c r="C914" s="23"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="A915" s="16"/>
-      <c r="B915" s="16"/>
-      <c r="C915" s="16"/>
+      <c r="A915" s="23"/>
+      <c r="B915" s="23"/>
+      <c r="C915" s="23"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="A916" s="16"/>
-      <c r="B916" s="16"/>
-      <c r="C916" s="16"/>
+      <c r="A916" s="23"/>
+      <c r="B916" s="23"/>
+      <c r="C916" s="23"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="A917" s="16"/>
-      <c r="B917" s="16"/>
-      <c r="C917" s="16"/>
+      <c r="A917" s="23"/>
+      <c r="B917" s="23"/>
+      <c r="C917" s="23"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="A918" s="16"/>
-      <c r="B918" s="16"/>
-      <c r="C918" s="16"/>
+      <c r="A918" s="23"/>
+      <c r="B918" s="23"/>
+      <c r="C918" s="23"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="A919" s="16"/>
-      <c r="B919" s="16"/>
-      <c r="C919" s="16"/>
+      <c r="A919" s="23"/>
+      <c r="B919" s="23"/>
+      <c r="C919" s="23"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="A920" s="16"/>
-      <c r="B920" s="16"/>
-      <c r="C920" s="16"/>
+      <c r="A920" s="23"/>
+      <c r="B920" s="23"/>
+      <c r="C920" s="23"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="A921" s="16"/>
-      <c r="B921" s="16"/>
-      <c r="C921" s="16"/>
+      <c r="A921" s="23"/>
+      <c r="B921" s="23"/>
+      <c r="C921" s="23"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="A922" s="16"/>
-      <c r="B922" s="16"/>
-      <c r="C922" s="16"/>
+      <c r="A922" s="23"/>
+      <c r="B922" s="23"/>
+      <c r="C922" s="23"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="A923" s="16"/>
-      <c r="B923" s="16"/>
-      <c r="C923" s="16"/>
+      <c r="A923" s="23"/>
+      <c r="B923" s="23"/>
+      <c r="C923" s="23"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="A924" s="16"/>
-      <c r="B924" s="16"/>
-      <c r="C924" s="16"/>
+      <c r="A924" s="23"/>
+      <c r="B924" s="23"/>
+      <c r="C924" s="23"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="A925" s="16"/>
-      <c r="B925" s="16"/>
-      <c r="C925" s="16"/>
+      <c r="A925" s="23"/>
+      <c r="B925" s="23"/>
+      <c r="C925" s="23"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="A926" s="16"/>
-      <c r="B926" s="16"/>
-      <c r="C926" s="16"/>
+      <c r="A926" s="23"/>
+      <c r="B926" s="23"/>
+      <c r="C926" s="23"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="A927" s="16"/>
-      <c r="B927" s="16"/>
-      <c r="C927" s="16"/>
+      <c r="A927" s="23"/>
+      <c r="B927" s="23"/>
+      <c r="C927" s="23"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="A928" s="16"/>
-      <c r="B928" s="16"/>
-      <c r="C928" s="16"/>
+      <c r="A928" s="23"/>
+      <c r="B928" s="23"/>
+      <c r="C928" s="23"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="A929" s="16"/>
-      <c r="B929" s="16"/>
-      <c r="C929" s="16"/>
+      <c r="A929" s="23"/>
+      <c r="B929" s="23"/>
+      <c r="C929" s="23"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="A930" s="16"/>
-      <c r="B930" s="16"/>
-      <c r="C930" s="16"/>
+      <c r="A930" s="23"/>
+      <c r="B930" s="23"/>
+      <c r="C930" s="23"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="A931" s="16"/>
-      <c r="B931" s="16"/>
-      <c r="C931" s="16"/>
+      <c r="A931" s="23"/>
+      <c r="B931" s="23"/>
+      <c r="C931" s="23"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="A932" s="16"/>
-      <c r="B932" s="16"/>
-      <c r="C932" s="16"/>
+      <c r="A932" s="23"/>
+      <c r="B932" s="23"/>
+      <c r="C932" s="23"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="A933" s="16"/>
-      <c r="B933" s="16"/>
-      <c r="C933" s="16"/>
+      <c r="A933" s="23"/>
+      <c r="B933" s="23"/>
+      <c r="C933" s="23"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="A934" s="16"/>
-      <c r="B934" s="16"/>
-      <c r="C934" s="16"/>
+      <c r="A934" s="23"/>
+      <c r="B934" s="23"/>
+      <c r="C934" s="23"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="A935" s="16"/>
-      <c r="B935" s="16"/>
-      <c r="C935" s="16"/>
+      <c r="A935" s="23"/>
+      <c r="B935" s="23"/>
+      <c r="C935" s="23"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="A936" s="16"/>
-      <c r="B936" s="16"/>
-      <c r="C936" s="16"/>
+      <c r="A936" s="23"/>
+      <c r="B936" s="23"/>
+      <c r="C936" s="23"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="A937" s="16"/>
-      <c r="B937" s="16"/>
-      <c r="C937" s="16"/>
+      <c r="A937" s="23"/>
+      <c r="B937" s="23"/>
+      <c r="C937" s="23"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="A938" s="16"/>
-      <c r="B938" s="16"/>
-      <c r="C938" s="16"/>
+      <c r="A938" s="23"/>
+      <c r="B938" s="23"/>
+      <c r="C938" s="23"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="A939" s="16"/>
-      <c r="B939" s="16"/>
-      <c r="C939" s="16"/>
+      <c r="A939" s="23"/>
+      <c r="B939" s="23"/>
+      <c r="C939" s="23"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="A940" s="16"/>
-      <c r="B940" s="16"/>
-      <c r="C940" s="16"/>
+      <c r="A940" s="23"/>
+      <c r="B940" s="23"/>
+      <c r="C940" s="23"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="A941" s="16"/>
-      <c r="B941" s="16"/>
-      <c r="C941" s="16"/>
+      <c r="A941" s="23"/>
+      <c r="B941" s="23"/>
+      <c r="C941" s="23"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="A942" s="16"/>
-      <c r="B942" s="16"/>
-      <c r="C942" s="16"/>
+      <c r="A942" s="23"/>
+      <c r="B942" s="23"/>
+      <c r="C942" s="23"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="A943" s="16"/>
-      <c r="B943" s="16"/>
-      <c r="C943" s="16"/>
+      <c r="A943" s="23"/>
+      <c r="B943" s="23"/>
+      <c r="C943" s="23"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="A944" s="16"/>
-      <c r="B944" s="16"/>
-      <c r="C944" s="16"/>
+      <c r="A944" s="23"/>
+      <c r="B944" s="23"/>
+      <c r="C944" s="23"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="A945" s="16"/>
-      <c r="B945" s="16"/>
-      <c r="C945" s="16"/>
+      <c r="A945" s="23"/>
+      <c r="B945" s="23"/>
+      <c r="C945" s="23"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="A946" s="16"/>
-      <c r="B946" s="16"/>
-      <c r="C946" s="16"/>
+      <c r="A946" s="23"/>
+      <c r="B946" s="23"/>
+      <c r="C946" s="23"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="A947" s="16"/>
-      <c r="B947" s="16"/>
-      <c r="C947" s="16"/>
+      <c r="A947" s="23"/>
+      <c r="B947" s="23"/>
+      <c r="C947" s="23"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="A948" s="16"/>
-      <c r="B948" s="16"/>
-      <c r="C948" s="16"/>
+      <c r="A948" s="23"/>
+      <c r="B948" s="23"/>
+      <c r="C948" s="23"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="A949" s="16"/>
-      <c r="B949" s="16"/>
-      <c r="C949" s="16"/>
+      <c r="A949" s="23"/>
+      <c r="B949" s="23"/>
+      <c r="C949" s="23"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="A950" s="16"/>
-      <c r="B950" s="16"/>
-      <c r="C950" s="16"/>
+      <c r="A950" s="23"/>
+      <c r="B950" s="23"/>
+      <c r="C950" s="23"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="A951" s="16"/>
-      <c r="B951" s="16"/>
-      <c r="C951" s="16"/>
+      <c r="A951" s="23"/>
+      <c r="B951" s="23"/>
+      <c r="C951" s="23"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="A952" s="16"/>
-      <c r="B952" s="16"/>
-      <c r="C952" s="16"/>
+      <c r="A952" s="23"/>
+      <c r="B952" s="23"/>
+      <c r="C952" s="23"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="A953" s="16"/>
-      <c r="B953" s="16"/>
-      <c r="C953" s="16"/>
+      <c r="A953" s="23"/>
+      <c r="B953" s="23"/>
+      <c r="C953" s="23"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="A954" s="16"/>
-      <c r="B954" s="16"/>
-      <c r="C954" s="16"/>
+      <c r="A954" s="23"/>
+      <c r="B954" s="23"/>
+      <c r="C954" s="23"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="A955" s="16"/>
-      <c r="B955" s="16"/>
-      <c r="C955" s="16"/>
+      <c r="A955" s="23"/>
+      <c r="B955" s="23"/>
+      <c r="C955" s="23"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="A956" s="16"/>
-      <c r="B956" s="16"/>
-      <c r="C956" s="16"/>
+      <c r="A956" s="23"/>
+      <c r="B956" s="23"/>
+      <c r="C956" s="23"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="A957" s="16"/>
-      <c r="B957" s="16"/>
-      <c r="C957" s="16"/>
+      <c r="A957" s="23"/>
+      <c r="B957" s="23"/>
+      <c r="C957" s="23"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="A958" s="16"/>
-      <c r="B958" s="16"/>
-      <c r="C958" s="16"/>
+      <c r="A958" s="23"/>
+      <c r="B958" s="23"/>
+      <c r="C958" s="23"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="A959" s="16"/>
-      <c r="B959" s="16"/>
-      <c r="C959" s="16"/>
+      <c r="A959" s="23"/>
+      <c r="B959" s="23"/>
+      <c r="C959" s="23"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="A960" s="16"/>
-      <c r="B960" s="16"/>
-      <c r="C960" s="16"/>
+      <c r="A960" s="23"/>
+      <c r="B960" s="23"/>
+      <c r="C960" s="23"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="A961" s="16"/>
-      <c r="B961" s="16"/>
-      <c r="C961" s="16"/>
+      <c r="A961" s="23"/>
+      <c r="B961" s="23"/>
+      <c r="C961" s="23"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="A962" s="16"/>
-      <c r="B962" s="16"/>
-      <c r="C962" s="16"/>
+      <c r="A962" s="23"/>
+      <c r="B962" s="23"/>
+      <c r="C962" s="23"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="A963" s="16"/>
-      <c r="B963" s="16"/>
-      <c r="C963" s="16"/>
+      <c r="A963" s="23"/>
+      <c r="B963" s="23"/>
+      <c r="C963" s="23"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="A964" s="16"/>
-      <c r="B964" s="16"/>
-      <c r="C964" s="16"/>
+      <c r="A964" s="23"/>
+      <c r="B964" s="23"/>
+      <c r="C964" s="23"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="A965" s="16"/>
-      <c r="B965" s="16"/>
-      <c r="C965" s="16"/>
+      <c r="A965" s="23"/>
+      <c r="B965" s="23"/>
+      <c r="C965" s="23"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="A966" s="16"/>
-      <c r="B966" s="16"/>
-      <c r="C966" s="16"/>
+      <c r="A966" s="23"/>
+      <c r="B966" s="23"/>
+      <c r="C966" s="23"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="A967" s="16"/>
-      <c r="B967" s="16"/>
-      <c r="C967" s="16"/>
+      <c r="A967" s="23"/>
+      <c r="B967" s="23"/>
+      <c r="C967" s="23"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="A968" s="16"/>
-      <c r="B968" s="16"/>
-      <c r="C968" s="16"/>
+      <c r="A968" s="23"/>
+      <c r="B968" s="23"/>
+      <c r="C968" s="23"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="A969" s="16"/>
-      <c r="B969" s="16"/>
-      <c r="C969" s="16"/>
+      <c r="A969" s="23"/>
+      <c r="B969" s="23"/>
+      <c r="C969" s="23"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="A970" s="16"/>
-      <c r="B970" s="16"/>
-      <c r="C970" s="16"/>
+      <c r="A970" s="23"/>
+      <c r="B970" s="23"/>
+      <c r="C970" s="23"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="A971" s="16"/>
-      <c r="B971" s="16"/>
-      <c r="C971" s="16"/>
+      <c r="A971" s="23"/>
+      <c r="B971" s="23"/>
+      <c r="C971" s="23"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="A972" s="16"/>
-      <c r="B972" s="16"/>
-      <c r="C972" s="16"/>
+      <c r="A972" s="23"/>
+      <c r="B972" s="23"/>
+      <c r="C972" s="23"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="A973" s="16"/>
-      <c r="B973" s="16"/>
-      <c r="C973" s="16"/>
+      <c r="A973" s="23"/>
+      <c r="B973" s="23"/>
+      <c r="C973" s="23"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="A974" s="16"/>
-      <c r="B974" s="16"/>
-      <c r="C974" s="16"/>
+      <c r="A974" s="23"/>
+      <c r="B974" s="23"/>
+      <c r="C974" s="23"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="A975" s="16"/>
-      <c r="B975" s="16"/>
-      <c r="C975" s="16"/>
+      <c r="A975" s="23"/>
+      <c r="B975" s="23"/>
+      <c r="C975" s="23"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="A976" s="16"/>
-      <c r="B976" s="16"/>
-      <c r="C976" s="16"/>
+      <c r="A976" s="23"/>
+      <c r="B976" s="23"/>
+      <c r="C976" s="23"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="A977" s="16"/>
-      <c r="B977" s="16"/>
-      <c r="C977" s="16"/>
+      <c r="A977" s="23"/>
+      <c r="B977" s="23"/>
+      <c r="C977" s="23"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="A978" s="16"/>
-      <c r="B978" s="16"/>
-      <c r="C978" s="16"/>
+      <c r="A978" s="23"/>
+      <c r="B978" s="23"/>
+      <c r="C978" s="23"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="A979" s="16"/>
-      <c r="B979" s="16"/>
-      <c r="C979" s="16"/>
+      <c r="A979" s="23"/>
+      <c r="B979" s="23"/>
+      <c r="C979" s="23"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="A980" s="16"/>
-      <c r="B980" s="16"/>
-      <c r="C980" s="16"/>
+      <c r="A980" s="23"/>
+      <c r="B980" s="23"/>
+      <c r="C980" s="23"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="A981" s="16"/>
-      <c r="B981" s="16"/>
-      <c r="C981" s="16"/>
+      <c r="A981" s="23"/>
+      <c r="B981" s="23"/>
+      <c r="C981" s="23"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="A982" s="16"/>
-      <c r="B982" s="16"/>
-      <c r="C982" s="16"/>
+      <c r="A982" s="23"/>
+      <c r="B982" s="23"/>
+      <c r="C982" s="23"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="A983" s="16"/>
-      <c r="B983" s="16"/>
-      <c r="C983" s="16"/>
+      <c r="A983" s="23"/>
+      <c r="B983" s="23"/>
+      <c r="C983" s="23"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="A984" s="16"/>
-      <c r="B984" s="16"/>
-      <c r="C984" s="16"/>
+      <c r="A984" s="23"/>
+      <c r="B984" s="23"/>
+      <c r="C984" s="23"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="A985" s="16"/>
-      <c r="B985" s="16"/>
-      <c r="C985" s="16"/>
+      <c r="A985" s="23"/>
+      <c r="B985" s="23"/>
+      <c r="C985" s="23"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="A986" s="16"/>
-      <c r="B986" s="16"/>
-      <c r="C986" s="16"/>
+      <c r="A986" s="23"/>
+      <c r="B986" s="23"/>
+      <c r="C986" s="23"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="A987" s="16"/>
-      <c r="B987" s="16"/>
-      <c r="C987" s="16"/>
+      <c r="A987" s="23"/>
+      <c r="B987" s="23"/>
+      <c r="C987" s="23"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="A988" s="16"/>
-      <c r="B988" s="16"/>
-      <c r="C988" s="16"/>
+      <c r="A988" s="23"/>
+      <c r="B988" s="23"/>
+      <c r="C988" s="23"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="A989" s="16"/>
-      <c r="B989" s="16"/>
-      <c r="C989" s="16"/>
+      <c r="A989" s="23"/>
+      <c r="B989" s="23"/>
+      <c r="C989" s="23"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="A990" s="16"/>
-      <c r="B990" s="16"/>
-      <c r="C990" s="16"/>
+      <c r="A990" s="23"/>
+      <c r="B990" s="23"/>
+      <c r="C990" s="23"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="A991" s="16"/>
-      <c r="B991" s="16"/>
-      <c r="C991" s="16"/>
+      <c r="A991" s="23"/>
+      <c r="B991" s="23"/>
+      <c r="C991" s="23"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="A992" s="16"/>
-      <c r="B992" s="16"/>
-      <c r="C992" s="16"/>
+      <c r="A992" s="23"/>
+      <c r="B992" s="23"/>
+      <c r="C992" s="23"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="A993" s="16"/>
-      <c r="B993" s="16"/>
-      <c r="C993" s="16"/>
+      <c r="A993" s="23"/>
+      <c r="B993" s="23"/>
+      <c r="C993" s="23"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="A994" s="16"/>
-      <c r="B994" s="16"/>
-      <c r="C994" s="16"/>
+      <c r="A994" s="23"/>
+      <c r="B994" s="23"/>
+      <c r="C994" s="23"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="A995" s="16"/>
-      <c r="B995" s="16"/>
-      <c r="C995" s="16"/>
+      <c r="A995" s="23"/>
+      <c r="B995" s="23"/>
+      <c r="C995" s="23"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="16"/>
-      <c r="B996" s="16"/>
-      <c r="C996" s="16"/>
+      <c r="A996" s="23"/>
+      <c r="B996" s="23"/>
+      <c r="C996" s="23"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="16"/>
-      <c r="B997" s="16"/>
-      <c r="C997" s="16"/>
+      <c r="A997" s="23"/>
+      <c r="B997" s="23"/>
+      <c r="C997" s="23"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="16"/>
-      <c r="B998" s="16"/>
-      <c r="C998" s="16"/>
+      <c r="A998" s="23"/>
+      <c r="B998" s="23"/>
+      <c r="C998" s="23"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="16"/>
-      <c r="B999" s="16"/>
-      <c r="C999" s="16"/>
+      <c r="A999" s="23"/>
+      <c r="B999" s="23"/>
+      <c r="C999" s="23"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="16"/>
-      <c r="B1000" s="16"/>
-      <c r="C1000" s="16"/>
+      <c r="A1000" s="23"/>
+      <c r="B1000" s="23"/>
+      <c r="C1000" s="23"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="A1001" s="16"/>
-      <c r="B1001" s="16"/>
-      <c r="C1001" s="16"/>
+      <c r="A1001" s="23"/>
+      <c r="B1001" s="23"/>
+      <c r="C1001" s="23"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6795,84 +6875,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="B1" s="18" t="s">
-        <v>97</v>
+      <c r="B1" s="25" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="19" t="s">
-        <v>98</v>
+      <c r="B3" s="26" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="19" t="s">
-        <v>99</v>
+      <c r="B4" s="26" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="19" t="s">
-        <v>100</v>
+      <c r="B5" s="26" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="19" t="s">
-        <v>101</v>
+      <c r="B6" s="26" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="19" t="s">
-        <v>102</v>
+      <c r="B7" s="26" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="19" t="s">
-        <v>103</v>
+      <c r="B8" s="26" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="19" t="s">
-        <v>104</v>
+      <c r="B9" s="26" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="19" t="s">
-        <v>105</v>
+      <c r="B10" s="26" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="19" t="s">
-        <v>106</v>
+      <c r="B11" s="26" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="19" t="s">
-        <v>107</v>
+      <c r="B12" s="26" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="19" t="s">
-        <v>108</v>
+      <c r="B13" s="26" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="19" t="s">
-        <v>109</v>
+      <c r="B14" s="26" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="19" t="s">
-        <v>110</v>
+      <c r="B15" s="26" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="19" t="s">
-        <v>111</v>
+      <c r="B16" s="26" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="19" t="s">
-        <v>112</v>
+      <c r="B17" s="26" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7885,237 +7965,237 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="20" t="s">
-        <v>113</v>
-      </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
+      <c r="A2" s="27" t="s">
+        <v>117</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="16"/>
-      <c r="B3" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="C3" s="16"/>
+      <c r="A3" s="23"/>
+      <c r="B3" s="28" t="s">
+        <v>118</v>
+      </c>
+      <c r="C3" s="23"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="16"/>
-      <c r="B4" s="22" t="s">
-        <v>115</v>
-      </c>
-      <c r="C4" s="16"/>
+      <c r="A4" s="23"/>
+      <c r="B4" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="C4" s="23"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="23" t="s">
-        <v>116</v>
-      </c>
-      <c r="B5" s="23"/>
-      <c r="C5" s="23"/>
+      <c r="A5" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="16"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="24" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="D7" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="E7" s="24" t="s">
+      <c r="A7" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="C7" s="32" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="E7" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="F7" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="G7" s="24" t="s">
-        <v>122</v>
+      <c r="F7" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="26">
+      <c r="A8" s="33">
         <v>1.0</v>
       </c>
-      <c r="B8" s="27" t="s">
-        <v>123</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>124</v>
-      </c>
-      <c r="D8" s="28" t="s">
-        <v>125</v>
-      </c>
-      <c r="E8" s="29" t="s">
-        <v>126</v>
-      </c>
-      <c r="F8" s="30"/>
-      <c r="G8" s="31"/>
+      <c r="B8" s="34" t="s">
+        <v>127</v>
+      </c>
+      <c r="C8" s="34" t="s">
+        <v>128</v>
+      </c>
+      <c r="D8" s="35" t="s">
+        <v>129</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="37"/>
+      <c r="G8" s="38"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="32">
+      <c r="A9" s="39">
         <v>2.0</v>
       </c>
-      <c r="B9" s="33" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="33" t="s">
+      <c r="B9" s="40" t="s">
         <v>127</v>
       </c>
-      <c r="D9" s="34" t="s">
-        <v>125</v>
-      </c>
-      <c r="E9" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="F9" s="36"/>
-      <c r="G9" s="31"/>
+      <c r="C9" s="40" t="s">
+        <v>131</v>
+      </c>
+      <c r="D9" s="41" t="s">
+        <v>129</v>
+      </c>
+      <c r="E9" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="F9" s="43"/>
+      <c r="G9" s="38"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="37">
+      <c r="A10" s="44">
         <v>3.0</v>
       </c>
-      <c r="B10" s="38" t="s">
-        <v>129</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>130</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>131</v>
-      </c>
-      <c r="E10" s="40" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" s="41"/>
-      <c r="G10" s="42"/>
+      <c r="B10" s="45" t="s">
+        <v>133</v>
+      </c>
+      <c r="C10" s="45" t="s">
+        <v>134</v>
+      </c>
+      <c r="D10" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E10" s="47" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="48"/>
+      <c r="G10" s="49"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="26"/>
-      <c r="B11" s="27"/>
-      <c r="C11" s="27"/>
-      <c r="D11" s="28" t="s">
-        <v>133</v>
-      </c>
-      <c r="E11" s="29" t="s">
-        <v>134</v>
-      </c>
-      <c r="F11" s="43"/>
-      <c r="G11" s="44"/>
+      <c r="A11" s="33"/>
+      <c r="B11" s="34"/>
+      <c r="C11" s="34"/>
+      <c r="D11" s="35" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>138</v>
+      </c>
+      <c r="F11" s="50"/>
+      <c r="G11" s="51"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="45">
+      <c r="A12" s="52">
         <v>4.0</v>
       </c>
-      <c r="B12" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="C12" s="46" t="s">
-        <v>136</v>
-      </c>
-      <c r="D12" s="47" t="s">
-        <v>137</v>
-      </c>
-      <c r="E12" s="48" t="s">
-        <v>138</v>
-      </c>
-      <c r="F12" s="49"/>
-      <c r="G12" s="50"/>
+      <c r="B12" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C12" s="53" t="s">
+        <v>140</v>
+      </c>
+      <c r="D12" s="54" t="s">
+        <v>141</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="F12" s="56"/>
+      <c r="G12" s="57"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="26"/>
-      <c r="B13" s="27"/>
-      <c r="C13" s="27"/>
-      <c r="D13" s="28" t="s">
+      <c r="A13" s="33"/>
+      <c r="B13" s="34"/>
+      <c r="C13" s="34"/>
+      <c r="D13" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>144</v>
+      </c>
+      <c r="F13" s="37"/>
+      <c r="G13" s="51"/>
+    </row>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="A14" s="52">
+        <v>5.0</v>
+      </c>
+      <c r="B14" s="53" t="s">
         <v>139</v>
       </c>
-      <c r="E13" s="29" t="s">
+      <c r="C14" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="D14" s="54" t="s">
+        <v>146</v>
+      </c>
+      <c r="E14" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="F14" s="56"/>
+      <c r="G14" s="57"/>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="33"/>
+      <c r="B15" s="34"/>
+      <c r="C15" s="34"/>
+      <c r="D15" s="35" t="s">
+        <v>143</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="F15" s="58" t="s">
+        <v>149</v>
+      </c>
+      <c r="G15" s="51"/>
+    </row>
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="A16" s="52">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="53" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="53" t="s">
         <v>140</v>
       </c>
-      <c r="F13" s="30"/>
-      <c r="G13" s="44"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="45">
-        <v>5.0</v>
-      </c>
-      <c r="B14" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="C14" s="46" t="s">
-        <v>141</v>
-      </c>
-      <c r="D14" s="47" t="s">
-        <v>142</v>
-      </c>
-      <c r="E14" s="48" t="s">
+      <c r="D16" s="54" t="s">
+        <v>150</v>
+      </c>
+      <c r="E16" s="55" t="s">
+        <v>151</v>
+      </c>
+      <c r="F16" s="59"/>
+      <c r="G16" s="57"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="A17" s="33"/>
+      <c r="B17" s="34"/>
+      <c r="C17" s="34"/>
+      <c r="D17" s="35" t="s">
         <v>143</v>
       </c>
-      <c r="F14" s="49"/>
-      <c r="G14" s="50"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="26"/>
-      <c r="B15" s="27"/>
-      <c r="C15" s="27"/>
-      <c r="D15" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E15" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F15" s="51" t="s">
-        <v>145</v>
-      </c>
-      <c r="G15" s="44"/>
-    </row>
-    <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="45">
-        <v>6.0</v>
-      </c>
-      <c r="B16" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="C16" s="46" t="s">
-        <v>136</v>
-      </c>
-      <c r="D16" s="47" t="s">
-        <v>146</v>
-      </c>
-      <c r="E16" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="F16" s="52"/>
-      <c r="G16" s="50"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="26"/>
-      <c r="B17" s="27"/>
-      <c r="C17" s="27"/>
-      <c r="D17" s="28" t="s">
-        <v>139</v>
-      </c>
-      <c r="E17" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F17" s="53"/>
-      <c r="G17" s="44"/>
+      <c r="E17" s="36" t="s">
+        <v>148</v>
+      </c>
+      <c r="F17" s="60"/>
+      <c r="G17" s="51"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="37"/>
-      <c r="B18" s="37"/>
-      <c r="C18" s="37"/>
-      <c r="D18" s="54"/>
-      <c r="E18" s="38"/>
-      <c r="F18" s="54"/>
-      <c r="G18" s="54"/>
+      <c r="A18" s="44"/>
+      <c r="B18" s="44"/>
+      <c r="C18" s="44"/>
+      <c r="D18" s="61"/>
+      <c r="E18" s="45"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="61"/>
     </row>
     <row r="19" ht="12.75" customHeight="1"/>
     <row r="20" ht="12.75" customHeight="1"/>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -22,6 +22,9 @@
   </si>
   <si>
     <t>Team Members In Black</t>
+  </si>
+  <si>
+    <t>Colour code</t>
   </si>
   <si>
     <t>Test 
@@ -68,6 +71,9 @@
   </si>
   <si>
     <t>Successful authentication and redirection to user dashboard</t>
+  </si>
+  <si>
+    <t>Whenever we reach the entry point of the frontend, two errors always pops up at the bottom that says user not authenticated as well as authentication required</t>
   </si>
   <si>
     <t>Implies not part of this Release</t>
@@ -545,6 +551,11 @@
       <name val="Arial"/>
     </font>
     <font>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="10.0"/>
       <color theme="1"/>
@@ -561,11 +572,6 @@
       <name val="Arial"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12.0"/>
       <color theme="1"/>
@@ -577,7 +583,7 @@
       <name val="Arimo"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -588,12 +594,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF00FF00"/>
         <bgColor rgb="FF00FF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -770,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="64">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -781,61 +781,67 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="top"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="6" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
-    <xf borderId="0" fillId="6" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="6" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
@@ -843,100 +849,100 @@
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
-    <xf borderId="5" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
+    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="6" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="6" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="4" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="4" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="3" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="8" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="9" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="9" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="11" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="11" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="12" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="13" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="13" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="12" fillId="8" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="12" fillId="7" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="14" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="14" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="15" fillId="7" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="15" fillId="6" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1172,8 +1178,9 @@
     <col customWidth="1" min="6" max="6" width="16.0"/>
     <col customWidth="1" min="7" max="7" width="17.25"/>
     <col customWidth="1" min="8" max="8" width="17.75"/>
-    <col customWidth="1" min="9" max="9" width="15.25"/>
-    <col customWidth="1" min="10" max="11" width="8.88"/>
+    <col customWidth="1" min="9" max="9" width="29.38"/>
+    <col customWidth="1" min="10" max="10" width="8.88"/>
+    <col customWidth="1" min="11" max="11" width="10.88"/>
     <col customWidth="1" min="12" max="12" width="40.25"/>
     <col customWidth="1" min="13" max="26" width="8.88"/>
   </cols>
@@ -1188,5652 +1195,5658 @@
       <c r="E1" s="3" t="s">
         <v>2</v>
       </c>
+      <c r="K1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L1" s="5"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="D2" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="I2" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J2" s="7"/>
-      <c r="K2" s="8"/>
-      <c r="L2" s="9" t="s">
+      <c r="H2" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="M2" s="7"/>
-      <c r="N2" s="7"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
+      <c r="I2" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="J2" s="9"/>
+      <c r="K2" s="10"/>
+      <c r="L2" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="9"/>
+      <c r="P2" s="9"/>
+      <c r="Q2" s="9"/>
+      <c r="R2" s="9"/>
+      <c r="S2" s="9"/>
+      <c r="T2" s="9"/>
+      <c r="U2" s="9"/>
+      <c r="V2" s="9"/>
+      <c r="W2" s="9"/>
+      <c r="X2" s="9"/>
+      <c r="Y2" s="9"/>
+      <c r="Z2" s="9"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="10">
+      <c r="A3" s="12">
         <v>1.0</v>
       </c>
-      <c r="B3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C3" s="11" t="s">
+      <c r="B3" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="C3" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="D3" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="13"/>
-      <c r="H3" s="12"/>
-      <c r="I3" s="13"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="15" t="s">
+      <c r="E3" s="13" t="s">
         <v>16</v>
       </c>
+      <c r="F3" s="14"/>
+      <c r="G3" s="15"/>
+      <c r="H3" s="16"/>
+      <c r="I3" s="13" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="17"/>
+      <c r="L3" s="18" t="s">
+        <v>18</v>
+      </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="16">
+      <c r="A4" s="19">
         <f t="shared" ref="A4:A12" si="1">A3+1</f>
         <v>2</v>
       </c>
-      <c r="B4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>18</v>
-      </c>
-      <c r="E4" s="11" t="s">
+      <c r="B4" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" s="20" t="s">
         <v>19</v>
       </c>
-      <c r="F4" s="18"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="18"/>
-      <c r="I4" s="18"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="15" t="s">
+      <c r="D4" s="13" t="s">
         <v>20</v>
       </c>
+      <c r="E4" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="21"/>
+      <c r="G4" s="21"/>
+      <c r="H4" s="21"/>
+      <c r="I4" s="21"/>
+      <c r="K4" s="22"/>
+      <c r="L4" s="18" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="16">
+      <c r="A5" s="19">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="B5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="17" t="s">
+      <c r="B5" s="13" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="20" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="18"/>
-      <c r="G5" s="18"/>
-      <c r="H5" s="18"/>
-      <c r="I5" s="18"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>24</v>
       </c>
+      <c r="E5" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="21"/>
+      <c r="G5" s="21"/>
+      <c r="H5" s="21"/>
+      <c r="I5" s="21"/>
+      <c r="K5" s="23"/>
+      <c r="L5" s="18" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="16">
+      <c r="A6" s="19">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="B6" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C6" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D6" s="17" t="s">
+      <c r="B6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="E6" s="17" t="s">
+      <c r="C6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="G6" s="18"/>
-      <c r="H6" s="18"/>
-      <c r="I6" s="18"/>
+      <c r="D6" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="21"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="21"/>
+      <c r="I6" s="21"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="16">
+      <c r="A7" s="19">
         <f t="shared" si="1"/>
         <v>5</v>
       </c>
-      <c r="B7" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C7" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
+      <c r="B7" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="20" t="s">
+        <v>31</v>
+      </c>
+      <c r="E7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="F7" s="21"/>
+      <c r="G7" s="21"/>
+      <c r="H7" s="21"/>
+      <c r="I7" s="21"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="16">
+      <c r="A8" s="19">
         <f t="shared" si="1"/>
         <v>6</v>
       </c>
-      <c r="B8" s="17" t="s">
-        <v>25</v>
-      </c>
-      <c r="C8" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D8" s="17" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" s="17" t="s">
+      <c r="B8" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
+      <c r="D8" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="21"/>
+      <c r="G8" s="21"/>
+      <c r="H8" s="21"/>
+      <c r="I8" s="21"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="16">
+      <c r="A9" s="19">
         <f t="shared" si="1"/>
         <v>7</v>
       </c>
-      <c r="B9" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C9" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E9" s="17" t="s">
+      <c r="B9" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
+      <c r="C9" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="21"/>
+      <c r="G9" s="21"/>
+      <c r="H9" s="21"/>
+      <c r="I9" s="21"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="16">
+      <c r="A10" s="19">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="B10" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="C10" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="D10" s="17" t="s">
-        <v>37</v>
-      </c>
-      <c r="E10" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
+      <c r="B10" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C10" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="F10" s="21"/>
+      <c r="G10" s="21"/>
+      <c r="H10" s="21"/>
+      <c r="I10" s="21"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="16">
+      <c r="A11" s="19">
         <f t="shared" si="1"/>
         <v>9</v>
       </c>
-      <c r="B11" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C11" s="17" t="s">
-        <v>40</v>
-      </c>
-      <c r="D11" s="17" t="s">
+      <c r="B11" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="E11" s="17" t="s">
+      <c r="C11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
+      <c r="D11" s="20" t="s">
+        <v>43</v>
+      </c>
+      <c r="E11" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="F11" s="21"/>
+      <c r="G11" s="21"/>
+      <c r="H11" s="21"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="16">
+      <c r="A12" s="19">
         <f t="shared" si="1"/>
         <v>10</v>
       </c>
-      <c r="B12" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C12" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D12" s="17" t="s">
-        <v>44</v>
-      </c>
-      <c r="E12" s="17" t="s">
+      <c r="B12" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
+      <c r="D12" s="20" t="s">
+        <v>46</v>
+      </c>
+      <c r="E12" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="F12" s="21"/>
+      <c r="G12" s="21"/>
+      <c r="H12" s="21"/>
+      <c r="I12" s="21"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="16"/>
-      <c r="B13" s="17" t="s">
-        <v>39</v>
-      </c>
-      <c r="C13" s="17" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="17" t="s">
-        <v>46</v>
-      </c>
-      <c r="E13" s="17" t="s">
-        <v>47</v>
-      </c>
-      <c r="F13" s="18"/>
-      <c r="G13" s="18"/>
-      <c r="H13" s="18"/>
-      <c r="I13" s="18"/>
+      <c r="A13" s="19"/>
+      <c r="B13" s="20" t="s">
+        <v>41</v>
+      </c>
+      <c r="C13" s="20" t="s">
+        <v>45</v>
+      </c>
+      <c r="D13" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="E13" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="F13" s="21"/>
+      <c r="G13" s="21"/>
+      <c r="H13" s="21"/>
+      <c r="I13" s="21"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="16">
+      <c r="A14" s="19">
         <f>A12+1</f>
         <v>11</v>
       </c>
-      <c r="B14" s="17" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="17" t="s">
+      <c r="B14" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="E14" s="17" t="s">
+      <c r="C14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="F14" s="18"/>
-      <c r="G14" s="18"/>
-      <c r="H14" s="18"/>
-      <c r="I14" s="18"/>
+      <c r="D14" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="F14" s="21"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="21"/>
+      <c r="I14" s="21"/>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="16">
+      <c r="A15" s="19">
         <f t="shared" ref="A15:A33" si="2">A14+1</f>
         <v>12</v>
       </c>
-      <c r="B15" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C15" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D15" s="17" t="s">
+      <c r="B15" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="E15" s="17" t="s">
+      <c r="C15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="F15" s="18"/>
-      <c r="G15" s="18"/>
-      <c r="H15" s="18"/>
-      <c r="I15" s="18"/>
+      <c r="D15" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="E15" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="16">
+      <c r="A16" s="19">
         <f t="shared" si="2"/>
         <v>13</v>
       </c>
-      <c r="B16" s="17" t="s">
-        <v>52</v>
-      </c>
-      <c r="C16" s="17" t="s">
+      <c r="B16" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C16" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="D16" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="D16" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="E16" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F16" s="18"/>
-      <c r="G16" s="18"/>
-      <c r="H16" s="18"/>
-      <c r="I16" s="18"/>
+      <c r="E16" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="16">
+      <c r="A17" s="19">
         <f t="shared" si="2"/>
         <v>14</v>
       </c>
-      <c r="B17" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="C17" s="17" t="s">
-        <v>53</v>
-      </c>
-      <c r="D17" s="17" t="s">
-        <v>59</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="B17" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="F17" s="18"/>
-      <c r="G17" s="18"/>
-      <c r="H17" s="18"/>
-      <c r="I17" s="18"/>
+      <c r="C17" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="D17" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="E17" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="F17" s="21"/>
+      <c r="G17" s="21"/>
+      <c r="H17" s="21"/>
+      <c r="I17" s="21"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="16">
+      <c r="A18" s="19">
         <f t="shared" si="2"/>
         <v>15</v>
       </c>
-      <c r="B18" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="C18" s="17" t="s">
-        <v>62</v>
-      </c>
-      <c r="D18" s="17" t="s">
+      <c r="B18" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="E18" s="17" t="s">
+      <c r="C18" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="F18" s="18"/>
-      <c r="G18" s="18"/>
-      <c r="H18" s="18"/>
-      <c r="I18" s="18"/>
+      <c r="D18" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="E18" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="F18" s="21"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="21"/>
+      <c r="I18" s="21"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
-      <c r="A19" s="16">
+      <c r="A19" s="19">
         <f t="shared" si="2"/>
         <v>16</v>
       </c>
-      <c r="B19" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>66</v>
-      </c>
-      <c r="D19" s="17" t="s">
+      <c r="B19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="E19" s="17" t="s">
+      <c r="C19" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F19" s="18"/>
-      <c r="G19" s="18"/>
-      <c r="H19" s="18"/>
-      <c r="I19" s="18"/>
+      <c r="D19" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="E19" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="F19" s="21"/>
+      <c r="G19" s="21"/>
+      <c r="H19" s="21"/>
+      <c r="I19" s="21"/>
     </row>
     <row r="20" ht="12.75" customHeight="1">
-      <c r="A20" s="16">
+      <c r="A20" s="19">
         <f t="shared" si="2"/>
         <v>17</v>
       </c>
-      <c r="B20" s="17" t="s">
-        <v>65</v>
-      </c>
-      <c r="C20" s="17" t="s">
+      <c r="B20" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="C20" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="D20" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="D20" s="17" t="s">
-        <v>67</v>
-      </c>
-      <c r="E20" s="17" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="18"/>
-      <c r="G20" s="18"/>
-      <c r="H20" s="18"/>
-      <c r="I20" s="18"/>
+      <c r="E20" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="F20" s="21"/>
+      <c r="G20" s="21"/>
+      <c r="H20" s="21"/>
+      <c r="I20" s="21"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
-      <c r="A21" s="16">
+      <c r="A21" s="19">
         <f t="shared" si="2"/>
         <v>18</v>
       </c>
-      <c r="B21" s="17" t="s">
-        <v>71</v>
-      </c>
-      <c r="C21" s="17" t="s">
-        <v>72</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="B21" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="E21" s="17" t="s">
+      <c r="C21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F21" s="18"/>
-      <c r="G21" s="18"/>
-      <c r="H21" s="18"/>
-      <c r="I21" s="18"/>
+      <c r="D21" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="E21" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="F21" s="21"/>
+      <c r="G21" s="21"/>
+      <c r="H21" s="21"/>
+      <c r="I21" s="21"/>
     </row>
     <row r="22" ht="12.75" customHeight="1">
-      <c r="A22" s="16">
+      <c r="A22" s="19">
         <f t="shared" si="2"/>
         <v>19</v>
       </c>
-      <c r="B22" s="17" t="s">
-        <v>75</v>
-      </c>
-      <c r="C22" s="17" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="17" t="s">
+      <c r="B22" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="E22" s="17" t="s">
+      <c r="C22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="F22" s="18"/>
-      <c r="G22" s="18"/>
-      <c r="H22" s="18"/>
-      <c r="I22" s="18"/>
+      <c r="D22" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="E22" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="F22" s="21"/>
+      <c r="G22" s="21"/>
+      <c r="H22" s="21"/>
+      <c r="I22" s="21"/>
     </row>
     <row r="23" ht="12.75" customHeight="1">
-      <c r="A23" s="16">
+      <c r="A23" s="19">
         <f t="shared" si="2"/>
         <v>20</v>
       </c>
-      <c r="B23" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C23" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="17" t="s">
-        <v>80</v>
-      </c>
-      <c r="E23" s="17" t="s">
+      <c r="B23" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="F23" s="18"/>
-      <c r="G23" s="18"/>
-      <c r="H23" s="18"/>
-      <c r="I23" s="18"/>
+      <c r="C23" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D23" s="20" t="s">
+        <v>82</v>
+      </c>
+      <c r="E23" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="F23" s="21"/>
+      <c r="G23" s="21"/>
+      <c r="H23" s="21"/>
+      <c r="I23" s="21"/>
     </row>
     <row r="24" ht="12.75" customHeight="1">
-      <c r="A24" s="16">
+      <c r="A24" s="19">
         <f t="shared" si="2"/>
         <v>21</v>
       </c>
-      <c r="B24" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="17" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="17" t="s">
-        <v>82</v>
-      </c>
-      <c r="E24" s="17" t="s">
-        <v>83</v>
-      </c>
-      <c r="F24" s="18"/>
-      <c r="G24" s="18"/>
-      <c r="H24" s="18"/>
-      <c r="I24" s="18"/>
+      <c r="B24" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C24" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="D24" s="20" t="s">
+        <v>84</v>
+      </c>
+      <c r="E24" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="21"/>
+      <c r="G24" s="21"/>
+      <c r="H24" s="21"/>
+      <c r="I24" s="21"/>
     </row>
     <row r="25" ht="12.75" customHeight="1">
-      <c r="A25" s="16">
+      <c r="A25" s="19">
         <f t="shared" si="2"/>
         <v>22</v>
       </c>
-      <c r="B25" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="C25" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D25" s="17" t="s">
-        <v>85</v>
-      </c>
-      <c r="E25" s="17" t="s">
+      <c r="B25" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="F25" s="18"/>
-      <c r="G25" s="18"/>
-      <c r="H25" s="18"/>
-      <c r="I25" s="18"/>
+      <c r="C25" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="E25" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="F25" s="21"/>
+      <c r="G25" s="21"/>
+      <c r="H25" s="21"/>
+      <c r="I25" s="21"/>
     </row>
     <row r="26" ht="12.75" customHeight="1">
-      <c r="A26" s="16">
+      <c r="A26" s="19">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C26" s="17" t="s">
-        <v>88</v>
-      </c>
-      <c r="D26" s="17" t="s">
+      <c r="B26" s="24" t="s">
         <v>89</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="C26" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="F26" s="18"/>
-      <c r="G26" s="18"/>
-      <c r="H26" s="18"/>
-      <c r="I26" s="18"/>
+      <c r="D26" s="20" t="s">
+        <v>91</v>
+      </c>
+      <c r="E26" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="F26" s="21"/>
+      <c r="G26" s="21"/>
+      <c r="H26" s="21"/>
+      <c r="I26" s="21"/>
     </row>
     <row r="27" ht="12.75" customHeight="1">
-      <c r="A27" s="16">
+      <c r="A27" s="19">
         <f t="shared" si="2"/>
         <v>24</v>
       </c>
-      <c r="B27" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C27" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D27" s="17" t="s">
-        <v>91</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F27" s="18"/>
-      <c r="G27" s="18"/>
-      <c r="H27" s="18"/>
-      <c r="I27" s="18"/>
+      <c r="B27" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C27" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D27" s="20" t="s">
+        <v>93</v>
+      </c>
+      <c r="E27" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="F27" s="21"/>
+      <c r="G27" s="21"/>
+      <c r="H27" s="21"/>
+      <c r="I27" s="21"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
-      <c r="A28" s="16">
+      <c r="A28" s="19">
         <f t="shared" si="2"/>
         <v>25</v>
       </c>
-      <c r="B28" s="17" t="s">
-        <v>87</v>
-      </c>
-      <c r="C28" s="17" t="s">
-        <v>26</v>
-      </c>
-      <c r="D28" s="17" t="s">
-        <v>93</v>
-      </c>
-      <c r="E28" s="17" t="s">
-        <v>94</v>
-      </c>
-      <c r="F28" s="18"/>
-      <c r="G28" s="18"/>
-      <c r="H28" s="18"/>
-      <c r="I28" s="18"/>
+      <c r="B28" s="20" t="s">
+        <v>89</v>
+      </c>
+      <c r="C28" s="20" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="20" t="s">
+        <v>95</v>
+      </c>
+      <c r="E28" s="20" t="s">
+        <v>96</v>
+      </c>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
     </row>
     <row r="29" ht="12.75" customHeight="1">
-      <c r="A29" s="16">
+      <c r="A29" s="19">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B29" s="18"/>
-      <c r="C29" s="18"/>
-      <c r="D29" s="18"/>
-      <c r="E29" s="18"/>
-      <c r="F29" s="18"/>
-      <c r="G29" s="18"/>
-      <c r="H29" s="18"/>
-      <c r="I29" s="18"/>
+      <c r="B29" s="21"/>
+      <c r="C29" s="21"/>
+      <c r="D29" s="21"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
-      <c r="A30" s="16">
+      <c r="A30" s="19">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B30" s="18"/>
-      <c r="C30" s="22"/>
-      <c r="D30" s="18"/>
-      <c r="E30" s="18"/>
-      <c r="F30" s="18"/>
-      <c r="G30" s="18"/>
-      <c r="H30" s="18"/>
-      <c r="I30" s="18"/>
+      <c r="B30" s="21"/>
+      <c r="C30" s="25"/>
+      <c r="D30" s="21"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="21"/>
+      <c r="H30" s="21"/>
+      <c r="I30" s="21"/>
     </row>
     <row r="31" ht="12.75" customHeight="1">
-      <c r="A31" s="16">
+      <c r="A31" s="19">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B31" s="18"/>
-      <c r="C31" s="22"/>
-      <c r="D31" s="18"/>
-      <c r="E31" s="18"/>
-      <c r="F31" s="18"/>
-      <c r="G31" s="18"/>
-      <c r="H31" s="18"/>
-      <c r="I31" s="18"/>
+      <c r="B31" s="21"/>
+      <c r="C31" s="25"/>
+      <c r="D31" s="21"/>
+      <c r="E31" s="21"/>
+      <c r="F31" s="21"/>
+      <c r="G31" s="21"/>
+      <c r="H31" s="21"/>
+      <c r="I31" s="21"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
-      <c r="A32" s="16">
+      <c r="A32" s="19">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="18"/>
-      <c r="G32" s="18"/>
-      <c r="H32" s="18"/>
-      <c r="I32" s="18"/>
+      <c r="B32" s="21"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="21"/>
+      <c r="F32" s="21"/>
+      <c r="G32" s="21"/>
+      <c r="H32" s="21"/>
+      <c r="I32" s="21"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
-      <c r="A33" s="16">
+      <c r="A33" s="19">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="18"/>
-      <c r="G33" s="18"/>
-      <c r="H33" s="18"/>
-      <c r="I33" s="18"/>
+      <c r="B33" s="21"/>
+      <c r="C33" s="21"/>
+      <c r="D33" s="21"/>
+      <c r="E33" s="21"/>
+      <c r="F33" s="21"/>
+      <c r="G33" s="21"/>
+      <c r="H33" s="21"/>
+      <c r="I33" s="21"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="23"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="23"/>
+      <c r="A34" s="26"/>
+      <c r="B34" s="26"/>
+      <c r="C34" s="26"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="23"/>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
+      <c r="A35" s="26"/>
+      <c r="B35" s="26"/>
+      <c r="C35" s="26"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="23"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
+      <c r="A36" s="26"/>
+      <c r="B36" s="26"/>
+      <c r="C36" s="26"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="23"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
+      <c r="A37" s="26"/>
+      <c r="B37" s="26"/>
+      <c r="C37" s="26"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="23"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="K38" s="24" t="s">
-        <v>95</v>
-      </c>
-      <c r="Q38" s="24"/>
-      <c r="R38" s="24"/>
-      <c r="S38" s="24"/>
-      <c r="T38" s="24"/>
+      <c r="A38" s="26"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="26"/>
+      <c r="K38" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="Q38" s="4"/>
+      <c r="R38" s="4"/>
+      <c r="S38" s="4"/>
+      <c r="T38" s="4"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="23"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="23"/>
-      <c r="K39" s="24" t="s">
-        <v>96</v>
-      </c>
-      <c r="Q39" s="24"/>
-      <c r="R39" s="24"/>
-      <c r="S39" s="24"/>
-      <c r="T39" s="24"/>
+      <c r="A39" s="26"/>
+      <c r="B39" s="26"/>
+      <c r="C39" s="26"/>
+      <c r="K39" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="Q39" s="4"/>
+      <c r="R39" s="4"/>
+      <c r="S39" s="4"/>
+      <c r="T39" s="4"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="23"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="23"/>
-      <c r="K40" s="24" t="s">
-        <v>97</v>
-      </c>
-      <c r="Q40" s="24"/>
-      <c r="R40" s="24"/>
-      <c r="S40" s="24"/>
-      <c r="T40" s="24"/>
+      <c r="A40" s="26"/>
+      <c r="B40" s="26"/>
+      <c r="C40" s="26"/>
+      <c r="K40" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q40" s="4"/>
+      <c r="R40" s="4"/>
+      <c r="S40" s="4"/>
+      <c r="T40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="23"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="23"/>
-      <c r="K41" s="24" t="s">
-        <v>98</v>
-      </c>
-      <c r="Q41" s="24"/>
-      <c r="R41" s="24"/>
-      <c r="S41" s="24"/>
-      <c r="T41" s="24"/>
+      <c r="A41" s="26"/>
+      <c r="B41" s="26"/>
+      <c r="C41" s="26"/>
+      <c r="K41" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q41" s="4"/>
+      <c r="R41" s="4"/>
+      <c r="S41" s="4"/>
+      <c r="T41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="23"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="23"/>
-      <c r="K42" s="24" t="s">
-        <v>99</v>
-      </c>
-      <c r="Q42" s="24"/>
-      <c r="R42" s="24"/>
-      <c r="S42" s="24"/>
-      <c r="T42" s="24"/>
+      <c r="A42" s="26"/>
+      <c r="B42" s="26"/>
+      <c r="C42" s="26"/>
+      <c r="K42" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="Q42" s="4"/>
+      <c r="R42" s="4"/>
+      <c r="S42" s="4"/>
+      <c r="T42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="23"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="23"/>
-      <c r="K43" s="24" t="s">
-        <v>100</v>
-      </c>
-      <c r="Q43" s="24"/>
-      <c r="R43" s="24"/>
-      <c r="S43" s="24"/>
-      <c r="T43" s="24"/>
+      <c r="A43" s="26"/>
+      <c r="B43" s="26"/>
+      <c r="C43" s="26"/>
+      <c r="K43" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="Q43" s="4"/>
+      <c r="R43" s="4"/>
+      <c r="S43" s="4"/>
+      <c r="T43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="23"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="23"/>
-      <c r="K44" s="24"/>
-      <c r="R44" s="24"/>
-      <c r="S44" s="24"/>
-      <c r="T44" s="24"/>
+      <c r="A44" s="26"/>
+      <c r="B44" s="26"/>
+      <c r="C44" s="26"/>
+      <c r="K44" s="4"/>
+      <c r="R44" s="4"/>
+      <c r="S44" s="4"/>
+      <c r="T44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="23"/>
-      <c r="B45" s="23"/>
-      <c r="C45" s="23"/>
-      <c r="K45" s="24"/>
-      <c r="R45" s="24"/>
-      <c r="S45" s="24"/>
-      <c r="T45" s="24"/>
+      <c r="A45" s="26"/>
+      <c r="B45" s="26"/>
+      <c r="C45" s="26"/>
+      <c r="K45" s="4"/>
+      <c r="R45" s="4"/>
+      <c r="S45" s="4"/>
+      <c r="T45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="23"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="23"/>
-      <c r="K46" s="24"/>
-      <c r="R46" s="24"/>
-      <c r="S46" s="24"/>
-      <c r="T46" s="24"/>
+      <c r="A46" s="26"/>
+      <c r="B46" s="26"/>
+      <c r="C46" s="26"/>
+      <c r="K46" s="4"/>
+      <c r="R46" s="4"/>
+      <c r="S46" s="4"/>
+      <c r="T46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="23"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="23"/>
-      <c r="K47" s="24"/>
-      <c r="R47" s="24"/>
-      <c r="S47" s="24"/>
-      <c r="T47" s="24"/>
+      <c r="A47" s="26"/>
+      <c r="B47" s="26"/>
+      <c r="C47" s="26"/>
+      <c r="K47" s="4"/>
+      <c r="R47" s="4"/>
+      <c r="S47" s="4"/>
+      <c r="T47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="23"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="23"/>
-      <c r="K48" s="24"/>
-      <c r="L48" s="24"/>
-      <c r="M48" s="24"/>
-      <c r="N48" s="24"/>
-      <c r="O48" s="24"/>
-      <c r="P48" s="24"/>
-      <c r="Q48" s="24"/>
-      <c r="R48" s="24"/>
-      <c r="S48" s="24"/>
-      <c r="T48" s="24"/>
+      <c r="A48" s="26"/>
+      <c r="B48" s="26"/>
+      <c r="C48" s="26"/>
+      <c r="K48" s="4"/>
+      <c r="L48" s="4"/>
+      <c r="M48" s="4"/>
+      <c r="N48" s="4"/>
+      <c r="O48" s="4"/>
+      <c r="P48" s="4"/>
+      <c r="Q48" s="4"/>
+      <c r="R48" s="4"/>
+      <c r="S48" s="4"/>
+      <c r="T48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="23"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="23"/>
-      <c r="K49" s="24"/>
-      <c r="L49" s="24"/>
-      <c r="M49" s="24"/>
-      <c r="N49" s="24"/>
-      <c r="O49" s="24"/>
-      <c r="P49" s="24"/>
-      <c r="Q49" s="24"/>
-      <c r="R49" s="24"/>
-      <c r="S49" s="24"/>
-      <c r="T49" s="24"/>
+      <c r="A49" s="26"/>
+      <c r="B49" s="26"/>
+      <c r="C49" s="26"/>
+      <c r="K49" s="4"/>
+      <c r="L49" s="4"/>
+      <c r="M49" s="4"/>
+      <c r="N49" s="4"/>
+      <c r="O49" s="4"/>
+      <c r="P49" s="4"/>
+      <c r="Q49" s="4"/>
+      <c r="R49" s="4"/>
+      <c r="S49" s="4"/>
+      <c r="T49" s="4"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="23"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="23"/>
-      <c r="K50" s="24"/>
-      <c r="L50" s="24"/>
-      <c r="M50" s="24"/>
-      <c r="N50" s="24"/>
-      <c r="O50" s="24"/>
-      <c r="P50" s="24"/>
-      <c r="Q50" s="24"/>
-      <c r="R50" s="24"/>
-      <c r="S50" s="24"/>
-      <c r="T50" s="24"/>
+      <c r="A50" s="26"/>
+      <c r="B50" s="26"/>
+      <c r="C50" s="26"/>
+      <c r="K50" s="4"/>
+      <c r="L50" s="4"/>
+      <c r="M50" s="4"/>
+      <c r="N50" s="4"/>
+      <c r="O50" s="4"/>
+      <c r="P50" s="4"/>
+      <c r="Q50" s="4"/>
+      <c r="R50" s="4"/>
+      <c r="S50" s="4"/>
+      <c r="T50" s="4"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="23"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="K51" s="24"/>
-      <c r="L51" s="24"/>
-      <c r="M51" s="24"/>
-      <c r="N51" s="24"/>
-      <c r="O51" s="24"/>
-      <c r="P51" s="24"/>
-      <c r="Q51" s="24"/>
-      <c r="R51" s="24"/>
-      <c r="S51" s="24"/>
-      <c r="T51" s="24"/>
+      <c r="A51" s="26"/>
+      <c r="B51" s="26"/>
+      <c r="C51" s="26"/>
+      <c r="K51" s="4"/>
+      <c r="L51" s="4"/>
+      <c r="M51" s="4"/>
+      <c r="N51" s="4"/>
+      <c r="O51" s="4"/>
+      <c r="P51" s="4"/>
+      <c r="Q51" s="4"/>
+      <c r="R51" s="4"/>
+      <c r="S51" s="4"/>
+      <c r="T51" s="4"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="23"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="K52" s="24"/>
-      <c r="L52" s="24"/>
-      <c r="M52" s="24"/>
-      <c r="N52" s="24"/>
-      <c r="O52" s="24"/>
-      <c r="P52" s="24"/>
-      <c r="Q52" s="24"/>
-      <c r="R52" s="24"/>
-      <c r="S52" s="24"/>
-      <c r="T52" s="24"/>
+      <c r="A52" s="26"/>
+      <c r="B52" s="26"/>
+      <c r="C52" s="26"/>
+      <c r="K52" s="4"/>
+      <c r="L52" s="4"/>
+      <c r="M52" s="4"/>
+      <c r="N52" s="4"/>
+      <c r="O52" s="4"/>
+      <c r="P52" s="4"/>
+      <c r="Q52" s="4"/>
+      <c r="R52" s="4"/>
+      <c r="S52" s="4"/>
+      <c r="T52" s="4"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="23"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="23"/>
+      <c r="A53" s="26"/>
+      <c r="B53" s="26"/>
+      <c r="C53" s="26"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="23"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
+      <c r="A54" s="26"/>
+      <c r="B54" s="26"/>
+      <c r="C54" s="26"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="23"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
+      <c r="A55" s="26"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="26"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="23"/>
-      <c r="B56" s="23"/>
-      <c r="C56" s="23"/>
+      <c r="A56" s="26"/>
+      <c r="B56" s="26"/>
+      <c r="C56" s="26"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="23"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="23"/>
+      <c r="A57" s="26"/>
+      <c r="B57" s="26"/>
+      <c r="C57" s="26"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="23"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="23"/>
+      <c r="A58" s="26"/>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="23"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="23"/>
+      <c r="A59" s="26"/>
+      <c r="B59" s="26"/>
+      <c r="C59" s="26"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="23"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="23"/>
+      <c r="A60" s="26"/>
+      <c r="B60" s="26"/>
+      <c r="C60" s="26"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="23"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="23"/>
+      <c r="A61" s="26"/>
+      <c r="B61" s="26"/>
+      <c r="C61" s="26"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="23"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="23"/>
+      <c r="A62" s="26"/>
+      <c r="B62" s="26"/>
+      <c r="C62" s="26"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="23"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="23"/>
+      <c r="A63" s="26"/>
+      <c r="B63" s="26"/>
+      <c r="C63" s="26"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="23"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
+      <c r="A64" s="26"/>
+      <c r="B64" s="26"/>
+      <c r="C64" s="26"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="23"/>
-      <c r="B65" s="23"/>
-      <c r="C65" s="23"/>
+      <c r="A65" s="26"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="26"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="23"/>
-      <c r="B66" s="23"/>
-      <c r="C66" s="23"/>
+      <c r="A66" s="26"/>
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="23"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="23"/>
+      <c r="A67" s="26"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="26"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="23"/>
-      <c r="B68" s="23"/>
-      <c r="C68" s="23"/>
+      <c r="A68" s="26"/>
+      <c r="B68" s="26"/>
+      <c r="C68" s="26"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="23"/>
-      <c r="B69" s="23"/>
-      <c r="C69" s="23"/>
+      <c r="A69" s="26"/>
+      <c r="B69" s="26"/>
+      <c r="C69" s="26"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="23"/>
-      <c r="B70" s="23"/>
-      <c r="C70" s="23"/>
+      <c r="A70" s="26"/>
+      <c r="B70" s="26"/>
+      <c r="C70" s="26"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="23"/>
-      <c r="B71" s="23"/>
-      <c r="C71" s="23"/>
+      <c r="A71" s="26"/>
+      <c r="B71" s="26"/>
+      <c r="C71" s="26"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="23"/>
-      <c r="B72" s="23"/>
-      <c r="C72" s="23"/>
+      <c r="A72" s="26"/>
+      <c r="B72" s="26"/>
+      <c r="C72" s="26"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="23"/>
-      <c r="B73" s="23"/>
-      <c r="C73" s="23"/>
+      <c r="A73" s="26"/>
+      <c r="B73" s="26"/>
+      <c r="C73" s="26"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="23"/>
-      <c r="B74" s="23"/>
-      <c r="C74" s="23"/>
+      <c r="A74" s="26"/>
+      <c r="B74" s="26"/>
+      <c r="C74" s="26"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="23"/>
-      <c r="B75" s="23"/>
-      <c r="C75" s="23"/>
+      <c r="A75" s="26"/>
+      <c r="B75" s="26"/>
+      <c r="C75" s="26"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="23"/>
-      <c r="B76" s="23"/>
-      <c r="C76" s="23"/>
+      <c r="A76" s="26"/>
+      <c r="B76" s="26"/>
+      <c r="C76" s="26"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="23"/>
-      <c r="B77" s="23"/>
-      <c r="C77" s="23"/>
+      <c r="A77" s="26"/>
+      <c r="B77" s="26"/>
+      <c r="C77" s="26"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="23"/>
-      <c r="B78" s="23"/>
-      <c r="C78" s="23"/>
+      <c r="A78" s="26"/>
+      <c r="B78" s="26"/>
+      <c r="C78" s="26"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="23"/>
-      <c r="B79" s="23"/>
-      <c r="C79" s="23"/>
+      <c r="A79" s="26"/>
+      <c r="B79" s="26"/>
+      <c r="C79" s="26"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="23"/>
-      <c r="B80" s="23"/>
-      <c r="C80" s="23"/>
+      <c r="A80" s="26"/>
+      <c r="B80" s="26"/>
+      <c r="C80" s="26"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="23"/>
-      <c r="B81" s="23"/>
-      <c r="C81" s="23"/>
+      <c r="A81" s="26"/>
+      <c r="B81" s="26"/>
+      <c r="C81" s="26"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="23"/>
-      <c r="B82" s="23"/>
-      <c r="C82" s="23"/>
+      <c r="A82" s="26"/>
+      <c r="B82" s="26"/>
+      <c r="C82" s="26"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="23"/>
-      <c r="B83" s="23"/>
-      <c r="C83" s="23"/>
+      <c r="A83" s="26"/>
+      <c r="B83" s="26"/>
+      <c r="C83" s="26"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="23"/>
-      <c r="B84" s="23"/>
-      <c r="C84" s="23"/>
+      <c r="A84" s="26"/>
+      <c r="B84" s="26"/>
+      <c r="C84" s="26"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="23"/>
-      <c r="B85" s="23"/>
-      <c r="C85" s="23"/>
+      <c r="A85" s="26"/>
+      <c r="B85" s="26"/>
+      <c r="C85" s="26"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="23"/>
-      <c r="B86" s="23"/>
-      <c r="C86" s="23"/>
+      <c r="A86" s="26"/>
+      <c r="B86" s="26"/>
+      <c r="C86" s="26"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="23"/>
-      <c r="B87" s="23"/>
-      <c r="C87" s="23"/>
+      <c r="A87" s="26"/>
+      <c r="B87" s="26"/>
+      <c r="C87" s="26"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="23"/>
-      <c r="B88" s="23"/>
-      <c r="C88" s="23"/>
+      <c r="A88" s="26"/>
+      <c r="B88" s="26"/>
+      <c r="C88" s="26"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="23"/>
-      <c r="B89" s="23"/>
-      <c r="C89" s="23"/>
+      <c r="A89" s="26"/>
+      <c r="B89" s="26"/>
+      <c r="C89" s="26"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="23"/>
-      <c r="B90" s="23"/>
-      <c r="C90" s="23"/>
+      <c r="A90" s="26"/>
+      <c r="B90" s="26"/>
+      <c r="C90" s="26"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="23"/>
-      <c r="B91" s="23"/>
-      <c r="C91" s="23"/>
+      <c r="A91" s="26"/>
+      <c r="B91" s="26"/>
+      <c r="C91" s="26"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="23"/>
-      <c r="B92" s="23"/>
-      <c r="C92" s="23"/>
+      <c r="A92" s="26"/>
+      <c r="B92" s="26"/>
+      <c r="C92" s="26"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="23"/>
-      <c r="B93" s="23"/>
-      <c r="C93" s="23"/>
+      <c r="A93" s="26"/>
+      <c r="B93" s="26"/>
+      <c r="C93" s="26"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="23"/>
-      <c r="B94" s="23"/>
-      <c r="C94" s="23"/>
+      <c r="A94" s="26"/>
+      <c r="B94" s="26"/>
+      <c r="C94" s="26"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="23"/>
-      <c r="B95" s="23"/>
-      <c r="C95" s="23"/>
+      <c r="A95" s="26"/>
+      <c r="B95" s="26"/>
+      <c r="C95" s="26"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="23"/>
-      <c r="B96" s="23"/>
-      <c r="C96" s="23"/>
+      <c r="A96" s="26"/>
+      <c r="B96" s="26"/>
+      <c r="C96" s="26"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="23"/>
-      <c r="B97" s="23"/>
-      <c r="C97" s="23"/>
+      <c r="A97" s="26"/>
+      <c r="B97" s="26"/>
+      <c r="C97" s="26"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="A98" s="23"/>
-      <c r="B98" s="23"/>
-      <c r="C98" s="23"/>
+      <c r="A98" s="26"/>
+      <c r="B98" s="26"/>
+      <c r="C98" s="26"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="A99" s="23"/>
-      <c r="B99" s="23"/>
-      <c r="C99" s="23"/>
+      <c r="A99" s="26"/>
+      <c r="B99" s="26"/>
+      <c r="C99" s="26"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="A100" s="23"/>
-      <c r="B100" s="23"/>
-      <c r="C100" s="23"/>
+      <c r="A100" s="26"/>
+      <c r="B100" s="26"/>
+      <c r="C100" s="26"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="A101" s="23"/>
-      <c r="B101" s="23"/>
-      <c r="C101" s="23"/>
+      <c r="A101" s="26"/>
+      <c r="B101" s="26"/>
+      <c r="C101" s="26"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="A102" s="23"/>
-      <c r="B102" s="23"/>
-      <c r="C102" s="23"/>
+      <c r="A102" s="26"/>
+      <c r="B102" s="26"/>
+      <c r="C102" s="26"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="A103" s="23"/>
-      <c r="B103" s="23"/>
-      <c r="C103" s="23"/>
+      <c r="A103" s="26"/>
+      <c r="B103" s="26"/>
+      <c r="C103" s="26"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" s="23"/>
-      <c r="B104" s="23"/>
-      <c r="C104" s="23"/>
+      <c r="A104" s="26"/>
+      <c r="B104" s="26"/>
+      <c r="C104" s="26"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="23"/>
-      <c r="B105" s="23"/>
-      <c r="C105" s="23"/>
+      <c r="A105" s="26"/>
+      <c r="B105" s="26"/>
+      <c r="C105" s="26"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="23"/>
-      <c r="B106" s="23"/>
-      <c r="C106" s="23"/>
+      <c r="A106" s="26"/>
+      <c r="B106" s="26"/>
+      <c r="C106" s="26"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="23"/>
-      <c r="B107" s="23"/>
-      <c r="C107" s="23"/>
+      <c r="A107" s="26"/>
+      <c r="B107" s="26"/>
+      <c r="C107" s="26"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="23"/>
-      <c r="B108" s="23"/>
-      <c r="C108" s="23"/>
+      <c r="A108" s="26"/>
+      <c r="B108" s="26"/>
+      <c r="C108" s="26"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="23"/>
-      <c r="B109" s="23"/>
-      <c r="C109" s="23"/>
+      <c r="A109" s="26"/>
+      <c r="B109" s="26"/>
+      <c r="C109" s="26"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="23"/>
-      <c r="B110" s="23"/>
-      <c r="C110" s="23"/>
+      <c r="A110" s="26"/>
+      <c r="B110" s="26"/>
+      <c r="C110" s="26"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="23"/>
-      <c r="B111" s="23"/>
-      <c r="C111" s="23"/>
+      <c r="A111" s="26"/>
+      <c r="B111" s="26"/>
+      <c r="C111" s="26"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="A112" s="23"/>
-      <c r="B112" s="23"/>
-      <c r="C112" s="23"/>
+      <c r="A112" s="26"/>
+      <c r="B112" s="26"/>
+      <c r="C112" s="26"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="A113" s="23"/>
-      <c r="B113" s="23"/>
-      <c r="C113" s="23"/>
+      <c r="A113" s="26"/>
+      <c r="B113" s="26"/>
+      <c r="C113" s="26"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="23"/>
-      <c r="B114" s="23"/>
-      <c r="C114" s="23"/>
+      <c r="A114" s="26"/>
+      <c r="B114" s="26"/>
+      <c r="C114" s="26"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="23"/>
-      <c r="B115" s="23"/>
-      <c r="C115" s="23"/>
+      <c r="A115" s="26"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="23"/>
-      <c r="B116" s="23"/>
-      <c r="C116" s="23"/>
+      <c r="A116" s="26"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="A117" s="23"/>
-      <c r="B117" s="23"/>
-      <c r="C117" s="23"/>
+      <c r="A117" s="26"/>
+      <c r="B117" s="26"/>
+      <c r="C117" s="26"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="A118" s="23"/>
-      <c r="B118" s="23"/>
-      <c r="C118" s="23"/>
+      <c r="A118" s="26"/>
+      <c r="B118" s="26"/>
+      <c r="C118" s="26"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="23"/>
-      <c r="B119" s="23"/>
-      <c r="C119" s="23"/>
+      <c r="A119" s="26"/>
+      <c r="B119" s="26"/>
+      <c r="C119" s="26"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="A120" s="23"/>
-      <c r="B120" s="23"/>
-      <c r="C120" s="23"/>
+      <c r="A120" s="26"/>
+      <c r="B120" s="26"/>
+      <c r="C120" s="26"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="A121" s="23"/>
-      <c r="B121" s="23"/>
-      <c r="C121" s="23"/>
+      <c r="A121" s="26"/>
+      <c r="B121" s="26"/>
+      <c r="C121" s="26"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="A122" s="23"/>
-      <c r="B122" s="23"/>
-      <c r="C122" s="23"/>
+      <c r="A122" s="26"/>
+      <c r="B122" s="26"/>
+      <c r="C122" s="26"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="A123" s="23"/>
-      <c r="B123" s="23"/>
-      <c r="C123" s="23"/>
+      <c r="A123" s="26"/>
+      <c r="B123" s="26"/>
+      <c r="C123" s="26"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="A124" s="23"/>
-      <c r="B124" s="23"/>
-      <c r="C124" s="23"/>
+      <c r="A124" s="26"/>
+      <c r="B124" s="26"/>
+      <c r="C124" s="26"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="A125" s="23"/>
-      <c r="B125" s="23"/>
-      <c r="C125" s="23"/>
+      <c r="A125" s="26"/>
+      <c r="B125" s="26"/>
+      <c r="C125" s="26"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="A126" s="23"/>
-      <c r="B126" s="23"/>
-      <c r="C126" s="23"/>
+      <c r="A126" s="26"/>
+      <c r="B126" s="26"/>
+      <c r="C126" s="26"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="23"/>
-      <c r="B127" s="23"/>
-      <c r="C127" s="23"/>
+      <c r="A127" s="26"/>
+      <c r="B127" s="26"/>
+      <c r="C127" s="26"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="23"/>
-      <c r="B128" s="23"/>
-      <c r="C128" s="23"/>
+      <c r="A128" s="26"/>
+      <c r="B128" s="26"/>
+      <c r="C128" s="26"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="A129" s="23"/>
-      <c r="B129" s="23"/>
-      <c r="C129" s="23"/>
+      <c r="A129" s="26"/>
+      <c r="B129" s="26"/>
+      <c r="C129" s="26"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="A130" s="23"/>
-      <c r="B130" s="23"/>
-      <c r="C130" s="23"/>
+      <c r="A130" s="26"/>
+      <c r="B130" s="26"/>
+      <c r="C130" s="26"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="A131" s="23"/>
-      <c r="B131" s="23"/>
-      <c r="C131" s="23"/>
+      <c r="A131" s="26"/>
+      <c r="B131" s="26"/>
+      <c r="C131" s="26"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="A132" s="23"/>
-      <c r="B132" s="23"/>
-      <c r="C132" s="23"/>
+      <c r="A132" s="26"/>
+      <c r="B132" s="26"/>
+      <c r="C132" s="26"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="A133" s="23"/>
-      <c r="B133" s="23"/>
-      <c r="C133" s="23"/>
+      <c r="A133" s="26"/>
+      <c r="B133" s="26"/>
+      <c r="C133" s="26"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="A134" s="23"/>
-      <c r="B134" s="23"/>
-      <c r="C134" s="23"/>
+      <c r="A134" s="26"/>
+      <c r="B134" s="26"/>
+      <c r="C134" s="26"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="A135" s="23"/>
-      <c r="B135" s="23"/>
-      <c r="C135" s="23"/>
+      <c r="A135" s="26"/>
+      <c r="B135" s="26"/>
+      <c r="C135" s="26"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="A136" s="23"/>
-      <c r="B136" s="23"/>
-      <c r="C136" s="23"/>
+      <c r="A136" s="26"/>
+      <c r="B136" s="26"/>
+      <c r="C136" s="26"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="A137" s="23"/>
-      <c r="B137" s="23"/>
-      <c r="C137" s="23"/>
+      <c r="A137" s="26"/>
+      <c r="B137" s="26"/>
+      <c r="C137" s="26"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="A138" s="23"/>
-      <c r="B138" s="23"/>
-      <c r="C138" s="23"/>
+      <c r="A138" s="26"/>
+      <c r="B138" s="26"/>
+      <c r="C138" s="26"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="A139" s="23"/>
-      <c r="B139" s="23"/>
-      <c r="C139" s="23"/>
+      <c r="A139" s="26"/>
+      <c r="B139" s="26"/>
+      <c r="C139" s="26"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="A140" s="23"/>
-      <c r="B140" s="23"/>
-      <c r="C140" s="23"/>
+      <c r="A140" s="26"/>
+      <c r="B140" s="26"/>
+      <c r="C140" s="26"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="A141" s="23"/>
-      <c r="B141" s="23"/>
-      <c r="C141" s="23"/>
+      <c r="A141" s="26"/>
+      <c r="B141" s="26"/>
+      <c r="C141" s="26"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="A142" s="23"/>
-      <c r="B142" s="23"/>
-      <c r="C142" s="23"/>
+      <c r="A142" s="26"/>
+      <c r="B142" s="26"/>
+      <c r="C142" s="26"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="A143" s="23"/>
-      <c r="B143" s="23"/>
-      <c r="C143" s="23"/>
+      <c r="A143" s="26"/>
+      <c r="B143" s="26"/>
+      <c r="C143" s="26"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="A144" s="23"/>
-      <c r="B144" s="23"/>
-      <c r="C144" s="23"/>
+      <c r="A144" s="26"/>
+      <c r="B144" s="26"/>
+      <c r="C144" s="26"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="A145" s="23"/>
-      <c r="B145" s="23"/>
-      <c r="C145" s="23"/>
+      <c r="A145" s="26"/>
+      <c r="B145" s="26"/>
+      <c r="C145" s="26"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="A146" s="23"/>
-      <c r="B146" s="23"/>
-      <c r="C146" s="23"/>
+      <c r="A146" s="26"/>
+      <c r="B146" s="26"/>
+      <c r="C146" s="26"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="A147" s="23"/>
-      <c r="B147" s="23"/>
-      <c r="C147" s="23"/>
+      <c r="A147" s="26"/>
+      <c r="B147" s="26"/>
+      <c r="C147" s="26"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="23"/>
-      <c r="B148" s="23"/>
-      <c r="C148" s="23"/>
+      <c r="A148" s="26"/>
+      <c r="B148" s="26"/>
+      <c r="C148" s="26"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="A149" s="23"/>
-      <c r="B149" s="23"/>
-      <c r="C149" s="23"/>
+      <c r="A149" s="26"/>
+      <c r="B149" s="26"/>
+      <c r="C149" s="26"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="A150" s="23"/>
-      <c r="B150" s="23"/>
-      <c r="C150" s="23"/>
+      <c r="A150" s="26"/>
+      <c r="B150" s="26"/>
+      <c r="C150" s="26"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="A151" s="23"/>
-      <c r="B151" s="23"/>
-      <c r="C151" s="23"/>
+      <c r="A151" s="26"/>
+      <c r="B151" s="26"/>
+      <c r="C151" s="26"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="A152" s="23"/>
-      <c r="B152" s="23"/>
-      <c r="C152" s="23"/>
+      <c r="A152" s="26"/>
+      <c r="B152" s="26"/>
+      <c r="C152" s="26"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="A153" s="23"/>
-      <c r="B153" s="23"/>
-      <c r="C153" s="23"/>
+      <c r="A153" s="26"/>
+      <c r="B153" s="26"/>
+      <c r="C153" s="26"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="A154" s="23"/>
-      <c r="B154" s="23"/>
-      <c r="C154" s="23"/>
+      <c r="A154" s="26"/>
+      <c r="B154" s="26"/>
+      <c r="C154" s="26"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="A155" s="23"/>
-      <c r="B155" s="23"/>
-      <c r="C155" s="23"/>
+      <c r="A155" s="26"/>
+      <c r="B155" s="26"/>
+      <c r="C155" s="26"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="A156" s="23"/>
-      <c r="B156" s="23"/>
-      <c r="C156" s="23"/>
+      <c r="A156" s="26"/>
+      <c r="B156" s="26"/>
+      <c r="C156" s="26"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="A157" s="23"/>
-      <c r="B157" s="23"/>
-      <c r="C157" s="23"/>
+      <c r="A157" s="26"/>
+      <c r="B157" s="26"/>
+      <c r="C157" s="26"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="A158" s="23"/>
-      <c r="B158" s="23"/>
-      <c r="C158" s="23"/>
+      <c r="A158" s="26"/>
+      <c r="B158" s="26"/>
+      <c r="C158" s="26"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="A159" s="23"/>
-      <c r="B159" s="23"/>
-      <c r="C159" s="23"/>
+      <c r="A159" s="26"/>
+      <c r="B159" s="26"/>
+      <c r="C159" s="26"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="A160" s="23"/>
-      <c r="B160" s="23"/>
-      <c r="C160" s="23"/>
+      <c r="A160" s="26"/>
+      <c r="B160" s="26"/>
+      <c r="C160" s="26"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="A161" s="23"/>
-      <c r="B161" s="23"/>
-      <c r="C161" s="23"/>
+      <c r="A161" s="26"/>
+      <c r="B161" s="26"/>
+      <c r="C161" s="26"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="A162" s="23"/>
-      <c r="B162" s="23"/>
-      <c r="C162" s="23"/>
+      <c r="A162" s="26"/>
+      <c r="B162" s="26"/>
+      <c r="C162" s="26"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="A163" s="23"/>
-      <c r="B163" s="23"/>
-      <c r="C163" s="23"/>
+      <c r="A163" s="26"/>
+      <c r="B163" s="26"/>
+      <c r="C163" s="26"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="A164" s="23"/>
-      <c r="B164" s="23"/>
-      <c r="C164" s="23"/>
+      <c r="A164" s="26"/>
+      <c r="B164" s="26"/>
+      <c r="C164" s="26"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="A165" s="23"/>
-      <c r="B165" s="23"/>
-      <c r="C165" s="23"/>
+      <c r="A165" s="26"/>
+      <c r="B165" s="26"/>
+      <c r="C165" s="26"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="A166" s="23"/>
-      <c r="B166" s="23"/>
-      <c r="C166" s="23"/>
+      <c r="A166" s="26"/>
+      <c r="B166" s="26"/>
+      <c r="C166" s="26"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="A167" s="23"/>
-      <c r="B167" s="23"/>
-      <c r="C167" s="23"/>
+      <c r="A167" s="26"/>
+      <c r="B167" s="26"/>
+      <c r="C167" s="26"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="23"/>
-      <c r="B168" s="23"/>
-      <c r="C168" s="23"/>
+      <c r="A168" s="26"/>
+      <c r="B168" s="26"/>
+      <c r="C168" s="26"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="A169" s="23"/>
-      <c r="B169" s="23"/>
-      <c r="C169" s="23"/>
+      <c r="A169" s="26"/>
+      <c r="B169" s="26"/>
+      <c r="C169" s="26"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="A170" s="23"/>
-      <c r="B170" s="23"/>
-      <c r="C170" s="23"/>
+      <c r="A170" s="26"/>
+      <c r="B170" s="26"/>
+      <c r="C170" s="26"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="A171" s="23"/>
-      <c r="B171" s="23"/>
-      <c r="C171" s="23"/>
+      <c r="A171" s="26"/>
+      <c r="B171" s="26"/>
+      <c r="C171" s="26"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="A172" s="23"/>
-      <c r="B172" s="23"/>
-      <c r="C172" s="23"/>
+      <c r="A172" s="26"/>
+      <c r="B172" s="26"/>
+      <c r="C172" s="26"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="A173" s="23"/>
-      <c r="B173" s="23"/>
-      <c r="C173" s="23"/>
+      <c r="A173" s="26"/>
+      <c r="B173" s="26"/>
+      <c r="C173" s="26"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="A174" s="23"/>
-      <c r="B174" s="23"/>
-      <c r="C174" s="23"/>
+      <c r="A174" s="26"/>
+      <c r="B174" s="26"/>
+      <c r="C174" s="26"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="A175" s="23"/>
-      <c r="B175" s="23"/>
-      <c r="C175" s="23"/>
+      <c r="A175" s="26"/>
+      <c r="B175" s="26"/>
+      <c r="C175" s="26"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="A176" s="23"/>
-      <c r="B176" s="23"/>
-      <c r="C176" s="23"/>
+      <c r="A176" s="26"/>
+      <c r="B176" s="26"/>
+      <c r="C176" s="26"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="A177" s="23"/>
-      <c r="B177" s="23"/>
-      <c r="C177" s="23"/>
+      <c r="A177" s="26"/>
+      <c r="B177" s="26"/>
+      <c r="C177" s="26"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="23"/>
-      <c r="B178" s="23"/>
-      <c r="C178" s="23"/>
+      <c r="A178" s="26"/>
+      <c r="B178" s="26"/>
+      <c r="C178" s="26"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="A179" s="23"/>
-      <c r="B179" s="23"/>
-      <c r="C179" s="23"/>
+      <c r="A179" s="26"/>
+      <c r="B179" s="26"/>
+      <c r="C179" s="26"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="A180" s="23"/>
-      <c r="B180" s="23"/>
-      <c r="C180" s="23"/>
+      <c r="A180" s="26"/>
+      <c r="B180" s="26"/>
+      <c r="C180" s="26"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="A181" s="23"/>
-      <c r="B181" s="23"/>
-      <c r="C181" s="23"/>
+      <c r="A181" s="26"/>
+      <c r="B181" s="26"/>
+      <c r="C181" s="26"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="A182" s="23"/>
-      <c r="B182" s="23"/>
-      <c r="C182" s="23"/>
+      <c r="A182" s="26"/>
+      <c r="B182" s="26"/>
+      <c r="C182" s="26"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="A183" s="23"/>
-      <c r="B183" s="23"/>
-      <c r="C183" s="23"/>
+      <c r="A183" s="26"/>
+      <c r="B183" s="26"/>
+      <c r="C183" s="26"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="A184" s="23"/>
-      <c r="B184" s="23"/>
-      <c r="C184" s="23"/>
+      <c r="A184" s="26"/>
+      <c r="B184" s="26"/>
+      <c r="C184" s="26"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="A185" s="23"/>
-      <c r="B185" s="23"/>
-      <c r="C185" s="23"/>
+      <c r="A185" s="26"/>
+      <c r="B185" s="26"/>
+      <c r="C185" s="26"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="A186" s="23"/>
-      <c r="B186" s="23"/>
-      <c r="C186" s="23"/>
+      <c r="A186" s="26"/>
+      <c r="B186" s="26"/>
+      <c r="C186" s="26"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="A187" s="23"/>
-      <c r="B187" s="23"/>
-      <c r="C187" s="23"/>
+      <c r="A187" s="26"/>
+      <c r="B187" s="26"/>
+      <c r="C187" s="26"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="23"/>
-      <c r="B188" s="23"/>
-      <c r="C188" s="23"/>
+      <c r="A188" s="26"/>
+      <c r="B188" s="26"/>
+      <c r="C188" s="26"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="A189" s="23"/>
-      <c r="B189" s="23"/>
-      <c r="C189" s="23"/>
+      <c r="A189" s="26"/>
+      <c r="B189" s="26"/>
+      <c r="C189" s="26"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="A190" s="23"/>
-      <c r="B190" s="23"/>
-      <c r="C190" s="23"/>
+      <c r="A190" s="26"/>
+      <c r="B190" s="26"/>
+      <c r="C190" s="26"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="A191" s="23"/>
-      <c r="B191" s="23"/>
-      <c r="C191" s="23"/>
+      <c r="A191" s="26"/>
+      <c r="B191" s="26"/>
+      <c r="C191" s="26"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="A192" s="23"/>
-      <c r="B192" s="23"/>
-      <c r="C192" s="23"/>
+      <c r="A192" s="26"/>
+      <c r="B192" s="26"/>
+      <c r="C192" s="26"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="A193" s="23"/>
-      <c r="B193" s="23"/>
-      <c r="C193" s="23"/>
+      <c r="A193" s="26"/>
+      <c r="B193" s="26"/>
+      <c r="C193" s="26"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="A194" s="23"/>
-      <c r="B194" s="23"/>
-      <c r="C194" s="23"/>
+      <c r="A194" s="26"/>
+      <c r="B194" s="26"/>
+      <c r="C194" s="26"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="A195" s="23"/>
-      <c r="B195" s="23"/>
-      <c r="C195" s="23"/>
+      <c r="A195" s="26"/>
+      <c r="B195" s="26"/>
+      <c r="C195" s="26"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="A196" s="23"/>
-      <c r="B196" s="23"/>
-      <c r="C196" s="23"/>
+      <c r="A196" s="26"/>
+      <c r="B196" s="26"/>
+      <c r="C196" s="26"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="A197" s="23"/>
-      <c r="B197" s="23"/>
-      <c r="C197" s="23"/>
+      <c r="A197" s="26"/>
+      <c r="B197" s="26"/>
+      <c r="C197" s="26"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="A198" s="23"/>
-      <c r="B198" s="23"/>
-      <c r="C198" s="23"/>
+      <c r="A198" s="26"/>
+      <c r="B198" s="26"/>
+      <c r="C198" s="26"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="A199" s="23"/>
-      <c r="B199" s="23"/>
-      <c r="C199" s="23"/>
+      <c r="A199" s="26"/>
+      <c r="B199" s="26"/>
+      <c r="C199" s="26"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="A200" s="23"/>
-      <c r="B200" s="23"/>
-      <c r="C200" s="23"/>
+      <c r="A200" s="26"/>
+      <c r="B200" s="26"/>
+      <c r="C200" s="26"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="A201" s="23"/>
-      <c r="B201" s="23"/>
-      <c r="C201" s="23"/>
+      <c r="A201" s="26"/>
+      <c r="B201" s="26"/>
+      <c r="C201" s="26"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="A202" s="23"/>
-      <c r="B202" s="23"/>
-      <c r="C202" s="23"/>
+      <c r="A202" s="26"/>
+      <c r="B202" s="26"/>
+      <c r="C202" s="26"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="A203" s="23"/>
-      <c r="B203" s="23"/>
-      <c r="C203" s="23"/>
+      <c r="A203" s="26"/>
+      <c r="B203" s="26"/>
+      <c r="C203" s="26"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="A204" s="23"/>
-      <c r="B204" s="23"/>
-      <c r="C204" s="23"/>
+      <c r="A204" s="26"/>
+      <c r="B204" s="26"/>
+      <c r="C204" s="26"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="A205" s="23"/>
-      <c r="B205" s="23"/>
-      <c r="C205" s="23"/>
+      <c r="A205" s="26"/>
+      <c r="B205" s="26"/>
+      <c r="C205" s="26"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="A206" s="23"/>
-      <c r="B206" s="23"/>
-      <c r="C206" s="23"/>
+      <c r="A206" s="26"/>
+      <c r="B206" s="26"/>
+      <c r="C206" s="26"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="A207" s="23"/>
-      <c r="B207" s="23"/>
-      <c r="C207" s="23"/>
+      <c r="A207" s="26"/>
+      <c r="B207" s="26"/>
+      <c r="C207" s="26"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="23"/>
-      <c r="B208" s="23"/>
-      <c r="C208" s="23"/>
+      <c r="A208" s="26"/>
+      <c r="B208" s="26"/>
+      <c r="C208" s="26"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="A209" s="23"/>
-      <c r="B209" s="23"/>
-      <c r="C209" s="23"/>
+      <c r="A209" s="26"/>
+      <c r="B209" s="26"/>
+      <c r="C209" s="26"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="A210" s="23"/>
-      <c r="B210" s="23"/>
-      <c r="C210" s="23"/>
+      <c r="A210" s="26"/>
+      <c r="B210" s="26"/>
+      <c r="C210" s="26"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="A211" s="23"/>
-      <c r="B211" s="23"/>
-      <c r="C211" s="23"/>
+      <c r="A211" s="26"/>
+      <c r="B211" s="26"/>
+      <c r="C211" s="26"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="A212" s="23"/>
-      <c r="B212" s="23"/>
-      <c r="C212" s="23"/>
+      <c r="A212" s="26"/>
+      <c r="B212" s="26"/>
+      <c r="C212" s="26"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="A213" s="23"/>
-      <c r="B213" s="23"/>
-      <c r="C213" s="23"/>
+      <c r="A213" s="26"/>
+      <c r="B213" s="26"/>
+      <c r="C213" s="26"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="A214" s="23"/>
-      <c r="B214" s="23"/>
-      <c r="C214" s="23"/>
+      <c r="A214" s="26"/>
+      <c r="B214" s="26"/>
+      <c r="C214" s="26"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="A215" s="23"/>
-      <c r="B215" s="23"/>
-      <c r="C215" s="23"/>
+      <c r="A215" s="26"/>
+      <c r="B215" s="26"/>
+      <c r="C215" s="26"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="A216" s="23"/>
-      <c r="B216" s="23"/>
-      <c r="C216" s="23"/>
+      <c r="A216" s="26"/>
+      <c r="B216" s="26"/>
+      <c r="C216" s="26"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="A217" s="23"/>
-      <c r="B217" s="23"/>
-      <c r="C217" s="23"/>
+      <c r="A217" s="26"/>
+      <c r="B217" s="26"/>
+      <c r="C217" s="26"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="A218" s="23"/>
-      <c r="B218" s="23"/>
-      <c r="C218" s="23"/>
+      <c r="A218" s="26"/>
+      <c r="B218" s="26"/>
+      <c r="C218" s="26"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="A219" s="23"/>
-      <c r="B219" s="23"/>
-      <c r="C219" s="23"/>
+      <c r="A219" s="26"/>
+      <c r="B219" s="26"/>
+      <c r="C219" s="26"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="A220" s="23"/>
-      <c r="B220" s="23"/>
-      <c r="C220" s="23"/>
+      <c r="A220" s="26"/>
+      <c r="B220" s="26"/>
+      <c r="C220" s="26"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="A221" s="23"/>
-      <c r="B221" s="23"/>
-      <c r="C221" s="23"/>
+      <c r="A221" s="26"/>
+      <c r="B221" s="26"/>
+      <c r="C221" s="26"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="A222" s="23"/>
-      <c r="B222" s="23"/>
-      <c r="C222" s="23"/>
+      <c r="A222" s="26"/>
+      <c r="B222" s="26"/>
+      <c r="C222" s="26"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="A223" s="23"/>
-      <c r="B223" s="23"/>
-      <c r="C223" s="23"/>
+      <c r="A223" s="26"/>
+      <c r="B223" s="26"/>
+      <c r="C223" s="26"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="A224" s="23"/>
-      <c r="B224" s="23"/>
-      <c r="C224" s="23"/>
+      <c r="A224" s="26"/>
+      <c r="B224" s="26"/>
+      <c r="C224" s="26"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="A225" s="23"/>
-      <c r="B225" s="23"/>
-      <c r="C225" s="23"/>
+      <c r="A225" s="26"/>
+      <c r="B225" s="26"/>
+      <c r="C225" s="26"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="23"/>
-      <c r="B226" s="23"/>
-      <c r="C226" s="23"/>
+      <c r="A226" s="26"/>
+      <c r="B226" s="26"/>
+      <c r="C226" s="26"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="23"/>
-      <c r="B227" s="23"/>
-      <c r="C227" s="23"/>
+      <c r="A227" s="26"/>
+      <c r="B227" s="26"/>
+      <c r="C227" s="26"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="23"/>
-      <c r="B228" s="23"/>
-      <c r="C228" s="23"/>
+      <c r="A228" s="26"/>
+      <c r="B228" s="26"/>
+      <c r="C228" s="26"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="23"/>
-      <c r="B229" s="23"/>
-      <c r="C229" s="23"/>
+      <c r="A229" s="26"/>
+      <c r="B229" s="26"/>
+      <c r="C229" s="26"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="23"/>
-      <c r="B230" s="23"/>
-      <c r="C230" s="23"/>
+      <c r="A230" s="26"/>
+      <c r="B230" s="26"/>
+      <c r="C230" s="26"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="A231" s="23"/>
-      <c r="B231" s="23"/>
-      <c r="C231" s="23"/>
+      <c r="A231" s="26"/>
+      <c r="B231" s="26"/>
+      <c r="C231" s="26"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="A232" s="23"/>
-      <c r="B232" s="23"/>
-      <c r="C232" s="23"/>
+      <c r="A232" s="26"/>
+      <c r="B232" s="26"/>
+      <c r="C232" s="26"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="A233" s="23"/>
-      <c r="B233" s="23"/>
-      <c r="C233" s="23"/>
+      <c r="A233" s="26"/>
+      <c r="B233" s="26"/>
+      <c r="C233" s="26"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="A234" s="23"/>
-      <c r="B234" s="23"/>
-      <c r="C234" s="23"/>
+      <c r="A234" s="26"/>
+      <c r="B234" s="26"/>
+      <c r="C234" s="26"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="A235" s="23"/>
-      <c r="B235" s="23"/>
-      <c r="C235" s="23"/>
+      <c r="A235" s="26"/>
+      <c r="B235" s="26"/>
+      <c r="C235" s="26"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="A236" s="23"/>
-      <c r="B236" s="23"/>
-      <c r="C236" s="23"/>
+      <c r="A236" s="26"/>
+      <c r="B236" s="26"/>
+      <c r="C236" s="26"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="A237" s="23"/>
-      <c r="B237" s="23"/>
-      <c r="C237" s="23"/>
+      <c r="A237" s="26"/>
+      <c r="B237" s="26"/>
+      <c r="C237" s="26"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="A238" s="23"/>
-      <c r="B238" s="23"/>
-      <c r="C238" s="23"/>
+      <c r="A238" s="26"/>
+      <c r="B238" s="26"/>
+      <c r="C238" s="26"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="A239" s="23"/>
-      <c r="B239" s="23"/>
-      <c r="C239" s="23"/>
+      <c r="A239" s="26"/>
+      <c r="B239" s="26"/>
+      <c r="C239" s="26"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="A240" s="23"/>
-      <c r="B240" s="23"/>
-      <c r="C240" s="23"/>
+      <c r="A240" s="26"/>
+      <c r="B240" s="26"/>
+      <c r="C240" s="26"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="A241" s="23"/>
-      <c r="B241" s="23"/>
-      <c r="C241" s="23"/>
+      <c r="A241" s="26"/>
+      <c r="B241" s="26"/>
+      <c r="C241" s="26"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="A242" s="23"/>
-      <c r="B242" s="23"/>
-      <c r="C242" s="23"/>
+      <c r="A242" s="26"/>
+      <c r="B242" s="26"/>
+      <c r="C242" s="26"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="A243" s="23"/>
-      <c r="B243" s="23"/>
-      <c r="C243" s="23"/>
+      <c r="A243" s="26"/>
+      <c r="B243" s="26"/>
+      <c r="C243" s="26"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="A244" s="23"/>
-      <c r="B244" s="23"/>
-      <c r="C244" s="23"/>
+      <c r="A244" s="26"/>
+      <c r="B244" s="26"/>
+      <c r="C244" s="26"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="A245" s="23"/>
-      <c r="B245" s="23"/>
-      <c r="C245" s="23"/>
+      <c r="A245" s="26"/>
+      <c r="B245" s="26"/>
+      <c r="C245" s="26"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="A246" s="23"/>
-      <c r="B246" s="23"/>
-      <c r="C246" s="23"/>
+      <c r="A246" s="26"/>
+      <c r="B246" s="26"/>
+      <c r="C246" s="26"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="A247" s="23"/>
-      <c r="B247" s="23"/>
-      <c r="C247" s="23"/>
+      <c r="A247" s="26"/>
+      <c r="B247" s="26"/>
+      <c r="C247" s="26"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="23"/>
-      <c r="B248" s="23"/>
-      <c r="C248" s="23"/>
+      <c r="A248" s="26"/>
+      <c r="B248" s="26"/>
+      <c r="C248" s="26"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="A249" s="23"/>
-      <c r="B249" s="23"/>
-      <c r="C249" s="23"/>
+      <c r="A249" s="26"/>
+      <c r="B249" s="26"/>
+      <c r="C249" s="26"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="A250" s="23"/>
-      <c r="B250" s="23"/>
-      <c r="C250" s="23"/>
+      <c r="A250" s="26"/>
+      <c r="B250" s="26"/>
+      <c r="C250" s="26"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="A251" s="23"/>
-      <c r="B251" s="23"/>
-      <c r="C251" s="23"/>
+      <c r="A251" s="26"/>
+      <c r="B251" s="26"/>
+      <c r="C251" s="26"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="A252" s="23"/>
-      <c r="B252" s="23"/>
-      <c r="C252" s="23"/>
+      <c r="A252" s="26"/>
+      <c r="B252" s="26"/>
+      <c r="C252" s="26"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="A253" s="23"/>
-      <c r="B253" s="23"/>
-      <c r="C253" s="23"/>
+      <c r="A253" s="26"/>
+      <c r="B253" s="26"/>
+      <c r="C253" s="26"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="A254" s="23"/>
-      <c r="B254" s="23"/>
-      <c r="C254" s="23"/>
+      <c r="A254" s="26"/>
+      <c r="B254" s="26"/>
+      <c r="C254" s="26"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="A255" s="23"/>
-      <c r="B255" s="23"/>
-      <c r="C255" s="23"/>
+      <c r="A255" s="26"/>
+      <c r="B255" s="26"/>
+      <c r="C255" s="26"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="A256" s="23"/>
-      <c r="B256" s="23"/>
-      <c r="C256" s="23"/>
+      <c r="A256" s="26"/>
+      <c r="B256" s="26"/>
+      <c r="C256" s="26"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="A257" s="23"/>
-      <c r="B257" s="23"/>
-      <c r="C257" s="23"/>
+      <c r="A257" s="26"/>
+      <c r="B257" s="26"/>
+      <c r="C257" s="26"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="A258" s="23"/>
-      <c r="B258" s="23"/>
-      <c r="C258" s="23"/>
+      <c r="A258" s="26"/>
+      <c r="B258" s="26"/>
+      <c r="C258" s="26"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="A259" s="23"/>
-      <c r="B259" s="23"/>
-      <c r="C259" s="23"/>
+      <c r="A259" s="26"/>
+      <c r="B259" s="26"/>
+      <c r="C259" s="26"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="A260" s="23"/>
-      <c r="B260" s="23"/>
-      <c r="C260" s="23"/>
+      <c r="A260" s="26"/>
+      <c r="B260" s="26"/>
+      <c r="C260" s="26"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="A261" s="23"/>
-      <c r="B261" s="23"/>
-      <c r="C261" s="23"/>
+      <c r="A261" s="26"/>
+      <c r="B261" s="26"/>
+      <c r="C261" s="26"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="A262" s="23"/>
-      <c r="B262" s="23"/>
-      <c r="C262" s="23"/>
+      <c r="A262" s="26"/>
+      <c r="B262" s="26"/>
+      <c r="C262" s="26"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="A263" s="23"/>
-      <c r="B263" s="23"/>
-      <c r="C263" s="23"/>
+      <c r="A263" s="26"/>
+      <c r="B263" s="26"/>
+      <c r="C263" s="26"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="A264" s="23"/>
-      <c r="B264" s="23"/>
-      <c r="C264" s="23"/>
+      <c r="A264" s="26"/>
+      <c r="B264" s="26"/>
+      <c r="C264" s="26"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="A265" s="23"/>
-      <c r="B265" s="23"/>
-      <c r="C265" s="23"/>
+      <c r="A265" s="26"/>
+      <c r="B265" s="26"/>
+      <c r="C265" s="26"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="A266" s="23"/>
-      <c r="B266" s="23"/>
-      <c r="C266" s="23"/>
+      <c r="A266" s="26"/>
+      <c r="B266" s="26"/>
+      <c r="C266" s="26"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="A267" s="23"/>
-      <c r="B267" s="23"/>
-      <c r="C267" s="23"/>
+      <c r="A267" s="26"/>
+      <c r="B267" s="26"/>
+      <c r="C267" s="26"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="23"/>
-      <c r="B268" s="23"/>
-      <c r="C268" s="23"/>
+      <c r="A268" s="26"/>
+      <c r="B268" s="26"/>
+      <c r="C268" s="26"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="A269" s="23"/>
-      <c r="B269" s="23"/>
-      <c r="C269" s="23"/>
+      <c r="A269" s="26"/>
+      <c r="B269" s="26"/>
+      <c r="C269" s="26"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="A270" s="23"/>
-      <c r="B270" s="23"/>
-      <c r="C270" s="23"/>
+      <c r="A270" s="26"/>
+      <c r="B270" s="26"/>
+      <c r="C270" s="26"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="A271" s="23"/>
-      <c r="B271" s="23"/>
-      <c r="C271" s="23"/>
+      <c r="A271" s="26"/>
+      <c r="B271" s="26"/>
+      <c r="C271" s="26"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="A272" s="23"/>
-      <c r="B272" s="23"/>
-      <c r="C272" s="23"/>
+      <c r="A272" s="26"/>
+      <c r="B272" s="26"/>
+      <c r="C272" s="26"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="A273" s="23"/>
-      <c r="B273" s="23"/>
-      <c r="C273" s="23"/>
+      <c r="A273" s="26"/>
+      <c r="B273" s="26"/>
+      <c r="C273" s="26"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="A274" s="23"/>
-      <c r="B274" s="23"/>
-      <c r="C274" s="23"/>
+      <c r="A274" s="26"/>
+      <c r="B274" s="26"/>
+      <c r="C274" s="26"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="A275" s="23"/>
-      <c r="B275" s="23"/>
-      <c r="C275" s="23"/>
+      <c r="A275" s="26"/>
+      <c r="B275" s="26"/>
+      <c r="C275" s="26"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="A276" s="23"/>
-      <c r="B276" s="23"/>
-      <c r="C276" s="23"/>
+      <c r="A276" s="26"/>
+      <c r="B276" s="26"/>
+      <c r="C276" s="26"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="A277" s="23"/>
-      <c r="B277" s="23"/>
-      <c r="C277" s="23"/>
+      <c r="A277" s="26"/>
+      <c r="B277" s="26"/>
+      <c r="C277" s="26"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="A278" s="23"/>
-      <c r="B278" s="23"/>
-      <c r="C278" s="23"/>
+      <c r="A278" s="26"/>
+      <c r="B278" s="26"/>
+      <c r="C278" s="26"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="A279" s="23"/>
-      <c r="B279" s="23"/>
-      <c r="C279" s="23"/>
+      <c r="A279" s="26"/>
+      <c r="B279" s="26"/>
+      <c r="C279" s="26"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="A280" s="23"/>
-      <c r="B280" s="23"/>
-      <c r="C280" s="23"/>
+      <c r="A280" s="26"/>
+      <c r="B280" s="26"/>
+      <c r="C280" s="26"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="A281" s="23"/>
-      <c r="B281" s="23"/>
-      <c r="C281" s="23"/>
+      <c r="A281" s="26"/>
+      <c r="B281" s="26"/>
+      <c r="C281" s="26"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="A282" s="23"/>
-      <c r="B282" s="23"/>
-      <c r="C282" s="23"/>
+      <c r="A282" s="26"/>
+      <c r="B282" s="26"/>
+      <c r="C282" s="26"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="A283" s="23"/>
-      <c r="B283" s="23"/>
-      <c r="C283" s="23"/>
+      <c r="A283" s="26"/>
+      <c r="B283" s="26"/>
+      <c r="C283" s="26"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="A284" s="23"/>
-      <c r="B284" s="23"/>
-      <c r="C284" s="23"/>
+      <c r="A284" s="26"/>
+      <c r="B284" s="26"/>
+      <c r="C284" s="26"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="A285" s="23"/>
-      <c r="B285" s="23"/>
-      <c r="C285" s="23"/>
+      <c r="A285" s="26"/>
+      <c r="B285" s="26"/>
+      <c r="C285" s="26"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="A286" s="23"/>
-      <c r="B286" s="23"/>
-      <c r="C286" s="23"/>
+      <c r="A286" s="26"/>
+      <c r="B286" s="26"/>
+      <c r="C286" s="26"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="A287" s="23"/>
-      <c r="B287" s="23"/>
-      <c r="C287" s="23"/>
+      <c r="A287" s="26"/>
+      <c r="B287" s="26"/>
+      <c r="C287" s="26"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="23"/>
-      <c r="B288" s="23"/>
-      <c r="C288" s="23"/>
+      <c r="A288" s="26"/>
+      <c r="B288" s="26"/>
+      <c r="C288" s="26"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="A289" s="23"/>
-      <c r="B289" s="23"/>
-      <c r="C289" s="23"/>
+      <c r="A289" s="26"/>
+      <c r="B289" s="26"/>
+      <c r="C289" s="26"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="A290" s="23"/>
-      <c r="B290" s="23"/>
-      <c r="C290" s="23"/>
+      <c r="A290" s="26"/>
+      <c r="B290" s="26"/>
+      <c r="C290" s="26"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="A291" s="23"/>
-      <c r="B291" s="23"/>
-      <c r="C291" s="23"/>
+      <c r="A291" s="26"/>
+      <c r="B291" s="26"/>
+      <c r="C291" s="26"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="A292" s="23"/>
-      <c r="B292" s="23"/>
-      <c r="C292" s="23"/>
+      <c r="A292" s="26"/>
+      <c r="B292" s="26"/>
+      <c r="C292" s="26"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="A293" s="23"/>
-      <c r="B293" s="23"/>
-      <c r="C293" s="23"/>
+      <c r="A293" s="26"/>
+      <c r="B293" s="26"/>
+      <c r="C293" s="26"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="A294" s="23"/>
-      <c r="B294" s="23"/>
-      <c r="C294" s="23"/>
+      <c r="A294" s="26"/>
+      <c r="B294" s="26"/>
+      <c r="C294" s="26"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="A295" s="23"/>
-      <c r="B295" s="23"/>
-      <c r="C295" s="23"/>
+      <c r="A295" s="26"/>
+      <c r="B295" s="26"/>
+      <c r="C295" s="26"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="A296" s="23"/>
-      <c r="B296" s="23"/>
-      <c r="C296" s="23"/>
+      <c r="A296" s="26"/>
+      <c r="B296" s="26"/>
+      <c r="C296" s="26"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="A297" s="23"/>
-      <c r="B297" s="23"/>
-      <c r="C297" s="23"/>
+      <c r="A297" s="26"/>
+      <c r="B297" s="26"/>
+      <c r="C297" s="26"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="A298" s="23"/>
-      <c r="B298" s="23"/>
-      <c r="C298" s="23"/>
+      <c r="A298" s="26"/>
+      <c r="B298" s="26"/>
+      <c r="C298" s="26"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="A299" s="23"/>
-      <c r="B299" s="23"/>
-      <c r="C299" s="23"/>
+      <c r="A299" s="26"/>
+      <c r="B299" s="26"/>
+      <c r="C299" s="26"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="A300" s="23"/>
-      <c r="B300" s="23"/>
-      <c r="C300" s="23"/>
+      <c r="A300" s="26"/>
+      <c r="B300" s="26"/>
+      <c r="C300" s="26"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="A301" s="23"/>
-      <c r="B301" s="23"/>
-      <c r="C301" s="23"/>
+      <c r="A301" s="26"/>
+      <c r="B301" s="26"/>
+      <c r="C301" s="26"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="A302" s="23"/>
-      <c r="B302" s="23"/>
-      <c r="C302" s="23"/>
+      <c r="A302" s="26"/>
+      <c r="B302" s="26"/>
+      <c r="C302" s="26"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="A303" s="23"/>
-      <c r="B303" s="23"/>
-      <c r="C303" s="23"/>
+      <c r="A303" s="26"/>
+      <c r="B303" s="26"/>
+      <c r="C303" s="26"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="A304" s="23"/>
-      <c r="B304" s="23"/>
-      <c r="C304" s="23"/>
+      <c r="A304" s="26"/>
+      <c r="B304" s="26"/>
+      <c r="C304" s="26"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="A305" s="23"/>
-      <c r="B305" s="23"/>
-      <c r="C305" s="23"/>
+      <c r="A305" s="26"/>
+      <c r="B305" s="26"/>
+      <c r="C305" s="26"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="A306" s="23"/>
-      <c r="B306" s="23"/>
-      <c r="C306" s="23"/>
+      <c r="A306" s="26"/>
+      <c r="B306" s="26"/>
+      <c r="C306" s="26"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="A307" s="23"/>
-      <c r="B307" s="23"/>
-      <c r="C307" s="23"/>
+      <c r="A307" s="26"/>
+      <c r="B307" s="26"/>
+      <c r="C307" s="26"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="23"/>
-      <c r="B308" s="23"/>
-      <c r="C308" s="23"/>
+      <c r="A308" s="26"/>
+      <c r="B308" s="26"/>
+      <c r="C308" s="26"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="A309" s="23"/>
-      <c r="B309" s="23"/>
-      <c r="C309" s="23"/>
+      <c r="A309" s="26"/>
+      <c r="B309" s="26"/>
+      <c r="C309" s="26"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="A310" s="23"/>
-      <c r="B310" s="23"/>
-      <c r="C310" s="23"/>
+      <c r="A310" s="26"/>
+      <c r="B310" s="26"/>
+      <c r="C310" s="26"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="A311" s="23"/>
-      <c r="B311" s="23"/>
-      <c r="C311" s="23"/>
+      <c r="A311" s="26"/>
+      <c r="B311" s="26"/>
+      <c r="C311" s="26"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="A312" s="23"/>
-      <c r="B312" s="23"/>
-      <c r="C312" s="23"/>
+      <c r="A312" s="26"/>
+      <c r="B312" s="26"/>
+      <c r="C312" s="26"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="A313" s="23"/>
-      <c r="B313" s="23"/>
-      <c r="C313" s="23"/>
+      <c r="A313" s="26"/>
+      <c r="B313" s="26"/>
+      <c r="C313" s="26"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="A314" s="23"/>
-      <c r="B314" s="23"/>
-      <c r="C314" s="23"/>
+      <c r="A314" s="26"/>
+      <c r="B314" s="26"/>
+      <c r="C314" s="26"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="A315" s="23"/>
-      <c r="B315" s="23"/>
-      <c r="C315" s="23"/>
+      <c r="A315" s="26"/>
+      <c r="B315" s="26"/>
+      <c r="C315" s="26"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="A316" s="23"/>
-      <c r="B316" s="23"/>
-      <c r="C316" s="23"/>
+      <c r="A316" s="26"/>
+      <c r="B316" s="26"/>
+      <c r="C316" s="26"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="A317" s="23"/>
-      <c r="B317" s="23"/>
-      <c r="C317" s="23"/>
+      <c r="A317" s="26"/>
+      <c r="B317" s="26"/>
+      <c r="C317" s="26"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="A318" s="23"/>
-      <c r="B318" s="23"/>
-      <c r="C318" s="23"/>
+      <c r="A318" s="26"/>
+      <c r="B318" s="26"/>
+      <c r="C318" s="26"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="A319" s="23"/>
-      <c r="B319" s="23"/>
-      <c r="C319" s="23"/>
+      <c r="A319" s="26"/>
+      <c r="B319" s="26"/>
+      <c r="C319" s="26"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="A320" s="23"/>
-      <c r="B320" s="23"/>
-      <c r="C320" s="23"/>
+      <c r="A320" s="26"/>
+      <c r="B320" s="26"/>
+      <c r="C320" s="26"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="A321" s="23"/>
-      <c r="B321" s="23"/>
-      <c r="C321" s="23"/>
+      <c r="A321" s="26"/>
+      <c r="B321" s="26"/>
+      <c r="C321" s="26"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="A322" s="23"/>
-      <c r="B322" s="23"/>
-      <c r="C322" s="23"/>
+      <c r="A322" s="26"/>
+      <c r="B322" s="26"/>
+      <c r="C322" s="26"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="A323" s="23"/>
-      <c r="B323" s="23"/>
-      <c r="C323" s="23"/>
+      <c r="A323" s="26"/>
+      <c r="B323" s="26"/>
+      <c r="C323" s="26"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="A324" s="23"/>
-      <c r="B324" s="23"/>
-      <c r="C324" s="23"/>
+      <c r="A324" s="26"/>
+      <c r="B324" s="26"/>
+      <c r="C324" s="26"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="A325" s="23"/>
-      <c r="B325" s="23"/>
-      <c r="C325" s="23"/>
+      <c r="A325" s="26"/>
+      <c r="B325" s="26"/>
+      <c r="C325" s="26"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="A326" s="23"/>
-      <c r="B326" s="23"/>
-      <c r="C326" s="23"/>
+      <c r="A326" s="26"/>
+      <c r="B326" s="26"/>
+      <c r="C326" s="26"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="A327" s="23"/>
-      <c r="B327" s="23"/>
-      <c r="C327" s="23"/>
+      <c r="A327" s="26"/>
+      <c r="B327" s="26"/>
+      <c r="C327" s="26"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="23"/>
-      <c r="B328" s="23"/>
-      <c r="C328" s="23"/>
+      <c r="A328" s="26"/>
+      <c r="B328" s="26"/>
+      <c r="C328" s="26"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="A329" s="23"/>
-      <c r="B329" s="23"/>
-      <c r="C329" s="23"/>
+      <c r="A329" s="26"/>
+      <c r="B329" s="26"/>
+      <c r="C329" s="26"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="A330" s="23"/>
-      <c r="B330" s="23"/>
-      <c r="C330" s="23"/>
+      <c r="A330" s="26"/>
+      <c r="B330" s="26"/>
+      <c r="C330" s="26"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="A331" s="23"/>
-      <c r="B331" s="23"/>
-      <c r="C331" s="23"/>
+      <c r="A331" s="26"/>
+      <c r="B331" s="26"/>
+      <c r="C331" s="26"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="A332" s="23"/>
-      <c r="B332" s="23"/>
-      <c r="C332" s="23"/>
+      <c r="A332" s="26"/>
+      <c r="B332" s="26"/>
+      <c r="C332" s="26"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="A333" s="23"/>
-      <c r="B333" s="23"/>
-      <c r="C333" s="23"/>
+      <c r="A333" s="26"/>
+      <c r="B333" s="26"/>
+      <c r="C333" s="26"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="A334" s="23"/>
-      <c r="B334" s="23"/>
-      <c r="C334" s="23"/>
+      <c r="A334" s="26"/>
+      <c r="B334" s="26"/>
+      <c r="C334" s="26"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="A335" s="23"/>
-      <c r="B335" s="23"/>
-      <c r="C335" s="23"/>
+      <c r="A335" s="26"/>
+      <c r="B335" s="26"/>
+      <c r="C335" s="26"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="A336" s="23"/>
-      <c r="B336" s="23"/>
-      <c r="C336" s="23"/>
+      <c r="A336" s="26"/>
+      <c r="B336" s="26"/>
+      <c r="C336" s="26"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="A337" s="23"/>
-      <c r="B337" s="23"/>
-      <c r="C337" s="23"/>
+      <c r="A337" s="26"/>
+      <c r="B337" s="26"/>
+      <c r="C337" s="26"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="A338" s="23"/>
-      <c r="B338" s="23"/>
-      <c r="C338" s="23"/>
+      <c r="A338" s="26"/>
+      <c r="B338" s="26"/>
+      <c r="C338" s="26"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="A339" s="23"/>
-      <c r="B339" s="23"/>
-      <c r="C339" s="23"/>
+      <c r="A339" s="26"/>
+      <c r="B339" s="26"/>
+      <c r="C339" s="26"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="A340" s="23"/>
-      <c r="B340" s="23"/>
-      <c r="C340" s="23"/>
+      <c r="A340" s="26"/>
+      <c r="B340" s="26"/>
+      <c r="C340" s="26"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="A341" s="23"/>
-      <c r="B341" s="23"/>
-      <c r="C341" s="23"/>
+      <c r="A341" s="26"/>
+      <c r="B341" s="26"/>
+      <c r="C341" s="26"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="A342" s="23"/>
-      <c r="B342" s="23"/>
-      <c r="C342" s="23"/>
+      <c r="A342" s="26"/>
+      <c r="B342" s="26"/>
+      <c r="C342" s="26"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="A343" s="23"/>
-      <c r="B343" s="23"/>
-      <c r="C343" s="23"/>
+      <c r="A343" s="26"/>
+      <c r="B343" s="26"/>
+      <c r="C343" s="26"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="A344" s="23"/>
-      <c r="B344" s="23"/>
-      <c r="C344" s="23"/>
+      <c r="A344" s="26"/>
+      <c r="B344" s="26"/>
+      <c r="C344" s="26"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="A345" s="23"/>
-      <c r="B345" s="23"/>
-      <c r="C345" s="23"/>
+      <c r="A345" s="26"/>
+      <c r="B345" s="26"/>
+      <c r="C345" s="26"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="A346" s="23"/>
-      <c r="B346" s="23"/>
-      <c r="C346" s="23"/>
+      <c r="A346" s="26"/>
+      <c r="B346" s="26"/>
+      <c r="C346" s="26"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="A347" s="23"/>
-      <c r="B347" s="23"/>
-      <c r="C347" s="23"/>
+      <c r="A347" s="26"/>
+      <c r="B347" s="26"/>
+      <c r="C347" s="26"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="23"/>
-      <c r="B348" s="23"/>
-      <c r="C348" s="23"/>
+      <c r="A348" s="26"/>
+      <c r="B348" s="26"/>
+      <c r="C348" s="26"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="A349" s="23"/>
-      <c r="B349" s="23"/>
-      <c r="C349" s="23"/>
+      <c r="A349" s="26"/>
+      <c r="B349" s="26"/>
+      <c r="C349" s="26"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="A350" s="23"/>
-      <c r="B350" s="23"/>
-      <c r="C350" s="23"/>
+      <c r="A350" s="26"/>
+      <c r="B350" s="26"/>
+      <c r="C350" s="26"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="A351" s="23"/>
-      <c r="B351" s="23"/>
-      <c r="C351" s="23"/>
+      <c r="A351" s="26"/>
+      <c r="B351" s="26"/>
+      <c r="C351" s="26"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="A352" s="23"/>
-      <c r="B352" s="23"/>
-      <c r="C352" s="23"/>
+      <c r="A352" s="26"/>
+      <c r="B352" s="26"/>
+      <c r="C352" s="26"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="A353" s="23"/>
-      <c r="B353" s="23"/>
-      <c r="C353" s="23"/>
+      <c r="A353" s="26"/>
+      <c r="B353" s="26"/>
+      <c r="C353" s="26"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="A354" s="23"/>
-      <c r="B354" s="23"/>
-      <c r="C354" s="23"/>
+      <c r="A354" s="26"/>
+      <c r="B354" s="26"/>
+      <c r="C354" s="26"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="A355" s="23"/>
-      <c r="B355" s="23"/>
-      <c r="C355" s="23"/>
+      <c r="A355" s="26"/>
+      <c r="B355" s="26"/>
+      <c r="C355" s="26"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="A356" s="23"/>
-      <c r="B356" s="23"/>
-      <c r="C356" s="23"/>
+      <c r="A356" s="26"/>
+      <c r="B356" s="26"/>
+      <c r="C356" s="26"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="A357" s="23"/>
-      <c r="B357" s="23"/>
-      <c r="C357" s="23"/>
+      <c r="A357" s="26"/>
+      <c r="B357" s="26"/>
+      <c r="C357" s="26"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="A358" s="23"/>
-      <c r="B358" s="23"/>
-      <c r="C358" s="23"/>
+      <c r="A358" s="26"/>
+      <c r="B358" s="26"/>
+      <c r="C358" s="26"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="A359" s="23"/>
-      <c r="B359" s="23"/>
-      <c r="C359" s="23"/>
+      <c r="A359" s="26"/>
+      <c r="B359" s="26"/>
+      <c r="C359" s="26"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="A360" s="23"/>
-      <c r="B360" s="23"/>
-      <c r="C360" s="23"/>
+      <c r="A360" s="26"/>
+      <c r="B360" s="26"/>
+      <c r="C360" s="26"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="A361" s="23"/>
-      <c r="B361" s="23"/>
-      <c r="C361" s="23"/>
+      <c r="A361" s="26"/>
+      <c r="B361" s="26"/>
+      <c r="C361" s="26"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="A362" s="23"/>
-      <c r="B362" s="23"/>
-      <c r="C362" s="23"/>
+      <c r="A362" s="26"/>
+      <c r="B362" s="26"/>
+      <c r="C362" s="26"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="A363" s="23"/>
-      <c r="B363" s="23"/>
-      <c r="C363" s="23"/>
+      <c r="A363" s="26"/>
+      <c r="B363" s="26"/>
+      <c r="C363" s="26"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="A364" s="23"/>
-      <c r="B364" s="23"/>
-      <c r="C364" s="23"/>
+      <c r="A364" s="26"/>
+      <c r="B364" s="26"/>
+      <c r="C364" s="26"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="A365" s="23"/>
-      <c r="B365" s="23"/>
-      <c r="C365" s="23"/>
+      <c r="A365" s="26"/>
+      <c r="B365" s="26"/>
+      <c r="C365" s="26"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="A366" s="23"/>
-      <c r="B366" s="23"/>
-      <c r="C366" s="23"/>
+      <c r="A366" s="26"/>
+      <c r="B366" s="26"/>
+      <c r="C366" s="26"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="A367" s="23"/>
-      <c r="B367" s="23"/>
-      <c r="C367" s="23"/>
+      <c r="A367" s="26"/>
+      <c r="B367" s="26"/>
+      <c r="C367" s="26"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="23"/>
-      <c r="B368" s="23"/>
-      <c r="C368" s="23"/>
+      <c r="A368" s="26"/>
+      <c r="B368" s="26"/>
+      <c r="C368" s="26"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="A369" s="23"/>
-      <c r="B369" s="23"/>
-      <c r="C369" s="23"/>
+      <c r="A369" s="26"/>
+      <c r="B369" s="26"/>
+      <c r="C369" s="26"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="A370" s="23"/>
-      <c r="B370" s="23"/>
-      <c r="C370" s="23"/>
+      <c r="A370" s="26"/>
+      <c r="B370" s="26"/>
+      <c r="C370" s="26"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="A371" s="23"/>
-      <c r="B371" s="23"/>
-      <c r="C371" s="23"/>
+      <c r="A371" s="26"/>
+      <c r="B371" s="26"/>
+      <c r="C371" s="26"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="A372" s="23"/>
-      <c r="B372" s="23"/>
-      <c r="C372" s="23"/>
+      <c r="A372" s="26"/>
+      <c r="B372" s="26"/>
+      <c r="C372" s="26"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="A373" s="23"/>
-      <c r="B373" s="23"/>
-      <c r="C373" s="23"/>
+      <c r="A373" s="26"/>
+      <c r="B373" s="26"/>
+      <c r="C373" s="26"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="A374" s="23"/>
-      <c r="B374" s="23"/>
-      <c r="C374" s="23"/>
+      <c r="A374" s="26"/>
+      <c r="B374" s="26"/>
+      <c r="C374" s="26"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="A375" s="23"/>
-      <c r="B375" s="23"/>
-      <c r="C375" s="23"/>
+      <c r="A375" s="26"/>
+      <c r="B375" s="26"/>
+      <c r="C375" s="26"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="A376" s="23"/>
-      <c r="B376" s="23"/>
-      <c r="C376" s="23"/>
+      <c r="A376" s="26"/>
+      <c r="B376" s="26"/>
+      <c r="C376" s="26"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="A377" s="23"/>
-      <c r="B377" s="23"/>
-      <c r="C377" s="23"/>
+      <c r="A377" s="26"/>
+      <c r="B377" s="26"/>
+      <c r="C377" s="26"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="A378" s="23"/>
-      <c r="B378" s="23"/>
-      <c r="C378" s="23"/>
+      <c r="A378" s="26"/>
+      <c r="B378" s="26"/>
+      <c r="C378" s="26"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="A379" s="23"/>
-      <c r="B379" s="23"/>
-      <c r="C379" s="23"/>
+      <c r="A379" s="26"/>
+      <c r="B379" s="26"/>
+      <c r="C379" s="26"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="A380" s="23"/>
-      <c r="B380" s="23"/>
-      <c r="C380" s="23"/>
+      <c r="A380" s="26"/>
+      <c r="B380" s="26"/>
+      <c r="C380" s="26"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="A381" s="23"/>
-      <c r="B381" s="23"/>
-      <c r="C381" s="23"/>
+      <c r="A381" s="26"/>
+      <c r="B381" s="26"/>
+      <c r="C381" s="26"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="A382" s="23"/>
-      <c r="B382" s="23"/>
-      <c r="C382" s="23"/>
+      <c r="A382" s="26"/>
+      <c r="B382" s="26"/>
+      <c r="C382" s="26"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="A383" s="23"/>
-      <c r="B383" s="23"/>
-      <c r="C383" s="23"/>
+      <c r="A383" s="26"/>
+      <c r="B383" s="26"/>
+      <c r="C383" s="26"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="A384" s="23"/>
-      <c r="B384" s="23"/>
-      <c r="C384" s="23"/>
+      <c r="A384" s="26"/>
+      <c r="B384" s="26"/>
+      <c r="C384" s="26"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="A385" s="23"/>
-      <c r="B385" s="23"/>
-      <c r="C385" s="23"/>
+      <c r="A385" s="26"/>
+      <c r="B385" s="26"/>
+      <c r="C385" s="26"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="A386" s="23"/>
-      <c r="B386" s="23"/>
-      <c r="C386" s="23"/>
+      <c r="A386" s="26"/>
+      <c r="B386" s="26"/>
+      <c r="C386" s="26"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="A387" s="23"/>
-      <c r="B387" s="23"/>
-      <c r="C387" s="23"/>
+      <c r="A387" s="26"/>
+      <c r="B387" s="26"/>
+      <c r="C387" s="26"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="A388" s="23"/>
-      <c r="B388" s="23"/>
-      <c r="C388" s="23"/>
+      <c r="A388" s="26"/>
+      <c r="B388" s="26"/>
+      <c r="C388" s="26"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="A389" s="23"/>
-      <c r="B389" s="23"/>
-      <c r="C389" s="23"/>
+      <c r="A389" s="26"/>
+      <c r="B389" s="26"/>
+      <c r="C389" s="26"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="A390" s="23"/>
-      <c r="B390" s="23"/>
-      <c r="C390" s="23"/>
+      <c r="A390" s="26"/>
+      <c r="B390" s="26"/>
+      <c r="C390" s="26"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="A391" s="23"/>
-      <c r="B391" s="23"/>
-      <c r="C391" s="23"/>
+      <c r="A391" s="26"/>
+      <c r="B391" s="26"/>
+      <c r="C391" s="26"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="A392" s="23"/>
-      <c r="B392" s="23"/>
-      <c r="C392" s="23"/>
+      <c r="A392" s="26"/>
+      <c r="B392" s="26"/>
+      <c r="C392" s="26"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="A393" s="23"/>
-      <c r="B393" s="23"/>
-      <c r="C393" s="23"/>
+      <c r="A393" s="26"/>
+      <c r="B393" s="26"/>
+      <c r="C393" s="26"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="A394" s="23"/>
-      <c r="B394" s="23"/>
-      <c r="C394" s="23"/>
+      <c r="A394" s="26"/>
+      <c r="B394" s="26"/>
+      <c r="C394" s="26"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="A395" s="23"/>
-      <c r="B395" s="23"/>
-      <c r="C395" s="23"/>
+      <c r="A395" s="26"/>
+      <c r="B395" s="26"/>
+      <c r="C395" s="26"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="A396" s="23"/>
-      <c r="B396" s="23"/>
-      <c r="C396" s="23"/>
+      <c r="A396" s="26"/>
+      <c r="B396" s="26"/>
+      <c r="C396" s="26"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="A397" s="23"/>
-      <c r="B397" s="23"/>
-      <c r="C397" s="23"/>
+      <c r="A397" s="26"/>
+      <c r="B397" s="26"/>
+      <c r="C397" s="26"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="A398" s="23"/>
-      <c r="B398" s="23"/>
-      <c r="C398" s="23"/>
+      <c r="A398" s="26"/>
+      <c r="B398" s="26"/>
+      <c r="C398" s="26"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="A399" s="23"/>
-      <c r="B399" s="23"/>
-      <c r="C399" s="23"/>
+      <c r="A399" s="26"/>
+      <c r="B399" s="26"/>
+      <c r="C399" s="26"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="A400" s="23"/>
-      <c r="B400" s="23"/>
-      <c r="C400" s="23"/>
+      <c r="A400" s="26"/>
+      <c r="B400" s="26"/>
+      <c r="C400" s="26"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="A401" s="23"/>
-      <c r="B401" s="23"/>
-      <c r="C401" s="23"/>
+      <c r="A401" s="26"/>
+      <c r="B401" s="26"/>
+      <c r="C401" s="26"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="A402" s="23"/>
-      <c r="B402" s="23"/>
-      <c r="C402" s="23"/>
+      <c r="A402" s="26"/>
+      <c r="B402" s="26"/>
+      <c r="C402" s="26"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="A403" s="23"/>
-      <c r="B403" s="23"/>
-      <c r="C403" s="23"/>
+      <c r="A403" s="26"/>
+      <c r="B403" s="26"/>
+      <c r="C403" s="26"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="A404" s="23"/>
-      <c r="B404" s="23"/>
-      <c r="C404" s="23"/>
+      <c r="A404" s="26"/>
+      <c r="B404" s="26"/>
+      <c r="C404" s="26"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="A405" s="23"/>
-      <c r="B405" s="23"/>
-      <c r="C405" s="23"/>
+      <c r="A405" s="26"/>
+      <c r="B405" s="26"/>
+      <c r="C405" s="26"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="A406" s="23"/>
-      <c r="B406" s="23"/>
-      <c r="C406" s="23"/>
+      <c r="A406" s="26"/>
+      <c r="B406" s="26"/>
+      <c r="C406" s="26"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="A407" s="23"/>
-      <c r="B407" s="23"/>
-      <c r="C407" s="23"/>
+      <c r="A407" s="26"/>
+      <c r="B407" s="26"/>
+      <c r="C407" s="26"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="A408" s="23"/>
-      <c r="B408" s="23"/>
-      <c r="C408" s="23"/>
+      <c r="A408" s="26"/>
+      <c r="B408" s="26"/>
+      <c r="C408" s="26"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="A409" s="23"/>
-      <c r="B409" s="23"/>
-      <c r="C409" s="23"/>
+      <c r="A409" s="26"/>
+      <c r="B409" s="26"/>
+      <c r="C409" s="26"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="A410" s="23"/>
-      <c r="B410" s="23"/>
-      <c r="C410" s="23"/>
+      <c r="A410" s="26"/>
+      <c r="B410" s="26"/>
+      <c r="C410" s="26"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="A411" s="23"/>
-      <c r="B411" s="23"/>
-      <c r="C411" s="23"/>
+      <c r="A411" s="26"/>
+      <c r="B411" s="26"/>
+      <c r="C411" s="26"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="A412" s="23"/>
-      <c r="B412" s="23"/>
-      <c r="C412" s="23"/>
+      <c r="A412" s="26"/>
+      <c r="B412" s="26"/>
+      <c r="C412" s="26"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="A413" s="23"/>
-      <c r="B413" s="23"/>
-      <c r="C413" s="23"/>
+      <c r="A413" s="26"/>
+      <c r="B413" s="26"/>
+      <c r="C413" s="26"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="A414" s="23"/>
-      <c r="B414" s="23"/>
-      <c r="C414" s="23"/>
+      <c r="A414" s="26"/>
+      <c r="B414" s="26"/>
+      <c r="C414" s="26"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="A415" s="23"/>
-      <c r="B415" s="23"/>
-      <c r="C415" s="23"/>
+      <c r="A415" s="26"/>
+      <c r="B415" s="26"/>
+      <c r="C415" s="26"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="A416" s="23"/>
-      <c r="B416" s="23"/>
-      <c r="C416" s="23"/>
+      <c r="A416" s="26"/>
+      <c r="B416" s="26"/>
+      <c r="C416" s="26"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="A417" s="23"/>
-      <c r="B417" s="23"/>
-      <c r="C417" s="23"/>
+      <c r="A417" s="26"/>
+      <c r="B417" s="26"/>
+      <c r="C417" s="26"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="A418" s="23"/>
-      <c r="B418" s="23"/>
-      <c r="C418" s="23"/>
+      <c r="A418" s="26"/>
+      <c r="B418" s="26"/>
+      <c r="C418" s="26"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="A419" s="23"/>
-      <c r="B419" s="23"/>
-      <c r="C419" s="23"/>
+      <c r="A419" s="26"/>
+      <c r="B419" s="26"/>
+      <c r="C419" s="26"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="A420" s="23"/>
-      <c r="B420" s="23"/>
-      <c r="C420" s="23"/>
+      <c r="A420" s="26"/>
+      <c r="B420" s="26"/>
+      <c r="C420" s="26"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="A421" s="23"/>
-      <c r="B421" s="23"/>
-      <c r="C421" s="23"/>
+      <c r="A421" s="26"/>
+      <c r="B421" s="26"/>
+      <c r="C421" s="26"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="A422" s="23"/>
-      <c r="B422" s="23"/>
-      <c r="C422" s="23"/>
+      <c r="A422" s="26"/>
+      <c r="B422" s="26"/>
+      <c r="C422" s="26"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="A423" s="23"/>
-      <c r="B423" s="23"/>
-      <c r="C423" s="23"/>
+      <c r="A423" s="26"/>
+      <c r="B423" s="26"/>
+      <c r="C423" s="26"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="A424" s="23"/>
-      <c r="B424" s="23"/>
-      <c r="C424" s="23"/>
+      <c r="A424" s="26"/>
+      <c r="B424" s="26"/>
+      <c r="C424" s="26"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="A425" s="23"/>
-      <c r="B425" s="23"/>
-      <c r="C425" s="23"/>
+      <c r="A425" s="26"/>
+      <c r="B425" s="26"/>
+      <c r="C425" s="26"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="A426" s="23"/>
-      <c r="B426" s="23"/>
-      <c r="C426" s="23"/>
+      <c r="A426" s="26"/>
+      <c r="B426" s="26"/>
+      <c r="C426" s="26"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="A427" s="23"/>
-      <c r="B427" s="23"/>
-      <c r="C427" s="23"/>
+      <c r="A427" s="26"/>
+      <c r="B427" s="26"/>
+      <c r="C427" s="26"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="A428" s="23"/>
-      <c r="B428" s="23"/>
-      <c r="C428" s="23"/>
+      <c r="A428" s="26"/>
+      <c r="B428" s="26"/>
+      <c r="C428" s="26"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="A429" s="23"/>
-      <c r="B429" s="23"/>
-      <c r="C429" s="23"/>
+      <c r="A429" s="26"/>
+      <c r="B429" s="26"/>
+      <c r="C429" s="26"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="A430" s="23"/>
-      <c r="B430" s="23"/>
-      <c r="C430" s="23"/>
+      <c r="A430" s="26"/>
+      <c r="B430" s="26"/>
+      <c r="C430" s="26"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="A431" s="23"/>
-      <c r="B431" s="23"/>
-      <c r="C431" s="23"/>
+      <c r="A431" s="26"/>
+      <c r="B431" s="26"/>
+      <c r="C431" s="26"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="A432" s="23"/>
-      <c r="B432" s="23"/>
-      <c r="C432" s="23"/>
+      <c r="A432" s="26"/>
+      <c r="B432" s="26"/>
+      <c r="C432" s="26"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="A433" s="23"/>
-      <c r="B433" s="23"/>
-      <c r="C433" s="23"/>
+      <c r="A433" s="26"/>
+      <c r="B433" s="26"/>
+      <c r="C433" s="26"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="A434" s="23"/>
-      <c r="B434" s="23"/>
-      <c r="C434" s="23"/>
+      <c r="A434" s="26"/>
+      <c r="B434" s="26"/>
+      <c r="C434" s="26"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="23"/>
-      <c r="B435" s="23"/>
-      <c r="C435" s="23"/>
+      <c r="A435" s="26"/>
+      <c r="B435" s="26"/>
+      <c r="C435" s="26"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="23"/>
-      <c r="B436" s="23"/>
-      <c r="C436" s="23"/>
+      <c r="A436" s="26"/>
+      <c r="B436" s="26"/>
+      <c r="C436" s="26"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="23"/>
-      <c r="B437" s="23"/>
-      <c r="C437" s="23"/>
+      <c r="A437" s="26"/>
+      <c r="B437" s="26"/>
+      <c r="C437" s="26"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="23"/>
-      <c r="B438" s="23"/>
-      <c r="C438" s="23"/>
+      <c r="A438" s="26"/>
+      <c r="B438" s="26"/>
+      <c r="C438" s="26"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="23"/>
-      <c r="B439" s="23"/>
-      <c r="C439" s="23"/>
+      <c r="A439" s="26"/>
+      <c r="B439" s="26"/>
+      <c r="C439" s="26"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="23"/>
-      <c r="B440" s="23"/>
-      <c r="C440" s="23"/>
+      <c r="A440" s="26"/>
+      <c r="B440" s="26"/>
+      <c r="C440" s="26"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="A441" s="23"/>
-      <c r="B441" s="23"/>
-      <c r="C441" s="23"/>
+      <c r="A441" s="26"/>
+      <c r="B441" s="26"/>
+      <c r="C441" s="26"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="A442" s="23"/>
-      <c r="B442" s="23"/>
-      <c r="C442" s="23"/>
+      <c r="A442" s="26"/>
+      <c r="B442" s="26"/>
+      <c r="C442" s="26"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="23"/>
-      <c r="B443" s="23"/>
-      <c r="C443" s="23"/>
+      <c r="A443" s="26"/>
+      <c r="B443" s="26"/>
+      <c r="C443" s="26"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="23"/>
-      <c r="B444" s="23"/>
-      <c r="C444" s="23"/>
+      <c r="A444" s="26"/>
+      <c r="B444" s="26"/>
+      <c r="C444" s="26"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="23"/>
-      <c r="B445" s="23"/>
-      <c r="C445" s="23"/>
+      <c r="A445" s="26"/>
+      <c r="B445" s="26"/>
+      <c r="C445" s="26"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="23"/>
-      <c r="B446" s="23"/>
-      <c r="C446" s="23"/>
+      <c r="A446" s="26"/>
+      <c r="B446" s="26"/>
+      <c r="C446" s="26"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="A447" s="23"/>
-      <c r="B447" s="23"/>
-      <c r="C447" s="23"/>
+      <c r="A447" s="26"/>
+      <c r="B447" s="26"/>
+      <c r="C447" s="26"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="A448" s="23"/>
-      <c r="B448" s="23"/>
-      <c r="C448" s="23"/>
+      <c r="A448" s="26"/>
+      <c r="B448" s="26"/>
+      <c r="C448" s="26"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="A449" s="23"/>
-      <c r="B449" s="23"/>
-      <c r="C449" s="23"/>
+      <c r="A449" s="26"/>
+      <c r="B449" s="26"/>
+      <c r="C449" s="26"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="A450" s="23"/>
-      <c r="B450" s="23"/>
-      <c r="C450" s="23"/>
+      <c r="A450" s="26"/>
+      <c r="B450" s="26"/>
+      <c r="C450" s="26"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="A451" s="23"/>
-      <c r="B451" s="23"/>
-      <c r="C451" s="23"/>
+      <c r="A451" s="26"/>
+      <c r="B451" s="26"/>
+      <c r="C451" s="26"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="A452" s="23"/>
-      <c r="B452" s="23"/>
-      <c r="C452" s="23"/>
+      <c r="A452" s="26"/>
+      <c r="B452" s="26"/>
+      <c r="C452" s="26"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="23"/>
-      <c r="B453" s="23"/>
-      <c r="C453" s="23"/>
+      <c r="A453" s="26"/>
+      <c r="B453" s="26"/>
+      <c r="C453" s="26"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="23"/>
-      <c r="B454" s="23"/>
-      <c r="C454" s="23"/>
+      <c r="A454" s="26"/>
+      <c r="B454" s="26"/>
+      <c r="C454" s="26"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="23"/>
-      <c r="B455" s="23"/>
-      <c r="C455" s="23"/>
+      <c r="A455" s="26"/>
+      <c r="B455" s="26"/>
+      <c r="C455" s="26"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="23"/>
-      <c r="B456" s="23"/>
-      <c r="C456" s="23"/>
+      <c r="A456" s="26"/>
+      <c r="B456" s="26"/>
+      <c r="C456" s="26"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="A457" s="23"/>
-      <c r="B457" s="23"/>
-      <c r="C457" s="23"/>
+      <c r="A457" s="26"/>
+      <c r="B457" s="26"/>
+      <c r="C457" s="26"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="A458" s="23"/>
-      <c r="B458" s="23"/>
-      <c r="C458" s="23"/>
+      <c r="A458" s="26"/>
+      <c r="B458" s="26"/>
+      <c r="C458" s="26"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="A459" s="23"/>
-      <c r="B459" s="23"/>
-      <c r="C459" s="23"/>
+      <c r="A459" s="26"/>
+      <c r="B459" s="26"/>
+      <c r="C459" s="26"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="A460" s="23"/>
-      <c r="B460" s="23"/>
-      <c r="C460" s="23"/>
+      <c r="A460" s="26"/>
+      <c r="B460" s="26"/>
+      <c r="C460" s="26"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="A461" s="23"/>
-      <c r="B461" s="23"/>
-      <c r="C461" s="23"/>
+      <c r="A461" s="26"/>
+      <c r="B461" s="26"/>
+      <c r="C461" s="26"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="A462" s="23"/>
-      <c r="B462" s="23"/>
-      <c r="C462" s="23"/>
+      <c r="A462" s="26"/>
+      <c r="B462" s="26"/>
+      <c r="C462" s="26"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="A463" s="23"/>
-      <c r="B463" s="23"/>
-      <c r="C463" s="23"/>
+      <c r="A463" s="26"/>
+      <c r="B463" s="26"/>
+      <c r="C463" s="26"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="A464" s="23"/>
-      <c r="B464" s="23"/>
-      <c r="C464" s="23"/>
+      <c r="A464" s="26"/>
+      <c r="B464" s="26"/>
+      <c r="C464" s="26"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="A465" s="23"/>
-      <c r="B465" s="23"/>
-      <c r="C465" s="23"/>
+      <c r="A465" s="26"/>
+      <c r="B465" s="26"/>
+      <c r="C465" s="26"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="A466" s="23"/>
-      <c r="B466" s="23"/>
-      <c r="C466" s="23"/>
+      <c r="A466" s="26"/>
+      <c r="B466" s="26"/>
+      <c r="C466" s="26"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="A467" s="23"/>
-      <c r="B467" s="23"/>
-      <c r="C467" s="23"/>
+      <c r="A467" s="26"/>
+      <c r="B467" s="26"/>
+      <c r="C467" s="26"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="A468" s="23"/>
-      <c r="B468" s="23"/>
-      <c r="C468" s="23"/>
+      <c r="A468" s="26"/>
+      <c r="B468" s="26"/>
+      <c r="C468" s="26"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="A469" s="23"/>
-      <c r="B469" s="23"/>
-      <c r="C469" s="23"/>
+      <c r="A469" s="26"/>
+      <c r="B469" s="26"/>
+      <c r="C469" s="26"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="A470" s="23"/>
-      <c r="B470" s="23"/>
-      <c r="C470" s="23"/>
+      <c r="A470" s="26"/>
+      <c r="B470" s="26"/>
+      <c r="C470" s="26"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="A471" s="23"/>
-      <c r="B471" s="23"/>
-      <c r="C471" s="23"/>
+      <c r="A471" s="26"/>
+      <c r="B471" s="26"/>
+      <c r="C471" s="26"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="A472" s="23"/>
-      <c r="B472" s="23"/>
-      <c r="C472" s="23"/>
+      <c r="A472" s="26"/>
+      <c r="B472" s="26"/>
+      <c r="C472" s="26"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="A473" s="23"/>
-      <c r="B473" s="23"/>
-      <c r="C473" s="23"/>
+      <c r="A473" s="26"/>
+      <c r="B473" s="26"/>
+      <c r="C473" s="26"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="A474" s="23"/>
-      <c r="B474" s="23"/>
-      <c r="C474" s="23"/>
+      <c r="A474" s="26"/>
+      <c r="B474" s="26"/>
+      <c r="C474" s="26"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="A475" s="23"/>
-      <c r="B475" s="23"/>
-      <c r="C475" s="23"/>
+      <c r="A475" s="26"/>
+      <c r="B475" s="26"/>
+      <c r="C475" s="26"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="A476" s="23"/>
-      <c r="B476" s="23"/>
-      <c r="C476" s="23"/>
+      <c r="A476" s="26"/>
+      <c r="B476" s="26"/>
+      <c r="C476" s="26"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="A477" s="23"/>
-      <c r="B477" s="23"/>
-      <c r="C477" s="23"/>
+      <c r="A477" s="26"/>
+      <c r="B477" s="26"/>
+      <c r="C477" s="26"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="A478" s="23"/>
-      <c r="B478" s="23"/>
-      <c r="C478" s="23"/>
+      <c r="A478" s="26"/>
+      <c r="B478" s="26"/>
+      <c r="C478" s="26"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="A479" s="23"/>
-      <c r="B479" s="23"/>
-      <c r="C479" s="23"/>
+      <c r="A479" s="26"/>
+      <c r="B479" s="26"/>
+      <c r="C479" s="26"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="A480" s="23"/>
-      <c r="B480" s="23"/>
-      <c r="C480" s="23"/>
+      <c r="A480" s="26"/>
+      <c r="B480" s="26"/>
+      <c r="C480" s="26"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="A481" s="23"/>
-      <c r="B481" s="23"/>
-      <c r="C481" s="23"/>
+      <c r="A481" s="26"/>
+      <c r="B481" s="26"/>
+      <c r="C481" s="26"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="A482" s="23"/>
-      <c r="B482" s="23"/>
-      <c r="C482" s="23"/>
+      <c r="A482" s="26"/>
+      <c r="B482" s="26"/>
+      <c r="C482" s="26"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="A483" s="23"/>
-      <c r="B483" s="23"/>
-      <c r="C483" s="23"/>
+      <c r="A483" s="26"/>
+      <c r="B483" s="26"/>
+      <c r="C483" s="26"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="A484" s="23"/>
-      <c r="B484" s="23"/>
-      <c r="C484" s="23"/>
+      <c r="A484" s="26"/>
+      <c r="B484" s="26"/>
+      <c r="C484" s="26"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="A485" s="23"/>
-      <c r="B485" s="23"/>
-      <c r="C485" s="23"/>
+      <c r="A485" s="26"/>
+      <c r="B485" s="26"/>
+      <c r="C485" s="26"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="A486" s="23"/>
-      <c r="B486" s="23"/>
-      <c r="C486" s="23"/>
+      <c r="A486" s="26"/>
+      <c r="B486" s="26"/>
+      <c r="C486" s="26"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="A487" s="23"/>
-      <c r="B487" s="23"/>
-      <c r="C487" s="23"/>
+      <c r="A487" s="26"/>
+      <c r="B487" s="26"/>
+      <c r="C487" s="26"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="A488" s="23"/>
-      <c r="B488" s="23"/>
-      <c r="C488" s="23"/>
+      <c r="A488" s="26"/>
+      <c r="B488" s="26"/>
+      <c r="C488" s="26"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="A489" s="23"/>
-      <c r="B489" s="23"/>
-      <c r="C489" s="23"/>
+      <c r="A489" s="26"/>
+      <c r="B489" s="26"/>
+      <c r="C489" s="26"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="A490" s="23"/>
-      <c r="B490" s="23"/>
-      <c r="C490" s="23"/>
+      <c r="A490" s="26"/>
+      <c r="B490" s="26"/>
+      <c r="C490" s="26"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="A491" s="23"/>
-      <c r="B491" s="23"/>
-      <c r="C491" s="23"/>
+      <c r="A491" s="26"/>
+      <c r="B491" s="26"/>
+      <c r="C491" s="26"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="A492" s="23"/>
-      <c r="B492" s="23"/>
-      <c r="C492" s="23"/>
+      <c r="A492" s="26"/>
+      <c r="B492" s="26"/>
+      <c r="C492" s="26"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="A493" s="23"/>
-      <c r="B493" s="23"/>
-      <c r="C493" s="23"/>
+      <c r="A493" s="26"/>
+      <c r="B493" s="26"/>
+      <c r="C493" s="26"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="A494" s="23"/>
-      <c r="B494" s="23"/>
-      <c r="C494" s="23"/>
+      <c r="A494" s="26"/>
+      <c r="B494" s="26"/>
+      <c r="C494" s="26"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="A495" s="23"/>
-      <c r="B495" s="23"/>
-      <c r="C495" s="23"/>
+      <c r="A495" s="26"/>
+      <c r="B495" s="26"/>
+      <c r="C495" s="26"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="A496" s="23"/>
-      <c r="B496" s="23"/>
-      <c r="C496" s="23"/>
+      <c r="A496" s="26"/>
+      <c r="B496" s="26"/>
+      <c r="C496" s="26"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="A497" s="23"/>
-      <c r="B497" s="23"/>
-      <c r="C497" s="23"/>
+      <c r="A497" s="26"/>
+      <c r="B497" s="26"/>
+      <c r="C497" s="26"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="A498" s="23"/>
-      <c r="B498" s="23"/>
-      <c r="C498" s="23"/>
+      <c r="A498" s="26"/>
+      <c r="B498" s="26"/>
+      <c r="C498" s="26"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="A499" s="23"/>
-      <c r="B499" s="23"/>
-      <c r="C499" s="23"/>
+      <c r="A499" s="26"/>
+      <c r="B499" s="26"/>
+      <c r="C499" s="26"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="A500" s="23"/>
-      <c r="B500" s="23"/>
-      <c r="C500" s="23"/>
+      <c r="A500" s="26"/>
+      <c r="B500" s="26"/>
+      <c r="C500" s="26"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="A501" s="23"/>
-      <c r="B501" s="23"/>
-      <c r="C501" s="23"/>
+      <c r="A501" s="26"/>
+      <c r="B501" s="26"/>
+      <c r="C501" s="26"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="A502" s="23"/>
-      <c r="B502" s="23"/>
-      <c r="C502" s="23"/>
+      <c r="A502" s="26"/>
+      <c r="B502" s="26"/>
+      <c r="C502" s="26"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="A503" s="23"/>
-      <c r="B503" s="23"/>
-      <c r="C503" s="23"/>
+      <c r="A503" s="26"/>
+      <c r="B503" s="26"/>
+      <c r="C503" s="26"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="A504" s="23"/>
-      <c r="B504" s="23"/>
-      <c r="C504" s="23"/>
+      <c r="A504" s="26"/>
+      <c r="B504" s="26"/>
+      <c r="C504" s="26"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="A505" s="23"/>
-      <c r="B505" s="23"/>
-      <c r="C505" s="23"/>
+      <c r="A505" s="26"/>
+      <c r="B505" s="26"/>
+      <c r="C505" s="26"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="A506" s="23"/>
-      <c r="B506" s="23"/>
-      <c r="C506" s="23"/>
+      <c r="A506" s="26"/>
+      <c r="B506" s="26"/>
+      <c r="C506" s="26"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="A507" s="23"/>
-      <c r="B507" s="23"/>
-      <c r="C507" s="23"/>
+      <c r="A507" s="26"/>
+      <c r="B507" s="26"/>
+      <c r="C507" s="26"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="A508" s="23"/>
-      <c r="B508" s="23"/>
-      <c r="C508" s="23"/>
+      <c r="A508" s="26"/>
+      <c r="B508" s="26"/>
+      <c r="C508" s="26"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="A509" s="23"/>
-      <c r="B509" s="23"/>
-      <c r="C509" s="23"/>
+      <c r="A509" s="26"/>
+      <c r="B509" s="26"/>
+      <c r="C509" s="26"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="A510" s="23"/>
-      <c r="B510" s="23"/>
-      <c r="C510" s="23"/>
+      <c r="A510" s="26"/>
+      <c r="B510" s="26"/>
+      <c r="C510" s="26"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="A511" s="23"/>
-      <c r="B511" s="23"/>
-      <c r="C511" s="23"/>
+      <c r="A511" s="26"/>
+      <c r="B511" s="26"/>
+      <c r="C511" s="26"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="A512" s="23"/>
-      <c r="B512" s="23"/>
-      <c r="C512" s="23"/>
+      <c r="A512" s="26"/>
+      <c r="B512" s="26"/>
+      <c r="C512" s="26"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="A513" s="23"/>
-      <c r="B513" s="23"/>
-      <c r="C513" s="23"/>
+      <c r="A513" s="26"/>
+      <c r="B513" s="26"/>
+      <c r="C513" s="26"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="A514" s="23"/>
-      <c r="B514" s="23"/>
-      <c r="C514" s="23"/>
+      <c r="A514" s="26"/>
+      <c r="B514" s="26"/>
+      <c r="C514" s="26"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="A515" s="23"/>
-      <c r="B515" s="23"/>
-      <c r="C515" s="23"/>
+      <c r="A515" s="26"/>
+      <c r="B515" s="26"/>
+      <c r="C515" s="26"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="A516" s="23"/>
-      <c r="B516" s="23"/>
-      <c r="C516" s="23"/>
+      <c r="A516" s="26"/>
+      <c r="B516" s="26"/>
+      <c r="C516" s="26"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="A517" s="23"/>
-      <c r="B517" s="23"/>
-      <c r="C517" s="23"/>
+      <c r="A517" s="26"/>
+      <c r="B517" s="26"/>
+      <c r="C517" s="26"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="A518" s="23"/>
-      <c r="B518" s="23"/>
-      <c r="C518" s="23"/>
+      <c r="A518" s="26"/>
+      <c r="B518" s="26"/>
+      <c r="C518" s="26"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="A519" s="23"/>
-      <c r="B519" s="23"/>
-      <c r="C519" s="23"/>
+      <c r="A519" s="26"/>
+      <c r="B519" s="26"/>
+      <c r="C519" s="26"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="A520" s="23"/>
-      <c r="B520" s="23"/>
-      <c r="C520" s="23"/>
+      <c r="A520" s="26"/>
+      <c r="B520" s="26"/>
+      <c r="C520" s="26"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="A521" s="23"/>
-      <c r="B521" s="23"/>
-      <c r="C521" s="23"/>
+      <c r="A521" s="26"/>
+      <c r="B521" s="26"/>
+      <c r="C521" s="26"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="A522" s="23"/>
-      <c r="B522" s="23"/>
-      <c r="C522" s="23"/>
+      <c r="A522" s="26"/>
+      <c r="B522" s="26"/>
+      <c r="C522" s="26"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="A523" s="23"/>
-      <c r="B523" s="23"/>
-      <c r="C523" s="23"/>
+      <c r="A523" s="26"/>
+      <c r="B523" s="26"/>
+      <c r="C523" s="26"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="A524" s="23"/>
-      <c r="B524" s="23"/>
-      <c r="C524" s="23"/>
+      <c r="A524" s="26"/>
+      <c r="B524" s="26"/>
+      <c r="C524" s="26"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="A525" s="23"/>
-      <c r="B525" s="23"/>
-      <c r="C525" s="23"/>
+      <c r="A525" s="26"/>
+      <c r="B525" s="26"/>
+      <c r="C525" s="26"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="A526" s="23"/>
-      <c r="B526" s="23"/>
-      <c r="C526" s="23"/>
+      <c r="A526" s="26"/>
+      <c r="B526" s="26"/>
+      <c r="C526" s="26"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="A527" s="23"/>
-      <c r="B527" s="23"/>
-      <c r="C527" s="23"/>
+      <c r="A527" s="26"/>
+      <c r="B527" s="26"/>
+      <c r="C527" s="26"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="A528" s="23"/>
-      <c r="B528" s="23"/>
-      <c r="C528" s="23"/>
+      <c r="A528" s="26"/>
+      <c r="B528" s="26"/>
+      <c r="C528" s="26"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="A529" s="23"/>
-      <c r="B529" s="23"/>
-      <c r="C529" s="23"/>
+      <c r="A529" s="26"/>
+      <c r="B529" s="26"/>
+      <c r="C529" s="26"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="A530" s="23"/>
-      <c r="B530" s="23"/>
-      <c r="C530" s="23"/>
+      <c r="A530" s="26"/>
+      <c r="B530" s="26"/>
+      <c r="C530" s="26"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="A531" s="23"/>
-      <c r="B531" s="23"/>
-      <c r="C531" s="23"/>
+      <c r="A531" s="26"/>
+      <c r="B531" s="26"/>
+      <c r="C531" s="26"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="A532" s="23"/>
-      <c r="B532" s="23"/>
-      <c r="C532" s="23"/>
+      <c r="A532" s="26"/>
+      <c r="B532" s="26"/>
+      <c r="C532" s="26"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="A533" s="23"/>
-      <c r="B533" s="23"/>
-      <c r="C533" s="23"/>
+      <c r="A533" s="26"/>
+      <c r="B533" s="26"/>
+      <c r="C533" s="26"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="A534" s="23"/>
-      <c r="B534" s="23"/>
-      <c r="C534" s="23"/>
+      <c r="A534" s="26"/>
+      <c r="B534" s="26"/>
+      <c r="C534" s="26"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="A535" s="23"/>
-      <c r="B535" s="23"/>
-      <c r="C535" s="23"/>
+      <c r="A535" s="26"/>
+      <c r="B535" s="26"/>
+      <c r="C535" s="26"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="A536" s="23"/>
-      <c r="B536" s="23"/>
-      <c r="C536" s="23"/>
+      <c r="A536" s="26"/>
+      <c r="B536" s="26"/>
+      <c r="C536" s="26"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="A537" s="23"/>
-      <c r="B537" s="23"/>
-      <c r="C537" s="23"/>
+      <c r="A537" s="26"/>
+      <c r="B537" s="26"/>
+      <c r="C537" s="26"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="A538" s="23"/>
-      <c r="B538" s="23"/>
-      <c r="C538" s="23"/>
+      <c r="A538" s="26"/>
+      <c r="B538" s="26"/>
+      <c r="C538" s="26"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="A539" s="23"/>
-      <c r="B539" s="23"/>
-      <c r="C539" s="23"/>
+      <c r="A539" s="26"/>
+      <c r="B539" s="26"/>
+      <c r="C539" s="26"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="A540" s="23"/>
-      <c r="B540" s="23"/>
-      <c r="C540" s="23"/>
+      <c r="A540" s="26"/>
+      <c r="B540" s="26"/>
+      <c r="C540" s="26"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="A541" s="23"/>
-      <c r="B541" s="23"/>
-      <c r="C541" s="23"/>
+      <c r="A541" s="26"/>
+      <c r="B541" s="26"/>
+      <c r="C541" s="26"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="A542" s="23"/>
-      <c r="B542" s="23"/>
-      <c r="C542" s="23"/>
+      <c r="A542" s="26"/>
+      <c r="B542" s="26"/>
+      <c r="C542" s="26"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="A543" s="23"/>
-      <c r="B543" s="23"/>
-      <c r="C543" s="23"/>
+      <c r="A543" s="26"/>
+      <c r="B543" s="26"/>
+      <c r="C543" s="26"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="A544" s="23"/>
-      <c r="B544" s="23"/>
-      <c r="C544" s="23"/>
+      <c r="A544" s="26"/>
+      <c r="B544" s="26"/>
+      <c r="C544" s="26"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="A545" s="23"/>
-      <c r="B545" s="23"/>
-      <c r="C545" s="23"/>
+      <c r="A545" s="26"/>
+      <c r="B545" s="26"/>
+      <c r="C545" s="26"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="A546" s="23"/>
-      <c r="B546" s="23"/>
-      <c r="C546" s="23"/>
+      <c r="A546" s="26"/>
+      <c r="B546" s="26"/>
+      <c r="C546" s="26"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="A547" s="23"/>
-      <c r="B547" s="23"/>
-      <c r="C547" s="23"/>
+      <c r="A547" s="26"/>
+      <c r="B547" s="26"/>
+      <c r="C547" s="26"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="A548" s="23"/>
-      <c r="B548" s="23"/>
-      <c r="C548" s="23"/>
+      <c r="A548" s="26"/>
+      <c r="B548" s="26"/>
+      <c r="C548" s="26"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="A549" s="23"/>
-      <c r="B549" s="23"/>
-      <c r="C549" s="23"/>
+      <c r="A549" s="26"/>
+      <c r="B549" s="26"/>
+      <c r="C549" s="26"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="A550" s="23"/>
-      <c r="B550" s="23"/>
-      <c r="C550" s="23"/>
+      <c r="A550" s="26"/>
+      <c r="B550" s="26"/>
+      <c r="C550" s="26"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="A551" s="23"/>
-      <c r="B551" s="23"/>
-      <c r="C551" s="23"/>
+      <c r="A551" s="26"/>
+      <c r="B551" s="26"/>
+      <c r="C551" s="26"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="A552" s="23"/>
-      <c r="B552" s="23"/>
-      <c r="C552" s="23"/>
+      <c r="A552" s="26"/>
+      <c r="B552" s="26"/>
+      <c r="C552" s="26"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="A553" s="23"/>
-      <c r="B553" s="23"/>
-      <c r="C553" s="23"/>
+      <c r="A553" s="26"/>
+      <c r="B553" s="26"/>
+      <c r="C553" s="26"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="A554" s="23"/>
-      <c r="B554" s="23"/>
-      <c r="C554" s="23"/>
+      <c r="A554" s="26"/>
+      <c r="B554" s="26"/>
+      <c r="C554" s="26"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="A555" s="23"/>
-      <c r="B555" s="23"/>
-      <c r="C555" s="23"/>
+      <c r="A555" s="26"/>
+      <c r="B555" s="26"/>
+      <c r="C555" s="26"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="A556" s="23"/>
-      <c r="B556" s="23"/>
-      <c r="C556" s="23"/>
+      <c r="A556" s="26"/>
+      <c r="B556" s="26"/>
+      <c r="C556" s="26"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="A557" s="23"/>
-      <c r="B557" s="23"/>
-      <c r="C557" s="23"/>
+      <c r="A557" s="26"/>
+      <c r="B557" s="26"/>
+      <c r="C557" s="26"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="A558" s="23"/>
-      <c r="B558" s="23"/>
-      <c r="C558" s="23"/>
+      <c r="A558" s="26"/>
+      <c r="B558" s="26"/>
+      <c r="C558" s="26"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="A559" s="23"/>
-      <c r="B559" s="23"/>
-      <c r="C559" s="23"/>
+      <c r="A559" s="26"/>
+      <c r="B559" s="26"/>
+      <c r="C559" s="26"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="A560" s="23"/>
-      <c r="B560" s="23"/>
-      <c r="C560" s="23"/>
+      <c r="A560" s="26"/>
+      <c r="B560" s="26"/>
+      <c r="C560" s="26"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="A561" s="23"/>
-      <c r="B561" s="23"/>
-      <c r="C561" s="23"/>
+      <c r="A561" s="26"/>
+      <c r="B561" s="26"/>
+      <c r="C561" s="26"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="A562" s="23"/>
-      <c r="B562" s="23"/>
-      <c r="C562" s="23"/>
+      <c r="A562" s="26"/>
+      <c r="B562" s="26"/>
+      <c r="C562" s="26"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="A563" s="23"/>
-      <c r="B563" s="23"/>
-      <c r="C563" s="23"/>
+      <c r="A563" s="26"/>
+      <c r="B563" s="26"/>
+      <c r="C563" s="26"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="A564" s="23"/>
-      <c r="B564" s="23"/>
-      <c r="C564" s="23"/>
+      <c r="A564" s="26"/>
+      <c r="B564" s="26"/>
+      <c r="C564" s="26"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="A565" s="23"/>
-      <c r="B565" s="23"/>
-      <c r="C565" s="23"/>
+      <c r="A565" s="26"/>
+      <c r="B565" s="26"/>
+      <c r="C565" s="26"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="A566" s="23"/>
-      <c r="B566" s="23"/>
-      <c r="C566" s="23"/>
+      <c r="A566" s="26"/>
+      <c r="B566" s="26"/>
+      <c r="C566" s="26"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="A567" s="23"/>
-      <c r="B567" s="23"/>
-      <c r="C567" s="23"/>
+      <c r="A567" s="26"/>
+      <c r="B567" s="26"/>
+      <c r="C567" s="26"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="A568" s="23"/>
-      <c r="B568" s="23"/>
-      <c r="C568" s="23"/>
+      <c r="A568" s="26"/>
+      <c r="B568" s="26"/>
+      <c r="C568" s="26"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="A569" s="23"/>
-      <c r="B569" s="23"/>
-      <c r="C569" s="23"/>
+      <c r="A569" s="26"/>
+      <c r="B569" s="26"/>
+      <c r="C569" s="26"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="A570" s="23"/>
-      <c r="B570" s="23"/>
-      <c r="C570" s="23"/>
+      <c r="A570" s="26"/>
+      <c r="B570" s="26"/>
+      <c r="C570" s="26"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="A571" s="23"/>
-      <c r="B571" s="23"/>
-      <c r="C571" s="23"/>
+      <c r="A571" s="26"/>
+      <c r="B571" s="26"/>
+      <c r="C571" s="26"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="A572" s="23"/>
-      <c r="B572" s="23"/>
-      <c r="C572" s="23"/>
+      <c r="A572" s="26"/>
+      <c r="B572" s="26"/>
+      <c r="C572" s="26"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="A573" s="23"/>
-      <c r="B573" s="23"/>
-      <c r="C573" s="23"/>
+      <c r="A573" s="26"/>
+      <c r="B573" s="26"/>
+      <c r="C573" s="26"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="A574" s="23"/>
-      <c r="B574" s="23"/>
-      <c r="C574" s="23"/>
+      <c r="A574" s="26"/>
+      <c r="B574" s="26"/>
+      <c r="C574" s="26"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="A575" s="23"/>
-      <c r="B575" s="23"/>
-      <c r="C575" s="23"/>
+      <c r="A575" s="26"/>
+      <c r="B575" s="26"/>
+      <c r="C575" s="26"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="A576" s="23"/>
-      <c r="B576" s="23"/>
-      <c r="C576" s="23"/>
+      <c r="A576" s="26"/>
+      <c r="B576" s="26"/>
+      <c r="C576" s="26"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="A577" s="23"/>
-      <c r="B577" s="23"/>
-      <c r="C577" s="23"/>
+      <c r="A577" s="26"/>
+      <c r="B577" s="26"/>
+      <c r="C577" s="26"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="A578" s="23"/>
-      <c r="B578" s="23"/>
-      <c r="C578" s="23"/>
+      <c r="A578" s="26"/>
+      <c r="B578" s="26"/>
+      <c r="C578" s="26"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="A579" s="23"/>
-      <c r="B579" s="23"/>
-      <c r="C579" s="23"/>
+      <c r="A579" s="26"/>
+      <c r="B579" s="26"/>
+      <c r="C579" s="26"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="A580" s="23"/>
-      <c r="B580" s="23"/>
-      <c r="C580" s="23"/>
+      <c r="A580" s="26"/>
+      <c r="B580" s="26"/>
+      <c r="C580" s="26"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="A581" s="23"/>
-      <c r="B581" s="23"/>
-      <c r="C581" s="23"/>
+      <c r="A581" s="26"/>
+      <c r="B581" s="26"/>
+      <c r="C581" s="26"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="A582" s="23"/>
-      <c r="B582" s="23"/>
-      <c r="C582" s="23"/>
+      <c r="A582" s="26"/>
+      <c r="B582" s="26"/>
+      <c r="C582" s="26"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="A583" s="23"/>
-      <c r="B583" s="23"/>
-      <c r="C583" s="23"/>
+      <c r="A583" s="26"/>
+      <c r="B583" s="26"/>
+      <c r="C583" s="26"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="A584" s="23"/>
-      <c r="B584" s="23"/>
-      <c r="C584" s="23"/>
+      <c r="A584" s="26"/>
+      <c r="B584" s="26"/>
+      <c r="C584" s="26"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="A585" s="23"/>
-      <c r="B585" s="23"/>
-      <c r="C585" s="23"/>
+      <c r="A585" s="26"/>
+      <c r="B585" s="26"/>
+      <c r="C585" s="26"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="A586" s="23"/>
-      <c r="B586" s="23"/>
-      <c r="C586" s="23"/>
+      <c r="A586" s="26"/>
+      <c r="B586" s="26"/>
+      <c r="C586" s="26"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="A587" s="23"/>
-      <c r="B587" s="23"/>
-      <c r="C587" s="23"/>
+      <c r="A587" s="26"/>
+      <c r="B587" s="26"/>
+      <c r="C587" s="26"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="A588" s="23"/>
-      <c r="B588" s="23"/>
-      <c r="C588" s="23"/>
+      <c r="A588" s="26"/>
+      <c r="B588" s="26"/>
+      <c r="C588" s="26"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="A589" s="23"/>
-      <c r="B589" s="23"/>
-      <c r="C589" s="23"/>
+      <c r="A589" s="26"/>
+      <c r="B589" s="26"/>
+      <c r="C589" s="26"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="A590" s="23"/>
-      <c r="B590" s="23"/>
-      <c r="C590" s="23"/>
+      <c r="A590" s="26"/>
+      <c r="B590" s="26"/>
+      <c r="C590" s="26"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="A591" s="23"/>
-      <c r="B591" s="23"/>
-      <c r="C591" s="23"/>
+      <c r="A591" s="26"/>
+      <c r="B591" s="26"/>
+      <c r="C591" s="26"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="A592" s="23"/>
-      <c r="B592" s="23"/>
-      <c r="C592" s="23"/>
+      <c r="A592" s="26"/>
+      <c r="B592" s="26"/>
+      <c r="C592" s="26"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="A593" s="23"/>
-      <c r="B593" s="23"/>
-      <c r="C593" s="23"/>
+      <c r="A593" s="26"/>
+      <c r="B593" s="26"/>
+      <c r="C593" s="26"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="A594" s="23"/>
-      <c r="B594" s="23"/>
-      <c r="C594" s="23"/>
+      <c r="A594" s="26"/>
+      <c r="B594" s="26"/>
+      <c r="C594" s="26"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="A595" s="23"/>
-      <c r="B595" s="23"/>
-      <c r="C595" s="23"/>
+      <c r="A595" s="26"/>
+      <c r="B595" s="26"/>
+      <c r="C595" s="26"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="A596" s="23"/>
-      <c r="B596" s="23"/>
-      <c r="C596" s="23"/>
+      <c r="A596" s="26"/>
+      <c r="B596" s="26"/>
+      <c r="C596" s="26"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="A597" s="23"/>
-      <c r="B597" s="23"/>
-      <c r="C597" s="23"/>
+      <c r="A597" s="26"/>
+      <c r="B597" s="26"/>
+      <c r="C597" s="26"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="A598" s="23"/>
-      <c r="B598" s="23"/>
-      <c r="C598" s="23"/>
+      <c r="A598" s="26"/>
+      <c r="B598" s="26"/>
+      <c r="C598" s="26"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="A599" s="23"/>
-      <c r="B599" s="23"/>
-      <c r="C599" s="23"/>
+      <c r="A599" s="26"/>
+      <c r="B599" s="26"/>
+      <c r="C599" s="26"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="A600" s="23"/>
-      <c r="B600" s="23"/>
-      <c r="C600" s="23"/>
+      <c r="A600" s="26"/>
+      <c r="B600" s="26"/>
+      <c r="C600" s="26"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="A601" s="23"/>
-      <c r="B601" s="23"/>
-      <c r="C601" s="23"/>
+      <c r="A601" s="26"/>
+      <c r="B601" s="26"/>
+      <c r="C601" s="26"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="A602" s="23"/>
-      <c r="B602" s="23"/>
-      <c r="C602" s="23"/>
+      <c r="A602" s="26"/>
+      <c r="B602" s="26"/>
+      <c r="C602" s="26"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="A603" s="23"/>
-      <c r="B603" s="23"/>
-      <c r="C603" s="23"/>
+      <c r="A603" s="26"/>
+      <c r="B603" s="26"/>
+      <c r="C603" s="26"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="A604" s="23"/>
-      <c r="B604" s="23"/>
-      <c r="C604" s="23"/>
+      <c r="A604" s="26"/>
+      <c r="B604" s="26"/>
+      <c r="C604" s="26"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="A605" s="23"/>
-      <c r="B605" s="23"/>
-      <c r="C605" s="23"/>
+      <c r="A605" s="26"/>
+      <c r="B605" s="26"/>
+      <c r="C605" s="26"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="A606" s="23"/>
-      <c r="B606" s="23"/>
-      <c r="C606" s="23"/>
+      <c r="A606" s="26"/>
+      <c r="B606" s="26"/>
+      <c r="C606" s="26"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="A607" s="23"/>
-      <c r="B607" s="23"/>
-      <c r="C607" s="23"/>
+      <c r="A607" s="26"/>
+      <c r="B607" s="26"/>
+      <c r="C607" s="26"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="A608" s="23"/>
-      <c r="B608" s="23"/>
-      <c r="C608" s="23"/>
+      <c r="A608" s="26"/>
+      <c r="B608" s="26"/>
+      <c r="C608" s="26"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="A609" s="23"/>
-      <c r="B609" s="23"/>
-      <c r="C609" s="23"/>
+      <c r="A609" s="26"/>
+      <c r="B609" s="26"/>
+      <c r="C609" s="26"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="A610" s="23"/>
-      <c r="B610" s="23"/>
-      <c r="C610" s="23"/>
+      <c r="A610" s="26"/>
+      <c r="B610" s="26"/>
+      <c r="C610" s="26"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="A611" s="23"/>
-      <c r="B611" s="23"/>
-      <c r="C611" s="23"/>
+      <c r="A611" s="26"/>
+      <c r="B611" s="26"/>
+      <c r="C611" s="26"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="A612" s="23"/>
-      <c r="B612" s="23"/>
-      <c r="C612" s="23"/>
+      <c r="A612" s="26"/>
+      <c r="B612" s="26"/>
+      <c r="C612" s="26"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="A613" s="23"/>
-      <c r="B613" s="23"/>
-      <c r="C613" s="23"/>
+      <c r="A613" s="26"/>
+      <c r="B613" s="26"/>
+      <c r="C613" s="26"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="A614" s="23"/>
-      <c r="B614" s="23"/>
-      <c r="C614" s="23"/>
+      <c r="A614" s="26"/>
+      <c r="B614" s="26"/>
+      <c r="C614" s="26"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="A615" s="23"/>
-      <c r="B615" s="23"/>
-      <c r="C615" s="23"/>
+      <c r="A615" s="26"/>
+      <c r="B615" s="26"/>
+      <c r="C615" s="26"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="A616" s="23"/>
-      <c r="B616" s="23"/>
-      <c r="C616" s="23"/>
+      <c r="A616" s="26"/>
+      <c r="B616" s="26"/>
+      <c r="C616" s="26"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="A617" s="23"/>
-      <c r="B617" s="23"/>
-      <c r="C617" s="23"/>
+      <c r="A617" s="26"/>
+      <c r="B617" s="26"/>
+      <c r="C617" s="26"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="A618" s="23"/>
-      <c r="B618" s="23"/>
-      <c r="C618" s="23"/>
+      <c r="A618" s="26"/>
+      <c r="B618" s="26"/>
+      <c r="C618" s="26"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="A619" s="23"/>
-      <c r="B619" s="23"/>
-      <c r="C619" s="23"/>
+      <c r="A619" s="26"/>
+      <c r="B619" s="26"/>
+      <c r="C619" s="26"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="A620" s="23"/>
-      <c r="B620" s="23"/>
-      <c r="C620" s="23"/>
+      <c r="A620" s="26"/>
+      <c r="B620" s="26"/>
+      <c r="C620" s="26"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="A621" s="23"/>
-      <c r="B621" s="23"/>
-      <c r="C621" s="23"/>
+      <c r="A621" s="26"/>
+      <c r="B621" s="26"/>
+      <c r="C621" s="26"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="A622" s="23"/>
-      <c r="B622" s="23"/>
-      <c r="C622" s="23"/>
+      <c r="A622" s="26"/>
+      <c r="B622" s="26"/>
+      <c r="C622" s="26"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="A623" s="23"/>
-      <c r="B623" s="23"/>
-      <c r="C623" s="23"/>
+      <c r="A623" s="26"/>
+      <c r="B623" s="26"/>
+      <c r="C623" s="26"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="A624" s="23"/>
-      <c r="B624" s="23"/>
-      <c r="C624" s="23"/>
+      <c r="A624" s="26"/>
+      <c r="B624" s="26"/>
+      <c r="C624" s="26"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="A625" s="23"/>
-      <c r="B625" s="23"/>
-      <c r="C625" s="23"/>
+      <c r="A625" s="26"/>
+      <c r="B625" s="26"/>
+      <c r="C625" s="26"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="A626" s="23"/>
-      <c r="B626" s="23"/>
-      <c r="C626" s="23"/>
+      <c r="A626" s="26"/>
+      <c r="B626" s="26"/>
+      <c r="C626" s="26"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="A627" s="23"/>
-      <c r="B627" s="23"/>
-      <c r="C627" s="23"/>
+      <c r="A627" s="26"/>
+      <c r="B627" s="26"/>
+      <c r="C627" s="26"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="A628" s="23"/>
-      <c r="B628" s="23"/>
-      <c r="C628" s="23"/>
+      <c r="A628" s="26"/>
+      <c r="B628" s="26"/>
+      <c r="C628" s="26"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="A629" s="23"/>
-      <c r="B629" s="23"/>
-      <c r="C629" s="23"/>
+      <c r="A629" s="26"/>
+      <c r="B629" s="26"/>
+      <c r="C629" s="26"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="A630" s="23"/>
-      <c r="B630" s="23"/>
-      <c r="C630" s="23"/>
+      <c r="A630" s="26"/>
+      <c r="B630" s="26"/>
+      <c r="C630" s="26"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="A631" s="23"/>
-      <c r="B631" s="23"/>
-      <c r="C631" s="23"/>
+      <c r="A631" s="26"/>
+      <c r="B631" s="26"/>
+      <c r="C631" s="26"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="A632" s="23"/>
-      <c r="B632" s="23"/>
-      <c r="C632" s="23"/>
+      <c r="A632" s="26"/>
+      <c r="B632" s="26"/>
+      <c r="C632" s="26"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="A633" s="23"/>
-      <c r="B633" s="23"/>
-      <c r="C633" s="23"/>
+      <c r="A633" s="26"/>
+      <c r="B633" s="26"/>
+      <c r="C633" s="26"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="A634" s="23"/>
-      <c r="B634" s="23"/>
-      <c r="C634" s="23"/>
+      <c r="A634" s="26"/>
+      <c r="B634" s="26"/>
+      <c r="C634" s="26"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="A635" s="23"/>
-      <c r="B635" s="23"/>
-      <c r="C635" s="23"/>
+      <c r="A635" s="26"/>
+      <c r="B635" s="26"/>
+      <c r="C635" s="26"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="A636" s="23"/>
-      <c r="B636" s="23"/>
-      <c r="C636" s="23"/>
+      <c r="A636" s="26"/>
+      <c r="B636" s="26"/>
+      <c r="C636" s="26"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="A637" s="23"/>
-      <c r="B637" s="23"/>
-      <c r="C637" s="23"/>
+      <c r="A637" s="26"/>
+      <c r="B637" s="26"/>
+      <c r="C637" s="26"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="A638" s="23"/>
-      <c r="B638" s="23"/>
-      <c r="C638" s="23"/>
+      <c r="A638" s="26"/>
+      <c r="B638" s="26"/>
+      <c r="C638" s="26"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="A639" s="23"/>
-      <c r="B639" s="23"/>
-      <c r="C639" s="23"/>
+      <c r="A639" s="26"/>
+      <c r="B639" s="26"/>
+      <c r="C639" s="26"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="A640" s="23"/>
-      <c r="B640" s="23"/>
-      <c r="C640" s="23"/>
+      <c r="A640" s="26"/>
+      <c r="B640" s="26"/>
+      <c r="C640" s="26"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="A641" s="23"/>
-      <c r="B641" s="23"/>
-      <c r="C641" s="23"/>
+      <c r="A641" s="26"/>
+      <c r="B641" s="26"/>
+      <c r="C641" s="26"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="A642" s="23"/>
-      <c r="B642" s="23"/>
-      <c r="C642" s="23"/>
+      <c r="A642" s="26"/>
+      <c r="B642" s="26"/>
+      <c r="C642" s="26"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="A643" s="23"/>
-      <c r="B643" s="23"/>
-      <c r="C643" s="23"/>
+      <c r="A643" s="26"/>
+      <c r="B643" s="26"/>
+      <c r="C643" s="26"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="A644" s="23"/>
-      <c r="B644" s="23"/>
-      <c r="C644" s="23"/>
+      <c r="A644" s="26"/>
+      <c r="B644" s="26"/>
+      <c r="C644" s="26"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="A645" s="23"/>
-      <c r="B645" s="23"/>
-      <c r="C645" s="23"/>
+      <c r="A645" s="26"/>
+      <c r="B645" s="26"/>
+      <c r="C645" s="26"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="A646" s="23"/>
-      <c r="B646" s="23"/>
-      <c r="C646" s="23"/>
+      <c r="A646" s="26"/>
+      <c r="B646" s="26"/>
+      <c r="C646" s="26"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="A647" s="23"/>
-      <c r="B647" s="23"/>
-      <c r="C647" s="23"/>
+      <c r="A647" s="26"/>
+      <c r="B647" s="26"/>
+      <c r="C647" s="26"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="A648" s="23"/>
-      <c r="B648" s="23"/>
-      <c r="C648" s="23"/>
+      <c r="A648" s="26"/>
+      <c r="B648" s="26"/>
+      <c r="C648" s="26"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="A649" s="23"/>
-      <c r="B649" s="23"/>
-      <c r="C649" s="23"/>
+      <c r="A649" s="26"/>
+      <c r="B649" s="26"/>
+      <c r="C649" s="26"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="A650" s="23"/>
-      <c r="B650" s="23"/>
-      <c r="C650" s="23"/>
+      <c r="A650" s="26"/>
+      <c r="B650" s="26"/>
+      <c r="C650" s="26"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="A651" s="23"/>
-      <c r="B651" s="23"/>
-      <c r="C651" s="23"/>
+      <c r="A651" s="26"/>
+      <c r="B651" s="26"/>
+      <c r="C651" s="26"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="A652" s="23"/>
-      <c r="B652" s="23"/>
-      <c r="C652" s="23"/>
+      <c r="A652" s="26"/>
+      <c r="B652" s="26"/>
+      <c r="C652" s="26"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="A653" s="23"/>
-      <c r="B653" s="23"/>
-      <c r="C653" s="23"/>
+      <c r="A653" s="26"/>
+      <c r="B653" s="26"/>
+      <c r="C653" s="26"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="A654" s="23"/>
-      <c r="B654" s="23"/>
-      <c r="C654" s="23"/>
+      <c r="A654" s="26"/>
+      <c r="B654" s="26"/>
+      <c r="C654" s="26"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="A655" s="23"/>
-      <c r="B655" s="23"/>
-      <c r="C655" s="23"/>
+      <c r="A655" s="26"/>
+      <c r="B655" s="26"/>
+      <c r="C655" s="26"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="A656" s="23"/>
-      <c r="B656" s="23"/>
-      <c r="C656" s="23"/>
+      <c r="A656" s="26"/>
+      <c r="B656" s="26"/>
+      <c r="C656" s="26"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="A657" s="23"/>
-      <c r="B657" s="23"/>
-      <c r="C657" s="23"/>
+      <c r="A657" s="26"/>
+      <c r="B657" s="26"/>
+      <c r="C657" s="26"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="A658" s="23"/>
-      <c r="B658" s="23"/>
-      <c r="C658" s="23"/>
+      <c r="A658" s="26"/>
+      <c r="B658" s="26"/>
+      <c r="C658" s="26"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="A659" s="23"/>
-      <c r="B659" s="23"/>
-      <c r="C659" s="23"/>
+      <c r="A659" s="26"/>
+      <c r="B659" s="26"/>
+      <c r="C659" s="26"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="A660" s="23"/>
-      <c r="B660" s="23"/>
-      <c r="C660" s="23"/>
+      <c r="A660" s="26"/>
+      <c r="B660" s="26"/>
+      <c r="C660" s="26"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="A661" s="23"/>
-      <c r="B661" s="23"/>
-      <c r="C661" s="23"/>
+      <c r="A661" s="26"/>
+      <c r="B661" s="26"/>
+      <c r="C661" s="26"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="A662" s="23"/>
-      <c r="B662" s="23"/>
-      <c r="C662" s="23"/>
+      <c r="A662" s="26"/>
+      <c r="B662" s="26"/>
+      <c r="C662" s="26"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="A663" s="23"/>
-      <c r="B663" s="23"/>
-      <c r="C663" s="23"/>
+      <c r="A663" s="26"/>
+      <c r="B663" s="26"/>
+      <c r="C663" s="26"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="A664" s="23"/>
-      <c r="B664" s="23"/>
-      <c r="C664" s="23"/>
+      <c r="A664" s="26"/>
+      <c r="B664" s="26"/>
+      <c r="C664" s="26"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="A665" s="23"/>
-      <c r="B665" s="23"/>
-      <c r="C665" s="23"/>
+      <c r="A665" s="26"/>
+      <c r="B665" s="26"/>
+      <c r="C665" s="26"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="A666" s="23"/>
-      <c r="B666" s="23"/>
-      <c r="C666" s="23"/>
+      <c r="A666" s="26"/>
+      <c r="B666" s="26"/>
+      <c r="C666" s="26"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="A667" s="23"/>
-      <c r="B667" s="23"/>
-      <c r="C667" s="23"/>
+      <c r="A667" s="26"/>
+      <c r="B667" s="26"/>
+      <c r="C667" s="26"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="A668" s="23"/>
-      <c r="B668" s="23"/>
-      <c r="C668" s="23"/>
+      <c r="A668" s="26"/>
+      <c r="B668" s="26"/>
+      <c r="C668" s="26"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="A669" s="23"/>
-      <c r="B669" s="23"/>
-      <c r="C669" s="23"/>
+      <c r="A669" s="26"/>
+      <c r="B669" s="26"/>
+      <c r="C669" s="26"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="A670" s="23"/>
-      <c r="B670" s="23"/>
-      <c r="C670" s="23"/>
+      <c r="A670" s="26"/>
+      <c r="B670" s="26"/>
+      <c r="C670" s="26"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="A671" s="23"/>
-      <c r="B671" s="23"/>
-      <c r="C671" s="23"/>
+      <c r="A671" s="26"/>
+      <c r="B671" s="26"/>
+      <c r="C671" s="26"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="A672" s="23"/>
-      <c r="B672" s="23"/>
-      <c r="C672" s="23"/>
+      <c r="A672" s="26"/>
+      <c r="B672" s="26"/>
+      <c r="C672" s="26"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="A673" s="23"/>
-      <c r="B673" s="23"/>
-      <c r="C673" s="23"/>
+      <c r="A673" s="26"/>
+      <c r="B673" s="26"/>
+      <c r="C673" s="26"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="A674" s="23"/>
-      <c r="B674" s="23"/>
-      <c r="C674" s="23"/>
+      <c r="A674" s="26"/>
+      <c r="B674" s="26"/>
+      <c r="C674" s="26"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="A675" s="23"/>
-      <c r="B675" s="23"/>
-      <c r="C675" s="23"/>
+      <c r="A675" s="26"/>
+      <c r="B675" s="26"/>
+      <c r="C675" s="26"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="A676" s="23"/>
-      <c r="B676" s="23"/>
-      <c r="C676" s="23"/>
+      <c r="A676" s="26"/>
+      <c r="B676" s="26"/>
+      <c r="C676" s="26"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="A677" s="23"/>
-      <c r="B677" s="23"/>
-      <c r="C677" s="23"/>
+      <c r="A677" s="26"/>
+      <c r="B677" s="26"/>
+      <c r="C677" s="26"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="A678" s="23"/>
-      <c r="B678" s="23"/>
-      <c r="C678" s="23"/>
+      <c r="A678" s="26"/>
+      <c r="B678" s="26"/>
+      <c r="C678" s="26"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="A679" s="23"/>
-      <c r="B679" s="23"/>
-      <c r="C679" s="23"/>
+      <c r="A679" s="26"/>
+      <c r="B679" s="26"/>
+      <c r="C679" s="26"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="A680" s="23"/>
-      <c r="B680" s="23"/>
-      <c r="C680" s="23"/>
+      <c r="A680" s="26"/>
+      <c r="B680" s="26"/>
+      <c r="C680" s="26"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="A681" s="23"/>
-      <c r="B681" s="23"/>
-      <c r="C681" s="23"/>
+      <c r="A681" s="26"/>
+      <c r="B681" s="26"/>
+      <c r="C681" s="26"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="A682" s="23"/>
-      <c r="B682" s="23"/>
-      <c r="C682" s="23"/>
+      <c r="A682" s="26"/>
+      <c r="B682" s="26"/>
+      <c r="C682" s="26"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="A683" s="23"/>
-      <c r="B683" s="23"/>
-      <c r="C683" s="23"/>
+      <c r="A683" s="26"/>
+      <c r="B683" s="26"/>
+      <c r="C683" s="26"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="A684" s="23"/>
-      <c r="B684" s="23"/>
-      <c r="C684" s="23"/>
+      <c r="A684" s="26"/>
+      <c r="B684" s="26"/>
+      <c r="C684" s="26"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="A685" s="23"/>
-      <c r="B685" s="23"/>
-      <c r="C685" s="23"/>
+      <c r="A685" s="26"/>
+      <c r="B685" s="26"/>
+      <c r="C685" s="26"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="A686" s="23"/>
-      <c r="B686" s="23"/>
-      <c r="C686" s="23"/>
+      <c r="A686" s="26"/>
+      <c r="B686" s="26"/>
+      <c r="C686" s="26"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="A687" s="23"/>
-      <c r="B687" s="23"/>
-      <c r="C687" s="23"/>
+      <c r="A687" s="26"/>
+      <c r="B687" s="26"/>
+      <c r="C687" s="26"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="A688" s="23"/>
-      <c r="B688" s="23"/>
-      <c r="C688" s="23"/>
+      <c r="A688" s="26"/>
+      <c r="B688" s="26"/>
+      <c r="C688" s="26"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="A689" s="23"/>
-      <c r="B689" s="23"/>
-      <c r="C689" s="23"/>
+      <c r="A689" s="26"/>
+      <c r="B689" s="26"/>
+      <c r="C689" s="26"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="A690" s="23"/>
-      <c r="B690" s="23"/>
-      <c r="C690" s="23"/>
+      <c r="A690" s="26"/>
+      <c r="B690" s="26"/>
+      <c r="C690" s="26"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="A691" s="23"/>
-      <c r="B691" s="23"/>
-      <c r="C691" s="23"/>
+      <c r="A691" s="26"/>
+      <c r="B691" s="26"/>
+      <c r="C691" s="26"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="A692" s="23"/>
-      <c r="B692" s="23"/>
-      <c r="C692" s="23"/>
+      <c r="A692" s="26"/>
+      <c r="B692" s="26"/>
+      <c r="C692" s="26"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="A693" s="23"/>
-      <c r="B693" s="23"/>
-      <c r="C693" s="23"/>
+      <c r="A693" s="26"/>
+      <c r="B693" s="26"/>
+      <c r="C693" s="26"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="A694" s="23"/>
-      <c r="B694" s="23"/>
-      <c r="C694" s="23"/>
+      <c r="A694" s="26"/>
+      <c r="B694" s="26"/>
+      <c r="C694" s="26"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="A695" s="23"/>
-      <c r="B695" s="23"/>
-      <c r="C695" s="23"/>
+      <c r="A695" s="26"/>
+      <c r="B695" s="26"/>
+      <c r="C695" s="26"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="A696" s="23"/>
-      <c r="B696" s="23"/>
-      <c r="C696" s="23"/>
+      <c r="A696" s="26"/>
+      <c r="B696" s="26"/>
+      <c r="C696" s="26"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="A697" s="23"/>
-      <c r="B697" s="23"/>
-      <c r="C697" s="23"/>
+      <c r="A697" s="26"/>
+      <c r="B697" s="26"/>
+      <c r="C697" s="26"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="A698" s="23"/>
-      <c r="B698" s="23"/>
-      <c r="C698" s="23"/>
+      <c r="A698" s="26"/>
+      <c r="B698" s="26"/>
+      <c r="C698" s="26"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="A699" s="23"/>
-      <c r="B699" s="23"/>
-      <c r="C699" s="23"/>
+      <c r="A699" s="26"/>
+      <c r="B699" s="26"/>
+      <c r="C699" s="26"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="A700" s="23"/>
-      <c r="B700" s="23"/>
-      <c r="C700" s="23"/>
+      <c r="A700" s="26"/>
+      <c r="B700" s="26"/>
+      <c r="C700" s="26"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="A701" s="23"/>
-      <c r="B701" s="23"/>
-      <c r="C701" s="23"/>
+      <c r="A701" s="26"/>
+      <c r="B701" s="26"/>
+      <c r="C701" s="26"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="A702" s="23"/>
-      <c r="B702" s="23"/>
-      <c r="C702" s="23"/>
+      <c r="A702" s="26"/>
+      <c r="B702" s="26"/>
+      <c r="C702" s="26"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="A703" s="23"/>
-      <c r="B703" s="23"/>
-      <c r="C703" s="23"/>
+      <c r="A703" s="26"/>
+      <c r="B703" s="26"/>
+      <c r="C703" s="26"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="A704" s="23"/>
-      <c r="B704" s="23"/>
-      <c r="C704" s="23"/>
+      <c r="A704" s="26"/>
+      <c r="B704" s="26"/>
+      <c r="C704" s="26"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="A705" s="23"/>
-      <c r="B705" s="23"/>
-      <c r="C705" s="23"/>
+      <c r="A705" s="26"/>
+      <c r="B705" s="26"/>
+      <c r="C705" s="26"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="A706" s="23"/>
-      <c r="B706" s="23"/>
-      <c r="C706" s="23"/>
+      <c r="A706" s="26"/>
+      <c r="B706" s="26"/>
+      <c r="C706" s="26"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="A707" s="23"/>
-      <c r="B707" s="23"/>
-      <c r="C707" s="23"/>
+      <c r="A707" s="26"/>
+      <c r="B707" s="26"/>
+      <c r="C707" s="26"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="23"/>
-      <c r="B708" s="23"/>
-      <c r="C708" s="23"/>
+      <c r="A708" s="26"/>
+      <c r="B708" s="26"/>
+      <c r="C708" s="26"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="A709" s="23"/>
-      <c r="B709" s="23"/>
-      <c r="C709" s="23"/>
+      <c r="A709" s="26"/>
+      <c r="B709" s="26"/>
+      <c r="C709" s="26"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="A710" s="23"/>
-      <c r="B710" s="23"/>
-      <c r="C710" s="23"/>
+      <c r="A710" s="26"/>
+      <c r="B710" s="26"/>
+      <c r="C710" s="26"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="A711" s="23"/>
-      <c r="B711" s="23"/>
-      <c r="C711" s="23"/>
+      <c r="A711" s="26"/>
+      <c r="B711" s="26"/>
+      <c r="C711" s="26"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="A712" s="23"/>
-      <c r="B712" s="23"/>
-      <c r="C712" s="23"/>
+      <c r="A712" s="26"/>
+      <c r="B712" s="26"/>
+      <c r="C712" s="26"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="A713" s="23"/>
-      <c r="B713" s="23"/>
-      <c r="C713" s="23"/>
+      <c r="A713" s="26"/>
+      <c r="B713" s="26"/>
+      <c r="C713" s="26"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="A714" s="23"/>
-      <c r="B714" s="23"/>
-      <c r="C714" s="23"/>
+      <c r="A714" s="26"/>
+      <c r="B714" s="26"/>
+      <c r="C714" s="26"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="A715" s="23"/>
-      <c r="B715" s="23"/>
-      <c r="C715" s="23"/>
+      <c r="A715" s="26"/>
+      <c r="B715" s="26"/>
+      <c r="C715" s="26"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="A716" s="23"/>
-      <c r="B716" s="23"/>
-      <c r="C716" s="23"/>
+      <c r="A716" s="26"/>
+      <c r="B716" s="26"/>
+      <c r="C716" s="26"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="A717" s="23"/>
-      <c r="B717" s="23"/>
-      <c r="C717" s="23"/>
+      <c r="A717" s="26"/>
+      <c r="B717" s="26"/>
+      <c r="C717" s="26"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="A718" s="23"/>
-      <c r="B718" s="23"/>
-      <c r="C718" s="23"/>
+      <c r="A718" s="26"/>
+      <c r="B718" s="26"/>
+      <c r="C718" s="26"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="A719" s="23"/>
-      <c r="B719" s="23"/>
-      <c r="C719" s="23"/>
+      <c r="A719" s="26"/>
+      <c r="B719" s="26"/>
+      <c r="C719" s="26"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="A720" s="23"/>
-      <c r="B720" s="23"/>
-      <c r="C720" s="23"/>
+      <c r="A720" s="26"/>
+      <c r="B720" s="26"/>
+      <c r="C720" s="26"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="A721" s="23"/>
-      <c r="B721" s="23"/>
-      <c r="C721" s="23"/>
+      <c r="A721" s="26"/>
+      <c r="B721" s="26"/>
+      <c r="C721" s="26"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="A722" s="23"/>
-      <c r="B722" s="23"/>
-      <c r="C722" s="23"/>
+      <c r="A722" s="26"/>
+      <c r="B722" s="26"/>
+      <c r="C722" s="26"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="A723" s="23"/>
-      <c r="B723" s="23"/>
-      <c r="C723" s="23"/>
+      <c r="A723" s="26"/>
+      <c r="B723" s="26"/>
+      <c r="C723" s="26"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="A724" s="23"/>
-      <c r="B724" s="23"/>
-      <c r="C724" s="23"/>
+      <c r="A724" s="26"/>
+      <c r="B724" s="26"/>
+      <c r="C724" s="26"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="A725" s="23"/>
-      <c r="B725" s="23"/>
-      <c r="C725" s="23"/>
+      <c r="A725" s="26"/>
+      <c r="B725" s="26"/>
+      <c r="C725" s="26"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="A726" s="23"/>
-      <c r="B726" s="23"/>
-      <c r="C726" s="23"/>
+      <c r="A726" s="26"/>
+      <c r="B726" s="26"/>
+      <c r="C726" s="26"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="A727" s="23"/>
-      <c r="B727" s="23"/>
-      <c r="C727" s="23"/>
+      <c r="A727" s="26"/>
+      <c r="B727" s="26"/>
+      <c r="C727" s="26"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="A728" s="23"/>
-      <c r="B728" s="23"/>
-      <c r="C728" s="23"/>
+      <c r="A728" s="26"/>
+      <c r="B728" s="26"/>
+      <c r="C728" s="26"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="A729" s="23"/>
-      <c r="B729" s="23"/>
-      <c r="C729" s="23"/>
+      <c r="A729" s="26"/>
+      <c r="B729" s="26"/>
+      <c r="C729" s="26"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="A730" s="23"/>
-      <c r="B730" s="23"/>
-      <c r="C730" s="23"/>
+      <c r="A730" s="26"/>
+      <c r="B730" s="26"/>
+      <c r="C730" s="26"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="A731" s="23"/>
-      <c r="B731" s="23"/>
-      <c r="C731" s="23"/>
+      <c r="A731" s="26"/>
+      <c r="B731" s="26"/>
+      <c r="C731" s="26"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="A732" s="23"/>
-      <c r="B732" s="23"/>
-      <c r="C732" s="23"/>
+      <c r="A732" s="26"/>
+      <c r="B732" s="26"/>
+      <c r="C732" s="26"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="A733" s="23"/>
-      <c r="B733" s="23"/>
-      <c r="C733" s="23"/>
+      <c r="A733" s="26"/>
+      <c r="B733" s="26"/>
+      <c r="C733" s="26"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="A734" s="23"/>
-      <c r="B734" s="23"/>
-      <c r="C734" s="23"/>
+      <c r="A734" s="26"/>
+      <c r="B734" s="26"/>
+      <c r="C734" s="26"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="A735" s="23"/>
-      <c r="B735" s="23"/>
-      <c r="C735" s="23"/>
+      <c r="A735" s="26"/>
+      <c r="B735" s="26"/>
+      <c r="C735" s="26"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="A736" s="23"/>
-      <c r="B736" s="23"/>
-      <c r="C736" s="23"/>
+      <c r="A736" s="26"/>
+      <c r="B736" s="26"/>
+      <c r="C736" s="26"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="A737" s="23"/>
-      <c r="B737" s="23"/>
-      <c r="C737" s="23"/>
+      <c r="A737" s="26"/>
+      <c r="B737" s="26"/>
+      <c r="C737" s="26"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="A738" s="23"/>
-      <c r="B738" s="23"/>
-      <c r="C738" s="23"/>
+      <c r="A738" s="26"/>
+      <c r="B738" s="26"/>
+      <c r="C738" s="26"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="A739" s="23"/>
-      <c r="B739" s="23"/>
-      <c r="C739" s="23"/>
+      <c r="A739" s="26"/>
+      <c r="B739" s="26"/>
+      <c r="C739" s="26"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="A740" s="23"/>
-      <c r="B740" s="23"/>
-      <c r="C740" s="23"/>
+      <c r="A740" s="26"/>
+      <c r="B740" s="26"/>
+      <c r="C740" s="26"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="A741" s="23"/>
-      <c r="B741" s="23"/>
-      <c r="C741" s="23"/>
+      <c r="A741" s="26"/>
+      <c r="B741" s="26"/>
+      <c r="C741" s="26"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="A742" s="23"/>
-      <c r="B742" s="23"/>
-      <c r="C742" s="23"/>
+      <c r="A742" s="26"/>
+      <c r="B742" s="26"/>
+      <c r="C742" s="26"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="A743" s="23"/>
-      <c r="B743" s="23"/>
-      <c r="C743" s="23"/>
+      <c r="A743" s="26"/>
+      <c r="B743" s="26"/>
+      <c r="C743" s="26"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="A744" s="23"/>
-      <c r="B744" s="23"/>
-      <c r="C744" s="23"/>
+      <c r="A744" s="26"/>
+      <c r="B744" s="26"/>
+      <c r="C744" s="26"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="A745" s="23"/>
-      <c r="B745" s="23"/>
-      <c r="C745" s="23"/>
+      <c r="A745" s="26"/>
+      <c r="B745" s="26"/>
+      <c r="C745" s="26"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="A746" s="23"/>
-      <c r="B746" s="23"/>
-      <c r="C746" s="23"/>
+      <c r="A746" s="26"/>
+      <c r="B746" s="26"/>
+      <c r="C746" s="26"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="A747" s="23"/>
-      <c r="B747" s="23"/>
-      <c r="C747" s="23"/>
+      <c r="A747" s="26"/>
+      <c r="B747" s="26"/>
+      <c r="C747" s="26"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="A748" s="23"/>
-      <c r="B748" s="23"/>
-      <c r="C748" s="23"/>
+      <c r="A748" s="26"/>
+      <c r="B748" s="26"/>
+      <c r="C748" s="26"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="A749" s="23"/>
-      <c r="B749" s="23"/>
-      <c r="C749" s="23"/>
+      <c r="A749" s="26"/>
+      <c r="B749" s="26"/>
+      <c r="C749" s="26"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="A750" s="23"/>
-      <c r="B750" s="23"/>
-      <c r="C750" s="23"/>
+      <c r="A750" s="26"/>
+      <c r="B750" s="26"/>
+      <c r="C750" s="26"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="A751" s="23"/>
-      <c r="B751" s="23"/>
-      <c r="C751" s="23"/>
+      <c r="A751" s="26"/>
+      <c r="B751" s="26"/>
+      <c r="C751" s="26"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="A752" s="23"/>
-      <c r="B752" s="23"/>
-      <c r="C752" s="23"/>
+      <c r="A752" s="26"/>
+      <c r="B752" s="26"/>
+      <c r="C752" s="26"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="A753" s="23"/>
-      <c r="B753" s="23"/>
-      <c r="C753" s="23"/>
+      <c r="A753" s="26"/>
+      <c r="B753" s="26"/>
+      <c r="C753" s="26"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="A754" s="23"/>
-      <c r="B754" s="23"/>
-      <c r="C754" s="23"/>
+      <c r="A754" s="26"/>
+      <c r="B754" s="26"/>
+      <c r="C754" s="26"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="A755" s="23"/>
-      <c r="B755" s="23"/>
-      <c r="C755" s="23"/>
+      <c r="A755" s="26"/>
+      <c r="B755" s="26"/>
+      <c r="C755" s="26"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="A756" s="23"/>
-      <c r="B756" s="23"/>
-      <c r="C756" s="23"/>
+      <c r="A756" s="26"/>
+      <c r="B756" s="26"/>
+      <c r="C756" s="26"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="A757" s="23"/>
-      <c r="B757" s="23"/>
-      <c r="C757" s="23"/>
+      <c r="A757" s="26"/>
+      <c r="B757" s="26"/>
+      <c r="C757" s="26"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="A758" s="23"/>
-      <c r="B758" s="23"/>
-      <c r="C758" s="23"/>
+      <c r="A758" s="26"/>
+      <c r="B758" s="26"/>
+      <c r="C758" s="26"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="A759" s="23"/>
-      <c r="B759" s="23"/>
-      <c r="C759" s="23"/>
+      <c r="A759" s="26"/>
+      <c r="B759" s="26"/>
+      <c r="C759" s="26"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="A760" s="23"/>
-      <c r="B760" s="23"/>
-      <c r="C760" s="23"/>
+      <c r="A760" s="26"/>
+      <c r="B760" s="26"/>
+      <c r="C760" s="26"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="A761" s="23"/>
-      <c r="B761" s="23"/>
-      <c r="C761" s="23"/>
+      <c r="A761" s="26"/>
+      <c r="B761" s="26"/>
+      <c r="C761" s="26"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="A762" s="23"/>
-      <c r="B762" s="23"/>
-      <c r="C762" s="23"/>
+      <c r="A762" s="26"/>
+      <c r="B762" s="26"/>
+      <c r="C762" s="26"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="A763" s="23"/>
-      <c r="B763" s="23"/>
-      <c r="C763" s="23"/>
+      <c r="A763" s="26"/>
+      <c r="B763" s="26"/>
+      <c r="C763" s="26"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="A764" s="23"/>
-      <c r="B764" s="23"/>
-      <c r="C764" s="23"/>
+      <c r="A764" s="26"/>
+      <c r="B764" s="26"/>
+      <c r="C764" s="26"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="A765" s="23"/>
-      <c r="B765" s="23"/>
-      <c r="C765" s="23"/>
+      <c r="A765" s="26"/>
+      <c r="B765" s="26"/>
+      <c r="C765" s="26"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="A766" s="23"/>
-      <c r="B766" s="23"/>
-      <c r="C766" s="23"/>
+      <c r="A766" s="26"/>
+      <c r="B766" s="26"/>
+      <c r="C766" s="26"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="A767" s="23"/>
-      <c r="B767" s="23"/>
-      <c r="C767" s="23"/>
+      <c r="A767" s="26"/>
+      <c r="B767" s="26"/>
+      <c r="C767" s="26"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="A768" s="23"/>
-      <c r="B768" s="23"/>
-      <c r="C768" s="23"/>
+      <c r="A768" s="26"/>
+      <c r="B768" s="26"/>
+      <c r="C768" s="26"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="A769" s="23"/>
-      <c r="B769" s="23"/>
-      <c r="C769" s="23"/>
+      <c r="A769" s="26"/>
+      <c r="B769" s="26"/>
+      <c r="C769" s="26"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="A770" s="23"/>
-      <c r="B770" s="23"/>
-      <c r="C770" s="23"/>
+      <c r="A770" s="26"/>
+      <c r="B770" s="26"/>
+      <c r="C770" s="26"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="A771" s="23"/>
-      <c r="B771" s="23"/>
-      <c r="C771" s="23"/>
+      <c r="A771" s="26"/>
+      <c r="B771" s="26"/>
+      <c r="C771" s="26"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="A772" s="23"/>
-      <c r="B772" s="23"/>
-      <c r="C772" s="23"/>
+      <c r="A772" s="26"/>
+      <c r="B772" s="26"/>
+      <c r="C772" s="26"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="A773" s="23"/>
-      <c r="B773" s="23"/>
-      <c r="C773" s="23"/>
+      <c r="A773" s="26"/>
+      <c r="B773" s="26"/>
+      <c r="C773" s="26"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="A774" s="23"/>
-      <c r="B774" s="23"/>
-      <c r="C774" s="23"/>
+      <c r="A774" s="26"/>
+      <c r="B774" s="26"/>
+      <c r="C774" s="26"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="A775" s="23"/>
-      <c r="B775" s="23"/>
-      <c r="C775" s="23"/>
+      <c r="A775" s="26"/>
+      <c r="B775" s="26"/>
+      <c r="C775" s="26"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="A776" s="23"/>
-      <c r="B776" s="23"/>
-      <c r="C776" s="23"/>
+      <c r="A776" s="26"/>
+      <c r="B776" s="26"/>
+      <c r="C776" s="26"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="A777" s="23"/>
-      <c r="B777" s="23"/>
-      <c r="C777" s="23"/>
+      <c r="A777" s="26"/>
+      <c r="B777" s="26"/>
+      <c r="C777" s="26"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="A778" s="23"/>
-      <c r="B778" s="23"/>
-      <c r="C778" s="23"/>
+      <c r="A778" s="26"/>
+      <c r="B778" s="26"/>
+      <c r="C778" s="26"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="A779" s="23"/>
-      <c r="B779" s="23"/>
-      <c r="C779" s="23"/>
+      <c r="A779" s="26"/>
+      <c r="B779" s="26"/>
+      <c r="C779" s="26"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="A780" s="23"/>
-      <c r="B780" s="23"/>
-      <c r="C780" s="23"/>
+      <c r="A780" s="26"/>
+      <c r="B780" s="26"/>
+      <c r="C780" s="26"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="A781" s="23"/>
-      <c r="B781" s="23"/>
-      <c r="C781" s="23"/>
+      <c r="A781" s="26"/>
+      <c r="B781" s="26"/>
+      <c r="C781" s="26"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="A782" s="23"/>
-      <c r="B782" s="23"/>
-      <c r="C782" s="23"/>
+      <c r="A782" s="26"/>
+      <c r="B782" s="26"/>
+      <c r="C782" s="26"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="A783" s="23"/>
-      <c r="B783" s="23"/>
-      <c r="C783" s="23"/>
+      <c r="A783" s="26"/>
+      <c r="B783" s="26"/>
+      <c r="C783" s="26"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="A784" s="23"/>
-      <c r="B784" s="23"/>
-      <c r="C784" s="23"/>
+      <c r="A784" s="26"/>
+      <c r="B784" s="26"/>
+      <c r="C784" s="26"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="A785" s="23"/>
-      <c r="B785" s="23"/>
-      <c r="C785" s="23"/>
+      <c r="A785" s="26"/>
+      <c r="B785" s="26"/>
+      <c r="C785" s="26"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="A786" s="23"/>
-      <c r="B786" s="23"/>
-      <c r="C786" s="23"/>
+      <c r="A786" s="26"/>
+      <c r="B786" s="26"/>
+      <c r="C786" s="26"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="A787" s="23"/>
-      <c r="B787" s="23"/>
-      <c r="C787" s="23"/>
+      <c r="A787" s="26"/>
+      <c r="B787" s="26"/>
+      <c r="C787" s="26"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="A788" s="23"/>
-      <c r="B788" s="23"/>
-      <c r="C788" s="23"/>
+      <c r="A788" s="26"/>
+      <c r="B788" s="26"/>
+      <c r="C788" s="26"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="A789" s="23"/>
-      <c r="B789" s="23"/>
-      <c r="C789" s="23"/>
+      <c r="A789" s="26"/>
+      <c r="B789" s="26"/>
+      <c r="C789" s="26"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="A790" s="23"/>
-      <c r="B790" s="23"/>
-      <c r="C790" s="23"/>
+      <c r="A790" s="26"/>
+      <c r="B790" s="26"/>
+      <c r="C790" s="26"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="A791" s="23"/>
-      <c r="B791" s="23"/>
-      <c r="C791" s="23"/>
+      <c r="A791" s="26"/>
+      <c r="B791" s="26"/>
+      <c r="C791" s="26"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="A792" s="23"/>
-      <c r="B792" s="23"/>
-      <c r="C792" s="23"/>
+      <c r="A792" s="26"/>
+      <c r="B792" s="26"/>
+      <c r="C792" s="26"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="A793" s="23"/>
-      <c r="B793" s="23"/>
-      <c r="C793" s="23"/>
+      <c r="A793" s="26"/>
+      <c r="B793" s="26"/>
+      <c r="C793" s="26"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="A794" s="23"/>
-      <c r="B794" s="23"/>
-      <c r="C794" s="23"/>
+      <c r="A794" s="26"/>
+      <c r="B794" s="26"/>
+      <c r="C794" s="26"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="A795" s="23"/>
-      <c r="B795" s="23"/>
-      <c r="C795" s="23"/>
+      <c r="A795" s="26"/>
+      <c r="B795" s="26"/>
+      <c r="C795" s="26"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="A796" s="23"/>
-      <c r="B796" s="23"/>
-      <c r="C796" s="23"/>
+      <c r="A796" s="26"/>
+      <c r="B796" s="26"/>
+      <c r="C796" s="26"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="A797" s="23"/>
-      <c r="B797" s="23"/>
-      <c r="C797" s="23"/>
+      <c r="A797" s="26"/>
+      <c r="B797" s="26"/>
+      <c r="C797" s="26"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="A798" s="23"/>
-      <c r="B798" s="23"/>
-      <c r="C798" s="23"/>
+      <c r="A798" s="26"/>
+      <c r="B798" s="26"/>
+      <c r="C798" s="26"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="A799" s="23"/>
-      <c r="B799" s="23"/>
-      <c r="C799" s="23"/>
+      <c r="A799" s="26"/>
+      <c r="B799" s="26"/>
+      <c r="C799" s="26"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="A800" s="23"/>
-      <c r="B800" s="23"/>
-      <c r="C800" s="23"/>
+      <c r="A800" s="26"/>
+      <c r="B800" s="26"/>
+      <c r="C800" s="26"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="A801" s="23"/>
-      <c r="B801" s="23"/>
-      <c r="C801" s="23"/>
+      <c r="A801" s="26"/>
+      <c r="B801" s="26"/>
+      <c r="C801" s="26"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="A802" s="23"/>
-      <c r="B802" s="23"/>
-      <c r="C802" s="23"/>
+      <c r="A802" s="26"/>
+      <c r="B802" s="26"/>
+      <c r="C802" s="26"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="A803" s="23"/>
-      <c r="B803" s="23"/>
-      <c r="C803" s="23"/>
+      <c r="A803" s="26"/>
+      <c r="B803" s="26"/>
+      <c r="C803" s="26"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="A804" s="23"/>
-      <c r="B804" s="23"/>
-      <c r="C804" s="23"/>
+      <c r="A804" s="26"/>
+      <c r="B804" s="26"/>
+      <c r="C804" s="26"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="A805" s="23"/>
-      <c r="B805" s="23"/>
-      <c r="C805" s="23"/>
+      <c r="A805" s="26"/>
+      <c r="B805" s="26"/>
+      <c r="C805" s="26"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="A806" s="23"/>
-      <c r="B806" s="23"/>
-      <c r="C806" s="23"/>
+      <c r="A806" s="26"/>
+      <c r="B806" s="26"/>
+      <c r="C806" s="26"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="A807" s="23"/>
-      <c r="B807" s="23"/>
-      <c r="C807" s="23"/>
+      <c r="A807" s="26"/>
+      <c r="B807" s="26"/>
+      <c r="C807" s="26"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="A808" s="23"/>
-      <c r="B808" s="23"/>
-      <c r="C808" s="23"/>
+      <c r="A808" s="26"/>
+      <c r="B808" s="26"/>
+      <c r="C808" s="26"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="A809" s="23"/>
-      <c r="B809" s="23"/>
-      <c r="C809" s="23"/>
+      <c r="A809" s="26"/>
+      <c r="B809" s="26"/>
+      <c r="C809" s="26"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="A810" s="23"/>
-      <c r="B810" s="23"/>
-      <c r="C810" s="23"/>
+      <c r="A810" s="26"/>
+      <c r="B810" s="26"/>
+      <c r="C810" s="26"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="A811" s="23"/>
-      <c r="B811" s="23"/>
-      <c r="C811" s="23"/>
+      <c r="A811" s="26"/>
+      <c r="B811" s="26"/>
+      <c r="C811" s="26"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="A812" s="23"/>
-      <c r="B812" s="23"/>
-      <c r="C812" s="23"/>
+      <c r="A812" s="26"/>
+      <c r="B812" s="26"/>
+      <c r="C812" s="26"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="A813" s="23"/>
-      <c r="B813" s="23"/>
-      <c r="C813" s="23"/>
+      <c r="A813" s="26"/>
+      <c r="B813" s="26"/>
+      <c r="C813" s="26"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="A814" s="23"/>
-      <c r="B814" s="23"/>
-      <c r="C814" s="23"/>
+      <c r="A814" s="26"/>
+      <c r="B814" s="26"/>
+      <c r="C814" s="26"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="A815" s="23"/>
-      <c r="B815" s="23"/>
-      <c r="C815" s="23"/>
+      <c r="A815" s="26"/>
+      <c r="B815" s="26"/>
+      <c r="C815" s="26"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="A816" s="23"/>
-      <c r="B816" s="23"/>
-      <c r="C816" s="23"/>
+      <c r="A816" s="26"/>
+      <c r="B816" s="26"/>
+      <c r="C816" s="26"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="A817" s="23"/>
-      <c r="B817" s="23"/>
-      <c r="C817" s="23"/>
+      <c r="A817" s="26"/>
+      <c r="B817" s="26"/>
+      <c r="C817" s="26"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="A818" s="23"/>
-      <c r="B818" s="23"/>
-      <c r="C818" s="23"/>
+      <c r="A818" s="26"/>
+      <c r="B818" s="26"/>
+      <c r="C818" s="26"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="A819" s="23"/>
-      <c r="B819" s="23"/>
-      <c r="C819" s="23"/>
+      <c r="A819" s="26"/>
+      <c r="B819" s="26"/>
+      <c r="C819" s="26"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="A820" s="23"/>
-      <c r="B820" s="23"/>
-      <c r="C820" s="23"/>
+      <c r="A820" s="26"/>
+      <c r="B820" s="26"/>
+      <c r="C820" s="26"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="A821" s="23"/>
-      <c r="B821" s="23"/>
-      <c r="C821" s="23"/>
+      <c r="A821" s="26"/>
+      <c r="B821" s="26"/>
+      <c r="C821" s="26"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="A822" s="23"/>
-      <c r="B822" s="23"/>
-      <c r="C822" s="23"/>
+      <c r="A822" s="26"/>
+      <c r="B822" s="26"/>
+      <c r="C822" s="26"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="A823" s="23"/>
-      <c r="B823" s="23"/>
-      <c r="C823" s="23"/>
+      <c r="A823" s="26"/>
+      <c r="B823" s="26"/>
+      <c r="C823" s="26"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="A824" s="23"/>
-      <c r="B824" s="23"/>
-      <c r="C824" s="23"/>
+      <c r="A824" s="26"/>
+      <c r="B824" s="26"/>
+      <c r="C824" s="26"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="A825" s="23"/>
-      <c r="B825" s="23"/>
-      <c r="C825" s="23"/>
+      <c r="A825" s="26"/>
+      <c r="B825" s="26"/>
+      <c r="C825" s="26"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="A826" s="23"/>
-      <c r="B826" s="23"/>
-      <c r="C826" s="23"/>
+      <c r="A826" s="26"/>
+      <c r="B826" s="26"/>
+      <c r="C826" s="26"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="A827" s="23"/>
-      <c r="B827" s="23"/>
-      <c r="C827" s="23"/>
+      <c r="A827" s="26"/>
+      <c r="B827" s="26"/>
+      <c r="C827" s="26"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="A828" s="23"/>
-      <c r="B828" s="23"/>
-      <c r="C828" s="23"/>
+      <c r="A828" s="26"/>
+      <c r="B828" s="26"/>
+      <c r="C828" s="26"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="A829" s="23"/>
-      <c r="B829" s="23"/>
-      <c r="C829" s="23"/>
+      <c r="A829" s="26"/>
+      <c r="B829" s="26"/>
+      <c r="C829" s="26"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="A830" s="23"/>
-      <c r="B830" s="23"/>
-      <c r="C830" s="23"/>
+      <c r="A830" s="26"/>
+      <c r="B830" s="26"/>
+      <c r="C830" s="26"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="A831" s="23"/>
-      <c r="B831" s="23"/>
-      <c r="C831" s="23"/>
+      <c r="A831" s="26"/>
+      <c r="B831" s="26"/>
+      <c r="C831" s="26"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="A832" s="23"/>
-      <c r="B832" s="23"/>
-      <c r="C832" s="23"/>
+      <c r="A832" s="26"/>
+      <c r="B832" s="26"/>
+      <c r="C832" s="26"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="A833" s="23"/>
-      <c r="B833" s="23"/>
-      <c r="C833" s="23"/>
+      <c r="A833" s="26"/>
+      <c r="B833" s="26"/>
+      <c r="C833" s="26"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="A834" s="23"/>
-      <c r="B834" s="23"/>
-      <c r="C834" s="23"/>
+      <c r="A834" s="26"/>
+      <c r="B834" s="26"/>
+      <c r="C834" s="26"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="A835" s="23"/>
-      <c r="B835" s="23"/>
-      <c r="C835" s="23"/>
+      <c r="A835" s="26"/>
+      <c r="B835" s="26"/>
+      <c r="C835" s="26"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="A836" s="23"/>
-      <c r="B836" s="23"/>
-      <c r="C836" s="23"/>
+      <c r="A836" s="26"/>
+      <c r="B836" s="26"/>
+      <c r="C836" s="26"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="A837" s="23"/>
-      <c r="B837" s="23"/>
-      <c r="C837" s="23"/>
+      <c r="A837" s="26"/>
+      <c r="B837" s="26"/>
+      <c r="C837" s="26"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="A838" s="23"/>
-      <c r="B838" s="23"/>
-      <c r="C838" s="23"/>
+      <c r="A838" s="26"/>
+      <c r="B838" s="26"/>
+      <c r="C838" s="26"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="A839" s="23"/>
-      <c r="B839" s="23"/>
-      <c r="C839" s="23"/>
+      <c r="A839" s="26"/>
+      <c r="B839" s="26"/>
+      <c r="C839" s="26"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="A840" s="23"/>
-      <c r="B840" s="23"/>
-      <c r="C840" s="23"/>
+      <c r="A840" s="26"/>
+      <c r="B840" s="26"/>
+      <c r="C840" s="26"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="A841" s="23"/>
-      <c r="B841" s="23"/>
-      <c r="C841" s="23"/>
+      <c r="A841" s="26"/>
+      <c r="B841" s="26"/>
+      <c r="C841" s="26"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="A842" s="23"/>
-      <c r="B842" s="23"/>
-      <c r="C842" s="23"/>
+      <c r="A842" s="26"/>
+      <c r="B842" s="26"/>
+      <c r="C842" s="26"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="A843" s="23"/>
-      <c r="B843" s="23"/>
-      <c r="C843" s="23"/>
+      <c r="A843" s="26"/>
+      <c r="B843" s="26"/>
+      <c r="C843" s="26"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="A844" s="23"/>
-      <c r="B844" s="23"/>
-      <c r="C844" s="23"/>
+      <c r="A844" s="26"/>
+      <c r="B844" s="26"/>
+      <c r="C844" s="26"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="A845" s="23"/>
-      <c r="B845" s="23"/>
-      <c r="C845" s="23"/>
+      <c r="A845" s="26"/>
+      <c r="B845" s="26"/>
+      <c r="C845" s="26"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="A846" s="23"/>
-      <c r="B846" s="23"/>
-      <c r="C846" s="23"/>
+      <c r="A846" s="26"/>
+      <c r="B846" s="26"/>
+      <c r="C846" s="26"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="A847" s="23"/>
-      <c r="B847" s="23"/>
-      <c r="C847" s="23"/>
+      <c r="A847" s="26"/>
+      <c r="B847" s="26"/>
+      <c r="C847" s="26"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="A848" s="23"/>
-      <c r="B848" s="23"/>
-      <c r="C848" s="23"/>
+      <c r="A848" s="26"/>
+      <c r="B848" s="26"/>
+      <c r="C848" s="26"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="A849" s="23"/>
-      <c r="B849" s="23"/>
-      <c r="C849" s="23"/>
+      <c r="A849" s="26"/>
+      <c r="B849" s="26"/>
+      <c r="C849" s="26"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="A850" s="23"/>
-      <c r="B850" s="23"/>
-      <c r="C850" s="23"/>
+      <c r="A850" s="26"/>
+      <c r="B850" s="26"/>
+      <c r="C850" s="26"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="A851" s="23"/>
-      <c r="B851" s="23"/>
-      <c r="C851" s="23"/>
+      <c r="A851" s="26"/>
+      <c r="B851" s="26"/>
+      <c r="C851" s="26"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="A852" s="23"/>
-      <c r="B852" s="23"/>
-      <c r="C852" s="23"/>
+      <c r="A852" s="26"/>
+      <c r="B852" s="26"/>
+      <c r="C852" s="26"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="A853" s="23"/>
-      <c r="B853" s="23"/>
-      <c r="C853" s="23"/>
+      <c r="A853" s="26"/>
+      <c r="B853" s="26"/>
+      <c r="C853" s="26"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="A854" s="23"/>
-      <c r="B854" s="23"/>
-      <c r="C854" s="23"/>
+      <c r="A854" s="26"/>
+      <c r="B854" s="26"/>
+      <c r="C854" s="26"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="A855" s="23"/>
-      <c r="B855" s="23"/>
-      <c r="C855" s="23"/>
+      <c r="A855" s="26"/>
+      <c r="B855" s="26"/>
+      <c r="C855" s="26"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="A856" s="23"/>
-      <c r="B856" s="23"/>
-      <c r="C856" s="23"/>
+      <c r="A856" s="26"/>
+      <c r="B856" s="26"/>
+      <c r="C856" s="26"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="A857" s="23"/>
-      <c r="B857" s="23"/>
-      <c r="C857" s="23"/>
+      <c r="A857" s="26"/>
+      <c r="B857" s="26"/>
+      <c r="C857" s="26"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="A858" s="23"/>
-      <c r="B858" s="23"/>
-      <c r="C858" s="23"/>
+      <c r="A858" s="26"/>
+      <c r="B858" s="26"/>
+      <c r="C858" s="26"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="A859" s="23"/>
-      <c r="B859" s="23"/>
-      <c r="C859" s="23"/>
+      <c r="A859" s="26"/>
+      <c r="B859" s="26"/>
+      <c r="C859" s="26"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="A860" s="23"/>
-      <c r="B860" s="23"/>
-      <c r="C860" s="23"/>
+      <c r="A860" s="26"/>
+      <c r="B860" s="26"/>
+      <c r="C860" s="26"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="A861" s="23"/>
-      <c r="B861" s="23"/>
-      <c r="C861" s="23"/>
+      <c r="A861" s="26"/>
+      <c r="B861" s="26"/>
+      <c r="C861" s="26"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="A862" s="23"/>
-      <c r="B862" s="23"/>
-      <c r="C862" s="23"/>
+      <c r="A862" s="26"/>
+      <c r="B862" s="26"/>
+      <c r="C862" s="26"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="A863" s="23"/>
-      <c r="B863" s="23"/>
-      <c r="C863" s="23"/>
+      <c r="A863" s="26"/>
+      <c r="B863" s="26"/>
+      <c r="C863" s="26"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="A864" s="23"/>
-      <c r="B864" s="23"/>
-      <c r="C864" s="23"/>
+      <c r="A864" s="26"/>
+      <c r="B864" s="26"/>
+      <c r="C864" s="26"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="A865" s="23"/>
-      <c r="B865" s="23"/>
-      <c r="C865" s="23"/>
+      <c r="A865" s="26"/>
+      <c r="B865" s="26"/>
+      <c r="C865" s="26"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="A866" s="23"/>
-      <c r="B866" s="23"/>
-      <c r="C866" s="23"/>
+      <c r="A866" s="26"/>
+      <c r="B866" s="26"/>
+      <c r="C866" s="26"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="A867" s="23"/>
-      <c r="B867" s="23"/>
-      <c r="C867" s="23"/>
+      <c r="A867" s="26"/>
+      <c r="B867" s="26"/>
+      <c r="C867" s="26"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="A868" s="23"/>
-      <c r="B868" s="23"/>
-      <c r="C868" s="23"/>
+      <c r="A868" s="26"/>
+      <c r="B868" s="26"/>
+      <c r="C868" s="26"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="A869" s="23"/>
-      <c r="B869" s="23"/>
-      <c r="C869" s="23"/>
+      <c r="A869" s="26"/>
+      <c r="B869" s="26"/>
+      <c r="C869" s="26"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="A870" s="23"/>
-      <c r="B870" s="23"/>
-      <c r="C870" s="23"/>
+      <c r="A870" s="26"/>
+      <c r="B870" s="26"/>
+      <c r="C870" s="26"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="23"/>
-      <c r="B871" s="23"/>
-      <c r="C871" s="23"/>
+      <c r="A871" s="26"/>
+      <c r="B871" s="26"/>
+      <c r="C871" s="26"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="A872" s="23"/>
-      <c r="B872" s="23"/>
-      <c r="C872" s="23"/>
+      <c r="A872" s="26"/>
+      <c r="B872" s="26"/>
+      <c r="C872" s="26"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="A873" s="23"/>
-      <c r="B873" s="23"/>
-      <c r="C873" s="23"/>
+      <c r="A873" s="26"/>
+      <c r="B873" s="26"/>
+      <c r="C873" s="26"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="A874" s="23"/>
-      <c r="B874" s="23"/>
-      <c r="C874" s="23"/>
+      <c r="A874" s="26"/>
+      <c r="B874" s="26"/>
+      <c r="C874" s="26"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="A875" s="23"/>
-      <c r="B875" s="23"/>
-      <c r="C875" s="23"/>
+      <c r="A875" s="26"/>
+      <c r="B875" s="26"/>
+      <c r="C875" s="26"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="23"/>
-      <c r="B876" s="23"/>
-      <c r="C876" s="23"/>
+      <c r="A876" s="26"/>
+      <c r="B876" s="26"/>
+      <c r="C876" s="26"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="A877" s="23"/>
-      <c r="B877" s="23"/>
-      <c r="C877" s="23"/>
+      <c r="A877" s="26"/>
+      <c r="B877" s="26"/>
+      <c r="C877" s="26"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="A878" s="23"/>
-      <c r="B878" s="23"/>
-      <c r="C878" s="23"/>
+      <c r="A878" s="26"/>
+      <c r="B878" s="26"/>
+      <c r="C878" s="26"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="A879" s="23"/>
-      <c r="B879" s="23"/>
-      <c r="C879" s="23"/>
+      <c r="A879" s="26"/>
+      <c r="B879" s="26"/>
+      <c r="C879" s="26"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="A880" s="23"/>
-      <c r="B880" s="23"/>
-      <c r="C880" s="23"/>
+      <c r="A880" s="26"/>
+      <c r="B880" s="26"/>
+      <c r="C880" s="26"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="A881" s="23"/>
-      <c r="B881" s="23"/>
-      <c r="C881" s="23"/>
+      <c r="A881" s="26"/>
+      <c r="B881" s="26"/>
+      <c r="C881" s="26"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="A882" s="23"/>
-      <c r="B882" s="23"/>
-      <c r="C882" s="23"/>
+      <c r="A882" s="26"/>
+      <c r="B882" s="26"/>
+      <c r="C882" s="26"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="A883" s="23"/>
-      <c r="B883" s="23"/>
-      <c r="C883" s="23"/>
+      <c r="A883" s="26"/>
+      <c r="B883" s="26"/>
+      <c r="C883" s="26"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="A884" s="23"/>
-      <c r="B884" s="23"/>
-      <c r="C884" s="23"/>
+      <c r="A884" s="26"/>
+      <c r="B884" s="26"/>
+      <c r="C884" s="26"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="A885" s="23"/>
-      <c r="B885" s="23"/>
-      <c r="C885" s="23"/>
+      <c r="A885" s="26"/>
+      <c r="B885" s="26"/>
+      <c r="C885" s="26"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="A886" s="23"/>
-      <c r="B886" s="23"/>
-      <c r="C886" s="23"/>
+      <c r="A886" s="26"/>
+      <c r="B886" s="26"/>
+      <c r="C886" s="26"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="A887" s="23"/>
-      <c r="B887" s="23"/>
-      <c r="C887" s="23"/>
+      <c r="A887" s="26"/>
+      <c r="B887" s="26"/>
+      <c r="C887" s="26"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="A888" s="23"/>
-      <c r="B888" s="23"/>
-      <c r="C888" s="23"/>
+      <c r="A888" s="26"/>
+      <c r="B888" s="26"/>
+      <c r="C888" s="26"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="A889" s="23"/>
-      <c r="B889" s="23"/>
-      <c r="C889" s="23"/>
+      <c r="A889" s="26"/>
+      <c r="B889" s="26"/>
+      <c r="C889" s="26"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="A890" s="23"/>
-      <c r="B890" s="23"/>
-      <c r="C890" s="23"/>
+      <c r="A890" s="26"/>
+      <c r="B890" s="26"/>
+      <c r="C890" s="26"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="A891" s="23"/>
-      <c r="B891" s="23"/>
-      <c r="C891" s="23"/>
+      <c r="A891" s="26"/>
+      <c r="B891" s="26"/>
+      <c r="C891" s="26"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="A892" s="23"/>
-      <c r="B892" s="23"/>
-      <c r="C892" s="23"/>
+      <c r="A892" s="26"/>
+      <c r="B892" s="26"/>
+      <c r="C892" s="26"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="A893" s="23"/>
-      <c r="B893" s="23"/>
-      <c r="C893" s="23"/>
+      <c r="A893" s="26"/>
+      <c r="B893" s="26"/>
+      <c r="C893" s="26"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="A894" s="23"/>
-      <c r="B894" s="23"/>
-      <c r="C894" s="23"/>
+      <c r="A894" s="26"/>
+      <c r="B894" s="26"/>
+      <c r="C894" s="26"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="A895" s="23"/>
-      <c r="B895" s="23"/>
-      <c r="C895" s="23"/>
+      <c r="A895" s="26"/>
+      <c r="B895" s="26"/>
+      <c r="C895" s="26"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="A896" s="23"/>
-      <c r="B896" s="23"/>
-      <c r="C896" s="23"/>
+      <c r="A896" s="26"/>
+      <c r="B896" s="26"/>
+      <c r="C896" s="26"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="A897" s="23"/>
-      <c r="B897" s="23"/>
-      <c r="C897" s="23"/>
+      <c r="A897" s="26"/>
+      <c r="B897" s="26"/>
+      <c r="C897" s="26"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="A898" s="23"/>
-      <c r="B898" s="23"/>
-      <c r="C898" s="23"/>
+      <c r="A898" s="26"/>
+      <c r="B898" s="26"/>
+      <c r="C898" s="26"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="A899" s="23"/>
-      <c r="B899" s="23"/>
-      <c r="C899" s="23"/>
+      <c r="A899" s="26"/>
+      <c r="B899" s="26"/>
+      <c r="C899" s="26"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="A900" s="23"/>
-      <c r="B900" s="23"/>
-      <c r="C900" s="23"/>
+      <c r="A900" s="26"/>
+      <c r="B900" s="26"/>
+      <c r="C900" s="26"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="A901" s="23"/>
-      <c r="B901" s="23"/>
-      <c r="C901" s="23"/>
+      <c r="A901" s="26"/>
+      <c r="B901" s="26"/>
+      <c r="C901" s="26"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="A902" s="23"/>
-      <c r="B902" s="23"/>
-      <c r="C902" s="23"/>
+      <c r="A902" s="26"/>
+      <c r="B902" s="26"/>
+      <c r="C902" s="26"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="A903" s="23"/>
-      <c r="B903" s="23"/>
-      <c r="C903" s="23"/>
+      <c r="A903" s="26"/>
+      <c r="B903" s="26"/>
+      <c r="C903" s="26"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="A904" s="23"/>
-      <c r="B904" s="23"/>
-      <c r="C904" s="23"/>
+      <c r="A904" s="26"/>
+      <c r="B904" s="26"/>
+      <c r="C904" s="26"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="A905" s="23"/>
-      <c r="B905" s="23"/>
-      <c r="C905" s="23"/>
+      <c r="A905" s="26"/>
+      <c r="B905" s="26"/>
+      <c r="C905" s="26"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="A906" s="23"/>
-      <c r="B906" s="23"/>
-      <c r="C906" s="23"/>
+      <c r="A906" s="26"/>
+      <c r="B906" s="26"/>
+      <c r="C906" s="26"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="A907" s="23"/>
-      <c r="B907" s="23"/>
-      <c r="C907" s="23"/>
+      <c r="A907" s="26"/>
+      <c r="B907" s="26"/>
+      <c r="C907" s="26"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="A908" s="23"/>
-      <c r="B908" s="23"/>
-      <c r="C908" s="23"/>
+      <c r="A908" s="26"/>
+      <c r="B908" s="26"/>
+      <c r="C908" s="26"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="A909" s="23"/>
-      <c r="B909" s="23"/>
-      <c r="C909" s="23"/>
+      <c r="A909" s="26"/>
+      <c r="B909" s="26"/>
+      <c r="C909" s="26"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="A910" s="23"/>
-      <c r="B910" s="23"/>
-      <c r="C910" s="23"/>
+      <c r="A910" s="26"/>
+      <c r="B910" s="26"/>
+      <c r="C910" s="26"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="A911" s="23"/>
-      <c r="B911" s="23"/>
-      <c r="C911" s="23"/>
+      <c r="A911" s="26"/>
+      <c r="B911" s="26"/>
+      <c r="C911" s="26"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="A912" s="23"/>
-      <c r="B912" s="23"/>
-      <c r="C912" s="23"/>
+      <c r="A912" s="26"/>
+      <c r="B912" s="26"/>
+      <c r="C912" s="26"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="A913" s="23"/>
-      <c r="B913" s="23"/>
-      <c r="C913" s="23"/>
+      <c r="A913" s="26"/>
+      <c r="B913" s="26"/>
+      <c r="C913" s="26"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="A914" s="23"/>
-      <c r="B914" s="23"/>
-      <c r="C914" s="23"/>
+      <c r="A914" s="26"/>
+      <c r="B914" s="26"/>
+      <c r="C914" s="26"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="A915" s="23"/>
-      <c r="B915" s="23"/>
-      <c r="C915" s="23"/>
+      <c r="A915" s="26"/>
+      <c r="B915" s="26"/>
+      <c r="C915" s="26"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="A916" s="23"/>
-      <c r="B916" s="23"/>
-      <c r="C916" s="23"/>
+      <c r="A916" s="26"/>
+      <c r="B916" s="26"/>
+      <c r="C916" s="26"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="A917" s="23"/>
-      <c r="B917" s="23"/>
-      <c r="C917" s="23"/>
+      <c r="A917" s="26"/>
+      <c r="B917" s="26"/>
+      <c r="C917" s="26"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="A918" s="23"/>
-      <c r="B918" s="23"/>
-      <c r="C918" s="23"/>
+      <c r="A918" s="26"/>
+      <c r="B918" s="26"/>
+      <c r="C918" s="26"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="A919" s="23"/>
-      <c r="B919" s="23"/>
-      <c r="C919" s="23"/>
+      <c r="A919" s="26"/>
+      <c r="B919" s="26"/>
+      <c r="C919" s="26"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="A920" s="23"/>
-      <c r="B920" s="23"/>
-      <c r="C920" s="23"/>
+      <c r="A920" s="26"/>
+      <c r="B920" s="26"/>
+      <c r="C920" s="26"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="A921" s="23"/>
-      <c r="B921" s="23"/>
-      <c r="C921" s="23"/>
+      <c r="A921" s="26"/>
+      <c r="B921" s="26"/>
+      <c r="C921" s="26"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="A922" s="23"/>
-      <c r="B922" s="23"/>
-      <c r="C922" s="23"/>
+      <c r="A922" s="26"/>
+      <c r="B922" s="26"/>
+      <c r="C922" s="26"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="A923" s="23"/>
-      <c r="B923" s="23"/>
-      <c r="C923" s="23"/>
+      <c r="A923" s="26"/>
+      <c r="B923" s="26"/>
+      <c r="C923" s="26"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="A924" s="23"/>
-      <c r="B924" s="23"/>
-      <c r="C924" s="23"/>
+      <c r="A924" s="26"/>
+      <c r="B924" s="26"/>
+      <c r="C924" s="26"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="A925" s="23"/>
-      <c r="B925" s="23"/>
-      <c r="C925" s="23"/>
+      <c r="A925" s="26"/>
+      <c r="B925" s="26"/>
+      <c r="C925" s="26"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="A926" s="23"/>
-      <c r="B926" s="23"/>
-      <c r="C926" s="23"/>
+      <c r="A926" s="26"/>
+      <c r="B926" s="26"/>
+      <c r="C926" s="26"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="A927" s="23"/>
-      <c r="B927" s="23"/>
-      <c r="C927" s="23"/>
+      <c r="A927" s="26"/>
+      <c r="B927" s="26"/>
+      <c r="C927" s="26"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="A928" s="23"/>
-      <c r="B928" s="23"/>
-      <c r="C928" s="23"/>
+      <c r="A928" s="26"/>
+      <c r="B928" s="26"/>
+      <c r="C928" s="26"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="A929" s="23"/>
-      <c r="B929" s="23"/>
-      <c r="C929" s="23"/>
+      <c r="A929" s="26"/>
+      <c r="B929" s="26"/>
+      <c r="C929" s="26"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="A930" s="23"/>
-      <c r="B930" s="23"/>
-      <c r="C930" s="23"/>
+      <c r="A930" s="26"/>
+      <c r="B930" s="26"/>
+      <c r="C930" s="26"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="A931" s="23"/>
-      <c r="B931" s="23"/>
-      <c r="C931" s="23"/>
+      <c r="A931" s="26"/>
+      <c r="B931" s="26"/>
+      <c r="C931" s="26"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="A932" s="23"/>
-      <c r="B932" s="23"/>
-      <c r="C932" s="23"/>
+      <c r="A932" s="26"/>
+      <c r="B932" s="26"/>
+      <c r="C932" s="26"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="A933" s="23"/>
-      <c r="B933" s="23"/>
-      <c r="C933" s="23"/>
+      <c r="A933" s="26"/>
+      <c r="B933" s="26"/>
+      <c r="C933" s="26"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="A934" s="23"/>
-      <c r="B934" s="23"/>
-      <c r="C934" s="23"/>
+      <c r="A934" s="26"/>
+      <c r="B934" s="26"/>
+      <c r="C934" s="26"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="A935" s="23"/>
-      <c r="B935" s="23"/>
-      <c r="C935" s="23"/>
+      <c r="A935" s="26"/>
+      <c r="B935" s="26"/>
+      <c r="C935" s="26"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="A936" s="23"/>
-      <c r="B936" s="23"/>
-      <c r="C936" s="23"/>
+      <c r="A936" s="26"/>
+      <c r="B936" s="26"/>
+      <c r="C936" s="26"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="A937" s="23"/>
-      <c r="B937" s="23"/>
-      <c r="C937" s="23"/>
+      <c r="A937" s="26"/>
+      <c r="B937" s="26"/>
+      <c r="C937" s="26"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="A938" s="23"/>
-      <c r="B938" s="23"/>
-      <c r="C938" s="23"/>
+      <c r="A938" s="26"/>
+      <c r="B938" s="26"/>
+      <c r="C938" s="26"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="A939" s="23"/>
-      <c r="B939" s="23"/>
-      <c r="C939" s="23"/>
+      <c r="A939" s="26"/>
+      <c r="B939" s="26"/>
+      <c r="C939" s="26"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="A940" s="23"/>
-      <c r="B940" s="23"/>
-      <c r="C940" s="23"/>
+      <c r="A940" s="26"/>
+      <c r="B940" s="26"/>
+      <c r="C940" s="26"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="A941" s="23"/>
-      <c r="B941" s="23"/>
-      <c r="C941" s="23"/>
+      <c r="A941" s="26"/>
+      <c r="B941" s="26"/>
+      <c r="C941" s="26"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="A942" s="23"/>
-      <c r="B942" s="23"/>
-      <c r="C942" s="23"/>
+      <c r="A942" s="26"/>
+      <c r="B942" s="26"/>
+      <c r="C942" s="26"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="A943" s="23"/>
-      <c r="B943" s="23"/>
-      <c r="C943" s="23"/>
+      <c r="A943" s="26"/>
+      <c r="B943" s="26"/>
+      <c r="C943" s="26"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="A944" s="23"/>
-      <c r="B944" s="23"/>
-      <c r="C944" s="23"/>
+      <c r="A944" s="26"/>
+      <c r="B944" s="26"/>
+      <c r="C944" s="26"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="A945" s="23"/>
-      <c r="B945" s="23"/>
-      <c r="C945" s="23"/>
+      <c r="A945" s="26"/>
+      <c r="B945" s="26"/>
+      <c r="C945" s="26"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="A946" s="23"/>
-      <c r="B946" s="23"/>
-      <c r="C946" s="23"/>
+      <c r="A946" s="26"/>
+      <c r="B946" s="26"/>
+      <c r="C946" s="26"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="A947" s="23"/>
-      <c r="B947" s="23"/>
-      <c r="C947" s="23"/>
+      <c r="A947" s="26"/>
+      <c r="B947" s="26"/>
+      <c r="C947" s="26"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="A948" s="23"/>
-      <c r="B948" s="23"/>
-      <c r="C948" s="23"/>
+      <c r="A948" s="26"/>
+      <c r="B948" s="26"/>
+      <c r="C948" s="26"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="A949" s="23"/>
-      <c r="B949" s="23"/>
-      <c r="C949" s="23"/>
+      <c r="A949" s="26"/>
+      <c r="B949" s="26"/>
+      <c r="C949" s="26"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="A950" s="23"/>
-      <c r="B950" s="23"/>
-      <c r="C950" s="23"/>
+      <c r="A950" s="26"/>
+      <c r="B950" s="26"/>
+      <c r="C950" s="26"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="A951" s="23"/>
-      <c r="B951" s="23"/>
-      <c r="C951" s="23"/>
+      <c r="A951" s="26"/>
+      <c r="B951" s="26"/>
+      <c r="C951" s="26"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="A952" s="23"/>
-      <c r="B952" s="23"/>
-      <c r="C952" s="23"/>
+      <c r="A952" s="26"/>
+      <c r="B952" s="26"/>
+      <c r="C952" s="26"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="A953" s="23"/>
-      <c r="B953" s="23"/>
-      <c r="C953" s="23"/>
+      <c r="A953" s="26"/>
+      <c r="B953" s="26"/>
+      <c r="C953" s="26"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="A954" s="23"/>
-      <c r="B954" s="23"/>
-      <c r="C954" s="23"/>
+      <c r="A954" s="26"/>
+      <c r="B954" s="26"/>
+      <c r="C954" s="26"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="A955" s="23"/>
-      <c r="B955" s="23"/>
-      <c r="C955" s="23"/>
+      <c r="A955" s="26"/>
+      <c r="B955" s="26"/>
+      <c r="C955" s="26"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="A956" s="23"/>
-      <c r="B956" s="23"/>
-      <c r="C956" s="23"/>
+      <c r="A956" s="26"/>
+      <c r="B956" s="26"/>
+      <c r="C956" s="26"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="A957" s="23"/>
-      <c r="B957" s="23"/>
-      <c r="C957" s="23"/>
+      <c r="A957" s="26"/>
+      <c r="B957" s="26"/>
+      <c r="C957" s="26"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="A958" s="23"/>
-      <c r="B958" s="23"/>
-      <c r="C958" s="23"/>
+      <c r="A958" s="26"/>
+      <c r="B958" s="26"/>
+      <c r="C958" s="26"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="A959" s="23"/>
-      <c r="B959" s="23"/>
-      <c r="C959" s="23"/>
+      <c r="A959" s="26"/>
+      <c r="B959" s="26"/>
+      <c r="C959" s="26"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="A960" s="23"/>
-      <c r="B960" s="23"/>
-      <c r="C960" s="23"/>
+      <c r="A960" s="26"/>
+      <c r="B960" s="26"/>
+      <c r="C960" s="26"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="A961" s="23"/>
-      <c r="B961" s="23"/>
-      <c r="C961" s="23"/>
+      <c r="A961" s="26"/>
+      <c r="B961" s="26"/>
+      <c r="C961" s="26"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="A962" s="23"/>
-      <c r="B962" s="23"/>
-      <c r="C962" s="23"/>
+      <c r="A962" s="26"/>
+      <c r="B962" s="26"/>
+      <c r="C962" s="26"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="A963" s="23"/>
-      <c r="B963" s="23"/>
-      <c r="C963" s="23"/>
+      <c r="A963" s="26"/>
+      <c r="B963" s="26"/>
+      <c r="C963" s="26"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="A964" s="23"/>
-      <c r="B964" s="23"/>
-      <c r="C964" s="23"/>
+      <c r="A964" s="26"/>
+      <c r="B964" s="26"/>
+      <c r="C964" s="26"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="A965" s="23"/>
-      <c r="B965" s="23"/>
-      <c r="C965" s="23"/>
+      <c r="A965" s="26"/>
+      <c r="B965" s="26"/>
+      <c r="C965" s="26"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="A966" s="23"/>
-      <c r="B966" s="23"/>
-      <c r="C966" s="23"/>
+      <c r="A966" s="26"/>
+      <c r="B966" s="26"/>
+      <c r="C966" s="26"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="A967" s="23"/>
-      <c r="B967" s="23"/>
-      <c r="C967" s="23"/>
+      <c r="A967" s="26"/>
+      <c r="B967" s="26"/>
+      <c r="C967" s="26"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="A968" s="23"/>
-      <c r="B968" s="23"/>
-      <c r="C968" s="23"/>
+      <c r="A968" s="26"/>
+      <c r="B968" s="26"/>
+      <c r="C968" s="26"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="A969" s="23"/>
-      <c r="B969" s="23"/>
-      <c r="C969" s="23"/>
+      <c r="A969" s="26"/>
+      <c r="B969" s="26"/>
+      <c r="C969" s="26"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="A970" s="23"/>
-      <c r="B970" s="23"/>
-      <c r="C970" s="23"/>
+      <c r="A970" s="26"/>
+      <c r="B970" s="26"/>
+      <c r="C970" s="26"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="A971" s="23"/>
-      <c r="B971" s="23"/>
-      <c r="C971" s="23"/>
+      <c r="A971" s="26"/>
+      <c r="B971" s="26"/>
+      <c r="C971" s="26"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="A972" s="23"/>
-      <c r="B972" s="23"/>
-      <c r="C972" s="23"/>
+      <c r="A972" s="26"/>
+      <c r="B972" s="26"/>
+      <c r="C972" s="26"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="A973" s="23"/>
-      <c r="B973" s="23"/>
-      <c r="C973" s="23"/>
+      <c r="A973" s="26"/>
+      <c r="B973" s="26"/>
+      <c r="C973" s="26"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="A974" s="23"/>
-      <c r="B974" s="23"/>
-      <c r="C974" s="23"/>
+      <c r="A974" s="26"/>
+      <c r="B974" s="26"/>
+      <c r="C974" s="26"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="A975" s="23"/>
-      <c r="B975" s="23"/>
-      <c r="C975" s="23"/>
+      <c r="A975" s="26"/>
+      <c r="B975" s="26"/>
+      <c r="C975" s="26"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="A976" s="23"/>
-      <c r="B976" s="23"/>
-      <c r="C976" s="23"/>
+      <c r="A976" s="26"/>
+      <c r="B976" s="26"/>
+      <c r="C976" s="26"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="A977" s="23"/>
-      <c r="B977" s="23"/>
-      <c r="C977" s="23"/>
+      <c r="A977" s="26"/>
+      <c r="B977" s="26"/>
+      <c r="C977" s="26"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="A978" s="23"/>
-      <c r="B978" s="23"/>
-      <c r="C978" s="23"/>
+      <c r="A978" s="26"/>
+      <c r="B978" s="26"/>
+      <c r="C978" s="26"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="A979" s="23"/>
-      <c r="B979" s="23"/>
-      <c r="C979" s="23"/>
+      <c r="A979" s="26"/>
+      <c r="B979" s="26"/>
+      <c r="C979" s="26"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="A980" s="23"/>
-      <c r="B980" s="23"/>
-      <c r="C980" s="23"/>
+      <c r="A980" s="26"/>
+      <c r="B980" s="26"/>
+      <c r="C980" s="26"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="A981" s="23"/>
-      <c r="B981" s="23"/>
-      <c r="C981" s="23"/>
+      <c r="A981" s="26"/>
+      <c r="B981" s="26"/>
+      <c r="C981" s="26"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="A982" s="23"/>
-      <c r="B982" s="23"/>
-      <c r="C982" s="23"/>
+      <c r="A982" s="26"/>
+      <c r="B982" s="26"/>
+      <c r="C982" s="26"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="A983" s="23"/>
-      <c r="B983" s="23"/>
-      <c r="C983" s="23"/>
+      <c r="A983" s="26"/>
+      <c r="B983" s="26"/>
+      <c r="C983" s="26"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="A984" s="23"/>
-      <c r="B984" s="23"/>
-      <c r="C984" s="23"/>
+      <c r="A984" s="26"/>
+      <c r="B984" s="26"/>
+      <c r="C984" s="26"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="A985" s="23"/>
-      <c r="B985" s="23"/>
-      <c r="C985" s="23"/>
+      <c r="A985" s="26"/>
+      <c r="B985" s="26"/>
+      <c r="C985" s="26"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="A986" s="23"/>
-      <c r="B986" s="23"/>
-      <c r="C986" s="23"/>
+      <c r="A986" s="26"/>
+      <c r="B986" s="26"/>
+      <c r="C986" s="26"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="A987" s="23"/>
-      <c r="B987" s="23"/>
-      <c r="C987" s="23"/>
+      <c r="A987" s="26"/>
+      <c r="B987" s="26"/>
+      <c r="C987" s="26"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="A988" s="23"/>
-      <c r="B988" s="23"/>
-      <c r="C988" s="23"/>
+      <c r="A988" s="26"/>
+      <c r="B988" s="26"/>
+      <c r="C988" s="26"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="A989" s="23"/>
-      <c r="B989" s="23"/>
-      <c r="C989" s="23"/>
+      <c r="A989" s="26"/>
+      <c r="B989" s="26"/>
+      <c r="C989" s="26"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="A990" s="23"/>
-      <c r="B990" s="23"/>
-      <c r="C990" s="23"/>
+      <c r="A990" s="26"/>
+      <c r="B990" s="26"/>
+      <c r="C990" s="26"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="A991" s="23"/>
-      <c r="B991" s="23"/>
-      <c r="C991" s="23"/>
+      <c r="A991" s="26"/>
+      <c r="B991" s="26"/>
+      <c r="C991" s="26"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="A992" s="23"/>
-      <c r="B992" s="23"/>
-      <c r="C992" s="23"/>
+      <c r="A992" s="26"/>
+      <c r="B992" s="26"/>
+      <c r="C992" s="26"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="A993" s="23"/>
-      <c r="B993" s="23"/>
-      <c r="C993" s="23"/>
+      <c r="A993" s="26"/>
+      <c r="B993" s="26"/>
+      <c r="C993" s="26"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="A994" s="23"/>
-      <c r="B994" s="23"/>
-      <c r="C994" s="23"/>
+      <c r="A994" s="26"/>
+      <c r="B994" s="26"/>
+      <c r="C994" s="26"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="A995" s="23"/>
-      <c r="B995" s="23"/>
-      <c r="C995" s="23"/>
+      <c r="A995" s="26"/>
+      <c r="B995" s="26"/>
+      <c r="C995" s="26"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="23"/>
-      <c r="B996" s="23"/>
-      <c r="C996" s="23"/>
+      <c r="A996" s="26"/>
+      <c r="B996" s="26"/>
+      <c r="C996" s="26"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="23"/>
-      <c r="B997" s="23"/>
-      <c r="C997" s="23"/>
+      <c r="A997" s="26"/>
+      <c r="B997" s="26"/>
+      <c r="C997" s="26"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="23"/>
-      <c r="B998" s="23"/>
-      <c r="C998" s="23"/>
+      <c r="A998" s="26"/>
+      <c r="B998" s="26"/>
+      <c r="C998" s="26"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="23"/>
-      <c r="B999" s="23"/>
-      <c r="C999" s="23"/>
+      <c r="A999" s="26"/>
+      <c r="B999" s="26"/>
+      <c r="C999" s="26"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="23"/>
-      <c r="B1000" s="23"/>
-      <c r="C1000" s="23"/>
+      <c r="A1000" s="26"/>
+      <c r="B1000" s="26"/>
+      <c r="C1000" s="26"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="A1001" s="23"/>
-      <c r="B1001" s="23"/>
-      <c r="C1001" s="23"/>
+      <c r="A1001" s="26"/>
+      <c r="B1001" s="26"/>
+      <c r="C1001" s="26"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6875,84 +6888,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="B1" s="25" t="s">
-        <v>101</v>
+      <c r="B1" s="27" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="26" t="s">
-        <v>102</v>
+      <c r="B3" s="28" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="26" t="s">
-        <v>103</v>
+      <c r="B4" s="28" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="26" t="s">
-        <v>104</v>
+      <c r="B5" s="28" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="26" t="s">
-        <v>105</v>
+      <c r="B6" s="28" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="26" t="s">
-        <v>106</v>
+      <c r="B7" s="28" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="26" t="s">
-        <v>107</v>
+      <c r="B8" s="28" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="26" t="s">
-        <v>108</v>
+      <c r="B9" s="28" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="26" t="s">
-        <v>109</v>
+      <c r="B10" s="28" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="26" t="s">
-        <v>110</v>
+      <c r="B11" s="28" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="26" t="s">
-        <v>111</v>
+      <c r="B12" s="28" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="26" t="s">
-        <v>112</v>
+      <c r="B13" s="28" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="26" t="s">
-        <v>113</v>
+      <c r="B14" s="28" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="26" t="s">
-        <v>114</v>
+      <c r="B15" s="28" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="26" t="s">
-        <v>115</v>
+      <c r="B16" s="28" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="26" t="s">
-        <v>116</v>
+      <c r="B17" s="28" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7965,237 +7978,237 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="27" t="s">
-        <v>117</v>
-      </c>
-      <c r="B2" s="27"/>
-      <c r="C2" s="27"/>
+      <c r="A2" s="29" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="29"/>
+      <c r="C2" s="29"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="23"/>
-      <c r="B3" s="28" t="s">
-        <v>118</v>
-      </c>
-      <c r="C3" s="23"/>
+      <c r="A3" s="26"/>
+      <c r="B3" s="30" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="26"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="23"/>
-      <c r="B4" s="29" t="s">
-        <v>119</v>
-      </c>
-      <c r="C4" s="23"/>
+      <c r="A4" s="26"/>
+      <c r="B4" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="26"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="30" t="s">
-        <v>120</v>
-      </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
+      <c r="A5" s="32" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="32"/>
+      <c r="C5" s="32"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
-      <c r="C6" s="23"/>
+      <c r="A6" s="26"/>
+      <c r="B6" s="26"/>
+      <c r="C6" s="26"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="31" t="s">
-        <v>121</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>122</v>
-      </c>
-      <c r="C7" s="32" t="s">
+      <c r="A7" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="D7" s="31" t="s">
+      <c r="B7" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="E7" s="31" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="31" t="s">
+      <c r="C7" s="34" t="s">
         <v>125</v>
       </c>
-      <c r="G7" s="31" t="s">
+      <c r="D7" s="33" t="s">
         <v>126</v>
       </c>
+      <c r="E7" s="33" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>127</v>
+      </c>
+      <c r="G7" s="33" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="33">
+      <c r="A8" s="35">
         <v>1.0</v>
       </c>
-      <c r="B8" s="34" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>128</v>
-      </c>
-      <c r="D8" s="35" t="s">
+      <c r="B8" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="E8" s="36" t="s">
+      <c r="C8" s="36" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="37"/>
-      <c r="G8" s="38"/>
+      <c r="D8" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="39"/>
+      <c r="G8" s="40"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="39">
+      <c r="A9" s="41">
         <v>2.0</v>
       </c>
-      <c r="B9" s="40" t="s">
-        <v>127</v>
-      </c>
-      <c r="C9" s="40" t="s">
+      <c r="B9" s="42" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="42" t="s">
+        <v>133</v>
+      </c>
+      <c r="D9" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="D9" s="41" t="s">
-        <v>129</v>
-      </c>
-      <c r="E9" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="F9" s="43"/>
-      <c r="G9" s="38"/>
+      <c r="E9" s="44" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="45"/>
+      <c r="G9" s="40"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="44">
+      <c r="A10" s="46">
         <v>3.0</v>
       </c>
-      <c r="B10" s="45" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="45" t="s">
-        <v>134</v>
-      </c>
-      <c r="D10" s="46" t="s">
+      <c r="B10" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="E10" s="47" t="s">
+      <c r="C10" s="47" t="s">
         <v>136</v>
       </c>
-      <c r="F10" s="48"/>
-      <c r="G10" s="49"/>
+      <c r="D10" s="48" t="s">
+        <v>137</v>
+      </c>
+      <c r="E10" s="49" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="50"/>
+      <c r="G10" s="51"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="33"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="34"/>
-      <c r="D11" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" s="36" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="51"/>
+      <c r="A11" s="35"/>
+      <c r="B11" s="36"/>
+      <c r="C11" s="36"/>
+      <c r="D11" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="E11" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="52"/>
+      <c r="G11" s="53"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="52">
+      <c r="A12" s="54">
         <v>4.0</v>
       </c>
-      <c r="B12" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="D12" s="54" t="s">
+      <c r="B12" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="E12" s="55" t="s">
+      <c r="C12" s="55" t="s">
         <v>142</v>
       </c>
-      <c r="F12" s="56"/>
-      <c r="G12" s="57"/>
+      <c r="D12" s="56" t="s">
+        <v>143</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="58"/>
+      <c r="G12" s="59"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="33"/>
-      <c r="B13" s="34"/>
-      <c r="C13" s="34"/>
-      <c r="D13" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="E13" s="36" t="s">
-        <v>144</v>
-      </c>
-      <c r="F13" s="37"/>
-      <c r="G13" s="51"/>
+      <c r="A13" s="35"/>
+      <c r="B13" s="36"/>
+      <c r="C13" s="36"/>
+      <c r="D13" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E13" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="39"/>
+      <c r="G13" s="53"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="52">
+      <c r="A14" s="54">
         <v>5.0</v>
       </c>
-      <c r="B14" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C14" s="53" t="s">
+      <c r="B14" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="55" t="s">
+        <v>147</v>
+      </c>
+      <c r="D14" s="56" t="s">
+        <v>148</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="58"/>
+      <c r="G14" s="59"/>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="35"/>
+      <c r="B15" s="36"/>
+      <c r="C15" s="36"/>
+      <c r="D15" s="37" t="s">
         <v>145</v>
       </c>
-      <c r="D14" s="54" t="s">
-        <v>146</v>
-      </c>
-      <c r="E14" s="55" t="s">
-        <v>147</v>
-      </c>
-      <c r="F14" s="56"/>
-      <c r="G14" s="57"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="33"/>
-      <c r="B15" s="34"/>
-      <c r="C15" s="34"/>
-      <c r="D15" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="E15" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="F15" s="58" t="s">
-        <v>149</v>
-      </c>
-      <c r="G15" s="51"/>
+      <c r="E15" s="38" t="s">
+        <v>150</v>
+      </c>
+      <c r="F15" s="60" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="53"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="52">
+      <c r="A16" s="54">
         <v>6.0</v>
       </c>
-      <c r="B16" s="53" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="53" t="s">
-        <v>140</v>
-      </c>
-      <c r="D16" s="54" t="s">
+      <c r="B16" s="55" t="s">
+        <v>141</v>
+      </c>
+      <c r="C16" s="55" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="56" t="s">
+        <v>152</v>
+      </c>
+      <c r="E16" s="57" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="61"/>
+      <c r="G16" s="59"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="A17" s="35"/>
+      <c r="B17" s="36"/>
+      <c r="C17" s="36"/>
+      <c r="D17" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="38" t="s">
         <v>150</v>
       </c>
-      <c r="E16" s="55" t="s">
-        <v>151</v>
-      </c>
-      <c r="F16" s="59"/>
-      <c r="G16" s="57"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="33"/>
-      <c r="B17" s="34"/>
-      <c r="C17" s="34"/>
-      <c r="D17" s="35" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="F17" s="60"/>
-      <c r="G17" s="51"/>
+      <c r="F17" s="62"/>
+      <c r="G17" s="53"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="44"/>
-      <c r="B18" s="44"/>
-      <c r="C18" s="44"/>
-      <c r="D18" s="61"/>
-      <c r="E18" s="45"/>
-      <c r="F18" s="61"/>
-      <c r="G18" s="61"/>
+      <c r="A18" s="46"/>
+      <c r="B18" s="46"/>
+      <c r="C18" s="46"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="47"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
     </row>
     <row r="19" ht="12.75" customHeight="1"/>
     <row r="20" ht="12.75" customHeight="1"/>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -71,9 +71,6 @@
   </si>
   <si>
     <t>Successful authentication and redirection to user dashboard</t>
-  </si>
-  <si>
-    <t>Whenever we reach the entry point of the frontend, two errors always pops up at the bottom that says user not authenticated as well as authentication required</t>
   </si>
   <si>
     <t>Implies not part of this Release</t>
@@ -817,7 +814,7 @@
     <xf borderId="2" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="4" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
+    <xf borderId="2" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
@@ -833,7 +830,7 @@
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1267,12 +1264,10 @@
       <c r="F3" s="14"/>
       <c r="G3" s="15"/>
       <c r="H3" s="16"/>
-      <c r="I3" s="13" t="s">
-        <v>17</v>
-      </c>
+      <c r="I3" s="13"/>
       <c r="K3" s="17"/>
       <c r="L3" s="18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
@@ -1284,13 +1279,13 @@
         <v>13</v>
       </c>
       <c r="C4" s="20" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="D4" s="13" t="s">
+      <c r="E4" s="13" t="s">
         <v>20</v>
-      </c>
-      <c r="E4" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="F4" s="21"/>
       <c r="G4" s="21"/>
@@ -1298,7 +1293,7 @@
       <c r="I4" s="21"/>
       <c r="K4" s="22"/>
       <c r="L4" s="18" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
@@ -1310,13 +1305,13 @@
         <v>13</v>
       </c>
       <c r="C5" s="20" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="D5" s="13" t="s">
+      <c r="E5" s="20" t="s">
         <v>24</v>
-      </c>
-      <c r="E5" s="20" t="s">
-        <v>25</v>
       </c>
       <c r="F5" s="21"/>
       <c r="G5" s="21"/>
@@ -1324,7 +1319,7 @@
       <c r="I5" s="21"/>
       <c r="K5" s="23"/>
       <c r="L5" s="18" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
@@ -1333,16 +1328,16 @@
         <v>4</v>
       </c>
       <c r="B6" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C6" s="20" t="s">
+      <c r="D6" s="20" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="E6" s="20" t="s">
         <v>29</v>
-      </c>
-      <c r="E6" s="20" t="s">
-        <v>30</v>
       </c>
       <c r="F6" s="21"/>
       <c r="G6" s="21"/>
@@ -1355,16 +1350,16 @@
         <v>5</v>
       </c>
       <c r="B7" s="20" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="20" t="s">
-        <v>28</v>
-      </c>
       <c r="D7" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="E7" s="20" t="s">
         <v>31</v>
-      </c>
-      <c r="E7" s="20" t="s">
-        <v>32</v>
       </c>
       <c r="F7" s="21"/>
       <c r="G7" s="21"/>
@@ -1377,16 +1372,16 @@
         <v>6</v>
       </c>
       <c r="B8" s="20" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="C8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="E8" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="21"/>
       <c r="G8" s="21"/>
@@ -1399,16 +1394,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="20" t="s">
+      <c r="E9" s="20" t="s">
         <v>37</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>38</v>
       </c>
       <c r="F9" s="21"/>
       <c r="G9" s="21"/>
@@ -1421,16 +1416,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="F10" s="21"/>
       <c r="G10" s="21"/>
@@ -1443,16 +1438,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="D11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="E11" s="20" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>44</v>
       </c>
       <c r="F11" s="21"/>
       <c r="G11" s="21"/>
@@ -1465,16 +1460,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="E12" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>47</v>
       </c>
       <c r="F12" s="21"/>
       <c r="G12" s="21"/>
@@ -1484,16 +1479,16 @@
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>48</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>49</v>
       </c>
       <c r="F13" s="21"/>
       <c r="G13" s="21"/>
@@ -1506,16 +1501,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="D14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="E14" s="20" t="s">
         <v>52</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>53</v>
       </c>
       <c r="F14" s="21"/>
       <c r="G14" s="21"/>
@@ -1528,16 +1523,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="E15" s="20" t="s">
         <v>56</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>57</v>
       </c>
       <c r="F15" s="21"/>
       <c r="G15" s="21"/>
@@ -1550,16 +1545,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>59</v>
       </c>
       <c r="F16" s="21"/>
       <c r="G16" s="21"/>
@@ -1572,16 +1567,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="E17" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>62</v>
       </c>
       <c r="F17" s="21"/>
       <c r="G17" s="21"/>
@@ -1594,16 +1589,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="E18" s="20" t="s">
         <v>65</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>66</v>
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="21"/>
@@ -1616,16 +1611,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="E19" s="20" t="s">
         <v>69</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>70</v>
       </c>
       <c r="F19" s="21"/>
       <c r="G19" s="21"/>
@@ -1638,16 +1633,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>72</v>
       </c>
       <c r="F20" s="21"/>
       <c r="G20" s="21"/>
@@ -1660,16 +1655,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="D21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="E21" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="F21" s="21"/>
       <c r="G21" s="21"/>
@@ -1682,16 +1677,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="E22" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="F22" s="21"/>
       <c r="G22" s="21"/>
@@ -1704,16 +1699,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="20" t="s">
+      <c r="E23" s="20" t="s">
         <v>82</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>83</v>
       </c>
       <c r="F23" s="21"/>
       <c r="G23" s="21"/>
@@ -1726,16 +1721,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="F24" s="21"/>
       <c r="G24" s="21"/>
@@ -1748,16 +1743,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="20" t="s">
+        <v>85</v>
+      </c>
+      <c r="C25" s="20" t="s">
+        <v>27</v>
+      </c>
+      <c r="D25" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="C25" s="20" t="s">
-        <v>28</v>
-      </c>
-      <c r="D25" s="20" t="s">
+      <c r="E25" s="20" t="s">
         <v>87</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>88</v>
       </c>
       <c r="F25" s="21"/>
       <c r="G25" s="21"/>
@@ -1770,16 +1765,16 @@
         <v>23</v>
       </c>
       <c r="B26" s="24" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="E26" s="20" t="s">
         <v>91</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>92</v>
       </c>
       <c r="F26" s="21"/>
       <c r="G26" s="21"/>
@@ -1792,16 +1787,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D27" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>94</v>
       </c>
       <c r="F27" s="21"/>
       <c r="G27" s="21"/>
@@ -1814,16 +1809,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="20" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="D28" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>95</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>96</v>
       </c>
       <c r="F28" s="21"/>
       <c r="G28" s="21"/>
@@ -1925,7 +1920,7 @@
       <c r="B38" s="26"/>
       <c r="C38" s="26"/>
       <c r="K38" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -1937,7 +1932,7 @@
       <c r="B39" s="26"/>
       <c r="C39" s="26"/>
       <c r="K39" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
@@ -1949,7 +1944,7 @@
       <c r="B40" s="26"/>
       <c r="C40" s="26"/>
       <c r="K40" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
@@ -1961,7 +1956,7 @@
       <c r="B41" s="26"/>
       <c r="C41" s="26"/>
       <c r="K41" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
@@ -1973,7 +1968,7 @@
       <c r="B42" s="26"/>
       <c r="C42" s="26"/>
       <c r="K42" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
@@ -1985,7 +1980,7 @@
       <c r="B43" s="26"/>
       <c r="C43" s="26"/>
       <c r="K43" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
@@ -6889,83 +6884,83 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="B1" s="27" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
       <c r="B3" s="28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="B4" s="28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="B5" s="28" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="B6" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="B7" s="28" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="B8" s="28" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="B9" s="28" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="B10" s="28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="B11" s="28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="B12" s="28" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="B13" s="28" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="B14" s="28" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="B15" s="28" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="B16" s="28" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="B17" s="28" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7979,7 +7974,7 @@
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
       <c r="A2" s="29" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B2" s="29"/>
       <c r="C2" s="29"/>
@@ -7987,20 +7982,20 @@
     <row r="3" ht="12.75" customHeight="1">
       <c r="A3" s="26"/>
       <c r="B3" s="30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C3" s="26"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
       <c r="A4" s="26"/>
       <c r="B4" s="31" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C4" s="26"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="32" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B5" s="32"/>
       <c r="C5" s="32"/>
@@ -8012,25 +8007,25 @@
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="B7" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="34" t="s">
+      <c r="C7" s="34" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="D7" s="33" t="s">
         <v>125</v>
-      </c>
-      <c r="D7" s="33" t="s">
-        <v>126</v>
       </c>
       <c r="E7" s="33" t="s">
         <v>8</v>
       </c>
       <c r="F7" s="33" t="s">
+        <v>126</v>
+      </c>
+      <c r="G7" s="33" t="s">
         <v>127</v>
-      </c>
-      <c r="G7" s="33" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -8038,16 +8033,16 @@
         <v>1.0</v>
       </c>
       <c r="B8" s="36" t="s">
+        <v>128</v>
+      </c>
+      <c r="C8" s="36" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="36" t="s">
+      <c r="D8" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="E8" s="38" t="s">
         <v>131</v>
-      </c>
-      <c r="E8" s="38" t="s">
-        <v>132</v>
       </c>
       <c r="F8" s="39"/>
       <c r="G8" s="40"/>
@@ -8057,16 +8052,16 @@
         <v>2.0</v>
       </c>
       <c r="B9" s="42" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C9" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="44" t="s">
         <v>133</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="44" t="s">
-        <v>134</v>
       </c>
       <c r="F9" s="45"/>
       <c r="G9" s="40"/>
@@ -8076,16 +8071,16 @@
         <v>3.0</v>
       </c>
       <c r="B10" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="C10" s="47" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="47" t="s">
+      <c r="D10" s="48" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="E10" s="49" t="s">
         <v>137</v>
-      </c>
-      <c r="E10" s="49" t="s">
-        <v>138</v>
       </c>
       <c r="F10" s="50"/>
       <c r="G10" s="51"/>
@@ -8095,10 +8090,10 @@
       <c r="B11" s="36"/>
       <c r="C11" s="36"/>
       <c r="D11" s="37" t="s">
+        <v>138</v>
+      </c>
+      <c r="E11" s="38" t="s">
         <v>139</v>
-      </c>
-      <c r="E11" s="38" t="s">
-        <v>140</v>
       </c>
       <c r="F11" s="52"/>
       <c r="G11" s="53"/>
@@ -8108,16 +8103,16 @@
         <v>4.0</v>
       </c>
       <c r="B12" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C12" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="55" t="s">
+      <c r="D12" s="56" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="E12" s="57" t="s">
         <v>143</v>
-      </c>
-      <c r="E12" s="57" t="s">
-        <v>144</v>
       </c>
       <c r="F12" s="58"/>
       <c r="G12" s="59"/>
@@ -8127,10 +8122,10 @@
       <c r="B13" s="36"/>
       <c r="C13" s="36"/>
       <c r="D13" s="37" t="s">
+        <v>144</v>
+      </c>
+      <c r="E13" s="38" t="s">
         <v>145</v>
-      </c>
-      <c r="E13" s="38" t="s">
-        <v>146</v>
       </c>
       <c r="F13" s="39"/>
       <c r="G13" s="53"/>
@@ -8140,16 +8135,16 @@
         <v>5.0</v>
       </c>
       <c r="B14" s="55" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C14" s="55" t="s">
+        <v>146</v>
+      </c>
+      <c r="D14" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="D14" s="56" t="s">
+      <c r="E14" s="57" t="s">
         <v>148</v>
-      </c>
-      <c r="E14" s="57" t="s">
-        <v>149</v>
       </c>
       <c r="F14" s="58"/>
       <c r="G14" s="59"/>
@@ -8159,13 +8154,13 @@
       <c r="B15" s="36"/>
       <c r="C15" s="36"/>
       <c r="D15" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E15" s="38" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="60" t="s">
         <v>150</v>
-      </c>
-      <c r="F15" s="60" t="s">
-        <v>151</v>
       </c>
       <c r="G15" s="53"/>
     </row>
@@ -8174,16 +8169,16 @@
         <v>6.0</v>
       </c>
       <c r="B16" s="55" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="55" t="s">
         <v>141</v>
       </c>
-      <c r="C16" s="55" t="s">
-        <v>142</v>
-      </c>
       <c r="D16" s="56" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="57" t="s">
         <v>152</v>
-      </c>
-      <c r="E16" s="57" t="s">
-        <v>153</v>
       </c>
       <c r="F16" s="61"/>
       <c r="G16" s="59"/>
@@ -8193,10 +8188,10 @@
       <c r="B17" s="36"/>
       <c r="C17" s="36"/>
       <c r="D17" s="37" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="E17" s="38" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F17" s="62"/>
       <c r="G17" s="53"/>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -113,7 +113,7 @@
     <t>1. Select date and time</t>
   </si>
   <si>
-    <t>Room grid shows available rooms in green and unavailable rooms in red</t>
+    <t>Room grid shows only the available rooms based on the filter</t>
   </si>
   <si>
     <t>1. Select past date</t>
@@ -238,6 +238,9 @@
   </si>
   <si>
     <t>User is successfully logged out and redirected to login page</t>
+  </si>
+  <si>
+    <t>Upon logout session credentials aren't being cleared due to which pressing login again logs in the same user</t>
   </si>
   <si>
     <t>Cancel Booking</t>
@@ -767,7 +770,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -827,12 +830,21 @@
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="3" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="2" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf borderId="3" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1288,10 +1300,10 @@
         <v>20</v>
       </c>
       <c r="F4" s="21"/>
-      <c r="G4" s="21"/>
-      <c r="H4" s="21"/>
-      <c r="I4" s="21"/>
-      <c r="K4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="23"/>
+      <c r="I4" s="22"/>
+      <c r="K4" s="24"/>
       <c r="L4" s="18" t="s">
         <v>21</v>
       </c>
@@ -1314,10 +1326,10 @@
         <v>24</v>
       </c>
       <c r="F5" s="21"/>
-      <c r="G5" s="21"/>
-      <c r="H5" s="21"/>
-      <c r="I5" s="21"/>
-      <c r="K5" s="23"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="23"/>
+      <c r="I5" s="22"/>
+      <c r="K5" s="25"/>
       <c r="L5" s="18" t="s">
         <v>25</v>
       </c>
@@ -1339,10 +1351,10 @@
       <c r="E6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="21"/>
-      <c r="G6" s="21"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
       <c r="H6" s="21"/>
-      <c r="I6" s="21"/>
+      <c r="I6" s="22"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="19">
@@ -1361,10 +1373,10 @@
       <c r="E7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="21"/>
-      <c r="G7" s="21"/>
-      <c r="H7" s="21"/>
-      <c r="I7" s="21"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="19">
@@ -1383,10 +1395,10 @@
       <c r="E8" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="F8" s="21"/>
-      <c r="G8" s="21"/>
-      <c r="H8" s="21"/>
-      <c r="I8" s="21"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="19">
@@ -1405,10 +1417,10 @@
       <c r="E9" s="20" t="s">
         <v>37</v>
       </c>
-      <c r="F9" s="21"/>
-      <c r="G9" s="21"/>
-      <c r="H9" s="21"/>
-      <c r="I9" s="21"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="19">
@@ -1427,10 +1439,10 @@
       <c r="E10" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="F10" s="21"/>
-      <c r="G10" s="21"/>
-      <c r="H10" s="21"/>
-      <c r="I10" s="21"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="19">
@@ -1449,10 +1461,10 @@
       <c r="E11" s="20" t="s">
         <v>43</v>
       </c>
-      <c r="F11" s="21"/>
-      <c r="G11" s="21"/>
-      <c r="H11" s="21"/>
-      <c r="I11" s="21"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="19">
@@ -1471,10 +1483,10 @@
       <c r="E12" s="20" t="s">
         <v>46</v>
       </c>
-      <c r="F12" s="21"/>
-      <c r="G12" s="21"/>
-      <c r="H12" s="21"/>
-      <c r="I12" s="21"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="19"/>
@@ -1490,10 +1502,10 @@
       <c r="E13" s="20" t="s">
         <v>48</v>
       </c>
-      <c r="F13" s="21"/>
-      <c r="G13" s="21"/>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="19">
@@ -1512,10 +1524,10 @@
       <c r="E14" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="F14" s="21"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="19">
@@ -1534,10 +1546,10 @@
       <c r="E15" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="F15" s="21"/>
-      <c r="G15" s="21"/>
-      <c r="H15" s="21"/>
-      <c r="I15" s="21"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="19">
@@ -1556,10 +1568,10 @@
       <c r="E16" s="20" t="s">
         <v>58</v>
       </c>
-      <c r="F16" s="21"/>
-      <c r="G16" s="21"/>
-      <c r="H16" s="21"/>
-      <c r="I16" s="21"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="19">
@@ -1578,10 +1590,10 @@
       <c r="E17" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="21"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="19">
@@ -1601,9 +1613,11 @@
         <v>65</v>
       </c>
       <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="21"/>
+      <c r="G18" s="22"/>
+      <c r="H18" s="26"/>
+      <c r="I18" s="20" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="19">
@@ -1611,21 +1625,21 @@
         <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="21"/>
+        <v>70</v>
+      </c>
+      <c r="F19" s="22"/>
+      <c r="G19" s="22"/>
+      <c r="H19" s="22"/>
+      <c r="I19" s="22"/>
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="19">
@@ -1633,21 +1647,21 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>71</v>
-      </c>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="21"/>
+        <v>72</v>
+      </c>
+      <c r="F20" s="22"/>
+      <c r="G20" s="22"/>
+      <c r="H20" s="22"/>
+      <c r="I20" s="22"/>
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="19">
@@ -1655,21 +1669,21 @@
         <v>18</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>75</v>
-      </c>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="21"/>
+        <v>76</v>
+      </c>
+      <c r="F21" s="22"/>
+      <c r="G21" s="22"/>
+      <c r="H21" s="22"/>
+      <c r="I21" s="22"/>
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="19">
@@ -1677,21 +1691,21 @@
         <v>19</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" s="21"/>
-      <c r="G22" s="21"/>
-      <c r="H22" s="21"/>
-      <c r="I22" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="F22" s="22"/>
+      <c r="G22" s="22"/>
+      <c r="H22" s="22"/>
+      <c r="I22" s="22"/>
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="19">
@@ -1699,21 +1713,21 @@
         <v>20</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>82</v>
-      </c>
-      <c r="F23" s="21"/>
-      <c r="G23" s="21"/>
-      <c r="H23" s="21"/>
-      <c r="I23" s="21"/>
+        <v>83</v>
+      </c>
+      <c r="F23" s="22"/>
+      <c r="G23" s="22"/>
+      <c r="H23" s="22"/>
+      <c r="I23" s="22"/>
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="19">
@@ -1721,21 +1735,21 @@
         <v>21</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>84</v>
-      </c>
-      <c r="F24" s="21"/>
-      <c r="G24" s="21"/>
-      <c r="H24" s="21"/>
-      <c r="I24" s="21"/>
+        <v>85</v>
+      </c>
+      <c r="F24" s="22"/>
+      <c r="G24" s="22"/>
+      <c r="H24" s="22"/>
+      <c r="I24" s="22"/>
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="19">
@@ -1743,43 +1757,43 @@
         <v>22</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>87</v>
-      </c>
-      <c r="F25" s="21"/>
-      <c r="G25" s="21"/>
-      <c r="H25" s="21"/>
-      <c r="I25" s="21"/>
+        <v>88</v>
+      </c>
+      <c r="F25" s="22"/>
+      <c r="G25" s="22"/>
+      <c r="H25" s="22"/>
+      <c r="I25" s="22"/>
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="19">
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="24" t="s">
-        <v>88</v>
+      <c r="B26" s="27" t="s">
+        <v>89</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>91</v>
-      </c>
-      <c r="F26" s="21"/>
-      <c r="G26" s="21"/>
-      <c r="H26" s="21"/>
-      <c r="I26" s="21"/>
+        <v>92</v>
+      </c>
+      <c r="F26" s="22"/>
+      <c r="G26" s="22"/>
+      <c r="H26" s="22"/>
+      <c r="I26" s="22"/>
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="19">
@@ -1787,21 +1801,21 @@
         <v>24</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>93</v>
-      </c>
-      <c r="F27" s="21"/>
-      <c r="G27" s="21"/>
-      <c r="H27" s="21"/>
-      <c r="I27" s="21"/>
+        <v>94</v>
+      </c>
+      <c r="F27" s="22"/>
+      <c r="G27" s="22"/>
+      <c r="H27" s="22"/>
+      <c r="I27" s="22"/>
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="19">
@@ -1809,118 +1823,118 @@
         <v>25</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>95</v>
-      </c>
-      <c r="F28" s="21"/>
-      <c r="G28" s="21"/>
-      <c r="H28" s="21"/>
-      <c r="I28" s="21"/>
+        <v>96</v>
+      </c>
+      <c r="F28" s="22"/>
+      <c r="G28" s="22"/>
+      <c r="H28" s="22"/>
+      <c r="I28" s="22"/>
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="19">
         <f t="shared" si="2"/>
         <v>26</v>
       </c>
-      <c r="B29" s="21"/>
-      <c r="C29" s="21"/>
-      <c r="D29" s="21"/>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="21"/>
+      <c r="B29" s="22"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="22"/>
+      <c r="E29" s="22"/>
+      <c r="F29" s="22"/>
+      <c r="G29" s="22"/>
+      <c r="H29" s="22"/>
+      <c r="I29" s="22"/>
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="19">
         <f t="shared" si="2"/>
         <v>27</v>
       </c>
-      <c r="B30" s="21"/>
-      <c r="C30" s="25"/>
-      <c r="D30" s="21"/>
-      <c r="E30" s="21"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="21"/>
+      <c r="B30" s="22"/>
+      <c r="C30" s="28"/>
+      <c r="D30" s="22"/>
+      <c r="E30" s="22"/>
+      <c r="F30" s="22"/>
+      <c r="G30" s="22"/>
+      <c r="H30" s="22"/>
+      <c r="I30" s="22"/>
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="19">
         <f t="shared" si="2"/>
         <v>28</v>
       </c>
-      <c r="B31" s="21"/>
-      <c r="C31" s="25"/>
-      <c r="D31" s="21"/>
-      <c r="E31" s="21"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="21"/>
+      <c r="B31" s="22"/>
+      <c r="C31" s="28"/>
+      <c r="D31" s="22"/>
+      <c r="E31" s="22"/>
+      <c r="F31" s="22"/>
+      <c r="G31" s="22"/>
+      <c r="H31" s="22"/>
+      <c r="I31" s="22"/>
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="19">
         <f t="shared" si="2"/>
         <v>29</v>
       </c>
-      <c r="B32" s="21"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="21"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="21"/>
+      <c r="B32" s="22"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="22"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="22"/>
+      <c r="G32" s="22"/>
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="19">
         <f t="shared" si="2"/>
         <v>30</v>
       </c>
-      <c r="B33" s="21"/>
-      <c r="C33" s="21"/>
-      <c r="D33" s="21"/>
-      <c r="E33" s="21"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="21"/>
+      <c r="B33" s="22"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="22"/>
+      <c r="E33" s="22"/>
+      <c r="F33" s="22"/>
+      <c r="G33" s="22"/>
+      <c r="H33" s="22"/>
+      <c r="I33" s="22"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="26"/>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="26"/>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="26"/>
-      <c r="B36" s="26"/>
-      <c r="C36" s="26"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="26"/>
-      <c r="B37" s="26"/>
-      <c r="C37" s="26"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="26"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="26"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
       <c r="K38" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -1928,11 +1942,11 @@
       <c r="T38" s="4"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="26"/>
-      <c r="B39" s="26"/>
-      <c r="C39" s="26"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
       <c r="K39" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
@@ -1940,11 +1954,11 @@
       <c r="T39" s="4"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="26"/>
-      <c r="B40" s="26"/>
-      <c r="C40" s="26"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
       <c r="K40" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
@@ -1952,11 +1966,11 @@
       <c r="T40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="26"/>
-      <c r="B41" s="26"/>
-      <c r="C41" s="26"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
       <c r="K41" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
@@ -1964,11 +1978,11 @@
       <c r="T41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="26"/>
-      <c r="B42" s="26"/>
-      <c r="C42" s="26"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
       <c r="K42" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
@@ -1976,11 +1990,11 @@
       <c r="T42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="26"/>
-      <c r="B43" s="26"/>
-      <c r="C43" s="26"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
       <c r="K43" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
@@ -1988,45 +2002,45 @@
       <c r="T43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="26"/>
-      <c r="B44" s="26"/>
-      <c r="C44" s="26"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="K44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="26"/>
-      <c r="B45" s="26"/>
-      <c r="C45" s="26"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
       <c r="K45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="26"/>
-      <c r="B46" s="26"/>
-      <c r="C46" s="26"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
       <c r="K46" s="4"/>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="26"/>
-      <c r="B47" s="26"/>
-      <c r="C47" s="26"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
       <c r="K47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="26"/>
-      <c r="B48" s="26"/>
-      <c r="C48" s="26"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -2039,9 +2053,9 @@
       <c r="T48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="26"/>
-      <c r="B49" s="26"/>
-      <c r="C49" s="26"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -2054,9 +2068,9 @@
       <c r="T49" s="4"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="26"/>
-      <c r="B50" s="26"/>
-      <c r="C50" s="26"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -2069,9 +2083,9 @@
       <c r="T50" s="4"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="26"/>
-      <c r="B51" s="26"/>
-      <c r="C51" s="26"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -2084,9 +2098,9 @@
       <c r="T51" s="4"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="26"/>
-      <c r="B52" s="26"/>
-      <c r="C52" s="26"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -2099,4749 +2113,4749 @@
       <c r="T52" s="4"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="26"/>
-      <c r="B53" s="26"/>
-      <c r="C53" s="26"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="26"/>
-      <c r="B54" s="26"/>
-      <c r="C54" s="26"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="26"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="26"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="26"/>
-      <c r="B56" s="26"/>
-      <c r="C56" s="26"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="26"/>
-      <c r="B57" s="26"/>
-      <c r="C57" s="26"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="26"/>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="26"/>
-      <c r="B59" s="26"/>
-      <c r="C59" s="26"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="26"/>
-      <c r="B60" s="26"/>
-      <c r="C60" s="26"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="26"/>
-      <c r="B61" s="26"/>
-      <c r="C61" s="26"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="26"/>
-      <c r="B62" s="26"/>
-      <c r="C62" s="26"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="26"/>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="26"/>
-      <c r="B64" s="26"/>
-      <c r="C64" s="26"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="26"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="26"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="26"/>
-      <c r="B66" s="26"/>
-      <c r="C66" s="26"/>
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="26"/>
-      <c r="B67" s="26"/>
-      <c r="C67" s="26"/>
+      <c r="A67" s="29"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="26"/>
-      <c r="B68" s="26"/>
-      <c r="C68" s="26"/>
+      <c r="A68" s="29"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="26"/>
-      <c r="B69" s="26"/>
-      <c r="C69" s="26"/>
+      <c r="A69" s="29"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="26"/>
-      <c r="B70" s="26"/>
-      <c r="C70" s="26"/>
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="26"/>
-      <c r="B71" s="26"/>
-      <c r="C71" s="26"/>
+      <c r="A71" s="29"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="26"/>
-      <c r="B72" s="26"/>
-      <c r="C72" s="26"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="26"/>
-      <c r="B73" s="26"/>
-      <c r="C73" s="26"/>
+      <c r="A73" s="29"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="26"/>
-      <c r="B74" s="26"/>
-      <c r="C74" s="26"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="26"/>
-      <c r="B75" s="26"/>
-      <c r="C75" s="26"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="26"/>
-      <c r="B76" s="26"/>
-      <c r="C76" s="26"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="26"/>
-      <c r="B77" s="26"/>
-      <c r="C77" s="26"/>
+      <c r="A77" s="29"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="26"/>
-      <c r="B78" s="26"/>
-      <c r="C78" s="26"/>
+      <c r="A78" s="29"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="26"/>
-      <c r="B79" s="26"/>
-      <c r="C79" s="26"/>
+      <c r="A79" s="29"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="26"/>
-      <c r="B80" s="26"/>
-      <c r="C80" s="26"/>
+      <c r="A80" s="29"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="26"/>
-      <c r="B81" s="26"/>
-      <c r="C81" s="26"/>
+      <c r="A81" s="29"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="26"/>
-      <c r="B82" s="26"/>
-      <c r="C82" s="26"/>
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="26"/>
-      <c r="B83" s="26"/>
-      <c r="C83" s="26"/>
+      <c r="A83" s="29"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="26"/>
-      <c r="B84" s="26"/>
-      <c r="C84" s="26"/>
+      <c r="A84" s="29"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="26"/>
-      <c r="B85" s="26"/>
-      <c r="C85" s="26"/>
+      <c r="A85" s="29"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="26"/>
-      <c r="B86" s="26"/>
-      <c r="C86" s="26"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="26"/>
-      <c r="B87" s="26"/>
-      <c r="C87" s="26"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="26"/>
-      <c r="B88" s="26"/>
-      <c r="C88" s="26"/>
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="26"/>
-      <c r="B89" s="26"/>
-      <c r="C89" s="26"/>
+      <c r="A89" s="29"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="26"/>
-      <c r="B90" s="26"/>
-      <c r="C90" s="26"/>
+      <c r="A90" s="29"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="26"/>
-      <c r="B91" s="26"/>
-      <c r="C91" s="26"/>
+      <c r="A91" s="29"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="26"/>
-      <c r="B92" s="26"/>
-      <c r="C92" s="26"/>
+      <c r="A92" s="29"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="26"/>
-      <c r="B93" s="26"/>
-      <c r="C93" s="26"/>
+      <c r="A93" s="29"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="26"/>
-      <c r="B94" s="26"/>
-      <c r="C94" s="26"/>
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="26"/>
-      <c r="B95" s="26"/>
-      <c r="C95" s="26"/>
+      <c r="A95" s="29"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="26"/>
-      <c r="B96" s="26"/>
-      <c r="C96" s="26"/>
+      <c r="A96" s="29"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="26"/>
-      <c r="B97" s="26"/>
-      <c r="C97" s="26"/>
+      <c r="A97" s="29"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="A98" s="26"/>
-      <c r="B98" s="26"/>
-      <c r="C98" s="26"/>
+      <c r="A98" s="29"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="A99" s="26"/>
-      <c r="B99" s="26"/>
-      <c r="C99" s="26"/>
+      <c r="A99" s="29"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="A100" s="26"/>
-      <c r="B100" s="26"/>
-      <c r="C100" s="26"/>
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="A101" s="26"/>
-      <c r="B101" s="26"/>
-      <c r="C101" s="26"/>
+      <c r="A101" s="29"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="A102" s="26"/>
-      <c r="B102" s="26"/>
-      <c r="C102" s="26"/>
+      <c r="A102" s="29"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="A103" s="26"/>
-      <c r="B103" s="26"/>
-      <c r="C103" s="26"/>
+      <c r="A103" s="29"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" s="26"/>
-      <c r="B104" s="26"/>
-      <c r="C104" s="26"/>
+      <c r="A104" s="29"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="26"/>
-      <c r="B105" s="26"/>
-      <c r="C105" s="26"/>
+      <c r="A105" s="29"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="26"/>
-      <c r="B106" s="26"/>
-      <c r="C106" s="26"/>
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="26"/>
-      <c r="B107" s="26"/>
-      <c r="C107" s="26"/>
+      <c r="A107" s="29"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="26"/>
-      <c r="B108" s="26"/>
-      <c r="C108" s="26"/>
+      <c r="A108" s="29"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="29"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="26"/>
-      <c r="B109" s="26"/>
-      <c r="C109" s="26"/>
+      <c r="A109" s="29"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="29"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="26"/>
-      <c r="B110" s="26"/>
-      <c r="C110" s="26"/>
+      <c r="A110" s="29"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="26"/>
-      <c r="B111" s="26"/>
-      <c r="C111" s="26"/>
+      <c r="A111" s="29"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="A112" s="26"/>
-      <c r="B112" s="26"/>
-      <c r="C112" s="26"/>
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="A113" s="26"/>
-      <c r="B113" s="26"/>
-      <c r="C113" s="26"/>
+      <c r="A113" s="29"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="29"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="26"/>
-      <c r="B114" s="26"/>
-      <c r="C114" s="26"/>
+      <c r="A114" s="29"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="29"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="26"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="26"/>
-      <c r="B116" s="26"/>
-      <c r="C116" s="26"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="A117" s="26"/>
-      <c r="B117" s="26"/>
-      <c r="C117" s="26"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="A118" s="26"/>
-      <c r="B118" s="26"/>
-      <c r="C118" s="26"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="26"/>
-      <c r="B119" s="26"/>
-      <c r="C119" s="26"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="A120" s="26"/>
-      <c r="B120" s="26"/>
-      <c r="C120" s="26"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="A121" s="26"/>
-      <c r="B121" s="26"/>
-      <c r="C121" s="26"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="A122" s="26"/>
-      <c r="B122" s="26"/>
-      <c r="C122" s="26"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="A123" s="26"/>
-      <c r="B123" s="26"/>
-      <c r="C123" s="26"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="A124" s="26"/>
-      <c r="B124" s="26"/>
-      <c r="C124" s="26"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="A125" s="26"/>
-      <c r="B125" s="26"/>
-      <c r="C125" s="26"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="A126" s="26"/>
-      <c r="B126" s="26"/>
-      <c r="C126" s="26"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="26"/>
-      <c r="B127" s="26"/>
-      <c r="C127" s="26"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="26"/>
-      <c r="B128" s="26"/>
-      <c r="C128" s="26"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="A129" s="26"/>
-      <c r="B129" s="26"/>
-      <c r="C129" s="26"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="A130" s="26"/>
-      <c r="B130" s="26"/>
-      <c r="C130" s="26"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="A131" s="26"/>
-      <c r="B131" s="26"/>
-      <c r="C131" s="26"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="A132" s="26"/>
-      <c r="B132" s="26"/>
-      <c r="C132" s="26"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="A133" s="26"/>
-      <c r="B133" s="26"/>
-      <c r="C133" s="26"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="A134" s="26"/>
-      <c r="B134" s="26"/>
-      <c r="C134" s="26"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="A135" s="26"/>
-      <c r="B135" s="26"/>
-      <c r="C135" s="26"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="A136" s="26"/>
-      <c r="B136" s="26"/>
-      <c r="C136" s="26"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="A137" s="26"/>
-      <c r="B137" s="26"/>
-      <c r="C137" s="26"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="A138" s="26"/>
-      <c r="B138" s="26"/>
-      <c r="C138" s="26"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="A139" s="26"/>
-      <c r="B139" s="26"/>
-      <c r="C139" s="26"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="A140" s="26"/>
-      <c r="B140" s="26"/>
-      <c r="C140" s="26"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="A141" s="26"/>
-      <c r="B141" s="26"/>
-      <c r="C141" s="26"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="A142" s="26"/>
-      <c r="B142" s="26"/>
-      <c r="C142" s="26"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="A143" s="26"/>
-      <c r="B143" s="26"/>
-      <c r="C143" s="26"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="A144" s="26"/>
-      <c r="B144" s="26"/>
-      <c r="C144" s="26"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="A145" s="26"/>
-      <c r="B145" s="26"/>
-      <c r="C145" s="26"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="A146" s="26"/>
-      <c r="B146" s="26"/>
-      <c r="C146" s="26"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="A147" s="26"/>
-      <c r="B147" s="26"/>
-      <c r="C147" s="26"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="26"/>
-      <c r="B148" s="26"/>
-      <c r="C148" s="26"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="A149" s="26"/>
-      <c r="B149" s="26"/>
-      <c r="C149" s="26"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="A150" s="26"/>
-      <c r="B150" s="26"/>
-      <c r="C150" s="26"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="A151" s="26"/>
-      <c r="B151" s="26"/>
-      <c r="C151" s="26"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="A152" s="26"/>
-      <c r="B152" s="26"/>
-      <c r="C152" s="26"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="A153" s="26"/>
-      <c r="B153" s="26"/>
-      <c r="C153" s="26"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="A154" s="26"/>
-      <c r="B154" s="26"/>
-      <c r="C154" s="26"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="A155" s="26"/>
-      <c r="B155" s="26"/>
-      <c r="C155" s="26"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="A156" s="26"/>
-      <c r="B156" s="26"/>
-      <c r="C156" s="26"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="A157" s="26"/>
-      <c r="B157" s="26"/>
-      <c r="C157" s="26"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="A158" s="26"/>
-      <c r="B158" s="26"/>
-      <c r="C158" s="26"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="A159" s="26"/>
-      <c r="B159" s="26"/>
-      <c r="C159" s="26"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
+      <c r="C159" s="29"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="A160" s="26"/>
-      <c r="B160" s="26"/>
-      <c r="C160" s="26"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="A161" s="26"/>
-      <c r="B161" s="26"/>
-      <c r="C161" s="26"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
+      <c r="C161" s="29"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="A162" s="26"/>
-      <c r="B162" s="26"/>
-      <c r="C162" s="26"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
+      <c r="C162" s="29"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="A163" s="26"/>
-      <c r="B163" s="26"/>
-      <c r="C163" s="26"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
+      <c r="C163" s="29"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="A164" s="26"/>
-      <c r="B164" s="26"/>
-      <c r="C164" s="26"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
+      <c r="C164" s="29"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="A165" s="26"/>
-      <c r="B165" s="26"/>
-      <c r="C165" s="26"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
+      <c r="C165" s="29"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="A166" s="26"/>
-      <c r="B166" s="26"/>
-      <c r="C166" s="26"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="A167" s="26"/>
-      <c r="B167" s="26"/>
-      <c r="C167" s="26"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="26"/>
-      <c r="B168" s="26"/>
-      <c r="C168" s="26"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
+      <c r="C168" s="29"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="A169" s="26"/>
-      <c r="B169" s="26"/>
-      <c r="C169" s="26"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
+      <c r="C169" s="29"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="A170" s="26"/>
-      <c r="B170" s="26"/>
-      <c r="C170" s="26"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
+      <c r="C170" s="29"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="A171" s="26"/>
-      <c r="B171" s="26"/>
-      <c r="C171" s="26"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
+      <c r="C171" s="29"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="A172" s="26"/>
-      <c r="B172" s="26"/>
-      <c r="C172" s="26"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="A173" s="26"/>
-      <c r="B173" s="26"/>
-      <c r="C173" s="26"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
+      <c r="C173" s="29"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="A174" s="26"/>
-      <c r="B174" s="26"/>
-      <c r="C174" s="26"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
+      <c r="C174" s="29"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="A175" s="26"/>
-      <c r="B175" s="26"/>
-      <c r="C175" s="26"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
+      <c r="C175" s="29"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="A176" s="26"/>
-      <c r="B176" s="26"/>
-      <c r="C176" s="26"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
+      <c r="C176" s="29"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="A177" s="26"/>
-      <c r="B177" s="26"/>
-      <c r="C177" s="26"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
+      <c r="C177" s="29"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="26"/>
-      <c r="B178" s="26"/>
-      <c r="C178" s="26"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="A179" s="26"/>
-      <c r="B179" s="26"/>
-      <c r="C179" s="26"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
+      <c r="C179" s="29"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="A180" s="26"/>
-      <c r="B180" s="26"/>
-      <c r="C180" s="26"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
+      <c r="C180" s="29"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="A181" s="26"/>
-      <c r="B181" s="26"/>
-      <c r="C181" s="26"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
+      <c r="C181" s="29"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="A182" s="26"/>
-      <c r="B182" s="26"/>
-      <c r="C182" s="26"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
+      <c r="C182" s="29"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="A183" s="26"/>
-      <c r="B183" s="26"/>
-      <c r="C183" s="26"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
+      <c r="C183" s="29"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="A184" s="26"/>
-      <c r="B184" s="26"/>
-      <c r="C184" s="26"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="A185" s="26"/>
-      <c r="B185" s="26"/>
-      <c r="C185" s="26"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
+      <c r="C185" s="29"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="A186" s="26"/>
-      <c r="B186" s="26"/>
-      <c r="C186" s="26"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
+      <c r="C186" s="29"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="A187" s="26"/>
-      <c r="B187" s="26"/>
-      <c r="C187" s="26"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
+      <c r="C187" s="29"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="26"/>
-      <c r="B188" s="26"/>
-      <c r="C188" s="26"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
+      <c r="C188" s="29"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="A189" s="26"/>
-      <c r="B189" s="26"/>
-      <c r="C189" s="26"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
+      <c r="C189" s="29"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="A190" s="26"/>
-      <c r="B190" s="26"/>
-      <c r="C190" s="26"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="A191" s="26"/>
-      <c r="B191" s="26"/>
-      <c r="C191" s="26"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
+      <c r="C191" s="29"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="A192" s="26"/>
-      <c r="B192" s="26"/>
-      <c r="C192" s="26"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
+      <c r="C192" s="29"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="A193" s="26"/>
-      <c r="B193" s="26"/>
-      <c r="C193" s="26"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
+      <c r="C193" s="29"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="A194" s="26"/>
-      <c r="B194" s="26"/>
-      <c r="C194" s="26"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
+      <c r="C194" s="29"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="A195" s="26"/>
-      <c r="B195" s="26"/>
-      <c r="C195" s="26"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
+      <c r="C195" s="29"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="A196" s="26"/>
-      <c r="B196" s="26"/>
-      <c r="C196" s="26"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="A197" s="26"/>
-      <c r="B197" s="26"/>
-      <c r="C197" s="26"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
+      <c r="C197" s="29"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="A198" s="26"/>
-      <c r="B198" s="26"/>
-      <c r="C198" s="26"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
+      <c r="C198" s="29"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="A199" s="26"/>
-      <c r="B199" s="26"/>
-      <c r="C199" s="26"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
+      <c r="C199" s="29"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="A200" s="26"/>
-      <c r="B200" s="26"/>
-      <c r="C200" s="26"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
+      <c r="C200" s="29"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="A201" s="26"/>
-      <c r="B201" s="26"/>
-      <c r="C201" s="26"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
+      <c r="C201" s="29"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="A202" s="26"/>
-      <c r="B202" s="26"/>
-      <c r="C202" s="26"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="A203" s="26"/>
-      <c r="B203" s="26"/>
-      <c r="C203" s="26"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
+      <c r="C203" s="29"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="A204" s="26"/>
-      <c r="B204" s="26"/>
-      <c r="C204" s="26"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
+      <c r="C204" s="29"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="A205" s="26"/>
-      <c r="B205" s="26"/>
-      <c r="C205" s="26"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
+      <c r="C205" s="29"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="A206" s="26"/>
-      <c r="B206" s="26"/>
-      <c r="C206" s="26"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
+      <c r="C206" s="29"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="A207" s="26"/>
-      <c r="B207" s="26"/>
-      <c r="C207" s="26"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
+      <c r="C207" s="29"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="26"/>
-      <c r="B208" s="26"/>
-      <c r="C208" s="26"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="A209" s="26"/>
-      <c r="B209" s="26"/>
-      <c r="C209" s="26"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
+      <c r="C209" s="29"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="A210" s="26"/>
-      <c r="B210" s="26"/>
-      <c r="C210" s="26"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
+      <c r="C210" s="29"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="A211" s="26"/>
-      <c r="B211" s="26"/>
-      <c r="C211" s="26"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
+      <c r="C211" s="29"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="A212" s="26"/>
-      <c r="B212" s="26"/>
-      <c r="C212" s="26"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
+      <c r="C212" s="29"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="A213" s="26"/>
-      <c r="B213" s="26"/>
-      <c r="C213" s="26"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
+      <c r="C213" s="29"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="A214" s="26"/>
-      <c r="B214" s="26"/>
-      <c r="C214" s="26"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="A215" s="26"/>
-      <c r="B215" s="26"/>
-      <c r="C215" s="26"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
+      <c r="C215" s="29"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="A216" s="26"/>
-      <c r="B216" s="26"/>
-      <c r="C216" s="26"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
+      <c r="C216" s="29"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="A217" s="26"/>
-      <c r="B217" s="26"/>
-      <c r="C217" s="26"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
+      <c r="C217" s="29"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="A218" s="26"/>
-      <c r="B218" s="26"/>
-      <c r="C218" s="26"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
+      <c r="C218" s="29"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="A219" s="26"/>
-      <c r="B219" s="26"/>
-      <c r="C219" s="26"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="A220" s="26"/>
-      <c r="B220" s="26"/>
-      <c r="C220" s="26"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="A221" s="26"/>
-      <c r="B221" s="26"/>
-      <c r="C221" s="26"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
+      <c r="C221" s="29"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="A222" s="26"/>
-      <c r="B222" s="26"/>
-      <c r="C222" s="26"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
+      <c r="C222" s="29"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="A223" s="26"/>
-      <c r="B223" s="26"/>
-      <c r="C223" s="26"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
+      <c r="C223" s="29"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="A224" s="26"/>
-      <c r="B224" s="26"/>
-      <c r="C224" s="26"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
+      <c r="C224" s="29"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="A225" s="26"/>
-      <c r="B225" s="26"/>
-      <c r="C225" s="26"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
+      <c r="C225" s="29"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="26"/>
-      <c r="B226" s="26"/>
-      <c r="C226" s="26"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="26"/>
-      <c r="B227" s="26"/>
-      <c r="C227" s="26"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
+      <c r="C227" s="29"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="26"/>
-      <c r="B228" s="26"/>
-      <c r="C228" s="26"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
+      <c r="C228" s="29"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="26"/>
-      <c r="B229" s="26"/>
-      <c r="C229" s="26"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
+      <c r="C229" s="29"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="26"/>
-      <c r="B230" s="26"/>
-      <c r="C230" s="26"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
+      <c r="C230" s="29"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="A231" s="26"/>
-      <c r="B231" s="26"/>
-      <c r="C231" s="26"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
+      <c r="C231" s="29"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="A232" s="26"/>
-      <c r="B232" s="26"/>
-      <c r="C232" s="26"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="A233" s="26"/>
-      <c r="B233" s="26"/>
-      <c r="C233" s="26"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
+      <c r="C233" s="29"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="A234" s="26"/>
-      <c r="B234" s="26"/>
-      <c r="C234" s="26"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
+      <c r="C234" s="29"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="A235" s="26"/>
-      <c r="B235" s="26"/>
-      <c r="C235" s="26"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
+      <c r="C235" s="29"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="A236" s="26"/>
-      <c r="B236" s="26"/>
-      <c r="C236" s="26"/>
+      <c r="A236" s="29"/>
+      <c r="B236" s="29"/>
+      <c r="C236" s="29"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="A237" s="26"/>
-      <c r="B237" s="26"/>
-      <c r="C237" s="26"/>
+      <c r="A237" s="29"/>
+      <c r="B237" s="29"/>
+      <c r="C237" s="29"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="A238" s="26"/>
-      <c r="B238" s="26"/>
-      <c r="C238" s="26"/>
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="A239" s="26"/>
-      <c r="B239" s="26"/>
-      <c r="C239" s="26"/>
+      <c r="A239" s="29"/>
+      <c r="B239" s="29"/>
+      <c r="C239" s="29"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="A240" s="26"/>
-      <c r="B240" s="26"/>
-      <c r="C240" s="26"/>
+      <c r="A240" s="29"/>
+      <c r="B240" s="29"/>
+      <c r="C240" s="29"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="A241" s="26"/>
-      <c r="B241" s="26"/>
-      <c r="C241" s="26"/>
+      <c r="A241" s="29"/>
+      <c r="B241" s="29"/>
+      <c r="C241" s="29"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="A242" s="26"/>
-      <c r="B242" s="26"/>
-      <c r="C242" s="26"/>
+      <c r="A242" s="29"/>
+      <c r="B242" s="29"/>
+      <c r="C242" s="29"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="A243" s="26"/>
-      <c r="B243" s="26"/>
-      <c r="C243" s="26"/>
+      <c r="A243" s="29"/>
+      <c r="B243" s="29"/>
+      <c r="C243" s="29"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="A244" s="26"/>
-      <c r="B244" s="26"/>
-      <c r="C244" s="26"/>
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="A245" s="26"/>
-      <c r="B245" s="26"/>
-      <c r="C245" s="26"/>
+      <c r="A245" s="29"/>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="A246" s="26"/>
-      <c r="B246" s="26"/>
-      <c r="C246" s="26"/>
+      <c r="A246" s="29"/>
+      <c r="B246" s="29"/>
+      <c r="C246" s="29"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="A247" s="26"/>
-      <c r="B247" s="26"/>
-      <c r="C247" s="26"/>
+      <c r="A247" s="29"/>
+      <c r="B247" s="29"/>
+      <c r="C247" s="29"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="26"/>
-      <c r="B248" s="26"/>
-      <c r="C248" s="26"/>
+      <c r="A248" s="29"/>
+      <c r="B248" s="29"/>
+      <c r="C248" s="29"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="A249" s="26"/>
-      <c r="B249" s="26"/>
-      <c r="C249" s="26"/>
+      <c r="A249" s="29"/>
+      <c r="B249" s="29"/>
+      <c r="C249" s="29"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="A250" s="26"/>
-      <c r="B250" s="26"/>
-      <c r="C250" s="26"/>
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="A251" s="26"/>
-      <c r="B251" s="26"/>
-      <c r="C251" s="26"/>
+      <c r="A251" s="29"/>
+      <c r="B251" s="29"/>
+      <c r="C251" s="29"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="A252" s="26"/>
-      <c r="B252" s="26"/>
-      <c r="C252" s="26"/>
+      <c r="A252" s="29"/>
+      <c r="B252" s="29"/>
+      <c r="C252" s="29"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="A253" s="26"/>
-      <c r="B253" s="26"/>
-      <c r="C253" s="26"/>
+      <c r="A253" s="29"/>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="A254" s="26"/>
-      <c r="B254" s="26"/>
-      <c r="C254" s="26"/>
+      <c r="A254" s="29"/>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="A255" s="26"/>
-      <c r="B255" s="26"/>
-      <c r="C255" s="26"/>
+      <c r="A255" s="29"/>
+      <c r="B255" s="29"/>
+      <c r="C255" s="29"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="A256" s="26"/>
-      <c r="B256" s="26"/>
-      <c r="C256" s="26"/>
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="A257" s="26"/>
-      <c r="B257" s="26"/>
-      <c r="C257" s="26"/>
+      <c r="A257" s="29"/>
+      <c r="B257" s="29"/>
+      <c r="C257" s="29"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="A258" s="26"/>
-      <c r="B258" s="26"/>
-      <c r="C258" s="26"/>
+      <c r="A258" s="29"/>
+      <c r="B258" s="29"/>
+      <c r="C258" s="29"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="A259" s="26"/>
-      <c r="B259" s="26"/>
-      <c r="C259" s="26"/>
+      <c r="A259" s="29"/>
+      <c r="B259" s="29"/>
+      <c r="C259" s="29"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="A260" s="26"/>
-      <c r="B260" s="26"/>
-      <c r="C260" s="26"/>
+      <c r="A260" s="29"/>
+      <c r="B260" s="29"/>
+      <c r="C260" s="29"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="A261" s="26"/>
-      <c r="B261" s="26"/>
-      <c r="C261" s="26"/>
+      <c r="A261" s="29"/>
+      <c r="B261" s="29"/>
+      <c r="C261" s="29"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="A262" s="26"/>
-      <c r="B262" s="26"/>
-      <c r="C262" s="26"/>
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="A263" s="26"/>
-      <c r="B263" s="26"/>
-      <c r="C263" s="26"/>
+      <c r="A263" s="29"/>
+      <c r="B263" s="29"/>
+      <c r="C263" s="29"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="A264" s="26"/>
-      <c r="B264" s="26"/>
-      <c r="C264" s="26"/>
+      <c r="A264" s="29"/>
+      <c r="B264" s="29"/>
+      <c r="C264" s="29"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="A265" s="26"/>
-      <c r="B265" s="26"/>
-      <c r="C265" s="26"/>
+      <c r="A265" s="29"/>
+      <c r="B265" s="29"/>
+      <c r="C265" s="29"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="A266" s="26"/>
-      <c r="B266" s="26"/>
-      <c r="C266" s="26"/>
+      <c r="A266" s="29"/>
+      <c r="B266" s="29"/>
+      <c r="C266" s="29"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="A267" s="26"/>
-      <c r="B267" s="26"/>
-      <c r="C267" s="26"/>
+      <c r="A267" s="29"/>
+      <c r="B267" s="29"/>
+      <c r="C267" s="29"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="26"/>
-      <c r="B268" s="26"/>
-      <c r="C268" s="26"/>
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="A269" s="26"/>
-      <c r="B269" s="26"/>
-      <c r="C269" s="26"/>
+      <c r="A269" s="29"/>
+      <c r="B269" s="29"/>
+      <c r="C269" s="29"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="A270" s="26"/>
-      <c r="B270" s="26"/>
-      <c r="C270" s="26"/>
+      <c r="A270" s="29"/>
+      <c r="B270" s="29"/>
+      <c r="C270" s="29"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="A271" s="26"/>
-      <c r="B271" s="26"/>
-      <c r="C271" s="26"/>
+      <c r="A271" s="29"/>
+      <c r="B271" s="29"/>
+      <c r="C271" s="29"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="A272" s="26"/>
-      <c r="B272" s="26"/>
-      <c r="C272" s="26"/>
+      <c r="A272" s="29"/>
+      <c r="B272" s="29"/>
+      <c r="C272" s="29"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="A273" s="26"/>
-      <c r="B273" s="26"/>
-      <c r="C273" s="26"/>
+      <c r="A273" s="29"/>
+      <c r="B273" s="29"/>
+      <c r="C273" s="29"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="A274" s="26"/>
-      <c r="B274" s="26"/>
-      <c r="C274" s="26"/>
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="A275" s="26"/>
-      <c r="B275" s="26"/>
-      <c r="C275" s="26"/>
+      <c r="A275" s="29"/>
+      <c r="B275" s="29"/>
+      <c r="C275" s="29"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="A276" s="26"/>
-      <c r="B276" s="26"/>
-      <c r="C276" s="26"/>
+      <c r="A276" s="29"/>
+      <c r="B276" s="29"/>
+      <c r="C276" s="29"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="A277" s="26"/>
-      <c r="B277" s="26"/>
-      <c r="C277" s="26"/>
+      <c r="A277" s="29"/>
+      <c r="B277" s="29"/>
+      <c r="C277" s="29"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="A278" s="26"/>
-      <c r="B278" s="26"/>
-      <c r="C278" s="26"/>
+      <c r="A278" s="29"/>
+      <c r="B278" s="29"/>
+      <c r="C278" s="29"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="A279" s="26"/>
-      <c r="B279" s="26"/>
-      <c r="C279" s="26"/>
+      <c r="A279" s="29"/>
+      <c r="B279" s="29"/>
+      <c r="C279" s="29"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="A280" s="26"/>
-      <c r="B280" s="26"/>
-      <c r="C280" s="26"/>
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="A281" s="26"/>
-      <c r="B281" s="26"/>
-      <c r="C281" s="26"/>
+      <c r="A281" s="29"/>
+      <c r="B281" s="29"/>
+      <c r="C281" s="29"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="A282" s="26"/>
-      <c r="B282" s="26"/>
-      <c r="C282" s="26"/>
+      <c r="A282" s="29"/>
+      <c r="B282" s="29"/>
+      <c r="C282" s="29"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="A283" s="26"/>
-      <c r="B283" s="26"/>
-      <c r="C283" s="26"/>
+      <c r="A283" s="29"/>
+      <c r="B283" s="29"/>
+      <c r="C283" s="29"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="A284" s="26"/>
-      <c r="B284" s="26"/>
-      <c r="C284" s="26"/>
+      <c r="A284" s="29"/>
+      <c r="B284" s="29"/>
+      <c r="C284" s="29"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="A285" s="26"/>
-      <c r="B285" s="26"/>
-      <c r="C285" s="26"/>
+      <c r="A285" s="29"/>
+      <c r="B285" s="29"/>
+      <c r="C285" s="29"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="A286" s="26"/>
-      <c r="B286" s="26"/>
-      <c r="C286" s="26"/>
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="A287" s="26"/>
-      <c r="B287" s="26"/>
-      <c r="C287" s="26"/>
+      <c r="A287" s="29"/>
+      <c r="B287" s="29"/>
+      <c r="C287" s="29"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="26"/>
-      <c r="B288" s="26"/>
-      <c r="C288" s="26"/>
+      <c r="A288" s="29"/>
+      <c r="B288" s="29"/>
+      <c r="C288" s="29"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="A289" s="26"/>
-      <c r="B289" s="26"/>
-      <c r="C289" s="26"/>
+      <c r="A289" s="29"/>
+      <c r="B289" s="29"/>
+      <c r="C289" s="29"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="A290" s="26"/>
-      <c r="B290" s="26"/>
-      <c r="C290" s="26"/>
+      <c r="A290" s="29"/>
+      <c r="B290" s="29"/>
+      <c r="C290" s="29"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="A291" s="26"/>
-      <c r="B291" s="26"/>
-      <c r="C291" s="26"/>
+      <c r="A291" s="29"/>
+      <c r="B291" s="29"/>
+      <c r="C291" s="29"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="A292" s="26"/>
-      <c r="B292" s="26"/>
-      <c r="C292" s="26"/>
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="A293" s="26"/>
-      <c r="B293" s="26"/>
-      <c r="C293" s="26"/>
+      <c r="A293" s="29"/>
+      <c r="B293" s="29"/>
+      <c r="C293" s="29"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="A294" s="26"/>
-      <c r="B294" s="26"/>
-      <c r="C294" s="26"/>
+      <c r="A294" s="29"/>
+      <c r="B294" s="29"/>
+      <c r="C294" s="29"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="A295" s="26"/>
-      <c r="B295" s="26"/>
-      <c r="C295" s="26"/>
+      <c r="A295" s="29"/>
+      <c r="B295" s="29"/>
+      <c r="C295" s="29"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="A296" s="26"/>
-      <c r="B296" s="26"/>
-      <c r="C296" s="26"/>
+      <c r="A296" s="29"/>
+      <c r="B296" s="29"/>
+      <c r="C296" s="29"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="A297" s="26"/>
-      <c r="B297" s="26"/>
-      <c r="C297" s="26"/>
+      <c r="A297" s="29"/>
+      <c r="B297" s="29"/>
+      <c r="C297" s="29"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="A298" s="26"/>
-      <c r="B298" s="26"/>
-      <c r="C298" s="26"/>
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="A299" s="26"/>
-      <c r="B299" s="26"/>
-      <c r="C299" s="26"/>
+      <c r="A299" s="29"/>
+      <c r="B299" s="29"/>
+      <c r="C299" s="29"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="A300" s="26"/>
-      <c r="B300" s="26"/>
-      <c r="C300" s="26"/>
+      <c r="A300" s="29"/>
+      <c r="B300" s="29"/>
+      <c r="C300" s="29"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="A301" s="26"/>
-      <c r="B301" s="26"/>
-      <c r="C301" s="26"/>
+      <c r="A301" s="29"/>
+      <c r="B301" s="29"/>
+      <c r="C301" s="29"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="A302" s="26"/>
-      <c r="B302" s="26"/>
-      <c r="C302" s="26"/>
+      <c r="A302" s="29"/>
+      <c r="B302" s="29"/>
+      <c r="C302" s="29"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="A303" s="26"/>
-      <c r="B303" s="26"/>
-      <c r="C303" s="26"/>
+      <c r="A303" s="29"/>
+      <c r="B303" s="29"/>
+      <c r="C303" s="29"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="A304" s="26"/>
-      <c r="B304" s="26"/>
-      <c r="C304" s="26"/>
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="A305" s="26"/>
-      <c r="B305" s="26"/>
-      <c r="C305" s="26"/>
+      <c r="A305" s="29"/>
+      <c r="B305" s="29"/>
+      <c r="C305" s="29"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="A306" s="26"/>
-      <c r="B306" s="26"/>
-      <c r="C306" s="26"/>
+      <c r="A306" s="29"/>
+      <c r="B306" s="29"/>
+      <c r="C306" s="29"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="A307" s="26"/>
-      <c r="B307" s="26"/>
-      <c r="C307" s="26"/>
+      <c r="A307" s="29"/>
+      <c r="B307" s="29"/>
+      <c r="C307" s="29"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="26"/>
-      <c r="B308" s="26"/>
-      <c r="C308" s="26"/>
+      <c r="A308" s="29"/>
+      <c r="B308" s="29"/>
+      <c r="C308" s="29"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="A309" s="26"/>
-      <c r="B309" s="26"/>
-      <c r="C309" s="26"/>
+      <c r="A309" s="29"/>
+      <c r="B309" s="29"/>
+      <c r="C309" s="29"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="A310" s="26"/>
-      <c r="B310" s="26"/>
-      <c r="C310" s="26"/>
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="A311" s="26"/>
-      <c r="B311" s="26"/>
-      <c r="C311" s="26"/>
+      <c r="A311" s="29"/>
+      <c r="B311" s="29"/>
+      <c r="C311" s="29"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="A312" s="26"/>
-      <c r="B312" s="26"/>
-      <c r="C312" s="26"/>
+      <c r="A312" s="29"/>
+      <c r="B312" s="29"/>
+      <c r="C312" s="29"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="A313" s="26"/>
-      <c r="B313" s="26"/>
-      <c r="C313" s="26"/>
+      <c r="A313" s="29"/>
+      <c r="B313" s="29"/>
+      <c r="C313" s="29"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="A314" s="26"/>
-      <c r="B314" s="26"/>
-      <c r="C314" s="26"/>
+      <c r="A314" s="29"/>
+      <c r="B314" s="29"/>
+      <c r="C314" s="29"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="A315" s="26"/>
-      <c r="B315" s="26"/>
-      <c r="C315" s="26"/>
+      <c r="A315" s="29"/>
+      <c r="B315" s="29"/>
+      <c r="C315" s="29"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="A316" s="26"/>
-      <c r="B316" s="26"/>
-      <c r="C316" s="26"/>
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="A317" s="26"/>
-      <c r="B317" s="26"/>
-      <c r="C317" s="26"/>
+      <c r="A317" s="29"/>
+      <c r="B317" s="29"/>
+      <c r="C317" s="29"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="A318" s="26"/>
-      <c r="B318" s="26"/>
-      <c r="C318" s="26"/>
+      <c r="A318" s="29"/>
+      <c r="B318" s="29"/>
+      <c r="C318" s="29"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="A319" s="26"/>
-      <c r="B319" s="26"/>
-      <c r="C319" s="26"/>
+      <c r="A319" s="29"/>
+      <c r="B319" s="29"/>
+      <c r="C319" s="29"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="A320" s="26"/>
-      <c r="B320" s="26"/>
-      <c r="C320" s="26"/>
+      <c r="A320" s="29"/>
+      <c r="B320" s="29"/>
+      <c r="C320" s="29"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="A321" s="26"/>
-      <c r="B321" s="26"/>
-      <c r="C321" s="26"/>
+      <c r="A321" s="29"/>
+      <c r="B321" s="29"/>
+      <c r="C321" s="29"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="A322" s="26"/>
-      <c r="B322" s="26"/>
-      <c r="C322" s="26"/>
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="A323" s="26"/>
-      <c r="B323" s="26"/>
-      <c r="C323" s="26"/>
+      <c r="A323" s="29"/>
+      <c r="B323" s="29"/>
+      <c r="C323" s="29"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="A324" s="26"/>
-      <c r="B324" s="26"/>
-      <c r="C324" s="26"/>
+      <c r="A324" s="29"/>
+      <c r="B324" s="29"/>
+      <c r="C324" s="29"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="A325" s="26"/>
-      <c r="B325" s="26"/>
-      <c r="C325" s="26"/>
+      <c r="A325" s="29"/>
+      <c r="B325" s="29"/>
+      <c r="C325" s="29"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="A326" s="26"/>
-      <c r="B326" s="26"/>
-      <c r="C326" s="26"/>
+      <c r="A326" s="29"/>
+      <c r="B326" s="29"/>
+      <c r="C326" s="29"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="A327" s="26"/>
-      <c r="B327" s="26"/>
-      <c r="C327" s="26"/>
+      <c r="A327" s="29"/>
+      <c r="B327" s="29"/>
+      <c r="C327" s="29"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="26"/>
-      <c r="B328" s="26"/>
-      <c r="C328" s="26"/>
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="A329" s="26"/>
-      <c r="B329" s="26"/>
-      <c r="C329" s="26"/>
+      <c r="A329" s="29"/>
+      <c r="B329" s="29"/>
+      <c r="C329" s="29"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="A330" s="26"/>
-      <c r="B330" s="26"/>
-      <c r="C330" s="26"/>
+      <c r="A330" s="29"/>
+      <c r="B330" s="29"/>
+      <c r="C330" s="29"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="A331" s="26"/>
-      <c r="B331" s="26"/>
-      <c r="C331" s="26"/>
+      <c r="A331" s="29"/>
+      <c r="B331" s="29"/>
+      <c r="C331" s="29"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="A332" s="26"/>
-      <c r="B332" s="26"/>
-      <c r="C332" s="26"/>
+      <c r="A332" s="29"/>
+      <c r="B332" s="29"/>
+      <c r="C332" s="29"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="A333" s="26"/>
-      <c r="B333" s="26"/>
-      <c r="C333" s="26"/>
+      <c r="A333" s="29"/>
+      <c r="B333" s="29"/>
+      <c r="C333" s="29"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="A334" s="26"/>
-      <c r="B334" s="26"/>
-      <c r="C334" s="26"/>
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="A335" s="26"/>
-      <c r="B335" s="26"/>
-      <c r="C335" s="26"/>
+      <c r="A335" s="29"/>
+      <c r="B335" s="29"/>
+      <c r="C335" s="29"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="A336" s="26"/>
-      <c r="B336" s="26"/>
-      <c r="C336" s="26"/>
+      <c r="A336" s="29"/>
+      <c r="B336" s="29"/>
+      <c r="C336" s="29"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="A337" s="26"/>
-      <c r="B337" s="26"/>
-      <c r="C337" s="26"/>
+      <c r="A337" s="29"/>
+      <c r="B337" s="29"/>
+      <c r="C337" s="29"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="A338" s="26"/>
-      <c r="B338" s="26"/>
-      <c r="C338" s="26"/>
+      <c r="A338" s="29"/>
+      <c r="B338" s="29"/>
+      <c r="C338" s="29"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="A339" s="26"/>
-      <c r="B339" s="26"/>
-      <c r="C339" s="26"/>
+      <c r="A339" s="29"/>
+      <c r="B339" s="29"/>
+      <c r="C339" s="29"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="A340" s="26"/>
-      <c r="B340" s="26"/>
-      <c r="C340" s="26"/>
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="A341" s="26"/>
-      <c r="B341" s="26"/>
-      <c r="C341" s="26"/>
+      <c r="A341" s="29"/>
+      <c r="B341" s="29"/>
+      <c r="C341" s="29"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="A342" s="26"/>
-      <c r="B342" s="26"/>
-      <c r="C342" s="26"/>
+      <c r="A342" s="29"/>
+      <c r="B342" s="29"/>
+      <c r="C342" s="29"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="A343" s="26"/>
-      <c r="B343" s="26"/>
-      <c r="C343" s="26"/>
+      <c r="A343" s="29"/>
+      <c r="B343" s="29"/>
+      <c r="C343" s="29"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="A344" s="26"/>
-      <c r="B344" s="26"/>
-      <c r="C344" s="26"/>
+      <c r="A344" s="29"/>
+      <c r="B344" s="29"/>
+      <c r="C344" s="29"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="A345" s="26"/>
-      <c r="B345" s="26"/>
-      <c r="C345" s="26"/>
+      <c r="A345" s="29"/>
+      <c r="B345" s="29"/>
+      <c r="C345" s="29"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="A346" s="26"/>
-      <c r="B346" s="26"/>
-      <c r="C346" s="26"/>
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="A347" s="26"/>
-      <c r="B347" s="26"/>
-      <c r="C347" s="26"/>
+      <c r="A347" s="29"/>
+      <c r="B347" s="29"/>
+      <c r="C347" s="29"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="26"/>
-      <c r="B348" s="26"/>
-      <c r="C348" s="26"/>
+      <c r="A348" s="29"/>
+      <c r="B348" s="29"/>
+      <c r="C348" s="29"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="A349" s="26"/>
-      <c r="B349" s="26"/>
-      <c r="C349" s="26"/>
+      <c r="A349" s="29"/>
+      <c r="B349" s="29"/>
+      <c r="C349" s="29"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="A350" s="26"/>
-      <c r="B350" s="26"/>
-      <c r="C350" s="26"/>
+      <c r="A350" s="29"/>
+      <c r="B350" s="29"/>
+      <c r="C350" s="29"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="A351" s="26"/>
-      <c r="B351" s="26"/>
-      <c r="C351" s="26"/>
+      <c r="A351" s="29"/>
+      <c r="B351" s="29"/>
+      <c r="C351" s="29"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="A352" s="26"/>
-      <c r="B352" s="26"/>
-      <c r="C352" s="26"/>
+      <c r="A352" s="29"/>
+      <c r="B352" s="29"/>
+      <c r="C352" s="29"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="A353" s="26"/>
-      <c r="B353" s="26"/>
-      <c r="C353" s="26"/>
+      <c r="A353" s="29"/>
+      <c r="B353" s="29"/>
+      <c r="C353" s="29"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="A354" s="26"/>
-      <c r="B354" s="26"/>
-      <c r="C354" s="26"/>
+      <c r="A354" s="29"/>
+      <c r="B354" s="29"/>
+      <c r="C354" s="29"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="A355" s="26"/>
-      <c r="B355" s="26"/>
-      <c r="C355" s="26"/>
+      <c r="A355" s="29"/>
+      <c r="B355" s="29"/>
+      <c r="C355" s="29"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="A356" s="26"/>
-      <c r="B356" s="26"/>
-      <c r="C356" s="26"/>
+      <c r="A356" s="29"/>
+      <c r="B356" s="29"/>
+      <c r="C356" s="29"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="A357" s="26"/>
-      <c r="B357" s="26"/>
-      <c r="C357" s="26"/>
+      <c r="A357" s="29"/>
+      <c r="B357" s="29"/>
+      <c r="C357" s="29"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="A358" s="26"/>
-      <c r="B358" s="26"/>
-      <c r="C358" s="26"/>
+      <c r="A358" s="29"/>
+      <c r="B358" s="29"/>
+      <c r="C358" s="29"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="A359" s="26"/>
-      <c r="B359" s="26"/>
-      <c r="C359" s="26"/>
+      <c r="A359" s="29"/>
+      <c r="B359" s="29"/>
+      <c r="C359" s="29"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="A360" s="26"/>
-      <c r="B360" s="26"/>
-      <c r="C360" s="26"/>
+      <c r="A360" s="29"/>
+      <c r="B360" s="29"/>
+      <c r="C360" s="29"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="A361" s="26"/>
-      <c r="B361" s="26"/>
-      <c r="C361" s="26"/>
+      <c r="A361" s="29"/>
+      <c r="B361" s="29"/>
+      <c r="C361" s="29"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="A362" s="26"/>
-      <c r="B362" s="26"/>
-      <c r="C362" s="26"/>
+      <c r="A362" s="29"/>
+      <c r="B362" s="29"/>
+      <c r="C362" s="29"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="A363" s="26"/>
-      <c r="B363" s="26"/>
-      <c r="C363" s="26"/>
+      <c r="A363" s="29"/>
+      <c r="B363" s="29"/>
+      <c r="C363" s="29"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="A364" s="26"/>
-      <c r="B364" s="26"/>
-      <c r="C364" s="26"/>
+      <c r="A364" s="29"/>
+      <c r="B364" s="29"/>
+      <c r="C364" s="29"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="A365" s="26"/>
-      <c r="B365" s="26"/>
-      <c r="C365" s="26"/>
+      <c r="A365" s="29"/>
+      <c r="B365" s="29"/>
+      <c r="C365" s="29"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="A366" s="26"/>
-      <c r="B366" s="26"/>
-      <c r="C366" s="26"/>
+      <c r="A366" s="29"/>
+      <c r="B366" s="29"/>
+      <c r="C366" s="29"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="A367" s="26"/>
-      <c r="B367" s="26"/>
-      <c r="C367" s="26"/>
+      <c r="A367" s="29"/>
+      <c r="B367" s="29"/>
+      <c r="C367" s="29"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="26"/>
-      <c r="B368" s="26"/>
-      <c r="C368" s="26"/>
+      <c r="A368" s="29"/>
+      <c r="B368" s="29"/>
+      <c r="C368" s="29"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="A369" s="26"/>
-      <c r="B369" s="26"/>
-      <c r="C369" s="26"/>
+      <c r="A369" s="29"/>
+      <c r="B369" s="29"/>
+      <c r="C369" s="29"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="A370" s="26"/>
-      <c r="B370" s="26"/>
-      <c r="C370" s="26"/>
+      <c r="A370" s="29"/>
+      <c r="B370" s="29"/>
+      <c r="C370" s="29"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="A371" s="26"/>
-      <c r="B371" s="26"/>
-      <c r="C371" s="26"/>
+      <c r="A371" s="29"/>
+      <c r="B371" s="29"/>
+      <c r="C371" s="29"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="A372" s="26"/>
-      <c r="B372" s="26"/>
-      <c r="C372" s="26"/>
+      <c r="A372" s="29"/>
+      <c r="B372" s="29"/>
+      <c r="C372" s="29"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="A373" s="26"/>
-      <c r="B373" s="26"/>
-      <c r="C373" s="26"/>
+      <c r="A373" s="29"/>
+      <c r="B373" s="29"/>
+      <c r="C373" s="29"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="A374" s="26"/>
-      <c r="B374" s="26"/>
-      <c r="C374" s="26"/>
+      <c r="A374" s="29"/>
+      <c r="B374" s="29"/>
+      <c r="C374" s="29"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="A375" s="26"/>
-      <c r="B375" s="26"/>
-      <c r="C375" s="26"/>
+      <c r="A375" s="29"/>
+      <c r="B375" s="29"/>
+      <c r="C375" s="29"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="A376" s="26"/>
-      <c r="B376" s="26"/>
-      <c r="C376" s="26"/>
+      <c r="A376" s="29"/>
+      <c r="B376" s="29"/>
+      <c r="C376" s="29"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="A377" s="26"/>
-      <c r="B377" s="26"/>
-      <c r="C377" s="26"/>
+      <c r="A377" s="29"/>
+      <c r="B377" s="29"/>
+      <c r="C377" s="29"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="A378" s="26"/>
-      <c r="B378" s="26"/>
-      <c r="C378" s="26"/>
+      <c r="A378" s="29"/>
+      <c r="B378" s="29"/>
+      <c r="C378" s="29"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="A379" s="26"/>
-      <c r="B379" s="26"/>
-      <c r="C379" s="26"/>
+      <c r="A379" s="29"/>
+      <c r="B379" s="29"/>
+      <c r="C379" s="29"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="A380" s="26"/>
-      <c r="B380" s="26"/>
-      <c r="C380" s="26"/>
+      <c r="A380" s="29"/>
+      <c r="B380" s="29"/>
+      <c r="C380" s="29"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="A381" s="26"/>
-      <c r="B381" s="26"/>
-      <c r="C381" s="26"/>
+      <c r="A381" s="29"/>
+      <c r="B381" s="29"/>
+      <c r="C381" s="29"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="A382" s="26"/>
-      <c r="B382" s="26"/>
-      <c r="C382" s="26"/>
+      <c r="A382" s="29"/>
+      <c r="B382" s="29"/>
+      <c r="C382" s="29"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="A383" s="26"/>
-      <c r="B383" s="26"/>
-      <c r="C383" s="26"/>
+      <c r="A383" s="29"/>
+      <c r="B383" s="29"/>
+      <c r="C383" s="29"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="A384" s="26"/>
-      <c r="B384" s="26"/>
-      <c r="C384" s="26"/>
+      <c r="A384" s="29"/>
+      <c r="B384" s="29"/>
+      <c r="C384" s="29"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="A385" s="26"/>
-      <c r="B385" s="26"/>
-      <c r="C385" s="26"/>
+      <c r="A385" s="29"/>
+      <c r="B385" s="29"/>
+      <c r="C385" s="29"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="A386" s="26"/>
-      <c r="B386" s="26"/>
-      <c r="C386" s="26"/>
+      <c r="A386" s="29"/>
+      <c r="B386" s="29"/>
+      <c r="C386" s="29"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="A387" s="26"/>
-      <c r="B387" s="26"/>
-      <c r="C387" s="26"/>
+      <c r="A387" s="29"/>
+      <c r="B387" s="29"/>
+      <c r="C387" s="29"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="A388" s="26"/>
-      <c r="B388" s="26"/>
-      <c r="C388" s="26"/>
+      <c r="A388" s="29"/>
+      <c r="B388" s="29"/>
+      <c r="C388" s="29"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="A389" s="26"/>
-      <c r="B389" s="26"/>
-      <c r="C389" s="26"/>
+      <c r="A389" s="29"/>
+      <c r="B389" s="29"/>
+      <c r="C389" s="29"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="A390" s="26"/>
-      <c r="B390" s="26"/>
-      <c r="C390" s="26"/>
+      <c r="A390" s="29"/>
+      <c r="B390" s="29"/>
+      <c r="C390" s="29"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="A391" s="26"/>
-      <c r="B391" s="26"/>
-      <c r="C391" s="26"/>
+      <c r="A391" s="29"/>
+      <c r="B391" s="29"/>
+      <c r="C391" s="29"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="A392" s="26"/>
-      <c r="B392" s="26"/>
-      <c r="C392" s="26"/>
+      <c r="A392" s="29"/>
+      <c r="B392" s="29"/>
+      <c r="C392" s="29"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="A393" s="26"/>
-      <c r="B393" s="26"/>
-      <c r="C393" s="26"/>
+      <c r="A393" s="29"/>
+      <c r="B393" s="29"/>
+      <c r="C393" s="29"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="A394" s="26"/>
-      <c r="B394" s="26"/>
-      <c r="C394" s="26"/>
+      <c r="A394" s="29"/>
+      <c r="B394" s="29"/>
+      <c r="C394" s="29"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="A395" s="26"/>
-      <c r="B395" s="26"/>
-      <c r="C395" s="26"/>
+      <c r="A395" s="29"/>
+      <c r="B395" s="29"/>
+      <c r="C395" s="29"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="A396" s="26"/>
-      <c r="B396" s="26"/>
-      <c r="C396" s="26"/>
+      <c r="A396" s="29"/>
+      <c r="B396" s="29"/>
+      <c r="C396" s="29"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="A397" s="26"/>
-      <c r="B397" s="26"/>
-      <c r="C397" s="26"/>
+      <c r="A397" s="29"/>
+      <c r="B397" s="29"/>
+      <c r="C397" s="29"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="A398" s="26"/>
-      <c r="B398" s="26"/>
-      <c r="C398" s="26"/>
+      <c r="A398" s="29"/>
+      <c r="B398" s="29"/>
+      <c r="C398" s="29"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="A399" s="26"/>
-      <c r="B399" s="26"/>
-      <c r="C399" s="26"/>
+      <c r="A399" s="29"/>
+      <c r="B399" s="29"/>
+      <c r="C399" s="29"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="A400" s="26"/>
-      <c r="B400" s="26"/>
-      <c r="C400" s="26"/>
+      <c r="A400" s="29"/>
+      <c r="B400" s="29"/>
+      <c r="C400" s="29"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="A401" s="26"/>
-      <c r="B401" s="26"/>
-      <c r="C401" s="26"/>
+      <c r="A401" s="29"/>
+      <c r="B401" s="29"/>
+      <c r="C401" s="29"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="A402" s="26"/>
-      <c r="B402" s="26"/>
-      <c r="C402" s="26"/>
+      <c r="A402" s="29"/>
+      <c r="B402" s="29"/>
+      <c r="C402" s="29"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="A403" s="26"/>
-      <c r="B403" s="26"/>
-      <c r="C403" s="26"/>
+      <c r="A403" s="29"/>
+      <c r="B403" s="29"/>
+      <c r="C403" s="29"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="A404" s="26"/>
-      <c r="B404" s="26"/>
-      <c r="C404" s="26"/>
+      <c r="A404" s="29"/>
+      <c r="B404" s="29"/>
+      <c r="C404" s="29"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="A405" s="26"/>
-      <c r="B405" s="26"/>
-      <c r="C405" s="26"/>
+      <c r="A405" s="29"/>
+      <c r="B405" s="29"/>
+      <c r="C405" s="29"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="A406" s="26"/>
-      <c r="B406" s="26"/>
-      <c r="C406" s="26"/>
+      <c r="A406" s="29"/>
+      <c r="B406" s="29"/>
+      <c r="C406" s="29"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="A407" s="26"/>
-      <c r="B407" s="26"/>
-      <c r="C407" s="26"/>
+      <c r="A407" s="29"/>
+      <c r="B407" s="29"/>
+      <c r="C407" s="29"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="A408" s="26"/>
-      <c r="B408" s="26"/>
-      <c r="C408" s="26"/>
+      <c r="A408" s="29"/>
+      <c r="B408" s="29"/>
+      <c r="C408" s="29"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="A409" s="26"/>
-      <c r="B409" s="26"/>
-      <c r="C409" s="26"/>
+      <c r="A409" s="29"/>
+      <c r="B409" s="29"/>
+      <c r="C409" s="29"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="A410" s="26"/>
-      <c r="B410" s="26"/>
-      <c r="C410" s="26"/>
+      <c r="A410" s="29"/>
+      <c r="B410" s="29"/>
+      <c r="C410" s="29"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="A411" s="26"/>
-      <c r="B411" s="26"/>
-      <c r="C411" s="26"/>
+      <c r="A411" s="29"/>
+      <c r="B411" s="29"/>
+      <c r="C411" s="29"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="A412" s="26"/>
-      <c r="B412" s="26"/>
-      <c r="C412" s="26"/>
+      <c r="A412" s="29"/>
+      <c r="B412" s="29"/>
+      <c r="C412" s="29"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="A413" s="26"/>
-      <c r="B413" s="26"/>
-      <c r="C413" s="26"/>
+      <c r="A413" s="29"/>
+      <c r="B413" s="29"/>
+      <c r="C413" s="29"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="A414" s="26"/>
-      <c r="B414" s="26"/>
-      <c r="C414" s="26"/>
+      <c r="A414" s="29"/>
+      <c r="B414" s="29"/>
+      <c r="C414" s="29"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="A415" s="26"/>
-      <c r="B415" s="26"/>
-      <c r="C415" s="26"/>
+      <c r="A415" s="29"/>
+      <c r="B415" s="29"/>
+      <c r="C415" s="29"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="A416" s="26"/>
-      <c r="B416" s="26"/>
-      <c r="C416" s="26"/>
+      <c r="A416" s="29"/>
+      <c r="B416" s="29"/>
+      <c r="C416" s="29"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="A417" s="26"/>
-      <c r="B417" s="26"/>
-      <c r="C417" s="26"/>
+      <c r="A417" s="29"/>
+      <c r="B417" s="29"/>
+      <c r="C417" s="29"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="A418" s="26"/>
-      <c r="B418" s="26"/>
-      <c r="C418" s="26"/>
+      <c r="A418" s="29"/>
+      <c r="B418" s="29"/>
+      <c r="C418" s="29"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="A419" s="26"/>
-      <c r="B419" s="26"/>
-      <c r="C419" s="26"/>
+      <c r="A419" s="29"/>
+      <c r="B419" s="29"/>
+      <c r="C419" s="29"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="A420" s="26"/>
-      <c r="B420" s="26"/>
-      <c r="C420" s="26"/>
+      <c r="A420" s="29"/>
+      <c r="B420" s="29"/>
+      <c r="C420" s="29"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="A421" s="26"/>
-      <c r="B421" s="26"/>
-      <c r="C421" s="26"/>
+      <c r="A421" s="29"/>
+      <c r="B421" s="29"/>
+      <c r="C421" s="29"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="A422" s="26"/>
-      <c r="B422" s="26"/>
-      <c r="C422" s="26"/>
+      <c r="A422" s="29"/>
+      <c r="B422" s="29"/>
+      <c r="C422" s="29"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="A423" s="26"/>
-      <c r="B423" s="26"/>
-      <c r="C423" s="26"/>
+      <c r="A423" s="29"/>
+      <c r="B423" s="29"/>
+      <c r="C423" s="29"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="A424" s="26"/>
-      <c r="B424" s="26"/>
-      <c r="C424" s="26"/>
+      <c r="A424" s="29"/>
+      <c r="B424" s="29"/>
+      <c r="C424" s="29"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="A425" s="26"/>
-      <c r="B425" s="26"/>
-      <c r="C425" s="26"/>
+      <c r="A425" s="29"/>
+      <c r="B425" s="29"/>
+      <c r="C425" s="29"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="A426" s="26"/>
-      <c r="B426" s="26"/>
-      <c r="C426" s="26"/>
+      <c r="A426" s="29"/>
+      <c r="B426" s="29"/>
+      <c r="C426" s="29"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="A427" s="26"/>
-      <c r="B427" s="26"/>
-      <c r="C427" s="26"/>
+      <c r="A427" s="29"/>
+      <c r="B427" s="29"/>
+      <c r="C427" s="29"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="A428" s="26"/>
-      <c r="B428" s="26"/>
-      <c r="C428" s="26"/>
+      <c r="A428" s="29"/>
+      <c r="B428" s="29"/>
+      <c r="C428" s="29"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="A429" s="26"/>
-      <c r="B429" s="26"/>
-      <c r="C429" s="26"/>
+      <c r="A429" s="29"/>
+      <c r="B429" s="29"/>
+      <c r="C429" s="29"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="A430" s="26"/>
-      <c r="B430" s="26"/>
-      <c r="C430" s="26"/>
+      <c r="A430" s="29"/>
+      <c r="B430" s="29"/>
+      <c r="C430" s="29"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="A431" s="26"/>
-      <c r="B431" s="26"/>
-      <c r="C431" s="26"/>
+      <c r="A431" s="29"/>
+      <c r="B431" s="29"/>
+      <c r="C431" s="29"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="A432" s="26"/>
-      <c r="B432" s="26"/>
-      <c r="C432" s="26"/>
+      <c r="A432" s="29"/>
+      <c r="B432" s="29"/>
+      <c r="C432" s="29"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="A433" s="26"/>
-      <c r="B433" s="26"/>
-      <c r="C433" s="26"/>
+      <c r="A433" s="29"/>
+      <c r="B433" s="29"/>
+      <c r="C433" s="29"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="A434" s="26"/>
-      <c r="B434" s="26"/>
-      <c r="C434" s="26"/>
+      <c r="A434" s="29"/>
+      <c r="B434" s="29"/>
+      <c r="C434" s="29"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="26"/>
-      <c r="B435" s="26"/>
-      <c r="C435" s="26"/>
+      <c r="A435" s="29"/>
+      <c r="B435" s="29"/>
+      <c r="C435" s="29"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="26"/>
-      <c r="B436" s="26"/>
-      <c r="C436" s="26"/>
+      <c r="A436" s="29"/>
+      <c r="B436" s="29"/>
+      <c r="C436" s="29"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="26"/>
-      <c r="B437" s="26"/>
-      <c r="C437" s="26"/>
+      <c r="A437" s="29"/>
+      <c r="B437" s="29"/>
+      <c r="C437" s="29"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="26"/>
-      <c r="B438" s="26"/>
-      <c r="C438" s="26"/>
+      <c r="A438" s="29"/>
+      <c r="B438" s="29"/>
+      <c r="C438" s="29"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="26"/>
-      <c r="B439" s="26"/>
-      <c r="C439" s="26"/>
+      <c r="A439" s="29"/>
+      <c r="B439" s="29"/>
+      <c r="C439" s="29"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="26"/>
-      <c r="B440" s="26"/>
-      <c r="C440" s="26"/>
+      <c r="A440" s="29"/>
+      <c r="B440" s="29"/>
+      <c r="C440" s="29"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="A441" s="26"/>
-      <c r="B441" s="26"/>
-      <c r="C441" s="26"/>
+      <c r="A441" s="29"/>
+      <c r="B441" s="29"/>
+      <c r="C441" s="29"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="A442" s="26"/>
-      <c r="B442" s="26"/>
-      <c r="C442" s="26"/>
+      <c r="A442" s="29"/>
+      <c r="B442" s="29"/>
+      <c r="C442" s="29"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="26"/>
-      <c r="B443" s="26"/>
-      <c r="C443" s="26"/>
+      <c r="A443" s="29"/>
+      <c r="B443" s="29"/>
+      <c r="C443" s="29"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="26"/>
-      <c r="B444" s="26"/>
-      <c r="C444" s="26"/>
+      <c r="A444" s="29"/>
+      <c r="B444" s="29"/>
+      <c r="C444" s="29"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="26"/>
-      <c r="B445" s="26"/>
-      <c r="C445" s="26"/>
+      <c r="A445" s="29"/>
+      <c r="B445" s="29"/>
+      <c r="C445" s="29"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="26"/>
-      <c r="B446" s="26"/>
-      <c r="C446" s="26"/>
+      <c r="A446" s="29"/>
+      <c r="B446" s="29"/>
+      <c r="C446" s="29"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="A447" s="26"/>
-      <c r="B447" s="26"/>
-      <c r="C447" s="26"/>
+      <c r="A447" s="29"/>
+      <c r="B447" s="29"/>
+      <c r="C447" s="29"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="A448" s="26"/>
-      <c r="B448" s="26"/>
-      <c r="C448" s="26"/>
+      <c r="A448" s="29"/>
+      <c r="B448" s="29"/>
+      <c r="C448" s="29"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="A449" s="26"/>
-      <c r="B449" s="26"/>
-      <c r="C449" s="26"/>
+      <c r="A449" s="29"/>
+      <c r="B449" s="29"/>
+      <c r="C449" s="29"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="A450" s="26"/>
-      <c r="B450" s="26"/>
-      <c r="C450" s="26"/>
+      <c r="A450" s="29"/>
+      <c r="B450" s="29"/>
+      <c r="C450" s="29"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="A451" s="26"/>
-      <c r="B451" s="26"/>
-      <c r="C451" s="26"/>
+      <c r="A451" s="29"/>
+      <c r="B451" s="29"/>
+      <c r="C451" s="29"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="A452" s="26"/>
-      <c r="B452" s="26"/>
-      <c r="C452" s="26"/>
+      <c r="A452" s="29"/>
+      <c r="B452" s="29"/>
+      <c r="C452" s="29"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="26"/>
-      <c r="B453" s="26"/>
-      <c r="C453" s="26"/>
+      <c r="A453" s="29"/>
+      <c r="B453" s="29"/>
+      <c r="C453" s="29"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="26"/>
-      <c r="B454" s="26"/>
-      <c r="C454" s="26"/>
+      <c r="A454" s="29"/>
+      <c r="B454" s="29"/>
+      <c r="C454" s="29"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="26"/>
-      <c r="B455" s="26"/>
-      <c r="C455" s="26"/>
+      <c r="A455" s="29"/>
+      <c r="B455" s="29"/>
+      <c r="C455" s="29"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="26"/>
-      <c r="B456" s="26"/>
-      <c r="C456" s="26"/>
+      <c r="A456" s="29"/>
+      <c r="B456" s="29"/>
+      <c r="C456" s="29"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="A457" s="26"/>
-      <c r="B457" s="26"/>
-      <c r="C457" s="26"/>
+      <c r="A457" s="29"/>
+      <c r="B457" s="29"/>
+      <c r="C457" s="29"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="A458" s="26"/>
-      <c r="B458" s="26"/>
-      <c r="C458" s="26"/>
+      <c r="A458" s="29"/>
+      <c r="B458" s="29"/>
+      <c r="C458" s="29"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="A459" s="26"/>
-      <c r="B459" s="26"/>
-      <c r="C459" s="26"/>
+      <c r="A459" s="29"/>
+      <c r="B459" s="29"/>
+      <c r="C459" s="29"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="A460" s="26"/>
-      <c r="B460" s="26"/>
-      <c r="C460" s="26"/>
+      <c r="A460" s="29"/>
+      <c r="B460" s="29"/>
+      <c r="C460" s="29"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="A461" s="26"/>
-      <c r="B461" s="26"/>
-      <c r="C461" s="26"/>
+      <c r="A461" s="29"/>
+      <c r="B461" s="29"/>
+      <c r="C461" s="29"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="A462" s="26"/>
-      <c r="B462" s="26"/>
-      <c r="C462" s="26"/>
+      <c r="A462" s="29"/>
+      <c r="B462" s="29"/>
+      <c r="C462" s="29"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="A463" s="26"/>
-      <c r="B463" s="26"/>
-      <c r="C463" s="26"/>
+      <c r="A463" s="29"/>
+      <c r="B463" s="29"/>
+      <c r="C463" s="29"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="A464" s="26"/>
-      <c r="B464" s="26"/>
-      <c r="C464" s="26"/>
+      <c r="A464" s="29"/>
+      <c r="B464" s="29"/>
+      <c r="C464" s="29"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="A465" s="26"/>
-      <c r="B465" s="26"/>
-      <c r="C465" s="26"/>
+      <c r="A465" s="29"/>
+      <c r="B465" s="29"/>
+      <c r="C465" s="29"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="A466" s="26"/>
-      <c r="B466" s="26"/>
-      <c r="C466" s="26"/>
+      <c r="A466" s="29"/>
+      <c r="B466" s="29"/>
+      <c r="C466" s="29"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="A467" s="26"/>
-      <c r="B467" s="26"/>
-      <c r="C467" s="26"/>
+      <c r="A467" s="29"/>
+      <c r="B467" s="29"/>
+      <c r="C467" s="29"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="A468" s="26"/>
-      <c r="B468" s="26"/>
-      <c r="C468" s="26"/>
+      <c r="A468" s="29"/>
+      <c r="B468" s="29"/>
+      <c r="C468" s="29"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="A469" s="26"/>
-      <c r="B469" s="26"/>
-      <c r="C469" s="26"/>
+      <c r="A469" s="29"/>
+      <c r="B469" s="29"/>
+      <c r="C469" s="29"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="A470" s="26"/>
-      <c r="B470" s="26"/>
-      <c r="C470" s="26"/>
+      <c r="A470" s="29"/>
+      <c r="B470" s="29"/>
+      <c r="C470" s="29"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="A471" s="26"/>
-      <c r="B471" s="26"/>
-      <c r="C471" s="26"/>
+      <c r="A471" s="29"/>
+      <c r="B471" s="29"/>
+      <c r="C471" s="29"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="A472" s="26"/>
-      <c r="B472" s="26"/>
-      <c r="C472" s="26"/>
+      <c r="A472" s="29"/>
+      <c r="B472" s="29"/>
+      <c r="C472" s="29"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="A473" s="26"/>
-      <c r="B473" s="26"/>
-      <c r="C473" s="26"/>
+      <c r="A473" s="29"/>
+      <c r="B473" s="29"/>
+      <c r="C473" s="29"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="A474" s="26"/>
-      <c r="B474" s="26"/>
-      <c r="C474" s="26"/>
+      <c r="A474" s="29"/>
+      <c r="B474" s="29"/>
+      <c r="C474" s="29"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="A475" s="26"/>
-      <c r="B475" s="26"/>
-      <c r="C475" s="26"/>
+      <c r="A475" s="29"/>
+      <c r="B475" s="29"/>
+      <c r="C475" s="29"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="A476" s="26"/>
-      <c r="B476" s="26"/>
-      <c r="C476" s="26"/>
+      <c r="A476" s="29"/>
+      <c r="B476" s="29"/>
+      <c r="C476" s="29"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="A477" s="26"/>
-      <c r="B477" s="26"/>
-      <c r="C477" s="26"/>
+      <c r="A477" s="29"/>
+      <c r="B477" s="29"/>
+      <c r="C477" s="29"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="A478" s="26"/>
-      <c r="B478" s="26"/>
-      <c r="C478" s="26"/>
+      <c r="A478" s="29"/>
+      <c r="B478" s="29"/>
+      <c r="C478" s="29"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="A479" s="26"/>
-      <c r="B479" s="26"/>
-      <c r="C479" s="26"/>
+      <c r="A479" s="29"/>
+      <c r="B479" s="29"/>
+      <c r="C479" s="29"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="A480" s="26"/>
-      <c r="B480" s="26"/>
-      <c r="C480" s="26"/>
+      <c r="A480" s="29"/>
+      <c r="B480" s="29"/>
+      <c r="C480" s="29"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="A481" s="26"/>
-      <c r="B481" s="26"/>
-      <c r="C481" s="26"/>
+      <c r="A481" s="29"/>
+      <c r="B481" s="29"/>
+      <c r="C481" s="29"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="A482" s="26"/>
-      <c r="B482" s="26"/>
-      <c r="C482" s="26"/>
+      <c r="A482" s="29"/>
+      <c r="B482" s="29"/>
+      <c r="C482" s="29"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="A483" s="26"/>
-      <c r="B483" s="26"/>
-      <c r="C483" s="26"/>
+      <c r="A483" s="29"/>
+      <c r="B483" s="29"/>
+      <c r="C483" s="29"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="A484" s="26"/>
-      <c r="B484" s="26"/>
-      <c r="C484" s="26"/>
+      <c r="A484" s="29"/>
+      <c r="B484" s="29"/>
+      <c r="C484" s="29"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="A485" s="26"/>
-      <c r="B485" s="26"/>
-      <c r="C485" s="26"/>
+      <c r="A485" s="29"/>
+      <c r="B485" s="29"/>
+      <c r="C485" s="29"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="A486" s="26"/>
-      <c r="B486" s="26"/>
-      <c r="C486" s="26"/>
+      <c r="A486" s="29"/>
+      <c r="B486" s="29"/>
+      <c r="C486" s="29"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="A487" s="26"/>
-      <c r="B487" s="26"/>
-      <c r="C487" s="26"/>
+      <c r="A487" s="29"/>
+      <c r="B487" s="29"/>
+      <c r="C487" s="29"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="A488" s="26"/>
-      <c r="B488" s="26"/>
-      <c r="C488" s="26"/>
+      <c r="A488" s="29"/>
+      <c r="B488" s="29"/>
+      <c r="C488" s="29"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="A489" s="26"/>
-      <c r="B489" s="26"/>
-      <c r="C489" s="26"/>
+      <c r="A489" s="29"/>
+      <c r="B489" s="29"/>
+      <c r="C489" s="29"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="A490" s="26"/>
-      <c r="B490" s="26"/>
-      <c r="C490" s="26"/>
+      <c r="A490" s="29"/>
+      <c r="B490" s="29"/>
+      <c r="C490" s="29"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="A491" s="26"/>
-      <c r="B491" s="26"/>
-      <c r="C491" s="26"/>
+      <c r="A491" s="29"/>
+      <c r="B491" s="29"/>
+      <c r="C491" s="29"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="A492" s="26"/>
-      <c r="B492" s="26"/>
-      <c r="C492" s="26"/>
+      <c r="A492" s="29"/>
+      <c r="B492" s="29"/>
+      <c r="C492" s="29"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="A493" s="26"/>
-      <c r="B493" s="26"/>
-      <c r="C493" s="26"/>
+      <c r="A493" s="29"/>
+      <c r="B493" s="29"/>
+      <c r="C493" s="29"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="A494" s="26"/>
-      <c r="B494" s="26"/>
-      <c r="C494" s="26"/>
+      <c r="A494" s="29"/>
+      <c r="B494" s="29"/>
+      <c r="C494" s="29"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="A495" s="26"/>
-      <c r="B495" s="26"/>
-      <c r="C495" s="26"/>
+      <c r="A495" s="29"/>
+      <c r="B495" s="29"/>
+      <c r="C495" s="29"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="A496" s="26"/>
-      <c r="B496" s="26"/>
-      <c r="C496" s="26"/>
+      <c r="A496" s="29"/>
+      <c r="B496" s="29"/>
+      <c r="C496" s="29"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="A497" s="26"/>
-      <c r="B497" s="26"/>
-      <c r="C497" s="26"/>
+      <c r="A497" s="29"/>
+      <c r="B497" s="29"/>
+      <c r="C497" s="29"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="A498" s="26"/>
-      <c r="B498" s="26"/>
-      <c r="C498" s="26"/>
+      <c r="A498" s="29"/>
+      <c r="B498" s="29"/>
+      <c r="C498" s="29"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="A499" s="26"/>
-      <c r="B499" s="26"/>
-      <c r="C499" s="26"/>
+      <c r="A499" s="29"/>
+      <c r="B499" s="29"/>
+      <c r="C499" s="29"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="A500" s="26"/>
-      <c r="B500" s="26"/>
-      <c r="C500" s="26"/>
+      <c r="A500" s="29"/>
+      <c r="B500" s="29"/>
+      <c r="C500" s="29"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="A501" s="26"/>
-      <c r="B501" s="26"/>
-      <c r="C501" s="26"/>
+      <c r="A501" s="29"/>
+      <c r="B501" s="29"/>
+      <c r="C501" s="29"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="A502" s="26"/>
-      <c r="B502" s="26"/>
-      <c r="C502" s="26"/>
+      <c r="A502" s="29"/>
+      <c r="B502" s="29"/>
+      <c r="C502" s="29"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="A503" s="26"/>
-      <c r="B503" s="26"/>
-      <c r="C503" s="26"/>
+      <c r="A503" s="29"/>
+      <c r="B503" s="29"/>
+      <c r="C503" s="29"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="A504" s="26"/>
-      <c r="B504" s="26"/>
-      <c r="C504" s="26"/>
+      <c r="A504" s="29"/>
+      <c r="B504" s="29"/>
+      <c r="C504" s="29"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="A505" s="26"/>
-      <c r="B505" s="26"/>
-      <c r="C505" s="26"/>
+      <c r="A505" s="29"/>
+      <c r="B505" s="29"/>
+      <c r="C505" s="29"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="A506" s="26"/>
-      <c r="B506" s="26"/>
-      <c r="C506" s="26"/>
+      <c r="A506" s="29"/>
+      <c r="B506" s="29"/>
+      <c r="C506" s="29"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="A507" s="26"/>
-      <c r="B507" s="26"/>
-      <c r="C507" s="26"/>
+      <c r="A507" s="29"/>
+      <c r="B507" s="29"/>
+      <c r="C507" s="29"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="A508" s="26"/>
-      <c r="B508" s="26"/>
-      <c r="C508" s="26"/>
+      <c r="A508" s="29"/>
+      <c r="B508" s="29"/>
+      <c r="C508" s="29"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="A509" s="26"/>
-      <c r="B509" s="26"/>
-      <c r="C509" s="26"/>
+      <c r="A509" s="29"/>
+      <c r="B509" s="29"/>
+      <c r="C509" s="29"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="A510" s="26"/>
-      <c r="B510" s="26"/>
-      <c r="C510" s="26"/>
+      <c r="A510" s="29"/>
+      <c r="B510" s="29"/>
+      <c r="C510" s="29"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="A511" s="26"/>
-      <c r="B511" s="26"/>
-      <c r="C511" s="26"/>
+      <c r="A511" s="29"/>
+      <c r="B511" s="29"/>
+      <c r="C511" s="29"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="A512" s="26"/>
-      <c r="B512" s="26"/>
-      <c r="C512" s="26"/>
+      <c r="A512" s="29"/>
+      <c r="B512" s="29"/>
+      <c r="C512" s="29"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="A513" s="26"/>
-      <c r="B513" s="26"/>
-      <c r="C513" s="26"/>
+      <c r="A513" s="29"/>
+      <c r="B513" s="29"/>
+      <c r="C513" s="29"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="A514" s="26"/>
-      <c r="B514" s="26"/>
-      <c r="C514" s="26"/>
+      <c r="A514" s="29"/>
+      <c r="B514" s="29"/>
+      <c r="C514" s="29"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="A515" s="26"/>
-      <c r="B515" s="26"/>
-      <c r="C515" s="26"/>
+      <c r="A515" s="29"/>
+      <c r="B515" s="29"/>
+      <c r="C515" s="29"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="A516" s="26"/>
-      <c r="B516" s="26"/>
-      <c r="C516" s="26"/>
+      <c r="A516" s="29"/>
+      <c r="B516" s="29"/>
+      <c r="C516" s="29"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="A517" s="26"/>
-      <c r="B517" s="26"/>
-      <c r="C517" s="26"/>
+      <c r="A517" s="29"/>
+      <c r="B517" s="29"/>
+      <c r="C517" s="29"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="A518" s="26"/>
-      <c r="B518" s="26"/>
-      <c r="C518" s="26"/>
+      <c r="A518" s="29"/>
+      <c r="B518" s="29"/>
+      <c r="C518" s="29"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="A519" s="26"/>
-      <c r="B519" s="26"/>
-      <c r="C519" s="26"/>
+      <c r="A519" s="29"/>
+      <c r="B519" s="29"/>
+      <c r="C519" s="29"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="A520" s="26"/>
-      <c r="B520" s="26"/>
-      <c r="C520" s="26"/>
+      <c r="A520" s="29"/>
+      <c r="B520" s="29"/>
+      <c r="C520" s="29"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="A521" s="26"/>
-      <c r="B521" s="26"/>
-      <c r="C521" s="26"/>
+      <c r="A521" s="29"/>
+      <c r="B521" s="29"/>
+      <c r="C521" s="29"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="A522" s="26"/>
-      <c r="B522" s="26"/>
-      <c r="C522" s="26"/>
+      <c r="A522" s="29"/>
+      <c r="B522" s="29"/>
+      <c r="C522" s="29"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="A523" s="26"/>
-      <c r="B523" s="26"/>
-      <c r="C523" s="26"/>
+      <c r="A523" s="29"/>
+      <c r="B523" s="29"/>
+      <c r="C523" s="29"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="A524" s="26"/>
-      <c r="B524" s="26"/>
-      <c r="C524" s="26"/>
+      <c r="A524" s="29"/>
+      <c r="B524" s="29"/>
+      <c r="C524" s="29"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="A525" s="26"/>
-      <c r="B525" s="26"/>
-      <c r="C525" s="26"/>
+      <c r="A525" s="29"/>
+      <c r="B525" s="29"/>
+      <c r="C525" s="29"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="A526" s="26"/>
-      <c r="B526" s="26"/>
-      <c r="C526" s="26"/>
+      <c r="A526" s="29"/>
+      <c r="B526" s="29"/>
+      <c r="C526" s="29"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="A527" s="26"/>
-      <c r="B527" s="26"/>
-      <c r="C527" s="26"/>
+      <c r="A527" s="29"/>
+      <c r="B527" s="29"/>
+      <c r="C527" s="29"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="A528" s="26"/>
-      <c r="B528" s="26"/>
-      <c r="C528" s="26"/>
+      <c r="A528" s="29"/>
+      <c r="B528" s="29"/>
+      <c r="C528" s="29"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="A529" s="26"/>
-      <c r="B529" s="26"/>
-      <c r="C529" s="26"/>
+      <c r="A529" s="29"/>
+      <c r="B529" s="29"/>
+      <c r="C529" s="29"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="A530" s="26"/>
-      <c r="B530" s="26"/>
-      <c r="C530" s="26"/>
+      <c r="A530" s="29"/>
+      <c r="B530" s="29"/>
+      <c r="C530" s="29"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="A531" s="26"/>
-      <c r="B531" s="26"/>
-      <c r="C531" s="26"/>
+      <c r="A531" s="29"/>
+      <c r="B531" s="29"/>
+      <c r="C531" s="29"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="A532" s="26"/>
-      <c r="B532" s="26"/>
-      <c r="C532" s="26"/>
+      <c r="A532" s="29"/>
+      <c r="B532" s="29"/>
+      <c r="C532" s="29"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="A533" s="26"/>
-      <c r="B533" s="26"/>
-      <c r="C533" s="26"/>
+      <c r="A533" s="29"/>
+      <c r="B533" s="29"/>
+      <c r="C533" s="29"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="A534" s="26"/>
-      <c r="B534" s="26"/>
-      <c r="C534" s="26"/>
+      <c r="A534" s="29"/>
+      <c r="B534" s="29"/>
+      <c r="C534" s="29"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="A535" s="26"/>
-      <c r="B535" s="26"/>
-      <c r="C535" s="26"/>
+      <c r="A535" s="29"/>
+      <c r="B535" s="29"/>
+      <c r="C535" s="29"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="A536" s="26"/>
-      <c r="B536" s="26"/>
-      <c r="C536" s="26"/>
+      <c r="A536" s="29"/>
+      <c r="B536" s="29"/>
+      <c r="C536" s="29"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="A537" s="26"/>
-      <c r="B537" s="26"/>
-      <c r="C537" s="26"/>
+      <c r="A537" s="29"/>
+      <c r="B537" s="29"/>
+      <c r="C537" s="29"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="A538" s="26"/>
-      <c r="B538" s="26"/>
-      <c r="C538" s="26"/>
+      <c r="A538" s="29"/>
+      <c r="B538" s="29"/>
+      <c r="C538" s="29"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="A539" s="26"/>
-      <c r="B539" s="26"/>
-      <c r="C539" s="26"/>
+      <c r="A539" s="29"/>
+      <c r="B539" s="29"/>
+      <c r="C539" s="29"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="A540" s="26"/>
-      <c r="B540" s="26"/>
-      <c r="C540" s="26"/>
+      <c r="A540" s="29"/>
+      <c r="B540" s="29"/>
+      <c r="C540" s="29"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="A541" s="26"/>
-      <c r="B541" s="26"/>
-      <c r="C541" s="26"/>
+      <c r="A541" s="29"/>
+      <c r="B541" s="29"/>
+      <c r="C541" s="29"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="A542" s="26"/>
-      <c r="B542" s="26"/>
-      <c r="C542" s="26"/>
+      <c r="A542" s="29"/>
+      <c r="B542" s="29"/>
+      <c r="C542" s="29"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="A543" s="26"/>
-      <c r="B543" s="26"/>
-      <c r="C543" s="26"/>
+      <c r="A543" s="29"/>
+      <c r="B543" s="29"/>
+      <c r="C543" s="29"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="A544" s="26"/>
-      <c r="B544" s="26"/>
-      <c r="C544" s="26"/>
+      <c r="A544" s="29"/>
+      <c r="B544" s="29"/>
+      <c r="C544" s="29"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="A545" s="26"/>
-      <c r="B545" s="26"/>
-      <c r="C545" s="26"/>
+      <c r="A545" s="29"/>
+      <c r="B545" s="29"/>
+      <c r="C545" s="29"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="A546" s="26"/>
-      <c r="B546" s="26"/>
-      <c r="C546" s="26"/>
+      <c r="A546" s="29"/>
+      <c r="B546" s="29"/>
+      <c r="C546" s="29"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="A547" s="26"/>
-      <c r="B547" s="26"/>
-      <c r="C547" s="26"/>
+      <c r="A547" s="29"/>
+      <c r="B547" s="29"/>
+      <c r="C547" s="29"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="A548" s="26"/>
-      <c r="B548" s="26"/>
-      <c r="C548" s="26"/>
+      <c r="A548" s="29"/>
+      <c r="B548" s="29"/>
+      <c r="C548" s="29"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="A549" s="26"/>
-      <c r="B549" s="26"/>
-      <c r="C549" s="26"/>
+      <c r="A549" s="29"/>
+      <c r="B549" s="29"/>
+      <c r="C549" s="29"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="A550" s="26"/>
-      <c r="B550" s="26"/>
-      <c r="C550" s="26"/>
+      <c r="A550" s="29"/>
+      <c r="B550" s="29"/>
+      <c r="C550" s="29"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="A551" s="26"/>
-      <c r="B551" s="26"/>
-      <c r="C551" s="26"/>
+      <c r="A551" s="29"/>
+      <c r="B551" s="29"/>
+      <c r="C551" s="29"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="A552" s="26"/>
-      <c r="B552" s="26"/>
-      <c r="C552" s="26"/>
+      <c r="A552" s="29"/>
+      <c r="B552" s="29"/>
+      <c r="C552" s="29"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="A553" s="26"/>
-      <c r="B553" s="26"/>
-      <c r="C553" s="26"/>
+      <c r="A553" s="29"/>
+      <c r="B553" s="29"/>
+      <c r="C553" s="29"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="A554" s="26"/>
-      <c r="B554" s="26"/>
-      <c r="C554" s="26"/>
+      <c r="A554" s="29"/>
+      <c r="B554" s="29"/>
+      <c r="C554" s="29"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="A555" s="26"/>
-      <c r="B555" s="26"/>
-      <c r="C555" s="26"/>
+      <c r="A555" s="29"/>
+      <c r="B555" s="29"/>
+      <c r="C555" s="29"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="A556" s="26"/>
-      <c r="B556" s="26"/>
-      <c r="C556" s="26"/>
+      <c r="A556" s="29"/>
+      <c r="B556" s="29"/>
+      <c r="C556" s="29"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="A557" s="26"/>
-      <c r="B557" s="26"/>
-      <c r="C557" s="26"/>
+      <c r="A557" s="29"/>
+      <c r="B557" s="29"/>
+      <c r="C557" s="29"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="A558" s="26"/>
-      <c r="B558" s="26"/>
-      <c r="C558" s="26"/>
+      <c r="A558" s="29"/>
+      <c r="B558" s="29"/>
+      <c r="C558" s="29"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="A559" s="26"/>
-      <c r="B559" s="26"/>
-      <c r="C559" s="26"/>
+      <c r="A559" s="29"/>
+      <c r="B559" s="29"/>
+      <c r="C559" s="29"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="A560" s="26"/>
-      <c r="B560" s="26"/>
-      <c r="C560" s="26"/>
+      <c r="A560" s="29"/>
+      <c r="B560" s="29"/>
+      <c r="C560" s="29"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="A561" s="26"/>
-      <c r="B561" s="26"/>
-      <c r="C561" s="26"/>
+      <c r="A561" s="29"/>
+      <c r="B561" s="29"/>
+      <c r="C561" s="29"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="A562" s="26"/>
-      <c r="B562" s="26"/>
-      <c r="C562" s="26"/>
+      <c r="A562" s="29"/>
+      <c r="B562" s="29"/>
+      <c r="C562" s="29"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="A563" s="26"/>
-      <c r="B563" s="26"/>
-      <c r="C563" s="26"/>
+      <c r="A563" s="29"/>
+      <c r="B563" s="29"/>
+      <c r="C563" s="29"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="A564" s="26"/>
-      <c r="B564" s="26"/>
-      <c r="C564" s="26"/>
+      <c r="A564" s="29"/>
+      <c r="B564" s="29"/>
+      <c r="C564" s="29"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="A565" s="26"/>
-      <c r="B565" s="26"/>
-      <c r="C565" s="26"/>
+      <c r="A565" s="29"/>
+      <c r="B565" s="29"/>
+      <c r="C565" s="29"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="A566" s="26"/>
-      <c r="B566" s="26"/>
-      <c r="C566" s="26"/>
+      <c r="A566" s="29"/>
+      <c r="B566" s="29"/>
+      <c r="C566" s="29"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="A567" s="26"/>
-      <c r="B567" s="26"/>
-      <c r="C567" s="26"/>
+      <c r="A567" s="29"/>
+      <c r="B567" s="29"/>
+      <c r="C567" s="29"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="A568" s="26"/>
-      <c r="B568" s="26"/>
-      <c r="C568" s="26"/>
+      <c r="A568" s="29"/>
+      <c r="B568" s="29"/>
+      <c r="C568" s="29"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="A569" s="26"/>
-      <c r="B569" s="26"/>
-      <c r="C569" s="26"/>
+      <c r="A569" s="29"/>
+      <c r="B569" s="29"/>
+      <c r="C569" s="29"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="A570" s="26"/>
-      <c r="B570" s="26"/>
-      <c r="C570" s="26"/>
+      <c r="A570" s="29"/>
+      <c r="B570" s="29"/>
+      <c r="C570" s="29"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="A571" s="26"/>
-      <c r="B571" s="26"/>
-      <c r="C571" s="26"/>
+      <c r="A571" s="29"/>
+      <c r="B571" s="29"/>
+      <c r="C571" s="29"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="A572" s="26"/>
-      <c r="B572" s="26"/>
-      <c r="C572" s="26"/>
+      <c r="A572" s="29"/>
+      <c r="B572" s="29"/>
+      <c r="C572" s="29"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="A573" s="26"/>
-      <c r="B573" s="26"/>
-      <c r="C573" s="26"/>
+      <c r="A573" s="29"/>
+      <c r="B573" s="29"/>
+      <c r="C573" s="29"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="A574" s="26"/>
-      <c r="B574" s="26"/>
-      <c r="C574" s="26"/>
+      <c r="A574" s="29"/>
+      <c r="B574" s="29"/>
+      <c r="C574" s="29"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="A575" s="26"/>
-      <c r="B575" s="26"/>
-      <c r="C575" s="26"/>
+      <c r="A575" s="29"/>
+      <c r="B575" s="29"/>
+      <c r="C575" s="29"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="A576" s="26"/>
-      <c r="B576" s="26"/>
-      <c r="C576" s="26"/>
+      <c r="A576" s="29"/>
+      <c r="B576" s="29"/>
+      <c r="C576" s="29"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="A577" s="26"/>
-      <c r="B577" s="26"/>
-      <c r="C577" s="26"/>
+      <c r="A577" s="29"/>
+      <c r="B577" s="29"/>
+      <c r="C577" s="29"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="A578" s="26"/>
-      <c r="B578" s="26"/>
-      <c r="C578" s="26"/>
+      <c r="A578" s="29"/>
+      <c r="B578" s="29"/>
+      <c r="C578" s="29"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="A579" s="26"/>
-      <c r="B579" s="26"/>
-      <c r="C579" s="26"/>
+      <c r="A579" s="29"/>
+      <c r="B579" s="29"/>
+      <c r="C579" s="29"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="A580" s="26"/>
-      <c r="B580" s="26"/>
-      <c r="C580" s="26"/>
+      <c r="A580" s="29"/>
+      <c r="B580" s="29"/>
+      <c r="C580" s="29"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="A581" s="26"/>
-      <c r="B581" s="26"/>
-      <c r="C581" s="26"/>
+      <c r="A581" s="29"/>
+      <c r="B581" s="29"/>
+      <c r="C581" s="29"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="A582" s="26"/>
-      <c r="B582" s="26"/>
-      <c r="C582" s="26"/>
+      <c r="A582" s="29"/>
+      <c r="B582" s="29"/>
+      <c r="C582" s="29"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="A583" s="26"/>
-      <c r="B583" s="26"/>
-      <c r="C583" s="26"/>
+      <c r="A583" s="29"/>
+      <c r="B583" s="29"/>
+      <c r="C583" s="29"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="A584" s="26"/>
-      <c r="B584" s="26"/>
-      <c r="C584" s="26"/>
+      <c r="A584" s="29"/>
+      <c r="B584" s="29"/>
+      <c r="C584" s="29"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="A585" s="26"/>
-      <c r="B585" s="26"/>
-      <c r="C585" s="26"/>
+      <c r="A585" s="29"/>
+      <c r="B585" s="29"/>
+      <c r="C585" s="29"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="A586" s="26"/>
-      <c r="B586" s="26"/>
-      <c r="C586" s="26"/>
+      <c r="A586" s="29"/>
+      <c r="B586" s="29"/>
+      <c r="C586" s="29"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="A587" s="26"/>
-      <c r="B587" s="26"/>
-      <c r="C587" s="26"/>
+      <c r="A587" s="29"/>
+      <c r="B587" s="29"/>
+      <c r="C587" s="29"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="A588" s="26"/>
-      <c r="B588" s="26"/>
-      <c r="C588" s="26"/>
+      <c r="A588" s="29"/>
+      <c r="B588" s="29"/>
+      <c r="C588" s="29"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="A589" s="26"/>
-      <c r="B589" s="26"/>
-      <c r="C589" s="26"/>
+      <c r="A589" s="29"/>
+      <c r="B589" s="29"/>
+      <c r="C589" s="29"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="A590" s="26"/>
-      <c r="B590" s="26"/>
-      <c r="C590" s="26"/>
+      <c r="A590" s="29"/>
+      <c r="B590" s="29"/>
+      <c r="C590" s="29"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="A591" s="26"/>
-      <c r="B591" s="26"/>
-      <c r="C591" s="26"/>
+      <c r="A591" s="29"/>
+      <c r="B591" s="29"/>
+      <c r="C591" s="29"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="A592" s="26"/>
-      <c r="B592" s="26"/>
-      <c r="C592" s="26"/>
+      <c r="A592" s="29"/>
+      <c r="B592" s="29"/>
+      <c r="C592" s="29"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="A593" s="26"/>
-      <c r="B593" s="26"/>
-      <c r="C593" s="26"/>
+      <c r="A593" s="29"/>
+      <c r="B593" s="29"/>
+      <c r="C593" s="29"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="A594" s="26"/>
-      <c r="B594" s="26"/>
-      <c r="C594" s="26"/>
+      <c r="A594" s="29"/>
+      <c r="B594" s="29"/>
+      <c r="C594" s="29"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="A595" s="26"/>
-      <c r="B595" s="26"/>
-      <c r="C595" s="26"/>
+      <c r="A595" s="29"/>
+      <c r="B595" s="29"/>
+      <c r="C595" s="29"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="A596" s="26"/>
-      <c r="B596" s="26"/>
-      <c r="C596" s="26"/>
+      <c r="A596" s="29"/>
+      <c r="B596" s="29"/>
+      <c r="C596" s="29"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="A597" s="26"/>
-      <c r="B597" s="26"/>
-      <c r="C597" s="26"/>
+      <c r="A597" s="29"/>
+      <c r="B597" s="29"/>
+      <c r="C597" s="29"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="A598" s="26"/>
-      <c r="B598" s="26"/>
-      <c r="C598" s="26"/>
+      <c r="A598" s="29"/>
+      <c r="B598" s="29"/>
+      <c r="C598" s="29"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="A599" s="26"/>
-      <c r="B599" s="26"/>
-      <c r="C599" s="26"/>
+      <c r="A599" s="29"/>
+      <c r="B599" s="29"/>
+      <c r="C599" s="29"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="A600" s="26"/>
-      <c r="B600" s="26"/>
-      <c r="C600" s="26"/>
+      <c r="A600" s="29"/>
+      <c r="B600" s="29"/>
+      <c r="C600" s="29"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="A601" s="26"/>
-      <c r="B601" s="26"/>
-      <c r="C601" s="26"/>
+      <c r="A601" s="29"/>
+      <c r="B601" s="29"/>
+      <c r="C601" s="29"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="A602" s="26"/>
-      <c r="B602" s="26"/>
-      <c r="C602" s="26"/>
+      <c r="A602" s="29"/>
+      <c r="B602" s="29"/>
+      <c r="C602" s="29"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="A603" s="26"/>
-      <c r="B603" s="26"/>
-      <c r="C603" s="26"/>
+      <c r="A603" s="29"/>
+      <c r="B603" s="29"/>
+      <c r="C603" s="29"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="A604" s="26"/>
-      <c r="B604" s="26"/>
-      <c r="C604" s="26"/>
+      <c r="A604" s="29"/>
+      <c r="B604" s="29"/>
+      <c r="C604" s="29"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="A605" s="26"/>
-      <c r="B605" s="26"/>
-      <c r="C605" s="26"/>
+      <c r="A605" s="29"/>
+      <c r="B605" s="29"/>
+      <c r="C605" s="29"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="A606" s="26"/>
-      <c r="B606" s="26"/>
-      <c r="C606" s="26"/>
+      <c r="A606" s="29"/>
+      <c r="B606" s="29"/>
+      <c r="C606" s="29"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="A607" s="26"/>
-      <c r="B607" s="26"/>
-      <c r="C607" s="26"/>
+      <c r="A607" s="29"/>
+      <c r="B607" s="29"/>
+      <c r="C607" s="29"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="A608" s="26"/>
-      <c r="B608" s="26"/>
-      <c r="C608" s="26"/>
+      <c r="A608" s="29"/>
+      <c r="B608" s="29"/>
+      <c r="C608" s="29"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="A609" s="26"/>
-      <c r="B609" s="26"/>
-      <c r="C609" s="26"/>
+      <c r="A609" s="29"/>
+      <c r="B609" s="29"/>
+      <c r="C609" s="29"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="A610" s="26"/>
-      <c r="B610" s="26"/>
-      <c r="C610" s="26"/>
+      <c r="A610" s="29"/>
+      <c r="B610" s="29"/>
+      <c r="C610" s="29"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="A611" s="26"/>
-      <c r="B611" s="26"/>
-      <c r="C611" s="26"/>
+      <c r="A611" s="29"/>
+      <c r="B611" s="29"/>
+      <c r="C611" s="29"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="A612" s="26"/>
-      <c r="B612" s="26"/>
-      <c r="C612" s="26"/>
+      <c r="A612" s="29"/>
+      <c r="B612" s="29"/>
+      <c r="C612" s="29"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="A613" s="26"/>
-      <c r="B613" s="26"/>
-      <c r="C613" s="26"/>
+      <c r="A613" s="29"/>
+      <c r="B613" s="29"/>
+      <c r="C613" s="29"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="A614" s="26"/>
-      <c r="B614" s="26"/>
-      <c r="C614" s="26"/>
+      <c r="A614" s="29"/>
+      <c r="B614" s="29"/>
+      <c r="C614" s="29"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="A615" s="26"/>
-      <c r="B615" s="26"/>
-      <c r="C615" s="26"/>
+      <c r="A615" s="29"/>
+      <c r="B615" s="29"/>
+      <c r="C615" s="29"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="A616" s="26"/>
-      <c r="B616" s="26"/>
-      <c r="C616" s="26"/>
+      <c r="A616" s="29"/>
+      <c r="B616" s="29"/>
+      <c r="C616" s="29"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="A617" s="26"/>
-      <c r="B617" s="26"/>
-      <c r="C617" s="26"/>
+      <c r="A617" s="29"/>
+      <c r="B617" s="29"/>
+      <c r="C617" s="29"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="A618" s="26"/>
-      <c r="B618" s="26"/>
-      <c r="C618" s="26"/>
+      <c r="A618" s="29"/>
+      <c r="B618" s="29"/>
+      <c r="C618" s="29"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="A619" s="26"/>
-      <c r="B619" s="26"/>
-      <c r="C619" s="26"/>
+      <c r="A619" s="29"/>
+      <c r="B619" s="29"/>
+      <c r="C619" s="29"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="A620" s="26"/>
-      <c r="B620" s="26"/>
-      <c r="C620" s="26"/>
+      <c r="A620" s="29"/>
+      <c r="B620" s="29"/>
+      <c r="C620" s="29"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="A621" s="26"/>
-      <c r="B621" s="26"/>
-      <c r="C621" s="26"/>
+      <c r="A621" s="29"/>
+      <c r="B621" s="29"/>
+      <c r="C621" s="29"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="A622" s="26"/>
-      <c r="B622" s="26"/>
-      <c r="C622" s="26"/>
+      <c r="A622" s="29"/>
+      <c r="B622" s="29"/>
+      <c r="C622" s="29"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="A623" s="26"/>
-      <c r="B623" s="26"/>
-      <c r="C623" s="26"/>
+      <c r="A623" s="29"/>
+      <c r="B623" s="29"/>
+      <c r="C623" s="29"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="A624" s="26"/>
-      <c r="B624" s="26"/>
-      <c r="C624" s="26"/>
+      <c r="A624" s="29"/>
+      <c r="B624" s="29"/>
+      <c r="C624" s="29"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="A625" s="26"/>
-      <c r="B625" s="26"/>
-      <c r="C625" s="26"/>
+      <c r="A625" s="29"/>
+      <c r="B625" s="29"/>
+      <c r="C625" s="29"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="A626" s="26"/>
-      <c r="B626" s="26"/>
-      <c r="C626" s="26"/>
+      <c r="A626" s="29"/>
+      <c r="B626" s="29"/>
+      <c r="C626" s="29"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="A627" s="26"/>
-      <c r="B627" s="26"/>
-      <c r="C627" s="26"/>
+      <c r="A627" s="29"/>
+      <c r="B627" s="29"/>
+      <c r="C627" s="29"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="A628" s="26"/>
-      <c r="B628" s="26"/>
-      <c r="C628" s="26"/>
+      <c r="A628" s="29"/>
+      <c r="B628" s="29"/>
+      <c r="C628" s="29"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="A629" s="26"/>
-      <c r="B629" s="26"/>
-      <c r="C629" s="26"/>
+      <c r="A629" s="29"/>
+      <c r="B629" s="29"/>
+      <c r="C629" s="29"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="A630" s="26"/>
-      <c r="B630" s="26"/>
-      <c r="C630" s="26"/>
+      <c r="A630" s="29"/>
+      <c r="B630" s="29"/>
+      <c r="C630" s="29"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="A631" s="26"/>
-      <c r="B631" s="26"/>
-      <c r="C631" s="26"/>
+      <c r="A631" s="29"/>
+      <c r="B631" s="29"/>
+      <c r="C631" s="29"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="A632" s="26"/>
-      <c r="B632" s="26"/>
-      <c r="C632" s="26"/>
+      <c r="A632" s="29"/>
+      <c r="B632" s="29"/>
+      <c r="C632" s="29"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="A633" s="26"/>
-      <c r="B633" s="26"/>
-      <c r="C633" s="26"/>
+      <c r="A633" s="29"/>
+      <c r="B633" s="29"/>
+      <c r="C633" s="29"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="A634" s="26"/>
-      <c r="B634" s="26"/>
-      <c r="C634" s="26"/>
+      <c r="A634" s="29"/>
+      <c r="B634" s="29"/>
+      <c r="C634" s="29"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="A635" s="26"/>
-      <c r="B635" s="26"/>
-      <c r="C635" s="26"/>
+      <c r="A635" s="29"/>
+      <c r="B635" s="29"/>
+      <c r="C635" s="29"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="A636" s="26"/>
-      <c r="B636" s="26"/>
-      <c r="C636" s="26"/>
+      <c r="A636" s="29"/>
+      <c r="B636" s="29"/>
+      <c r="C636" s="29"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="A637" s="26"/>
-      <c r="B637" s="26"/>
-      <c r="C637" s="26"/>
+      <c r="A637" s="29"/>
+      <c r="B637" s="29"/>
+      <c r="C637" s="29"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="A638" s="26"/>
-      <c r="B638" s="26"/>
-      <c r="C638" s="26"/>
+      <c r="A638" s="29"/>
+      <c r="B638" s="29"/>
+      <c r="C638" s="29"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="A639" s="26"/>
-      <c r="B639" s="26"/>
-      <c r="C639" s="26"/>
+      <c r="A639" s="29"/>
+      <c r="B639" s="29"/>
+      <c r="C639" s="29"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="A640" s="26"/>
-      <c r="B640" s="26"/>
-      <c r="C640" s="26"/>
+      <c r="A640" s="29"/>
+      <c r="B640" s="29"/>
+      <c r="C640" s="29"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="A641" s="26"/>
-      <c r="B641" s="26"/>
-      <c r="C641" s="26"/>
+      <c r="A641" s="29"/>
+      <c r="B641" s="29"/>
+      <c r="C641" s="29"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="A642" s="26"/>
-      <c r="B642" s="26"/>
-      <c r="C642" s="26"/>
+      <c r="A642" s="29"/>
+      <c r="B642" s="29"/>
+      <c r="C642" s="29"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="A643" s="26"/>
-      <c r="B643" s="26"/>
-      <c r="C643" s="26"/>
+      <c r="A643" s="29"/>
+      <c r="B643" s="29"/>
+      <c r="C643" s="29"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="A644" s="26"/>
-      <c r="B644" s="26"/>
-      <c r="C644" s="26"/>
+      <c r="A644" s="29"/>
+      <c r="B644" s="29"/>
+      <c r="C644" s="29"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="A645" s="26"/>
-      <c r="B645" s="26"/>
-      <c r="C645" s="26"/>
+      <c r="A645" s="29"/>
+      <c r="B645" s="29"/>
+      <c r="C645" s="29"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="A646" s="26"/>
-      <c r="B646" s="26"/>
-      <c r="C646" s="26"/>
+      <c r="A646" s="29"/>
+      <c r="B646" s="29"/>
+      <c r="C646" s="29"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="A647" s="26"/>
-      <c r="B647" s="26"/>
-      <c r="C647" s="26"/>
+      <c r="A647" s="29"/>
+      <c r="B647" s="29"/>
+      <c r="C647" s="29"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="A648" s="26"/>
-      <c r="B648" s="26"/>
-      <c r="C648" s="26"/>
+      <c r="A648" s="29"/>
+      <c r="B648" s="29"/>
+      <c r="C648" s="29"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="A649" s="26"/>
-      <c r="B649" s="26"/>
-      <c r="C649" s="26"/>
+      <c r="A649" s="29"/>
+      <c r="B649" s="29"/>
+      <c r="C649" s="29"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="A650" s="26"/>
-      <c r="B650" s="26"/>
-      <c r="C650" s="26"/>
+      <c r="A650" s="29"/>
+      <c r="B650" s="29"/>
+      <c r="C650" s="29"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="A651" s="26"/>
-      <c r="B651" s="26"/>
-      <c r="C651" s="26"/>
+      <c r="A651" s="29"/>
+      <c r="B651" s="29"/>
+      <c r="C651" s="29"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="A652" s="26"/>
-      <c r="B652" s="26"/>
-      <c r="C652" s="26"/>
+      <c r="A652" s="29"/>
+      <c r="B652" s="29"/>
+      <c r="C652" s="29"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="A653" s="26"/>
-      <c r="B653" s="26"/>
-      <c r="C653" s="26"/>
+      <c r="A653" s="29"/>
+      <c r="B653" s="29"/>
+      <c r="C653" s="29"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="A654" s="26"/>
-      <c r="B654" s="26"/>
-      <c r="C654" s="26"/>
+      <c r="A654" s="29"/>
+      <c r="B654" s="29"/>
+      <c r="C654" s="29"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="A655" s="26"/>
-      <c r="B655" s="26"/>
-      <c r="C655" s="26"/>
+      <c r="A655" s="29"/>
+      <c r="B655" s="29"/>
+      <c r="C655" s="29"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="A656" s="26"/>
-      <c r="B656" s="26"/>
-      <c r="C656" s="26"/>
+      <c r="A656" s="29"/>
+      <c r="B656" s="29"/>
+      <c r="C656" s="29"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="A657" s="26"/>
-      <c r="B657" s="26"/>
-      <c r="C657" s="26"/>
+      <c r="A657" s="29"/>
+      <c r="B657" s="29"/>
+      <c r="C657" s="29"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="A658" s="26"/>
-      <c r="B658" s="26"/>
-      <c r="C658" s="26"/>
+      <c r="A658" s="29"/>
+      <c r="B658" s="29"/>
+      <c r="C658" s="29"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="A659" s="26"/>
-      <c r="B659" s="26"/>
-      <c r="C659" s="26"/>
+      <c r="A659" s="29"/>
+      <c r="B659" s="29"/>
+      <c r="C659" s="29"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="A660" s="26"/>
-      <c r="B660" s="26"/>
-      <c r="C660" s="26"/>
+      <c r="A660" s="29"/>
+      <c r="B660" s="29"/>
+      <c r="C660" s="29"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="A661" s="26"/>
-      <c r="B661" s="26"/>
-      <c r="C661" s="26"/>
+      <c r="A661" s="29"/>
+      <c r="B661" s="29"/>
+      <c r="C661" s="29"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="A662" s="26"/>
-      <c r="B662" s="26"/>
-      <c r="C662" s="26"/>
+      <c r="A662" s="29"/>
+      <c r="B662" s="29"/>
+      <c r="C662" s="29"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="A663" s="26"/>
-      <c r="B663" s="26"/>
-      <c r="C663" s="26"/>
+      <c r="A663" s="29"/>
+      <c r="B663" s="29"/>
+      <c r="C663" s="29"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="A664" s="26"/>
-      <c r="B664" s="26"/>
-      <c r="C664" s="26"/>
+      <c r="A664" s="29"/>
+      <c r="B664" s="29"/>
+      <c r="C664" s="29"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="A665" s="26"/>
-      <c r="B665" s="26"/>
-      <c r="C665" s="26"/>
+      <c r="A665" s="29"/>
+      <c r="B665" s="29"/>
+      <c r="C665" s="29"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="A666" s="26"/>
-      <c r="B666" s="26"/>
-      <c r="C666" s="26"/>
+      <c r="A666" s="29"/>
+      <c r="B666" s="29"/>
+      <c r="C666" s="29"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="A667" s="26"/>
-      <c r="B667" s="26"/>
-      <c r="C667" s="26"/>
+      <c r="A667" s="29"/>
+      <c r="B667" s="29"/>
+      <c r="C667" s="29"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="A668" s="26"/>
-      <c r="B668" s="26"/>
-      <c r="C668" s="26"/>
+      <c r="A668" s="29"/>
+      <c r="B668" s="29"/>
+      <c r="C668" s="29"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="A669" s="26"/>
-      <c r="B669" s="26"/>
-      <c r="C669" s="26"/>
+      <c r="A669" s="29"/>
+      <c r="B669" s="29"/>
+      <c r="C669" s="29"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="A670" s="26"/>
-      <c r="B670" s="26"/>
-      <c r="C670" s="26"/>
+      <c r="A670" s="29"/>
+      <c r="B670" s="29"/>
+      <c r="C670" s="29"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="A671" s="26"/>
-      <c r="B671" s="26"/>
-      <c r="C671" s="26"/>
+      <c r="A671" s="29"/>
+      <c r="B671" s="29"/>
+      <c r="C671" s="29"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="A672" s="26"/>
-      <c r="B672" s="26"/>
-      <c r="C672" s="26"/>
+      <c r="A672" s="29"/>
+      <c r="B672" s="29"/>
+      <c r="C672" s="29"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="A673" s="26"/>
-      <c r="B673" s="26"/>
-      <c r="C673" s="26"/>
+      <c r="A673" s="29"/>
+      <c r="B673" s="29"/>
+      <c r="C673" s="29"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="A674" s="26"/>
-      <c r="B674" s="26"/>
-      <c r="C674" s="26"/>
+      <c r="A674" s="29"/>
+      <c r="B674" s="29"/>
+      <c r="C674" s="29"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="A675" s="26"/>
-      <c r="B675" s="26"/>
-      <c r="C675" s="26"/>
+      <c r="A675" s="29"/>
+      <c r="B675" s="29"/>
+      <c r="C675" s="29"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="A676" s="26"/>
-      <c r="B676" s="26"/>
-      <c r="C676" s="26"/>
+      <c r="A676" s="29"/>
+      <c r="B676" s="29"/>
+      <c r="C676" s="29"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="A677" s="26"/>
-      <c r="B677" s="26"/>
-      <c r="C677" s="26"/>
+      <c r="A677" s="29"/>
+      <c r="B677" s="29"/>
+      <c r="C677" s="29"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="A678" s="26"/>
-      <c r="B678" s="26"/>
-      <c r="C678" s="26"/>
+      <c r="A678" s="29"/>
+      <c r="B678" s="29"/>
+      <c r="C678" s="29"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="A679" s="26"/>
-      <c r="B679" s="26"/>
-      <c r="C679" s="26"/>
+      <c r="A679" s="29"/>
+      <c r="B679" s="29"/>
+      <c r="C679" s="29"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="A680" s="26"/>
-      <c r="B680" s="26"/>
-      <c r="C680" s="26"/>
+      <c r="A680" s="29"/>
+      <c r="B680" s="29"/>
+      <c r="C680" s="29"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="A681" s="26"/>
-      <c r="B681" s="26"/>
-      <c r="C681" s="26"/>
+      <c r="A681" s="29"/>
+      <c r="B681" s="29"/>
+      <c r="C681" s="29"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="A682" s="26"/>
-      <c r="B682" s="26"/>
-      <c r="C682" s="26"/>
+      <c r="A682" s="29"/>
+      <c r="B682" s="29"/>
+      <c r="C682" s="29"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="A683" s="26"/>
-      <c r="B683" s="26"/>
-      <c r="C683" s="26"/>
+      <c r="A683" s="29"/>
+      <c r="B683" s="29"/>
+      <c r="C683" s="29"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="A684" s="26"/>
-      <c r="B684" s="26"/>
-      <c r="C684" s="26"/>
+      <c r="A684" s="29"/>
+      <c r="B684" s="29"/>
+      <c r="C684" s="29"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="A685" s="26"/>
-      <c r="B685" s="26"/>
-      <c r="C685" s="26"/>
+      <c r="A685" s="29"/>
+      <c r="B685" s="29"/>
+      <c r="C685" s="29"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="A686" s="26"/>
-      <c r="B686" s="26"/>
-      <c r="C686" s="26"/>
+      <c r="A686" s="29"/>
+      <c r="B686" s="29"/>
+      <c r="C686" s="29"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="A687" s="26"/>
-      <c r="B687" s="26"/>
-      <c r="C687" s="26"/>
+      <c r="A687" s="29"/>
+      <c r="B687" s="29"/>
+      <c r="C687" s="29"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="A688" s="26"/>
-      <c r="B688" s="26"/>
-      <c r="C688" s="26"/>
+      <c r="A688" s="29"/>
+      <c r="B688" s="29"/>
+      <c r="C688" s="29"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="A689" s="26"/>
-      <c r="B689" s="26"/>
-      <c r="C689" s="26"/>
+      <c r="A689" s="29"/>
+      <c r="B689" s="29"/>
+      <c r="C689" s="29"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="A690" s="26"/>
-      <c r="B690" s="26"/>
-      <c r="C690" s="26"/>
+      <c r="A690" s="29"/>
+      <c r="B690" s="29"/>
+      <c r="C690" s="29"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="A691" s="26"/>
-      <c r="B691" s="26"/>
-      <c r="C691" s="26"/>
+      <c r="A691" s="29"/>
+      <c r="B691" s="29"/>
+      <c r="C691" s="29"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="A692" s="26"/>
-      <c r="B692" s="26"/>
-      <c r="C692" s="26"/>
+      <c r="A692" s="29"/>
+      <c r="B692" s="29"/>
+      <c r="C692" s="29"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="A693" s="26"/>
-      <c r="B693" s="26"/>
-      <c r="C693" s="26"/>
+      <c r="A693" s="29"/>
+      <c r="B693" s="29"/>
+      <c r="C693" s="29"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="A694" s="26"/>
-      <c r="B694" s="26"/>
-      <c r="C694" s="26"/>
+      <c r="A694" s="29"/>
+      <c r="B694" s="29"/>
+      <c r="C694" s="29"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="A695" s="26"/>
-      <c r="B695" s="26"/>
-      <c r="C695" s="26"/>
+      <c r="A695" s="29"/>
+      <c r="B695" s="29"/>
+      <c r="C695" s="29"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="A696" s="26"/>
-      <c r="B696" s="26"/>
-      <c r="C696" s="26"/>
+      <c r="A696" s="29"/>
+      <c r="B696" s="29"/>
+      <c r="C696" s="29"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="A697" s="26"/>
-      <c r="B697" s="26"/>
-      <c r="C697" s="26"/>
+      <c r="A697" s="29"/>
+      <c r="B697" s="29"/>
+      <c r="C697" s="29"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="A698" s="26"/>
-      <c r="B698" s="26"/>
-      <c r="C698" s="26"/>
+      <c r="A698" s="29"/>
+      <c r="B698" s="29"/>
+      <c r="C698" s="29"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="A699" s="26"/>
-      <c r="B699" s="26"/>
-      <c r="C699" s="26"/>
+      <c r="A699" s="29"/>
+      <c r="B699" s="29"/>
+      <c r="C699" s="29"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="A700" s="26"/>
-      <c r="B700" s="26"/>
-      <c r="C700" s="26"/>
+      <c r="A700" s="29"/>
+      <c r="B700" s="29"/>
+      <c r="C700" s="29"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="A701" s="26"/>
-      <c r="B701" s="26"/>
-      <c r="C701" s="26"/>
+      <c r="A701" s="29"/>
+      <c r="B701" s="29"/>
+      <c r="C701" s="29"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="A702" s="26"/>
-      <c r="B702" s="26"/>
-      <c r="C702" s="26"/>
+      <c r="A702" s="29"/>
+      <c r="B702" s="29"/>
+      <c r="C702" s="29"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="A703" s="26"/>
-      <c r="B703" s="26"/>
-      <c r="C703" s="26"/>
+      <c r="A703" s="29"/>
+      <c r="B703" s="29"/>
+      <c r="C703" s="29"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="A704" s="26"/>
-      <c r="B704" s="26"/>
-      <c r="C704" s="26"/>
+      <c r="A704" s="29"/>
+      <c r="B704" s="29"/>
+      <c r="C704" s="29"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="A705" s="26"/>
-      <c r="B705" s="26"/>
-      <c r="C705" s="26"/>
+      <c r="A705" s="29"/>
+      <c r="B705" s="29"/>
+      <c r="C705" s="29"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="A706" s="26"/>
-      <c r="B706" s="26"/>
-      <c r="C706" s="26"/>
+      <c r="A706" s="29"/>
+      <c r="B706" s="29"/>
+      <c r="C706" s="29"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="A707" s="26"/>
-      <c r="B707" s="26"/>
-      <c r="C707" s="26"/>
+      <c r="A707" s="29"/>
+      <c r="B707" s="29"/>
+      <c r="C707" s="29"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="26"/>
-      <c r="B708" s="26"/>
-      <c r="C708" s="26"/>
+      <c r="A708" s="29"/>
+      <c r="B708" s="29"/>
+      <c r="C708" s="29"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="A709" s="26"/>
-      <c r="B709" s="26"/>
-      <c r="C709" s="26"/>
+      <c r="A709" s="29"/>
+      <c r="B709" s="29"/>
+      <c r="C709" s="29"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="A710" s="26"/>
-      <c r="B710" s="26"/>
-      <c r="C710" s="26"/>
+      <c r="A710" s="29"/>
+      <c r="B710" s="29"/>
+      <c r="C710" s="29"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="A711" s="26"/>
-      <c r="B711" s="26"/>
-      <c r="C711" s="26"/>
+      <c r="A711" s="29"/>
+      <c r="B711" s="29"/>
+      <c r="C711" s="29"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="A712" s="26"/>
-      <c r="B712" s="26"/>
-      <c r="C712" s="26"/>
+      <c r="A712" s="29"/>
+      <c r="B712" s="29"/>
+      <c r="C712" s="29"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="A713" s="26"/>
-      <c r="B713" s="26"/>
-      <c r="C713" s="26"/>
+      <c r="A713" s="29"/>
+      <c r="B713" s="29"/>
+      <c r="C713" s="29"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="A714" s="26"/>
-      <c r="B714" s="26"/>
-      <c r="C714" s="26"/>
+      <c r="A714" s="29"/>
+      <c r="B714" s="29"/>
+      <c r="C714" s="29"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="A715" s="26"/>
-      <c r="B715" s="26"/>
-      <c r="C715" s="26"/>
+      <c r="A715" s="29"/>
+      <c r="B715" s="29"/>
+      <c r="C715" s="29"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="A716" s="26"/>
-      <c r="B716" s="26"/>
-      <c r="C716" s="26"/>
+      <c r="A716" s="29"/>
+      <c r="B716" s="29"/>
+      <c r="C716" s="29"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="A717" s="26"/>
-      <c r="B717" s="26"/>
-      <c r="C717" s="26"/>
+      <c r="A717" s="29"/>
+      <c r="B717" s="29"/>
+      <c r="C717" s="29"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="A718" s="26"/>
-      <c r="B718" s="26"/>
-      <c r="C718" s="26"/>
+      <c r="A718" s="29"/>
+      <c r="B718" s="29"/>
+      <c r="C718" s="29"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="A719" s="26"/>
-      <c r="B719" s="26"/>
-      <c r="C719" s="26"/>
+      <c r="A719" s="29"/>
+      <c r="B719" s="29"/>
+      <c r="C719" s="29"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="A720" s="26"/>
-      <c r="B720" s="26"/>
-      <c r="C720" s="26"/>
+      <c r="A720" s="29"/>
+      <c r="B720" s="29"/>
+      <c r="C720" s="29"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="A721" s="26"/>
-      <c r="B721" s="26"/>
-      <c r="C721" s="26"/>
+      <c r="A721" s="29"/>
+      <c r="B721" s="29"/>
+      <c r="C721" s="29"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="A722" s="26"/>
-      <c r="B722" s="26"/>
-      <c r="C722" s="26"/>
+      <c r="A722" s="29"/>
+      <c r="B722" s="29"/>
+      <c r="C722" s="29"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="A723" s="26"/>
-      <c r="B723" s="26"/>
-      <c r="C723" s="26"/>
+      <c r="A723" s="29"/>
+      <c r="B723" s="29"/>
+      <c r="C723" s="29"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="A724" s="26"/>
-      <c r="B724" s="26"/>
-      <c r="C724" s="26"/>
+      <c r="A724" s="29"/>
+      <c r="B724" s="29"/>
+      <c r="C724" s="29"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="A725" s="26"/>
-      <c r="B725" s="26"/>
-      <c r="C725" s="26"/>
+      <c r="A725" s="29"/>
+      <c r="B725" s="29"/>
+      <c r="C725" s="29"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="A726" s="26"/>
-      <c r="B726" s="26"/>
-      <c r="C726" s="26"/>
+      <c r="A726" s="29"/>
+      <c r="B726" s="29"/>
+      <c r="C726" s="29"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="A727" s="26"/>
-      <c r="B727" s="26"/>
-      <c r="C727" s="26"/>
+      <c r="A727" s="29"/>
+      <c r="B727" s="29"/>
+      <c r="C727" s="29"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="A728" s="26"/>
-      <c r="B728" s="26"/>
-      <c r="C728" s="26"/>
+      <c r="A728" s="29"/>
+      <c r="B728" s="29"/>
+      <c r="C728" s="29"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="A729" s="26"/>
-      <c r="B729" s="26"/>
-      <c r="C729" s="26"/>
+      <c r="A729" s="29"/>
+      <c r="B729" s="29"/>
+      <c r="C729" s="29"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="A730" s="26"/>
-      <c r="B730" s="26"/>
-      <c r="C730" s="26"/>
+      <c r="A730" s="29"/>
+      <c r="B730" s="29"/>
+      <c r="C730" s="29"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="A731" s="26"/>
-      <c r="B731" s="26"/>
-      <c r="C731" s="26"/>
+      <c r="A731" s="29"/>
+      <c r="B731" s="29"/>
+      <c r="C731" s="29"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="A732" s="26"/>
-      <c r="B732" s="26"/>
-      <c r="C732" s="26"/>
+      <c r="A732" s="29"/>
+      <c r="B732" s="29"/>
+      <c r="C732" s="29"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="A733" s="26"/>
-      <c r="B733" s="26"/>
-      <c r="C733" s="26"/>
+      <c r="A733" s="29"/>
+      <c r="B733" s="29"/>
+      <c r="C733" s="29"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="A734" s="26"/>
-      <c r="B734" s="26"/>
-      <c r="C734" s="26"/>
+      <c r="A734" s="29"/>
+      <c r="B734" s="29"/>
+      <c r="C734" s="29"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="A735" s="26"/>
-      <c r="B735" s="26"/>
-      <c r="C735" s="26"/>
+      <c r="A735" s="29"/>
+      <c r="B735" s="29"/>
+      <c r="C735" s="29"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="A736" s="26"/>
-      <c r="B736" s="26"/>
-      <c r="C736" s="26"/>
+      <c r="A736" s="29"/>
+      <c r="B736" s="29"/>
+      <c r="C736" s="29"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="A737" s="26"/>
-      <c r="B737" s="26"/>
-      <c r="C737" s="26"/>
+      <c r="A737" s="29"/>
+      <c r="B737" s="29"/>
+      <c r="C737" s="29"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="A738" s="26"/>
-      <c r="B738" s="26"/>
-      <c r="C738" s="26"/>
+      <c r="A738" s="29"/>
+      <c r="B738" s="29"/>
+      <c r="C738" s="29"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="A739" s="26"/>
-      <c r="B739" s="26"/>
-      <c r="C739" s="26"/>
+      <c r="A739" s="29"/>
+      <c r="B739" s="29"/>
+      <c r="C739" s="29"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="A740" s="26"/>
-      <c r="B740" s="26"/>
-      <c r="C740" s="26"/>
+      <c r="A740" s="29"/>
+      <c r="B740" s="29"/>
+      <c r="C740" s="29"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="A741" s="26"/>
-      <c r="B741" s="26"/>
-      <c r="C741" s="26"/>
+      <c r="A741" s="29"/>
+      <c r="B741" s="29"/>
+      <c r="C741" s="29"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="A742" s="26"/>
-      <c r="B742" s="26"/>
-      <c r="C742" s="26"/>
+      <c r="A742" s="29"/>
+      <c r="B742" s="29"/>
+      <c r="C742" s="29"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="A743" s="26"/>
-      <c r="B743" s="26"/>
-      <c r="C743" s="26"/>
+      <c r="A743" s="29"/>
+      <c r="B743" s="29"/>
+      <c r="C743" s="29"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="A744" s="26"/>
-      <c r="B744" s="26"/>
-      <c r="C744" s="26"/>
+      <c r="A744" s="29"/>
+      <c r="B744" s="29"/>
+      <c r="C744" s="29"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="A745" s="26"/>
-      <c r="B745" s="26"/>
-      <c r="C745" s="26"/>
+      <c r="A745" s="29"/>
+      <c r="B745" s="29"/>
+      <c r="C745" s="29"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="A746" s="26"/>
-      <c r="B746" s="26"/>
-      <c r="C746" s="26"/>
+      <c r="A746" s="29"/>
+      <c r="B746" s="29"/>
+      <c r="C746" s="29"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="A747" s="26"/>
-      <c r="B747" s="26"/>
-      <c r="C747" s="26"/>
+      <c r="A747" s="29"/>
+      <c r="B747" s="29"/>
+      <c r="C747" s="29"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="A748" s="26"/>
-      <c r="B748" s="26"/>
-      <c r="C748" s="26"/>
+      <c r="A748" s="29"/>
+      <c r="B748" s="29"/>
+      <c r="C748" s="29"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="A749" s="26"/>
-      <c r="B749" s="26"/>
-      <c r="C749" s="26"/>
+      <c r="A749" s="29"/>
+      <c r="B749" s="29"/>
+      <c r="C749" s="29"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="A750" s="26"/>
-      <c r="B750" s="26"/>
-      <c r="C750" s="26"/>
+      <c r="A750" s="29"/>
+      <c r="B750" s="29"/>
+      <c r="C750" s="29"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="A751" s="26"/>
-      <c r="B751" s="26"/>
-      <c r="C751" s="26"/>
+      <c r="A751" s="29"/>
+      <c r="B751" s="29"/>
+      <c r="C751" s="29"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="A752" s="26"/>
-      <c r="B752" s="26"/>
-      <c r="C752" s="26"/>
+      <c r="A752" s="29"/>
+      <c r="B752" s="29"/>
+      <c r="C752" s="29"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="A753" s="26"/>
-      <c r="B753" s="26"/>
-      <c r="C753" s="26"/>
+      <c r="A753" s="29"/>
+      <c r="B753" s="29"/>
+      <c r="C753" s="29"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="A754" s="26"/>
-      <c r="B754" s="26"/>
-      <c r="C754" s="26"/>
+      <c r="A754" s="29"/>
+      <c r="B754" s="29"/>
+      <c r="C754" s="29"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="A755" s="26"/>
-      <c r="B755" s="26"/>
-      <c r="C755" s="26"/>
+      <c r="A755" s="29"/>
+      <c r="B755" s="29"/>
+      <c r="C755" s="29"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="A756" s="26"/>
-      <c r="B756" s="26"/>
-      <c r="C756" s="26"/>
+      <c r="A756" s="29"/>
+      <c r="B756" s="29"/>
+      <c r="C756" s="29"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="A757" s="26"/>
-      <c r="B757" s="26"/>
-      <c r="C757" s="26"/>
+      <c r="A757" s="29"/>
+      <c r="B757" s="29"/>
+      <c r="C757" s="29"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="A758" s="26"/>
-      <c r="B758" s="26"/>
-      <c r="C758" s="26"/>
+      <c r="A758" s="29"/>
+      <c r="B758" s="29"/>
+      <c r="C758" s="29"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="A759" s="26"/>
-      <c r="B759" s="26"/>
-      <c r="C759" s="26"/>
+      <c r="A759" s="29"/>
+      <c r="B759" s="29"/>
+      <c r="C759" s="29"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="A760" s="26"/>
-      <c r="B760" s="26"/>
-      <c r="C760" s="26"/>
+      <c r="A760" s="29"/>
+      <c r="B760" s="29"/>
+      <c r="C760" s="29"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="A761" s="26"/>
-      <c r="B761" s="26"/>
-      <c r="C761" s="26"/>
+      <c r="A761" s="29"/>
+      <c r="B761" s="29"/>
+      <c r="C761" s="29"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="A762" s="26"/>
-      <c r="B762" s="26"/>
-      <c r="C762" s="26"/>
+      <c r="A762" s="29"/>
+      <c r="B762" s="29"/>
+      <c r="C762" s="29"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="A763" s="26"/>
-      <c r="B763" s="26"/>
-      <c r="C763" s="26"/>
+      <c r="A763" s="29"/>
+      <c r="B763" s="29"/>
+      <c r="C763" s="29"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="A764" s="26"/>
-      <c r="B764" s="26"/>
-      <c r="C764" s="26"/>
+      <c r="A764" s="29"/>
+      <c r="B764" s="29"/>
+      <c r="C764" s="29"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="A765" s="26"/>
-      <c r="B765" s="26"/>
-      <c r="C765" s="26"/>
+      <c r="A765" s="29"/>
+      <c r="B765" s="29"/>
+      <c r="C765" s="29"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="A766" s="26"/>
-      <c r="B766" s="26"/>
-      <c r="C766" s="26"/>
+      <c r="A766" s="29"/>
+      <c r="B766" s="29"/>
+      <c r="C766" s="29"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="A767" s="26"/>
-      <c r="B767" s="26"/>
-      <c r="C767" s="26"/>
+      <c r="A767" s="29"/>
+      <c r="B767" s="29"/>
+      <c r="C767" s="29"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="A768" s="26"/>
-      <c r="B768" s="26"/>
-      <c r="C768" s="26"/>
+      <c r="A768" s="29"/>
+      <c r="B768" s="29"/>
+      <c r="C768" s="29"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="A769" s="26"/>
-      <c r="B769" s="26"/>
-      <c r="C769" s="26"/>
+      <c r="A769" s="29"/>
+      <c r="B769" s="29"/>
+      <c r="C769" s="29"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="A770" s="26"/>
-      <c r="B770" s="26"/>
-      <c r="C770" s="26"/>
+      <c r="A770" s="29"/>
+      <c r="B770" s="29"/>
+      <c r="C770" s="29"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="A771" s="26"/>
-      <c r="B771" s="26"/>
-      <c r="C771" s="26"/>
+      <c r="A771" s="29"/>
+      <c r="B771" s="29"/>
+      <c r="C771" s="29"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="A772" s="26"/>
-      <c r="B772" s="26"/>
-      <c r="C772" s="26"/>
+      <c r="A772" s="29"/>
+      <c r="B772" s="29"/>
+      <c r="C772" s="29"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="A773" s="26"/>
-      <c r="B773" s="26"/>
-      <c r="C773" s="26"/>
+      <c r="A773" s="29"/>
+      <c r="B773" s="29"/>
+      <c r="C773" s="29"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="A774" s="26"/>
-      <c r="B774" s="26"/>
-      <c r="C774" s="26"/>
+      <c r="A774" s="29"/>
+      <c r="B774" s="29"/>
+      <c r="C774" s="29"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="A775" s="26"/>
-      <c r="B775" s="26"/>
-      <c r="C775" s="26"/>
+      <c r="A775" s="29"/>
+      <c r="B775" s="29"/>
+      <c r="C775" s="29"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="A776" s="26"/>
-      <c r="B776" s="26"/>
-      <c r="C776" s="26"/>
+      <c r="A776" s="29"/>
+      <c r="B776" s="29"/>
+      <c r="C776" s="29"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="A777" s="26"/>
-      <c r="B777" s="26"/>
-      <c r="C777" s="26"/>
+      <c r="A777" s="29"/>
+      <c r="B777" s="29"/>
+      <c r="C777" s="29"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="A778" s="26"/>
-      <c r="B778" s="26"/>
-      <c r="C778" s="26"/>
+      <c r="A778" s="29"/>
+      <c r="B778" s="29"/>
+      <c r="C778" s="29"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="A779" s="26"/>
-      <c r="B779" s="26"/>
-      <c r="C779" s="26"/>
+      <c r="A779" s="29"/>
+      <c r="B779" s="29"/>
+      <c r="C779" s="29"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="A780" s="26"/>
-      <c r="B780" s="26"/>
-      <c r="C780" s="26"/>
+      <c r="A780" s="29"/>
+      <c r="B780" s="29"/>
+      <c r="C780" s="29"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="A781" s="26"/>
-      <c r="B781" s="26"/>
-      <c r="C781" s="26"/>
+      <c r="A781" s="29"/>
+      <c r="B781" s="29"/>
+      <c r="C781" s="29"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="A782" s="26"/>
-      <c r="B782" s="26"/>
-      <c r="C782" s="26"/>
+      <c r="A782" s="29"/>
+      <c r="B782" s="29"/>
+      <c r="C782" s="29"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="A783" s="26"/>
-      <c r="B783" s="26"/>
-      <c r="C783" s="26"/>
+      <c r="A783" s="29"/>
+      <c r="B783" s="29"/>
+      <c r="C783" s="29"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="A784" s="26"/>
-      <c r="B784" s="26"/>
-      <c r="C784" s="26"/>
+      <c r="A784" s="29"/>
+      <c r="B784" s="29"/>
+      <c r="C784" s="29"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="A785" s="26"/>
-      <c r="B785" s="26"/>
-      <c r="C785" s="26"/>
+      <c r="A785" s="29"/>
+      <c r="B785" s="29"/>
+      <c r="C785" s="29"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="A786" s="26"/>
-      <c r="B786" s="26"/>
-      <c r="C786" s="26"/>
+      <c r="A786" s="29"/>
+      <c r="B786" s="29"/>
+      <c r="C786" s="29"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="A787" s="26"/>
-      <c r="B787" s="26"/>
-      <c r="C787" s="26"/>
+      <c r="A787" s="29"/>
+      <c r="B787" s="29"/>
+      <c r="C787" s="29"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="A788" s="26"/>
-      <c r="B788" s="26"/>
-      <c r="C788" s="26"/>
+      <c r="A788" s="29"/>
+      <c r="B788" s="29"/>
+      <c r="C788" s="29"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="A789" s="26"/>
-      <c r="B789" s="26"/>
-      <c r="C789" s="26"/>
+      <c r="A789" s="29"/>
+      <c r="B789" s="29"/>
+      <c r="C789" s="29"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="A790" s="26"/>
-      <c r="B790" s="26"/>
-      <c r="C790" s="26"/>
+      <c r="A790" s="29"/>
+      <c r="B790" s="29"/>
+      <c r="C790" s="29"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="A791" s="26"/>
-      <c r="B791" s="26"/>
-      <c r="C791" s="26"/>
+      <c r="A791" s="29"/>
+      <c r="B791" s="29"/>
+      <c r="C791" s="29"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="A792" s="26"/>
-      <c r="B792" s="26"/>
-      <c r="C792" s="26"/>
+      <c r="A792" s="29"/>
+      <c r="B792" s="29"/>
+      <c r="C792" s="29"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="A793" s="26"/>
-      <c r="B793" s="26"/>
-      <c r="C793" s="26"/>
+      <c r="A793" s="29"/>
+      <c r="B793" s="29"/>
+      <c r="C793" s="29"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="A794" s="26"/>
-      <c r="B794" s="26"/>
-      <c r="C794" s="26"/>
+      <c r="A794" s="29"/>
+      <c r="B794" s="29"/>
+      <c r="C794" s="29"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="A795" s="26"/>
-      <c r="B795" s="26"/>
-      <c r="C795" s="26"/>
+      <c r="A795" s="29"/>
+      <c r="B795" s="29"/>
+      <c r="C795" s="29"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="A796" s="26"/>
-      <c r="B796" s="26"/>
-      <c r="C796" s="26"/>
+      <c r="A796" s="29"/>
+      <c r="B796" s="29"/>
+      <c r="C796" s="29"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="A797" s="26"/>
-      <c r="B797" s="26"/>
-      <c r="C797" s="26"/>
+      <c r="A797" s="29"/>
+      <c r="B797" s="29"/>
+      <c r="C797" s="29"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="A798" s="26"/>
-      <c r="B798" s="26"/>
-      <c r="C798" s="26"/>
+      <c r="A798" s="29"/>
+      <c r="B798" s="29"/>
+      <c r="C798" s="29"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="A799" s="26"/>
-      <c r="B799" s="26"/>
-      <c r="C799" s="26"/>
+      <c r="A799" s="29"/>
+      <c r="B799" s="29"/>
+      <c r="C799" s="29"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="A800" s="26"/>
-      <c r="B800" s="26"/>
-      <c r="C800" s="26"/>
+      <c r="A800" s="29"/>
+      <c r="B800" s="29"/>
+      <c r="C800" s="29"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="A801" s="26"/>
-      <c r="B801" s="26"/>
-      <c r="C801" s="26"/>
+      <c r="A801" s="29"/>
+      <c r="B801" s="29"/>
+      <c r="C801" s="29"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="A802" s="26"/>
-      <c r="B802" s="26"/>
-      <c r="C802" s="26"/>
+      <c r="A802" s="29"/>
+      <c r="B802" s="29"/>
+      <c r="C802" s="29"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="A803" s="26"/>
-      <c r="B803" s="26"/>
-      <c r="C803" s="26"/>
+      <c r="A803" s="29"/>
+      <c r="B803" s="29"/>
+      <c r="C803" s="29"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="A804" s="26"/>
-      <c r="B804" s="26"/>
-      <c r="C804" s="26"/>
+      <c r="A804" s="29"/>
+      <c r="B804" s="29"/>
+      <c r="C804" s="29"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="A805" s="26"/>
-      <c r="B805" s="26"/>
-      <c r="C805" s="26"/>
+      <c r="A805" s="29"/>
+      <c r="B805" s="29"/>
+      <c r="C805" s="29"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="A806" s="26"/>
-      <c r="B806" s="26"/>
-      <c r="C806" s="26"/>
+      <c r="A806" s="29"/>
+      <c r="B806" s="29"/>
+      <c r="C806" s="29"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="A807" s="26"/>
-      <c r="B807" s="26"/>
-      <c r="C807" s="26"/>
+      <c r="A807" s="29"/>
+      <c r="B807" s="29"/>
+      <c r="C807" s="29"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="A808" s="26"/>
-      <c r="B808" s="26"/>
-      <c r="C808" s="26"/>
+      <c r="A808" s="29"/>
+      <c r="B808" s="29"/>
+      <c r="C808" s="29"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="A809" s="26"/>
-      <c r="B809" s="26"/>
-      <c r="C809" s="26"/>
+      <c r="A809" s="29"/>
+      <c r="B809" s="29"/>
+      <c r="C809" s="29"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="A810" s="26"/>
-      <c r="B810" s="26"/>
-      <c r="C810" s="26"/>
+      <c r="A810" s="29"/>
+      <c r="B810" s="29"/>
+      <c r="C810" s="29"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="A811" s="26"/>
-      <c r="B811" s="26"/>
-      <c r="C811" s="26"/>
+      <c r="A811" s="29"/>
+      <c r="B811" s="29"/>
+      <c r="C811" s="29"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="A812" s="26"/>
-      <c r="B812" s="26"/>
-      <c r="C812" s="26"/>
+      <c r="A812" s="29"/>
+      <c r="B812" s="29"/>
+      <c r="C812" s="29"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="A813" s="26"/>
-      <c r="B813" s="26"/>
-      <c r="C813" s="26"/>
+      <c r="A813" s="29"/>
+      <c r="B813" s="29"/>
+      <c r="C813" s="29"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="A814" s="26"/>
-      <c r="B814" s="26"/>
-      <c r="C814" s="26"/>
+      <c r="A814" s="29"/>
+      <c r="B814" s="29"/>
+      <c r="C814" s="29"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="A815" s="26"/>
-      <c r="B815" s="26"/>
-      <c r="C815" s="26"/>
+      <c r="A815" s="29"/>
+      <c r="B815" s="29"/>
+      <c r="C815" s="29"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="A816" s="26"/>
-      <c r="B816" s="26"/>
-      <c r="C816" s="26"/>
+      <c r="A816" s="29"/>
+      <c r="B816" s="29"/>
+      <c r="C816" s="29"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="A817" s="26"/>
-      <c r="B817" s="26"/>
-      <c r="C817" s="26"/>
+      <c r="A817" s="29"/>
+      <c r="B817" s="29"/>
+      <c r="C817" s="29"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="A818" s="26"/>
-      <c r="B818" s="26"/>
-      <c r="C818" s="26"/>
+      <c r="A818" s="29"/>
+      <c r="B818" s="29"/>
+      <c r="C818" s="29"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="A819" s="26"/>
-      <c r="B819" s="26"/>
-      <c r="C819" s="26"/>
+      <c r="A819" s="29"/>
+      <c r="B819" s="29"/>
+      <c r="C819" s="29"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="A820" s="26"/>
-      <c r="B820" s="26"/>
-      <c r="C820" s="26"/>
+      <c r="A820" s="29"/>
+      <c r="B820" s="29"/>
+      <c r="C820" s="29"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="A821" s="26"/>
-      <c r="B821" s="26"/>
-      <c r="C821" s="26"/>
+      <c r="A821" s="29"/>
+      <c r="B821" s="29"/>
+      <c r="C821" s="29"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="A822" s="26"/>
-      <c r="B822" s="26"/>
-      <c r="C822" s="26"/>
+      <c r="A822" s="29"/>
+      <c r="B822" s="29"/>
+      <c r="C822" s="29"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="A823" s="26"/>
-      <c r="B823" s="26"/>
-      <c r="C823" s="26"/>
+      <c r="A823" s="29"/>
+      <c r="B823" s="29"/>
+      <c r="C823" s="29"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="A824" s="26"/>
-      <c r="B824" s="26"/>
-      <c r="C824" s="26"/>
+      <c r="A824" s="29"/>
+      <c r="B824" s="29"/>
+      <c r="C824" s="29"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="A825" s="26"/>
-      <c r="B825" s="26"/>
-      <c r="C825" s="26"/>
+      <c r="A825" s="29"/>
+      <c r="B825" s="29"/>
+      <c r="C825" s="29"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="A826" s="26"/>
-      <c r="B826" s="26"/>
-      <c r="C826" s="26"/>
+      <c r="A826" s="29"/>
+      <c r="B826" s="29"/>
+      <c r="C826" s="29"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="A827" s="26"/>
-      <c r="B827" s="26"/>
-      <c r="C827" s="26"/>
+      <c r="A827" s="29"/>
+      <c r="B827" s="29"/>
+      <c r="C827" s="29"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="A828" s="26"/>
-      <c r="B828" s="26"/>
-      <c r="C828" s="26"/>
+      <c r="A828" s="29"/>
+      <c r="B828" s="29"/>
+      <c r="C828" s="29"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="A829" s="26"/>
-      <c r="B829" s="26"/>
-      <c r="C829" s="26"/>
+      <c r="A829" s="29"/>
+      <c r="B829" s="29"/>
+      <c r="C829" s="29"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="A830" s="26"/>
-      <c r="B830" s="26"/>
-      <c r="C830" s="26"/>
+      <c r="A830" s="29"/>
+      <c r="B830" s="29"/>
+      <c r="C830" s="29"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="A831" s="26"/>
-      <c r="B831" s="26"/>
-      <c r="C831" s="26"/>
+      <c r="A831" s="29"/>
+      <c r="B831" s="29"/>
+      <c r="C831" s="29"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="A832" s="26"/>
-      <c r="B832" s="26"/>
-      <c r="C832" s="26"/>
+      <c r="A832" s="29"/>
+      <c r="B832" s="29"/>
+      <c r="C832" s="29"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="A833" s="26"/>
-      <c r="B833" s="26"/>
-      <c r="C833" s="26"/>
+      <c r="A833" s="29"/>
+      <c r="B833" s="29"/>
+      <c r="C833" s="29"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="A834" s="26"/>
-      <c r="B834" s="26"/>
-      <c r="C834" s="26"/>
+      <c r="A834" s="29"/>
+      <c r="B834" s="29"/>
+      <c r="C834" s="29"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="A835" s="26"/>
-      <c r="B835" s="26"/>
-      <c r="C835" s="26"/>
+      <c r="A835" s="29"/>
+      <c r="B835" s="29"/>
+      <c r="C835" s="29"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="A836" s="26"/>
-      <c r="B836" s="26"/>
-      <c r="C836" s="26"/>
+      <c r="A836" s="29"/>
+      <c r="B836" s="29"/>
+      <c r="C836" s="29"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="A837" s="26"/>
-      <c r="B837" s="26"/>
-      <c r="C837" s="26"/>
+      <c r="A837" s="29"/>
+      <c r="B837" s="29"/>
+      <c r="C837" s="29"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="A838" s="26"/>
-      <c r="B838" s="26"/>
-      <c r="C838" s="26"/>
+      <c r="A838" s="29"/>
+      <c r="B838" s="29"/>
+      <c r="C838" s="29"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="A839" s="26"/>
-      <c r="B839" s="26"/>
-      <c r="C839" s="26"/>
+      <c r="A839" s="29"/>
+      <c r="B839" s="29"/>
+      <c r="C839" s="29"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="A840" s="26"/>
-      <c r="B840" s="26"/>
-      <c r="C840" s="26"/>
+      <c r="A840" s="29"/>
+      <c r="B840" s="29"/>
+      <c r="C840" s="29"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="A841" s="26"/>
-      <c r="B841" s="26"/>
-      <c r="C841" s="26"/>
+      <c r="A841" s="29"/>
+      <c r="B841" s="29"/>
+      <c r="C841" s="29"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="A842" s="26"/>
-      <c r="B842" s="26"/>
-      <c r="C842" s="26"/>
+      <c r="A842" s="29"/>
+      <c r="B842" s="29"/>
+      <c r="C842" s="29"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="A843" s="26"/>
-      <c r="B843" s="26"/>
-      <c r="C843" s="26"/>
+      <c r="A843" s="29"/>
+      <c r="B843" s="29"/>
+      <c r="C843" s="29"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="A844" s="26"/>
-      <c r="B844" s="26"/>
-      <c r="C844" s="26"/>
+      <c r="A844" s="29"/>
+      <c r="B844" s="29"/>
+      <c r="C844" s="29"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="A845" s="26"/>
-      <c r="B845" s="26"/>
-      <c r="C845" s="26"/>
+      <c r="A845" s="29"/>
+      <c r="B845" s="29"/>
+      <c r="C845" s="29"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="A846" s="26"/>
-      <c r="B846" s="26"/>
-      <c r="C846" s="26"/>
+      <c r="A846" s="29"/>
+      <c r="B846" s="29"/>
+      <c r="C846" s="29"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="A847" s="26"/>
-      <c r="B847" s="26"/>
-      <c r="C847" s="26"/>
+      <c r="A847" s="29"/>
+      <c r="B847" s="29"/>
+      <c r="C847" s="29"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="A848" s="26"/>
-      <c r="B848" s="26"/>
-      <c r="C848" s="26"/>
+      <c r="A848" s="29"/>
+      <c r="B848" s="29"/>
+      <c r="C848" s="29"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="A849" s="26"/>
-      <c r="B849" s="26"/>
-      <c r="C849" s="26"/>
+      <c r="A849" s="29"/>
+      <c r="B849" s="29"/>
+      <c r="C849" s="29"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="A850" s="26"/>
-      <c r="B850" s="26"/>
-      <c r="C850" s="26"/>
+      <c r="A850" s="29"/>
+      <c r="B850" s="29"/>
+      <c r="C850" s="29"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="A851" s="26"/>
-      <c r="B851" s="26"/>
-      <c r="C851" s="26"/>
+      <c r="A851" s="29"/>
+      <c r="B851" s="29"/>
+      <c r="C851" s="29"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="A852" s="26"/>
-      <c r="B852" s="26"/>
-      <c r="C852" s="26"/>
+      <c r="A852" s="29"/>
+      <c r="B852" s="29"/>
+      <c r="C852" s="29"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="A853" s="26"/>
-      <c r="B853" s="26"/>
-      <c r="C853" s="26"/>
+      <c r="A853" s="29"/>
+      <c r="B853" s="29"/>
+      <c r="C853" s="29"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="A854" s="26"/>
-      <c r="B854" s="26"/>
-      <c r="C854" s="26"/>
+      <c r="A854" s="29"/>
+      <c r="B854" s="29"/>
+      <c r="C854" s="29"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="A855" s="26"/>
-      <c r="B855" s="26"/>
-      <c r="C855" s="26"/>
+      <c r="A855" s="29"/>
+      <c r="B855" s="29"/>
+      <c r="C855" s="29"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="A856" s="26"/>
-      <c r="B856" s="26"/>
-      <c r="C856" s="26"/>
+      <c r="A856" s="29"/>
+      <c r="B856" s="29"/>
+      <c r="C856" s="29"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="A857" s="26"/>
-      <c r="B857" s="26"/>
-      <c r="C857" s="26"/>
+      <c r="A857" s="29"/>
+      <c r="B857" s="29"/>
+      <c r="C857" s="29"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="A858" s="26"/>
-      <c r="B858" s="26"/>
-      <c r="C858" s="26"/>
+      <c r="A858" s="29"/>
+      <c r="B858" s="29"/>
+      <c r="C858" s="29"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="A859" s="26"/>
-      <c r="B859" s="26"/>
-      <c r="C859" s="26"/>
+      <c r="A859" s="29"/>
+      <c r="B859" s="29"/>
+      <c r="C859" s="29"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="A860" s="26"/>
-      <c r="B860" s="26"/>
-      <c r="C860" s="26"/>
+      <c r="A860" s="29"/>
+      <c r="B860" s="29"/>
+      <c r="C860" s="29"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="A861" s="26"/>
-      <c r="B861" s="26"/>
-      <c r="C861" s="26"/>
+      <c r="A861" s="29"/>
+      <c r="B861" s="29"/>
+      <c r="C861" s="29"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="A862" s="26"/>
-      <c r="B862" s="26"/>
-      <c r="C862" s="26"/>
+      <c r="A862" s="29"/>
+      <c r="B862" s="29"/>
+      <c r="C862" s="29"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="A863" s="26"/>
-      <c r="B863" s="26"/>
-      <c r="C863" s="26"/>
+      <c r="A863" s="29"/>
+      <c r="B863" s="29"/>
+      <c r="C863" s="29"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="A864" s="26"/>
-      <c r="B864" s="26"/>
-      <c r="C864" s="26"/>
+      <c r="A864" s="29"/>
+      <c r="B864" s="29"/>
+      <c r="C864" s="29"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="A865" s="26"/>
-      <c r="B865" s="26"/>
-      <c r="C865" s="26"/>
+      <c r="A865" s="29"/>
+      <c r="B865" s="29"/>
+      <c r="C865" s="29"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="A866" s="26"/>
-      <c r="B866" s="26"/>
-      <c r="C866" s="26"/>
+      <c r="A866" s="29"/>
+      <c r="B866" s="29"/>
+      <c r="C866" s="29"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="A867" s="26"/>
-      <c r="B867" s="26"/>
-      <c r="C867" s="26"/>
+      <c r="A867" s="29"/>
+      <c r="B867" s="29"/>
+      <c r="C867" s="29"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="A868" s="26"/>
-      <c r="B868" s="26"/>
-      <c r="C868" s="26"/>
+      <c r="A868" s="29"/>
+      <c r="B868" s="29"/>
+      <c r="C868" s="29"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="A869" s="26"/>
-      <c r="B869" s="26"/>
-      <c r="C869" s="26"/>
+      <c r="A869" s="29"/>
+      <c r="B869" s="29"/>
+      <c r="C869" s="29"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="A870" s="26"/>
-      <c r="B870" s="26"/>
-      <c r="C870" s="26"/>
+      <c r="A870" s="29"/>
+      <c r="B870" s="29"/>
+      <c r="C870" s="29"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="26"/>
-      <c r="B871" s="26"/>
-      <c r="C871" s="26"/>
+      <c r="A871" s="29"/>
+      <c r="B871" s="29"/>
+      <c r="C871" s="29"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="A872" s="26"/>
-      <c r="B872" s="26"/>
-      <c r="C872" s="26"/>
+      <c r="A872" s="29"/>
+      <c r="B872" s="29"/>
+      <c r="C872" s="29"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="A873" s="26"/>
-      <c r="B873" s="26"/>
-      <c r="C873" s="26"/>
+      <c r="A873" s="29"/>
+      <c r="B873" s="29"/>
+      <c r="C873" s="29"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="A874" s="26"/>
-      <c r="B874" s="26"/>
-      <c r="C874" s="26"/>
+      <c r="A874" s="29"/>
+      <c r="B874" s="29"/>
+      <c r="C874" s="29"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="A875" s="26"/>
-      <c r="B875" s="26"/>
-      <c r="C875" s="26"/>
+      <c r="A875" s="29"/>
+      <c r="B875" s="29"/>
+      <c r="C875" s="29"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="26"/>
-      <c r="B876" s="26"/>
-      <c r="C876" s="26"/>
+      <c r="A876" s="29"/>
+      <c r="B876" s="29"/>
+      <c r="C876" s="29"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="A877" s="26"/>
-      <c r="B877" s="26"/>
-      <c r="C877" s="26"/>
+      <c r="A877" s="29"/>
+      <c r="B877" s="29"/>
+      <c r="C877" s="29"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="A878" s="26"/>
-      <c r="B878" s="26"/>
-      <c r="C878" s="26"/>
+      <c r="A878" s="29"/>
+      <c r="B878" s="29"/>
+      <c r="C878" s="29"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="A879" s="26"/>
-      <c r="B879" s="26"/>
-      <c r="C879" s="26"/>
+      <c r="A879" s="29"/>
+      <c r="B879" s="29"/>
+      <c r="C879" s="29"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="A880" s="26"/>
-      <c r="B880" s="26"/>
-      <c r="C880" s="26"/>
+      <c r="A880" s="29"/>
+      <c r="B880" s="29"/>
+      <c r="C880" s="29"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="A881" s="26"/>
-      <c r="B881" s="26"/>
-      <c r="C881" s="26"/>
+      <c r="A881" s="29"/>
+      <c r="B881" s="29"/>
+      <c r="C881" s="29"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="A882" s="26"/>
-      <c r="B882" s="26"/>
-      <c r="C882" s="26"/>
+      <c r="A882" s="29"/>
+      <c r="B882" s="29"/>
+      <c r="C882" s="29"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="A883" s="26"/>
-      <c r="B883" s="26"/>
-      <c r="C883" s="26"/>
+      <c r="A883" s="29"/>
+      <c r="B883" s="29"/>
+      <c r="C883" s="29"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="A884" s="26"/>
-      <c r="B884" s="26"/>
-      <c r="C884" s="26"/>
+      <c r="A884" s="29"/>
+      <c r="B884" s="29"/>
+      <c r="C884" s="29"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="A885" s="26"/>
-      <c r="B885" s="26"/>
-      <c r="C885" s="26"/>
+      <c r="A885" s="29"/>
+      <c r="B885" s="29"/>
+      <c r="C885" s="29"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="A886" s="26"/>
-      <c r="B886" s="26"/>
-      <c r="C886" s="26"/>
+      <c r="A886" s="29"/>
+      <c r="B886" s="29"/>
+      <c r="C886" s="29"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="A887" s="26"/>
-      <c r="B887" s="26"/>
-      <c r="C887" s="26"/>
+      <c r="A887" s="29"/>
+      <c r="B887" s="29"/>
+      <c r="C887" s="29"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="A888" s="26"/>
-      <c r="B888" s="26"/>
-      <c r="C888" s="26"/>
+      <c r="A888" s="29"/>
+      <c r="B888" s="29"/>
+      <c r="C888" s="29"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="A889" s="26"/>
-      <c r="B889" s="26"/>
-      <c r="C889" s="26"/>
+      <c r="A889" s="29"/>
+      <c r="B889" s="29"/>
+      <c r="C889" s="29"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="A890" s="26"/>
-      <c r="B890" s="26"/>
-      <c r="C890" s="26"/>
+      <c r="A890" s="29"/>
+      <c r="B890" s="29"/>
+      <c r="C890" s="29"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="A891" s="26"/>
-      <c r="B891" s="26"/>
-      <c r="C891" s="26"/>
+      <c r="A891" s="29"/>
+      <c r="B891" s="29"/>
+      <c r="C891" s="29"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="A892" s="26"/>
-      <c r="B892" s="26"/>
-      <c r="C892" s="26"/>
+      <c r="A892" s="29"/>
+      <c r="B892" s="29"/>
+      <c r="C892" s="29"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="A893" s="26"/>
-      <c r="B893" s="26"/>
-      <c r="C893" s="26"/>
+      <c r="A893" s="29"/>
+      <c r="B893" s="29"/>
+      <c r="C893" s="29"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="A894" s="26"/>
-      <c r="B894" s="26"/>
-      <c r="C894" s="26"/>
+      <c r="A894" s="29"/>
+      <c r="B894" s="29"/>
+      <c r="C894" s="29"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="A895" s="26"/>
-      <c r="B895" s="26"/>
-      <c r="C895" s="26"/>
+      <c r="A895" s="29"/>
+      <c r="B895" s="29"/>
+      <c r="C895" s="29"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="A896" s="26"/>
-      <c r="B896" s="26"/>
-      <c r="C896" s="26"/>
+      <c r="A896" s="29"/>
+      <c r="B896" s="29"/>
+      <c r="C896" s="29"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="A897" s="26"/>
-      <c r="B897" s="26"/>
-      <c r="C897" s="26"/>
+      <c r="A897" s="29"/>
+      <c r="B897" s="29"/>
+      <c r="C897" s="29"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="A898" s="26"/>
-      <c r="B898" s="26"/>
-      <c r="C898" s="26"/>
+      <c r="A898" s="29"/>
+      <c r="B898" s="29"/>
+      <c r="C898" s="29"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="A899" s="26"/>
-      <c r="B899" s="26"/>
-      <c r="C899" s="26"/>
+      <c r="A899" s="29"/>
+      <c r="B899" s="29"/>
+      <c r="C899" s="29"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="A900" s="26"/>
-      <c r="B900" s="26"/>
-      <c r="C900" s="26"/>
+      <c r="A900" s="29"/>
+      <c r="B900" s="29"/>
+      <c r="C900" s="29"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="A901" s="26"/>
-      <c r="B901" s="26"/>
-      <c r="C901" s="26"/>
+      <c r="A901" s="29"/>
+      <c r="B901" s="29"/>
+      <c r="C901" s="29"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="A902" s="26"/>
-      <c r="B902" s="26"/>
-      <c r="C902" s="26"/>
+      <c r="A902" s="29"/>
+      <c r="B902" s="29"/>
+      <c r="C902" s="29"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="A903" s="26"/>
-      <c r="B903" s="26"/>
-      <c r="C903" s="26"/>
+      <c r="A903" s="29"/>
+      <c r="B903" s="29"/>
+      <c r="C903" s="29"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="A904" s="26"/>
-      <c r="B904" s="26"/>
-      <c r="C904" s="26"/>
+      <c r="A904" s="29"/>
+      <c r="B904" s="29"/>
+      <c r="C904" s="29"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="A905" s="26"/>
-      <c r="B905" s="26"/>
-      <c r="C905" s="26"/>
+      <c r="A905" s="29"/>
+      <c r="B905" s="29"/>
+      <c r="C905" s="29"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="A906" s="26"/>
-      <c r="B906" s="26"/>
-      <c r="C906" s="26"/>
+      <c r="A906" s="29"/>
+      <c r="B906" s="29"/>
+      <c r="C906" s="29"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="A907" s="26"/>
-      <c r="B907" s="26"/>
-      <c r="C907" s="26"/>
+      <c r="A907" s="29"/>
+      <c r="B907" s="29"/>
+      <c r="C907" s="29"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="A908" s="26"/>
-      <c r="B908" s="26"/>
-      <c r="C908" s="26"/>
+      <c r="A908" s="29"/>
+      <c r="B908" s="29"/>
+      <c r="C908" s="29"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="A909" s="26"/>
-      <c r="B909" s="26"/>
-      <c r="C909" s="26"/>
+      <c r="A909" s="29"/>
+      <c r="B909" s="29"/>
+      <c r="C909" s="29"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="A910" s="26"/>
-      <c r="B910" s="26"/>
-      <c r="C910" s="26"/>
+      <c r="A910" s="29"/>
+      <c r="B910" s="29"/>
+      <c r="C910" s="29"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="A911" s="26"/>
-      <c r="B911" s="26"/>
-      <c r="C911" s="26"/>
+      <c r="A911" s="29"/>
+      <c r="B911" s="29"/>
+      <c r="C911" s="29"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="A912" s="26"/>
-      <c r="B912" s="26"/>
-      <c r="C912" s="26"/>
+      <c r="A912" s="29"/>
+      <c r="B912" s="29"/>
+      <c r="C912" s="29"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="A913" s="26"/>
-      <c r="B913" s="26"/>
-      <c r="C913" s="26"/>
+      <c r="A913" s="29"/>
+      <c r="B913" s="29"/>
+      <c r="C913" s="29"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="A914" s="26"/>
-      <c r="B914" s="26"/>
-      <c r="C914" s="26"/>
+      <c r="A914" s="29"/>
+      <c r="B914" s="29"/>
+      <c r="C914" s="29"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="A915" s="26"/>
-      <c r="B915" s="26"/>
-      <c r="C915" s="26"/>
+      <c r="A915" s="29"/>
+      <c r="B915" s="29"/>
+      <c r="C915" s="29"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="A916" s="26"/>
-      <c r="B916" s="26"/>
-      <c r="C916" s="26"/>
+      <c r="A916" s="29"/>
+      <c r="B916" s="29"/>
+      <c r="C916" s="29"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="A917" s="26"/>
-      <c r="B917" s="26"/>
-      <c r="C917" s="26"/>
+      <c r="A917" s="29"/>
+      <c r="B917" s="29"/>
+      <c r="C917" s="29"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="A918" s="26"/>
-      <c r="B918" s="26"/>
-      <c r="C918" s="26"/>
+      <c r="A918" s="29"/>
+      <c r="B918" s="29"/>
+      <c r="C918" s="29"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="A919" s="26"/>
-      <c r="B919" s="26"/>
-      <c r="C919" s="26"/>
+      <c r="A919" s="29"/>
+      <c r="B919" s="29"/>
+      <c r="C919" s="29"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="A920" s="26"/>
-      <c r="B920" s="26"/>
-      <c r="C920" s="26"/>
+      <c r="A920" s="29"/>
+      <c r="B920" s="29"/>
+      <c r="C920" s="29"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="A921" s="26"/>
-      <c r="B921" s="26"/>
-      <c r="C921" s="26"/>
+      <c r="A921" s="29"/>
+      <c r="B921" s="29"/>
+      <c r="C921" s="29"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="A922" s="26"/>
-      <c r="B922" s="26"/>
-      <c r="C922" s="26"/>
+      <c r="A922" s="29"/>
+      <c r="B922" s="29"/>
+      <c r="C922" s="29"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="A923" s="26"/>
-      <c r="B923" s="26"/>
-      <c r="C923" s="26"/>
+      <c r="A923" s="29"/>
+      <c r="B923" s="29"/>
+      <c r="C923" s="29"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="A924" s="26"/>
-      <c r="B924" s="26"/>
-      <c r="C924" s="26"/>
+      <c r="A924" s="29"/>
+      <c r="B924" s="29"/>
+      <c r="C924" s="29"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="A925" s="26"/>
-      <c r="B925" s="26"/>
-      <c r="C925" s="26"/>
+      <c r="A925" s="29"/>
+      <c r="B925" s="29"/>
+      <c r="C925" s="29"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="A926" s="26"/>
-      <c r="B926" s="26"/>
-      <c r="C926" s="26"/>
+      <c r="A926" s="29"/>
+      <c r="B926" s="29"/>
+      <c r="C926" s="29"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="A927" s="26"/>
-      <c r="B927" s="26"/>
-      <c r="C927" s="26"/>
+      <c r="A927" s="29"/>
+      <c r="B927" s="29"/>
+      <c r="C927" s="29"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="A928" s="26"/>
-      <c r="B928" s="26"/>
-      <c r="C928" s="26"/>
+      <c r="A928" s="29"/>
+      <c r="B928" s="29"/>
+      <c r="C928" s="29"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="A929" s="26"/>
-      <c r="B929" s="26"/>
-      <c r="C929" s="26"/>
+      <c r="A929" s="29"/>
+      <c r="B929" s="29"/>
+      <c r="C929" s="29"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="A930" s="26"/>
-      <c r="B930" s="26"/>
-      <c r="C930" s="26"/>
+      <c r="A930" s="29"/>
+      <c r="B930" s="29"/>
+      <c r="C930" s="29"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="A931" s="26"/>
-      <c r="B931" s="26"/>
-      <c r="C931" s="26"/>
+      <c r="A931" s="29"/>
+      <c r="B931" s="29"/>
+      <c r="C931" s="29"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="A932" s="26"/>
-      <c r="B932" s="26"/>
-      <c r="C932" s="26"/>
+      <c r="A932" s="29"/>
+      <c r="B932" s="29"/>
+      <c r="C932" s="29"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="A933" s="26"/>
-      <c r="B933" s="26"/>
-      <c r="C933" s="26"/>
+      <c r="A933" s="29"/>
+      <c r="B933" s="29"/>
+      <c r="C933" s="29"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="A934" s="26"/>
-      <c r="B934" s="26"/>
-      <c r="C934" s="26"/>
+      <c r="A934" s="29"/>
+      <c r="B934" s="29"/>
+      <c r="C934" s="29"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="A935" s="26"/>
-      <c r="B935" s="26"/>
-      <c r="C935" s="26"/>
+      <c r="A935" s="29"/>
+      <c r="B935" s="29"/>
+      <c r="C935" s="29"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="A936" s="26"/>
-      <c r="B936" s="26"/>
-      <c r="C936" s="26"/>
+      <c r="A936" s="29"/>
+      <c r="B936" s="29"/>
+      <c r="C936" s="29"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="A937" s="26"/>
-      <c r="B937" s="26"/>
-      <c r="C937" s="26"/>
+      <c r="A937" s="29"/>
+      <c r="B937" s="29"/>
+      <c r="C937" s="29"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="A938" s="26"/>
-      <c r="B938" s="26"/>
-      <c r="C938" s="26"/>
+      <c r="A938" s="29"/>
+      <c r="B938" s="29"/>
+      <c r="C938" s="29"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="A939" s="26"/>
-      <c r="B939" s="26"/>
-      <c r="C939" s="26"/>
+      <c r="A939" s="29"/>
+      <c r="B939" s="29"/>
+      <c r="C939" s="29"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="A940" s="26"/>
-      <c r="B940" s="26"/>
-      <c r="C940" s="26"/>
+      <c r="A940" s="29"/>
+      <c r="B940" s="29"/>
+      <c r="C940" s="29"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="A941" s="26"/>
-      <c r="B941" s="26"/>
-      <c r="C941" s="26"/>
+      <c r="A941" s="29"/>
+      <c r="B941" s="29"/>
+      <c r="C941" s="29"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="A942" s="26"/>
-      <c r="B942" s="26"/>
-      <c r="C942" s="26"/>
+      <c r="A942" s="29"/>
+      <c r="B942" s="29"/>
+      <c r="C942" s="29"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="A943" s="26"/>
-      <c r="B943" s="26"/>
-      <c r="C943" s="26"/>
+      <c r="A943" s="29"/>
+      <c r="B943" s="29"/>
+      <c r="C943" s="29"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="A944" s="26"/>
-      <c r="B944" s="26"/>
-      <c r="C944" s="26"/>
+      <c r="A944" s="29"/>
+      <c r="B944" s="29"/>
+      <c r="C944" s="29"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="A945" s="26"/>
-      <c r="B945" s="26"/>
-      <c r="C945" s="26"/>
+      <c r="A945" s="29"/>
+      <c r="B945" s="29"/>
+      <c r="C945" s="29"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="A946" s="26"/>
-      <c r="B946" s="26"/>
-      <c r="C946" s="26"/>
+      <c r="A946" s="29"/>
+      <c r="B946" s="29"/>
+      <c r="C946" s="29"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="A947" s="26"/>
-      <c r="B947" s="26"/>
-      <c r="C947" s="26"/>
+      <c r="A947" s="29"/>
+      <c r="B947" s="29"/>
+      <c r="C947" s="29"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="A948" s="26"/>
-      <c r="B948" s="26"/>
-      <c r="C948" s="26"/>
+      <c r="A948" s="29"/>
+      <c r="B948" s="29"/>
+      <c r="C948" s="29"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="A949" s="26"/>
-      <c r="B949" s="26"/>
-      <c r="C949" s="26"/>
+      <c r="A949" s="29"/>
+      <c r="B949" s="29"/>
+      <c r="C949" s="29"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="A950" s="26"/>
-      <c r="B950" s="26"/>
-      <c r="C950" s="26"/>
+      <c r="A950" s="29"/>
+      <c r="B950" s="29"/>
+      <c r="C950" s="29"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="A951" s="26"/>
-      <c r="B951" s="26"/>
-      <c r="C951" s="26"/>
+      <c r="A951" s="29"/>
+      <c r="B951" s="29"/>
+      <c r="C951" s="29"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="A952" s="26"/>
-      <c r="B952" s="26"/>
-      <c r="C952" s="26"/>
+      <c r="A952" s="29"/>
+      <c r="B952" s="29"/>
+      <c r="C952" s="29"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="A953" s="26"/>
-      <c r="B953" s="26"/>
-      <c r="C953" s="26"/>
+      <c r="A953" s="29"/>
+      <c r="B953" s="29"/>
+      <c r="C953" s="29"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="A954" s="26"/>
-      <c r="B954" s="26"/>
-      <c r="C954" s="26"/>
+      <c r="A954" s="29"/>
+      <c r="B954" s="29"/>
+      <c r="C954" s="29"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="A955" s="26"/>
-      <c r="B955" s="26"/>
-      <c r="C955" s="26"/>
+      <c r="A955" s="29"/>
+      <c r="B955" s="29"/>
+      <c r="C955" s="29"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="A956" s="26"/>
-      <c r="B956" s="26"/>
-      <c r="C956" s="26"/>
+      <c r="A956" s="29"/>
+      <c r="B956" s="29"/>
+      <c r="C956" s="29"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="A957" s="26"/>
-      <c r="B957" s="26"/>
-      <c r="C957" s="26"/>
+      <c r="A957" s="29"/>
+      <c r="B957" s="29"/>
+      <c r="C957" s="29"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="A958" s="26"/>
-      <c r="B958" s="26"/>
-      <c r="C958" s="26"/>
+      <c r="A958" s="29"/>
+      <c r="B958" s="29"/>
+      <c r="C958" s="29"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="A959" s="26"/>
-      <c r="B959" s="26"/>
-      <c r="C959" s="26"/>
+      <c r="A959" s="29"/>
+      <c r="B959" s="29"/>
+      <c r="C959" s="29"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="A960" s="26"/>
-      <c r="B960" s="26"/>
-      <c r="C960" s="26"/>
+      <c r="A960" s="29"/>
+      <c r="B960" s="29"/>
+      <c r="C960" s="29"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="A961" s="26"/>
-      <c r="B961" s="26"/>
-      <c r="C961" s="26"/>
+      <c r="A961" s="29"/>
+      <c r="B961" s="29"/>
+      <c r="C961" s="29"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="A962" s="26"/>
-      <c r="B962" s="26"/>
-      <c r="C962" s="26"/>
+      <c r="A962" s="29"/>
+      <c r="B962" s="29"/>
+      <c r="C962" s="29"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="A963" s="26"/>
-      <c r="B963" s="26"/>
-      <c r="C963" s="26"/>
+      <c r="A963" s="29"/>
+      <c r="B963" s="29"/>
+      <c r="C963" s="29"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="A964" s="26"/>
-      <c r="B964" s="26"/>
-      <c r="C964" s="26"/>
+      <c r="A964" s="29"/>
+      <c r="B964" s="29"/>
+      <c r="C964" s="29"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="A965" s="26"/>
-      <c r="B965" s="26"/>
-      <c r="C965" s="26"/>
+      <c r="A965" s="29"/>
+      <c r="B965" s="29"/>
+      <c r="C965" s="29"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="A966" s="26"/>
-      <c r="B966" s="26"/>
-      <c r="C966" s="26"/>
+      <c r="A966" s="29"/>
+      <c r="B966" s="29"/>
+      <c r="C966" s="29"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="A967" s="26"/>
-      <c r="B967" s="26"/>
-      <c r="C967" s="26"/>
+      <c r="A967" s="29"/>
+      <c r="B967" s="29"/>
+      <c r="C967" s="29"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="A968" s="26"/>
-      <c r="B968" s="26"/>
-      <c r="C968" s="26"/>
+      <c r="A968" s="29"/>
+      <c r="B968" s="29"/>
+      <c r="C968" s="29"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="A969" s="26"/>
-      <c r="B969" s="26"/>
-      <c r="C969" s="26"/>
+      <c r="A969" s="29"/>
+      <c r="B969" s="29"/>
+      <c r="C969" s="29"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="A970" s="26"/>
-      <c r="B970" s="26"/>
-      <c r="C970" s="26"/>
+      <c r="A970" s="29"/>
+      <c r="B970" s="29"/>
+      <c r="C970" s="29"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="A971" s="26"/>
-      <c r="B971" s="26"/>
-      <c r="C971" s="26"/>
+      <c r="A971" s="29"/>
+      <c r="B971" s="29"/>
+      <c r="C971" s="29"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="A972" s="26"/>
-      <c r="B972" s="26"/>
-      <c r="C972" s="26"/>
+      <c r="A972" s="29"/>
+      <c r="B972" s="29"/>
+      <c r="C972" s="29"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="A973" s="26"/>
-      <c r="B973" s="26"/>
-      <c r="C973" s="26"/>
+      <c r="A973" s="29"/>
+      <c r="B973" s="29"/>
+      <c r="C973" s="29"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="A974" s="26"/>
-      <c r="B974" s="26"/>
-      <c r="C974" s="26"/>
+      <c r="A974" s="29"/>
+      <c r="B974" s="29"/>
+      <c r="C974" s="29"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="A975" s="26"/>
-      <c r="B975" s="26"/>
-      <c r="C975" s="26"/>
+      <c r="A975" s="29"/>
+      <c r="B975" s="29"/>
+      <c r="C975" s="29"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="A976" s="26"/>
-      <c r="B976" s="26"/>
-      <c r="C976" s="26"/>
+      <c r="A976" s="29"/>
+      <c r="B976" s="29"/>
+      <c r="C976" s="29"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="A977" s="26"/>
-      <c r="B977" s="26"/>
-      <c r="C977" s="26"/>
+      <c r="A977" s="29"/>
+      <c r="B977" s="29"/>
+      <c r="C977" s="29"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="A978" s="26"/>
-      <c r="B978" s="26"/>
-      <c r="C978" s="26"/>
+      <c r="A978" s="29"/>
+      <c r="B978" s="29"/>
+      <c r="C978" s="29"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="A979" s="26"/>
-      <c r="B979" s="26"/>
-      <c r="C979" s="26"/>
+      <c r="A979" s="29"/>
+      <c r="B979" s="29"/>
+      <c r="C979" s="29"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="A980" s="26"/>
-      <c r="B980" s="26"/>
-      <c r="C980" s="26"/>
+      <c r="A980" s="29"/>
+      <c r="B980" s="29"/>
+      <c r="C980" s="29"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="A981" s="26"/>
-      <c r="B981" s="26"/>
-      <c r="C981" s="26"/>
+      <c r="A981" s="29"/>
+      <c r="B981" s="29"/>
+      <c r="C981" s="29"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="A982" s="26"/>
-      <c r="B982" s="26"/>
-      <c r="C982" s="26"/>
+      <c r="A982" s="29"/>
+      <c r="B982" s="29"/>
+      <c r="C982" s="29"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="A983" s="26"/>
-      <c r="B983" s="26"/>
-      <c r="C983" s="26"/>
+      <c r="A983" s="29"/>
+      <c r="B983" s="29"/>
+      <c r="C983" s="29"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="A984" s="26"/>
-      <c r="B984" s="26"/>
-      <c r="C984" s="26"/>
+      <c r="A984" s="29"/>
+      <c r="B984" s="29"/>
+      <c r="C984" s="29"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="A985" s="26"/>
-      <c r="B985" s="26"/>
-      <c r="C985" s="26"/>
+      <c r="A985" s="29"/>
+      <c r="B985" s="29"/>
+      <c r="C985" s="29"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="A986" s="26"/>
-      <c r="B986" s="26"/>
-      <c r="C986" s="26"/>
+      <c r="A986" s="29"/>
+      <c r="B986" s="29"/>
+      <c r="C986" s="29"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="A987" s="26"/>
-      <c r="B987" s="26"/>
-      <c r="C987" s="26"/>
+      <c r="A987" s="29"/>
+      <c r="B987" s="29"/>
+      <c r="C987" s="29"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="A988" s="26"/>
-      <c r="B988" s="26"/>
-      <c r="C988" s="26"/>
+      <c r="A988" s="29"/>
+      <c r="B988" s="29"/>
+      <c r="C988" s="29"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="A989" s="26"/>
-      <c r="B989" s="26"/>
-      <c r="C989" s="26"/>
+      <c r="A989" s="29"/>
+      <c r="B989" s="29"/>
+      <c r="C989" s="29"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="A990" s="26"/>
-      <c r="B990" s="26"/>
-      <c r="C990" s="26"/>
+      <c r="A990" s="29"/>
+      <c r="B990" s="29"/>
+      <c r="C990" s="29"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="A991" s="26"/>
-      <c r="B991" s="26"/>
-      <c r="C991" s="26"/>
+      <c r="A991" s="29"/>
+      <c r="B991" s="29"/>
+      <c r="C991" s="29"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="A992" s="26"/>
-      <c r="B992" s="26"/>
-      <c r="C992" s="26"/>
+      <c r="A992" s="29"/>
+      <c r="B992" s="29"/>
+      <c r="C992" s="29"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="A993" s="26"/>
-      <c r="B993" s="26"/>
-      <c r="C993" s="26"/>
+      <c r="A993" s="29"/>
+      <c r="B993" s="29"/>
+      <c r="C993" s="29"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="A994" s="26"/>
-      <c r="B994" s="26"/>
-      <c r="C994" s="26"/>
+      <c r="A994" s="29"/>
+      <c r="B994" s="29"/>
+      <c r="C994" s="29"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="A995" s="26"/>
-      <c r="B995" s="26"/>
-      <c r="C995" s="26"/>
+      <c r="A995" s="29"/>
+      <c r="B995" s="29"/>
+      <c r="C995" s="29"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="26"/>
-      <c r="B996" s="26"/>
-      <c r="C996" s="26"/>
+      <c r="A996" s="29"/>
+      <c r="B996" s="29"/>
+      <c r="C996" s="29"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="26"/>
-      <c r="B997" s="26"/>
-      <c r="C997" s="26"/>
+      <c r="A997" s="29"/>
+      <c r="B997" s="29"/>
+      <c r="C997" s="29"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="26"/>
-      <c r="B998" s="26"/>
-      <c r="C998" s="26"/>
+      <c r="A998" s="29"/>
+      <c r="B998" s="29"/>
+      <c r="C998" s="29"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="26"/>
-      <c r="B999" s="26"/>
-      <c r="C999" s="26"/>
+      <c r="A999" s="29"/>
+      <c r="B999" s="29"/>
+      <c r="C999" s="29"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="26"/>
-      <c r="B1000" s="26"/>
-      <c r="C1000" s="26"/>
+      <c r="A1000" s="29"/>
+      <c r="B1000" s="29"/>
+      <c r="C1000" s="29"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="A1001" s="26"/>
-      <c r="B1001" s="26"/>
-      <c r="C1001" s="26"/>
+      <c r="A1001" s="29"/>
+      <c r="B1001" s="29"/>
+      <c r="C1001" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6883,84 +6897,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="B1" s="27" t="s">
-        <v>102</v>
+      <c r="B1" s="30" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="28" t="s">
-        <v>103</v>
+      <c r="B3" s="31" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="28" t="s">
-        <v>104</v>
+      <c r="B4" s="31" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="28" t="s">
-        <v>105</v>
+      <c r="B5" s="31" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="28" t="s">
-        <v>106</v>
+      <c r="B6" s="31" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="28" t="s">
-        <v>107</v>
+      <c r="B7" s="31" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="28" t="s">
-        <v>108</v>
+      <c r="B8" s="31" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="28" t="s">
-        <v>109</v>
+      <c r="B9" s="31" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="28" t="s">
-        <v>110</v>
+      <c r="B10" s="31" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="28" t="s">
-        <v>111</v>
+      <c r="B11" s="31" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="28" t="s">
-        <v>112</v>
+      <c r="B12" s="31" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="28" t="s">
-        <v>113</v>
+      <c r="B13" s="31" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="28" t="s">
-        <v>114</v>
+      <c r="B14" s="31" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="28" t="s">
-        <v>115</v>
+      <c r="B15" s="31" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="28" t="s">
-        <v>116</v>
+      <c r="B16" s="31" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="28" t="s">
-        <v>117</v>
+      <c r="B17" s="31" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7973,237 +7987,237 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="29"/>
-      <c r="C2" s="29"/>
+      <c r="A2" s="32" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="26"/>
-      <c r="B3" s="30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="26"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="29"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="26"/>
-      <c r="B4" s="31" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="26"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="34" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="29"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="32" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="32"/>
-      <c r="C5" s="32"/>
+      <c r="A5" s="35" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="34" t="s">
+      <c r="A7" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="34" t="s">
+      <c r="B7" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="33" t="s">
+      <c r="C7" s="37" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="33" t="s">
+      <c r="D7" s="36" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="33" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="33" t="s">
+      <c r="F7" s="36" t="s">
         <v>127</v>
       </c>
+      <c r="G7" s="36" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="35">
+      <c r="A8" s="38">
         <v>1.0</v>
       </c>
-      <c r="B8" s="36" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="36" t="s">
+      <c r="B8" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="37" t="s">
+      <c r="C8" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="38" t="s">
+      <c r="D8" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="39"/>
-      <c r="G8" s="40"/>
+      <c r="E8" s="41" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="41">
+      <c r="A9" s="44">
         <v>2.0</v>
       </c>
-      <c r="B9" s="42" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="42" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="43" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="44" t="s">
+      <c r="B9" s="45" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="45"/>
-      <c r="G9" s="40"/>
+      <c r="D9" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="47" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="48"/>
+      <c r="G9" s="43"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="46">
+      <c r="A10" s="49">
         <v>3.0</v>
       </c>
-      <c r="B10" s="47" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="47" t="s">
+      <c r="B10" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="48" t="s">
+      <c r="C10" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="49" t="s">
+      <c r="D10" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="51"/>
+      <c r="E10" s="52" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="35"/>
-      <c r="B11" s="36"/>
-      <c r="C11" s="36"/>
-      <c r="D11" s="37" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="38" t="s">
+      <c r="A11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="52"/>
-      <c r="G11" s="53"/>
+      <c r="E11" s="41" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="55"/>
+      <c r="G11" s="56"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="54">
+      <c r="A12" s="57">
         <v>4.0</v>
       </c>
-      <c r="B12" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="55" t="s">
+      <c r="B12" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="56" t="s">
+      <c r="C12" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="E12" s="57" t="s">
+      <c r="D12" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="58"/>
-      <c r="G12" s="59"/>
+      <c r="E12" s="60" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="61"/>
+      <c r="G12" s="62"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="35"/>
-      <c r="B13" s="36"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="38" t="s">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="F13" s="39"/>
-      <c r="G13" s="53"/>
+      <c r="E13" s="41" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="42"/>
+      <c r="G13" s="56"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="54">
+      <c r="A14" s="57">
         <v>5.0</v>
       </c>
-      <c r="B14" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="55" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="56" t="s">
+      <c r="B14" s="58" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="58" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="57" t="s">
+      <c r="D14" s="59" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="58"/>
-      <c r="G14" s="59"/>
+      <c r="E14" s="60" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="35"/>
-      <c r="B15" s="36"/>
-      <c r="C15" s="36"/>
-      <c r="D15" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="60" t="s">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="53"/>
+      <c r="F15" s="63" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="56"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="54">
+      <c r="A16" s="57">
         <v>6.0</v>
       </c>
-      <c r="B16" s="55" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="55" t="s">
+      <c r="B16" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="57" t="s">
+      <c r="C16" s="58" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="59" t="s">
         <v>152</v>
       </c>
-      <c r="F16" s="61"/>
-      <c r="G16" s="59"/>
+      <c r="E16" s="60" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="64"/>
+      <c r="G16" s="62"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="35"/>
-      <c r="B17" s="36"/>
-      <c r="C17" s="36"/>
-      <c r="D17" s="37" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="38" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="62"/>
-      <c r="G17" s="53"/>
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="40" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="41" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="65"/>
+      <c r="G17" s="56"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="46"/>
-      <c r="B18" s="46"/>
-      <c r="C18" s="46"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="47"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
     </row>
     <row r="19" ht="12.75" customHeight="1"/>
     <row r="20" ht="12.75" customHeight="1"/>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -238,9 +238,6 @@
   </si>
   <si>
     <t>User is successfully logged out and redirected to login page</t>
-  </si>
-  <si>
-    <t>Upon logout session credentials aren't being cleared due to which pressing login again logs in the same user</t>
   </si>
   <si>
     <t>Cancel Booking</t>
@@ -770,7 +767,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -842,9 +839,6 @@
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -1614,10 +1608,8 @@
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="22"/>
-      <c r="H18" s="26"/>
-      <c r="I18" s="20" t="s">
-        <v>66</v>
-      </c>
+      <c r="H18" s="23"/>
+      <c r="I18" s="20"/>
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="19">
@@ -1625,16 +1617,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="E19" s="20" t="s">
         <v>69</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>70</v>
       </c>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
@@ -1647,16 +1639,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>72</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
@@ -1669,16 +1661,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="D21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="E21" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -1691,16 +1683,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="E22" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -1713,16 +1705,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C23" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D23" s="20" t="s">
+        <v>81</v>
+      </c>
+      <c r="E23" s="20" t="s">
         <v>82</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>83</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -1735,16 +1727,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="20" t="s">
         <v>50</v>
       </c>
       <c r="D24" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -1757,16 +1749,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>87</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>88</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -1778,17 +1770,17 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="26" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="E26" s="20" t="s">
         <v>91</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>92</v>
       </c>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -1801,16 +1793,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>94</v>
       </c>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
@@ -1823,16 +1815,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>95</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>96</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
@@ -1859,7 +1851,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="22"/>
-      <c r="C30" s="28"/>
+      <c r="C30" s="27"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -1873,7 +1865,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="22"/>
-      <c r="C31" s="28"/>
+      <c r="C31" s="27"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -1910,31 +1902,31 @@
       <c r="I33" s="22"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="29"/>
-      <c r="B34" s="29"/>
-      <c r="C34" s="29"/>
+      <c r="A34" s="28"/>
+      <c r="B34" s="28"/>
+      <c r="C34" s="28"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="29"/>
-      <c r="B35" s="29"/>
-      <c r="C35" s="29"/>
+      <c r="A35" s="28"/>
+      <c r="B35" s="28"/>
+      <c r="C35" s="28"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="29"/>
-      <c r="B36" s="29"/>
-      <c r="C36" s="29"/>
+      <c r="A36" s="28"/>
+      <c r="B36" s="28"/>
+      <c r="C36" s="28"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="29"/>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
+      <c r="A37" s="28"/>
+      <c r="B37" s="28"/>
+      <c r="C37" s="28"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="29"/>
-      <c r="B38" s="29"/>
-      <c r="C38" s="29"/>
+      <c r="A38" s="28"/>
+      <c r="B38" s="28"/>
+      <c r="C38" s="28"/>
       <c r="K38" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -1942,11 +1934,11 @@
       <c r="T38" s="4"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="29"/>
-      <c r="B39" s="29"/>
-      <c r="C39" s="29"/>
+      <c r="A39" s="28"/>
+      <c r="B39" s="28"/>
+      <c r="C39" s="28"/>
       <c r="K39" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
@@ -1954,11 +1946,11 @@
       <c r="T39" s="4"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="29"/>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
+      <c r="A40" s="28"/>
+      <c r="B40" s="28"/>
+      <c r="C40" s="28"/>
       <c r="K40" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
@@ -1966,11 +1958,11 @@
       <c r="T40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="29"/>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
+      <c r="A41" s="28"/>
+      <c r="B41" s="28"/>
+      <c r="C41" s="28"/>
       <c r="K41" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
@@ -1978,11 +1970,11 @@
       <c r="T41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="29"/>
-      <c r="B42" s="29"/>
-      <c r="C42" s="29"/>
+      <c r="A42" s="28"/>
+      <c r="B42" s="28"/>
+      <c r="C42" s="28"/>
       <c r="K42" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
@@ -1990,11 +1982,11 @@
       <c r="T42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="29"/>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
+      <c r="A43" s="28"/>
+      <c r="B43" s="28"/>
+      <c r="C43" s="28"/>
       <c r="K43" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
@@ -2002,45 +1994,45 @@
       <c r="T43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="29"/>
-      <c r="B44" s="29"/>
-      <c r="C44" s="29"/>
+      <c r="A44" s="28"/>
+      <c r="B44" s="28"/>
+      <c r="C44" s="28"/>
       <c r="K44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="29"/>
-      <c r="B45" s="29"/>
-      <c r="C45" s="29"/>
+      <c r="A45" s="28"/>
+      <c r="B45" s="28"/>
+      <c r="C45" s="28"/>
       <c r="K45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="29"/>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
+      <c r="A46" s="28"/>
+      <c r="B46" s="28"/>
+      <c r="C46" s="28"/>
       <c r="K46" s="4"/>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="29"/>
-      <c r="B47" s="29"/>
-      <c r="C47" s="29"/>
+      <c r="A47" s="28"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
       <c r="K47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="29"/>
-      <c r="B48" s="29"/>
-      <c r="C48" s="29"/>
+      <c r="A48" s="28"/>
+      <c r="B48" s="28"/>
+      <c r="C48" s="28"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -2053,9 +2045,9 @@
       <c r="T48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="29"/>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
+      <c r="A49" s="28"/>
+      <c r="B49" s="28"/>
+      <c r="C49" s="28"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -2068,9 +2060,9 @@
       <c r="T49" s="4"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="29"/>
-      <c r="B50" s="29"/>
-      <c r="C50" s="29"/>
+      <c r="A50" s="28"/>
+      <c r="B50" s="28"/>
+      <c r="C50" s="28"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -2083,9 +2075,9 @@
       <c r="T50" s="4"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="29"/>
-      <c r="B51" s="29"/>
-      <c r="C51" s="29"/>
+      <c r="A51" s="28"/>
+      <c r="B51" s="28"/>
+      <c r="C51" s="28"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -2098,9 +2090,9 @@
       <c r="T51" s="4"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="29"/>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
+      <c r="A52" s="28"/>
+      <c r="B52" s="28"/>
+      <c r="C52" s="28"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -2113,4749 +2105,4749 @@
       <c r="T52" s="4"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="29"/>
-      <c r="B53" s="29"/>
-      <c r="C53" s="29"/>
+      <c r="A53" s="28"/>
+      <c r="B53" s="28"/>
+      <c r="C53" s="28"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="29"/>
-      <c r="B54" s="29"/>
-      <c r="C54" s="29"/>
+      <c r="A54" s="28"/>
+      <c r="B54" s="28"/>
+      <c r="C54" s="28"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="29"/>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
+      <c r="A55" s="28"/>
+      <c r="B55" s="28"/>
+      <c r="C55" s="28"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="29"/>
-      <c r="B56" s="29"/>
-      <c r="C56" s="29"/>
+      <c r="A56" s="28"/>
+      <c r="B56" s="28"/>
+      <c r="C56" s="28"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="29"/>
-      <c r="B57" s="29"/>
-      <c r="C57" s="29"/>
+      <c r="A57" s="28"/>
+      <c r="B57" s="28"/>
+      <c r="C57" s="28"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="29"/>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
+      <c r="A58" s="28"/>
+      <c r="B58" s="28"/>
+      <c r="C58" s="28"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="29"/>
-      <c r="B59" s="29"/>
-      <c r="C59" s="29"/>
+      <c r="A59" s="28"/>
+      <c r="B59" s="28"/>
+      <c r="C59" s="28"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="29"/>
-      <c r="B60" s="29"/>
-      <c r="C60" s="29"/>
+      <c r="A60" s="28"/>
+      <c r="B60" s="28"/>
+      <c r="C60" s="28"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="29"/>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
+      <c r="A61" s="28"/>
+      <c r="B61" s="28"/>
+      <c r="C61" s="28"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="29"/>
-      <c r="B62" s="29"/>
-      <c r="C62" s="29"/>
+      <c r="A62" s="28"/>
+      <c r="B62" s="28"/>
+      <c r="C62" s="28"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="29"/>
-      <c r="B63" s="29"/>
-      <c r="C63" s="29"/>
+      <c r="A63" s="28"/>
+      <c r="B63" s="28"/>
+      <c r="C63" s="28"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="29"/>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
+      <c r="A64" s="28"/>
+      <c r="B64" s="28"/>
+      <c r="C64" s="28"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="29"/>
-      <c r="B65" s="29"/>
-      <c r="C65" s="29"/>
+      <c r="A65" s="28"/>
+      <c r="B65" s="28"/>
+      <c r="C65" s="28"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="29"/>
-      <c r="B66" s="29"/>
-      <c r="C66" s="29"/>
+      <c r="A66" s="28"/>
+      <c r="B66" s="28"/>
+      <c r="C66" s="28"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="29"/>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
+      <c r="A67" s="28"/>
+      <c r="B67" s="28"/>
+      <c r="C67" s="28"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="29"/>
-      <c r="B68" s="29"/>
-      <c r="C68" s="29"/>
+      <c r="A68" s="28"/>
+      <c r="B68" s="28"/>
+      <c r="C68" s="28"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="29"/>
-      <c r="B69" s="29"/>
-      <c r="C69" s="29"/>
+      <c r="A69" s="28"/>
+      <c r="B69" s="28"/>
+      <c r="C69" s="28"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="29"/>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
+      <c r="A70" s="28"/>
+      <c r="B70" s="28"/>
+      <c r="C70" s="28"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="29"/>
-      <c r="B71" s="29"/>
-      <c r="C71" s="29"/>
+      <c r="A71" s="28"/>
+      <c r="B71" s="28"/>
+      <c r="C71" s="28"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="29"/>
-      <c r="B72" s="29"/>
-      <c r="C72" s="29"/>
+      <c r="A72" s="28"/>
+      <c r="B72" s="28"/>
+      <c r="C72" s="28"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="29"/>
-      <c r="B73" s="29"/>
-      <c r="C73" s="29"/>
+      <c r="A73" s="28"/>
+      <c r="B73" s="28"/>
+      <c r="C73" s="28"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="29"/>
-      <c r="B74" s="29"/>
-      <c r="C74" s="29"/>
+      <c r="A74" s="28"/>
+      <c r="B74" s="28"/>
+      <c r="C74" s="28"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="29"/>
-      <c r="B75" s="29"/>
-      <c r="C75" s="29"/>
+      <c r="A75" s="28"/>
+      <c r="B75" s="28"/>
+      <c r="C75" s="28"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="29"/>
-      <c r="B76" s="29"/>
-      <c r="C76" s="29"/>
+      <c r="A76" s="28"/>
+      <c r="B76" s="28"/>
+      <c r="C76" s="28"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="29"/>
-      <c r="B77" s="29"/>
-      <c r="C77" s="29"/>
+      <c r="A77" s="28"/>
+      <c r="B77" s="28"/>
+      <c r="C77" s="28"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="29"/>
-      <c r="B78" s="29"/>
-      <c r="C78" s="29"/>
+      <c r="A78" s="28"/>
+      <c r="B78" s="28"/>
+      <c r="C78" s="28"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="29"/>
-      <c r="B79" s="29"/>
-      <c r="C79" s="29"/>
+      <c r="A79" s="28"/>
+      <c r="B79" s="28"/>
+      <c r="C79" s="28"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="29"/>
-      <c r="B80" s="29"/>
-      <c r="C80" s="29"/>
+      <c r="A80" s="28"/>
+      <c r="B80" s="28"/>
+      <c r="C80" s="28"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="29"/>
-      <c r="B81" s="29"/>
-      <c r="C81" s="29"/>
+      <c r="A81" s="28"/>
+      <c r="B81" s="28"/>
+      <c r="C81" s="28"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="29"/>
-      <c r="B82" s="29"/>
-      <c r="C82" s="29"/>
+      <c r="A82" s="28"/>
+      <c r="B82" s="28"/>
+      <c r="C82" s="28"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="29"/>
-      <c r="B83" s="29"/>
-      <c r="C83" s="29"/>
+      <c r="A83" s="28"/>
+      <c r="B83" s="28"/>
+      <c r="C83" s="28"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="29"/>
-      <c r="B84" s="29"/>
-      <c r="C84" s="29"/>
+      <c r="A84" s="28"/>
+      <c r="B84" s="28"/>
+      <c r="C84" s="28"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="29"/>
-      <c r="B85" s="29"/>
-      <c r="C85" s="29"/>
+      <c r="A85" s="28"/>
+      <c r="B85" s="28"/>
+      <c r="C85" s="28"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="29"/>
-      <c r="B86" s="29"/>
-      <c r="C86" s="29"/>
+      <c r="A86" s="28"/>
+      <c r="B86" s="28"/>
+      <c r="C86" s="28"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="29"/>
-      <c r="B87" s="29"/>
-      <c r="C87" s="29"/>
+      <c r="A87" s="28"/>
+      <c r="B87" s="28"/>
+      <c r="C87" s="28"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="29"/>
-      <c r="B88" s="29"/>
-      <c r="C88" s="29"/>
+      <c r="A88" s="28"/>
+      <c r="B88" s="28"/>
+      <c r="C88" s="28"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="29"/>
-      <c r="B89" s="29"/>
-      <c r="C89" s="29"/>
+      <c r="A89" s="28"/>
+      <c r="B89" s="28"/>
+      <c r="C89" s="28"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="29"/>
-      <c r="B90" s="29"/>
-      <c r="C90" s="29"/>
+      <c r="A90" s="28"/>
+      <c r="B90" s="28"/>
+      <c r="C90" s="28"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="29"/>
-      <c r="B91" s="29"/>
-      <c r="C91" s="29"/>
+      <c r="A91" s="28"/>
+      <c r="B91" s="28"/>
+      <c r="C91" s="28"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="29"/>
-      <c r="B92" s="29"/>
-      <c r="C92" s="29"/>
+      <c r="A92" s="28"/>
+      <c r="B92" s="28"/>
+      <c r="C92" s="28"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="29"/>
-      <c r="B93" s="29"/>
-      <c r="C93" s="29"/>
+      <c r="A93" s="28"/>
+      <c r="B93" s="28"/>
+      <c r="C93" s="28"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="29"/>
-      <c r="B94" s="29"/>
-      <c r="C94" s="29"/>
+      <c r="A94" s="28"/>
+      <c r="B94" s="28"/>
+      <c r="C94" s="28"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="29"/>
-      <c r="B95" s="29"/>
-      <c r="C95" s="29"/>
+      <c r="A95" s="28"/>
+      <c r="B95" s="28"/>
+      <c r="C95" s="28"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="29"/>
-      <c r="B96" s="29"/>
-      <c r="C96" s="29"/>
+      <c r="A96" s="28"/>
+      <c r="B96" s="28"/>
+      <c r="C96" s="28"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="29"/>
-      <c r="B97" s="29"/>
-      <c r="C97" s="29"/>
+      <c r="A97" s="28"/>
+      <c r="B97" s="28"/>
+      <c r="C97" s="28"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="A98" s="29"/>
-      <c r="B98" s="29"/>
-      <c r="C98" s="29"/>
+      <c r="A98" s="28"/>
+      <c r="B98" s="28"/>
+      <c r="C98" s="28"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="A99" s="29"/>
-      <c r="B99" s="29"/>
-      <c r="C99" s="29"/>
+      <c r="A99" s="28"/>
+      <c r="B99" s="28"/>
+      <c r="C99" s="28"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="A100" s="29"/>
-      <c r="B100" s="29"/>
-      <c r="C100" s="29"/>
+      <c r="A100" s="28"/>
+      <c r="B100" s="28"/>
+      <c r="C100" s="28"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="A101" s="29"/>
-      <c r="B101" s="29"/>
-      <c r="C101" s="29"/>
+      <c r="A101" s="28"/>
+      <c r="B101" s="28"/>
+      <c r="C101" s="28"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="A102" s="29"/>
-      <c r="B102" s="29"/>
-      <c r="C102" s="29"/>
+      <c r="A102" s="28"/>
+      <c r="B102" s="28"/>
+      <c r="C102" s="28"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="A103" s="29"/>
-      <c r="B103" s="29"/>
-      <c r="C103" s="29"/>
+      <c r="A103" s="28"/>
+      <c r="B103" s="28"/>
+      <c r="C103" s="28"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" s="29"/>
-      <c r="B104" s="29"/>
-      <c r="C104" s="29"/>
+      <c r="A104" s="28"/>
+      <c r="B104" s="28"/>
+      <c r="C104" s="28"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="29"/>
-      <c r="B105" s="29"/>
-      <c r="C105" s="29"/>
+      <c r="A105" s="28"/>
+      <c r="B105" s="28"/>
+      <c r="C105" s="28"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="29"/>
-      <c r="B106" s="29"/>
-      <c r="C106" s="29"/>
+      <c r="A106" s="28"/>
+      <c r="B106" s="28"/>
+      <c r="C106" s="28"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="29"/>
-      <c r="B107" s="29"/>
-      <c r="C107" s="29"/>
+      <c r="A107" s="28"/>
+      <c r="B107" s="28"/>
+      <c r="C107" s="28"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="29"/>
-      <c r="B108" s="29"/>
-      <c r="C108" s="29"/>
+      <c r="A108" s="28"/>
+      <c r="B108" s="28"/>
+      <c r="C108" s="28"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="29"/>
-      <c r="B109" s="29"/>
-      <c r="C109" s="29"/>
+      <c r="A109" s="28"/>
+      <c r="B109" s="28"/>
+      <c r="C109" s="28"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="29"/>
-      <c r="B110" s="29"/>
-      <c r="C110" s="29"/>
+      <c r="A110" s="28"/>
+      <c r="B110" s="28"/>
+      <c r="C110" s="28"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="29"/>
-      <c r="B111" s="29"/>
-      <c r="C111" s="29"/>
+      <c r="A111" s="28"/>
+      <c r="B111" s="28"/>
+      <c r="C111" s="28"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="A112" s="29"/>
-      <c r="B112" s="29"/>
-      <c r="C112" s="29"/>
+      <c r="A112" s="28"/>
+      <c r="B112" s="28"/>
+      <c r="C112" s="28"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="A113" s="29"/>
-      <c r="B113" s="29"/>
-      <c r="C113" s="29"/>
+      <c r="A113" s="28"/>
+      <c r="B113" s="28"/>
+      <c r="C113" s="28"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="29"/>
-      <c r="B114" s="29"/>
-      <c r="C114" s="29"/>
+      <c r="A114" s="28"/>
+      <c r="B114" s="28"/>
+      <c r="C114" s="28"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="29"/>
-      <c r="B115" s="29"/>
-      <c r="C115" s="29"/>
+      <c r="A115" s="28"/>
+      <c r="B115" s="28"/>
+      <c r="C115" s="28"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="29"/>
-      <c r="B116" s="29"/>
-      <c r="C116" s="29"/>
+      <c r="A116" s="28"/>
+      <c r="B116" s="28"/>
+      <c r="C116" s="28"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="A117" s="29"/>
-      <c r="B117" s="29"/>
-      <c r="C117" s="29"/>
+      <c r="A117" s="28"/>
+      <c r="B117" s="28"/>
+      <c r="C117" s="28"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="A118" s="29"/>
-      <c r="B118" s="29"/>
-      <c r="C118" s="29"/>
+      <c r="A118" s="28"/>
+      <c r="B118" s="28"/>
+      <c r="C118" s="28"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="29"/>
-      <c r="B119" s="29"/>
-      <c r="C119" s="29"/>
+      <c r="A119" s="28"/>
+      <c r="B119" s="28"/>
+      <c r="C119" s="28"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="A120" s="29"/>
-      <c r="B120" s="29"/>
-      <c r="C120" s="29"/>
+      <c r="A120" s="28"/>
+      <c r="B120" s="28"/>
+      <c r="C120" s="28"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="A121" s="29"/>
-      <c r="B121" s="29"/>
-      <c r="C121" s="29"/>
+      <c r="A121" s="28"/>
+      <c r="B121" s="28"/>
+      <c r="C121" s="28"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="A122" s="29"/>
-      <c r="B122" s="29"/>
-      <c r="C122" s="29"/>
+      <c r="A122" s="28"/>
+      <c r="B122" s="28"/>
+      <c r="C122" s="28"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="A123" s="29"/>
-      <c r="B123" s="29"/>
-      <c r="C123" s="29"/>
+      <c r="A123" s="28"/>
+      <c r="B123" s="28"/>
+      <c r="C123" s="28"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="A124" s="29"/>
-      <c r="B124" s="29"/>
-      <c r="C124" s="29"/>
+      <c r="A124" s="28"/>
+      <c r="B124" s="28"/>
+      <c r="C124" s="28"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="A125" s="29"/>
-      <c r="B125" s="29"/>
-      <c r="C125" s="29"/>
+      <c r="A125" s="28"/>
+      <c r="B125" s="28"/>
+      <c r="C125" s="28"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="A126" s="29"/>
-      <c r="B126" s="29"/>
-      <c r="C126" s="29"/>
+      <c r="A126" s="28"/>
+      <c r="B126" s="28"/>
+      <c r="C126" s="28"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="29"/>
-      <c r="B127" s="29"/>
-      <c r="C127" s="29"/>
+      <c r="A127" s="28"/>
+      <c r="B127" s="28"/>
+      <c r="C127" s="28"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="29"/>
-      <c r="B128" s="29"/>
-      <c r="C128" s="29"/>
+      <c r="A128" s="28"/>
+      <c r="B128" s="28"/>
+      <c r="C128" s="28"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="A129" s="29"/>
-      <c r="B129" s="29"/>
-      <c r="C129" s="29"/>
+      <c r="A129" s="28"/>
+      <c r="B129" s="28"/>
+      <c r="C129" s="28"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="A130" s="29"/>
-      <c r="B130" s="29"/>
-      <c r="C130" s="29"/>
+      <c r="A130" s="28"/>
+      <c r="B130" s="28"/>
+      <c r="C130" s="28"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="A131" s="29"/>
-      <c r="B131" s="29"/>
-      <c r="C131" s="29"/>
+      <c r="A131" s="28"/>
+      <c r="B131" s="28"/>
+      <c r="C131" s="28"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="A132" s="29"/>
-      <c r="B132" s="29"/>
-      <c r="C132" s="29"/>
+      <c r="A132" s="28"/>
+      <c r="B132" s="28"/>
+      <c r="C132" s="28"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="A133" s="29"/>
-      <c r="B133" s="29"/>
-      <c r="C133" s="29"/>
+      <c r="A133" s="28"/>
+      <c r="B133" s="28"/>
+      <c r="C133" s="28"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="A134" s="29"/>
-      <c r="B134" s="29"/>
-      <c r="C134" s="29"/>
+      <c r="A134" s="28"/>
+      <c r="B134" s="28"/>
+      <c r="C134" s="28"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="A135" s="29"/>
-      <c r="B135" s="29"/>
-      <c r="C135" s="29"/>
+      <c r="A135" s="28"/>
+      <c r="B135" s="28"/>
+      <c r="C135" s="28"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="A136" s="29"/>
-      <c r="B136" s="29"/>
-      <c r="C136" s="29"/>
+      <c r="A136" s="28"/>
+      <c r="B136" s="28"/>
+      <c r="C136" s="28"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="A137" s="29"/>
-      <c r="B137" s="29"/>
-      <c r="C137" s="29"/>
+      <c r="A137" s="28"/>
+      <c r="B137" s="28"/>
+      <c r="C137" s="28"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="A138" s="29"/>
-      <c r="B138" s="29"/>
-      <c r="C138" s="29"/>
+      <c r="A138" s="28"/>
+      <c r="B138" s="28"/>
+      <c r="C138" s="28"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="A139" s="29"/>
-      <c r="B139" s="29"/>
-      <c r="C139" s="29"/>
+      <c r="A139" s="28"/>
+      <c r="B139" s="28"/>
+      <c r="C139" s="28"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="A140" s="29"/>
-      <c r="B140" s="29"/>
-      <c r="C140" s="29"/>
+      <c r="A140" s="28"/>
+      <c r="B140" s="28"/>
+      <c r="C140" s="28"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="A141" s="29"/>
-      <c r="B141" s="29"/>
-      <c r="C141" s="29"/>
+      <c r="A141" s="28"/>
+      <c r="B141" s="28"/>
+      <c r="C141" s="28"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="A142" s="29"/>
-      <c r="B142" s="29"/>
-      <c r="C142" s="29"/>
+      <c r="A142" s="28"/>
+      <c r="B142" s="28"/>
+      <c r="C142" s="28"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="A143" s="29"/>
-      <c r="B143" s="29"/>
-      <c r="C143" s="29"/>
+      <c r="A143" s="28"/>
+      <c r="B143" s="28"/>
+      <c r="C143" s="28"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="A144" s="29"/>
-      <c r="B144" s="29"/>
-      <c r="C144" s="29"/>
+      <c r="A144" s="28"/>
+      <c r="B144" s="28"/>
+      <c r="C144" s="28"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="A145" s="29"/>
-      <c r="B145" s="29"/>
-      <c r="C145" s="29"/>
+      <c r="A145" s="28"/>
+      <c r="B145" s="28"/>
+      <c r="C145" s="28"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="A146" s="29"/>
-      <c r="B146" s="29"/>
-      <c r="C146" s="29"/>
+      <c r="A146" s="28"/>
+      <c r="B146" s="28"/>
+      <c r="C146" s="28"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="A147" s="29"/>
-      <c r="B147" s="29"/>
-      <c r="C147" s="29"/>
+      <c r="A147" s="28"/>
+      <c r="B147" s="28"/>
+      <c r="C147" s="28"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="29"/>
-      <c r="B148" s="29"/>
-      <c r="C148" s="29"/>
+      <c r="A148" s="28"/>
+      <c r="B148" s="28"/>
+      <c r="C148" s="28"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="A149" s="29"/>
-      <c r="B149" s="29"/>
-      <c r="C149" s="29"/>
+      <c r="A149" s="28"/>
+      <c r="B149" s="28"/>
+      <c r="C149" s="28"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="A150" s="29"/>
-      <c r="B150" s="29"/>
-      <c r="C150" s="29"/>
+      <c r="A150" s="28"/>
+      <c r="B150" s="28"/>
+      <c r="C150" s="28"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="A151" s="29"/>
-      <c r="B151" s="29"/>
-      <c r="C151" s="29"/>
+      <c r="A151" s="28"/>
+      <c r="B151" s="28"/>
+      <c r="C151" s="28"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="A152" s="29"/>
-      <c r="B152" s="29"/>
-      <c r="C152" s="29"/>
+      <c r="A152" s="28"/>
+      <c r="B152" s="28"/>
+      <c r="C152" s="28"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="A153" s="29"/>
-      <c r="B153" s="29"/>
-      <c r="C153" s="29"/>
+      <c r="A153" s="28"/>
+      <c r="B153" s="28"/>
+      <c r="C153" s="28"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="A154" s="29"/>
-      <c r="B154" s="29"/>
-      <c r="C154" s="29"/>
+      <c r="A154" s="28"/>
+      <c r="B154" s="28"/>
+      <c r="C154" s="28"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="A155" s="29"/>
-      <c r="B155" s="29"/>
-      <c r="C155" s="29"/>
+      <c r="A155" s="28"/>
+      <c r="B155" s="28"/>
+      <c r="C155" s="28"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="A156" s="29"/>
-      <c r="B156" s="29"/>
-      <c r="C156" s="29"/>
+      <c r="A156" s="28"/>
+      <c r="B156" s="28"/>
+      <c r="C156" s="28"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="A157" s="29"/>
-      <c r="B157" s="29"/>
-      <c r="C157" s="29"/>
+      <c r="A157" s="28"/>
+      <c r="B157" s="28"/>
+      <c r="C157" s="28"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="A158" s="29"/>
-      <c r="B158" s="29"/>
-      <c r="C158" s="29"/>
+      <c r="A158" s="28"/>
+      <c r="B158" s="28"/>
+      <c r="C158" s="28"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="A159" s="29"/>
-      <c r="B159" s="29"/>
-      <c r="C159" s="29"/>
+      <c r="A159" s="28"/>
+      <c r="B159" s="28"/>
+      <c r="C159" s="28"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="A160" s="29"/>
-      <c r="B160" s="29"/>
-      <c r="C160" s="29"/>
+      <c r="A160" s="28"/>
+      <c r="B160" s="28"/>
+      <c r="C160" s="28"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="A161" s="29"/>
-      <c r="B161" s="29"/>
-      <c r="C161" s="29"/>
+      <c r="A161" s="28"/>
+      <c r="B161" s="28"/>
+      <c r="C161" s="28"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="A162" s="29"/>
-      <c r="B162" s="29"/>
-      <c r="C162" s="29"/>
+      <c r="A162" s="28"/>
+      <c r="B162" s="28"/>
+      <c r="C162" s="28"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="A163" s="29"/>
-      <c r="B163" s="29"/>
-      <c r="C163" s="29"/>
+      <c r="A163" s="28"/>
+      <c r="B163" s="28"/>
+      <c r="C163" s="28"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="A164" s="29"/>
-      <c r="B164" s="29"/>
-      <c r="C164" s="29"/>
+      <c r="A164" s="28"/>
+      <c r="B164" s="28"/>
+      <c r="C164" s="28"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="A165" s="29"/>
-      <c r="B165" s="29"/>
-      <c r="C165" s="29"/>
+      <c r="A165" s="28"/>
+      <c r="B165" s="28"/>
+      <c r="C165" s="28"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="A166" s="29"/>
-      <c r="B166" s="29"/>
-      <c r="C166" s="29"/>
+      <c r="A166" s="28"/>
+      <c r="B166" s="28"/>
+      <c r="C166" s="28"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="A167" s="29"/>
-      <c r="B167" s="29"/>
-      <c r="C167" s="29"/>
+      <c r="A167" s="28"/>
+      <c r="B167" s="28"/>
+      <c r="C167" s="28"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="29"/>
-      <c r="B168" s="29"/>
-      <c r="C168" s="29"/>
+      <c r="A168" s="28"/>
+      <c r="B168" s="28"/>
+      <c r="C168" s="28"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="A169" s="29"/>
-      <c r="B169" s="29"/>
-      <c r="C169" s="29"/>
+      <c r="A169" s="28"/>
+      <c r="B169" s="28"/>
+      <c r="C169" s="28"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="A170" s="29"/>
-      <c r="B170" s="29"/>
-      <c r="C170" s="29"/>
+      <c r="A170" s="28"/>
+      <c r="B170" s="28"/>
+      <c r="C170" s="28"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="A171" s="29"/>
-      <c r="B171" s="29"/>
-      <c r="C171" s="29"/>
+      <c r="A171" s="28"/>
+      <c r="B171" s="28"/>
+      <c r="C171" s="28"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="A172" s="29"/>
-      <c r="B172" s="29"/>
-      <c r="C172" s="29"/>
+      <c r="A172" s="28"/>
+      <c r="B172" s="28"/>
+      <c r="C172" s="28"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="A173" s="29"/>
-      <c r="B173" s="29"/>
-      <c r="C173" s="29"/>
+      <c r="A173" s="28"/>
+      <c r="B173" s="28"/>
+      <c r="C173" s="28"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="A174" s="29"/>
-      <c r="B174" s="29"/>
-      <c r="C174" s="29"/>
+      <c r="A174" s="28"/>
+      <c r="B174" s="28"/>
+      <c r="C174" s="28"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="A175" s="29"/>
-      <c r="B175" s="29"/>
-      <c r="C175" s="29"/>
+      <c r="A175" s="28"/>
+      <c r="B175" s="28"/>
+      <c r="C175" s="28"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="A176" s="29"/>
-      <c r="B176" s="29"/>
-      <c r="C176" s="29"/>
+      <c r="A176" s="28"/>
+      <c r="B176" s="28"/>
+      <c r="C176" s="28"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="A177" s="29"/>
-      <c r="B177" s="29"/>
-      <c r="C177" s="29"/>
+      <c r="A177" s="28"/>
+      <c r="B177" s="28"/>
+      <c r="C177" s="28"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="29"/>
-      <c r="B178" s="29"/>
-      <c r="C178" s="29"/>
+      <c r="A178" s="28"/>
+      <c r="B178" s="28"/>
+      <c r="C178" s="28"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="A179" s="29"/>
-      <c r="B179" s="29"/>
-      <c r="C179" s="29"/>
+      <c r="A179" s="28"/>
+      <c r="B179" s="28"/>
+      <c r="C179" s="28"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="A180" s="29"/>
-      <c r="B180" s="29"/>
-      <c r="C180" s="29"/>
+      <c r="A180" s="28"/>
+      <c r="B180" s="28"/>
+      <c r="C180" s="28"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="A181" s="29"/>
-      <c r="B181" s="29"/>
-      <c r="C181" s="29"/>
+      <c r="A181" s="28"/>
+      <c r="B181" s="28"/>
+      <c r="C181" s="28"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="A182" s="29"/>
-      <c r="B182" s="29"/>
-      <c r="C182" s="29"/>
+      <c r="A182" s="28"/>
+      <c r="B182" s="28"/>
+      <c r="C182" s="28"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="A183" s="29"/>
-      <c r="B183" s="29"/>
-      <c r="C183" s="29"/>
+      <c r="A183" s="28"/>
+      <c r="B183" s="28"/>
+      <c r="C183" s="28"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="A184" s="29"/>
-      <c r="B184" s="29"/>
-      <c r="C184" s="29"/>
+      <c r="A184" s="28"/>
+      <c r="B184" s="28"/>
+      <c r="C184" s="28"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="A185" s="29"/>
-      <c r="B185" s="29"/>
-      <c r="C185" s="29"/>
+      <c r="A185" s="28"/>
+      <c r="B185" s="28"/>
+      <c r="C185" s="28"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="A186" s="29"/>
-      <c r="B186" s="29"/>
-      <c r="C186" s="29"/>
+      <c r="A186" s="28"/>
+      <c r="B186" s="28"/>
+      <c r="C186" s="28"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="A187" s="29"/>
-      <c r="B187" s="29"/>
-      <c r="C187" s="29"/>
+      <c r="A187" s="28"/>
+      <c r="B187" s="28"/>
+      <c r="C187" s="28"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="29"/>
-      <c r="B188" s="29"/>
-      <c r="C188" s="29"/>
+      <c r="A188" s="28"/>
+      <c r="B188" s="28"/>
+      <c r="C188" s="28"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="A189" s="29"/>
-      <c r="B189" s="29"/>
-      <c r="C189" s="29"/>
+      <c r="A189" s="28"/>
+      <c r="B189" s="28"/>
+      <c r="C189" s="28"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="A190" s="29"/>
-      <c r="B190" s="29"/>
-      <c r="C190" s="29"/>
+      <c r="A190" s="28"/>
+      <c r="B190" s="28"/>
+      <c r="C190" s="28"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="A191" s="29"/>
-      <c r="B191" s="29"/>
-      <c r="C191" s="29"/>
+      <c r="A191" s="28"/>
+      <c r="B191" s="28"/>
+      <c r="C191" s="28"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="A192" s="29"/>
-      <c r="B192" s="29"/>
-      <c r="C192" s="29"/>
+      <c r="A192" s="28"/>
+      <c r="B192" s="28"/>
+      <c r="C192" s="28"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="A193" s="29"/>
-      <c r="B193" s="29"/>
-      <c r="C193" s="29"/>
+      <c r="A193" s="28"/>
+      <c r="B193" s="28"/>
+      <c r="C193" s="28"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="A194" s="29"/>
-      <c r="B194" s="29"/>
-      <c r="C194" s="29"/>
+      <c r="A194" s="28"/>
+      <c r="B194" s="28"/>
+      <c r="C194" s="28"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="A195" s="29"/>
-      <c r="B195" s="29"/>
-      <c r="C195" s="29"/>
+      <c r="A195" s="28"/>
+      <c r="B195" s="28"/>
+      <c r="C195" s="28"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="A196" s="29"/>
-      <c r="B196" s="29"/>
-      <c r="C196" s="29"/>
+      <c r="A196" s="28"/>
+      <c r="B196" s="28"/>
+      <c r="C196" s="28"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="A197" s="29"/>
-      <c r="B197" s="29"/>
-      <c r="C197" s="29"/>
+      <c r="A197" s="28"/>
+      <c r="B197" s="28"/>
+      <c r="C197" s="28"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="A198" s="29"/>
-      <c r="B198" s="29"/>
-      <c r="C198" s="29"/>
+      <c r="A198" s="28"/>
+      <c r="B198" s="28"/>
+      <c r="C198" s="28"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="A199" s="29"/>
-      <c r="B199" s="29"/>
-      <c r="C199" s="29"/>
+      <c r="A199" s="28"/>
+      <c r="B199" s="28"/>
+      <c r="C199" s="28"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="A200" s="29"/>
-      <c r="B200" s="29"/>
-      <c r="C200" s="29"/>
+      <c r="A200" s="28"/>
+      <c r="B200" s="28"/>
+      <c r="C200" s="28"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="A201" s="29"/>
-      <c r="B201" s="29"/>
-      <c r="C201" s="29"/>
+      <c r="A201" s="28"/>
+      <c r="B201" s="28"/>
+      <c r="C201" s="28"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="A202" s="29"/>
-      <c r="B202" s="29"/>
-      <c r="C202" s="29"/>
+      <c r="A202" s="28"/>
+      <c r="B202" s="28"/>
+      <c r="C202" s="28"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="A203" s="29"/>
-      <c r="B203" s="29"/>
-      <c r="C203" s="29"/>
+      <c r="A203" s="28"/>
+      <c r="B203" s="28"/>
+      <c r="C203" s="28"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="A204" s="29"/>
-      <c r="B204" s="29"/>
-      <c r="C204" s="29"/>
+      <c r="A204" s="28"/>
+      <c r="B204" s="28"/>
+      <c r="C204" s="28"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="A205" s="29"/>
-      <c r="B205" s="29"/>
-      <c r="C205" s="29"/>
+      <c r="A205" s="28"/>
+      <c r="B205" s="28"/>
+      <c r="C205" s="28"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="A206" s="29"/>
-      <c r="B206" s="29"/>
-      <c r="C206" s="29"/>
+      <c r="A206" s="28"/>
+      <c r="B206" s="28"/>
+      <c r="C206" s="28"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="A207" s="29"/>
-      <c r="B207" s="29"/>
-      <c r="C207" s="29"/>
+      <c r="A207" s="28"/>
+      <c r="B207" s="28"/>
+      <c r="C207" s="28"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="29"/>
-      <c r="B208" s="29"/>
-      <c r="C208" s="29"/>
+      <c r="A208" s="28"/>
+      <c r="B208" s="28"/>
+      <c r="C208" s="28"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="A209" s="29"/>
-      <c r="B209" s="29"/>
-      <c r="C209" s="29"/>
+      <c r="A209" s="28"/>
+      <c r="B209" s="28"/>
+      <c r="C209" s="28"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="A210" s="29"/>
-      <c r="B210" s="29"/>
-      <c r="C210" s="29"/>
+      <c r="A210" s="28"/>
+      <c r="B210" s="28"/>
+      <c r="C210" s="28"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="A211" s="29"/>
-      <c r="B211" s="29"/>
-      <c r="C211" s="29"/>
+      <c r="A211" s="28"/>
+      <c r="B211" s="28"/>
+      <c r="C211" s="28"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="A212" s="29"/>
-      <c r="B212" s="29"/>
-      <c r="C212" s="29"/>
+      <c r="A212" s="28"/>
+      <c r="B212" s="28"/>
+      <c r="C212" s="28"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="A213" s="29"/>
-      <c r="B213" s="29"/>
-      <c r="C213" s="29"/>
+      <c r="A213" s="28"/>
+      <c r="B213" s="28"/>
+      <c r="C213" s="28"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="A214" s="29"/>
-      <c r="B214" s="29"/>
-      <c r="C214" s="29"/>
+      <c r="A214" s="28"/>
+      <c r="B214" s="28"/>
+      <c r="C214" s="28"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="A215" s="29"/>
-      <c r="B215" s="29"/>
-      <c r="C215" s="29"/>
+      <c r="A215" s="28"/>
+      <c r="B215" s="28"/>
+      <c r="C215" s="28"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="A216" s="29"/>
-      <c r="B216" s="29"/>
-      <c r="C216" s="29"/>
+      <c r="A216" s="28"/>
+      <c r="B216" s="28"/>
+      <c r="C216" s="28"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="A217" s="29"/>
-      <c r="B217" s="29"/>
-      <c r="C217" s="29"/>
+      <c r="A217" s="28"/>
+      <c r="B217" s="28"/>
+      <c r="C217" s="28"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="A218" s="29"/>
-      <c r="B218" s="29"/>
-      <c r="C218" s="29"/>
+      <c r="A218" s="28"/>
+      <c r="B218" s="28"/>
+      <c r="C218" s="28"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="A219" s="29"/>
-      <c r="B219" s="29"/>
-      <c r="C219" s="29"/>
+      <c r="A219" s="28"/>
+      <c r="B219" s="28"/>
+      <c r="C219" s="28"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="A220" s="29"/>
-      <c r="B220" s="29"/>
-      <c r="C220" s="29"/>
+      <c r="A220" s="28"/>
+      <c r="B220" s="28"/>
+      <c r="C220" s="28"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="A221" s="29"/>
-      <c r="B221" s="29"/>
-      <c r="C221" s="29"/>
+      <c r="A221" s="28"/>
+      <c r="B221" s="28"/>
+      <c r="C221" s="28"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="A222" s="29"/>
-      <c r="B222" s="29"/>
-      <c r="C222" s="29"/>
+      <c r="A222" s="28"/>
+      <c r="B222" s="28"/>
+      <c r="C222" s="28"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="A223" s="29"/>
-      <c r="B223" s="29"/>
-      <c r="C223" s="29"/>
+      <c r="A223" s="28"/>
+      <c r="B223" s="28"/>
+      <c r="C223" s="28"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="A224" s="29"/>
-      <c r="B224" s="29"/>
-      <c r="C224" s="29"/>
+      <c r="A224" s="28"/>
+      <c r="B224" s="28"/>
+      <c r="C224" s="28"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="A225" s="29"/>
-      <c r="B225" s="29"/>
-      <c r="C225" s="29"/>
+      <c r="A225" s="28"/>
+      <c r="B225" s="28"/>
+      <c r="C225" s="28"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="29"/>
-      <c r="B226" s="29"/>
-      <c r="C226" s="29"/>
+      <c r="A226" s="28"/>
+      <c r="B226" s="28"/>
+      <c r="C226" s="28"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="29"/>
-      <c r="B227" s="29"/>
-      <c r="C227" s="29"/>
+      <c r="A227" s="28"/>
+      <c r="B227" s="28"/>
+      <c r="C227" s="28"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="29"/>
-      <c r="B228" s="29"/>
-      <c r="C228" s="29"/>
+      <c r="A228" s="28"/>
+      <c r="B228" s="28"/>
+      <c r="C228" s="28"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="29"/>
-      <c r="B229" s="29"/>
-      <c r="C229" s="29"/>
+      <c r="A229" s="28"/>
+      <c r="B229" s="28"/>
+      <c r="C229" s="28"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="29"/>
-      <c r="B230" s="29"/>
-      <c r="C230" s="29"/>
+      <c r="A230" s="28"/>
+      <c r="B230" s="28"/>
+      <c r="C230" s="28"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="A231" s="29"/>
-      <c r="B231" s="29"/>
-      <c r="C231" s="29"/>
+      <c r="A231" s="28"/>
+      <c r="B231" s="28"/>
+      <c r="C231" s="28"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="A232" s="29"/>
-      <c r="B232" s="29"/>
-      <c r="C232" s="29"/>
+      <c r="A232" s="28"/>
+      <c r="B232" s="28"/>
+      <c r="C232" s="28"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="A233" s="29"/>
-      <c r="B233" s="29"/>
-      <c r="C233" s="29"/>
+      <c r="A233" s="28"/>
+      <c r="B233" s="28"/>
+      <c r="C233" s="28"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="A234" s="29"/>
-      <c r="B234" s="29"/>
-      <c r="C234" s="29"/>
+      <c r="A234" s="28"/>
+      <c r="B234" s="28"/>
+      <c r="C234" s="28"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="A235" s="29"/>
-      <c r="B235" s="29"/>
-      <c r="C235" s="29"/>
+      <c r="A235" s="28"/>
+      <c r="B235" s="28"/>
+      <c r="C235" s="28"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="A236" s="29"/>
-      <c r="B236" s="29"/>
-      <c r="C236" s="29"/>
+      <c r="A236" s="28"/>
+      <c r="B236" s="28"/>
+      <c r="C236" s="28"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="A237" s="29"/>
-      <c r="B237" s="29"/>
-      <c r="C237" s="29"/>
+      <c r="A237" s="28"/>
+      <c r="B237" s="28"/>
+      <c r="C237" s="28"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="A238" s="29"/>
-      <c r="B238" s="29"/>
-      <c r="C238" s="29"/>
+      <c r="A238" s="28"/>
+      <c r="B238" s="28"/>
+      <c r="C238" s="28"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="A239" s="29"/>
-      <c r="B239" s="29"/>
-      <c r="C239" s="29"/>
+      <c r="A239" s="28"/>
+      <c r="B239" s="28"/>
+      <c r="C239" s="28"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="A240" s="29"/>
-      <c r="B240" s="29"/>
-      <c r="C240" s="29"/>
+      <c r="A240" s="28"/>
+      <c r="B240" s="28"/>
+      <c r="C240" s="28"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="A241" s="29"/>
-      <c r="B241" s="29"/>
-      <c r="C241" s="29"/>
+      <c r="A241" s="28"/>
+      <c r="B241" s="28"/>
+      <c r="C241" s="28"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="A242" s="29"/>
-      <c r="B242" s="29"/>
-      <c r="C242" s="29"/>
+      <c r="A242" s="28"/>
+      <c r="B242" s="28"/>
+      <c r="C242" s="28"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="A243" s="29"/>
-      <c r="B243" s="29"/>
-      <c r="C243" s="29"/>
+      <c r="A243" s="28"/>
+      <c r="B243" s="28"/>
+      <c r="C243" s="28"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="A244" s="29"/>
-      <c r="B244" s="29"/>
-      <c r="C244" s="29"/>
+      <c r="A244" s="28"/>
+      <c r="B244" s="28"/>
+      <c r="C244" s="28"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="A245" s="29"/>
-      <c r="B245" s="29"/>
-      <c r="C245" s="29"/>
+      <c r="A245" s="28"/>
+      <c r="B245" s="28"/>
+      <c r="C245" s="28"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="A246" s="29"/>
-      <c r="B246" s="29"/>
-      <c r="C246" s="29"/>
+      <c r="A246" s="28"/>
+      <c r="B246" s="28"/>
+      <c r="C246" s="28"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="A247" s="29"/>
-      <c r="B247" s="29"/>
-      <c r="C247" s="29"/>
+      <c r="A247" s="28"/>
+      <c r="B247" s="28"/>
+      <c r="C247" s="28"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="29"/>
-      <c r="B248" s="29"/>
-      <c r="C248" s="29"/>
+      <c r="A248" s="28"/>
+      <c r="B248" s="28"/>
+      <c r="C248" s="28"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="A249" s="29"/>
-      <c r="B249" s="29"/>
-      <c r="C249" s="29"/>
+      <c r="A249" s="28"/>
+      <c r="B249" s="28"/>
+      <c r="C249" s="28"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="A250" s="29"/>
-      <c r="B250" s="29"/>
-      <c r="C250" s="29"/>
+      <c r="A250" s="28"/>
+      <c r="B250" s="28"/>
+      <c r="C250" s="28"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="A251" s="29"/>
-      <c r="B251" s="29"/>
-      <c r="C251" s="29"/>
+      <c r="A251" s="28"/>
+      <c r="B251" s="28"/>
+      <c r="C251" s="28"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="A252" s="29"/>
-      <c r="B252" s="29"/>
-      <c r="C252" s="29"/>
+      <c r="A252" s="28"/>
+      <c r="B252" s="28"/>
+      <c r="C252" s="28"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="A253" s="29"/>
-      <c r="B253" s="29"/>
-      <c r="C253" s="29"/>
+      <c r="A253" s="28"/>
+      <c r="B253" s="28"/>
+      <c r="C253" s="28"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="A254" s="29"/>
-      <c r="B254" s="29"/>
-      <c r="C254" s="29"/>
+      <c r="A254" s="28"/>
+      <c r="B254" s="28"/>
+      <c r="C254" s="28"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="A255" s="29"/>
-      <c r="B255" s="29"/>
-      <c r="C255" s="29"/>
+      <c r="A255" s="28"/>
+      <c r="B255" s="28"/>
+      <c r="C255" s="28"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="A256" s="29"/>
-      <c r="B256" s="29"/>
-      <c r="C256" s="29"/>
+      <c r="A256" s="28"/>
+      <c r="B256" s="28"/>
+      <c r="C256" s="28"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="A257" s="29"/>
-      <c r="B257" s="29"/>
-      <c r="C257" s="29"/>
+      <c r="A257" s="28"/>
+      <c r="B257" s="28"/>
+      <c r="C257" s="28"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="A258" s="29"/>
-      <c r="B258" s="29"/>
-      <c r="C258" s="29"/>
+      <c r="A258" s="28"/>
+      <c r="B258" s="28"/>
+      <c r="C258" s="28"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="A259" s="29"/>
-      <c r="B259" s="29"/>
-      <c r="C259" s="29"/>
+      <c r="A259" s="28"/>
+      <c r="B259" s="28"/>
+      <c r="C259" s="28"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="A260" s="29"/>
-      <c r="B260" s="29"/>
-      <c r="C260" s="29"/>
+      <c r="A260" s="28"/>
+      <c r="B260" s="28"/>
+      <c r="C260" s="28"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="A261" s="29"/>
-      <c r="B261" s="29"/>
-      <c r="C261" s="29"/>
+      <c r="A261" s="28"/>
+      <c r="B261" s="28"/>
+      <c r="C261" s="28"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="A262" s="29"/>
-      <c r="B262" s="29"/>
-      <c r="C262" s="29"/>
+      <c r="A262" s="28"/>
+      <c r="B262" s="28"/>
+      <c r="C262" s="28"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="A263" s="29"/>
-      <c r="B263" s="29"/>
-      <c r="C263" s="29"/>
+      <c r="A263" s="28"/>
+      <c r="B263" s="28"/>
+      <c r="C263" s="28"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="A264" s="29"/>
-      <c r="B264" s="29"/>
-      <c r="C264" s="29"/>
+      <c r="A264" s="28"/>
+      <c r="B264" s="28"/>
+      <c r="C264" s="28"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="A265" s="29"/>
-      <c r="B265" s="29"/>
-      <c r="C265" s="29"/>
+      <c r="A265" s="28"/>
+      <c r="B265" s="28"/>
+      <c r="C265" s="28"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="A266" s="29"/>
-      <c r="B266" s="29"/>
-      <c r="C266" s="29"/>
+      <c r="A266" s="28"/>
+      <c r="B266" s="28"/>
+      <c r="C266" s="28"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="A267" s="29"/>
-      <c r="B267" s="29"/>
-      <c r="C267" s="29"/>
+      <c r="A267" s="28"/>
+      <c r="B267" s="28"/>
+      <c r="C267" s="28"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="29"/>
-      <c r="B268" s="29"/>
-      <c r="C268" s="29"/>
+      <c r="A268" s="28"/>
+      <c r="B268" s="28"/>
+      <c r="C268" s="28"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="A269" s="29"/>
-      <c r="B269" s="29"/>
-      <c r="C269" s="29"/>
+      <c r="A269" s="28"/>
+      <c r="B269" s="28"/>
+      <c r="C269" s="28"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="A270" s="29"/>
-      <c r="B270" s="29"/>
-      <c r="C270" s="29"/>
+      <c r="A270" s="28"/>
+      <c r="B270" s="28"/>
+      <c r="C270" s="28"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="A271" s="29"/>
-      <c r="B271" s="29"/>
-      <c r="C271" s="29"/>
+      <c r="A271" s="28"/>
+      <c r="B271" s="28"/>
+      <c r="C271" s="28"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="A272" s="29"/>
-      <c r="B272" s="29"/>
-      <c r="C272" s="29"/>
+      <c r="A272" s="28"/>
+      <c r="B272" s="28"/>
+      <c r="C272" s="28"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="A273" s="29"/>
-      <c r="B273" s="29"/>
-      <c r="C273" s="29"/>
+      <c r="A273" s="28"/>
+      <c r="B273" s="28"/>
+      <c r="C273" s="28"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="A274" s="29"/>
-      <c r="B274" s="29"/>
-      <c r="C274" s="29"/>
+      <c r="A274" s="28"/>
+      <c r="B274" s="28"/>
+      <c r="C274" s="28"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="A275" s="29"/>
-      <c r="B275" s="29"/>
-      <c r="C275" s="29"/>
+      <c r="A275" s="28"/>
+      <c r="B275" s="28"/>
+      <c r="C275" s="28"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="A276" s="29"/>
-      <c r="B276" s="29"/>
-      <c r="C276" s="29"/>
+      <c r="A276" s="28"/>
+      <c r="B276" s="28"/>
+      <c r="C276" s="28"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="A277" s="29"/>
-      <c r="B277" s="29"/>
-      <c r="C277" s="29"/>
+      <c r="A277" s="28"/>
+      <c r="B277" s="28"/>
+      <c r="C277" s="28"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="A278" s="29"/>
-      <c r="B278" s="29"/>
-      <c r="C278" s="29"/>
+      <c r="A278" s="28"/>
+      <c r="B278" s="28"/>
+      <c r="C278" s="28"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="A279" s="29"/>
-      <c r="B279" s="29"/>
-      <c r="C279" s="29"/>
+      <c r="A279" s="28"/>
+      <c r="B279" s="28"/>
+      <c r="C279" s="28"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="A280" s="29"/>
-      <c r="B280" s="29"/>
-      <c r="C280" s="29"/>
+      <c r="A280" s="28"/>
+      <c r="B280" s="28"/>
+      <c r="C280" s="28"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="A281" s="29"/>
-      <c r="B281" s="29"/>
-      <c r="C281" s="29"/>
+      <c r="A281" s="28"/>
+      <c r="B281" s="28"/>
+      <c r="C281" s="28"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="A282" s="29"/>
-      <c r="B282" s="29"/>
-      <c r="C282" s="29"/>
+      <c r="A282" s="28"/>
+      <c r="B282" s="28"/>
+      <c r="C282" s="28"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="A283" s="29"/>
-      <c r="B283" s="29"/>
-      <c r="C283" s="29"/>
+      <c r="A283" s="28"/>
+      <c r="B283" s="28"/>
+      <c r="C283" s="28"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="A284" s="29"/>
-      <c r="B284" s="29"/>
-      <c r="C284" s="29"/>
+      <c r="A284" s="28"/>
+      <c r="B284" s="28"/>
+      <c r="C284" s="28"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="A285" s="29"/>
-      <c r="B285" s="29"/>
-      <c r="C285" s="29"/>
+      <c r="A285" s="28"/>
+      <c r="B285" s="28"/>
+      <c r="C285" s="28"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="A286" s="29"/>
-      <c r="B286" s="29"/>
-      <c r="C286" s="29"/>
+      <c r="A286" s="28"/>
+      <c r="B286" s="28"/>
+      <c r="C286" s="28"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="A287" s="29"/>
-      <c r="B287" s="29"/>
-      <c r="C287" s="29"/>
+      <c r="A287" s="28"/>
+      <c r="B287" s="28"/>
+      <c r="C287" s="28"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="29"/>
-      <c r="B288" s="29"/>
-      <c r="C288" s="29"/>
+      <c r="A288" s="28"/>
+      <c r="B288" s="28"/>
+      <c r="C288" s="28"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="A289" s="29"/>
-      <c r="B289" s="29"/>
-      <c r="C289" s="29"/>
+      <c r="A289" s="28"/>
+      <c r="B289" s="28"/>
+      <c r="C289" s="28"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="A290" s="29"/>
-      <c r="B290" s="29"/>
-      <c r="C290" s="29"/>
+      <c r="A290" s="28"/>
+      <c r="B290" s="28"/>
+      <c r="C290" s="28"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="A291" s="29"/>
-      <c r="B291" s="29"/>
-      <c r="C291" s="29"/>
+      <c r="A291" s="28"/>
+      <c r="B291" s="28"/>
+      <c r="C291" s="28"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="A292" s="29"/>
-      <c r="B292" s="29"/>
-      <c r="C292" s="29"/>
+      <c r="A292" s="28"/>
+      <c r="B292" s="28"/>
+      <c r="C292" s="28"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="A293" s="29"/>
-      <c r="B293" s="29"/>
-      <c r="C293" s="29"/>
+      <c r="A293" s="28"/>
+      <c r="B293" s="28"/>
+      <c r="C293" s="28"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="A294" s="29"/>
-      <c r="B294" s="29"/>
-      <c r="C294" s="29"/>
+      <c r="A294" s="28"/>
+      <c r="B294" s="28"/>
+      <c r="C294" s="28"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="A295" s="29"/>
-      <c r="B295" s="29"/>
-      <c r="C295" s="29"/>
+      <c r="A295" s="28"/>
+      <c r="B295" s="28"/>
+      <c r="C295" s="28"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="A296" s="29"/>
-      <c r="B296" s="29"/>
-      <c r="C296" s="29"/>
+      <c r="A296" s="28"/>
+      <c r="B296" s="28"/>
+      <c r="C296" s="28"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="A297" s="29"/>
-      <c r="B297" s="29"/>
-      <c r="C297" s="29"/>
+      <c r="A297" s="28"/>
+      <c r="B297" s="28"/>
+      <c r="C297" s="28"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="A298" s="29"/>
-      <c r="B298" s="29"/>
-      <c r="C298" s="29"/>
+      <c r="A298" s="28"/>
+      <c r="B298" s="28"/>
+      <c r="C298" s="28"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="A299" s="29"/>
-      <c r="B299" s="29"/>
-      <c r="C299" s="29"/>
+      <c r="A299" s="28"/>
+      <c r="B299" s="28"/>
+      <c r="C299" s="28"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="A300" s="29"/>
-      <c r="B300" s="29"/>
-      <c r="C300" s="29"/>
+      <c r="A300" s="28"/>
+      <c r="B300" s="28"/>
+      <c r="C300" s="28"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="A301" s="29"/>
-      <c r="B301" s="29"/>
-      <c r="C301" s="29"/>
+      <c r="A301" s="28"/>
+      <c r="B301" s="28"/>
+      <c r="C301" s="28"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="A302" s="29"/>
-      <c r="B302" s="29"/>
-      <c r="C302" s="29"/>
+      <c r="A302" s="28"/>
+      <c r="B302" s="28"/>
+      <c r="C302" s="28"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="A303" s="29"/>
-      <c r="B303" s="29"/>
-      <c r="C303" s="29"/>
+      <c r="A303" s="28"/>
+      <c r="B303" s="28"/>
+      <c r="C303" s="28"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="A304" s="29"/>
-      <c r="B304" s="29"/>
-      <c r="C304" s="29"/>
+      <c r="A304" s="28"/>
+      <c r="B304" s="28"/>
+      <c r="C304" s="28"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="A305" s="29"/>
-      <c r="B305" s="29"/>
-      <c r="C305" s="29"/>
+      <c r="A305" s="28"/>
+      <c r="B305" s="28"/>
+      <c r="C305" s="28"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="A306" s="29"/>
-      <c r="B306" s="29"/>
-      <c r="C306" s="29"/>
+      <c r="A306" s="28"/>
+      <c r="B306" s="28"/>
+      <c r="C306" s="28"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="A307" s="29"/>
-      <c r="B307" s="29"/>
-      <c r="C307" s="29"/>
+      <c r="A307" s="28"/>
+      <c r="B307" s="28"/>
+      <c r="C307" s="28"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="29"/>
-      <c r="B308" s="29"/>
-      <c r="C308" s="29"/>
+      <c r="A308" s="28"/>
+      <c r="B308" s="28"/>
+      <c r="C308" s="28"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="A309" s="29"/>
-      <c r="B309" s="29"/>
-      <c r="C309" s="29"/>
+      <c r="A309" s="28"/>
+      <c r="B309" s="28"/>
+      <c r="C309" s="28"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="A310" s="29"/>
-      <c r="B310" s="29"/>
-      <c r="C310" s="29"/>
+      <c r="A310" s="28"/>
+      <c r="B310" s="28"/>
+      <c r="C310" s="28"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="A311" s="29"/>
-      <c r="B311" s="29"/>
-      <c r="C311" s="29"/>
+      <c r="A311" s="28"/>
+      <c r="B311" s="28"/>
+      <c r="C311" s="28"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="A312" s="29"/>
-      <c r="B312" s="29"/>
-      <c r="C312" s="29"/>
+      <c r="A312" s="28"/>
+      <c r="B312" s="28"/>
+      <c r="C312" s="28"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="A313" s="29"/>
-      <c r="B313" s="29"/>
-      <c r="C313" s="29"/>
+      <c r="A313" s="28"/>
+      <c r="B313" s="28"/>
+      <c r="C313" s="28"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="A314" s="29"/>
-      <c r="B314" s="29"/>
-      <c r="C314" s="29"/>
+      <c r="A314" s="28"/>
+      <c r="B314" s="28"/>
+      <c r="C314" s="28"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="A315" s="29"/>
-      <c r="B315" s="29"/>
-      <c r="C315" s="29"/>
+      <c r="A315" s="28"/>
+      <c r="B315" s="28"/>
+      <c r="C315" s="28"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="A316" s="29"/>
-      <c r="B316" s="29"/>
-      <c r="C316" s="29"/>
+      <c r="A316" s="28"/>
+      <c r="B316" s="28"/>
+      <c r="C316" s="28"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="A317" s="29"/>
-      <c r="B317" s="29"/>
-      <c r="C317" s="29"/>
+      <c r="A317" s="28"/>
+      <c r="B317" s="28"/>
+      <c r="C317" s="28"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="A318" s="29"/>
-      <c r="B318" s="29"/>
-      <c r="C318" s="29"/>
+      <c r="A318" s="28"/>
+      <c r="B318" s="28"/>
+      <c r="C318" s="28"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="A319" s="29"/>
-      <c r="B319" s="29"/>
-      <c r="C319" s="29"/>
+      <c r="A319" s="28"/>
+      <c r="B319" s="28"/>
+      <c r="C319" s="28"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="A320" s="29"/>
-      <c r="B320" s="29"/>
-      <c r="C320" s="29"/>
+      <c r="A320" s="28"/>
+      <c r="B320" s="28"/>
+      <c r="C320" s="28"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="A321" s="29"/>
-      <c r="B321" s="29"/>
-      <c r="C321" s="29"/>
+      <c r="A321" s="28"/>
+      <c r="B321" s="28"/>
+      <c r="C321" s="28"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="A322" s="29"/>
-      <c r="B322" s="29"/>
-      <c r="C322" s="29"/>
+      <c r="A322" s="28"/>
+      <c r="B322" s="28"/>
+      <c r="C322" s="28"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="A323" s="29"/>
-      <c r="B323" s="29"/>
-      <c r="C323" s="29"/>
+      <c r="A323" s="28"/>
+      <c r="B323" s="28"/>
+      <c r="C323" s="28"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="A324" s="29"/>
-      <c r="B324" s="29"/>
-      <c r="C324" s="29"/>
+      <c r="A324" s="28"/>
+      <c r="B324" s="28"/>
+      <c r="C324" s="28"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="A325" s="29"/>
-      <c r="B325" s="29"/>
-      <c r="C325" s="29"/>
+      <c r="A325" s="28"/>
+      <c r="B325" s="28"/>
+      <c r="C325" s="28"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="A326" s="29"/>
-      <c r="B326" s="29"/>
-      <c r="C326" s="29"/>
+      <c r="A326" s="28"/>
+      <c r="B326" s="28"/>
+      <c r="C326" s="28"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="A327" s="29"/>
-      <c r="B327" s="29"/>
-      <c r="C327" s="29"/>
+      <c r="A327" s="28"/>
+      <c r="B327" s="28"/>
+      <c r="C327" s="28"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="29"/>
-      <c r="B328" s="29"/>
-      <c r="C328" s="29"/>
+      <c r="A328" s="28"/>
+      <c r="B328" s="28"/>
+      <c r="C328" s="28"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="A329" s="29"/>
-      <c r="B329" s="29"/>
-      <c r="C329" s="29"/>
+      <c r="A329" s="28"/>
+      <c r="B329" s="28"/>
+      <c r="C329" s="28"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="A330" s="29"/>
-      <c r="B330" s="29"/>
-      <c r="C330" s="29"/>
+      <c r="A330" s="28"/>
+      <c r="B330" s="28"/>
+      <c r="C330" s="28"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="A331" s="29"/>
-      <c r="B331" s="29"/>
-      <c r="C331" s="29"/>
+      <c r="A331" s="28"/>
+      <c r="B331" s="28"/>
+      <c r="C331" s="28"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="A332" s="29"/>
-      <c r="B332" s="29"/>
-      <c r="C332" s="29"/>
+      <c r="A332" s="28"/>
+      <c r="B332" s="28"/>
+      <c r="C332" s="28"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="A333" s="29"/>
-      <c r="B333" s="29"/>
-      <c r="C333" s="29"/>
+      <c r="A333" s="28"/>
+      <c r="B333" s="28"/>
+      <c r="C333" s="28"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="A334" s="29"/>
-      <c r="B334" s="29"/>
-      <c r="C334" s="29"/>
+      <c r="A334" s="28"/>
+      <c r="B334" s="28"/>
+      <c r="C334" s="28"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="A335" s="29"/>
-      <c r="B335" s="29"/>
-      <c r="C335" s="29"/>
+      <c r="A335" s="28"/>
+      <c r="B335" s="28"/>
+      <c r="C335" s="28"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="A336" s="29"/>
-      <c r="B336" s="29"/>
-      <c r="C336" s="29"/>
+      <c r="A336" s="28"/>
+      <c r="B336" s="28"/>
+      <c r="C336" s="28"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="A337" s="29"/>
-      <c r="B337" s="29"/>
-      <c r="C337" s="29"/>
+      <c r="A337" s="28"/>
+      <c r="B337" s="28"/>
+      <c r="C337" s="28"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="A338" s="29"/>
-      <c r="B338" s="29"/>
-      <c r="C338" s="29"/>
+      <c r="A338" s="28"/>
+      <c r="B338" s="28"/>
+      <c r="C338" s="28"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="A339" s="29"/>
-      <c r="B339" s="29"/>
-      <c r="C339" s="29"/>
+      <c r="A339" s="28"/>
+      <c r="B339" s="28"/>
+      <c r="C339" s="28"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="A340" s="29"/>
-      <c r="B340" s="29"/>
-      <c r="C340" s="29"/>
+      <c r="A340" s="28"/>
+      <c r="B340" s="28"/>
+      <c r="C340" s="28"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="A341" s="29"/>
-      <c r="B341" s="29"/>
-      <c r="C341" s="29"/>
+      <c r="A341" s="28"/>
+      <c r="B341" s="28"/>
+      <c r="C341" s="28"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="A342" s="29"/>
-      <c r="B342" s="29"/>
-      <c r="C342" s="29"/>
+      <c r="A342" s="28"/>
+      <c r="B342" s="28"/>
+      <c r="C342" s="28"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="A343" s="29"/>
-      <c r="B343" s="29"/>
-      <c r="C343" s="29"/>
+      <c r="A343" s="28"/>
+      <c r="B343" s="28"/>
+      <c r="C343" s="28"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="A344" s="29"/>
-      <c r="B344" s="29"/>
-      <c r="C344" s="29"/>
+      <c r="A344" s="28"/>
+      <c r="B344" s="28"/>
+      <c r="C344" s="28"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="A345" s="29"/>
-      <c r="B345" s="29"/>
-      <c r="C345" s="29"/>
+      <c r="A345" s="28"/>
+      <c r="B345" s="28"/>
+      <c r="C345" s="28"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="A346" s="29"/>
-      <c r="B346" s="29"/>
-      <c r="C346" s="29"/>
+      <c r="A346" s="28"/>
+      <c r="B346" s="28"/>
+      <c r="C346" s="28"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="A347" s="29"/>
-      <c r="B347" s="29"/>
-      <c r="C347" s="29"/>
+      <c r="A347" s="28"/>
+      <c r="B347" s="28"/>
+      <c r="C347" s="28"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="29"/>
-      <c r="B348" s="29"/>
-      <c r="C348" s="29"/>
+      <c r="A348" s="28"/>
+      <c r="B348" s="28"/>
+      <c r="C348" s="28"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="A349" s="29"/>
-      <c r="B349" s="29"/>
-      <c r="C349" s="29"/>
+      <c r="A349" s="28"/>
+      <c r="B349" s="28"/>
+      <c r="C349" s="28"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="A350" s="29"/>
-      <c r="B350" s="29"/>
-      <c r="C350" s="29"/>
+      <c r="A350" s="28"/>
+      <c r="B350" s="28"/>
+      <c r="C350" s="28"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="A351" s="29"/>
-      <c r="B351" s="29"/>
-      <c r="C351" s="29"/>
+      <c r="A351" s="28"/>
+      <c r="B351" s="28"/>
+      <c r="C351" s="28"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="A352" s="29"/>
-      <c r="B352" s="29"/>
-      <c r="C352" s="29"/>
+      <c r="A352" s="28"/>
+      <c r="B352" s="28"/>
+      <c r="C352" s="28"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="A353" s="29"/>
-      <c r="B353" s="29"/>
-      <c r="C353" s="29"/>
+      <c r="A353" s="28"/>
+      <c r="B353" s="28"/>
+      <c r="C353" s="28"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="A354" s="29"/>
-      <c r="B354" s="29"/>
-      <c r="C354" s="29"/>
+      <c r="A354" s="28"/>
+      <c r="B354" s="28"/>
+      <c r="C354" s="28"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="A355" s="29"/>
-      <c r="B355" s="29"/>
-      <c r="C355" s="29"/>
+      <c r="A355" s="28"/>
+      <c r="B355" s="28"/>
+      <c r="C355" s="28"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="A356" s="29"/>
-      <c r="B356" s="29"/>
-      <c r="C356" s="29"/>
+      <c r="A356" s="28"/>
+      <c r="B356" s="28"/>
+      <c r="C356" s="28"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="A357" s="29"/>
-      <c r="B357" s="29"/>
-      <c r="C357" s="29"/>
+      <c r="A357" s="28"/>
+      <c r="B357" s="28"/>
+      <c r="C357" s="28"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="A358" s="29"/>
-      <c r="B358" s="29"/>
-      <c r="C358" s="29"/>
+      <c r="A358" s="28"/>
+      <c r="B358" s="28"/>
+      <c r="C358" s="28"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="A359" s="29"/>
-      <c r="B359" s="29"/>
-      <c r="C359" s="29"/>
+      <c r="A359" s="28"/>
+      <c r="B359" s="28"/>
+      <c r="C359" s="28"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="A360" s="29"/>
-      <c r="B360" s="29"/>
-      <c r="C360" s="29"/>
+      <c r="A360" s="28"/>
+      <c r="B360" s="28"/>
+      <c r="C360" s="28"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="A361" s="29"/>
-      <c r="B361" s="29"/>
-      <c r="C361" s="29"/>
+      <c r="A361" s="28"/>
+      <c r="B361" s="28"/>
+      <c r="C361" s="28"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="A362" s="29"/>
-      <c r="B362" s="29"/>
-      <c r="C362" s="29"/>
+      <c r="A362" s="28"/>
+      <c r="B362" s="28"/>
+      <c r="C362" s="28"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="A363" s="29"/>
-      <c r="B363" s="29"/>
-      <c r="C363" s="29"/>
+      <c r="A363" s="28"/>
+      <c r="B363" s="28"/>
+      <c r="C363" s="28"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="A364" s="29"/>
-      <c r="B364" s="29"/>
-      <c r="C364" s="29"/>
+      <c r="A364" s="28"/>
+      <c r="B364" s="28"/>
+      <c r="C364" s="28"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="A365" s="29"/>
-      <c r="B365" s="29"/>
-      <c r="C365" s="29"/>
+      <c r="A365" s="28"/>
+      <c r="B365" s="28"/>
+      <c r="C365" s="28"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="A366" s="29"/>
-      <c r="B366" s="29"/>
-      <c r="C366" s="29"/>
+      <c r="A366" s="28"/>
+      <c r="B366" s="28"/>
+      <c r="C366" s="28"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="A367" s="29"/>
-      <c r="B367" s="29"/>
-      <c r="C367" s="29"/>
+      <c r="A367" s="28"/>
+      <c r="B367" s="28"/>
+      <c r="C367" s="28"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="29"/>
-      <c r="B368" s="29"/>
-      <c r="C368" s="29"/>
+      <c r="A368" s="28"/>
+      <c r="B368" s="28"/>
+      <c r="C368" s="28"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="A369" s="29"/>
-      <c r="B369" s="29"/>
-      <c r="C369" s="29"/>
+      <c r="A369" s="28"/>
+      <c r="B369" s="28"/>
+      <c r="C369" s="28"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="A370" s="29"/>
-      <c r="B370" s="29"/>
-      <c r="C370" s="29"/>
+      <c r="A370" s="28"/>
+      <c r="B370" s="28"/>
+      <c r="C370" s="28"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="A371" s="29"/>
-      <c r="B371" s="29"/>
-      <c r="C371" s="29"/>
+      <c r="A371" s="28"/>
+      <c r="B371" s="28"/>
+      <c r="C371" s="28"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="A372" s="29"/>
-      <c r="B372" s="29"/>
-      <c r="C372" s="29"/>
+      <c r="A372" s="28"/>
+      <c r="B372" s="28"/>
+      <c r="C372" s="28"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="A373" s="29"/>
-      <c r="B373" s="29"/>
-      <c r="C373" s="29"/>
+      <c r="A373" s="28"/>
+      <c r="B373" s="28"/>
+      <c r="C373" s="28"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="A374" s="29"/>
-      <c r="B374" s="29"/>
-      <c r="C374" s="29"/>
+      <c r="A374" s="28"/>
+      <c r="B374" s="28"/>
+      <c r="C374" s="28"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="A375" s="29"/>
-      <c r="B375" s="29"/>
-      <c r="C375" s="29"/>
+      <c r="A375" s="28"/>
+      <c r="B375" s="28"/>
+      <c r="C375" s="28"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="A376" s="29"/>
-      <c r="B376" s="29"/>
-      <c r="C376" s="29"/>
+      <c r="A376" s="28"/>
+      <c r="B376" s="28"/>
+      <c r="C376" s="28"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="A377" s="29"/>
-      <c r="B377" s="29"/>
-      <c r="C377" s="29"/>
+      <c r="A377" s="28"/>
+      <c r="B377" s="28"/>
+      <c r="C377" s="28"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="A378" s="29"/>
-      <c r="B378" s="29"/>
-      <c r="C378" s="29"/>
+      <c r="A378" s="28"/>
+      <c r="B378" s="28"/>
+      <c r="C378" s="28"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="A379" s="29"/>
-      <c r="B379" s="29"/>
-      <c r="C379" s="29"/>
+      <c r="A379" s="28"/>
+      <c r="B379" s="28"/>
+      <c r="C379" s="28"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="A380" s="29"/>
-      <c r="B380" s="29"/>
-      <c r="C380" s="29"/>
+      <c r="A380" s="28"/>
+      <c r="B380" s="28"/>
+      <c r="C380" s="28"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="A381" s="29"/>
-      <c r="B381" s="29"/>
-      <c r="C381" s="29"/>
+      <c r="A381" s="28"/>
+      <c r="B381" s="28"/>
+      <c r="C381" s="28"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="A382" s="29"/>
-      <c r="B382" s="29"/>
-      <c r="C382" s="29"/>
+      <c r="A382" s="28"/>
+      <c r="B382" s="28"/>
+      <c r="C382" s="28"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="A383" s="29"/>
-      <c r="B383" s="29"/>
-      <c r="C383" s="29"/>
+      <c r="A383" s="28"/>
+      <c r="B383" s="28"/>
+      <c r="C383" s="28"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="A384" s="29"/>
-      <c r="B384" s="29"/>
-      <c r="C384" s="29"/>
+      <c r="A384" s="28"/>
+      <c r="B384" s="28"/>
+      <c r="C384" s="28"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="A385" s="29"/>
-      <c r="B385" s="29"/>
-      <c r="C385" s="29"/>
+      <c r="A385" s="28"/>
+      <c r="B385" s="28"/>
+      <c r="C385" s="28"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="A386" s="29"/>
-      <c r="B386" s="29"/>
-      <c r="C386" s="29"/>
+      <c r="A386" s="28"/>
+      <c r="B386" s="28"/>
+      <c r="C386" s="28"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="A387" s="29"/>
-      <c r="B387" s="29"/>
-      <c r="C387" s="29"/>
+      <c r="A387" s="28"/>
+      <c r="B387" s="28"/>
+      <c r="C387" s="28"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="A388" s="29"/>
-      <c r="B388" s="29"/>
-      <c r="C388" s="29"/>
+      <c r="A388" s="28"/>
+      <c r="B388" s="28"/>
+      <c r="C388" s="28"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="A389" s="29"/>
-      <c r="B389" s="29"/>
-      <c r="C389" s="29"/>
+      <c r="A389" s="28"/>
+      <c r="B389" s="28"/>
+      <c r="C389" s="28"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="A390" s="29"/>
-      <c r="B390" s="29"/>
-      <c r="C390" s="29"/>
+      <c r="A390" s="28"/>
+      <c r="B390" s="28"/>
+      <c r="C390" s="28"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="A391" s="29"/>
-      <c r="B391" s="29"/>
-      <c r="C391" s="29"/>
+      <c r="A391" s="28"/>
+      <c r="B391" s="28"/>
+      <c r="C391" s="28"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="A392" s="29"/>
-      <c r="B392" s="29"/>
-      <c r="C392" s="29"/>
+      <c r="A392" s="28"/>
+      <c r="B392" s="28"/>
+      <c r="C392" s="28"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="A393" s="29"/>
-      <c r="B393" s="29"/>
-      <c r="C393" s="29"/>
+      <c r="A393" s="28"/>
+      <c r="B393" s="28"/>
+      <c r="C393" s="28"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="A394" s="29"/>
-      <c r="B394" s="29"/>
-      <c r="C394" s="29"/>
+      <c r="A394" s="28"/>
+      <c r="B394" s="28"/>
+      <c r="C394" s="28"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="A395" s="29"/>
-      <c r="B395" s="29"/>
-      <c r="C395" s="29"/>
+      <c r="A395" s="28"/>
+      <c r="B395" s="28"/>
+      <c r="C395" s="28"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="A396" s="29"/>
-      <c r="B396" s="29"/>
-      <c r="C396" s="29"/>
+      <c r="A396" s="28"/>
+      <c r="B396" s="28"/>
+      <c r="C396" s="28"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="A397" s="29"/>
-      <c r="B397" s="29"/>
-      <c r="C397" s="29"/>
+      <c r="A397" s="28"/>
+      <c r="B397" s="28"/>
+      <c r="C397" s="28"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="A398" s="29"/>
-      <c r="B398" s="29"/>
-      <c r="C398" s="29"/>
+      <c r="A398" s="28"/>
+      <c r="B398" s="28"/>
+      <c r="C398" s="28"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="A399" s="29"/>
-      <c r="B399" s="29"/>
-      <c r="C399" s="29"/>
+      <c r="A399" s="28"/>
+      <c r="B399" s="28"/>
+      <c r="C399" s="28"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="A400" s="29"/>
-      <c r="B400" s="29"/>
-      <c r="C400" s="29"/>
+      <c r="A400" s="28"/>
+      <c r="B400" s="28"/>
+      <c r="C400" s="28"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="A401" s="29"/>
-      <c r="B401" s="29"/>
-      <c r="C401" s="29"/>
+      <c r="A401" s="28"/>
+      <c r="B401" s="28"/>
+      <c r="C401" s="28"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="A402" s="29"/>
-      <c r="B402" s="29"/>
-      <c r="C402" s="29"/>
+      <c r="A402" s="28"/>
+      <c r="B402" s="28"/>
+      <c r="C402" s="28"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="A403" s="29"/>
-      <c r="B403" s="29"/>
-      <c r="C403" s="29"/>
+      <c r="A403" s="28"/>
+      <c r="B403" s="28"/>
+      <c r="C403" s="28"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="A404" s="29"/>
-      <c r="B404" s="29"/>
-      <c r="C404" s="29"/>
+      <c r="A404" s="28"/>
+      <c r="B404" s="28"/>
+      <c r="C404" s="28"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="A405" s="29"/>
-      <c r="B405" s="29"/>
-      <c r="C405" s="29"/>
+      <c r="A405" s="28"/>
+      <c r="B405" s="28"/>
+      <c r="C405" s="28"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="A406" s="29"/>
-      <c r="B406" s="29"/>
-      <c r="C406" s="29"/>
+      <c r="A406" s="28"/>
+      <c r="B406" s="28"/>
+      <c r="C406" s="28"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="A407" s="29"/>
-      <c r="B407" s="29"/>
-      <c r="C407" s="29"/>
+      <c r="A407" s="28"/>
+      <c r="B407" s="28"/>
+      <c r="C407" s="28"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="A408" s="29"/>
-      <c r="B408" s="29"/>
-      <c r="C408" s="29"/>
+      <c r="A408" s="28"/>
+      <c r="B408" s="28"/>
+      <c r="C408" s="28"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="A409" s="29"/>
-      <c r="B409" s="29"/>
-      <c r="C409" s="29"/>
+      <c r="A409" s="28"/>
+      <c r="B409" s="28"/>
+      <c r="C409" s="28"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="A410" s="29"/>
-      <c r="B410" s="29"/>
-      <c r="C410" s="29"/>
+      <c r="A410" s="28"/>
+      <c r="B410" s="28"/>
+      <c r="C410" s="28"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="A411" s="29"/>
-      <c r="B411" s="29"/>
-      <c r="C411" s="29"/>
+      <c r="A411" s="28"/>
+      <c r="B411" s="28"/>
+      <c r="C411" s="28"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="A412" s="29"/>
-      <c r="B412" s="29"/>
-      <c r="C412" s="29"/>
+      <c r="A412" s="28"/>
+      <c r="B412" s="28"/>
+      <c r="C412" s="28"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="A413" s="29"/>
-      <c r="B413" s="29"/>
-      <c r="C413" s="29"/>
+      <c r="A413" s="28"/>
+      <c r="B413" s="28"/>
+      <c r="C413" s="28"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="A414" s="29"/>
-      <c r="B414" s="29"/>
-      <c r="C414" s="29"/>
+      <c r="A414" s="28"/>
+      <c r="B414" s="28"/>
+      <c r="C414" s="28"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="A415" s="29"/>
-      <c r="B415" s="29"/>
-      <c r="C415" s="29"/>
+      <c r="A415" s="28"/>
+      <c r="B415" s="28"/>
+      <c r="C415" s="28"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="A416" s="29"/>
-      <c r="B416" s="29"/>
-      <c r="C416" s="29"/>
+      <c r="A416" s="28"/>
+      <c r="B416" s="28"/>
+      <c r="C416" s="28"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="A417" s="29"/>
-      <c r="B417" s="29"/>
-      <c r="C417" s="29"/>
+      <c r="A417" s="28"/>
+      <c r="B417" s="28"/>
+      <c r="C417" s="28"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="A418" s="29"/>
-      <c r="B418" s="29"/>
-      <c r="C418" s="29"/>
+      <c r="A418" s="28"/>
+      <c r="B418" s="28"/>
+      <c r="C418" s="28"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="A419" s="29"/>
-      <c r="B419" s="29"/>
-      <c r="C419" s="29"/>
+      <c r="A419" s="28"/>
+      <c r="B419" s="28"/>
+      <c r="C419" s="28"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="A420" s="29"/>
-      <c r="B420" s="29"/>
-      <c r="C420" s="29"/>
+      <c r="A420" s="28"/>
+      <c r="B420" s="28"/>
+      <c r="C420" s="28"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="A421" s="29"/>
-      <c r="B421" s="29"/>
-      <c r="C421" s="29"/>
+      <c r="A421" s="28"/>
+      <c r="B421" s="28"/>
+      <c r="C421" s="28"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="A422" s="29"/>
-      <c r="B422" s="29"/>
-      <c r="C422" s="29"/>
+      <c r="A422" s="28"/>
+      <c r="B422" s="28"/>
+      <c r="C422" s="28"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="A423" s="29"/>
-      <c r="B423" s="29"/>
-      <c r="C423" s="29"/>
+      <c r="A423" s="28"/>
+      <c r="B423" s="28"/>
+      <c r="C423" s="28"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="A424" s="29"/>
-      <c r="B424" s="29"/>
-      <c r="C424" s="29"/>
+      <c r="A424" s="28"/>
+      <c r="B424" s="28"/>
+      <c r="C424" s="28"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="A425" s="29"/>
-      <c r="B425" s="29"/>
-      <c r="C425" s="29"/>
+      <c r="A425" s="28"/>
+      <c r="B425" s="28"/>
+      <c r="C425" s="28"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="A426" s="29"/>
-      <c r="B426" s="29"/>
-      <c r="C426" s="29"/>
+      <c r="A426" s="28"/>
+      <c r="B426" s="28"/>
+      <c r="C426" s="28"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="A427" s="29"/>
-      <c r="B427" s="29"/>
-      <c r="C427" s="29"/>
+      <c r="A427" s="28"/>
+      <c r="B427" s="28"/>
+      <c r="C427" s="28"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="A428" s="29"/>
-      <c r="B428" s="29"/>
-      <c r="C428" s="29"/>
+      <c r="A428" s="28"/>
+      <c r="B428" s="28"/>
+      <c r="C428" s="28"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="A429" s="29"/>
-      <c r="B429" s="29"/>
-      <c r="C429" s="29"/>
+      <c r="A429" s="28"/>
+      <c r="B429" s="28"/>
+      <c r="C429" s="28"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="A430" s="29"/>
-      <c r="B430" s="29"/>
-      <c r="C430" s="29"/>
+      <c r="A430" s="28"/>
+      <c r="B430" s="28"/>
+      <c r="C430" s="28"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="A431" s="29"/>
-      <c r="B431" s="29"/>
-      <c r="C431" s="29"/>
+      <c r="A431" s="28"/>
+      <c r="B431" s="28"/>
+      <c r="C431" s="28"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="A432" s="29"/>
-      <c r="B432" s="29"/>
-      <c r="C432" s="29"/>
+      <c r="A432" s="28"/>
+      <c r="B432" s="28"/>
+      <c r="C432" s="28"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="A433" s="29"/>
-      <c r="B433" s="29"/>
-      <c r="C433" s="29"/>
+      <c r="A433" s="28"/>
+      <c r="B433" s="28"/>
+      <c r="C433" s="28"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="A434" s="29"/>
-      <c r="B434" s="29"/>
-      <c r="C434" s="29"/>
+      <c r="A434" s="28"/>
+      <c r="B434" s="28"/>
+      <c r="C434" s="28"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="29"/>
-      <c r="B435" s="29"/>
-      <c r="C435" s="29"/>
+      <c r="A435" s="28"/>
+      <c r="B435" s="28"/>
+      <c r="C435" s="28"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="29"/>
-      <c r="B436" s="29"/>
-      <c r="C436" s="29"/>
+      <c r="A436" s="28"/>
+      <c r="B436" s="28"/>
+      <c r="C436" s="28"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="29"/>
-      <c r="B437" s="29"/>
-      <c r="C437" s="29"/>
+      <c r="A437" s="28"/>
+      <c r="B437" s="28"/>
+      <c r="C437" s="28"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="29"/>
-      <c r="B438" s="29"/>
-      <c r="C438" s="29"/>
+      <c r="A438" s="28"/>
+      <c r="B438" s="28"/>
+      <c r="C438" s="28"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="29"/>
-      <c r="B439" s="29"/>
-      <c r="C439" s="29"/>
+      <c r="A439" s="28"/>
+      <c r="B439" s="28"/>
+      <c r="C439" s="28"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="29"/>
-      <c r="B440" s="29"/>
-      <c r="C440" s="29"/>
+      <c r="A440" s="28"/>
+      <c r="B440" s="28"/>
+      <c r="C440" s="28"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="A441" s="29"/>
-      <c r="B441" s="29"/>
-      <c r="C441" s="29"/>
+      <c r="A441" s="28"/>
+      <c r="B441" s="28"/>
+      <c r="C441" s="28"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="A442" s="29"/>
-      <c r="B442" s="29"/>
-      <c r="C442" s="29"/>
+      <c r="A442" s="28"/>
+      <c r="B442" s="28"/>
+      <c r="C442" s="28"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="29"/>
-      <c r="B443" s="29"/>
-      <c r="C443" s="29"/>
+      <c r="A443" s="28"/>
+      <c r="B443" s="28"/>
+      <c r="C443" s="28"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="29"/>
-      <c r="B444" s="29"/>
-      <c r="C444" s="29"/>
+      <c r="A444" s="28"/>
+      <c r="B444" s="28"/>
+      <c r="C444" s="28"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="29"/>
-      <c r="B445" s="29"/>
-      <c r="C445" s="29"/>
+      <c r="A445" s="28"/>
+      <c r="B445" s="28"/>
+      <c r="C445" s="28"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="29"/>
-      <c r="B446" s="29"/>
-      <c r="C446" s="29"/>
+      <c r="A446" s="28"/>
+      <c r="B446" s="28"/>
+      <c r="C446" s="28"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="A447" s="29"/>
-      <c r="B447" s="29"/>
-      <c r="C447" s="29"/>
+      <c r="A447" s="28"/>
+      <c r="B447" s="28"/>
+      <c r="C447" s="28"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="A448" s="29"/>
-      <c r="B448" s="29"/>
-      <c r="C448" s="29"/>
+      <c r="A448" s="28"/>
+      <c r="B448" s="28"/>
+      <c r="C448" s="28"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="A449" s="29"/>
-      <c r="B449" s="29"/>
-      <c r="C449" s="29"/>
+      <c r="A449" s="28"/>
+      <c r="B449" s="28"/>
+      <c r="C449" s="28"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="A450" s="29"/>
-      <c r="B450" s="29"/>
-      <c r="C450" s="29"/>
+      <c r="A450" s="28"/>
+      <c r="B450" s="28"/>
+      <c r="C450" s="28"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="A451" s="29"/>
-      <c r="B451" s="29"/>
-      <c r="C451" s="29"/>
+      <c r="A451" s="28"/>
+      <c r="B451" s="28"/>
+      <c r="C451" s="28"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="A452" s="29"/>
-      <c r="B452" s="29"/>
-      <c r="C452" s="29"/>
+      <c r="A452" s="28"/>
+      <c r="B452" s="28"/>
+      <c r="C452" s="28"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="29"/>
-      <c r="B453" s="29"/>
-      <c r="C453" s="29"/>
+      <c r="A453" s="28"/>
+      <c r="B453" s="28"/>
+      <c r="C453" s="28"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="29"/>
-      <c r="B454" s="29"/>
-      <c r="C454" s="29"/>
+      <c r="A454" s="28"/>
+      <c r="B454" s="28"/>
+      <c r="C454" s="28"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="29"/>
-      <c r="B455" s="29"/>
-      <c r="C455" s="29"/>
+      <c r="A455" s="28"/>
+      <c r="B455" s="28"/>
+      <c r="C455" s="28"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="29"/>
-      <c r="B456" s="29"/>
-      <c r="C456" s="29"/>
+      <c r="A456" s="28"/>
+      <c r="B456" s="28"/>
+      <c r="C456" s="28"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="A457" s="29"/>
-      <c r="B457" s="29"/>
-      <c r="C457" s="29"/>
+      <c r="A457" s="28"/>
+      <c r="B457" s="28"/>
+      <c r="C457" s="28"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="A458" s="29"/>
-      <c r="B458" s="29"/>
-      <c r="C458" s="29"/>
+      <c r="A458" s="28"/>
+      <c r="B458" s="28"/>
+      <c r="C458" s="28"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="A459" s="29"/>
-      <c r="B459" s="29"/>
-      <c r="C459" s="29"/>
+      <c r="A459" s="28"/>
+      <c r="B459" s="28"/>
+      <c r="C459" s="28"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="A460" s="29"/>
-      <c r="B460" s="29"/>
-      <c r="C460" s="29"/>
+      <c r="A460" s="28"/>
+      <c r="B460" s="28"/>
+      <c r="C460" s="28"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="A461" s="29"/>
-      <c r="B461" s="29"/>
-      <c r="C461" s="29"/>
+      <c r="A461" s="28"/>
+      <c r="B461" s="28"/>
+      <c r="C461" s="28"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="A462" s="29"/>
-      <c r="B462" s="29"/>
-      <c r="C462" s="29"/>
+      <c r="A462" s="28"/>
+      <c r="B462" s="28"/>
+      <c r="C462" s="28"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="A463" s="29"/>
-      <c r="B463" s="29"/>
-      <c r="C463" s="29"/>
+      <c r="A463" s="28"/>
+      <c r="B463" s="28"/>
+      <c r="C463" s="28"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="A464" s="29"/>
-      <c r="B464" s="29"/>
-      <c r="C464" s="29"/>
+      <c r="A464" s="28"/>
+      <c r="B464" s="28"/>
+      <c r="C464" s="28"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="A465" s="29"/>
-      <c r="B465" s="29"/>
-      <c r="C465" s="29"/>
+      <c r="A465" s="28"/>
+      <c r="B465" s="28"/>
+      <c r="C465" s="28"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="A466" s="29"/>
-      <c r="B466" s="29"/>
-      <c r="C466" s="29"/>
+      <c r="A466" s="28"/>
+      <c r="B466" s="28"/>
+      <c r="C466" s="28"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="A467" s="29"/>
-      <c r="B467" s="29"/>
-      <c r="C467" s="29"/>
+      <c r="A467" s="28"/>
+      <c r="B467" s="28"/>
+      <c r="C467" s="28"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="A468" s="29"/>
-      <c r="B468" s="29"/>
-      <c r="C468" s="29"/>
+      <c r="A468" s="28"/>
+      <c r="B468" s="28"/>
+      <c r="C468" s="28"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="A469" s="29"/>
-      <c r="B469" s="29"/>
-      <c r="C469" s="29"/>
+      <c r="A469" s="28"/>
+      <c r="B469" s="28"/>
+      <c r="C469" s="28"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="A470" s="29"/>
-      <c r="B470" s="29"/>
-      <c r="C470" s="29"/>
+      <c r="A470" s="28"/>
+      <c r="B470" s="28"/>
+      <c r="C470" s="28"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="A471" s="29"/>
-      <c r="B471" s="29"/>
-      <c r="C471" s="29"/>
+      <c r="A471" s="28"/>
+      <c r="B471" s="28"/>
+      <c r="C471" s="28"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="A472" s="29"/>
-      <c r="B472" s="29"/>
-      <c r="C472" s="29"/>
+      <c r="A472" s="28"/>
+      <c r="B472" s="28"/>
+      <c r="C472" s="28"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="A473" s="29"/>
-      <c r="B473" s="29"/>
-      <c r="C473" s="29"/>
+      <c r="A473" s="28"/>
+      <c r="B473" s="28"/>
+      <c r="C473" s="28"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="A474" s="29"/>
-      <c r="B474" s="29"/>
-      <c r="C474" s="29"/>
+      <c r="A474" s="28"/>
+      <c r="B474" s="28"/>
+      <c r="C474" s="28"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="A475" s="29"/>
-      <c r="B475" s="29"/>
-      <c r="C475" s="29"/>
+      <c r="A475" s="28"/>
+      <c r="B475" s="28"/>
+      <c r="C475" s="28"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="A476" s="29"/>
-      <c r="B476" s="29"/>
-      <c r="C476" s="29"/>
+      <c r="A476" s="28"/>
+      <c r="B476" s="28"/>
+      <c r="C476" s="28"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="A477" s="29"/>
-      <c r="B477" s="29"/>
-      <c r="C477" s="29"/>
+      <c r="A477" s="28"/>
+      <c r="B477" s="28"/>
+      <c r="C477" s="28"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="A478" s="29"/>
-      <c r="B478" s="29"/>
-      <c r="C478" s="29"/>
+      <c r="A478" s="28"/>
+      <c r="B478" s="28"/>
+      <c r="C478" s="28"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="A479" s="29"/>
-      <c r="B479" s="29"/>
-      <c r="C479" s="29"/>
+      <c r="A479" s="28"/>
+      <c r="B479" s="28"/>
+      <c r="C479" s="28"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="A480" s="29"/>
-      <c r="B480" s="29"/>
-      <c r="C480" s="29"/>
+      <c r="A480" s="28"/>
+      <c r="B480" s="28"/>
+      <c r="C480" s="28"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="A481" s="29"/>
-      <c r="B481" s="29"/>
-      <c r="C481" s="29"/>
+      <c r="A481" s="28"/>
+      <c r="B481" s="28"/>
+      <c r="C481" s="28"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="A482" s="29"/>
-      <c r="B482" s="29"/>
-      <c r="C482" s="29"/>
+      <c r="A482" s="28"/>
+      <c r="B482" s="28"/>
+      <c r="C482" s="28"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="A483" s="29"/>
-      <c r="B483" s="29"/>
-      <c r="C483" s="29"/>
+      <c r="A483" s="28"/>
+      <c r="B483" s="28"/>
+      <c r="C483" s="28"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="A484" s="29"/>
-      <c r="B484" s="29"/>
-      <c r="C484" s="29"/>
+      <c r="A484" s="28"/>
+      <c r="B484" s="28"/>
+      <c r="C484" s="28"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="A485" s="29"/>
-      <c r="B485" s="29"/>
-      <c r="C485" s="29"/>
+      <c r="A485" s="28"/>
+      <c r="B485" s="28"/>
+      <c r="C485" s="28"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="A486" s="29"/>
-      <c r="B486" s="29"/>
-      <c r="C486" s="29"/>
+      <c r="A486" s="28"/>
+      <c r="B486" s="28"/>
+      <c r="C486" s="28"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="A487" s="29"/>
-      <c r="B487" s="29"/>
-      <c r="C487" s="29"/>
+      <c r="A487" s="28"/>
+      <c r="B487" s="28"/>
+      <c r="C487" s="28"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="A488" s="29"/>
-      <c r="B488" s="29"/>
-      <c r="C488" s="29"/>
+      <c r="A488" s="28"/>
+      <c r="B488" s="28"/>
+      <c r="C488" s="28"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="A489" s="29"/>
-      <c r="B489" s="29"/>
-      <c r="C489" s="29"/>
+      <c r="A489" s="28"/>
+      <c r="B489" s="28"/>
+      <c r="C489" s="28"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="A490" s="29"/>
-      <c r="B490" s="29"/>
-      <c r="C490" s="29"/>
+      <c r="A490" s="28"/>
+      <c r="B490" s="28"/>
+      <c r="C490" s="28"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="A491" s="29"/>
-      <c r="B491" s="29"/>
-      <c r="C491" s="29"/>
+      <c r="A491" s="28"/>
+      <c r="B491" s="28"/>
+      <c r="C491" s="28"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="A492" s="29"/>
-      <c r="B492" s="29"/>
-      <c r="C492" s="29"/>
+      <c r="A492" s="28"/>
+      <c r="B492" s="28"/>
+      <c r="C492" s="28"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="A493" s="29"/>
-      <c r="B493" s="29"/>
-      <c r="C493" s="29"/>
+      <c r="A493" s="28"/>
+      <c r="B493" s="28"/>
+      <c r="C493" s="28"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="A494" s="29"/>
-      <c r="B494" s="29"/>
-      <c r="C494" s="29"/>
+      <c r="A494" s="28"/>
+      <c r="B494" s="28"/>
+      <c r="C494" s="28"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="A495" s="29"/>
-      <c r="B495" s="29"/>
-      <c r="C495" s="29"/>
+      <c r="A495" s="28"/>
+      <c r="B495" s="28"/>
+      <c r="C495" s="28"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="A496" s="29"/>
-      <c r="B496" s="29"/>
-      <c r="C496" s="29"/>
+      <c r="A496" s="28"/>
+      <c r="B496" s="28"/>
+      <c r="C496" s="28"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="A497" s="29"/>
-      <c r="B497" s="29"/>
-      <c r="C497" s="29"/>
+      <c r="A497" s="28"/>
+      <c r="B497" s="28"/>
+      <c r="C497" s="28"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="A498" s="29"/>
-      <c r="B498" s="29"/>
-      <c r="C498" s="29"/>
+      <c r="A498" s="28"/>
+      <c r="B498" s="28"/>
+      <c r="C498" s="28"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="A499" s="29"/>
-      <c r="B499" s="29"/>
-      <c r="C499" s="29"/>
+      <c r="A499" s="28"/>
+      <c r="B499" s="28"/>
+      <c r="C499" s="28"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="A500" s="29"/>
-      <c r="B500" s="29"/>
-      <c r="C500" s="29"/>
+      <c r="A500" s="28"/>
+      <c r="B500" s="28"/>
+      <c r="C500" s="28"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="A501" s="29"/>
-      <c r="B501" s="29"/>
-      <c r="C501" s="29"/>
+      <c r="A501" s="28"/>
+      <c r="B501" s="28"/>
+      <c r="C501" s="28"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="A502" s="29"/>
-      <c r="B502" s="29"/>
-      <c r="C502" s="29"/>
+      <c r="A502" s="28"/>
+      <c r="B502" s="28"/>
+      <c r="C502" s="28"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="A503" s="29"/>
-      <c r="B503" s="29"/>
-      <c r="C503" s="29"/>
+      <c r="A503" s="28"/>
+      <c r="B503" s="28"/>
+      <c r="C503" s="28"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="A504" s="29"/>
-      <c r="B504" s="29"/>
-      <c r="C504" s="29"/>
+      <c r="A504" s="28"/>
+      <c r="B504" s="28"/>
+      <c r="C504" s="28"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="A505" s="29"/>
-      <c r="B505" s="29"/>
-      <c r="C505" s="29"/>
+      <c r="A505" s="28"/>
+      <c r="B505" s="28"/>
+      <c r="C505" s="28"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="A506" s="29"/>
-      <c r="B506" s="29"/>
-      <c r="C506" s="29"/>
+      <c r="A506" s="28"/>
+      <c r="B506" s="28"/>
+      <c r="C506" s="28"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="A507" s="29"/>
-      <c r="B507" s="29"/>
-      <c r="C507" s="29"/>
+      <c r="A507" s="28"/>
+      <c r="B507" s="28"/>
+      <c r="C507" s="28"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="A508" s="29"/>
-      <c r="B508" s="29"/>
-      <c r="C508" s="29"/>
+      <c r="A508" s="28"/>
+      <c r="B508" s="28"/>
+      <c r="C508" s="28"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="A509" s="29"/>
-      <c r="B509" s="29"/>
-      <c r="C509" s="29"/>
+      <c r="A509" s="28"/>
+      <c r="B509" s="28"/>
+      <c r="C509" s="28"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="A510" s="29"/>
-      <c r="B510" s="29"/>
-      <c r="C510" s="29"/>
+      <c r="A510" s="28"/>
+      <c r="B510" s="28"/>
+      <c r="C510" s="28"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="A511" s="29"/>
-      <c r="B511" s="29"/>
-      <c r="C511" s="29"/>
+      <c r="A511" s="28"/>
+      <c r="B511" s="28"/>
+      <c r="C511" s="28"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="A512" s="29"/>
-      <c r="B512" s="29"/>
-      <c r="C512" s="29"/>
+      <c r="A512" s="28"/>
+      <c r="B512" s="28"/>
+      <c r="C512" s="28"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="A513" s="29"/>
-      <c r="B513" s="29"/>
-      <c r="C513" s="29"/>
+      <c r="A513" s="28"/>
+      <c r="B513" s="28"/>
+      <c r="C513" s="28"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="A514" s="29"/>
-      <c r="B514" s="29"/>
-      <c r="C514" s="29"/>
+      <c r="A514" s="28"/>
+      <c r="B514" s="28"/>
+      <c r="C514" s="28"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="A515" s="29"/>
-      <c r="B515" s="29"/>
-      <c r="C515" s="29"/>
+      <c r="A515" s="28"/>
+      <c r="B515" s="28"/>
+      <c r="C515" s="28"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="A516" s="29"/>
-      <c r="B516" s="29"/>
-      <c r="C516" s="29"/>
+      <c r="A516" s="28"/>
+      <c r="B516" s="28"/>
+      <c r="C516" s="28"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="A517" s="29"/>
-      <c r="B517" s="29"/>
-      <c r="C517" s="29"/>
+      <c r="A517" s="28"/>
+      <c r="B517" s="28"/>
+      <c r="C517" s="28"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="A518" s="29"/>
-      <c r="B518" s="29"/>
-      <c r="C518" s="29"/>
+      <c r="A518" s="28"/>
+      <c r="B518" s="28"/>
+      <c r="C518" s="28"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="A519" s="29"/>
-      <c r="B519" s="29"/>
-      <c r="C519" s="29"/>
+      <c r="A519" s="28"/>
+      <c r="B519" s="28"/>
+      <c r="C519" s="28"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="A520" s="29"/>
-      <c r="B520" s="29"/>
-      <c r="C520" s="29"/>
+      <c r="A520" s="28"/>
+      <c r="B520" s="28"/>
+      <c r="C520" s="28"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="A521" s="29"/>
-      <c r="B521" s="29"/>
-      <c r="C521" s="29"/>
+      <c r="A521" s="28"/>
+      <c r="B521" s="28"/>
+      <c r="C521" s="28"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="A522" s="29"/>
-      <c r="B522" s="29"/>
-      <c r="C522" s="29"/>
+      <c r="A522" s="28"/>
+      <c r="B522" s="28"/>
+      <c r="C522" s="28"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="A523" s="29"/>
-      <c r="B523" s="29"/>
-      <c r="C523" s="29"/>
+      <c r="A523" s="28"/>
+      <c r="B523" s="28"/>
+      <c r="C523" s="28"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="A524" s="29"/>
-      <c r="B524" s="29"/>
-      <c r="C524" s="29"/>
+      <c r="A524" s="28"/>
+      <c r="B524" s="28"/>
+      <c r="C524" s="28"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="A525" s="29"/>
-      <c r="B525" s="29"/>
-      <c r="C525" s="29"/>
+      <c r="A525" s="28"/>
+      <c r="B525" s="28"/>
+      <c r="C525" s="28"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="A526" s="29"/>
-      <c r="B526" s="29"/>
-      <c r="C526" s="29"/>
+      <c r="A526" s="28"/>
+      <c r="B526" s="28"/>
+      <c r="C526" s="28"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="A527" s="29"/>
-      <c r="B527" s="29"/>
-      <c r="C527" s="29"/>
+      <c r="A527" s="28"/>
+      <c r="B527" s="28"/>
+      <c r="C527" s="28"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="A528" s="29"/>
-      <c r="B528" s="29"/>
-      <c r="C528" s="29"/>
+      <c r="A528" s="28"/>
+      <c r="B528" s="28"/>
+      <c r="C528" s="28"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="A529" s="29"/>
-      <c r="B529" s="29"/>
-      <c r="C529" s="29"/>
+      <c r="A529" s="28"/>
+      <c r="B529" s="28"/>
+      <c r="C529" s="28"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="A530" s="29"/>
-      <c r="B530" s="29"/>
-      <c r="C530" s="29"/>
+      <c r="A530" s="28"/>
+      <c r="B530" s="28"/>
+      <c r="C530" s="28"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="A531" s="29"/>
-      <c r="B531" s="29"/>
-      <c r="C531" s="29"/>
+      <c r="A531" s="28"/>
+      <c r="B531" s="28"/>
+      <c r="C531" s="28"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="A532" s="29"/>
-      <c r="B532" s="29"/>
-      <c r="C532" s="29"/>
+      <c r="A532" s="28"/>
+      <c r="B532" s="28"/>
+      <c r="C532" s="28"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="A533" s="29"/>
-      <c r="B533" s="29"/>
-      <c r="C533" s="29"/>
+      <c r="A533" s="28"/>
+      <c r="B533" s="28"/>
+      <c r="C533" s="28"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="A534" s="29"/>
-      <c r="B534" s="29"/>
-      <c r="C534" s="29"/>
+      <c r="A534" s="28"/>
+      <c r="B534" s="28"/>
+      <c r="C534" s="28"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="A535" s="29"/>
-      <c r="B535" s="29"/>
-      <c r="C535" s="29"/>
+      <c r="A535" s="28"/>
+      <c r="B535" s="28"/>
+      <c r="C535" s="28"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="A536" s="29"/>
-      <c r="B536" s="29"/>
-      <c r="C536" s="29"/>
+      <c r="A536" s="28"/>
+      <c r="B536" s="28"/>
+      <c r="C536" s="28"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="A537" s="29"/>
-      <c r="B537" s="29"/>
-      <c r="C537" s="29"/>
+      <c r="A537" s="28"/>
+      <c r="B537" s="28"/>
+      <c r="C537" s="28"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="A538" s="29"/>
-      <c r="B538" s="29"/>
-      <c r="C538" s="29"/>
+      <c r="A538" s="28"/>
+      <c r="B538" s="28"/>
+      <c r="C538" s="28"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="A539" s="29"/>
-      <c r="B539" s="29"/>
-      <c r="C539" s="29"/>
+      <c r="A539" s="28"/>
+      <c r="B539" s="28"/>
+      <c r="C539" s="28"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="A540" s="29"/>
-      <c r="B540" s="29"/>
-      <c r="C540" s="29"/>
+      <c r="A540" s="28"/>
+      <c r="B540" s="28"/>
+      <c r="C540" s="28"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="A541" s="29"/>
-      <c r="B541" s="29"/>
-      <c r="C541" s="29"/>
+      <c r="A541" s="28"/>
+      <c r="B541" s="28"/>
+      <c r="C541" s="28"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="A542" s="29"/>
-      <c r="B542" s="29"/>
-      <c r="C542" s="29"/>
+      <c r="A542" s="28"/>
+      <c r="B542" s="28"/>
+      <c r="C542" s="28"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="A543" s="29"/>
-      <c r="B543" s="29"/>
-      <c r="C543" s="29"/>
+      <c r="A543" s="28"/>
+      <c r="B543" s="28"/>
+      <c r="C543" s="28"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="A544" s="29"/>
-      <c r="B544" s="29"/>
-      <c r="C544" s="29"/>
+      <c r="A544" s="28"/>
+      <c r="B544" s="28"/>
+      <c r="C544" s="28"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="A545" s="29"/>
-      <c r="B545" s="29"/>
-      <c r="C545" s="29"/>
+      <c r="A545" s="28"/>
+      <c r="B545" s="28"/>
+      <c r="C545" s="28"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="A546" s="29"/>
-      <c r="B546" s="29"/>
-      <c r="C546" s="29"/>
+      <c r="A546" s="28"/>
+      <c r="B546" s="28"/>
+      <c r="C546" s="28"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="A547" s="29"/>
-      <c r="B547" s="29"/>
-      <c r="C547" s="29"/>
+      <c r="A547" s="28"/>
+      <c r="B547" s="28"/>
+      <c r="C547" s="28"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="A548" s="29"/>
-      <c r="B548" s="29"/>
-      <c r="C548" s="29"/>
+      <c r="A548" s="28"/>
+      <c r="B548" s="28"/>
+      <c r="C548" s="28"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="A549" s="29"/>
-      <c r="B549" s="29"/>
-      <c r="C549" s="29"/>
+      <c r="A549" s="28"/>
+      <c r="B549" s="28"/>
+      <c r="C549" s="28"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="A550" s="29"/>
-      <c r="B550" s="29"/>
-      <c r="C550" s="29"/>
+      <c r="A550" s="28"/>
+      <c r="B550" s="28"/>
+      <c r="C550" s="28"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="A551" s="29"/>
-      <c r="B551" s="29"/>
-      <c r="C551" s="29"/>
+      <c r="A551" s="28"/>
+      <c r="B551" s="28"/>
+      <c r="C551" s="28"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="A552" s="29"/>
-      <c r="B552" s="29"/>
-      <c r="C552" s="29"/>
+      <c r="A552" s="28"/>
+      <c r="B552" s="28"/>
+      <c r="C552" s="28"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="A553" s="29"/>
-      <c r="B553" s="29"/>
-      <c r="C553" s="29"/>
+      <c r="A553" s="28"/>
+      <c r="B553" s="28"/>
+      <c r="C553" s="28"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="A554" s="29"/>
-      <c r="B554" s="29"/>
-      <c r="C554" s="29"/>
+      <c r="A554" s="28"/>
+      <c r="B554" s="28"/>
+      <c r="C554" s="28"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="A555" s="29"/>
-      <c r="B555" s="29"/>
-      <c r="C555" s="29"/>
+      <c r="A555" s="28"/>
+      <c r="B555" s="28"/>
+      <c r="C555" s="28"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="A556" s="29"/>
-      <c r="B556" s="29"/>
-      <c r="C556" s="29"/>
+      <c r="A556" s="28"/>
+      <c r="B556" s="28"/>
+      <c r="C556" s="28"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="A557" s="29"/>
-      <c r="B557" s="29"/>
-      <c r="C557" s="29"/>
+      <c r="A557" s="28"/>
+      <c r="B557" s="28"/>
+      <c r="C557" s="28"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="A558" s="29"/>
-      <c r="B558" s="29"/>
-      <c r="C558" s="29"/>
+      <c r="A558" s="28"/>
+      <c r="B558" s="28"/>
+      <c r="C558" s="28"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="A559" s="29"/>
-      <c r="B559" s="29"/>
-      <c r="C559" s="29"/>
+      <c r="A559" s="28"/>
+      <c r="B559" s="28"/>
+      <c r="C559" s="28"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="A560" s="29"/>
-      <c r="B560" s="29"/>
-      <c r="C560" s="29"/>
+      <c r="A560" s="28"/>
+      <c r="B560" s="28"/>
+      <c r="C560" s="28"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="A561" s="29"/>
-      <c r="B561" s="29"/>
-      <c r="C561" s="29"/>
+      <c r="A561" s="28"/>
+      <c r="B561" s="28"/>
+      <c r="C561" s="28"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="A562" s="29"/>
-      <c r="B562" s="29"/>
-      <c r="C562" s="29"/>
+      <c r="A562" s="28"/>
+      <c r="B562" s="28"/>
+      <c r="C562" s="28"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="A563" s="29"/>
-      <c r="B563" s="29"/>
-      <c r="C563" s="29"/>
+      <c r="A563" s="28"/>
+      <c r="B563" s="28"/>
+      <c r="C563" s="28"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="A564" s="29"/>
-      <c r="B564" s="29"/>
-      <c r="C564" s="29"/>
+      <c r="A564" s="28"/>
+      <c r="B564" s="28"/>
+      <c r="C564" s="28"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="A565" s="29"/>
-      <c r="B565" s="29"/>
-      <c r="C565" s="29"/>
+      <c r="A565" s="28"/>
+      <c r="B565" s="28"/>
+      <c r="C565" s="28"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="A566" s="29"/>
-      <c r="B566" s="29"/>
-      <c r="C566" s="29"/>
+      <c r="A566" s="28"/>
+      <c r="B566" s="28"/>
+      <c r="C566" s="28"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="A567" s="29"/>
-      <c r="B567" s="29"/>
-      <c r="C567" s="29"/>
+      <c r="A567" s="28"/>
+      <c r="B567" s="28"/>
+      <c r="C567" s="28"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="A568" s="29"/>
-      <c r="B568" s="29"/>
-      <c r="C568" s="29"/>
+      <c r="A568" s="28"/>
+      <c r="B568" s="28"/>
+      <c r="C568" s="28"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="A569" s="29"/>
-      <c r="B569" s="29"/>
-      <c r="C569" s="29"/>
+      <c r="A569" s="28"/>
+      <c r="B569" s="28"/>
+      <c r="C569" s="28"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="A570" s="29"/>
-      <c r="B570" s="29"/>
-      <c r="C570" s="29"/>
+      <c r="A570" s="28"/>
+      <c r="B570" s="28"/>
+      <c r="C570" s="28"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="A571" s="29"/>
-      <c r="B571" s="29"/>
-      <c r="C571" s="29"/>
+      <c r="A571" s="28"/>
+      <c r="B571" s="28"/>
+      <c r="C571" s="28"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="A572" s="29"/>
-      <c r="B572" s="29"/>
-      <c r="C572" s="29"/>
+      <c r="A572" s="28"/>
+      <c r="B572" s="28"/>
+      <c r="C572" s="28"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="A573" s="29"/>
-      <c r="B573" s="29"/>
-      <c r="C573" s="29"/>
+      <c r="A573" s="28"/>
+      <c r="B573" s="28"/>
+      <c r="C573" s="28"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="A574" s="29"/>
-      <c r="B574" s="29"/>
-      <c r="C574" s="29"/>
+      <c r="A574" s="28"/>
+      <c r="B574" s="28"/>
+      <c r="C574" s="28"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="A575" s="29"/>
-      <c r="B575" s="29"/>
-      <c r="C575" s="29"/>
+      <c r="A575" s="28"/>
+      <c r="B575" s="28"/>
+      <c r="C575" s="28"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="A576" s="29"/>
-      <c r="B576" s="29"/>
-      <c r="C576" s="29"/>
+      <c r="A576" s="28"/>
+      <c r="B576" s="28"/>
+      <c r="C576" s="28"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="A577" s="29"/>
-      <c r="B577" s="29"/>
-      <c r="C577" s="29"/>
+      <c r="A577" s="28"/>
+      <c r="B577" s="28"/>
+      <c r="C577" s="28"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="A578" s="29"/>
-      <c r="B578" s="29"/>
-      <c r="C578" s="29"/>
+      <c r="A578" s="28"/>
+      <c r="B578" s="28"/>
+      <c r="C578" s="28"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="A579" s="29"/>
-      <c r="B579" s="29"/>
-      <c r="C579" s="29"/>
+      <c r="A579" s="28"/>
+      <c r="B579" s="28"/>
+      <c r="C579" s="28"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="A580" s="29"/>
-      <c r="B580" s="29"/>
-      <c r="C580" s="29"/>
+      <c r="A580" s="28"/>
+      <c r="B580" s="28"/>
+      <c r="C580" s="28"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="A581" s="29"/>
-      <c r="B581" s="29"/>
-      <c r="C581" s="29"/>
+      <c r="A581" s="28"/>
+      <c r="B581" s="28"/>
+      <c r="C581" s="28"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="A582" s="29"/>
-      <c r="B582" s="29"/>
-      <c r="C582" s="29"/>
+      <c r="A582" s="28"/>
+      <c r="B582" s="28"/>
+      <c r="C582" s="28"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="A583" s="29"/>
-      <c r="B583" s="29"/>
-      <c r="C583" s="29"/>
+      <c r="A583" s="28"/>
+      <c r="B583" s="28"/>
+      <c r="C583" s="28"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="A584" s="29"/>
-      <c r="B584" s="29"/>
-      <c r="C584" s="29"/>
+      <c r="A584" s="28"/>
+      <c r="B584" s="28"/>
+      <c r="C584" s="28"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="A585" s="29"/>
-      <c r="B585" s="29"/>
-      <c r="C585" s="29"/>
+      <c r="A585" s="28"/>
+      <c r="B585" s="28"/>
+      <c r="C585" s="28"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="A586" s="29"/>
-      <c r="B586" s="29"/>
-      <c r="C586" s="29"/>
+      <c r="A586" s="28"/>
+      <c r="B586" s="28"/>
+      <c r="C586" s="28"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="A587" s="29"/>
-      <c r="B587" s="29"/>
-      <c r="C587" s="29"/>
+      <c r="A587" s="28"/>
+      <c r="B587" s="28"/>
+      <c r="C587" s="28"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="A588" s="29"/>
-      <c r="B588" s="29"/>
-      <c r="C588" s="29"/>
+      <c r="A588" s="28"/>
+      <c r="B588" s="28"/>
+      <c r="C588" s="28"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="A589" s="29"/>
-      <c r="B589" s="29"/>
-      <c r="C589" s="29"/>
+      <c r="A589" s="28"/>
+      <c r="B589" s="28"/>
+      <c r="C589" s="28"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="A590" s="29"/>
-      <c r="B590" s="29"/>
-      <c r="C590" s="29"/>
+      <c r="A590" s="28"/>
+      <c r="B590" s="28"/>
+      <c r="C590" s="28"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="A591" s="29"/>
-      <c r="B591" s="29"/>
-      <c r="C591" s="29"/>
+      <c r="A591" s="28"/>
+      <c r="B591" s="28"/>
+      <c r="C591" s="28"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="A592" s="29"/>
-      <c r="B592" s="29"/>
-      <c r="C592" s="29"/>
+      <c r="A592" s="28"/>
+      <c r="B592" s="28"/>
+      <c r="C592" s="28"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="A593" s="29"/>
-      <c r="B593" s="29"/>
-      <c r="C593" s="29"/>
+      <c r="A593" s="28"/>
+      <c r="B593" s="28"/>
+      <c r="C593" s="28"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="A594" s="29"/>
-      <c r="B594" s="29"/>
-      <c r="C594" s="29"/>
+      <c r="A594" s="28"/>
+      <c r="B594" s="28"/>
+      <c r="C594" s="28"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="A595" s="29"/>
-      <c r="B595" s="29"/>
-      <c r="C595" s="29"/>
+      <c r="A595" s="28"/>
+      <c r="B595" s="28"/>
+      <c r="C595" s="28"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="A596" s="29"/>
-      <c r="B596" s="29"/>
-      <c r="C596" s="29"/>
+      <c r="A596" s="28"/>
+      <c r="B596" s="28"/>
+      <c r="C596" s="28"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="A597" s="29"/>
-      <c r="B597" s="29"/>
-      <c r="C597" s="29"/>
+      <c r="A597" s="28"/>
+      <c r="B597" s="28"/>
+      <c r="C597" s="28"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="A598" s="29"/>
-      <c r="B598" s="29"/>
-      <c r="C598" s="29"/>
+      <c r="A598" s="28"/>
+      <c r="B598" s="28"/>
+      <c r="C598" s="28"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="A599" s="29"/>
-      <c r="B599" s="29"/>
-      <c r="C599" s="29"/>
+      <c r="A599" s="28"/>
+      <c r="B599" s="28"/>
+      <c r="C599" s="28"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="A600" s="29"/>
-      <c r="B600" s="29"/>
-      <c r="C600" s="29"/>
+      <c r="A600" s="28"/>
+      <c r="B600" s="28"/>
+      <c r="C600" s="28"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="A601" s="29"/>
-      <c r="B601" s="29"/>
-      <c r="C601" s="29"/>
+      <c r="A601" s="28"/>
+      <c r="B601" s="28"/>
+      <c r="C601" s="28"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="A602" s="29"/>
-      <c r="B602" s="29"/>
-      <c r="C602" s="29"/>
+      <c r="A602" s="28"/>
+      <c r="B602" s="28"/>
+      <c r="C602" s="28"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="A603" s="29"/>
-      <c r="B603" s="29"/>
-      <c r="C603" s="29"/>
+      <c r="A603" s="28"/>
+      <c r="B603" s="28"/>
+      <c r="C603" s="28"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="A604" s="29"/>
-      <c r="B604" s="29"/>
-      <c r="C604" s="29"/>
+      <c r="A604" s="28"/>
+      <c r="B604" s="28"/>
+      <c r="C604" s="28"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="A605" s="29"/>
-      <c r="B605" s="29"/>
-      <c r="C605" s="29"/>
+      <c r="A605" s="28"/>
+      <c r="B605" s="28"/>
+      <c r="C605" s="28"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="A606" s="29"/>
-      <c r="B606" s="29"/>
-      <c r="C606" s="29"/>
+      <c r="A606" s="28"/>
+      <c r="B606" s="28"/>
+      <c r="C606" s="28"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="A607" s="29"/>
-      <c r="B607" s="29"/>
-      <c r="C607" s="29"/>
+      <c r="A607" s="28"/>
+      <c r="B607" s="28"/>
+      <c r="C607" s="28"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="A608" s="29"/>
-      <c r="B608" s="29"/>
-      <c r="C608" s="29"/>
+      <c r="A608" s="28"/>
+      <c r="B608" s="28"/>
+      <c r="C608" s="28"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="A609" s="29"/>
-      <c r="B609" s="29"/>
-      <c r="C609" s="29"/>
+      <c r="A609" s="28"/>
+      <c r="B609" s="28"/>
+      <c r="C609" s="28"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="A610" s="29"/>
-      <c r="B610" s="29"/>
-      <c r="C610" s="29"/>
+      <c r="A610" s="28"/>
+      <c r="B610" s="28"/>
+      <c r="C610" s="28"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="A611" s="29"/>
-      <c r="B611" s="29"/>
-      <c r="C611" s="29"/>
+      <c r="A611" s="28"/>
+      <c r="B611" s="28"/>
+      <c r="C611" s="28"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="A612" s="29"/>
-      <c r="B612" s="29"/>
-      <c r="C612" s="29"/>
+      <c r="A612" s="28"/>
+      <c r="B612" s="28"/>
+      <c r="C612" s="28"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="A613" s="29"/>
-      <c r="B613" s="29"/>
-      <c r="C613" s="29"/>
+      <c r="A613" s="28"/>
+      <c r="B613" s="28"/>
+      <c r="C613" s="28"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="A614" s="29"/>
-      <c r="B614" s="29"/>
-      <c r="C614" s="29"/>
+      <c r="A614" s="28"/>
+      <c r="B614" s="28"/>
+      <c r="C614" s="28"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="A615" s="29"/>
-      <c r="B615" s="29"/>
-      <c r="C615" s="29"/>
+      <c r="A615" s="28"/>
+      <c r="B615" s="28"/>
+      <c r="C615" s="28"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="A616" s="29"/>
-      <c r="B616" s="29"/>
-      <c r="C616" s="29"/>
+      <c r="A616" s="28"/>
+      <c r="B616" s="28"/>
+      <c r="C616" s="28"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="A617" s="29"/>
-      <c r="B617" s="29"/>
-      <c r="C617" s="29"/>
+      <c r="A617" s="28"/>
+      <c r="B617" s="28"/>
+      <c r="C617" s="28"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="A618" s="29"/>
-      <c r="B618" s="29"/>
-      <c r="C618" s="29"/>
+      <c r="A618" s="28"/>
+      <c r="B618" s="28"/>
+      <c r="C618" s="28"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="A619" s="29"/>
-      <c r="B619" s="29"/>
-      <c r="C619" s="29"/>
+      <c r="A619" s="28"/>
+      <c r="B619" s="28"/>
+      <c r="C619" s="28"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="A620" s="29"/>
-      <c r="B620" s="29"/>
-      <c r="C620" s="29"/>
+      <c r="A620" s="28"/>
+      <c r="B620" s="28"/>
+      <c r="C620" s="28"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="A621" s="29"/>
-      <c r="B621" s="29"/>
-      <c r="C621" s="29"/>
+      <c r="A621" s="28"/>
+      <c r="B621" s="28"/>
+      <c r="C621" s="28"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="A622" s="29"/>
-      <c r="B622" s="29"/>
-      <c r="C622" s="29"/>
+      <c r="A622" s="28"/>
+      <c r="B622" s="28"/>
+      <c r="C622" s="28"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="A623" s="29"/>
-      <c r="B623" s="29"/>
-      <c r="C623" s="29"/>
+      <c r="A623" s="28"/>
+      <c r="B623" s="28"/>
+      <c r="C623" s="28"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="A624" s="29"/>
-      <c r="B624" s="29"/>
-      <c r="C624" s="29"/>
+      <c r="A624" s="28"/>
+      <c r="B624" s="28"/>
+      <c r="C624" s="28"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="A625" s="29"/>
-      <c r="B625" s="29"/>
-      <c r="C625" s="29"/>
+      <c r="A625" s="28"/>
+      <c r="B625" s="28"/>
+      <c r="C625" s="28"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="A626" s="29"/>
-      <c r="B626" s="29"/>
-      <c r="C626" s="29"/>
+      <c r="A626" s="28"/>
+      <c r="B626" s="28"/>
+      <c r="C626" s="28"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="A627" s="29"/>
-      <c r="B627" s="29"/>
-      <c r="C627" s="29"/>
+      <c r="A627" s="28"/>
+      <c r="B627" s="28"/>
+      <c r="C627" s="28"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="A628" s="29"/>
-      <c r="B628" s="29"/>
-      <c r="C628" s="29"/>
+      <c r="A628" s="28"/>
+      <c r="B628" s="28"/>
+      <c r="C628" s="28"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="A629" s="29"/>
-      <c r="B629" s="29"/>
-      <c r="C629" s="29"/>
+      <c r="A629" s="28"/>
+      <c r="B629" s="28"/>
+      <c r="C629" s="28"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="A630" s="29"/>
-      <c r="B630" s="29"/>
-      <c r="C630" s="29"/>
+      <c r="A630" s="28"/>
+      <c r="B630" s="28"/>
+      <c r="C630" s="28"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="A631" s="29"/>
-      <c r="B631" s="29"/>
-      <c r="C631" s="29"/>
+      <c r="A631" s="28"/>
+      <c r="B631" s="28"/>
+      <c r="C631" s="28"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="A632" s="29"/>
-      <c r="B632" s="29"/>
-      <c r="C632" s="29"/>
+      <c r="A632" s="28"/>
+      <c r="B632" s="28"/>
+      <c r="C632" s="28"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="A633" s="29"/>
-      <c r="B633" s="29"/>
-      <c r="C633" s="29"/>
+      <c r="A633" s="28"/>
+      <c r="B633" s="28"/>
+      <c r="C633" s="28"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="A634" s="29"/>
-      <c r="B634" s="29"/>
-      <c r="C634" s="29"/>
+      <c r="A634" s="28"/>
+      <c r="B634" s="28"/>
+      <c r="C634" s="28"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="A635" s="29"/>
-      <c r="B635" s="29"/>
-      <c r="C635" s="29"/>
+      <c r="A635" s="28"/>
+      <c r="B635" s="28"/>
+      <c r="C635" s="28"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="A636" s="29"/>
-      <c r="B636" s="29"/>
-      <c r="C636" s="29"/>
+      <c r="A636" s="28"/>
+      <c r="B636" s="28"/>
+      <c r="C636" s="28"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="A637" s="29"/>
-      <c r="B637" s="29"/>
-      <c r="C637" s="29"/>
+      <c r="A637" s="28"/>
+      <c r="B637" s="28"/>
+      <c r="C637" s="28"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="A638" s="29"/>
-      <c r="B638" s="29"/>
-      <c r="C638" s="29"/>
+      <c r="A638" s="28"/>
+      <c r="B638" s="28"/>
+      <c r="C638" s="28"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="A639" s="29"/>
-      <c r="B639" s="29"/>
-      <c r="C639" s="29"/>
+      <c r="A639" s="28"/>
+      <c r="B639" s="28"/>
+      <c r="C639" s="28"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="A640" s="29"/>
-      <c r="B640" s="29"/>
-      <c r="C640" s="29"/>
+      <c r="A640" s="28"/>
+      <c r="B640" s="28"/>
+      <c r="C640" s="28"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="A641" s="29"/>
-      <c r="B641" s="29"/>
-      <c r="C641" s="29"/>
+      <c r="A641" s="28"/>
+      <c r="B641" s="28"/>
+      <c r="C641" s="28"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="A642" s="29"/>
-      <c r="B642" s="29"/>
-      <c r="C642" s="29"/>
+      <c r="A642" s="28"/>
+      <c r="B642" s="28"/>
+      <c r="C642" s="28"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="A643" s="29"/>
-      <c r="B643" s="29"/>
-      <c r="C643" s="29"/>
+      <c r="A643" s="28"/>
+      <c r="B643" s="28"/>
+      <c r="C643" s="28"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="A644" s="29"/>
-      <c r="B644" s="29"/>
-      <c r="C644" s="29"/>
+      <c r="A644" s="28"/>
+      <c r="B644" s="28"/>
+      <c r="C644" s="28"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="A645" s="29"/>
-      <c r="B645" s="29"/>
-      <c r="C645" s="29"/>
+      <c r="A645" s="28"/>
+      <c r="B645" s="28"/>
+      <c r="C645" s="28"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="A646" s="29"/>
-      <c r="B646" s="29"/>
-      <c r="C646" s="29"/>
+      <c r="A646" s="28"/>
+      <c r="B646" s="28"/>
+      <c r="C646" s="28"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="A647" s="29"/>
-      <c r="B647" s="29"/>
-      <c r="C647" s="29"/>
+      <c r="A647" s="28"/>
+      <c r="B647" s="28"/>
+      <c r="C647" s="28"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="A648" s="29"/>
-      <c r="B648" s="29"/>
-      <c r="C648" s="29"/>
+      <c r="A648" s="28"/>
+      <c r="B648" s="28"/>
+      <c r="C648" s="28"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="A649" s="29"/>
-      <c r="B649" s="29"/>
-      <c r="C649" s="29"/>
+      <c r="A649" s="28"/>
+      <c r="B649" s="28"/>
+      <c r="C649" s="28"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="A650" s="29"/>
-      <c r="B650" s="29"/>
-      <c r="C650" s="29"/>
+      <c r="A650" s="28"/>
+      <c r="B650" s="28"/>
+      <c r="C650" s="28"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="A651" s="29"/>
-      <c r="B651" s="29"/>
-      <c r="C651" s="29"/>
+      <c r="A651" s="28"/>
+      <c r="B651" s="28"/>
+      <c r="C651" s="28"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="A652" s="29"/>
-      <c r="B652" s="29"/>
-      <c r="C652" s="29"/>
+      <c r="A652" s="28"/>
+      <c r="B652" s="28"/>
+      <c r="C652" s="28"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="A653" s="29"/>
-      <c r="B653" s="29"/>
-      <c r="C653" s="29"/>
+      <c r="A653" s="28"/>
+      <c r="B653" s="28"/>
+      <c r="C653" s="28"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="A654" s="29"/>
-      <c r="B654" s="29"/>
-      <c r="C654" s="29"/>
+      <c r="A654" s="28"/>
+      <c r="B654" s="28"/>
+      <c r="C654" s="28"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="A655" s="29"/>
-      <c r="B655" s="29"/>
-      <c r="C655" s="29"/>
+      <c r="A655" s="28"/>
+      <c r="B655" s="28"/>
+      <c r="C655" s="28"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="A656" s="29"/>
-      <c r="B656" s="29"/>
-      <c r="C656" s="29"/>
+      <c r="A656" s="28"/>
+      <c r="B656" s="28"/>
+      <c r="C656" s="28"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="A657" s="29"/>
-      <c r="B657" s="29"/>
-      <c r="C657" s="29"/>
+      <c r="A657" s="28"/>
+      <c r="B657" s="28"/>
+      <c r="C657" s="28"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="A658" s="29"/>
-      <c r="B658" s="29"/>
-      <c r="C658" s="29"/>
+      <c r="A658" s="28"/>
+      <c r="B658" s="28"/>
+      <c r="C658" s="28"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="A659" s="29"/>
-      <c r="B659" s="29"/>
-      <c r="C659" s="29"/>
+      <c r="A659" s="28"/>
+      <c r="B659" s="28"/>
+      <c r="C659" s="28"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="A660" s="29"/>
-      <c r="B660" s="29"/>
-      <c r="C660" s="29"/>
+      <c r="A660" s="28"/>
+      <c r="B660" s="28"/>
+      <c r="C660" s="28"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="A661" s="29"/>
-      <c r="B661" s="29"/>
-      <c r="C661" s="29"/>
+      <c r="A661" s="28"/>
+      <c r="B661" s="28"/>
+      <c r="C661" s="28"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="A662" s="29"/>
-      <c r="B662" s="29"/>
-      <c r="C662" s="29"/>
+      <c r="A662" s="28"/>
+      <c r="B662" s="28"/>
+      <c r="C662" s="28"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="A663" s="29"/>
-      <c r="B663" s="29"/>
-      <c r="C663" s="29"/>
+      <c r="A663" s="28"/>
+      <c r="B663" s="28"/>
+      <c r="C663" s="28"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="A664" s="29"/>
-      <c r="B664" s="29"/>
-      <c r="C664" s="29"/>
+      <c r="A664" s="28"/>
+      <c r="B664" s="28"/>
+      <c r="C664" s="28"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="A665" s="29"/>
-      <c r="B665" s="29"/>
-      <c r="C665" s="29"/>
+      <c r="A665" s="28"/>
+      <c r="B665" s="28"/>
+      <c r="C665" s="28"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="A666" s="29"/>
-      <c r="B666" s="29"/>
-      <c r="C666" s="29"/>
+      <c r="A666" s="28"/>
+      <c r="B666" s="28"/>
+      <c r="C666" s="28"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="A667" s="29"/>
-      <c r="B667" s="29"/>
-      <c r="C667" s="29"/>
+      <c r="A667" s="28"/>
+      <c r="B667" s="28"/>
+      <c r="C667" s="28"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="A668" s="29"/>
-      <c r="B668" s="29"/>
-      <c r="C668" s="29"/>
+      <c r="A668" s="28"/>
+      <c r="B668" s="28"/>
+      <c r="C668" s="28"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="A669" s="29"/>
-      <c r="B669" s="29"/>
-      <c r="C669" s="29"/>
+      <c r="A669" s="28"/>
+      <c r="B669" s="28"/>
+      <c r="C669" s="28"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="A670" s="29"/>
-      <c r="B670" s="29"/>
-      <c r="C670" s="29"/>
+      <c r="A670" s="28"/>
+      <c r="B670" s="28"/>
+      <c r="C670" s="28"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="A671" s="29"/>
-      <c r="B671" s="29"/>
-      <c r="C671" s="29"/>
+      <c r="A671" s="28"/>
+      <c r="B671" s="28"/>
+      <c r="C671" s="28"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="A672" s="29"/>
-      <c r="B672" s="29"/>
-      <c r="C672" s="29"/>
+      <c r="A672" s="28"/>
+      <c r="B672" s="28"/>
+      <c r="C672" s="28"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="A673" s="29"/>
-      <c r="B673" s="29"/>
-      <c r="C673" s="29"/>
+      <c r="A673" s="28"/>
+      <c r="B673" s="28"/>
+      <c r="C673" s="28"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="A674" s="29"/>
-      <c r="B674" s="29"/>
-      <c r="C674" s="29"/>
+      <c r="A674" s="28"/>
+      <c r="B674" s="28"/>
+      <c r="C674" s="28"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="A675" s="29"/>
-      <c r="B675" s="29"/>
-      <c r="C675" s="29"/>
+      <c r="A675" s="28"/>
+      <c r="B675" s="28"/>
+      <c r="C675" s="28"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="A676" s="29"/>
-      <c r="B676" s="29"/>
-      <c r="C676" s="29"/>
+      <c r="A676" s="28"/>
+      <c r="B676" s="28"/>
+      <c r="C676" s="28"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="A677" s="29"/>
-      <c r="B677" s="29"/>
-      <c r="C677" s="29"/>
+      <c r="A677" s="28"/>
+      <c r="B677" s="28"/>
+      <c r="C677" s="28"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="A678" s="29"/>
-      <c r="B678" s="29"/>
-      <c r="C678" s="29"/>
+      <c r="A678" s="28"/>
+      <c r="B678" s="28"/>
+      <c r="C678" s="28"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="A679" s="29"/>
-      <c r="B679" s="29"/>
-      <c r="C679" s="29"/>
+      <c r="A679" s="28"/>
+      <c r="B679" s="28"/>
+      <c r="C679" s="28"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="A680" s="29"/>
-      <c r="B680" s="29"/>
-      <c r="C680" s="29"/>
+      <c r="A680" s="28"/>
+      <c r="B680" s="28"/>
+      <c r="C680" s="28"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="A681" s="29"/>
-      <c r="B681" s="29"/>
-      <c r="C681" s="29"/>
+      <c r="A681" s="28"/>
+      <c r="B681" s="28"/>
+      <c r="C681" s="28"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="A682" s="29"/>
-      <c r="B682" s="29"/>
-      <c r="C682" s="29"/>
+      <c r="A682" s="28"/>
+      <c r="B682" s="28"/>
+      <c r="C682" s="28"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="A683" s="29"/>
-      <c r="B683" s="29"/>
-      <c r="C683" s="29"/>
+      <c r="A683" s="28"/>
+      <c r="B683" s="28"/>
+      <c r="C683" s="28"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="A684" s="29"/>
-      <c r="B684" s="29"/>
-      <c r="C684" s="29"/>
+      <c r="A684" s="28"/>
+      <c r="B684" s="28"/>
+      <c r="C684" s="28"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="A685" s="29"/>
-      <c r="B685" s="29"/>
-      <c r="C685" s="29"/>
+      <c r="A685" s="28"/>
+      <c r="B685" s="28"/>
+      <c r="C685" s="28"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="A686" s="29"/>
-      <c r="B686" s="29"/>
-      <c r="C686" s="29"/>
+      <c r="A686" s="28"/>
+      <c r="B686" s="28"/>
+      <c r="C686" s="28"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="A687" s="29"/>
-      <c r="B687" s="29"/>
-      <c r="C687" s="29"/>
+      <c r="A687" s="28"/>
+      <c r="B687" s="28"/>
+      <c r="C687" s="28"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="A688" s="29"/>
-      <c r="B688" s="29"/>
-      <c r="C688" s="29"/>
+      <c r="A688" s="28"/>
+      <c r="B688" s="28"/>
+      <c r="C688" s="28"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="A689" s="29"/>
-      <c r="B689" s="29"/>
-      <c r="C689" s="29"/>
+      <c r="A689" s="28"/>
+      <c r="B689" s="28"/>
+      <c r="C689" s="28"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="A690" s="29"/>
-      <c r="B690" s="29"/>
-      <c r="C690" s="29"/>
+      <c r="A690" s="28"/>
+      <c r="B690" s="28"/>
+      <c r="C690" s="28"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="A691" s="29"/>
-      <c r="B691" s="29"/>
-      <c r="C691" s="29"/>
+      <c r="A691" s="28"/>
+      <c r="B691" s="28"/>
+      <c r="C691" s="28"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="A692" s="29"/>
-      <c r="B692" s="29"/>
-      <c r="C692" s="29"/>
+      <c r="A692" s="28"/>
+      <c r="B692" s="28"/>
+      <c r="C692" s="28"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="A693" s="29"/>
-      <c r="B693" s="29"/>
-      <c r="C693" s="29"/>
+      <c r="A693" s="28"/>
+      <c r="B693" s="28"/>
+      <c r="C693" s="28"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="A694" s="29"/>
-      <c r="B694" s="29"/>
-      <c r="C694" s="29"/>
+      <c r="A694" s="28"/>
+      <c r="B694" s="28"/>
+      <c r="C694" s="28"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="A695" s="29"/>
-      <c r="B695" s="29"/>
-      <c r="C695" s="29"/>
+      <c r="A695" s="28"/>
+      <c r="B695" s="28"/>
+      <c r="C695" s="28"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="A696" s="29"/>
-      <c r="B696" s="29"/>
-      <c r="C696" s="29"/>
+      <c r="A696" s="28"/>
+      <c r="B696" s="28"/>
+      <c r="C696" s="28"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="A697" s="29"/>
-      <c r="B697" s="29"/>
-      <c r="C697" s="29"/>
+      <c r="A697" s="28"/>
+      <c r="B697" s="28"/>
+      <c r="C697" s="28"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="A698" s="29"/>
-      <c r="B698" s="29"/>
-      <c r="C698" s="29"/>
+      <c r="A698" s="28"/>
+      <c r="B698" s="28"/>
+      <c r="C698" s="28"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="A699" s="29"/>
-      <c r="B699" s="29"/>
-      <c r="C699" s="29"/>
+      <c r="A699" s="28"/>
+      <c r="B699" s="28"/>
+      <c r="C699" s="28"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="A700" s="29"/>
-      <c r="B700" s="29"/>
-      <c r="C700" s="29"/>
+      <c r="A700" s="28"/>
+      <c r="B700" s="28"/>
+      <c r="C700" s="28"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="A701" s="29"/>
-      <c r="B701" s="29"/>
-      <c r="C701" s="29"/>
+      <c r="A701" s="28"/>
+      <c r="B701" s="28"/>
+      <c r="C701" s="28"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="A702" s="29"/>
-      <c r="B702" s="29"/>
-      <c r="C702" s="29"/>
+      <c r="A702" s="28"/>
+      <c r="B702" s="28"/>
+      <c r="C702" s="28"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="A703" s="29"/>
-      <c r="B703" s="29"/>
-      <c r="C703" s="29"/>
+      <c r="A703" s="28"/>
+      <c r="B703" s="28"/>
+      <c r="C703" s="28"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="A704" s="29"/>
-      <c r="B704" s="29"/>
-      <c r="C704" s="29"/>
+      <c r="A704" s="28"/>
+      <c r="B704" s="28"/>
+      <c r="C704" s="28"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="A705" s="29"/>
-      <c r="B705" s="29"/>
-      <c r="C705" s="29"/>
+      <c r="A705" s="28"/>
+      <c r="B705" s="28"/>
+      <c r="C705" s="28"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="A706" s="29"/>
-      <c r="B706" s="29"/>
-      <c r="C706" s="29"/>
+      <c r="A706" s="28"/>
+      <c r="B706" s="28"/>
+      <c r="C706" s="28"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="A707" s="29"/>
-      <c r="B707" s="29"/>
-      <c r="C707" s="29"/>
+      <c r="A707" s="28"/>
+      <c r="B707" s="28"/>
+      <c r="C707" s="28"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="29"/>
-      <c r="B708" s="29"/>
-      <c r="C708" s="29"/>
+      <c r="A708" s="28"/>
+      <c r="B708" s="28"/>
+      <c r="C708" s="28"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="A709" s="29"/>
-      <c r="B709" s="29"/>
-      <c r="C709" s="29"/>
+      <c r="A709" s="28"/>
+      <c r="B709" s="28"/>
+      <c r="C709" s="28"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="A710" s="29"/>
-      <c r="B710" s="29"/>
-      <c r="C710" s="29"/>
+      <c r="A710" s="28"/>
+      <c r="B710" s="28"/>
+      <c r="C710" s="28"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="A711" s="29"/>
-      <c r="B711" s="29"/>
-      <c r="C711" s="29"/>
+      <c r="A711" s="28"/>
+      <c r="B711" s="28"/>
+      <c r="C711" s="28"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="A712" s="29"/>
-      <c r="B712" s="29"/>
-      <c r="C712" s="29"/>
+      <c r="A712" s="28"/>
+      <c r="B712" s="28"/>
+      <c r="C712" s="28"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="A713" s="29"/>
-      <c r="B713" s="29"/>
-      <c r="C713" s="29"/>
+      <c r="A713" s="28"/>
+      <c r="B713" s="28"/>
+      <c r="C713" s="28"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="A714" s="29"/>
-      <c r="B714" s="29"/>
-      <c r="C714" s="29"/>
+      <c r="A714" s="28"/>
+      <c r="B714" s="28"/>
+      <c r="C714" s="28"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="A715" s="29"/>
-      <c r="B715" s="29"/>
-      <c r="C715" s="29"/>
+      <c r="A715" s="28"/>
+      <c r="B715" s="28"/>
+      <c r="C715" s="28"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="A716" s="29"/>
-      <c r="B716" s="29"/>
-      <c r="C716" s="29"/>
+      <c r="A716" s="28"/>
+      <c r="B716" s="28"/>
+      <c r="C716" s="28"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="A717" s="29"/>
-      <c r="B717" s="29"/>
-      <c r="C717" s="29"/>
+      <c r="A717" s="28"/>
+      <c r="B717" s="28"/>
+      <c r="C717" s="28"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="A718" s="29"/>
-      <c r="B718" s="29"/>
-      <c r="C718" s="29"/>
+      <c r="A718" s="28"/>
+      <c r="B718" s="28"/>
+      <c r="C718" s="28"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="A719" s="29"/>
-      <c r="B719" s="29"/>
-      <c r="C719" s="29"/>
+      <c r="A719" s="28"/>
+      <c r="B719" s="28"/>
+      <c r="C719" s="28"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="A720" s="29"/>
-      <c r="B720" s="29"/>
-      <c r="C720" s="29"/>
+      <c r="A720" s="28"/>
+      <c r="B720" s="28"/>
+      <c r="C720" s="28"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="A721" s="29"/>
-      <c r="B721" s="29"/>
-      <c r="C721" s="29"/>
+      <c r="A721" s="28"/>
+      <c r="B721" s="28"/>
+      <c r="C721" s="28"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="A722" s="29"/>
-      <c r="B722" s="29"/>
-      <c r="C722" s="29"/>
+      <c r="A722" s="28"/>
+      <c r="B722" s="28"/>
+      <c r="C722" s="28"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="A723" s="29"/>
-      <c r="B723" s="29"/>
-      <c r="C723" s="29"/>
+      <c r="A723" s="28"/>
+      <c r="B723" s="28"/>
+      <c r="C723" s="28"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="A724" s="29"/>
-      <c r="B724" s="29"/>
-      <c r="C724" s="29"/>
+      <c r="A724" s="28"/>
+      <c r="B724" s="28"/>
+      <c r="C724" s="28"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="A725" s="29"/>
-      <c r="B725" s="29"/>
-      <c r="C725" s="29"/>
+      <c r="A725" s="28"/>
+      <c r="B725" s="28"/>
+      <c r="C725" s="28"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="A726" s="29"/>
-      <c r="B726" s="29"/>
-      <c r="C726" s="29"/>
+      <c r="A726" s="28"/>
+      <c r="B726" s="28"/>
+      <c r="C726" s="28"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="A727" s="29"/>
-      <c r="B727" s="29"/>
-      <c r="C727" s="29"/>
+      <c r="A727" s="28"/>
+      <c r="B727" s="28"/>
+      <c r="C727" s="28"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="A728" s="29"/>
-      <c r="B728" s="29"/>
-      <c r="C728" s="29"/>
+      <c r="A728" s="28"/>
+      <c r="B728" s="28"/>
+      <c r="C728" s="28"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="A729" s="29"/>
-      <c r="B729" s="29"/>
-      <c r="C729" s="29"/>
+      <c r="A729" s="28"/>
+      <c r="B729" s="28"/>
+      <c r="C729" s="28"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="A730" s="29"/>
-      <c r="B730" s="29"/>
-      <c r="C730" s="29"/>
+      <c r="A730" s="28"/>
+      <c r="B730" s="28"/>
+      <c r="C730" s="28"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="A731" s="29"/>
-      <c r="B731" s="29"/>
-      <c r="C731" s="29"/>
+      <c r="A731" s="28"/>
+      <c r="B731" s="28"/>
+      <c r="C731" s="28"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="A732" s="29"/>
-      <c r="B732" s="29"/>
-      <c r="C732" s="29"/>
+      <c r="A732" s="28"/>
+      <c r="B732" s="28"/>
+      <c r="C732" s="28"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="A733" s="29"/>
-      <c r="B733" s="29"/>
-      <c r="C733" s="29"/>
+      <c r="A733" s="28"/>
+      <c r="B733" s="28"/>
+      <c r="C733" s="28"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="A734" s="29"/>
-      <c r="B734" s="29"/>
-      <c r="C734" s="29"/>
+      <c r="A734" s="28"/>
+      <c r="B734" s="28"/>
+      <c r="C734" s="28"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="A735" s="29"/>
-      <c r="B735" s="29"/>
-      <c r="C735" s="29"/>
+      <c r="A735" s="28"/>
+      <c r="B735" s="28"/>
+      <c r="C735" s="28"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="A736" s="29"/>
-      <c r="B736" s="29"/>
-      <c r="C736" s="29"/>
+      <c r="A736" s="28"/>
+      <c r="B736" s="28"/>
+      <c r="C736" s="28"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="A737" s="29"/>
-      <c r="B737" s="29"/>
-      <c r="C737" s="29"/>
+      <c r="A737" s="28"/>
+      <c r="B737" s="28"/>
+      <c r="C737" s="28"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="A738" s="29"/>
-      <c r="B738" s="29"/>
-      <c r="C738" s="29"/>
+      <c r="A738" s="28"/>
+      <c r="B738" s="28"/>
+      <c r="C738" s="28"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="A739" s="29"/>
-      <c r="B739" s="29"/>
-      <c r="C739" s="29"/>
+      <c r="A739" s="28"/>
+      <c r="B739" s="28"/>
+      <c r="C739" s="28"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="A740" s="29"/>
-      <c r="B740" s="29"/>
-      <c r="C740" s="29"/>
+      <c r="A740" s="28"/>
+      <c r="B740" s="28"/>
+      <c r="C740" s="28"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="A741" s="29"/>
-      <c r="B741" s="29"/>
-      <c r="C741" s="29"/>
+      <c r="A741" s="28"/>
+      <c r="B741" s="28"/>
+      <c r="C741" s="28"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="A742" s="29"/>
-      <c r="B742" s="29"/>
-      <c r="C742" s="29"/>
+      <c r="A742" s="28"/>
+      <c r="B742" s="28"/>
+      <c r="C742" s="28"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="A743" s="29"/>
-      <c r="B743" s="29"/>
-      <c r="C743" s="29"/>
+      <c r="A743" s="28"/>
+      <c r="B743" s="28"/>
+      <c r="C743" s="28"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="A744" s="29"/>
-      <c r="B744" s="29"/>
-      <c r="C744" s="29"/>
+      <c r="A744" s="28"/>
+      <c r="B744" s="28"/>
+      <c r="C744" s="28"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="A745" s="29"/>
-      <c r="B745" s="29"/>
-      <c r="C745" s="29"/>
+      <c r="A745" s="28"/>
+      <c r="B745" s="28"/>
+      <c r="C745" s="28"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="A746" s="29"/>
-      <c r="B746" s="29"/>
-      <c r="C746" s="29"/>
+      <c r="A746" s="28"/>
+      <c r="B746" s="28"/>
+      <c r="C746" s="28"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="A747" s="29"/>
-      <c r="B747" s="29"/>
-      <c r="C747" s="29"/>
+      <c r="A747" s="28"/>
+      <c r="B747" s="28"/>
+      <c r="C747" s="28"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="A748" s="29"/>
-      <c r="B748" s="29"/>
-      <c r="C748" s="29"/>
+      <c r="A748" s="28"/>
+      <c r="B748" s="28"/>
+      <c r="C748" s="28"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="A749" s="29"/>
-      <c r="B749" s="29"/>
-      <c r="C749" s="29"/>
+      <c r="A749" s="28"/>
+      <c r="B749" s="28"/>
+      <c r="C749" s="28"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="A750" s="29"/>
-      <c r="B750" s="29"/>
-      <c r="C750" s="29"/>
+      <c r="A750" s="28"/>
+      <c r="B750" s="28"/>
+      <c r="C750" s="28"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="A751" s="29"/>
-      <c r="B751" s="29"/>
-      <c r="C751" s="29"/>
+      <c r="A751" s="28"/>
+      <c r="B751" s="28"/>
+      <c r="C751" s="28"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="A752" s="29"/>
-      <c r="B752" s="29"/>
-      <c r="C752" s="29"/>
+      <c r="A752" s="28"/>
+      <c r="B752" s="28"/>
+      <c r="C752" s="28"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="A753" s="29"/>
-      <c r="B753" s="29"/>
-      <c r="C753" s="29"/>
+      <c r="A753" s="28"/>
+      <c r="B753" s="28"/>
+      <c r="C753" s="28"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="A754" s="29"/>
-      <c r="B754" s="29"/>
-      <c r="C754" s="29"/>
+      <c r="A754" s="28"/>
+      <c r="B754" s="28"/>
+      <c r="C754" s="28"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="A755" s="29"/>
-      <c r="B755" s="29"/>
-      <c r="C755" s="29"/>
+      <c r="A755" s="28"/>
+      <c r="B755" s="28"/>
+      <c r="C755" s="28"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="A756" s="29"/>
-      <c r="B756" s="29"/>
-      <c r="C756" s="29"/>
+      <c r="A756" s="28"/>
+      <c r="B756" s="28"/>
+      <c r="C756" s="28"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="A757" s="29"/>
-      <c r="B757" s="29"/>
-      <c r="C757" s="29"/>
+      <c r="A757" s="28"/>
+      <c r="B757" s="28"/>
+      <c r="C757" s="28"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="A758" s="29"/>
-      <c r="B758" s="29"/>
-      <c r="C758" s="29"/>
+      <c r="A758" s="28"/>
+      <c r="B758" s="28"/>
+      <c r="C758" s="28"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="A759" s="29"/>
-      <c r="B759" s="29"/>
-      <c r="C759" s="29"/>
+      <c r="A759" s="28"/>
+      <c r="B759" s="28"/>
+      <c r="C759" s="28"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="A760" s="29"/>
-      <c r="B760" s="29"/>
-      <c r="C760" s="29"/>
+      <c r="A760" s="28"/>
+      <c r="B760" s="28"/>
+      <c r="C760" s="28"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="A761" s="29"/>
-      <c r="B761" s="29"/>
-      <c r="C761" s="29"/>
+      <c r="A761" s="28"/>
+      <c r="B761" s="28"/>
+      <c r="C761" s="28"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="A762" s="29"/>
-      <c r="B762" s="29"/>
-      <c r="C762" s="29"/>
+      <c r="A762" s="28"/>
+      <c r="B762" s="28"/>
+      <c r="C762" s="28"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="A763" s="29"/>
-      <c r="B763" s="29"/>
-      <c r="C763" s="29"/>
+      <c r="A763" s="28"/>
+      <c r="B763" s="28"/>
+      <c r="C763" s="28"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="A764" s="29"/>
-      <c r="B764" s="29"/>
-      <c r="C764" s="29"/>
+      <c r="A764" s="28"/>
+      <c r="B764" s="28"/>
+      <c r="C764" s="28"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="A765" s="29"/>
-      <c r="B765" s="29"/>
-      <c r="C765" s="29"/>
+      <c r="A765" s="28"/>
+      <c r="B765" s="28"/>
+      <c r="C765" s="28"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="A766" s="29"/>
-      <c r="B766" s="29"/>
-      <c r="C766" s="29"/>
+      <c r="A766" s="28"/>
+      <c r="B766" s="28"/>
+      <c r="C766" s="28"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="A767" s="29"/>
-      <c r="B767" s="29"/>
-      <c r="C767" s="29"/>
+      <c r="A767" s="28"/>
+      <c r="B767" s="28"/>
+      <c r="C767" s="28"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="A768" s="29"/>
-      <c r="B768" s="29"/>
-      <c r="C768" s="29"/>
+      <c r="A768" s="28"/>
+      <c r="B768" s="28"/>
+      <c r="C768" s="28"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="A769" s="29"/>
-      <c r="B769" s="29"/>
-      <c r="C769" s="29"/>
+      <c r="A769" s="28"/>
+      <c r="B769" s="28"/>
+      <c r="C769" s="28"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="A770" s="29"/>
-      <c r="B770" s="29"/>
-      <c r="C770" s="29"/>
+      <c r="A770" s="28"/>
+      <c r="B770" s="28"/>
+      <c r="C770" s="28"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="A771" s="29"/>
-      <c r="B771" s="29"/>
-      <c r="C771" s="29"/>
+      <c r="A771" s="28"/>
+      <c r="B771" s="28"/>
+      <c r="C771" s="28"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="A772" s="29"/>
-      <c r="B772" s="29"/>
-      <c r="C772" s="29"/>
+      <c r="A772" s="28"/>
+      <c r="B772" s="28"/>
+      <c r="C772" s="28"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="A773" s="29"/>
-      <c r="B773" s="29"/>
-      <c r="C773" s="29"/>
+      <c r="A773" s="28"/>
+      <c r="B773" s="28"/>
+      <c r="C773" s="28"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="A774" s="29"/>
-      <c r="B774" s="29"/>
-      <c r="C774" s="29"/>
+      <c r="A774" s="28"/>
+      <c r="B774" s="28"/>
+      <c r="C774" s="28"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="A775" s="29"/>
-      <c r="B775" s="29"/>
-      <c r="C775" s="29"/>
+      <c r="A775" s="28"/>
+      <c r="B775" s="28"/>
+      <c r="C775" s="28"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="A776" s="29"/>
-      <c r="B776" s="29"/>
-      <c r="C776" s="29"/>
+      <c r="A776" s="28"/>
+      <c r="B776" s="28"/>
+      <c r="C776" s="28"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="A777" s="29"/>
-      <c r="B777" s="29"/>
-      <c r="C777" s="29"/>
+      <c r="A777" s="28"/>
+      <c r="B777" s="28"/>
+      <c r="C777" s="28"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="A778" s="29"/>
-      <c r="B778" s="29"/>
-      <c r="C778" s="29"/>
+      <c r="A778" s="28"/>
+      <c r="B778" s="28"/>
+      <c r="C778" s="28"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="A779" s="29"/>
-      <c r="B779" s="29"/>
-      <c r="C779" s="29"/>
+      <c r="A779" s="28"/>
+      <c r="B779" s="28"/>
+      <c r="C779" s="28"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="A780" s="29"/>
-      <c r="B780" s="29"/>
-      <c r="C780" s="29"/>
+      <c r="A780" s="28"/>
+      <c r="B780" s="28"/>
+      <c r="C780" s="28"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="A781" s="29"/>
-      <c r="B781" s="29"/>
-      <c r="C781" s="29"/>
+      <c r="A781" s="28"/>
+      <c r="B781" s="28"/>
+      <c r="C781" s="28"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="A782" s="29"/>
-      <c r="B782" s="29"/>
-      <c r="C782" s="29"/>
+      <c r="A782" s="28"/>
+      <c r="B782" s="28"/>
+      <c r="C782" s="28"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="A783" s="29"/>
-      <c r="B783" s="29"/>
-      <c r="C783" s="29"/>
+      <c r="A783" s="28"/>
+      <c r="B783" s="28"/>
+      <c r="C783" s="28"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="A784" s="29"/>
-      <c r="B784" s="29"/>
-      <c r="C784" s="29"/>
+      <c r="A784" s="28"/>
+      <c r="B784" s="28"/>
+      <c r="C784" s="28"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="A785" s="29"/>
-      <c r="B785" s="29"/>
-      <c r="C785" s="29"/>
+      <c r="A785" s="28"/>
+      <c r="B785" s="28"/>
+      <c r="C785" s="28"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="A786" s="29"/>
-      <c r="B786" s="29"/>
-      <c r="C786" s="29"/>
+      <c r="A786" s="28"/>
+      <c r="B786" s="28"/>
+      <c r="C786" s="28"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="A787" s="29"/>
-      <c r="B787" s="29"/>
-      <c r="C787" s="29"/>
+      <c r="A787" s="28"/>
+      <c r="B787" s="28"/>
+      <c r="C787" s="28"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="A788" s="29"/>
-      <c r="B788" s="29"/>
-      <c r="C788" s="29"/>
+      <c r="A788" s="28"/>
+      <c r="B788" s="28"/>
+      <c r="C788" s="28"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="A789" s="29"/>
-      <c r="B789" s="29"/>
-      <c r="C789" s="29"/>
+      <c r="A789" s="28"/>
+      <c r="B789" s="28"/>
+      <c r="C789" s="28"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="A790" s="29"/>
-      <c r="B790" s="29"/>
-      <c r="C790" s="29"/>
+      <c r="A790" s="28"/>
+      <c r="B790" s="28"/>
+      <c r="C790" s="28"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="A791" s="29"/>
-      <c r="B791" s="29"/>
-      <c r="C791" s="29"/>
+      <c r="A791" s="28"/>
+      <c r="B791" s="28"/>
+      <c r="C791" s="28"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="A792" s="29"/>
-      <c r="B792" s="29"/>
-      <c r="C792" s="29"/>
+      <c r="A792" s="28"/>
+      <c r="B792" s="28"/>
+      <c r="C792" s="28"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="A793" s="29"/>
-      <c r="B793" s="29"/>
-      <c r="C793" s="29"/>
+      <c r="A793" s="28"/>
+      <c r="B793" s="28"/>
+      <c r="C793" s="28"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="A794" s="29"/>
-      <c r="B794" s="29"/>
-      <c r="C794" s="29"/>
+      <c r="A794" s="28"/>
+      <c r="B794" s="28"/>
+      <c r="C794" s="28"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="A795" s="29"/>
-      <c r="B795" s="29"/>
-      <c r="C795" s="29"/>
+      <c r="A795" s="28"/>
+      <c r="B795" s="28"/>
+      <c r="C795" s="28"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="A796" s="29"/>
-      <c r="B796" s="29"/>
-      <c r="C796" s="29"/>
+      <c r="A796" s="28"/>
+      <c r="B796" s="28"/>
+      <c r="C796" s="28"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="A797" s="29"/>
-      <c r="B797" s="29"/>
-      <c r="C797" s="29"/>
+      <c r="A797" s="28"/>
+      <c r="B797" s="28"/>
+      <c r="C797" s="28"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="A798" s="29"/>
-      <c r="B798" s="29"/>
-      <c r="C798" s="29"/>
+      <c r="A798" s="28"/>
+      <c r="B798" s="28"/>
+      <c r="C798" s="28"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="A799" s="29"/>
-      <c r="B799" s="29"/>
-      <c r="C799" s="29"/>
+      <c r="A799" s="28"/>
+      <c r="B799" s="28"/>
+      <c r="C799" s="28"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="A800" s="29"/>
-      <c r="B800" s="29"/>
-      <c r="C800" s="29"/>
+      <c r="A800" s="28"/>
+      <c r="B800" s="28"/>
+      <c r="C800" s="28"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="A801" s="29"/>
-      <c r="B801" s="29"/>
-      <c r="C801" s="29"/>
+      <c r="A801" s="28"/>
+      <c r="B801" s="28"/>
+      <c r="C801" s="28"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="A802" s="29"/>
-      <c r="B802" s="29"/>
-      <c r="C802" s="29"/>
+      <c r="A802" s="28"/>
+      <c r="B802" s="28"/>
+      <c r="C802" s="28"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="A803" s="29"/>
-      <c r="B803" s="29"/>
-      <c r="C803" s="29"/>
+      <c r="A803" s="28"/>
+      <c r="B803" s="28"/>
+      <c r="C803" s="28"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="A804" s="29"/>
-      <c r="B804" s="29"/>
-      <c r="C804" s="29"/>
+      <c r="A804" s="28"/>
+      <c r="B804" s="28"/>
+      <c r="C804" s="28"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="A805" s="29"/>
-      <c r="B805" s="29"/>
-      <c r="C805" s="29"/>
+      <c r="A805" s="28"/>
+      <c r="B805" s="28"/>
+      <c r="C805" s="28"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="A806" s="29"/>
-      <c r="B806" s="29"/>
-      <c r="C806" s="29"/>
+      <c r="A806" s="28"/>
+      <c r="B806" s="28"/>
+      <c r="C806" s="28"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="A807" s="29"/>
-      <c r="B807" s="29"/>
-      <c r="C807" s="29"/>
+      <c r="A807" s="28"/>
+      <c r="B807" s="28"/>
+      <c r="C807" s="28"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="A808" s="29"/>
-      <c r="B808" s="29"/>
-      <c r="C808" s="29"/>
+      <c r="A808" s="28"/>
+      <c r="B808" s="28"/>
+      <c r="C808" s="28"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="A809" s="29"/>
-      <c r="B809" s="29"/>
-      <c r="C809" s="29"/>
+      <c r="A809" s="28"/>
+      <c r="B809" s="28"/>
+      <c r="C809" s="28"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="A810" s="29"/>
-      <c r="B810" s="29"/>
-      <c r="C810" s="29"/>
+      <c r="A810" s="28"/>
+      <c r="B810" s="28"/>
+      <c r="C810" s="28"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="A811" s="29"/>
-      <c r="B811" s="29"/>
-      <c r="C811" s="29"/>
+      <c r="A811" s="28"/>
+      <c r="B811" s="28"/>
+      <c r="C811" s="28"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="A812" s="29"/>
-      <c r="B812" s="29"/>
-      <c r="C812" s="29"/>
+      <c r="A812" s="28"/>
+      <c r="B812" s="28"/>
+      <c r="C812" s="28"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="A813" s="29"/>
-      <c r="B813" s="29"/>
-      <c r="C813" s="29"/>
+      <c r="A813" s="28"/>
+      <c r="B813" s="28"/>
+      <c r="C813" s="28"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="A814" s="29"/>
-      <c r="B814" s="29"/>
-      <c r="C814" s="29"/>
+      <c r="A814" s="28"/>
+      <c r="B814" s="28"/>
+      <c r="C814" s="28"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="A815" s="29"/>
-      <c r="B815" s="29"/>
-      <c r="C815" s="29"/>
+      <c r="A815" s="28"/>
+      <c r="B815" s="28"/>
+      <c r="C815" s="28"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="A816" s="29"/>
-      <c r="B816" s="29"/>
-      <c r="C816" s="29"/>
+      <c r="A816" s="28"/>
+      <c r="B816" s="28"/>
+      <c r="C816" s="28"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="A817" s="29"/>
-      <c r="B817" s="29"/>
-      <c r="C817" s="29"/>
+      <c r="A817" s="28"/>
+      <c r="B817" s="28"/>
+      <c r="C817" s="28"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="A818" s="29"/>
-      <c r="B818" s="29"/>
-      <c r="C818" s="29"/>
+      <c r="A818" s="28"/>
+      <c r="B818" s="28"/>
+      <c r="C818" s="28"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="A819" s="29"/>
-      <c r="B819" s="29"/>
-      <c r="C819" s="29"/>
+      <c r="A819" s="28"/>
+      <c r="B819" s="28"/>
+      <c r="C819" s="28"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="A820" s="29"/>
-      <c r="B820" s="29"/>
-      <c r="C820" s="29"/>
+      <c r="A820" s="28"/>
+      <c r="B820" s="28"/>
+      <c r="C820" s="28"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="A821" s="29"/>
-      <c r="B821" s="29"/>
-      <c r="C821" s="29"/>
+      <c r="A821" s="28"/>
+      <c r="B821" s="28"/>
+      <c r="C821" s="28"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="A822" s="29"/>
-      <c r="B822" s="29"/>
-      <c r="C822" s="29"/>
+      <c r="A822" s="28"/>
+      <c r="B822" s="28"/>
+      <c r="C822" s="28"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="A823" s="29"/>
-      <c r="B823" s="29"/>
-      <c r="C823" s="29"/>
+      <c r="A823" s="28"/>
+      <c r="B823" s="28"/>
+      <c r="C823" s="28"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="A824" s="29"/>
-      <c r="B824" s="29"/>
-      <c r="C824" s="29"/>
+      <c r="A824" s="28"/>
+      <c r="B824" s="28"/>
+      <c r="C824" s="28"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="A825" s="29"/>
-      <c r="B825" s="29"/>
-      <c r="C825" s="29"/>
+      <c r="A825" s="28"/>
+      <c r="B825" s="28"/>
+      <c r="C825" s="28"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="A826" s="29"/>
-      <c r="B826" s="29"/>
-      <c r="C826" s="29"/>
+      <c r="A826" s="28"/>
+      <c r="B826" s="28"/>
+      <c r="C826" s="28"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="A827" s="29"/>
-      <c r="B827" s="29"/>
-      <c r="C827" s="29"/>
+      <c r="A827" s="28"/>
+      <c r="B827" s="28"/>
+      <c r="C827" s="28"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="A828" s="29"/>
-      <c r="B828" s="29"/>
-      <c r="C828" s="29"/>
+      <c r="A828" s="28"/>
+      <c r="B828" s="28"/>
+      <c r="C828" s="28"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="A829" s="29"/>
-      <c r="B829" s="29"/>
-      <c r="C829" s="29"/>
+      <c r="A829" s="28"/>
+      <c r="B829" s="28"/>
+      <c r="C829" s="28"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="A830" s="29"/>
-      <c r="B830" s="29"/>
-      <c r="C830" s="29"/>
+      <c r="A830" s="28"/>
+      <c r="B830" s="28"/>
+      <c r="C830" s="28"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="A831" s="29"/>
-      <c r="B831" s="29"/>
-      <c r="C831" s="29"/>
+      <c r="A831" s="28"/>
+      <c r="B831" s="28"/>
+      <c r="C831" s="28"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="A832" s="29"/>
-      <c r="B832" s="29"/>
-      <c r="C832" s="29"/>
+      <c r="A832" s="28"/>
+      <c r="B832" s="28"/>
+      <c r="C832" s="28"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="A833" s="29"/>
-      <c r="B833" s="29"/>
-      <c r="C833" s="29"/>
+      <c r="A833" s="28"/>
+      <c r="B833" s="28"/>
+      <c r="C833" s="28"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="A834" s="29"/>
-      <c r="B834" s="29"/>
-      <c r="C834" s="29"/>
+      <c r="A834" s="28"/>
+      <c r="B834" s="28"/>
+      <c r="C834" s="28"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="A835" s="29"/>
-      <c r="B835" s="29"/>
-      <c r="C835" s="29"/>
+      <c r="A835" s="28"/>
+      <c r="B835" s="28"/>
+      <c r="C835" s="28"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="A836" s="29"/>
-      <c r="B836" s="29"/>
-      <c r="C836" s="29"/>
+      <c r="A836" s="28"/>
+      <c r="B836" s="28"/>
+      <c r="C836" s="28"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="A837" s="29"/>
-      <c r="B837" s="29"/>
-      <c r="C837" s="29"/>
+      <c r="A837" s="28"/>
+      <c r="B837" s="28"/>
+      <c r="C837" s="28"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="A838" s="29"/>
-      <c r="B838" s="29"/>
-      <c r="C838" s="29"/>
+      <c r="A838" s="28"/>
+      <c r="B838" s="28"/>
+      <c r="C838" s="28"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="A839" s="29"/>
-      <c r="B839" s="29"/>
-      <c r="C839" s="29"/>
+      <c r="A839" s="28"/>
+      <c r="B839" s="28"/>
+      <c r="C839" s="28"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="A840" s="29"/>
-      <c r="B840" s="29"/>
-      <c r="C840" s="29"/>
+      <c r="A840" s="28"/>
+      <c r="B840" s="28"/>
+      <c r="C840" s="28"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="A841" s="29"/>
-      <c r="B841" s="29"/>
-      <c r="C841" s="29"/>
+      <c r="A841" s="28"/>
+      <c r="B841" s="28"/>
+      <c r="C841" s="28"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="A842" s="29"/>
-      <c r="B842" s="29"/>
-      <c r="C842" s="29"/>
+      <c r="A842" s="28"/>
+      <c r="B842" s="28"/>
+      <c r="C842" s="28"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="A843" s="29"/>
-      <c r="B843" s="29"/>
-      <c r="C843" s="29"/>
+      <c r="A843" s="28"/>
+      <c r="B843" s="28"/>
+      <c r="C843" s="28"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="A844" s="29"/>
-      <c r="B844" s="29"/>
-      <c r="C844" s="29"/>
+      <c r="A844" s="28"/>
+      <c r="B844" s="28"/>
+      <c r="C844" s="28"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="A845" s="29"/>
-      <c r="B845" s="29"/>
-      <c r="C845" s="29"/>
+      <c r="A845" s="28"/>
+      <c r="B845" s="28"/>
+      <c r="C845" s="28"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="A846" s="29"/>
-      <c r="B846" s="29"/>
-      <c r="C846" s="29"/>
+      <c r="A846" s="28"/>
+      <c r="B846" s="28"/>
+      <c r="C846" s="28"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="A847" s="29"/>
-      <c r="B847" s="29"/>
-      <c r="C847" s="29"/>
+      <c r="A847" s="28"/>
+      <c r="B847" s="28"/>
+      <c r="C847" s="28"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="A848" s="29"/>
-      <c r="B848" s="29"/>
-      <c r="C848" s="29"/>
+      <c r="A848" s="28"/>
+      <c r="B848" s="28"/>
+      <c r="C848" s="28"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="A849" s="29"/>
-      <c r="B849" s="29"/>
-      <c r="C849" s="29"/>
+      <c r="A849" s="28"/>
+      <c r="B849" s="28"/>
+      <c r="C849" s="28"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="A850" s="29"/>
-      <c r="B850" s="29"/>
-      <c r="C850" s="29"/>
+      <c r="A850" s="28"/>
+      <c r="B850" s="28"/>
+      <c r="C850" s="28"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="A851" s="29"/>
-      <c r="B851" s="29"/>
-      <c r="C851" s="29"/>
+      <c r="A851" s="28"/>
+      <c r="B851" s="28"/>
+      <c r="C851" s="28"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="A852" s="29"/>
-      <c r="B852" s="29"/>
-      <c r="C852" s="29"/>
+      <c r="A852" s="28"/>
+      <c r="B852" s="28"/>
+      <c r="C852" s="28"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="A853" s="29"/>
-      <c r="B853" s="29"/>
-      <c r="C853" s="29"/>
+      <c r="A853" s="28"/>
+      <c r="B853" s="28"/>
+      <c r="C853" s="28"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="A854" s="29"/>
-      <c r="B854" s="29"/>
-      <c r="C854" s="29"/>
+      <c r="A854" s="28"/>
+      <c r="B854" s="28"/>
+      <c r="C854" s="28"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="A855" s="29"/>
-      <c r="B855" s="29"/>
-      <c r="C855" s="29"/>
+      <c r="A855" s="28"/>
+      <c r="B855" s="28"/>
+      <c r="C855" s="28"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="A856" s="29"/>
-      <c r="B856" s="29"/>
-      <c r="C856" s="29"/>
+      <c r="A856" s="28"/>
+      <c r="B856" s="28"/>
+      <c r="C856" s="28"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="A857" s="29"/>
-      <c r="B857" s="29"/>
-      <c r="C857" s="29"/>
+      <c r="A857" s="28"/>
+      <c r="B857" s="28"/>
+      <c r="C857" s="28"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="A858" s="29"/>
-      <c r="B858" s="29"/>
-      <c r="C858" s="29"/>
+      <c r="A858" s="28"/>
+      <c r="B858" s="28"/>
+      <c r="C858" s="28"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="A859" s="29"/>
-      <c r="B859" s="29"/>
-      <c r="C859" s="29"/>
+      <c r="A859" s="28"/>
+      <c r="B859" s="28"/>
+      <c r="C859" s="28"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="A860" s="29"/>
-      <c r="B860" s="29"/>
-      <c r="C860" s="29"/>
+      <c r="A860" s="28"/>
+      <c r="B860" s="28"/>
+      <c r="C860" s="28"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="A861" s="29"/>
-      <c r="B861" s="29"/>
-      <c r="C861" s="29"/>
+      <c r="A861" s="28"/>
+      <c r="B861" s="28"/>
+      <c r="C861" s="28"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="A862" s="29"/>
-      <c r="B862" s="29"/>
-      <c r="C862" s="29"/>
+      <c r="A862" s="28"/>
+      <c r="B862" s="28"/>
+      <c r="C862" s="28"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="A863" s="29"/>
-      <c r="B863" s="29"/>
-      <c r="C863" s="29"/>
+      <c r="A863" s="28"/>
+      <c r="B863" s="28"/>
+      <c r="C863" s="28"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="A864" s="29"/>
-      <c r="B864" s="29"/>
-      <c r="C864" s="29"/>
+      <c r="A864" s="28"/>
+      <c r="B864" s="28"/>
+      <c r="C864" s="28"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="A865" s="29"/>
-      <c r="B865" s="29"/>
-      <c r="C865" s="29"/>
+      <c r="A865" s="28"/>
+      <c r="B865" s="28"/>
+      <c r="C865" s="28"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="A866" s="29"/>
-      <c r="B866" s="29"/>
-      <c r="C866" s="29"/>
+      <c r="A866" s="28"/>
+      <c r="B866" s="28"/>
+      <c r="C866" s="28"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="A867" s="29"/>
-      <c r="B867" s="29"/>
-      <c r="C867" s="29"/>
+      <c r="A867" s="28"/>
+      <c r="B867" s="28"/>
+      <c r="C867" s="28"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="A868" s="29"/>
-      <c r="B868" s="29"/>
-      <c r="C868" s="29"/>
+      <c r="A868" s="28"/>
+      <c r="B868" s="28"/>
+      <c r="C868" s="28"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="A869" s="29"/>
-      <c r="B869" s="29"/>
-      <c r="C869" s="29"/>
+      <c r="A869" s="28"/>
+      <c r="B869" s="28"/>
+      <c r="C869" s="28"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="A870" s="29"/>
-      <c r="B870" s="29"/>
-      <c r="C870" s="29"/>
+      <c r="A870" s="28"/>
+      <c r="B870" s="28"/>
+      <c r="C870" s="28"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="29"/>
-      <c r="B871" s="29"/>
-      <c r="C871" s="29"/>
+      <c r="A871" s="28"/>
+      <c r="B871" s="28"/>
+      <c r="C871" s="28"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="A872" s="29"/>
-      <c r="B872" s="29"/>
-      <c r="C872" s="29"/>
+      <c r="A872" s="28"/>
+      <c r="B872" s="28"/>
+      <c r="C872" s="28"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="A873" s="29"/>
-      <c r="B873" s="29"/>
-      <c r="C873" s="29"/>
+      <c r="A873" s="28"/>
+      <c r="B873" s="28"/>
+      <c r="C873" s="28"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="A874" s="29"/>
-      <c r="B874" s="29"/>
-      <c r="C874" s="29"/>
+      <c r="A874" s="28"/>
+      <c r="B874" s="28"/>
+      <c r="C874" s="28"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="A875" s="29"/>
-      <c r="B875" s="29"/>
-      <c r="C875" s="29"/>
+      <c r="A875" s="28"/>
+      <c r="B875" s="28"/>
+      <c r="C875" s="28"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="29"/>
-      <c r="B876" s="29"/>
-      <c r="C876" s="29"/>
+      <c r="A876" s="28"/>
+      <c r="B876" s="28"/>
+      <c r="C876" s="28"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="A877" s="29"/>
-      <c r="B877" s="29"/>
-      <c r="C877" s="29"/>
+      <c r="A877" s="28"/>
+      <c r="B877" s="28"/>
+      <c r="C877" s="28"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="A878" s="29"/>
-      <c r="B878" s="29"/>
-      <c r="C878" s="29"/>
+      <c r="A878" s="28"/>
+      <c r="B878" s="28"/>
+      <c r="C878" s="28"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="A879" s="29"/>
-      <c r="B879" s="29"/>
-      <c r="C879" s="29"/>
+      <c r="A879" s="28"/>
+      <c r="B879" s="28"/>
+      <c r="C879" s="28"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="A880" s="29"/>
-      <c r="B880" s="29"/>
-      <c r="C880" s="29"/>
+      <c r="A880" s="28"/>
+      <c r="B880" s="28"/>
+      <c r="C880" s="28"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="A881" s="29"/>
-      <c r="B881" s="29"/>
-      <c r="C881" s="29"/>
+      <c r="A881" s="28"/>
+      <c r="B881" s="28"/>
+      <c r="C881" s="28"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="A882" s="29"/>
-      <c r="B882" s="29"/>
-      <c r="C882" s="29"/>
+      <c r="A882" s="28"/>
+      <c r="B882" s="28"/>
+      <c r="C882" s="28"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="A883" s="29"/>
-      <c r="B883" s="29"/>
-      <c r="C883" s="29"/>
+      <c r="A883" s="28"/>
+      <c r="B883" s="28"/>
+      <c r="C883" s="28"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="A884" s="29"/>
-      <c r="B884" s="29"/>
-      <c r="C884" s="29"/>
+      <c r="A884" s="28"/>
+      <c r="B884" s="28"/>
+      <c r="C884" s="28"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="A885" s="29"/>
-      <c r="B885" s="29"/>
-      <c r="C885" s="29"/>
+      <c r="A885" s="28"/>
+      <c r="B885" s="28"/>
+      <c r="C885" s="28"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="A886" s="29"/>
-      <c r="B886" s="29"/>
-      <c r="C886" s="29"/>
+      <c r="A886" s="28"/>
+      <c r="B886" s="28"/>
+      <c r="C886" s="28"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="A887" s="29"/>
-      <c r="B887" s="29"/>
-      <c r="C887" s="29"/>
+      <c r="A887" s="28"/>
+      <c r="B887" s="28"/>
+      <c r="C887" s="28"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="A888" s="29"/>
-      <c r="B888" s="29"/>
-      <c r="C888" s="29"/>
+      <c r="A888" s="28"/>
+      <c r="B888" s="28"/>
+      <c r="C888" s="28"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="A889" s="29"/>
-      <c r="B889" s="29"/>
-      <c r="C889" s="29"/>
+      <c r="A889" s="28"/>
+      <c r="B889" s="28"/>
+      <c r="C889" s="28"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="A890" s="29"/>
-      <c r="B890" s="29"/>
-      <c r="C890" s="29"/>
+      <c r="A890" s="28"/>
+      <c r="B890" s="28"/>
+      <c r="C890" s="28"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="A891" s="29"/>
-      <c r="B891" s="29"/>
-      <c r="C891" s="29"/>
+      <c r="A891" s="28"/>
+      <c r="B891" s="28"/>
+      <c r="C891" s="28"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="A892" s="29"/>
-      <c r="B892" s="29"/>
-      <c r="C892" s="29"/>
+      <c r="A892" s="28"/>
+      <c r="B892" s="28"/>
+      <c r="C892" s="28"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="A893" s="29"/>
-      <c r="B893" s="29"/>
-      <c r="C893" s="29"/>
+      <c r="A893" s="28"/>
+      <c r="B893" s="28"/>
+      <c r="C893" s="28"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="A894" s="29"/>
-      <c r="B894" s="29"/>
-      <c r="C894" s="29"/>
+      <c r="A894" s="28"/>
+      <c r="B894" s="28"/>
+      <c r="C894" s="28"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="A895" s="29"/>
-      <c r="B895" s="29"/>
-      <c r="C895" s="29"/>
+      <c r="A895" s="28"/>
+      <c r="B895" s="28"/>
+      <c r="C895" s="28"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="A896" s="29"/>
-      <c r="B896" s="29"/>
-      <c r="C896" s="29"/>
+      <c r="A896" s="28"/>
+      <c r="B896" s="28"/>
+      <c r="C896" s="28"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="A897" s="29"/>
-      <c r="B897" s="29"/>
-      <c r="C897" s="29"/>
+      <c r="A897" s="28"/>
+      <c r="B897" s="28"/>
+      <c r="C897" s="28"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="A898" s="29"/>
-      <c r="B898" s="29"/>
-      <c r="C898" s="29"/>
+      <c r="A898" s="28"/>
+      <c r="B898" s="28"/>
+      <c r="C898" s="28"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="A899" s="29"/>
-      <c r="B899" s="29"/>
-      <c r="C899" s="29"/>
+      <c r="A899" s="28"/>
+      <c r="B899" s="28"/>
+      <c r="C899" s="28"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="A900" s="29"/>
-      <c r="B900" s="29"/>
-      <c r="C900" s="29"/>
+      <c r="A900" s="28"/>
+      <c r="B900" s="28"/>
+      <c r="C900" s="28"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="A901" s="29"/>
-      <c r="B901" s="29"/>
-      <c r="C901" s="29"/>
+      <c r="A901" s="28"/>
+      <c r="B901" s="28"/>
+      <c r="C901" s="28"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="A902" s="29"/>
-      <c r="B902" s="29"/>
-      <c r="C902" s="29"/>
+      <c r="A902" s="28"/>
+      <c r="B902" s="28"/>
+      <c r="C902" s="28"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="A903" s="29"/>
-      <c r="B903" s="29"/>
-      <c r="C903" s="29"/>
+      <c r="A903" s="28"/>
+      <c r="B903" s="28"/>
+      <c r="C903" s="28"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="A904" s="29"/>
-      <c r="B904" s="29"/>
-      <c r="C904" s="29"/>
+      <c r="A904" s="28"/>
+      <c r="B904" s="28"/>
+      <c r="C904" s="28"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="A905" s="29"/>
-      <c r="B905" s="29"/>
-      <c r="C905" s="29"/>
+      <c r="A905" s="28"/>
+      <c r="B905" s="28"/>
+      <c r="C905" s="28"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="A906" s="29"/>
-      <c r="B906" s="29"/>
-      <c r="C906" s="29"/>
+      <c r="A906" s="28"/>
+      <c r="B906" s="28"/>
+      <c r="C906" s="28"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="A907" s="29"/>
-      <c r="B907" s="29"/>
-      <c r="C907" s="29"/>
+      <c r="A907" s="28"/>
+      <c r="B907" s="28"/>
+      <c r="C907" s="28"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="A908" s="29"/>
-      <c r="B908" s="29"/>
-      <c r="C908" s="29"/>
+      <c r="A908" s="28"/>
+      <c r="B908" s="28"/>
+      <c r="C908" s="28"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="A909" s="29"/>
-      <c r="B909" s="29"/>
-      <c r="C909" s="29"/>
+      <c r="A909" s="28"/>
+      <c r="B909" s="28"/>
+      <c r="C909" s="28"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="A910" s="29"/>
-      <c r="B910" s="29"/>
-      <c r="C910" s="29"/>
+      <c r="A910" s="28"/>
+      <c r="B910" s="28"/>
+      <c r="C910" s="28"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="A911" s="29"/>
-      <c r="B911" s="29"/>
-      <c r="C911" s="29"/>
+      <c r="A911" s="28"/>
+      <c r="B911" s="28"/>
+      <c r="C911" s="28"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="A912" s="29"/>
-      <c r="B912" s="29"/>
-      <c r="C912" s="29"/>
+      <c r="A912" s="28"/>
+      <c r="B912" s="28"/>
+      <c r="C912" s="28"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="A913" s="29"/>
-      <c r="B913" s="29"/>
-      <c r="C913" s="29"/>
+      <c r="A913" s="28"/>
+      <c r="B913" s="28"/>
+      <c r="C913" s="28"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="A914" s="29"/>
-      <c r="B914" s="29"/>
-      <c r="C914" s="29"/>
+      <c r="A914" s="28"/>
+      <c r="B914" s="28"/>
+      <c r="C914" s="28"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="A915" s="29"/>
-      <c r="B915" s="29"/>
-      <c r="C915" s="29"/>
+      <c r="A915" s="28"/>
+      <c r="B915" s="28"/>
+      <c r="C915" s="28"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="A916" s="29"/>
-      <c r="B916" s="29"/>
-      <c r="C916" s="29"/>
+      <c r="A916" s="28"/>
+      <c r="B916" s="28"/>
+      <c r="C916" s="28"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="A917" s="29"/>
-      <c r="B917" s="29"/>
-      <c r="C917" s="29"/>
+      <c r="A917" s="28"/>
+      <c r="B917" s="28"/>
+      <c r="C917" s="28"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="A918" s="29"/>
-      <c r="B918" s="29"/>
-      <c r="C918" s="29"/>
+      <c r="A918" s="28"/>
+      <c r="B918" s="28"/>
+      <c r="C918" s="28"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="A919" s="29"/>
-      <c r="B919" s="29"/>
-      <c r="C919" s="29"/>
+      <c r="A919" s="28"/>
+      <c r="B919" s="28"/>
+      <c r="C919" s="28"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="A920" s="29"/>
-      <c r="B920" s="29"/>
-      <c r="C920" s="29"/>
+      <c r="A920" s="28"/>
+      <c r="B920" s="28"/>
+      <c r="C920" s="28"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="A921" s="29"/>
-      <c r="B921" s="29"/>
-      <c r="C921" s="29"/>
+      <c r="A921" s="28"/>
+      <c r="B921" s="28"/>
+      <c r="C921" s="28"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="A922" s="29"/>
-      <c r="B922" s="29"/>
-      <c r="C922" s="29"/>
+      <c r="A922" s="28"/>
+      <c r="B922" s="28"/>
+      <c r="C922" s="28"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="A923" s="29"/>
-      <c r="B923" s="29"/>
-      <c r="C923" s="29"/>
+      <c r="A923" s="28"/>
+      <c r="B923" s="28"/>
+      <c r="C923" s="28"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="A924" s="29"/>
-      <c r="B924" s="29"/>
-      <c r="C924" s="29"/>
+      <c r="A924" s="28"/>
+      <c r="B924" s="28"/>
+      <c r="C924" s="28"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="A925" s="29"/>
-      <c r="B925" s="29"/>
-      <c r="C925" s="29"/>
+      <c r="A925" s="28"/>
+      <c r="B925" s="28"/>
+      <c r="C925" s="28"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="A926" s="29"/>
-      <c r="B926" s="29"/>
-      <c r="C926" s="29"/>
+      <c r="A926" s="28"/>
+      <c r="B926" s="28"/>
+      <c r="C926" s="28"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="A927" s="29"/>
-      <c r="B927" s="29"/>
-      <c r="C927" s="29"/>
+      <c r="A927" s="28"/>
+      <c r="B927" s="28"/>
+      <c r="C927" s="28"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="A928" s="29"/>
-      <c r="B928" s="29"/>
-      <c r="C928" s="29"/>
+      <c r="A928" s="28"/>
+      <c r="B928" s="28"/>
+      <c r="C928" s="28"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="A929" s="29"/>
-      <c r="B929" s="29"/>
-      <c r="C929" s="29"/>
+      <c r="A929" s="28"/>
+      <c r="B929" s="28"/>
+      <c r="C929" s="28"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="A930" s="29"/>
-      <c r="B930" s="29"/>
-      <c r="C930" s="29"/>
+      <c r="A930" s="28"/>
+      <c r="B930" s="28"/>
+      <c r="C930" s="28"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="A931" s="29"/>
-      <c r="B931" s="29"/>
-      <c r="C931" s="29"/>
+      <c r="A931" s="28"/>
+      <c r="B931" s="28"/>
+      <c r="C931" s="28"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="A932" s="29"/>
-      <c r="B932" s="29"/>
-      <c r="C932" s="29"/>
+      <c r="A932" s="28"/>
+      <c r="B932" s="28"/>
+      <c r="C932" s="28"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="A933" s="29"/>
-      <c r="B933" s="29"/>
-      <c r="C933" s="29"/>
+      <c r="A933" s="28"/>
+      <c r="B933" s="28"/>
+      <c r="C933" s="28"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="A934" s="29"/>
-      <c r="B934" s="29"/>
-      <c r="C934" s="29"/>
+      <c r="A934" s="28"/>
+      <c r="B934" s="28"/>
+      <c r="C934" s="28"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="A935" s="29"/>
-      <c r="B935" s="29"/>
-      <c r="C935" s="29"/>
+      <c r="A935" s="28"/>
+      <c r="B935" s="28"/>
+      <c r="C935" s="28"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="A936" s="29"/>
-      <c r="B936" s="29"/>
-      <c r="C936" s="29"/>
+      <c r="A936" s="28"/>
+      <c r="B936" s="28"/>
+      <c r="C936" s="28"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="A937" s="29"/>
-      <c r="B937" s="29"/>
-      <c r="C937" s="29"/>
+      <c r="A937" s="28"/>
+      <c r="B937" s="28"/>
+      <c r="C937" s="28"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="A938" s="29"/>
-      <c r="B938" s="29"/>
-      <c r="C938" s="29"/>
+      <c r="A938" s="28"/>
+      <c r="B938" s="28"/>
+      <c r="C938" s="28"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="A939" s="29"/>
-      <c r="B939" s="29"/>
-      <c r="C939" s="29"/>
+      <c r="A939" s="28"/>
+      <c r="B939" s="28"/>
+      <c r="C939" s="28"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="A940" s="29"/>
-      <c r="B940" s="29"/>
-      <c r="C940" s="29"/>
+      <c r="A940" s="28"/>
+      <c r="B940" s="28"/>
+      <c r="C940" s="28"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="A941" s="29"/>
-      <c r="B941" s="29"/>
-      <c r="C941" s="29"/>
+      <c r="A941" s="28"/>
+      <c r="B941" s="28"/>
+      <c r="C941" s="28"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="A942" s="29"/>
-      <c r="B942" s="29"/>
-      <c r="C942" s="29"/>
+      <c r="A942" s="28"/>
+      <c r="B942" s="28"/>
+      <c r="C942" s="28"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="A943" s="29"/>
-      <c r="B943" s="29"/>
-      <c r="C943" s="29"/>
+      <c r="A943" s="28"/>
+      <c r="B943" s="28"/>
+      <c r="C943" s="28"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="A944" s="29"/>
-      <c r="B944" s="29"/>
-      <c r="C944" s="29"/>
+      <c r="A944" s="28"/>
+      <c r="B944" s="28"/>
+      <c r="C944" s="28"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="A945" s="29"/>
-      <c r="B945" s="29"/>
-      <c r="C945" s="29"/>
+      <c r="A945" s="28"/>
+      <c r="B945" s="28"/>
+      <c r="C945" s="28"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="A946" s="29"/>
-      <c r="B946" s="29"/>
-      <c r="C946" s="29"/>
+      <c r="A946" s="28"/>
+      <c r="B946" s="28"/>
+      <c r="C946" s="28"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="A947" s="29"/>
-      <c r="B947" s="29"/>
-      <c r="C947" s="29"/>
+      <c r="A947" s="28"/>
+      <c r="B947" s="28"/>
+      <c r="C947" s="28"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="A948" s="29"/>
-      <c r="B948" s="29"/>
-      <c r="C948" s="29"/>
+      <c r="A948" s="28"/>
+      <c r="B948" s="28"/>
+      <c r="C948" s="28"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="A949" s="29"/>
-      <c r="B949" s="29"/>
-      <c r="C949" s="29"/>
+      <c r="A949" s="28"/>
+      <c r="B949" s="28"/>
+      <c r="C949" s="28"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="A950" s="29"/>
-      <c r="B950" s="29"/>
-      <c r="C950" s="29"/>
+      <c r="A950" s="28"/>
+      <c r="B950" s="28"/>
+      <c r="C950" s="28"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="A951" s="29"/>
-      <c r="B951" s="29"/>
-      <c r="C951" s="29"/>
+      <c r="A951" s="28"/>
+      <c r="B951" s="28"/>
+      <c r="C951" s="28"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="A952" s="29"/>
-      <c r="B952" s="29"/>
-      <c r="C952" s="29"/>
+      <c r="A952" s="28"/>
+      <c r="B952" s="28"/>
+      <c r="C952" s="28"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="A953" s="29"/>
-      <c r="B953" s="29"/>
-      <c r="C953" s="29"/>
+      <c r="A953" s="28"/>
+      <c r="B953" s="28"/>
+      <c r="C953" s="28"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="A954" s="29"/>
-      <c r="B954" s="29"/>
-      <c r="C954" s="29"/>
+      <c r="A954" s="28"/>
+      <c r="B954" s="28"/>
+      <c r="C954" s="28"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="A955" s="29"/>
-      <c r="B955" s="29"/>
-      <c r="C955" s="29"/>
+      <c r="A955" s="28"/>
+      <c r="B955" s="28"/>
+      <c r="C955" s="28"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="A956" s="29"/>
-      <c r="B956" s="29"/>
-      <c r="C956" s="29"/>
+      <c r="A956" s="28"/>
+      <c r="B956" s="28"/>
+      <c r="C956" s="28"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="A957" s="29"/>
-      <c r="B957" s="29"/>
-      <c r="C957" s="29"/>
+      <c r="A957" s="28"/>
+      <c r="B957" s="28"/>
+      <c r="C957" s="28"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="A958" s="29"/>
-      <c r="B958" s="29"/>
-      <c r="C958" s="29"/>
+      <c r="A958" s="28"/>
+      <c r="B958" s="28"/>
+      <c r="C958" s="28"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="A959" s="29"/>
-      <c r="B959" s="29"/>
-      <c r="C959" s="29"/>
+      <c r="A959" s="28"/>
+      <c r="B959" s="28"/>
+      <c r="C959" s="28"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="A960" s="29"/>
-      <c r="B960" s="29"/>
-      <c r="C960" s="29"/>
+      <c r="A960" s="28"/>
+      <c r="B960" s="28"/>
+      <c r="C960" s="28"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="A961" s="29"/>
-      <c r="B961" s="29"/>
-      <c r="C961" s="29"/>
+      <c r="A961" s="28"/>
+      <c r="B961" s="28"/>
+      <c r="C961" s="28"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="A962" s="29"/>
-      <c r="B962" s="29"/>
-      <c r="C962" s="29"/>
+      <c r="A962" s="28"/>
+      <c r="B962" s="28"/>
+      <c r="C962" s="28"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="A963" s="29"/>
-      <c r="B963" s="29"/>
-      <c r="C963" s="29"/>
+      <c r="A963" s="28"/>
+      <c r="B963" s="28"/>
+      <c r="C963" s="28"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="A964" s="29"/>
-      <c r="B964" s="29"/>
-      <c r="C964" s="29"/>
+      <c r="A964" s="28"/>
+      <c r="B964" s="28"/>
+      <c r="C964" s="28"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="A965" s="29"/>
-      <c r="B965" s="29"/>
-      <c r="C965" s="29"/>
+      <c r="A965" s="28"/>
+      <c r="B965" s="28"/>
+      <c r="C965" s="28"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="A966" s="29"/>
-      <c r="B966" s="29"/>
-      <c r="C966" s="29"/>
+      <c r="A966" s="28"/>
+      <c r="B966" s="28"/>
+      <c r="C966" s="28"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="A967" s="29"/>
-      <c r="B967" s="29"/>
-      <c r="C967" s="29"/>
+      <c r="A967" s="28"/>
+      <c r="B967" s="28"/>
+      <c r="C967" s="28"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="A968" s="29"/>
-      <c r="B968" s="29"/>
-      <c r="C968" s="29"/>
+      <c r="A968" s="28"/>
+      <c r="B968" s="28"/>
+      <c r="C968" s="28"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="A969" s="29"/>
-      <c r="B969" s="29"/>
-      <c r="C969" s="29"/>
+      <c r="A969" s="28"/>
+      <c r="B969" s="28"/>
+      <c r="C969" s="28"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="A970" s="29"/>
-      <c r="B970" s="29"/>
-      <c r="C970" s="29"/>
+      <c r="A970" s="28"/>
+      <c r="B970" s="28"/>
+      <c r="C970" s="28"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="A971" s="29"/>
-      <c r="B971" s="29"/>
-      <c r="C971" s="29"/>
+      <c r="A971" s="28"/>
+      <c r="B971" s="28"/>
+      <c r="C971" s="28"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="A972" s="29"/>
-      <c r="B972" s="29"/>
-      <c r="C972" s="29"/>
+      <c r="A972" s="28"/>
+      <c r="B972" s="28"/>
+      <c r="C972" s="28"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="A973" s="29"/>
-      <c r="B973" s="29"/>
-      <c r="C973" s="29"/>
+      <c r="A973" s="28"/>
+      <c r="B973" s="28"/>
+      <c r="C973" s="28"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="A974" s="29"/>
-      <c r="B974" s="29"/>
-      <c r="C974" s="29"/>
+      <c r="A974" s="28"/>
+      <c r="B974" s="28"/>
+      <c r="C974" s="28"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="A975" s="29"/>
-      <c r="B975" s="29"/>
-      <c r="C975" s="29"/>
+      <c r="A975" s="28"/>
+      <c r="B975" s="28"/>
+      <c r="C975" s="28"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="A976" s="29"/>
-      <c r="B976" s="29"/>
-      <c r="C976" s="29"/>
+      <c r="A976" s="28"/>
+      <c r="B976" s="28"/>
+      <c r="C976" s="28"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="A977" s="29"/>
-      <c r="B977" s="29"/>
-      <c r="C977" s="29"/>
+      <c r="A977" s="28"/>
+      <c r="B977" s="28"/>
+      <c r="C977" s="28"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="A978" s="29"/>
-      <c r="B978" s="29"/>
-      <c r="C978" s="29"/>
+      <c r="A978" s="28"/>
+      <c r="B978" s="28"/>
+      <c r="C978" s="28"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="A979" s="29"/>
-      <c r="B979" s="29"/>
-      <c r="C979" s="29"/>
+      <c r="A979" s="28"/>
+      <c r="B979" s="28"/>
+      <c r="C979" s="28"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="A980" s="29"/>
-      <c r="B980" s="29"/>
-      <c r="C980" s="29"/>
+      <c r="A980" s="28"/>
+      <c r="B980" s="28"/>
+      <c r="C980" s="28"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="A981" s="29"/>
-      <c r="B981" s="29"/>
-      <c r="C981" s="29"/>
+      <c r="A981" s="28"/>
+      <c r="B981" s="28"/>
+      <c r="C981" s="28"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="A982" s="29"/>
-      <c r="B982" s="29"/>
-      <c r="C982" s="29"/>
+      <c r="A982" s="28"/>
+      <c r="B982" s="28"/>
+      <c r="C982" s="28"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="A983" s="29"/>
-      <c r="B983" s="29"/>
-      <c r="C983" s="29"/>
+      <c r="A983" s="28"/>
+      <c r="B983" s="28"/>
+      <c r="C983" s="28"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="A984" s="29"/>
-      <c r="B984" s="29"/>
-      <c r="C984" s="29"/>
+      <c r="A984" s="28"/>
+      <c r="B984" s="28"/>
+      <c r="C984" s="28"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="A985" s="29"/>
-      <c r="B985" s="29"/>
-      <c r="C985" s="29"/>
+      <c r="A985" s="28"/>
+      <c r="B985" s="28"/>
+      <c r="C985" s="28"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="A986" s="29"/>
-      <c r="B986" s="29"/>
-      <c r="C986" s="29"/>
+      <c r="A986" s="28"/>
+      <c r="B986" s="28"/>
+      <c r="C986" s="28"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="A987" s="29"/>
-      <c r="B987" s="29"/>
-      <c r="C987" s="29"/>
+      <c r="A987" s="28"/>
+      <c r="B987" s="28"/>
+      <c r="C987" s="28"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="A988" s="29"/>
-      <c r="B988" s="29"/>
-      <c r="C988" s="29"/>
+      <c r="A988" s="28"/>
+      <c r="B988" s="28"/>
+      <c r="C988" s="28"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="A989" s="29"/>
-      <c r="B989" s="29"/>
-      <c r="C989" s="29"/>
+      <c r="A989" s="28"/>
+      <c r="B989" s="28"/>
+      <c r="C989" s="28"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="A990" s="29"/>
-      <c r="B990" s="29"/>
-      <c r="C990" s="29"/>
+      <c r="A990" s="28"/>
+      <c r="B990" s="28"/>
+      <c r="C990" s="28"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="A991" s="29"/>
-      <c r="B991" s="29"/>
-      <c r="C991" s="29"/>
+      <c r="A991" s="28"/>
+      <c r="B991" s="28"/>
+      <c r="C991" s="28"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="A992" s="29"/>
-      <c r="B992" s="29"/>
-      <c r="C992" s="29"/>
+      <c r="A992" s="28"/>
+      <c r="B992" s="28"/>
+      <c r="C992" s="28"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="A993" s="29"/>
-      <c r="B993" s="29"/>
-      <c r="C993" s="29"/>
+      <c r="A993" s="28"/>
+      <c r="B993" s="28"/>
+      <c r="C993" s="28"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="A994" s="29"/>
-      <c r="B994" s="29"/>
-      <c r="C994" s="29"/>
+      <c r="A994" s="28"/>
+      <c r="B994" s="28"/>
+      <c r="C994" s="28"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="A995" s="29"/>
-      <c r="B995" s="29"/>
-      <c r="C995" s="29"/>
+      <c r="A995" s="28"/>
+      <c r="B995" s="28"/>
+      <c r="C995" s="28"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="29"/>
-      <c r="B996" s="29"/>
-      <c r="C996" s="29"/>
+      <c r="A996" s="28"/>
+      <c r="B996" s="28"/>
+      <c r="C996" s="28"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="29"/>
-      <c r="B997" s="29"/>
-      <c r="C997" s="29"/>
+      <c r="A997" s="28"/>
+      <c r="B997" s="28"/>
+      <c r="C997" s="28"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="29"/>
-      <c r="B998" s="29"/>
-      <c r="C998" s="29"/>
+      <c r="A998" s="28"/>
+      <c r="B998" s="28"/>
+      <c r="C998" s="28"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="29"/>
-      <c r="B999" s="29"/>
-      <c r="C999" s="29"/>
+      <c r="A999" s="28"/>
+      <c r="B999" s="28"/>
+      <c r="C999" s="28"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="29"/>
-      <c r="B1000" s="29"/>
-      <c r="C1000" s="29"/>
+      <c r="A1000" s="28"/>
+      <c r="B1000" s="28"/>
+      <c r="C1000" s="28"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="A1001" s="29"/>
-      <c r="B1001" s="29"/>
-      <c r="C1001" s="29"/>
+      <c r="A1001" s="28"/>
+      <c r="B1001" s="28"/>
+      <c r="C1001" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6897,84 +6889,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="B1" s="30" t="s">
-        <v>103</v>
+      <c r="B1" s="29" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="30" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="B4" s="30" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="31" t="s">
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="B5" s="30" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="31" t="s">
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="B6" s="30" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="31" t="s">
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="B7" s="30" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="31" t="s">
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="B8" s="30" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="31" t="s">
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="B9" s="30" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="31" t="s">
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="B10" s="30" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="31" t="s">
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="B11" s="30" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="31" t="s">
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="B12" s="30" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="31" t="s">
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="B13" s="30" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="31" t="s">
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="B14" s="30" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="31" t="s">
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="B15" s="30" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="31" t="s">
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="B16" s="30" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="31" t="s">
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="B17" s="30" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="31" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7987,237 +7979,237 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="31"/>
+      <c r="C2" s="31"/>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="28"/>
+      <c r="B3" s="32" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="32"/>
-      <c r="C2" s="32"/>
-    </row>
-    <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="29"/>
-      <c r="B3" s="33" t="s">
+      <c r="C3" s="28"/>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="28"/>
+      <c r="B4" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="29"/>
-    </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="29"/>
-      <c r="B4" s="34" t="s">
+      <c r="C4" s="28"/>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="34" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="29"/>
-    </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="35" t="s">
+      <c r="B5" s="34"/>
+      <c r="C5" s="34"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="28"/>
+      <c r="B6" s="28"/>
+      <c r="C6" s="28"/>
+    </row>
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="A7" s="35" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-    </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-    </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="36" t="s">
+      <c r="B7" s="36" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="37" t="s">
+      <c r="C7" s="36" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="37" t="s">
+      <c r="D7" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="36" t="s">
+      <c r="E7" s="35" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="36" t="s">
+      <c r="G7" s="35" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="36" t="s">
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="37">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="38" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="38">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="39" t="s">
+      <c r="C8" s="38" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="39" t="s">
+      <c r="D8" s="39" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="40" t="s">
+      <c r="E8" s="40" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="41" t="s">
+      <c r="F8" s="41"/>
+      <c r="G8" s="42"/>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="43">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="44" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="42"/>
-      <c r="G8" s="43"/>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="44">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="45" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="45" t="s">
+      <c r="D9" s="45" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="46" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="47" t="s">
+      <c r="F9" s="47"/>
+      <c r="G9" s="42"/>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="48">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="49" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="48"/>
-      <c r="G9" s="43"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="49">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="50" t="s">
+      <c r="C10" s="49" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="50" t="s">
+      <c r="D10" s="50" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="51" t="s">
+      <c r="E10" s="51" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="52" t="s">
+      <c r="F10" s="52"/>
+      <c r="G10" s="53"/>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="37"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="38"/>
+      <c r="D11" s="39" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54"/>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="38"/>
-      <c r="B11" s="39"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="40" t="s">
+      <c r="E11" s="40" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="41" t="s">
+      <c r="F11" s="54"/>
+      <c r="G11" s="55"/>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="56">
+        <v>4.0</v>
+      </c>
+      <c r="B12" s="57" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="55"/>
-      <c r="G11" s="56"/>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="57">
-        <v>4.0</v>
-      </c>
-      <c r="B12" s="58" t="s">
+      <c r="C12" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="58" t="s">
+      <c r="D12" s="58" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="59" t="s">
+      <c r="E12" s="59" t="s">
         <v>143</v>
       </c>
-      <c r="E12" s="60" t="s">
+      <c r="F12" s="60"/>
+      <c r="G12" s="61"/>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="37"/>
+      <c r="B13" s="38"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="39" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="61"/>
-      <c r="G12" s="62"/>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="38"/>
-      <c r="B13" s="39"/>
-      <c r="C13" s="39"/>
-      <c r="D13" s="40" t="s">
+      <c r="E13" s="40" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="41" t="s">
+      <c r="F13" s="41"/>
+      <c r="G13" s="55"/>
+    </row>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="A14" s="56">
+        <v>5.0</v>
+      </c>
+      <c r="B14" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="57" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="42"/>
-      <c r="G13" s="56"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="57">
-        <v>5.0</v>
-      </c>
-      <c r="B14" s="58" t="s">
+      <c r="D14" s="58" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="59" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="60"/>
+      <c r="G14" s="61"/>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="37"/>
+      <c r="B15" s="38"/>
+      <c r="C15" s="38"/>
+      <c r="D15" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="40" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="62" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="55"/>
+    </row>
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="A16" s="56">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="57" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="57" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="58" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="59" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="60" t="s">
+      <c r="D16" s="58" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="59" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="63"/>
+      <c r="G16" s="61"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="A17" s="37"/>
+      <c r="B17" s="38"/>
+      <c r="C17" s="38"/>
+      <c r="D17" s="39" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="F14" s="61"/>
-      <c r="G14" s="62"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="38"/>
-      <c r="B15" s="39"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="63" t="s">
-        <v>151</v>
-      </c>
-      <c r="G15" s="56"/>
-    </row>
-    <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="57">
-        <v>6.0</v>
-      </c>
-      <c r="B16" s="58" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="58" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="59" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" s="60" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="64"/>
-      <c r="G16" s="62"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="38"/>
-      <c r="B17" s="39"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="40" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" s="65"/>
-      <c r="G17" s="56"/>
+      <c r="F17" s="64"/>
+      <c r="G17" s="55"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="49"/>
-      <c r="B18" s="49"/>
-      <c r="C18" s="49"/>
-      <c r="D18" s="66"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="66"/>
-      <c r="G18" s="66"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="48"/>
+      <c r="C18" s="48"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="49"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
     </row>
     <row r="19" ht="12.75" customHeight="1"/>
     <row r="20" ht="12.75" customHeight="1"/>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -120,6 +120,9 @@
   </si>
   <si>
     <t>Error message shows saying date selected must be current or in the future</t>
+  </si>
+  <si>
+    <t>The room filter still shows the available rooms without the pop up of an error</t>
   </si>
   <si>
     <t>User logged in and IMS connected</t>
@@ -528,7 +531,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -566,6 +569,11 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FF00FF00"/>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
     <font>
@@ -767,7 +775,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -840,15 +848,21 @@
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="3" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="left"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
@@ -856,7 +870,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyBorder="1" applyFont="1"/>
     <xf borderId="5" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
@@ -1345,7 +1359,7 @@
       <c r="E6" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="F6" s="22"/>
+      <c r="F6" s="23"/>
       <c r="G6" s="22"/>
       <c r="H6" s="21"/>
       <c r="I6" s="22"/>
@@ -1367,9 +1381,11 @@
       <c r="E7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="H7" s="27"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -1381,13 +1397,13 @@
         <v>26</v>
       </c>
       <c r="C8" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D8" s="20" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E8" s="20" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
@@ -1400,16 +1416,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C9" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D9" s="20" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="E9" s="20" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
@@ -1422,16 +1438,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D10" s="20" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E10" s="20" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
@@ -1444,16 +1460,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C11" s="20" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D11" s="20" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E11" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
@@ -1466,16 +1482,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C12" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D12" s="20" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
@@ -1485,16 +1501,16 @@
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="20" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D13" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E13" s="20" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
@@ -1507,16 +1523,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="20" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C14" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D14" s="20" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E14" s="20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
@@ -1529,16 +1545,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C15" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D15" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E15" s="20" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
@@ -1551,16 +1567,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C16" s="20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E16" s="20" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
@@ -1573,16 +1589,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="20" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C17" s="20" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="E17" s="20" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
@@ -1595,16 +1611,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="20" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C18" s="20" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D18" s="20" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="E18" s="20" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="22"/>
@@ -1617,16 +1633,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C19" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D19" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E19" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
@@ -1639,16 +1655,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C20" s="20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D20" s="20" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="E20" s="20" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
@@ -1661,16 +1677,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="20" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C21" s="20" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="D21" s="20" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E21" s="20" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -1683,16 +1699,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="20" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="D22" s="20" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="E22" s="20" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -1705,16 +1721,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C23" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D23" s="20" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E23" s="20" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -1727,16 +1743,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D24" s="20" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="E24" s="20" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -1749,16 +1765,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="20" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E25" s="20" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -1770,17 +1786,17 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="26" t="s">
-        <v>88</v>
+      <c r="B26" s="28" t="s">
+        <v>89</v>
       </c>
       <c r="C26" s="20" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="D26" s="20" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="E26" s="20" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -1793,16 +1809,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="20" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E27" s="20" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
@@ -1815,16 +1831,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="20" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="E28" s="20" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
@@ -1851,7 +1867,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="22"/>
-      <c r="C30" s="27"/>
+      <c r="C30" s="29"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -1865,7 +1881,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="22"/>
-      <c r="C31" s="27"/>
+      <c r="C31" s="29"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -1902,31 +1918,31 @@
       <c r="I33" s="22"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
+      <c r="A34" s="30"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="30"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
+      <c r="A35" s="30"/>
+      <c r="B35" s="30"/>
+      <c r="C35" s="30"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
+      <c r="A36" s="30"/>
+      <c r="B36" s="30"/>
+      <c r="C36" s="30"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
+      <c r="A37" s="30"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
+      <c r="A38" s="30"/>
+      <c r="B38" s="30"/>
+      <c r="C38" s="30"/>
       <c r="K38" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -1934,11 +1950,11 @@
       <c r="T38" s="4"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
+      <c r="A39" s="30"/>
+      <c r="B39" s="30"/>
+      <c r="C39" s="30"/>
       <c r="K39" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
@@ -1946,11 +1962,11 @@
       <c r="T39" s="4"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
+      <c r="A40" s="30"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
       <c r="K40" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
@@ -1958,11 +1974,11 @@
       <c r="T40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
+      <c r="A41" s="30"/>
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
       <c r="K41" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
@@ -1970,11 +1986,11 @@
       <c r="T41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="28"/>
-      <c r="B42" s="28"/>
-      <c r="C42" s="28"/>
+      <c r="A42" s="30"/>
+      <c r="B42" s="30"/>
+      <c r="C42" s="30"/>
       <c r="K42" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
@@ -1982,11 +1998,11 @@
       <c r="T42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="28"/>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
+      <c r="A43" s="30"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
       <c r="K43" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
@@ -1994,45 +2010,45 @@
       <c r="T43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="28"/>
-      <c r="B44" s="28"/>
-      <c r="C44" s="28"/>
+      <c r="A44" s="30"/>
+      <c r="B44" s="30"/>
+      <c r="C44" s="30"/>
       <c r="K44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="28"/>
-      <c r="B45" s="28"/>
-      <c r="C45" s="28"/>
+      <c r="A45" s="30"/>
+      <c r="B45" s="30"/>
+      <c r="C45" s="30"/>
       <c r="K45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="28"/>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
+      <c r="A46" s="30"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
       <c r="K46" s="4"/>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="28"/>
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
+      <c r="A47" s="30"/>
+      <c r="B47" s="30"/>
+      <c r="C47" s="30"/>
       <c r="K47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="28"/>
-      <c r="B48" s="28"/>
-      <c r="C48" s="28"/>
+      <c r="A48" s="30"/>
+      <c r="B48" s="30"/>
+      <c r="C48" s="30"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -2045,9 +2061,9 @@
       <c r="T48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="28"/>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
+      <c r="A49" s="30"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -2060,9 +2076,9 @@
       <c r="T49" s="4"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="28"/>
-      <c r="B50" s="28"/>
-      <c r="C50" s="28"/>
+      <c r="A50" s="30"/>
+      <c r="B50" s="30"/>
+      <c r="C50" s="30"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -2075,9 +2091,9 @@
       <c r="T50" s="4"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="28"/>
-      <c r="B51" s="28"/>
-      <c r="C51" s="28"/>
+      <c r="A51" s="30"/>
+      <c r="B51" s="30"/>
+      <c r="C51" s="30"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -2090,9 +2106,9 @@
       <c r="T51" s="4"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="28"/>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
+      <c r="A52" s="30"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -2105,4749 +2121,4749 @@
       <c r="T52" s="4"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="28"/>
-      <c r="B53" s="28"/>
-      <c r="C53" s="28"/>
+      <c r="A53" s="30"/>
+      <c r="B53" s="30"/>
+      <c r="C53" s="30"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="28"/>
-      <c r="B54" s="28"/>
-      <c r="C54" s="28"/>
+      <c r="A54" s="30"/>
+      <c r="B54" s="30"/>
+      <c r="C54" s="30"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="28"/>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
+      <c r="A55" s="30"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="28"/>
-      <c r="B56" s="28"/>
-      <c r="C56" s="28"/>
+      <c r="A56" s="30"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="30"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="28"/>
-      <c r="B57" s="28"/>
-      <c r="C57" s="28"/>
+      <c r="A57" s="30"/>
+      <c r="B57" s="30"/>
+      <c r="C57" s="30"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="28"/>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
+      <c r="A58" s="30"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="28"/>
-      <c r="B59" s="28"/>
-      <c r="C59" s="28"/>
+      <c r="A59" s="30"/>
+      <c r="B59" s="30"/>
+      <c r="C59" s="30"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="28"/>
-      <c r="B60" s="28"/>
-      <c r="C60" s="28"/>
+      <c r="A60" s="30"/>
+      <c r="B60" s="30"/>
+      <c r="C60" s="30"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="28"/>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
+      <c r="A61" s="30"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="28"/>
-      <c r="B62" s="28"/>
-      <c r="C62" s="28"/>
+      <c r="A62" s="30"/>
+      <c r="B62" s="30"/>
+      <c r="C62" s="30"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="28"/>
-      <c r="B63" s="28"/>
-      <c r="C63" s="28"/>
+      <c r="A63" s="30"/>
+      <c r="B63" s="30"/>
+      <c r="C63" s="30"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="28"/>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
+      <c r="A64" s="30"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="28"/>
-      <c r="B65" s="28"/>
-      <c r="C65" s="28"/>
+      <c r="A65" s="30"/>
+      <c r="B65" s="30"/>
+      <c r="C65" s="30"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="28"/>
-      <c r="B66" s="28"/>
-      <c r="C66" s="28"/>
+      <c r="A66" s="30"/>
+      <c r="B66" s="30"/>
+      <c r="C66" s="30"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="28"/>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
+      <c r="A67" s="30"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="28"/>
-      <c r="B68" s="28"/>
-      <c r="C68" s="28"/>
+      <c r="A68" s="30"/>
+      <c r="B68" s="30"/>
+      <c r="C68" s="30"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="28"/>
-      <c r="B69" s="28"/>
-      <c r="C69" s="28"/>
+      <c r="A69" s="30"/>
+      <c r="B69" s="30"/>
+      <c r="C69" s="30"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="28"/>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
+      <c r="A70" s="30"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="28"/>
-      <c r="B71" s="28"/>
-      <c r="C71" s="28"/>
+      <c r="A71" s="30"/>
+      <c r="B71" s="30"/>
+      <c r="C71" s="30"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="28"/>
-      <c r="B72" s="28"/>
-      <c r="C72" s="28"/>
+      <c r="A72" s="30"/>
+      <c r="B72" s="30"/>
+      <c r="C72" s="30"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="28"/>
-      <c r="B73" s="28"/>
-      <c r="C73" s="28"/>
+      <c r="A73" s="30"/>
+      <c r="B73" s="30"/>
+      <c r="C73" s="30"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="28"/>
-      <c r="B74" s="28"/>
-      <c r="C74" s="28"/>
+      <c r="A74" s="30"/>
+      <c r="B74" s="30"/>
+      <c r="C74" s="30"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="28"/>
-      <c r="B75" s="28"/>
-      <c r="C75" s="28"/>
+      <c r="A75" s="30"/>
+      <c r="B75" s="30"/>
+      <c r="C75" s="30"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="28"/>
-      <c r="B76" s="28"/>
-      <c r="C76" s="28"/>
+      <c r="A76" s="30"/>
+      <c r="B76" s="30"/>
+      <c r="C76" s="30"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="28"/>
-      <c r="B77" s="28"/>
-      <c r="C77" s="28"/>
+      <c r="A77" s="30"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="30"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="28"/>
-      <c r="B78" s="28"/>
-      <c r="C78" s="28"/>
+      <c r="A78" s="30"/>
+      <c r="B78" s="30"/>
+      <c r="C78" s="30"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="28"/>
-      <c r="B79" s="28"/>
-      <c r="C79" s="28"/>
+      <c r="A79" s="30"/>
+      <c r="B79" s="30"/>
+      <c r="C79" s="30"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="28"/>
-      <c r="B80" s="28"/>
-      <c r="C80" s="28"/>
+      <c r="A80" s="30"/>
+      <c r="B80" s="30"/>
+      <c r="C80" s="30"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="28"/>
-      <c r="B81" s="28"/>
-      <c r="C81" s="28"/>
+      <c r="A81" s="30"/>
+      <c r="B81" s="30"/>
+      <c r="C81" s="30"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="28"/>
-      <c r="B82" s="28"/>
-      <c r="C82" s="28"/>
+      <c r="A82" s="30"/>
+      <c r="B82" s="30"/>
+      <c r="C82" s="30"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="28"/>
-      <c r="B83" s="28"/>
-      <c r="C83" s="28"/>
+      <c r="A83" s="30"/>
+      <c r="B83" s="30"/>
+      <c r="C83" s="30"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="28"/>
-      <c r="B84" s="28"/>
-      <c r="C84" s="28"/>
+      <c r="A84" s="30"/>
+      <c r="B84" s="30"/>
+      <c r="C84" s="30"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="28"/>
-      <c r="B85" s="28"/>
-      <c r="C85" s="28"/>
+      <c r="A85" s="30"/>
+      <c r="B85" s="30"/>
+      <c r="C85" s="30"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="28"/>
-      <c r="B86" s="28"/>
-      <c r="C86" s="28"/>
+      <c r="A86" s="30"/>
+      <c r="B86" s="30"/>
+      <c r="C86" s="30"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="28"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="28"/>
+      <c r="A87" s="30"/>
+      <c r="B87" s="30"/>
+      <c r="C87" s="30"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="28"/>
-      <c r="B88" s="28"/>
-      <c r="C88" s="28"/>
+      <c r="A88" s="30"/>
+      <c r="B88" s="30"/>
+      <c r="C88" s="30"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="28"/>
-      <c r="B89" s="28"/>
-      <c r="C89" s="28"/>
+      <c r="A89" s="30"/>
+      <c r="B89" s="30"/>
+      <c r="C89" s="30"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="28"/>
-      <c r="B90" s="28"/>
-      <c r="C90" s="28"/>
+      <c r="A90" s="30"/>
+      <c r="B90" s="30"/>
+      <c r="C90" s="30"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="28"/>
-      <c r="B91" s="28"/>
-      <c r="C91" s="28"/>
+      <c r="A91" s="30"/>
+      <c r="B91" s="30"/>
+      <c r="C91" s="30"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="28"/>
-      <c r="B92" s="28"/>
-      <c r="C92" s="28"/>
+      <c r="A92" s="30"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="30"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="28"/>
-      <c r="B93" s="28"/>
-      <c r="C93" s="28"/>
+      <c r="A93" s="30"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="30"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="28"/>
-      <c r="B94" s="28"/>
-      <c r="C94" s="28"/>
+      <c r="A94" s="30"/>
+      <c r="B94" s="30"/>
+      <c r="C94" s="30"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="28"/>
-      <c r="B95" s="28"/>
-      <c r="C95" s="28"/>
+      <c r="A95" s="30"/>
+      <c r="B95" s="30"/>
+      <c r="C95" s="30"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="28"/>
-      <c r="B96" s="28"/>
-      <c r="C96" s="28"/>
+      <c r="A96" s="30"/>
+      <c r="B96" s="30"/>
+      <c r="C96" s="30"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="28"/>
-      <c r="B97" s="28"/>
-      <c r="C97" s="28"/>
+      <c r="A97" s="30"/>
+      <c r="B97" s="30"/>
+      <c r="C97" s="30"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="A98" s="28"/>
-      <c r="B98" s="28"/>
-      <c r="C98" s="28"/>
+      <c r="A98" s="30"/>
+      <c r="B98" s="30"/>
+      <c r="C98" s="30"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="A99" s="28"/>
-      <c r="B99" s="28"/>
-      <c r="C99" s="28"/>
+      <c r="A99" s="30"/>
+      <c r="B99" s="30"/>
+      <c r="C99" s="30"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="A100" s="28"/>
-      <c r="B100" s="28"/>
-      <c r="C100" s="28"/>
+      <c r="A100" s="30"/>
+      <c r="B100" s="30"/>
+      <c r="C100" s="30"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="A101" s="28"/>
-      <c r="B101" s="28"/>
-      <c r="C101" s="28"/>
+      <c r="A101" s="30"/>
+      <c r="B101" s="30"/>
+      <c r="C101" s="30"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="A102" s="28"/>
-      <c r="B102" s="28"/>
-      <c r="C102" s="28"/>
+      <c r="A102" s="30"/>
+      <c r="B102" s="30"/>
+      <c r="C102" s="30"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="A103" s="28"/>
-      <c r="B103" s="28"/>
-      <c r="C103" s="28"/>
+      <c r="A103" s="30"/>
+      <c r="B103" s="30"/>
+      <c r="C103" s="30"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" s="28"/>
-      <c r="B104" s="28"/>
-      <c r="C104" s="28"/>
+      <c r="A104" s="30"/>
+      <c r="B104" s="30"/>
+      <c r="C104" s="30"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="28"/>
-      <c r="B105" s="28"/>
-      <c r="C105" s="28"/>
+      <c r="A105" s="30"/>
+      <c r="B105" s="30"/>
+      <c r="C105" s="30"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="28"/>
-      <c r="B106" s="28"/>
-      <c r="C106" s="28"/>
+      <c r="A106" s="30"/>
+      <c r="B106" s="30"/>
+      <c r="C106" s="30"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="28"/>
-      <c r="B107" s="28"/>
-      <c r="C107" s="28"/>
+      <c r="A107" s="30"/>
+      <c r="B107" s="30"/>
+      <c r="C107" s="30"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="28"/>
-      <c r="B108" s="28"/>
-      <c r="C108" s="28"/>
+      <c r="A108" s="30"/>
+      <c r="B108" s="30"/>
+      <c r="C108" s="30"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="28"/>
-      <c r="B109" s="28"/>
-      <c r="C109" s="28"/>
+      <c r="A109" s="30"/>
+      <c r="B109" s="30"/>
+      <c r="C109" s="30"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="28"/>
-      <c r="B110" s="28"/>
-      <c r="C110" s="28"/>
+      <c r="A110" s="30"/>
+      <c r="B110" s="30"/>
+      <c r="C110" s="30"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="28"/>
-      <c r="B111" s="28"/>
-      <c r="C111" s="28"/>
+      <c r="A111" s="30"/>
+      <c r="B111" s="30"/>
+      <c r="C111" s="30"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="A112" s="28"/>
-      <c r="B112" s="28"/>
-      <c r="C112" s="28"/>
+      <c r="A112" s="30"/>
+      <c r="B112" s="30"/>
+      <c r="C112" s="30"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="A113" s="28"/>
-      <c r="B113" s="28"/>
-      <c r="C113" s="28"/>
+      <c r="A113" s="30"/>
+      <c r="B113" s="30"/>
+      <c r="C113" s="30"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="28"/>
-      <c r="B114" s="28"/>
-      <c r="C114" s="28"/>
+      <c r="A114" s="30"/>
+      <c r="B114" s="30"/>
+      <c r="C114" s="30"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="28"/>
-      <c r="B115" s="28"/>
-      <c r="C115" s="28"/>
+      <c r="A115" s="30"/>
+      <c r="B115" s="30"/>
+      <c r="C115" s="30"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="28"/>
-      <c r="B116" s="28"/>
-      <c r="C116" s="28"/>
+      <c r="A116" s="30"/>
+      <c r="B116" s="30"/>
+      <c r="C116" s="30"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="A117" s="28"/>
-      <c r="B117" s="28"/>
-      <c r="C117" s="28"/>
+      <c r="A117" s="30"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="30"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="A118" s="28"/>
-      <c r="B118" s="28"/>
-      <c r="C118" s="28"/>
+      <c r="A118" s="30"/>
+      <c r="B118" s="30"/>
+      <c r="C118" s="30"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="28"/>
-      <c r="B119" s="28"/>
-      <c r="C119" s="28"/>
+      <c r="A119" s="30"/>
+      <c r="B119" s="30"/>
+      <c r="C119" s="30"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="A120" s="28"/>
-      <c r="B120" s="28"/>
-      <c r="C120" s="28"/>
+      <c r="A120" s="30"/>
+      <c r="B120" s="30"/>
+      <c r="C120" s="30"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="A121" s="28"/>
-      <c r="B121" s="28"/>
-      <c r="C121" s="28"/>
+      <c r="A121" s="30"/>
+      <c r="B121" s="30"/>
+      <c r="C121" s="30"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="A122" s="28"/>
-      <c r="B122" s="28"/>
-      <c r="C122" s="28"/>
+      <c r="A122" s="30"/>
+      <c r="B122" s="30"/>
+      <c r="C122" s="30"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="A123" s="28"/>
-      <c r="B123" s="28"/>
-      <c r="C123" s="28"/>
+      <c r="A123" s="30"/>
+      <c r="B123" s="30"/>
+      <c r="C123" s="30"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="A124" s="28"/>
-      <c r="B124" s="28"/>
-      <c r="C124" s="28"/>
+      <c r="A124" s="30"/>
+      <c r="B124" s="30"/>
+      <c r="C124" s="30"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="A125" s="28"/>
-      <c r="B125" s="28"/>
-      <c r="C125" s="28"/>
+      <c r="A125" s="30"/>
+      <c r="B125" s="30"/>
+      <c r="C125" s="30"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="A126" s="28"/>
-      <c r="B126" s="28"/>
-      <c r="C126" s="28"/>
+      <c r="A126" s="30"/>
+      <c r="B126" s="30"/>
+      <c r="C126" s="30"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="28"/>
-      <c r="B127" s="28"/>
-      <c r="C127" s="28"/>
+      <c r="A127" s="30"/>
+      <c r="B127" s="30"/>
+      <c r="C127" s="30"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="28"/>
-      <c r="B128" s="28"/>
-      <c r="C128" s="28"/>
+      <c r="A128" s="30"/>
+      <c r="B128" s="30"/>
+      <c r="C128" s="30"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="A129" s="28"/>
-      <c r="B129" s="28"/>
-      <c r="C129" s="28"/>
+      <c r="A129" s="30"/>
+      <c r="B129" s="30"/>
+      <c r="C129" s="30"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="A130" s="28"/>
-      <c r="B130" s="28"/>
-      <c r="C130" s="28"/>
+      <c r="A130" s="30"/>
+      <c r="B130" s="30"/>
+      <c r="C130" s="30"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="A131" s="28"/>
-      <c r="B131" s="28"/>
-      <c r="C131" s="28"/>
+      <c r="A131" s="30"/>
+      <c r="B131" s="30"/>
+      <c r="C131" s="30"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="A132" s="28"/>
-      <c r="B132" s="28"/>
-      <c r="C132" s="28"/>
+      <c r="A132" s="30"/>
+      <c r="B132" s="30"/>
+      <c r="C132" s="30"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="A133" s="28"/>
-      <c r="B133" s="28"/>
-      <c r="C133" s="28"/>
+      <c r="A133" s="30"/>
+      <c r="B133" s="30"/>
+      <c r="C133" s="30"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="A134" s="28"/>
-      <c r="B134" s="28"/>
-      <c r="C134" s="28"/>
+      <c r="A134" s="30"/>
+      <c r="B134" s="30"/>
+      <c r="C134" s="30"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="A135" s="28"/>
-      <c r="B135" s="28"/>
-      <c r="C135" s="28"/>
+      <c r="A135" s="30"/>
+      <c r="B135" s="30"/>
+      <c r="C135" s="30"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="A136" s="28"/>
-      <c r="B136" s="28"/>
-      <c r="C136" s="28"/>
+      <c r="A136" s="30"/>
+      <c r="B136" s="30"/>
+      <c r="C136" s="30"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="A137" s="28"/>
-      <c r="B137" s="28"/>
-      <c r="C137" s="28"/>
+      <c r="A137" s="30"/>
+      <c r="B137" s="30"/>
+      <c r="C137" s="30"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="A138" s="28"/>
-      <c r="B138" s="28"/>
-      <c r="C138" s="28"/>
+      <c r="A138" s="30"/>
+      <c r="B138" s="30"/>
+      <c r="C138" s="30"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="A139" s="28"/>
-      <c r="B139" s="28"/>
-      <c r="C139" s="28"/>
+      <c r="A139" s="30"/>
+      <c r="B139" s="30"/>
+      <c r="C139" s="30"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="A140" s="28"/>
-      <c r="B140" s="28"/>
-      <c r="C140" s="28"/>
+      <c r="A140" s="30"/>
+      <c r="B140" s="30"/>
+      <c r="C140" s="30"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="A141" s="28"/>
-      <c r="B141" s="28"/>
-      <c r="C141" s="28"/>
+      <c r="A141" s="30"/>
+      <c r="B141" s="30"/>
+      <c r="C141" s="30"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="A142" s="28"/>
-      <c r="B142" s="28"/>
-      <c r="C142" s="28"/>
+      <c r="A142" s="30"/>
+      <c r="B142" s="30"/>
+      <c r="C142" s="30"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="A143" s="28"/>
-      <c r="B143" s="28"/>
-      <c r="C143" s="28"/>
+      <c r="A143" s="30"/>
+      <c r="B143" s="30"/>
+      <c r="C143" s="30"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="A144" s="28"/>
-      <c r="B144" s="28"/>
-      <c r="C144" s="28"/>
+      <c r="A144" s="30"/>
+      <c r="B144" s="30"/>
+      <c r="C144" s="30"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="A145" s="28"/>
-      <c r="B145" s="28"/>
-      <c r="C145" s="28"/>
+      <c r="A145" s="30"/>
+      <c r="B145" s="30"/>
+      <c r="C145" s="30"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="A146" s="28"/>
-      <c r="B146" s="28"/>
-      <c r="C146" s="28"/>
+      <c r="A146" s="30"/>
+      <c r="B146" s="30"/>
+      <c r="C146" s="30"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="A147" s="28"/>
-      <c r="B147" s="28"/>
-      <c r="C147" s="28"/>
+      <c r="A147" s="30"/>
+      <c r="B147" s="30"/>
+      <c r="C147" s="30"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="28"/>
-      <c r="B148" s="28"/>
-      <c r="C148" s="28"/>
+      <c r="A148" s="30"/>
+      <c r="B148" s="30"/>
+      <c r="C148" s="30"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="A149" s="28"/>
-      <c r="B149" s="28"/>
-      <c r="C149" s="28"/>
+      <c r="A149" s="30"/>
+      <c r="B149" s="30"/>
+      <c r="C149" s="30"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="A150" s="28"/>
-      <c r="B150" s="28"/>
-      <c r="C150" s="28"/>
+      <c r="A150" s="30"/>
+      <c r="B150" s="30"/>
+      <c r="C150" s="30"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="A151" s="28"/>
-      <c r="B151" s="28"/>
-      <c r="C151" s="28"/>
+      <c r="A151" s="30"/>
+      <c r="B151" s="30"/>
+      <c r="C151" s="30"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="A152" s="28"/>
-      <c r="B152" s="28"/>
-      <c r="C152" s="28"/>
+      <c r="A152" s="30"/>
+      <c r="B152" s="30"/>
+      <c r="C152" s="30"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="A153" s="28"/>
-      <c r="B153" s="28"/>
-      <c r="C153" s="28"/>
+      <c r="A153" s="30"/>
+      <c r="B153" s="30"/>
+      <c r="C153" s="30"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="A154" s="28"/>
-      <c r="B154" s="28"/>
-      <c r="C154" s="28"/>
+      <c r="A154" s="30"/>
+      <c r="B154" s="30"/>
+      <c r="C154" s="30"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="A155" s="28"/>
-      <c r="B155" s="28"/>
-      <c r="C155" s="28"/>
+      <c r="A155" s="30"/>
+      <c r="B155" s="30"/>
+      <c r="C155" s="30"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="A156" s="28"/>
-      <c r="B156" s="28"/>
-      <c r="C156" s="28"/>
+      <c r="A156" s="30"/>
+      <c r="B156" s="30"/>
+      <c r="C156" s="30"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="A157" s="28"/>
-      <c r="B157" s="28"/>
-      <c r="C157" s="28"/>
+      <c r="A157" s="30"/>
+      <c r="B157" s="30"/>
+      <c r="C157" s="30"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="A158" s="28"/>
-      <c r="B158" s="28"/>
-      <c r="C158" s="28"/>
+      <c r="A158" s="30"/>
+      <c r="B158" s="30"/>
+      <c r="C158" s="30"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="A159" s="28"/>
-      <c r="B159" s="28"/>
-      <c r="C159" s="28"/>
+      <c r="A159" s="30"/>
+      <c r="B159" s="30"/>
+      <c r="C159" s="30"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="A160" s="28"/>
-      <c r="B160" s="28"/>
-      <c r="C160" s="28"/>
+      <c r="A160" s="30"/>
+      <c r="B160" s="30"/>
+      <c r="C160" s="30"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="A161" s="28"/>
-      <c r="B161" s="28"/>
-      <c r="C161" s="28"/>
+      <c r="A161" s="30"/>
+      <c r="B161" s="30"/>
+      <c r="C161" s="30"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="A162" s="28"/>
-      <c r="B162" s="28"/>
-      <c r="C162" s="28"/>
+      <c r="A162" s="30"/>
+      <c r="B162" s="30"/>
+      <c r="C162" s="30"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="A163" s="28"/>
-      <c r="B163" s="28"/>
-      <c r="C163" s="28"/>
+      <c r="A163" s="30"/>
+      <c r="B163" s="30"/>
+      <c r="C163" s="30"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="A164" s="28"/>
-      <c r="B164" s="28"/>
-      <c r="C164" s="28"/>
+      <c r="A164" s="30"/>
+      <c r="B164" s="30"/>
+      <c r="C164" s="30"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="A165" s="28"/>
-      <c r="B165" s="28"/>
-      <c r="C165" s="28"/>
+      <c r="A165" s="30"/>
+      <c r="B165" s="30"/>
+      <c r="C165" s="30"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="A166" s="28"/>
-      <c r="B166" s="28"/>
-      <c r="C166" s="28"/>
+      <c r="A166" s="30"/>
+      <c r="B166" s="30"/>
+      <c r="C166" s="30"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="A167" s="28"/>
-      <c r="B167" s="28"/>
-      <c r="C167" s="28"/>
+      <c r="A167" s="30"/>
+      <c r="B167" s="30"/>
+      <c r="C167" s="30"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="28"/>
-      <c r="B168" s="28"/>
-      <c r="C168" s="28"/>
+      <c r="A168" s="30"/>
+      <c r="B168" s="30"/>
+      <c r="C168" s="30"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="A169" s="28"/>
-      <c r="B169" s="28"/>
-      <c r="C169" s="28"/>
+      <c r="A169" s="30"/>
+      <c r="B169" s="30"/>
+      <c r="C169" s="30"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="A170" s="28"/>
-      <c r="B170" s="28"/>
-      <c r="C170" s="28"/>
+      <c r="A170" s="30"/>
+      <c r="B170" s="30"/>
+      <c r="C170" s="30"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="A171" s="28"/>
-      <c r="B171" s="28"/>
-      <c r="C171" s="28"/>
+      <c r="A171" s="30"/>
+      <c r="B171" s="30"/>
+      <c r="C171" s="30"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="A172" s="28"/>
-      <c r="B172" s="28"/>
-      <c r="C172" s="28"/>
+      <c r="A172" s="30"/>
+      <c r="B172" s="30"/>
+      <c r="C172" s="30"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="A173" s="28"/>
-      <c r="B173" s="28"/>
-      <c r="C173" s="28"/>
+      <c r="A173" s="30"/>
+      <c r="B173" s="30"/>
+      <c r="C173" s="30"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="A174" s="28"/>
-      <c r="B174" s="28"/>
-      <c r="C174" s="28"/>
+      <c r="A174" s="30"/>
+      <c r="B174" s="30"/>
+      <c r="C174" s="30"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="A175" s="28"/>
-      <c r="B175" s="28"/>
-      <c r="C175" s="28"/>
+      <c r="A175" s="30"/>
+      <c r="B175" s="30"/>
+      <c r="C175" s="30"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="A176" s="28"/>
-      <c r="B176" s="28"/>
-      <c r="C176" s="28"/>
+      <c r="A176" s="30"/>
+      <c r="B176" s="30"/>
+      <c r="C176" s="30"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="A177" s="28"/>
-      <c r="B177" s="28"/>
-      <c r="C177" s="28"/>
+      <c r="A177" s="30"/>
+      <c r="B177" s="30"/>
+      <c r="C177" s="30"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="28"/>
-      <c r="B178" s="28"/>
-      <c r="C178" s="28"/>
+      <c r="A178" s="30"/>
+      <c r="B178" s="30"/>
+      <c r="C178" s="30"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="A179" s="28"/>
-      <c r="B179" s="28"/>
-      <c r="C179" s="28"/>
+      <c r="A179" s="30"/>
+      <c r="B179" s="30"/>
+      <c r="C179" s="30"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="A180" s="28"/>
-      <c r="B180" s="28"/>
-      <c r="C180" s="28"/>
+      <c r="A180" s="30"/>
+      <c r="B180" s="30"/>
+      <c r="C180" s="30"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="A181" s="28"/>
-      <c r="B181" s="28"/>
-      <c r="C181" s="28"/>
+      <c r="A181" s="30"/>
+      <c r="B181" s="30"/>
+      <c r="C181" s="30"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="A182" s="28"/>
-      <c r="B182" s="28"/>
-      <c r="C182" s="28"/>
+      <c r="A182" s="30"/>
+      <c r="B182" s="30"/>
+      <c r="C182" s="30"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="A183" s="28"/>
-      <c r="B183" s="28"/>
-      <c r="C183" s="28"/>
+      <c r="A183" s="30"/>
+      <c r="B183" s="30"/>
+      <c r="C183" s="30"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="A184" s="28"/>
-      <c r="B184" s="28"/>
-      <c r="C184" s="28"/>
+      <c r="A184" s="30"/>
+      <c r="B184" s="30"/>
+      <c r="C184" s="30"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="A185" s="28"/>
-      <c r="B185" s="28"/>
-      <c r="C185" s="28"/>
+      <c r="A185" s="30"/>
+      <c r="B185" s="30"/>
+      <c r="C185" s="30"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="A186" s="28"/>
-      <c r="B186" s="28"/>
-      <c r="C186" s="28"/>
+      <c r="A186" s="30"/>
+      <c r="B186" s="30"/>
+      <c r="C186" s="30"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="A187" s="28"/>
-      <c r="B187" s="28"/>
-      <c r="C187" s="28"/>
+      <c r="A187" s="30"/>
+      <c r="B187" s="30"/>
+      <c r="C187" s="30"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="28"/>
-      <c r="B188" s="28"/>
-      <c r="C188" s="28"/>
+      <c r="A188" s="30"/>
+      <c r="B188" s="30"/>
+      <c r="C188" s="30"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="A189" s="28"/>
-      <c r="B189" s="28"/>
-      <c r="C189" s="28"/>
+      <c r="A189" s="30"/>
+      <c r="B189" s="30"/>
+      <c r="C189" s="30"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="A190" s="28"/>
-      <c r="B190" s="28"/>
-      <c r="C190" s="28"/>
+      <c r="A190" s="30"/>
+      <c r="B190" s="30"/>
+      <c r="C190" s="30"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="A191" s="28"/>
-      <c r="B191" s="28"/>
-      <c r="C191" s="28"/>
+      <c r="A191" s="30"/>
+      <c r="B191" s="30"/>
+      <c r="C191" s="30"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="A192" s="28"/>
-      <c r="B192" s="28"/>
-      <c r="C192" s="28"/>
+      <c r="A192" s="30"/>
+      <c r="B192" s="30"/>
+      <c r="C192" s="30"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="A193" s="28"/>
-      <c r="B193" s="28"/>
-      <c r="C193" s="28"/>
+      <c r="A193" s="30"/>
+      <c r="B193" s="30"/>
+      <c r="C193" s="30"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="A194" s="28"/>
-      <c r="B194" s="28"/>
-      <c r="C194" s="28"/>
+      <c r="A194" s="30"/>
+      <c r="B194" s="30"/>
+      <c r="C194" s="30"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="A195" s="28"/>
-      <c r="B195" s="28"/>
-      <c r="C195" s="28"/>
+      <c r="A195" s="30"/>
+      <c r="B195" s="30"/>
+      <c r="C195" s="30"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="A196" s="28"/>
-      <c r="B196" s="28"/>
-      <c r="C196" s="28"/>
+      <c r="A196" s="30"/>
+      <c r="B196" s="30"/>
+      <c r="C196" s="30"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="A197" s="28"/>
-      <c r="B197" s="28"/>
-      <c r="C197" s="28"/>
+      <c r="A197" s="30"/>
+      <c r="B197" s="30"/>
+      <c r="C197" s="30"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="A198" s="28"/>
-      <c r="B198" s="28"/>
-      <c r="C198" s="28"/>
+      <c r="A198" s="30"/>
+      <c r="B198" s="30"/>
+      <c r="C198" s="30"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="A199" s="28"/>
-      <c r="B199" s="28"/>
-      <c r="C199" s="28"/>
+      <c r="A199" s="30"/>
+      <c r="B199" s="30"/>
+      <c r="C199" s="30"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="A200" s="28"/>
-      <c r="B200" s="28"/>
-      <c r="C200" s="28"/>
+      <c r="A200" s="30"/>
+      <c r="B200" s="30"/>
+      <c r="C200" s="30"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="A201" s="28"/>
-      <c r="B201" s="28"/>
-      <c r="C201" s="28"/>
+      <c r="A201" s="30"/>
+      <c r="B201" s="30"/>
+      <c r="C201" s="30"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="A202" s="28"/>
-      <c r="B202" s="28"/>
-      <c r="C202" s="28"/>
+      <c r="A202" s="30"/>
+      <c r="B202" s="30"/>
+      <c r="C202" s="30"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="A203" s="28"/>
-      <c r="B203" s="28"/>
-      <c r="C203" s="28"/>
+      <c r="A203" s="30"/>
+      <c r="B203" s="30"/>
+      <c r="C203" s="30"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="A204" s="28"/>
-      <c r="B204" s="28"/>
-      <c r="C204" s="28"/>
+      <c r="A204" s="30"/>
+      <c r="B204" s="30"/>
+      <c r="C204" s="30"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="A205" s="28"/>
-      <c r="B205" s="28"/>
-      <c r="C205" s="28"/>
+      <c r="A205" s="30"/>
+      <c r="B205" s="30"/>
+      <c r="C205" s="30"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="A206" s="28"/>
-      <c r="B206" s="28"/>
-      <c r="C206" s="28"/>
+      <c r="A206" s="30"/>
+      <c r="B206" s="30"/>
+      <c r="C206" s="30"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="A207" s="28"/>
-      <c r="B207" s="28"/>
-      <c r="C207" s="28"/>
+      <c r="A207" s="30"/>
+      <c r="B207" s="30"/>
+      <c r="C207" s="30"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="28"/>
-      <c r="B208" s="28"/>
-      <c r="C208" s="28"/>
+      <c r="A208" s="30"/>
+      <c r="B208" s="30"/>
+      <c r="C208" s="30"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="A209" s="28"/>
-      <c r="B209" s="28"/>
-      <c r="C209" s="28"/>
+      <c r="A209" s="30"/>
+      <c r="B209" s="30"/>
+      <c r="C209" s="30"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="A210" s="28"/>
-      <c r="B210" s="28"/>
-      <c r="C210" s="28"/>
+      <c r="A210" s="30"/>
+      <c r="B210" s="30"/>
+      <c r="C210" s="30"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="A211" s="28"/>
-      <c r="B211" s="28"/>
-      <c r="C211" s="28"/>
+      <c r="A211" s="30"/>
+      <c r="B211" s="30"/>
+      <c r="C211" s="30"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="A212" s="28"/>
-      <c r="B212" s="28"/>
-      <c r="C212" s="28"/>
+      <c r="A212" s="30"/>
+      <c r="B212" s="30"/>
+      <c r="C212" s="30"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="A213" s="28"/>
-      <c r="B213" s="28"/>
-      <c r="C213" s="28"/>
+      <c r="A213" s="30"/>
+      <c r="B213" s="30"/>
+      <c r="C213" s="30"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="A214" s="28"/>
-      <c r="B214" s="28"/>
-      <c r="C214" s="28"/>
+      <c r="A214" s="30"/>
+      <c r="B214" s="30"/>
+      <c r="C214" s="30"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="A215" s="28"/>
-      <c r="B215" s="28"/>
-      <c r="C215" s="28"/>
+      <c r="A215" s="30"/>
+      <c r="B215" s="30"/>
+      <c r="C215" s="30"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="A216" s="28"/>
-      <c r="B216" s="28"/>
-      <c r="C216" s="28"/>
+      <c r="A216" s="30"/>
+      <c r="B216" s="30"/>
+      <c r="C216" s="30"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="A217" s="28"/>
-      <c r="B217" s="28"/>
-      <c r="C217" s="28"/>
+      <c r="A217" s="30"/>
+      <c r="B217" s="30"/>
+      <c r="C217" s="30"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="A218" s="28"/>
-      <c r="B218" s="28"/>
-      <c r="C218" s="28"/>
+      <c r="A218" s="30"/>
+      <c r="B218" s="30"/>
+      <c r="C218" s="30"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="A219" s="28"/>
-      <c r="B219" s="28"/>
-      <c r="C219" s="28"/>
+      <c r="A219" s="30"/>
+      <c r="B219" s="30"/>
+      <c r="C219" s="30"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="A220" s="28"/>
-      <c r="B220" s="28"/>
-      <c r="C220" s="28"/>
+      <c r="A220" s="30"/>
+      <c r="B220" s="30"/>
+      <c r="C220" s="30"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="A221" s="28"/>
-      <c r="B221" s="28"/>
-      <c r="C221" s="28"/>
+      <c r="A221" s="30"/>
+      <c r="B221" s="30"/>
+      <c r="C221" s="30"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="A222" s="28"/>
-      <c r="B222" s="28"/>
-      <c r="C222" s="28"/>
+      <c r="A222" s="30"/>
+      <c r="B222" s="30"/>
+      <c r="C222" s="30"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="A223" s="28"/>
-      <c r="B223" s="28"/>
-      <c r="C223" s="28"/>
+      <c r="A223" s="30"/>
+      <c r="B223" s="30"/>
+      <c r="C223" s="30"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="A224" s="28"/>
-      <c r="B224" s="28"/>
-      <c r="C224" s="28"/>
+      <c r="A224" s="30"/>
+      <c r="B224" s="30"/>
+      <c r="C224" s="30"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="A225" s="28"/>
-      <c r="B225" s="28"/>
-      <c r="C225" s="28"/>
+      <c r="A225" s="30"/>
+      <c r="B225" s="30"/>
+      <c r="C225" s="30"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="28"/>
-      <c r="B226" s="28"/>
-      <c r="C226" s="28"/>
+      <c r="A226" s="30"/>
+      <c r="B226" s="30"/>
+      <c r="C226" s="30"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="28"/>
-      <c r="B227" s="28"/>
-      <c r="C227" s="28"/>
+      <c r="A227" s="30"/>
+      <c r="B227" s="30"/>
+      <c r="C227" s="30"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="28"/>
-      <c r="B228" s="28"/>
-      <c r="C228" s="28"/>
+      <c r="A228" s="30"/>
+      <c r="B228" s="30"/>
+      <c r="C228" s="30"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="28"/>
-      <c r="B229" s="28"/>
-      <c r="C229" s="28"/>
+      <c r="A229" s="30"/>
+      <c r="B229" s="30"/>
+      <c r="C229" s="30"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="28"/>
-      <c r="B230" s="28"/>
-      <c r="C230" s="28"/>
+      <c r="A230" s="30"/>
+      <c r="B230" s="30"/>
+      <c r="C230" s="30"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="A231" s="28"/>
-      <c r="B231" s="28"/>
-      <c r="C231" s="28"/>
+      <c r="A231" s="30"/>
+      <c r="B231" s="30"/>
+      <c r="C231" s="30"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="A232" s="28"/>
-      <c r="B232" s="28"/>
-      <c r="C232" s="28"/>
+      <c r="A232" s="30"/>
+      <c r="B232" s="30"/>
+      <c r="C232" s="30"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="A233" s="28"/>
-      <c r="B233" s="28"/>
-      <c r="C233" s="28"/>
+      <c r="A233" s="30"/>
+      <c r="B233" s="30"/>
+      <c r="C233" s="30"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="A234" s="28"/>
-      <c r="B234" s="28"/>
-      <c r="C234" s="28"/>
+      <c r="A234" s="30"/>
+      <c r="B234" s="30"/>
+      <c r="C234" s="30"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="A235" s="28"/>
-      <c r="B235" s="28"/>
-      <c r="C235" s="28"/>
+      <c r="A235" s="30"/>
+      <c r="B235" s="30"/>
+      <c r="C235" s="30"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="A236" s="28"/>
-      <c r="B236" s="28"/>
-      <c r="C236" s="28"/>
+      <c r="A236" s="30"/>
+      <c r="B236" s="30"/>
+      <c r="C236" s="30"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="A237" s="28"/>
-      <c r="B237" s="28"/>
-      <c r="C237" s="28"/>
+      <c r="A237" s="30"/>
+      <c r="B237" s="30"/>
+      <c r="C237" s="30"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="A238" s="28"/>
-      <c r="B238" s="28"/>
-      <c r="C238" s="28"/>
+      <c r="A238" s="30"/>
+      <c r="B238" s="30"/>
+      <c r="C238" s="30"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="A239" s="28"/>
-      <c r="B239" s="28"/>
-      <c r="C239" s="28"/>
+      <c r="A239" s="30"/>
+      <c r="B239" s="30"/>
+      <c r="C239" s="30"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="A240" s="28"/>
-      <c r="B240" s="28"/>
-      <c r="C240" s="28"/>
+      <c r="A240" s="30"/>
+      <c r="B240" s="30"/>
+      <c r="C240" s="30"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="A241" s="28"/>
-      <c r="B241" s="28"/>
-      <c r="C241" s="28"/>
+      <c r="A241" s="30"/>
+      <c r="B241" s="30"/>
+      <c r="C241" s="30"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="A242" s="28"/>
-      <c r="B242" s="28"/>
-      <c r="C242" s="28"/>
+      <c r="A242" s="30"/>
+      <c r="B242" s="30"/>
+      <c r="C242" s="30"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="A243" s="28"/>
-      <c r="B243" s="28"/>
-      <c r="C243" s="28"/>
+      <c r="A243" s="30"/>
+      <c r="B243" s="30"/>
+      <c r="C243" s="30"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="A244" s="28"/>
-      <c r="B244" s="28"/>
-      <c r="C244" s="28"/>
+      <c r="A244" s="30"/>
+      <c r="B244" s="30"/>
+      <c r="C244" s="30"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="A245" s="28"/>
-      <c r="B245" s="28"/>
-      <c r="C245" s="28"/>
+      <c r="A245" s="30"/>
+      <c r="B245" s="30"/>
+      <c r="C245" s="30"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="A246" s="28"/>
-      <c r="B246" s="28"/>
-      <c r="C246" s="28"/>
+      <c r="A246" s="30"/>
+      <c r="B246" s="30"/>
+      <c r="C246" s="30"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="A247" s="28"/>
-      <c r="B247" s="28"/>
-      <c r="C247" s="28"/>
+      <c r="A247" s="30"/>
+      <c r="B247" s="30"/>
+      <c r="C247" s="30"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="28"/>
-      <c r="B248" s="28"/>
-      <c r="C248" s="28"/>
+      <c r="A248" s="30"/>
+      <c r="B248" s="30"/>
+      <c r="C248" s="30"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="A249" s="28"/>
-      <c r="B249" s="28"/>
-      <c r="C249" s="28"/>
+      <c r="A249" s="30"/>
+      <c r="B249" s="30"/>
+      <c r="C249" s="30"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="A250" s="28"/>
-      <c r="B250" s="28"/>
-      <c r="C250" s="28"/>
+      <c r="A250" s="30"/>
+      <c r="B250" s="30"/>
+      <c r="C250" s="30"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="A251" s="28"/>
-      <c r="B251" s="28"/>
-      <c r="C251" s="28"/>
+      <c r="A251" s="30"/>
+      <c r="B251" s="30"/>
+      <c r="C251" s="30"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="A252" s="28"/>
-      <c r="B252" s="28"/>
-      <c r="C252" s="28"/>
+      <c r="A252" s="30"/>
+      <c r="B252" s="30"/>
+      <c r="C252" s="30"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="A253" s="28"/>
-      <c r="B253" s="28"/>
-      <c r="C253" s="28"/>
+      <c r="A253" s="30"/>
+      <c r="B253" s="30"/>
+      <c r="C253" s="30"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="A254" s="28"/>
-      <c r="B254" s="28"/>
-      <c r="C254" s="28"/>
+      <c r="A254" s="30"/>
+      <c r="B254" s="30"/>
+      <c r="C254" s="30"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="A255" s="28"/>
-      <c r="B255" s="28"/>
-      <c r="C255" s="28"/>
+      <c r="A255" s="30"/>
+      <c r="B255" s="30"/>
+      <c r="C255" s="30"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="A256" s="28"/>
-      <c r="B256" s="28"/>
-      <c r="C256" s="28"/>
+      <c r="A256" s="30"/>
+      <c r="B256" s="30"/>
+      <c r="C256" s="30"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="A257" s="28"/>
-      <c r="B257" s="28"/>
-      <c r="C257" s="28"/>
+      <c r="A257" s="30"/>
+      <c r="B257" s="30"/>
+      <c r="C257" s="30"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="A258" s="28"/>
-      <c r="B258" s="28"/>
-      <c r="C258" s="28"/>
+      <c r="A258" s="30"/>
+      <c r="B258" s="30"/>
+      <c r="C258" s="30"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="A259" s="28"/>
-      <c r="B259" s="28"/>
-      <c r="C259" s="28"/>
+      <c r="A259" s="30"/>
+      <c r="B259" s="30"/>
+      <c r="C259" s="30"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="A260" s="28"/>
-      <c r="B260" s="28"/>
-      <c r="C260" s="28"/>
+      <c r="A260" s="30"/>
+      <c r="B260" s="30"/>
+      <c r="C260" s="30"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="A261" s="28"/>
-      <c r="B261" s="28"/>
-      <c r="C261" s="28"/>
+      <c r="A261" s="30"/>
+      <c r="B261" s="30"/>
+      <c r="C261" s="30"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="A262" s="28"/>
-      <c r="B262" s="28"/>
-      <c r="C262" s="28"/>
+      <c r="A262" s="30"/>
+      <c r="B262" s="30"/>
+      <c r="C262" s="30"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="A263" s="28"/>
-      <c r="B263" s="28"/>
-      <c r="C263" s="28"/>
+      <c r="A263" s="30"/>
+      <c r="B263" s="30"/>
+      <c r="C263" s="30"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="A264" s="28"/>
-      <c r="B264" s="28"/>
-      <c r="C264" s="28"/>
+      <c r="A264" s="30"/>
+      <c r="B264" s="30"/>
+      <c r="C264" s="30"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="A265" s="28"/>
-      <c r="B265" s="28"/>
-      <c r="C265" s="28"/>
+      <c r="A265" s="30"/>
+      <c r="B265" s="30"/>
+      <c r="C265" s="30"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="A266" s="28"/>
-      <c r="B266" s="28"/>
-      <c r="C266" s="28"/>
+      <c r="A266" s="30"/>
+      <c r="B266" s="30"/>
+      <c r="C266" s="30"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="A267" s="28"/>
-      <c r="B267" s="28"/>
-      <c r="C267" s="28"/>
+      <c r="A267" s="30"/>
+      <c r="B267" s="30"/>
+      <c r="C267" s="30"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="28"/>
-      <c r="B268" s="28"/>
-      <c r="C268" s="28"/>
+      <c r="A268" s="30"/>
+      <c r="B268" s="30"/>
+      <c r="C268" s="30"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="A269" s="28"/>
-      <c r="B269" s="28"/>
-      <c r="C269" s="28"/>
+      <c r="A269" s="30"/>
+      <c r="B269" s="30"/>
+      <c r="C269" s="30"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="A270" s="28"/>
-      <c r="B270" s="28"/>
-      <c r="C270" s="28"/>
+      <c r="A270" s="30"/>
+      <c r="B270" s="30"/>
+      <c r="C270" s="30"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="A271" s="28"/>
-      <c r="B271" s="28"/>
-      <c r="C271" s="28"/>
+      <c r="A271" s="30"/>
+      <c r="B271" s="30"/>
+      <c r="C271" s="30"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="A272" s="28"/>
-      <c r="B272" s="28"/>
-      <c r="C272" s="28"/>
+      <c r="A272" s="30"/>
+      <c r="B272" s="30"/>
+      <c r="C272" s="30"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="A273" s="28"/>
-      <c r="B273" s="28"/>
-      <c r="C273" s="28"/>
+      <c r="A273" s="30"/>
+      <c r="B273" s="30"/>
+      <c r="C273" s="30"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="A274" s="28"/>
-      <c r="B274" s="28"/>
-      <c r="C274" s="28"/>
+      <c r="A274" s="30"/>
+      <c r="B274" s="30"/>
+      <c r="C274" s="30"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="A275" s="28"/>
-      <c r="B275" s="28"/>
-      <c r="C275" s="28"/>
+      <c r="A275" s="30"/>
+      <c r="B275" s="30"/>
+      <c r="C275" s="30"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="A276" s="28"/>
-      <c r="B276" s="28"/>
-      <c r="C276" s="28"/>
+      <c r="A276" s="30"/>
+      <c r="B276" s="30"/>
+      <c r="C276" s="30"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="A277" s="28"/>
-      <c r="B277" s="28"/>
-      <c r="C277" s="28"/>
+      <c r="A277" s="30"/>
+      <c r="B277" s="30"/>
+      <c r="C277" s="30"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="A278" s="28"/>
-      <c r="B278" s="28"/>
-      <c r="C278" s="28"/>
+      <c r="A278" s="30"/>
+      <c r="B278" s="30"/>
+      <c r="C278" s="30"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="A279" s="28"/>
-      <c r="B279" s="28"/>
-      <c r="C279" s="28"/>
+      <c r="A279" s="30"/>
+      <c r="B279" s="30"/>
+      <c r="C279" s="30"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="A280" s="28"/>
-      <c r="B280" s="28"/>
-      <c r="C280" s="28"/>
+      <c r="A280" s="30"/>
+      <c r="B280" s="30"/>
+      <c r="C280" s="30"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="A281" s="28"/>
-      <c r="B281" s="28"/>
-      <c r="C281" s="28"/>
+      <c r="A281" s="30"/>
+      <c r="B281" s="30"/>
+      <c r="C281" s="30"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="A282" s="28"/>
-      <c r="B282" s="28"/>
-      <c r="C282" s="28"/>
+      <c r="A282" s="30"/>
+      <c r="B282" s="30"/>
+      <c r="C282" s="30"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="A283" s="28"/>
-      <c r="B283" s="28"/>
-      <c r="C283" s="28"/>
+      <c r="A283" s="30"/>
+      <c r="B283" s="30"/>
+      <c r="C283" s="30"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="A284" s="28"/>
-      <c r="B284" s="28"/>
-      <c r="C284" s="28"/>
+      <c r="A284" s="30"/>
+      <c r="B284" s="30"/>
+      <c r="C284" s="30"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="A285" s="28"/>
-      <c r="B285" s="28"/>
-      <c r="C285" s="28"/>
+      <c r="A285" s="30"/>
+      <c r="B285" s="30"/>
+      <c r="C285" s="30"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="A286" s="28"/>
-      <c r="B286" s="28"/>
-      <c r="C286" s="28"/>
+      <c r="A286" s="30"/>
+      <c r="B286" s="30"/>
+      <c r="C286" s="30"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="A287" s="28"/>
-      <c r="B287" s="28"/>
-      <c r="C287" s="28"/>
+      <c r="A287" s="30"/>
+      <c r="B287" s="30"/>
+      <c r="C287" s="30"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="28"/>
-      <c r="B288" s="28"/>
-      <c r="C288" s="28"/>
+      <c r="A288" s="30"/>
+      <c r="B288" s="30"/>
+      <c r="C288" s="30"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="A289" s="28"/>
-      <c r="B289" s="28"/>
-      <c r="C289" s="28"/>
+      <c r="A289" s="30"/>
+      <c r="B289" s="30"/>
+      <c r="C289" s="30"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="A290" s="28"/>
-      <c r="B290" s="28"/>
-      <c r="C290" s="28"/>
+      <c r="A290" s="30"/>
+      <c r="B290" s="30"/>
+      <c r="C290" s="30"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="A291" s="28"/>
-      <c r="B291" s="28"/>
-      <c r="C291" s="28"/>
+      <c r="A291" s="30"/>
+      <c r="B291" s="30"/>
+      <c r="C291" s="30"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="A292" s="28"/>
-      <c r="B292" s="28"/>
-      <c r="C292" s="28"/>
+      <c r="A292" s="30"/>
+      <c r="B292" s="30"/>
+      <c r="C292" s="30"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="A293" s="28"/>
-      <c r="B293" s="28"/>
-      <c r="C293" s="28"/>
+      <c r="A293" s="30"/>
+      <c r="B293" s="30"/>
+      <c r="C293" s="30"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="A294" s="28"/>
-      <c r="B294" s="28"/>
-      <c r="C294" s="28"/>
+      <c r="A294" s="30"/>
+      <c r="B294" s="30"/>
+      <c r="C294" s="30"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="A295" s="28"/>
-      <c r="B295" s="28"/>
-      <c r="C295" s="28"/>
+      <c r="A295" s="30"/>
+      <c r="B295" s="30"/>
+      <c r="C295" s="30"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="A296" s="28"/>
-      <c r="B296" s="28"/>
-      <c r="C296" s="28"/>
+      <c r="A296" s="30"/>
+      <c r="B296" s="30"/>
+      <c r="C296" s="30"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="A297" s="28"/>
-      <c r="B297" s="28"/>
-      <c r="C297" s="28"/>
+      <c r="A297" s="30"/>
+      <c r="B297" s="30"/>
+      <c r="C297" s="30"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="A298" s="28"/>
-      <c r="B298" s="28"/>
-      <c r="C298" s="28"/>
+      <c r="A298" s="30"/>
+      <c r="B298" s="30"/>
+      <c r="C298" s="30"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="A299" s="28"/>
-      <c r="B299" s="28"/>
-      <c r="C299" s="28"/>
+      <c r="A299" s="30"/>
+      <c r="B299" s="30"/>
+      <c r="C299" s="30"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="A300" s="28"/>
-      <c r="B300" s="28"/>
-      <c r="C300" s="28"/>
+      <c r="A300" s="30"/>
+      <c r="B300" s="30"/>
+      <c r="C300" s="30"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="A301" s="28"/>
-      <c r="B301" s="28"/>
-      <c r="C301" s="28"/>
+      <c r="A301" s="30"/>
+      <c r="B301" s="30"/>
+      <c r="C301" s="30"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="A302" s="28"/>
-      <c r="B302" s="28"/>
-      <c r="C302" s="28"/>
+      <c r="A302" s="30"/>
+      <c r="B302" s="30"/>
+      <c r="C302" s="30"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="A303" s="28"/>
-      <c r="B303" s="28"/>
-      <c r="C303" s="28"/>
+      <c r="A303" s="30"/>
+      <c r="B303" s="30"/>
+      <c r="C303" s="30"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="A304" s="28"/>
-      <c r="B304" s="28"/>
-      <c r="C304" s="28"/>
+      <c r="A304" s="30"/>
+      <c r="B304" s="30"/>
+      <c r="C304" s="30"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="A305" s="28"/>
-      <c r="B305" s="28"/>
-      <c r="C305" s="28"/>
+      <c r="A305" s="30"/>
+      <c r="B305" s="30"/>
+      <c r="C305" s="30"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="A306" s="28"/>
-      <c r="B306" s="28"/>
-      <c r="C306" s="28"/>
+      <c r="A306" s="30"/>
+      <c r="B306" s="30"/>
+      <c r="C306" s="30"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="A307" s="28"/>
-      <c r="B307" s="28"/>
-      <c r="C307" s="28"/>
+      <c r="A307" s="30"/>
+      <c r="B307" s="30"/>
+      <c r="C307" s="30"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="28"/>
-      <c r="B308" s="28"/>
-      <c r="C308" s="28"/>
+      <c r="A308" s="30"/>
+      <c r="B308" s="30"/>
+      <c r="C308" s="30"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="A309" s="28"/>
-      <c r="B309" s="28"/>
-      <c r="C309" s="28"/>
+      <c r="A309" s="30"/>
+      <c r="B309" s="30"/>
+      <c r="C309" s="30"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="A310" s="28"/>
-      <c r="B310" s="28"/>
-      <c r="C310" s="28"/>
+      <c r="A310" s="30"/>
+      <c r="B310" s="30"/>
+      <c r="C310" s="30"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="A311" s="28"/>
-      <c r="B311" s="28"/>
-      <c r="C311" s="28"/>
+      <c r="A311" s="30"/>
+      <c r="B311" s="30"/>
+      <c r="C311" s="30"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="A312" s="28"/>
-      <c r="B312" s="28"/>
-      <c r="C312" s="28"/>
+      <c r="A312" s="30"/>
+      <c r="B312" s="30"/>
+      <c r="C312" s="30"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="A313" s="28"/>
-      <c r="B313" s="28"/>
-      <c r="C313" s="28"/>
+      <c r="A313" s="30"/>
+      <c r="B313" s="30"/>
+      <c r="C313" s="30"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="A314" s="28"/>
-      <c r="B314" s="28"/>
-      <c r="C314" s="28"/>
+      <c r="A314" s="30"/>
+      <c r="B314" s="30"/>
+      <c r="C314" s="30"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="A315" s="28"/>
-      <c r="B315" s="28"/>
-      <c r="C315" s="28"/>
+      <c r="A315" s="30"/>
+      <c r="B315" s="30"/>
+      <c r="C315" s="30"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="A316" s="28"/>
-      <c r="B316" s="28"/>
-      <c r="C316" s="28"/>
+      <c r="A316" s="30"/>
+      <c r="B316" s="30"/>
+      <c r="C316" s="30"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="A317" s="28"/>
-      <c r="B317" s="28"/>
-      <c r="C317" s="28"/>
+      <c r="A317" s="30"/>
+      <c r="B317" s="30"/>
+      <c r="C317" s="30"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="A318" s="28"/>
-      <c r="B318" s="28"/>
-      <c r="C318" s="28"/>
+      <c r="A318" s="30"/>
+      <c r="B318" s="30"/>
+      <c r="C318" s="30"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="A319" s="28"/>
-      <c r="B319" s="28"/>
-      <c r="C319" s="28"/>
+      <c r="A319" s="30"/>
+      <c r="B319" s="30"/>
+      <c r="C319" s="30"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="A320" s="28"/>
-      <c r="B320" s="28"/>
-      <c r="C320" s="28"/>
+      <c r="A320" s="30"/>
+      <c r="B320" s="30"/>
+      <c r="C320" s="30"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="A321" s="28"/>
-      <c r="B321" s="28"/>
-      <c r="C321" s="28"/>
+      <c r="A321" s="30"/>
+      <c r="B321" s="30"/>
+      <c r="C321" s="30"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="A322" s="28"/>
-      <c r="B322" s="28"/>
-      <c r="C322" s="28"/>
+      <c r="A322" s="30"/>
+      <c r="B322" s="30"/>
+      <c r="C322" s="30"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="A323" s="28"/>
-      <c r="B323" s="28"/>
-      <c r="C323" s="28"/>
+      <c r="A323" s="30"/>
+      <c r="B323" s="30"/>
+      <c r="C323" s="30"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="A324" s="28"/>
-      <c r="B324" s="28"/>
-      <c r="C324" s="28"/>
+      <c r="A324" s="30"/>
+      <c r="B324" s="30"/>
+      <c r="C324" s="30"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="A325" s="28"/>
-      <c r="B325" s="28"/>
-      <c r="C325" s="28"/>
+      <c r="A325" s="30"/>
+      <c r="B325" s="30"/>
+      <c r="C325" s="30"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="A326" s="28"/>
-      <c r="B326" s="28"/>
-      <c r="C326" s="28"/>
+      <c r="A326" s="30"/>
+      <c r="B326" s="30"/>
+      <c r="C326" s="30"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="A327" s="28"/>
-      <c r="B327" s="28"/>
-      <c r="C327" s="28"/>
+      <c r="A327" s="30"/>
+      <c r="B327" s="30"/>
+      <c r="C327" s="30"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="28"/>
-      <c r="B328" s="28"/>
-      <c r="C328" s="28"/>
+      <c r="A328" s="30"/>
+      <c r="B328" s="30"/>
+      <c r="C328" s="30"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="A329" s="28"/>
-      <c r="B329" s="28"/>
-      <c r="C329" s="28"/>
+      <c r="A329" s="30"/>
+      <c r="B329" s="30"/>
+      <c r="C329" s="30"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="A330" s="28"/>
-      <c r="B330" s="28"/>
-      <c r="C330" s="28"/>
+      <c r="A330" s="30"/>
+      <c r="B330" s="30"/>
+      <c r="C330" s="30"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="A331" s="28"/>
-      <c r="B331" s="28"/>
-      <c r="C331" s="28"/>
+      <c r="A331" s="30"/>
+      <c r="B331" s="30"/>
+      <c r="C331" s="30"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="A332" s="28"/>
-      <c r="B332" s="28"/>
-      <c r="C332" s="28"/>
+      <c r="A332" s="30"/>
+      <c r="B332" s="30"/>
+      <c r="C332" s="30"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="A333" s="28"/>
-      <c r="B333" s="28"/>
-      <c r="C333" s="28"/>
+      <c r="A333" s="30"/>
+      <c r="B333" s="30"/>
+      <c r="C333" s="30"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="A334" s="28"/>
-      <c r="B334" s="28"/>
-      <c r="C334" s="28"/>
+      <c r="A334" s="30"/>
+      <c r="B334" s="30"/>
+      <c r="C334" s="30"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="A335" s="28"/>
-      <c r="B335" s="28"/>
-      <c r="C335" s="28"/>
+      <c r="A335" s="30"/>
+      <c r="B335" s="30"/>
+      <c r="C335" s="30"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="A336" s="28"/>
-      <c r="B336" s="28"/>
-      <c r="C336" s="28"/>
+      <c r="A336" s="30"/>
+      <c r="B336" s="30"/>
+      <c r="C336" s="30"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="A337" s="28"/>
-      <c r="B337" s="28"/>
-      <c r="C337" s="28"/>
+      <c r="A337" s="30"/>
+      <c r="B337" s="30"/>
+      <c r="C337" s="30"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="A338" s="28"/>
-      <c r="B338" s="28"/>
-      <c r="C338" s="28"/>
+      <c r="A338" s="30"/>
+      <c r="B338" s="30"/>
+      <c r="C338" s="30"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="A339" s="28"/>
-      <c r="B339" s="28"/>
-      <c r="C339" s="28"/>
+      <c r="A339" s="30"/>
+      <c r="B339" s="30"/>
+      <c r="C339" s="30"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="A340" s="28"/>
-      <c r="B340" s="28"/>
-      <c r="C340" s="28"/>
+      <c r="A340" s="30"/>
+      <c r="B340" s="30"/>
+      <c r="C340" s="30"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="A341" s="28"/>
-      <c r="B341" s="28"/>
-      <c r="C341" s="28"/>
+      <c r="A341" s="30"/>
+      <c r="B341" s="30"/>
+      <c r="C341" s="30"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="A342" s="28"/>
-      <c r="B342" s="28"/>
-      <c r="C342" s="28"/>
+      <c r="A342" s="30"/>
+      <c r="B342" s="30"/>
+      <c r="C342" s="30"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="A343" s="28"/>
-      <c r="B343" s="28"/>
-      <c r="C343" s="28"/>
+      <c r="A343" s="30"/>
+      <c r="B343" s="30"/>
+      <c r="C343" s="30"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="A344" s="28"/>
-      <c r="B344" s="28"/>
-      <c r="C344" s="28"/>
+      <c r="A344" s="30"/>
+      <c r="B344" s="30"/>
+      <c r="C344" s="30"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="A345" s="28"/>
-      <c r="B345" s="28"/>
-      <c r="C345" s="28"/>
+      <c r="A345" s="30"/>
+      <c r="B345" s="30"/>
+      <c r="C345" s="30"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="A346" s="28"/>
-      <c r="B346" s="28"/>
-      <c r="C346" s="28"/>
+      <c r="A346" s="30"/>
+      <c r="B346" s="30"/>
+      <c r="C346" s="30"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="A347" s="28"/>
-      <c r="B347" s="28"/>
-      <c r="C347" s="28"/>
+      <c r="A347" s="30"/>
+      <c r="B347" s="30"/>
+      <c r="C347" s="30"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="28"/>
-      <c r="B348" s="28"/>
-      <c r="C348" s="28"/>
+      <c r="A348" s="30"/>
+      <c r="B348" s="30"/>
+      <c r="C348" s="30"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="A349" s="28"/>
-      <c r="B349" s="28"/>
-      <c r="C349" s="28"/>
+      <c r="A349" s="30"/>
+      <c r="B349" s="30"/>
+      <c r="C349" s="30"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="A350" s="28"/>
-      <c r="B350" s="28"/>
-      <c r="C350" s="28"/>
+      <c r="A350" s="30"/>
+      <c r="B350" s="30"/>
+      <c r="C350" s="30"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="A351" s="28"/>
-      <c r="B351" s="28"/>
-      <c r="C351" s="28"/>
+      <c r="A351" s="30"/>
+      <c r="B351" s="30"/>
+      <c r="C351" s="30"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="A352" s="28"/>
-      <c r="B352" s="28"/>
-      <c r="C352" s="28"/>
+      <c r="A352" s="30"/>
+      <c r="B352" s="30"/>
+      <c r="C352" s="30"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="A353" s="28"/>
-      <c r="B353" s="28"/>
-      <c r="C353" s="28"/>
+      <c r="A353" s="30"/>
+      <c r="B353" s="30"/>
+      <c r="C353" s="30"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="A354" s="28"/>
-      <c r="B354" s="28"/>
-      <c r="C354" s="28"/>
+      <c r="A354" s="30"/>
+      <c r="B354" s="30"/>
+      <c r="C354" s="30"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="A355" s="28"/>
-      <c r="B355" s="28"/>
-      <c r="C355" s="28"/>
+      <c r="A355" s="30"/>
+      <c r="B355" s="30"/>
+      <c r="C355" s="30"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="A356" s="28"/>
-      <c r="B356" s="28"/>
-      <c r="C356" s="28"/>
+      <c r="A356" s="30"/>
+      <c r="B356" s="30"/>
+      <c r="C356" s="30"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="A357" s="28"/>
-      <c r="B357" s="28"/>
-      <c r="C357" s="28"/>
+      <c r="A357" s="30"/>
+      <c r="B357" s="30"/>
+      <c r="C357" s="30"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="A358" s="28"/>
-      <c r="B358" s="28"/>
-      <c r="C358" s="28"/>
+      <c r="A358" s="30"/>
+      <c r="B358" s="30"/>
+      <c r="C358" s="30"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="A359" s="28"/>
-      <c r="B359" s="28"/>
-      <c r="C359" s="28"/>
+      <c r="A359" s="30"/>
+      <c r="B359" s="30"/>
+      <c r="C359" s="30"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="A360" s="28"/>
-      <c r="B360" s="28"/>
-      <c r="C360" s="28"/>
+      <c r="A360" s="30"/>
+      <c r="B360" s="30"/>
+      <c r="C360" s="30"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="A361" s="28"/>
-      <c r="B361" s="28"/>
-      <c r="C361" s="28"/>
+      <c r="A361" s="30"/>
+      <c r="B361" s="30"/>
+      <c r="C361" s="30"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="A362" s="28"/>
-      <c r="B362" s="28"/>
-      <c r="C362" s="28"/>
+      <c r="A362" s="30"/>
+      <c r="B362" s="30"/>
+      <c r="C362" s="30"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="A363" s="28"/>
-      <c r="B363" s="28"/>
-      <c r="C363" s="28"/>
+      <c r="A363" s="30"/>
+      <c r="B363" s="30"/>
+      <c r="C363" s="30"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="A364" s="28"/>
-      <c r="B364" s="28"/>
-      <c r="C364" s="28"/>
+      <c r="A364" s="30"/>
+      <c r="B364" s="30"/>
+      <c r="C364" s="30"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="A365" s="28"/>
-      <c r="B365" s="28"/>
-      <c r="C365" s="28"/>
+      <c r="A365" s="30"/>
+      <c r="B365" s="30"/>
+      <c r="C365" s="30"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="A366" s="28"/>
-      <c r="B366" s="28"/>
-      <c r="C366" s="28"/>
+      <c r="A366" s="30"/>
+      <c r="B366" s="30"/>
+      <c r="C366" s="30"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="A367" s="28"/>
-      <c r="B367" s="28"/>
-      <c r="C367" s="28"/>
+      <c r="A367" s="30"/>
+      <c r="B367" s="30"/>
+      <c r="C367" s="30"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="28"/>
-      <c r="B368" s="28"/>
-      <c r="C368" s="28"/>
+      <c r="A368" s="30"/>
+      <c r="B368" s="30"/>
+      <c r="C368" s="30"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="A369" s="28"/>
-      <c r="B369" s="28"/>
-      <c r="C369" s="28"/>
+      <c r="A369" s="30"/>
+      <c r="B369" s="30"/>
+      <c r="C369" s="30"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="A370" s="28"/>
-      <c r="B370" s="28"/>
-      <c r="C370" s="28"/>
+      <c r="A370" s="30"/>
+      <c r="B370" s="30"/>
+      <c r="C370" s="30"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="A371" s="28"/>
-      <c r="B371" s="28"/>
-      <c r="C371" s="28"/>
+      <c r="A371" s="30"/>
+      <c r="B371" s="30"/>
+      <c r="C371" s="30"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="A372" s="28"/>
-      <c r="B372" s="28"/>
-      <c r="C372" s="28"/>
+      <c r="A372" s="30"/>
+      <c r="B372" s="30"/>
+      <c r="C372" s="30"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="A373" s="28"/>
-      <c r="B373" s="28"/>
-      <c r="C373" s="28"/>
+      <c r="A373" s="30"/>
+      <c r="B373" s="30"/>
+      <c r="C373" s="30"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="A374" s="28"/>
-      <c r="B374" s="28"/>
-      <c r="C374" s="28"/>
+      <c r="A374" s="30"/>
+      <c r="B374" s="30"/>
+      <c r="C374" s="30"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="A375" s="28"/>
-      <c r="B375" s="28"/>
-      <c r="C375" s="28"/>
+      <c r="A375" s="30"/>
+      <c r="B375" s="30"/>
+      <c r="C375" s="30"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="A376" s="28"/>
-      <c r="B376" s="28"/>
-      <c r="C376" s="28"/>
+      <c r="A376" s="30"/>
+      <c r="B376" s="30"/>
+      <c r="C376" s="30"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="A377" s="28"/>
-      <c r="B377" s="28"/>
-      <c r="C377" s="28"/>
+      <c r="A377" s="30"/>
+      <c r="B377" s="30"/>
+      <c r="C377" s="30"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="A378" s="28"/>
-      <c r="B378" s="28"/>
-      <c r="C378" s="28"/>
+      <c r="A378" s="30"/>
+      <c r="B378" s="30"/>
+      <c r="C378" s="30"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="A379" s="28"/>
-      <c r="B379" s="28"/>
-      <c r="C379" s="28"/>
+      <c r="A379" s="30"/>
+      <c r="B379" s="30"/>
+      <c r="C379" s="30"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="A380" s="28"/>
-      <c r="B380" s="28"/>
-      <c r="C380" s="28"/>
+      <c r="A380" s="30"/>
+      <c r="B380" s="30"/>
+      <c r="C380" s="30"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="A381" s="28"/>
-      <c r="B381" s="28"/>
-      <c r="C381" s="28"/>
+      <c r="A381" s="30"/>
+      <c r="B381" s="30"/>
+      <c r="C381" s="30"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="A382" s="28"/>
-      <c r="B382" s="28"/>
-      <c r="C382" s="28"/>
+      <c r="A382" s="30"/>
+      <c r="B382" s="30"/>
+      <c r="C382" s="30"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="A383" s="28"/>
-      <c r="B383" s="28"/>
-      <c r="C383" s="28"/>
+      <c r="A383" s="30"/>
+      <c r="B383" s="30"/>
+      <c r="C383" s="30"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="A384" s="28"/>
-      <c r="B384" s="28"/>
-      <c r="C384" s="28"/>
+      <c r="A384" s="30"/>
+      <c r="B384" s="30"/>
+      <c r="C384" s="30"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="A385" s="28"/>
-      <c r="B385" s="28"/>
-      <c r="C385" s="28"/>
+      <c r="A385" s="30"/>
+      <c r="B385" s="30"/>
+      <c r="C385" s="30"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="A386" s="28"/>
-      <c r="B386" s="28"/>
-      <c r="C386" s="28"/>
+      <c r="A386" s="30"/>
+      <c r="B386" s="30"/>
+      <c r="C386" s="30"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="A387" s="28"/>
-      <c r="B387" s="28"/>
-      <c r="C387" s="28"/>
+      <c r="A387" s="30"/>
+      <c r="B387" s="30"/>
+      <c r="C387" s="30"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="A388" s="28"/>
-      <c r="B388" s="28"/>
-      <c r="C388" s="28"/>
+      <c r="A388" s="30"/>
+      <c r="B388" s="30"/>
+      <c r="C388" s="30"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="A389" s="28"/>
-      <c r="B389" s="28"/>
-      <c r="C389" s="28"/>
+      <c r="A389" s="30"/>
+      <c r="B389" s="30"/>
+      <c r="C389" s="30"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="A390" s="28"/>
-      <c r="B390" s="28"/>
-      <c r="C390" s="28"/>
+      <c r="A390" s="30"/>
+      <c r="B390" s="30"/>
+      <c r="C390" s="30"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="A391" s="28"/>
-      <c r="B391" s="28"/>
-      <c r="C391" s="28"/>
+      <c r="A391" s="30"/>
+      <c r="B391" s="30"/>
+      <c r="C391" s="30"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="A392" s="28"/>
-      <c r="B392" s="28"/>
-      <c r="C392" s="28"/>
+      <c r="A392" s="30"/>
+      <c r="B392" s="30"/>
+      <c r="C392" s="30"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="A393" s="28"/>
-      <c r="B393" s="28"/>
-      <c r="C393" s="28"/>
+      <c r="A393" s="30"/>
+      <c r="B393" s="30"/>
+      <c r="C393" s="30"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="A394" s="28"/>
-      <c r="B394" s="28"/>
-      <c r="C394" s="28"/>
+      <c r="A394" s="30"/>
+      <c r="B394" s="30"/>
+      <c r="C394" s="30"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="A395" s="28"/>
-      <c r="B395" s="28"/>
-      <c r="C395" s="28"/>
+      <c r="A395" s="30"/>
+      <c r="B395" s="30"/>
+      <c r="C395" s="30"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="A396" s="28"/>
-      <c r="B396" s="28"/>
-      <c r="C396" s="28"/>
+      <c r="A396" s="30"/>
+      <c r="B396" s="30"/>
+      <c r="C396" s="30"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="A397" s="28"/>
-      <c r="B397" s="28"/>
-      <c r="C397" s="28"/>
+      <c r="A397" s="30"/>
+      <c r="B397" s="30"/>
+      <c r="C397" s="30"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="A398" s="28"/>
-      <c r="B398" s="28"/>
-      <c r="C398" s="28"/>
+      <c r="A398" s="30"/>
+      <c r="B398" s="30"/>
+      <c r="C398" s="30"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="A399" s="28"/>
-      <c r="B399" s="28"/>
-      <c r="C399" s="28"/>
+      <c r="A399" s="30"/>
+      <c r="B399" s="30"/>
+      <c r="C399" s="30"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="A400" s="28"/>
-      <c r="B400" s="28"/>
-      <c r="C400" s="28"/>
+      <c r="A400" s="30"/>
+      <c r="B400" s="30"/>
+      <c r="C400" s="30"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="A401" s="28"/>
-      <c r="B401" s="28"/>
-      <c r="C401" s="28"/>
+      <c r="A401" s="30"/>
+      <c r="B401" s="30"/>
+      <c r="C401" s="30"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="A402" s="28"/>
-      <c r="B402" s="28"/>
-      <c r="C402" s="28"/>
+      <c r="A402" s="30"/>
+      <c r="B402" s="30"/>
+      <c r="C402" s="30"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="A403" s="28"/>
-      <c r="B403" s="28"/>
-      <c r="C403" s="28"/>
+      <c r="A403" s="30"/>
+      <c r="B403" s="30"/>
+      <c r="C403" s="30"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="A404" s="28"/>
-      <c r="B404" s="28"/>
-      <c r="C404" s="28"/>
+      <c r="A404" s="30"/>
+      <c r="B404" s="30"/>
+      <c r="C404" s="30"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="A405" s="28"/>
-      <c r="B405" s="28"/>
-      <c r="C405" s="28"/>
+      <c r="A405" s="30"/>
+      <c r="B405" s="30"/>
+      <c r="C405" s="30"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="A406" s="28"/>
-      <c r="B406" s="28"/>
-      <c r="C406" s="28"/>
+      <c r="A406" s="30"/>
+      <c r="B406" s="30"/>
+      <c r="C406" s="30"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="A407" s="28"/>
-      <c r="B407" s="28"/>
-      <c r="C407" s="28"/>
+      <c r="A407" s="30"/>
+      <c r="B407" s="30"/>
+      <c r="C407" s="30"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="A408" s="28"/>
-      <c r="B408" s="28"/>
-      <c r="C408" s="28"/>
+      <c r="A408" s="30"/>
+      <c r="B408" s="30"/>
+      <c r="C408" s="30"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="A409" s="28"/>
-      <c r="B409" s="28"/>
-      <c r="C409" s="28"/>
+      <c r="A409" s="30"/>
+      <c r="B409" s="30"/>
+      <c r="C409" s="30"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="A410" s="28"/>
-      <c r="B410" s="28"/>
-      <c r="C410" s="28"/>
+      <c r="A410" s="30"/>
+      <c r="B410" s="30"/>
+      <c r="C410" s="30"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="A411" s="28"/>
-      <c r="B411" s="28"/>
-      <c r="C411" s="28"/>
+      <c r="A411" s="30"/>
+      <c r="B411" s="30"/>
+      <c r="C411" s="30"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="A412" s="28"/>
-      <c r="B412" s="28"/>
-      <c r="C412" s="28"/>
+      <c r="A412" s="30"/>
+      <c r="B412" s="30"/>
+      <c r="C412" s="30"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="A413" s="28"/>
-      <c r="B413" s="28"/>
-      <c r="C413" s="28"/>
+      <c r="A413" s="30"/>
+      <c r="B413" s="30"/>
+      <c r="C413" s="30"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="A414" s="28"/>
-      <c r="B414" s="28"/>
-      <c r="C414" s="28"/>
+      <c r="A414" s="30"/>
+      <c r="B414" s="30"/>
+      <c r="C414" s="30"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="A415" s="28"/>
-      <c r="B415" s="28"/>
-      <c r="C415" s="28"/>
+      <c r="A415" s="30"/>
+      <c r="B415" s="30"/>
+      <c r="C415" s="30"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="A416" s="28"/>
-      <c r="B416" s="28"/>
-      <c r="C416" s="28"/>
+      <c r="A416" s="30"/>
+      <c r="B416" s="30"/>
+      <c r="C416" s="30"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="A417" s="28"/>
-      <c r="B417" s="28"/>
-      <c r="C417" s="28"/>
+      <c r="A417" s="30"/>
+      <c r="B417" s="30"/>
+      <c r="C417" s="30"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="A418" s="28"/>
-      <c r="B418" s="28"/>
-      <c r="C418" s="28"/>
+      <c r="A418" s="30"/>
+      <c r="B418" s="30"/>
+      <c r="C418" s="30"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="A419" s="28"/>
-      <c r="B419" s="28"/>
-      <c r="C419" s="28"/>
+      <c r="A419" s="30"/>
+      <c r="B419" s="30"/>
+      <c r="C419" s="30"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="A420" s="28"/>
-      <c r="B420" s="28"/>
-      <c r="C420" s="28"/>
+      <c r="A420" s="30"/>
+      <c r="B420" s="30"/>
+      <c r="C420" s="30"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="A421" s="28"/>
-      <c r="B421" s="28"/>
-      <c r="C421" s="28"/>
+      <c r="A421" s="30"/>
+      <c r="B421" s="30"/>
+      <c r="C421" s="30"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="A422" s="28"/>
-      <c r="B422" s="28"/>
-      <c r="C422" s="28"/>
+      <c r="A422" s="30"/>
+      <c r="B422" s="30"/>
+      <c r="C422" s="30"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="A423" s="28"/>
-      <c r="B423" s="28"/>
-      <c r="C423" s="28"/>
+      <c r="A423" s="30"/>
+      <c r="B423" s="30"/>
+      <c r="C423" s="30"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="A424" s="28"/>
-      <c r="B424" s="28"/>
-      <c r="C424" s="28"/>
+      <c r="A424" s="30"/>
+      <c r="B424" s="30"/>
+      <c r="C424" s="30"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="A425" s="28"/>
-      <c r="B425" s="28"/>
-      <c r="C425" s="28"/>
+      <c r="A425" s="30"/>
+      <c r="B425" s="30"/>
+      <c r="C425" s="30"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="A426" s="28"/>
-      <c r="B426" s="28"/>
-      <c r="C426" s="28"/>
+      <c r="A426" s="30"/>
+      <c r="B426" s="30"/>
+      <c r="C426" s="30"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="A427" s="28"/>
-      <c r="B427" s="28"/>
-      <c r="C427" s="28"/>
+      <c r="A427" s="30"/>
+      <c r="B427" s="30"/>
+      <c r="C427" s="30"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="A428" s="28"/>
-      <c r="B428" s="28"/>
-      <c r="C428" s="28"/>
+      <c r="A428" s="30"/>
+      <c r="B428" s="30"/>
+      <c r="C428" s="30"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="A429" s="28"/>
-      <c r="B429" s="28"/>
-      <c r="C429" s="28"/>
+      <c r="A429" s="30"/>
+      <c r="B429" s="30"/>
+      <c r="C429" s="30"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="A430" s="28"/>
-      <c r="B430" s="28"/>
-      <c r="C430" s="28"/>
+      <c r="A430" s="30"/>
+      <c r="B430" s="30"/>
+      <c r="C430" s="30"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="A431" s="28"/>
-      <c r="B431" s="28"/>
-      <c r="C431" s="28"/>
+      <c r="A431" s="30"/>
+      <c r="B431" s="30"/>
+      <c r="C431" s="30"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="A432" s="28"/>
-      <c r="B432" s="28"/>
-      <c r="C432" s="28"/>
+      <c r="A432" s="30"/>
+      <c r="B432" s="30"/>
+      <c r="C432" s="30"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="A433" s="28"/>
-      <c r="B433" s="28"/>
-      <c r="C433" s="28"/>
+      <c r="A433" s="30"/>
+      <c r="B433" s="30"/>
+      <c r="C433" s="30"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="A434" s="28"/>
-      <c r="B434" s="28"/>
-      <c r="C434" s="28"/>
+      <c r="A434" s="30"/>
+      <c r="B434" s="30"/>
+      <c r="C434" s="30"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="28"/>
-      <c r="B435" s="28"/>
-      <c r="C435" s="28"/>
+      <c r="A435" s="30"/>
+      <c r="B435" s="30"/>
+      <c r="C435" s="30"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="28"/>
-      <c r="B436" s="28"/>
-      <c r="C436" s="28"/>
+      <c r="A436" s="30"/>
+      <c r="B436" s="30"/>
+      <c r="C436" s="30"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="28"/>
-      <c r="B437" s="28"/>
-      <c r="C437" s="28"/>
+      <c r="A437" s="30"/>
+      <c r="B437" s="30"/>
+      <c r="C437" s="30"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="28"/>
-      <c r="B438" s="28"/>
-      <c r="C438" s="28"/>
+      <c r="A438" s="30"/>
+      <c r="B438" s="30"/>
+      <c r="C438" s="30"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="28"/>
-      <c r="B439" s="28"/>
-      <c r="C439" s="28"/>
+      <c r="A439" s="30"/>
+      <c r="B439" s="30"/>
+      <c r="C439" s="30"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="28"/>
-      <c r="B440" s="28"/>
-      <c r="C440" s="28"/>
+      <c r="A440" s="30"/>
+      <c r="B440" s="30"/>
+      <c r="C440" s="30"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="A441" s="28"/>
-      <c r="B441" s="28"/>
-      <c r="C441" s="28"/>
+      <c r="A441" s="30"/>
+      <c r="B441" s="30"/>
+      <c r="C441" s="30"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="A442" s="28"/>
-      <c r="B442" s="28"/>
-      <c r="C442" s="28"/>
+      <c r="A442" s="30"/>
+      <c r="B442" s="30"/>
+      <c r="C442" s="30"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="28"/>
-      <c r="B443" s="28"/>
-      <c r="C443" s="28"/>
+      <c r="A443" s="30"/>
+      <c r="B443" s="30"/>
+      <c r="C443" s="30"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="28"/>
-      <c r="B444" s="28"/>
-      <c r="C444" s="28"/>
+      <c r="A444" s="30"/>
+      <c r="B444" s="30"/>
+      <c r="C444" s="30"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="28"/>
-      <c r="B445" s="28"/>
-      <c r="C445" s="28"/>
+      <c r="A445" s="30"/>
+      <c r="B445" s="30"/>
+      <c r="C445" s="30"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="28"/>
-      <c r="B446" s="28"/>
-      <c r="C446" s="28"/>
+      <c r="A446" s="30"/>
+      <c r="B446" s="30"/>
+      <c r="C446" s="30"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="A447" s="28"/>
-      <c r="B447" s="28"/>
-      <c r="C447" s="28"/>
+      <c r="A447" s="30"/>
+      <c r="B447" s="30"/>
+      <c r="C447" s="30"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="A448" s="28"/>
-      <c r="B448" s="28"/>
-      <c r="C448" s="28"/>
+      <c r="A448" s="30"/>
+      <c r="B448" s="30"/>
+      <c r="C448" s="30"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="A449" s="28"/>
-      <c r="B449" s="28"/>
-      <c r="C449" s="28"/>
+      <c r="A449" s="30"/>
+      <c r="B449" s="30"/>
+      <c r="C449" s="30"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="A450" s="28"/>
-      <c r="B450" s="28"/>
-      <c r="C450" s="28"/>
+      <c r="A450" s="30"/>
+      <c r="B450" s="30"/>
+      <c r="C450" s="30"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="A451" s="28"/>
-      <c r="B451" s="28"/>
-      <c r="C451" s="28"/>
+      <c r="A451" s="30"/>
+      <c r="B451" s="30"/>
+      <c r="C451" s="30"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="A452" s="28"/>
-      <c r="B452" s="28"/>
-      <c r="C452" s="28"/>
+      <c r="A452" s="30"/>
+      <c r="B452" s="30"/>
+      <c r="C452" s="30"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="28"/>
-      <c r="B453" s="28"/>
-      <c r="C453" s="28"/>
+      <c r="A453" s="30"/>
+      <c r="B453" s="30"/>
+      <c r="C453" s="30"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="28"/>
-      <c r="B454" s="28"/>
-      <c r="C454" s="28"/>
+      <c r="A454" s="30"/>
+      <c r="B454" s="30"/>
+      <c r="C454" s="30"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="28"/>
-      <c r="B455" s="28"/>
-      <c r="C455" s="28"/>
+      <c r="A455" s="30"/>
+      <c r="B455" s="30"/>
+      <c r="C455" s="30"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="28"/>
-      <c r="B456" s="28"/>
-      <c r="C456" s="28"/>
+      <c r="A456" s="30"/>
+      <c r="B456" s="30"/>
+      <c r="C456" s="30"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="A457" s="28"/>
-      <c r="B457" s="28"/>
-      <c r="C457" s="28"/>
+      <c r="A457" s="30"/>
+      <c r="B457" s="30"/>
+      <c r="C457" s="30"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="A458" s="28"/>
-      <c r="B458" s="28"/>
-      <c r="C458" s="28"/>
+      <c r="A458" s="30"/>
+      <c r="B458" s="30"/>
+      <c r="C458" s="30"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="A459" s="28"/>
-      <c r="B459" s="28"/>
-      <c r="C459" s="28"/>
+      <c r="A459" s="30"/>
+      <c r="B459" s="30"/>
+      <c r="C459" s="30"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="A460" s="28"/>
-      <c r="B460" s="28"/>
-      <c r="C460" s="28"/>
+      <c r="A460" s="30"/>
+      <c r="B460" s="30"/>
+      <c r="C460" s="30"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="A461" s="28"/>
-      <c r="B461" s="28"/>
-      <c r="C461" s="28"/>
+      <c r="A461" s="30"/>
+      <c r="B461" s="30"/>
+      <c r="C461" s="30"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="A462" s="28"/>
-      <c r="B462" s="28"/>
-      <c r="C462" s="28"/>
+      <c r="A462" s="30"/>
+      <c r="B462" s="30"/>
+      <c r="C462" s="30"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="A463" s="28"/>
-      <c r="B463" s="28"/>
-      <c r="C463" s="28"/>
+      <c r="A463" s="30"/>
+      <c r="B463" s="30"/>
+      <c r="C463" s="30"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="A464" s="28"/>
-      <c r="B464" s="28"/>
-      <c r="C464" s="28"/>
+      <c r="A464" s="30"/>
+      <c r="B464" s="30"/>
+      <c r="C464" s="30"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="A465" s="28"/>
-      <c r="B465" s="28"/>
-      <c r="C465" s="28"/>
+      <c r="A465" s="30"/>
+      <c r="B465" s="30"/>
+      <c r="C465" s="30"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="A466" s="28"/>
-      <c r="B466" s="28"/>
-      <c r="C466" s="28"/>
+      <c r="A466" s="30"/>
+      <c r="B466" s="30"/>
+      <c r="C466" s="30"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="A467" s="28"/>
-      <c r="B467" s="28"/>
-      <c r="C467" s="28"/>
+      <c r="A467" s="30"/>
+      <c r="B467" s="30"/>
+      <c r="C467" s="30"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="A468" s="28"/>
-      <c r="B468" s="28"/>
-      <c r="C468" s="28"/>
+      <c r="A468" s="30"/>
+      <c r="B468" s="30"/>
+      <c r="C468" s="30"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="A469" s="28"/>
-      <c r="B469" s="28"/>
-      <c r="C469" s="28"/>
+      <c r="A469" s="30"/>
+      <c r="B469" s="30"/>
+      <c r="C469" s="30"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="A470" s="28"/>
-      <c r="B470" s="28"/>
-      <c r="C470" s="28"/>
+      <c r="A470" s="30"/>
+      <c r="B470" s="30"/>
+      <c r="C470" s="30"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="A471" s="28"/>
-      <c r="B471" s="28"/>
-      <c r="C471" s="28"/>
+      <c r="A471" s="30"/>
+      <c r="B471" s="30"/>
+      <c r="C471" s="30"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="A472" s="28"/>
-      <c r="B472" s="28"/>
-      <c r="C472" s="28"/>
+      <c r="A472" s="30"/>
+      <c r="B472" s="30"/>
+      <c r="C472" s="30"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="A473" s="28"/>
-      <c r="B473" s="28"/>
-      <c r="C473" s="28"/>
+      <c r="A473" s="30"/>
+      <c r="B473" s="30"/>
+      <c r="C473" s="30"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="A474" s="28"/>
-      <c r="B474" s="28"/>
-      <c r="C474" s="28"/>
+      <c r="A474" s="30"/>
+      <c r="B474" s="30"/>
+      <c r="C474" s="30"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="A475" s="28"/>
-      <c r="B475" s="28"/>
-      <c r="C475" s="28"/>
+      <c r="A475" s="30"/>
+      <c r="B475" s="30"/>
+      <c r="C475" s="30"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="A476" s="28"/>
-      <c r="B476" s="28"/>
-      <c r="C476" s="28"/>
+      <c r="A476" s="30"/>
+      <c r="B476" s="30"/>
+      <c r="C476" s="30"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="A477" s="28"/>
-      <c r="B477" s="28"/>
-      <c r="C477" s="28"/>
+      <c r="A477" s="30"/>
+      <c r="B477" s="30"/>
+      <c r="C477" s="30"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="A478" s="28"/>
-      <c r="B478" s="28"/>
-      <c r="C478" s="28"/>
+      <c r="A478" s="30"/>
+      <c r="B478" s="30"/>
+      <c r="C478" s="30"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="A479" s="28"/>
-      <c r="B479" s="28"/>
-      <c r="C479" s="28"/>
+      <c r="A479" s="30"/>
+      <c r="B479" s="30"/>
+      <c r="C479" s="30"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="A480" s="28"/>
-      <c r="B480" s="28"/>
-      <c r="C480" s="28"/>
+      <c r="A480" s="30"/>
+      <c r="B480" s="30"/>
+      <c r="C480" s="30"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="A481" s="28"/>
-      <c r="B481" s="28"/>
-      <c r="C481" s="28"/>
+      <c r="A481" s="30"/>
+      <c r="B481" s="30"/>
+      <c r="C481" s="30"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="A482" s="28"/>
-      <c r="B482" s="28"/>
-      <c r="C482" s="28"/>
+      <c r="A482" s="30"/>
+      <c r="B482" s="30"/>
+      <c r="C482" s="30"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="A483" s="28"/>
-      <c r="B483" s="28"/>
-      <c r="C483" s="28"/>
+      <c r="A483" s="30"/>
+      <c r="B483" s="30"/>
+      <c r="C483" s="30"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="A484" s="28"/>
-      <c r="B484" s="28"/>
-      <c r="C484" s="28"/>
+      <c r="A484" s="30"/>
+      <c r="B484" s="30"/>
+      <c r="C484" s="30"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="A485" s="28"/>
-      <c r="B485" s="28"/>
-      <c r="C485" s="28"/>
+      <c r="A485" s="30"/>
+      <c r="B485" s="30"/>
+      <c r="C485" s="30"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="A486" s="28"/>
-      <c r="B486" s="28"/>
-      <c r="C486" s="28"/>
+      <c r="A486" s="30"/>
+      <c r="B486" s="30"/>
+      <c r="C486" s="30"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="A487" s="28"/>
-      <c r="B487" s="28"/>
-      <c r="C487" s="28"/>
+      <c r="A487" s="30"/>
+      <c r="B487" s="30"/>
+      <c r="C487" s="30"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="A488" s="28"/>
-      <c r="B488" s="28"/>
-      <c r="C488" s="28"/>
+      <c r="A488" s="30"/>
+      <c r="B488" s="30"/>
+      <c r="C488" s="30"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="A489" s="28"/>
-      <c r="B489" s="28"/>
-      <c r="C489" s="28"/>
+      <c r="A489" s="30"/>
+      <c r="B489" s="30"/>
+      <c r="C489" s="30"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="A490" s="28"/>
-      <c r="B490" s="28"/>
-      <c r="C490" s="28"/>
+      <c r="A490" s="30"/>
+      <c r="B490" s="30"/>
+      <c r="C490" s="30"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="A491" s="28"/>
-      <c r="B491" s="28"/>
-      <c r="C491" s="28"/>
+      <c r="A491" s="30"/>
+      <c r="B491" s="30"/>
+      <c r="C491" s="30"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="A492" s="28"/>
-      <c r="B492" s="28"/>
-      <c r="C492" s="28"/>
+      <c r="A492" s="30"/>
+      <c r="B492" s="30"/>
+      <c r="C492" s="30"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="A493" s="28"/>
-      <c r="B493" s="28"/>
-      <c r="C493" s="28"/>
+      <c r="A493" s="30"/>
+      <c r="B493" s="30"/>
+      <c r="C493" s="30"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="A494" s="28"/>
-      <c r="B494" s="28"/>
-      <c r="C494" s="28"/>
+      <c r="A494" s="30"/>
+      <c r="B494" s="30"/>
+      <c r="C494" s="30"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="A495" s="28"/>
-      <c r="B495" s="28"/>
-      <c r="C495" s="28"/>
+      <c r="A495" s="30"/>
+      <c r="B495" s="30"/>
+      <c r="C495" s="30"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="A496" s="28"/>
-      <c r="B496" s="28"/>
-      <c r="C496" s="28"/>
+      <c r="A496" s="30"/>
+      <c r="B496" s="30"/>
+      <c r="C496" s="30"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="A497" s="28"/>
-      <c r="B497" s="28"/>
-      <c r="C497" s="28"/>
+      <c r="A497" s="30"/>
+      <c r="B497" s="30"/>
+      <c r="C497" s="30"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="A498" s="28"/>
-      <c r="B498" s="28"/>
-      <c r="C498" s="28"/>
+      <c r="A498" s="30"/>
+      <c r="B498" s="30"/>
+      <c r="C498" s="30"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="A499" s="28"/>
-      <c r="B499" s="28"/>
-      <c r="C499" s="28"/>
+      <c r="A499" s="30"/>
+      <c r="B499" s="30"/>
+      <c r="C499" s="30"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="A500" s="28"/>
-      <c r="B500" s="28"/>
-      <c r="C500" s="28"/>
+      <c r="A500" s="30"/>
+      <c r="B500" s="30"/>
+      <c r="C500" s="30"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="A501" s="28"/>
-      <c r="B501" s="28"/>
-      <c r="C501" s="28"/>
+      <c r="A501" s="30"/>
+      <c r="B501" s="30"/>
+      <c r="C501" s="30"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="A502" s="28"/>
-      <c r="B502" s="28"/>
-      <c r="C502" s="28"/>
+      <c r="A502" s="30"/>
+      <c r="B502" s="30"/>
+      <c r="C502" s="30"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="A503" s="28"/>
-      <c r="B503" s="28"/>
-      <c r="C503" s="28"/>
+      <c r="A503" s="30"/>
+      <c r="B503" s="30"/>
+      <c r="C503" s="30"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="A504" s="28"/>
-      <c r="B504" s="28"/>
-      <c r="C504" s="28"/>
+      <c r="A504" s="30"/>
+      <c r="B504" s="30"/>
+      <c r="C504" s="30"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="A505" s="28"/>
-      <c r="B505" s="28"/>
-      <c r="C505" s="28"/>
+      <c r="A505" s="30"/>
+      <c r="B505" s="30"/>
+      <c r="C505" s="30"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="A506" s="28"/>
-      <c r="B506" s="28"/>
-      <c r="C506" s="28"/>
+      <c r="A506" s="30"/>
+      <c r="B506" s="30"/>
+      <c r="C506" s="30"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="A507" s="28"/>
-      <c r="B507" s="28"/>
-      <c r="C507" s="28"/>
+      <c r="A507" s="30"/>
+      <c r="B507" s="30"/>
+      <c r="C507" s="30"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="A508" s="28"/>
-      <c r="B508" s="28"/>
-      <c r="C508" s="28"/>
+      <c r="A508" s="30"/>
+      <c r="B508" s="30"/>
+      <c r="C508" s="30"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="A509" s="28"/>
-      <c r="B509" s="28"/>
-      <c r="C509" s="28"/>
+      <c r="A509" s="30"/>
+      <c r="B509" s="30"/>
+      <c r="C509" s="30"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="A510" s="28"/>
-      <c r="B510" s="28"/>
-      <c r="C510" s="28"/>
+      <c r="A510" s="30"/>
+      <c r="B510" s="30"/>
+      <c r="C510" s="30"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="A511" s="28"/>
-      <c r="B511" s="28"/>
-      <c r="C511" s="28"/>
+      <c r="A511" s="30"/>
+      <c r="B511" s="30"/>
+      <c r="C511" s="30"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="A512" s="28"/>
-      <c r="B512" s="28"/>
-      <c r="C512" s="28"/>
+      <c r="A512" s="30"/>
+      <c r="B512" s="30"/>
+      <c r="C512" s="30"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="A513" s="28"/>
-      <c r="B513" s="28"/>
-      <c r="C513" s="28"/>
+      <c r="A513" s="30"/>
+      <c r="B513" s="30"/>
+      <c r="C513" s="30"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="A514" s="28"/>
-      <c r="B514" s="28"/>
-      <c r="C514" s="28"/>
+      <c r="A514" s="30"/>
+      <c r="B514" s="30"/>
+      <c r="C514" s="30"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="A515" s="28"/>
-      <c r="B515" s="28"/>
-      <c r="C515" s="28"/>
+      <c r="A515" s="30"/>
+      <c r="B515" s="30"/>
+      <c r="C515" s="30"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="A516" s="28"/>
-      <c r="B516" s="28"/>
-      <c r="C516" s="28"/>
+      <c r="A516" s="30"/>
+      <c r="B516" s="30"/>
+      <c r="C516" s="30"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="A517" s="28"/>
-      <c r="B517" s="28"/>
-      <c r="C517" s="28"/>
+      <c r="A517" s="30"/>
+      <c r="B517" s="30"/>
+      <c r="C517" s="30"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="A518" s="28"/>
-      <c r="B518" s="28"/>
-      <c r="C518" s="28"/>
+      <c r="A518" s="30"/>
+      <c r="B518" s="30"/>
+      <c r="C518" s="30"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="A519" s="28"/>
-      <c r="B519" s="28"/>
-      <c r="C519" s="28"/>
+      <c r="A519" s="30"/>
+      <c r="B519" s="30"/>
+      <c r="C519" s="30"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="A520" s="28"/>
-      <c r="B520" s="28"/>
-      <c r="C520" s="28"/>
+      <c r="A520" s="30"/>
+      <c r="B520" s="30"/>
+      <c r="C520" s="30"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="A521" s="28"/>
-      <c r="B521" s="28"/>
-      <c r="C521" s="28"/>
+      <c r="A521" s="30"/>
+      <c r="B521" s="30"/>
+      <c r="C521" s="30"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="A522" s="28"/>
-      <c r="B522" s="28"/>
-      <c r="C522" s="28"/>
+      <c r="A522" s="30"/>
+      <c r="B522" s="30"/>
+      <c r="C522" s="30"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="A523" s="28"/>
-      <c r="B523" s="28"/>
-      <c r="C523" s="28"/>
+      <c r="A523" s="30"/>
+      <c r="B523" s="30"/>
+      <c r="C523" s="30"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="A524" s="28"/>
-      <c r="B524" s="28"/>
-      <c r="C524" s="28"/>
+      <c r="A524" s="30"/>
+      <c r="B524" s="30"/>
+      <c r="C524" s="30"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="A525" s="28"/>
-      <c r="B525" s="28"/>
-      <c r="C525" s="28"/>
+      <c r="A525" s="30"/>
+      <c r="B525" s="30"/>
+      <c r="C525" s="30"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="A526" s="28"/>
-      <c r="B526" s="28"/>
-      <c r="C526" s="28"/>
+      <c r="A526" s="30"/>
+      <c r="B526" s="30"/>
+      <c r="C526" s="30"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="A527" s="28"/>
-      <c r="B527" s="28"/>
-      <c r="C527" s="28"/>
+      <c r="A527" s="30"/>
+      <c r="B527" s="30"/>
+      <c r="C527" s="30"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="A528" s="28"/>
-      <c r="B528" s="28"/>
-      <c r="C528" s="28"/>
+      <c r="A528" s="30"/>
+      <c r="B528" s="30"/>
+      <c r="C528" s="30"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="A529" s="28"/>
-      <c r="B529" s="28"/>
-      <c r="C529" s="28"/>
+      <c r="A529" s="30"/>
+      <c r="B529" s="30"/>
+      <c r="C529" s="30"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="A530" s="28"/>
-      <c r="B530" s="28"/>
-      <c r="C530" s="28"/>
+      <c r="A530" s="30"/>
+      <c r="B530" s="30"/>
+      <c r="C530" s="30"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="A531" s="28"/>
-      <c r="B531" s="28"/>
-      <c r="C531" s="28"/>
+      <c r="A531" s="30"/>
+      <c r="B531" s="30"/>
+      <c r="C531" s="30"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="A532" s="28"/>
-      <c r="B532" s="28"/>
-      <c r="C532" s="28"/>
+      <c r="A532" s="30"/>
+      <c r="B532" s="30"/>
+      <c r="C532" s="30"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="A533" s="28"/>
-      <c r="B533" s="28"/>
-      <c r="C533" s="28"/>
+      <c r="A533" s="30"/>
+      <c r="B533" s="30"/>
+      <c r="C533" s="30"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="A534" s="28"/>
-      <c r="B534" s="28"/>
-      <c r="C534" s="28"/>
+      <c r="A534" s="30"/>
+      <c r="B534" s="30"/>
+      <c r="C534" s="30"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="A535" s="28"/>
-      <c r="B535" s="28"/>
-      <c r="C535" s="28"/>
+      <c r="A535" s="30"/>
+      <c r="B535" s="30"/>
+      <c r="C535" s="30"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="A536" s="28"/>
-      <c r="B536" s="28"/>
-      <c r="C536" s="28"/>
+      <c r="A536" s="30"/>
+      <c r="B536" s="30"/>
+      <c r="C536" s="30"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="A537" s="28"/>
-      <c r="B537" s="28"/>
-      <c r="C537" s="28"/>
+      <c r="A537" s="30"/>
+      <c r="B537" s="30"/>
+      <c r="C537" s="30"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="A538" s="28"/>
-      <c r="B538" s="28"/>
-      <c r="C538" s="28"/>
+      <c r="A538" s="30"/>
+      <c r="B538" s="30"/>
+      <c r="C538" s="30"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="A539" s="28"/>
-      <c r="B539" s="28"/>
-      <c r="C539" s="28"/>
+      <c r="A539" s="30"/>
+      <c r="B539" s="30"/>
+      <c r="C539" s="30"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="A540" s="28"/>
-      <c r="B540" s="28"/>
-      <c r="C540" s="28"/>
+      <c r="A540" s="30"/>
+      <c r="B540" s="30"/>
+      <c r="C540" s="30"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="A541" s="28"/>
-      <c r="B541" s="28"/>
-      <c r="C541" s="28"/>
+      <c r="A541" s="30"/>
+      <c r="B541" s="30"/>
+      <c r="C541" s="30"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="A542" s="28"/>
-      <c r="B542" s="28"/>
-      <c r="C542" s="28"/>
+      <c r="A542" s="30"/>
+      <c r="B542" s="30"/>
+      <c r="C542" s="30"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="A543" s="28"/>
-      <c r="B543" s="28"/>
-      <c r="C543" s="28"/>
+      <c r="A543" s="30"/>
+      <c r="B543" s="30"/>
+      <c r="C543" s="30"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="A544" s="28"/>
-      <c r="B544" s="28"/>
-      <c r="C544" s="28"/>
+      <c r="A544" s="30"/>
+      <c r="B544" s="30"/>
+      <c r="C544" s="30"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="A545" s="28"/>
-      <c r="B545" s="28"/>
-      <c r="C545" s="28"/>
+      <c r="A545" s="30"/>
+      <c r="B545" s="30"/>
+      <c r="C545" s="30"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="A546" s="28"/>
-      <c r="B546" s="28"/>
-      <c r="C546" s="28"/>
+      <c r="A546" s="30"/>
+      <c r="B546" s="30"/>
+      <c r="C546" s="30"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="A547" s="28"/>
-      <c r="B547" s="28"/>
-      <c r="C547" s="28"/>
+      <c r="A547" s="30"/>
+      <c r="B547" s="30"/>
+      <c r="C547" s="30"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="A548" s="28"/>
-      <c r="B548" s="28"/>
-      <c r="C548" s="28"/>
+      <c r="A548" s="30"/>
+      <c r="B548" s="30"/>
+      <c r="C548" s="30"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="A549" s="28"/>
-      <c r="B549" s="28"/>
-      <c r="C549" s="28"/>
+      <c r="A549" s="30"/>
+      <c r="B549" s="30"/>
+      <c r="C549" s="30"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="A550" s="28"/>
-      <c r="B550" s="28"/>
-      <c r="C550" s="28"/>
+      <c r="A550" s="30"/>
+      <c r="B550" s="30"/>
+      <c r="C550" s="30"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="A551" s="28"/>
-      <c r="B551" s="28"/>
-      <c r="C551" s="28"/>
+      <c r="A551" s="30"/>
+      <c r="B551" s="30"/>
+      <c r="C551" s="30"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="A552" s="28"/>
-      <c r="B552" s="28"/>
-      <c r="C552" s="28"/>
+      <c r="A552" s="30"/>
+      <c r="B552" s="30"/>
+      <c r="C552" s="30"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="A553" s="28"/>
-      <c r="B553" s="28"/>
-      <c r="C553" s="28"/>
+      <c r="A553" s="30"/>
+      <c r="B553" s="30"/>
+      <c r="C553" s="30"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="A554" s="28"/>
-      <c r="B554" s="28"/>
-      <c r="C554" s="28"/>
+      <c r="A554" s="30"/>
+      <c r="B554" s="30"/>
+      <c r="C554" s="30"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="A555" s="28"/>
-      <c r="B555" s="28"/>
-      <c r="C555" s="28"/>
+      <c r="A555" s="30"/>
+      <c r="B555" s="30"/>
+      <c r="C555" s="30"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="A556" s="28"/>
-      <c r="B556" s="28"/>
-      <c r="C556" s="28"/>
+      <c r="A556" s="30"/>
+      <c r="B556" s="30"/>
+      <c r="C556" s="30"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="A557" s="28"/>
-      <c r="B557" s="28"/>
-      <c r="C557" s="28"/>
+      <c r="A557" s="30"/>
+      <c r="B557" s="30"/>
+      <c r="C557" s="30"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="A558" s="28"/>
-      <c r="B558" s="28"/>
-      <c r="C558" s="28"/>
+      <c r="A558" s="30"/>
+      <c r="B558" s="30"/>
+      <c r="C558" s="30"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="A559" s="28"/>
-      <c r="B559" s="28"/>
-      <c r="C559" s="28"/>
+      <c r="A559" s="30"/>
+      <c r="B559" s="30"/>
+      <c r="C559" s="30"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="A560" s="28"/>
-      <c r="B560" s="28"/>
-      <c r="C560" s="28"/>
+      <c r="A560" s="30"/>
+      <c r="B560" s="30"/>
+      <c r="C560" s="30"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="A561" s="28"/>
-      <c r="B561" s="28"/>
-      <c r="C561" s="28"/>
+      <c r="A561" s="30"/>
+      <c r="B561" s="30"/>
+      <c r="C561" s="30"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="A562" s="28"/>
-      <c r="B562" s="28"/>
-      <c r="C562" s="28"/>
+      <c r="A562" s="30"/>
+      <c r="B562" s="30"/>
+      <c r="C562" s="30"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="A563" s="28"/>
-      <c r="B563" s="28"/>
-      <c r="C563" s="28"/>
+      <c r="A563" s="30"/>
+      <c r="B563" s="30"/>
+      <c r="C563" s="30"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="A564" s="28"/>
-      <c r="B564" s="28"/>
-      <c r="C564" s="28"/>
+      <c r="A564" s="30"/>
+      <c r="B564" s="30"/>
+      <c r="C564" s="30"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="A565" s="28"/>
-      <c r="B565" s="28"/>
-      <c r="C565" s="28"/>
+      <c r="A565" s="30"/>
+      <c r="B565" s="30"/>
+      <c r="C565" s="30"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="A566" s="28"/>
-      <c r="B566" s="28"/>
-      <c r="C566" s="28"/>
+      <c r="A566" s="30"/>
+      <c r="B566" s="30"/>
+      <c r="C566" s="30"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="A567" s="28"/>
-      <c r="B567" s="28"/>
-      <c r="C567" s="28"/>
+      <c r="A567" s="30"/>
+      <c r="B567" s="30"/>
+      <c r="C567" s="30"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="A568" s="28"/>
-      <c r="B568" s="28"/>
-      <c r="C568" s="28"/>
+      <c r="A568" s="30"/>
+      <c r="B568" s="30"/>
+      <c r="C568" s="30"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="A569" s="28"/>
-      <c r="B569" s="28"/>
-      <c r="C569" s="28"/>
+      <c r="A569" s="30"/>
+      <c r="B569" s="30"/>
+      <c r="C569" s="30"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="A570" s="28"/>
-      <c r="B570" s="28"/>
-      <c r="C570" s="28"/>
+      <c r="A570" s="30"/>
+      <c r="B570" s="30"/>
+      <c r="C570" s="30"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="A571" s="28"/>
-      <c r="B571" s="28"/>
-      <c r="C571" s="28"/>
+      <c r="A571" s="30"/>
+      <c r="B571" s="30"/>
+      <c r="C571" s="30"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="A572" s="28"/>
-      <c r="B572" s="28"/>
-      <c r="C572" s="28"/>
+      <c r="A572" s="30"/>
+      <c r="B572" s="30"/>
+      <c r="C572" s="30"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="A573" s="28"/>
-      <c r="B573" s="28"/>
-      <c r="C573" s="28"/>
+      <c r="A573" s="30"/>
+      <c r="B573" s="30"/>
+      <c r="C573" s="30"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="A574" s="28"/>
-      <c r="B574" s="28"/>
-      <c r="C574" s="28"/>
+      <c r="A574" s="30"/>
+      <c r="B574" s="30"/>
+      <c r="C574" s="30"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="A575" s="28"/>
-      <c r="B575" s="28"/>
-      <c r="C575" s="28"/>
+      <c r="A575" s="30"/>
+      <c r="B575" s="30"/>
+      <c r="C575" s="30"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="A576" s="28"/>
-      <c r="B576" s="28"/>
-      <c r="C576" s="28"/>
+      <c r="A576" s="30"/>
+      <c r="B576" s="30"/>
+      <c r="C576" s="30"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="A577" s="28"/>
-      <c r="B577" s="28"/>
-      <c r="C577" s="28"/>
+      <c r="A577" s="30"/>
+      <c r="B577" s="30"/>
+      <c r="C577" s="30"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="A578" s="28"/>
-      <c r="B578" s="28"/>
-      <c r="C578" s="28"/>
+      <c r="A578" s="30"/>
+      <c r="B578" s="30"/>
+      <c r="C578" s="30"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="A579" s="28"/>
-      <c r="B579" s="28"/>
-      <c r="C579" s="28"/>
+      <c r="A579" s="30"/>
+      <c r="B579" s="30"/>
+      <c r="C579" s="30"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="A580" s="28"/>
-      <c r="B580" s="28"/>
-      <c r="C580" s="28"/>
+      <c r="A580" s="30"/>
+      <c r="B580" s="30"/>
+      <c r="C580" s="30"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="A581" s="28"/>
-      <c r="B581" s="28"/>
-      <c r="C581" s="28"/>
+      <c r="A581" s="30"/>
+      <c r="B581" s="30"/>
+      <c r="C581" s="30"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="A582" s="28"/>
-      <c r="B582" s="28"/>
-      <c r="C582" s="28"/>
+      <c r="A582" s="30"/>
+      <c r="B582" s="30"/>
+      <c r="C582" s="30"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="A583" s="28"/>
-      <c r="B583" s="28"/>
-      <c r="C583" s="28"/>
+      <c r="A583" s="30"/>
+      <c r="B583" s="30"/>
+      <c r="C583" s="30"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="A584" s="28"/>
-      <c r="B584" s="28"/>
-      <c r="C584" s="28"/>
+      <c r="A584" s="30"/>
+      <c r="B584" s="30"/>
+      <c r="C584" s="30"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="A585" s="28"/>
-      <c r="B585" s="28"/>
-      <c r="C585" s="28"/>
+      <c r="A585" s="30"/>
+      <c r="B585" s="30"/>
+      <c r="C585" s="30"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="A586" s="28"/>
-      <c r="B586" s="28"/>
-      <c r="C586" s="28"/>
+      <c r="A586" s="30"/>
+      <c r="B586" s="30"/>
+      <c r="C586" s="30"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="A587" s="28"/>
-      <c r="B587" s="28"/>
-      <c r="C587" s="28"/>
+      <c r="A587" s="30"/>
+      <c r="B587" s="30"/>
+      <c r="C587" s="30"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="A588" s="28"/>
-      <c r="B588" s="28"/>
-      <c r="C588" s="28"/>
+      <c r="A588" s="30"/>
+      <c r="B588" s="30"/>
+      <c r="C588" s="30"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="A589" s="28"/>
-      <c r="B589" s="28"/>
-      <c r="C589" s="28"/>
+      <c r="A589" s="30"/>
+      <c r="B589" s="30"/>
+      <c r="C589" s="30"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="A590" s="28"/>
-      <c r="B590" s="28"/>
-      <c r="C590" s="28"/>
+      <c r="A590" s="30"/>
+      <c r="B590" s="30"/>
+      <c r="C590" s="30"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="A591" s="28"/>
-      <c r="B591" s="28"/>
-      <c r="C591" s="28"/>
+      <c r="A591" s="30"/>
+      <c r="B591" s="30"/>
+      <c r="C591" s="30"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="A592" s="28"/>
-      <c r="B592" s="28"/>
-      <c r="C592" s="28"/>
+      <c r="A592" s="30"/>
+      <c r="B592" s="30"/>
+      <c r="C592" s="30"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="A593" s="28"/>
-      <c r="B593" s="28"/>
-      <c r="C593" s="28"/>
+      <c r="A593" s="30"/>
+      <c r="B593" s="30"/>
+      <c r="C593" s="30"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="A594" s="28"/>
-      <c r="B594" s="28"/>
-      <c r="C594" s="28"/>
+      <c r="A594" s="30"/>
+      <c r="B594" s="30"/>
+      <c r="C594" s="30"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="A595" s="28"/>
-      <c r="B595" s="28"/>
-      <c r="C595" s="28"/>
+      <c r="A595" s="30"/>
+      <c r="B595" s="30"/>
+      <c r="C595" s="30"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="A596" s="28"/>
-      <c r="B596" s="28"/>
-      <c r="C596" s="28"/>
+      <c r="A596" s="30"/>
+      <c r="B596" s="30"/>
+      <c r="C596" s="30"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="A597" s="28"/>
-      <c r="B597" s="28"/>
-      <c r="C597" s="28"/>
+      <c r="A597" s="30"/>
+      <c r="B597" s="30"/>
+      <c r="C597" s="30"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="A598" s="28"/>
-      <c r="B598" s="28"/>
-      <c r="C598" s="28"/>
+      <c r="A598" s="30"/>
+      <c r="B598" s="30"/>
+      <c r="C598" s="30"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="A599" s="28"/>
-      <c r="B599" s="28"/>
-      <c r="C599" s="28"/>
+      <c r="A599" s="30"/>
+      <c r="B599" s="30"/>
+      <c r="C599" s="30"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="A600" s="28"/>
-      <c r="B600" s="28"/>
-      <c r="C600" s="28"/>
+      <c r="A600" s="30"/>
+      <c r="B600" s="30"/>
+      <c r="C600" s="30"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="A601" s="28"/>
-      <c r="B601" s="28"/>
-      <c r="C601" s="28"/>
+      <c r="A601" s="30"/>
+      <c r="B601" s="30"/>
+      <c r="C601" s="30"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="A602" s="28"/>
-      <c r="B602" s="28"/>
-      <c r="C602" s="28"/>
+      <c r="A602" s="30"/>
+      <c r="B602" s="30"/>
+      <c r="C602" s="30"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="A603" s="28"/>
-      <c r="B603" s="28"/>
-      <c r="C603" s="28"/>
+      <c r="A603" s="30"/>
+      <c r="B603" s="30"/>
+      <c r="C603" s="30"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="A604" s="28"/>
-      <c r="B604" s="28"/>
-      <c r="C604" s="28"/>
+      <c r="A604" s="30"/>
+      <c r="B604" s="30"/>
+      <c r="C604" s="30"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="A605" s="28"/>
-      <c r="B605" s="28"/>
-      <c r="C605" s="28"/>
+      <c r="A605" s="30"/>
+      <c r="B605" s="30"/>
+      <c r="C605" s="30"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="A606" s="28"/>
-      <c r="B606" s="28"/>
-      <c r="C606" s="28"/>
+      <c r="A606" s="30"/>
+      <c r="B606" s="30"/>
+      <c r="C606" s="30"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="A607" s="28"/>
-      <c r="B607" s="28"/>
-      <c r="C607" s="28"/>
+      <c r="A607" s="30"/>
+      <c r="B607" s="30"/>
+      <c r="C607" s="30"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="A608" s="28"/>
-      <c r="B608" s="28"/>
-      <c r="C608" s="28"/>
+      <c r="A608" s="30"/>
+      <c r="B608" s="30"/>
+      <c r="C608" s="30"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="A609" s="28"/>
-      <c r="B609" s="28"/>
-      <c r="C609" s="28"/>
+      <c r="A609" s="30"/>
+      <c r="B609" s="30"/>
+      <c r="C609" s="30"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="A610" s="28"/>
-      <c r="B610" s="28"/>
-      <c r="C610" s="28"/>
+      <c r="A610" s="30"/>
+      <c r="B610" s="30"/>
+      <c r="C610" s="30"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="A611" s="28"/>
-      <c r="B611" s="28"/>
-      <c r="C611" s="28"/>
+      <c r="A611" s="30"/>
+      <c r="B611" s="30"/>
+      <c r="C611" s="30"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="A612" s="28"/>
-      <c r="B612" s="28"/>
-      <c r="C612" s="28"/>
+      <c r="A612" s="30"/>
+      <c r="B612" s="30"/>
+      <c r="C612" s="30"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="A613" s="28"/>
-      <c r="B613" s="28"/>
-      <c r="C613" s="28"/>
+      <c r="A613" s="30"/>
+      <c r="B613" s="30"/>
+      <c r="C613" s="30"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="A614" s="28"/>
-      <c r="B614" s="28"/>
-      <c r="C614" s="28"/>
+      <c r="A614" s="30"/>
+      <c r="B614" s="30"/>
+      <c r="C614" s="30"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="A615" s="28"/>
-      <c r="B615" s="28"/>
-      <c r="C615" s="28"/>
+      <c r="A615" s="30"/>
+      <c r="B615" s="30"/>
+      <c r="C615" s="30"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="A616" s="28"/>
-      <c r="B616" s="28"/>
-      <c r="C616" s="28"/>
+      <c r="A616" s="30"/>
+      <c r="B616" s="30"/>
+      <c r="C616" s="30"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="A617" s="28"/>
-      <c r="B617" s="28"/>
-      <c r="C617" s="28"/>
+      <c r="A617" s="30"/>
+      <c r="B617" s="30"/>
+      <c r="C617" s="30"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="A618" s="28"/>
-      <c r="B618" s="28"/>
-      <c r="C618" s="28"/>
+      <c r="A618" s="30"/>
+      <c r="B618" s="30"/>
+      <c r="C618" s="30"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="A619" s="28"/>
-      <c r="B619" s="28"/>
-      <c r="C619" s="28"/>
+      <c r="A619" s="30"/>
+      <c r="B619" s="30"/>
+      <c r="C619" s="30"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="A620" s="28"/>
-      <c r="B620" s="28"/>
-      <c r="C620" s="28"/>
+      <c r="A620" s="30"/>
+      <c r="B620" s="30"/>
+      <c r="C620" s="30"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="A621" s="28"/>
-      <c r="B621" s="28"/>
-      <c r="C621" s="28"/>
+      <c r="A621" s="30"/>
+      <c r="B621" s="30"/>
+      <c r="C621" s="30"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="A622" s="28"/>
-      <c r="B622" s="28"/>
-      <c r="C622" s="28"/>
+      <c r="A622" s="30"/>
+      <c r="B622" s="30"/>
+      <c r="C622" s="30"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="A623" s="28"/>
-      <c r="B623" s="28"/>
-      <c r="C623" s="28"/>
+      <c r="A623" s="30"/>
+      <c r="B623" s="30"/>
+      <c r="C623" s="30"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="A624" s="28"/>
-      <c r="B624" s="28"/>
-      <c r="C624" s="28"/>
+      <c r="A624" s="30"/>
+      <c r="B624" s="30"/>
+      <c r="C624" s="30"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="A625" s="28"/>
-      <c r="B625" s="28"/>
-      <c r="C625" s="28"/>
+      <c r="A625" s="30"/>
+      <c r="B625" s="30"/>
+      <c r="C625" s="30"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="A626" s="28"/>
-      <c r="B626" s="28"/>
-      <c r="C626" s="28"/>
+      <c r="A626" s="30"/>
+      <c r="B626" s="30"/>
+      <c r="C626" s="30"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="A627" s="28"/>
-      <c r="B627" s="28"/>
-      <c r="C627" s="28"/>
+      <c r="A627" s="30"/>
+      <c r="B627" s="30"/>
+      <c r="C627" s="30"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="A628" s="28"/>
-      <c r="B628" s="28"/>
-      <c r="C628" s="28"/>
+      <c r="A628" s="30"/>
+      <c r="B628" s="30"/>
+      <c r="C628" s="30"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="A629" s="28"/>
-      <c r="B629" s="28"/>
-      <c r="C629" s="28"/>
+      <c r="A629" s="30"/>
+      <c r="B629" s="30"/>
+      <c r="C629" s="30"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="A630" s="28"/>
-      <c r="B630" s="28"/>
-      <c r="C630" s="28"/>
+      <c r="A630" s="30"/>
+      <c r="B630" s="30"/>
+      <c r="C630" s="30"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="A631" s="28"/>
-      <c r="B631" s="28"/>
-      <c r="C631" s="28"/>
+      <c r="A631" s="30"/>
+      <c r="B631" s="30"/>
+      <c r="C631" s="30"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="A632" s="28"/>
-      <c r="B632" s="28"/>
-      <c r="C632" s="28"/>
+      <c r="A632" s="30"/>
+      <c r="B632" s="30"/>
+      <c r="C632" s="30"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="A633" s="28"/>
-      <c r="B633" s="28"/>
-      <c r="C633" s="28"/>
+      <c r="A633" s="30"/>
+      <c r="B633" s="30"/>
+      <c r="C633" s="30"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="A634" s="28"/>
-      <c r="B634" s="28"/>
-      <c r="C634" s="28"/>
+      <c r="A634" s="30"/>
+      <c r="B634" s="30"/>
+      <c r="C634" s="30"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="A635" s="28"/>
-      <c r="B635" s="28"/>
-      <c r="C635" s="28"/>
+      <c r="A635" s="30"/>
+      <c r="B635" s="30"/>
+      <c r="C635" s="30"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="A636" s="28"/>
-      <c r="B636" s="28"/>
-      <c r="C636" s="28"/>
+      <c r="A636" s="30"/>
+      <c r="B636" s="30"/>
+      <c r="C636" s="30"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="A637" s="28"/>
-      <c r="B637" s="28"/>
-      <c r="C637" s="28"/>
+      <c r="A637" s="30"/>
+      <c r="B637" s="30"/>
+      <c r="C637" s="30"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="A638" s="28"/>
-      <c r="B638" s="28"/>
-      <c r="C638" s="28"/>
+      <c r="A638" s="30"/>
+      <c r="B638" s="30"/>
+      <c r="C638" s="30"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="A639" s="28"/>
-      <c r="B639" s="28"/>
-      <c r="C639" s="28"/>
+      <c r="A639" s="30"/>
+      <c r="B639" s="30"/>
+      <c r="C639" s="30"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="A640" s="28"/>
-      <c r="B640" s="28"/>
-      <c r="C640" s="28"/>
+      <c r="A640" s="30"/>
+      <c r="B640" s="30"/>
+      <c r="C640" s="30"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="A641" s="28"/>
-      <c r="B641" s="28"/>
-      <c r="C641" s="28"/>
+      <c r="A641" s="30"/>
+      <c r="B641" s="30"/>
+      <c r="C641" s="30"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="A642" s="28"/>
-      <c r="B642" s="28"/>
-      <c r="C642" s="28"/>
+      <c r="A642" s="30"/>
+      <c r="B642" s="30"/>
+      <c r="C642" s="30"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="A643" s="28"/>
-      <c r="B643" s="28"/>
-      <c r="C643" s="28"/>
+      <c r="A643" s="30"/>
+      <c r="B643" s="30"/>
+      <c r="C643" s="30"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="A644" s="28"/>
-      <c r="B644" s="28"/>
-      <c r="C644" s="28"/>
+      <c r="A644" s="30"/>
+      <c r="B644" s="30"/>
+      <c r="C644" s="30"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="A645" s="28"/>
-      <c r="B645" s="28"/>
-      <c r="C645" s="28"/>
+      <c r="A645" s="30"/>
+      <c r="B645" s="30"/>
+      <c r="C645" s="30"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="A646" s="28"/>
-      <c r="B646" s="28"/>
-      <c r="C646" s="28"/>
+      <c r="A646" s="30"/>
+      <c r="B646" s="30"/>
+      <c r="C646" s="30"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="A647" s="28"/>
-      <c r="B647" s="28"/>
-      <c r="C647" s="28"/>
+      <c r="A647" s="30"/>
+      <c r="B647" s="30"/>
+      <c r="C647" s="30"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="A648" s="28"/>
-      <c r="B648" s="28"/>
-      <c r="C648" s="28"/>
+      <c r="A648" s="30"/>
+      <c r="B648" s="30"/>
+      <c r="C648" s="30"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="A649" s="28"/>
-      <c r="B649" s="28"/>
-      <c r="C649" s="28"/>
+      <c r="A649" s="30"/>
+      <c r="B649" s="30"/>
+      <c r="C649" s="30"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="A650" s="28"/>
-      <c r="B650" s="28"/>
-      <c r="C650" s="28"/>
+      <c r="A650" s="30"/>
+      <c r="B650" s="30"/>
+      <c r="C650" s="30"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="A651" s="28"/>
-      <c r="B651" s="28"/>
-      <c r="C651" s="28"/>
+      <c r="A651" s="30"/>
+      <c r="B651" s="30"/>
+      <c r="C651" s="30"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="A652" s="28"/>
-      <c r="B652" s="28"/>
-      <c r="C652" s="28"/>
+      <c r="A652" s="30"/>
+      <c r="B652" s="30"/>
+      <c r="C652" s="30"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="A653" s="28"/>
-      <c r="B653" s="28"/>
-      <c r="C653" s="28"/>
+      <c r="A653" s="30"/>
+      <c r="B653" s="30"/>
+      <c r="C653" s="30"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="A654" s="28"/>
-      <c r="B654" s="28"/>
-      <c r="C654" s="28"/>
+      <c r="A654" s="30"/>
+      <c r="B654" s="30"/>
+      <c r="C654" s="30"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="A655" s="28"/>
-      <c r="B655" s="28"/>
-      <c r="C655" s="28"/>
+      <c r="A655" s="30"/>
+      <c r="B655" s="30"/>
+      <c r="C655" s="30"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="A656" s="28"/>
-      <c r="B656" s="28"/>
-      <c r="C656" s="28"/>
+      <c r="A656" s="30"/>
+      <c r="B656" s="30"/>
+      <c r="C656" s="30"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="A657" s="28"/>
-      <c r="B657" s="28"/>
-      <c r="C657" s="28"/>
+      <c r="A657" s="30"/>
+      <c r="B657" s="30"/>
+      <c r="C657" s="30"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="A658" s="28"/>
-      <c r="B658" s="28"/>
-      <c r="C658" s="28"/>
+      <c r="A658" s="30"/>
+      <c r="B658" s="30"/>
+      <c r="C658" s="30"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="A659" s="28"/>
-      <c r="B659" s="28"/>
-      <c r="C659" s="28"/>
+      <c r="A659" s="30"/>
+      <c r="B659" s="30"/>
+      <c r="C659" s="30"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="A660" s="28"/>
-      <c r="B660" s="28"/>
-      <c r="C660" s="28"/>
+      <c r="A660" s="30"/>
+      <c r="B660" s="30"/>
+      <c r="C660" s="30"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="A661" s="28"/>
-      <c r="B661" s="28"/>
-      <c r="C661" s="28"/>
+      <c r="A661" s="30"/>
+      <c r="B661" s="30"/>
+      <c r="C661" s="30"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="A662" s="28"/>
-      <c r="B662" s="28"/>
-      <c r="C662" s="28"/>
+      <c r="A662" s="30"/>
+      <c r="B662" s="30"/>
+      <c r="C662" s="30"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="A663" s="28"/>
-      <c r="B663" s="28"/>
-      <c r="C663" s="28"/>
+      <c r="A663" s="30"/>
+      <c r="B663" s="30"/>
+      <c r="C663" s="30"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="A664" s="28"/>
-      <c r="B664" s="28"/>
-      <c r="C664" s="28"/>
+      <c r="A664" s="30"/>
+      <c r="B664" s="30"/>
+      <c r="C664" s="30"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="A665" s="28"/>
-      <c r="B665" s="28"/>
-      <c r="C665" s="28"/>
+      <c r="A665" s="30"/>
+      <c r="B665" s="30"/>
+      <c r="C665" s="30"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="A666" s="28"/>
-      <c r="B666" s="28"/>
-      <c r="C666" s="28"/>
+      <c r="A666" s="30"/>
+      <c r="B666" s="30"/>
+      <c r="C666" s="30"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="A667" s="28"/>
-      <c r="B667" s="28"/>
-      <c r="C667" s="28"/>
+      <c r="A667" s="30"/>
+      <c r="B667" s="30"/>
+      <c r="C667" s="30"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="A668" s="28"/>
-      <c r="B668" s="28"/>
-      <c r="C668" s="28"/>
+      <c r="A668" s="30"/>
+      <c r="B668" s="30"/>
+      <c r="C668" s="30"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="A669" s="28"/>
-      <c r="B669" s="28"/>
-      <c r="C669" s="28"/>
+      <c r="A669" s="30"/>
+      <c r="B669" s="30"/>
+      <c r="C669" s="30"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="A670" s="28"/>
-      <c r="B670" s="28"/>
-      <c r="C670" s="28"/>
+      <c r="A670" s="30"/>
+      <c r="B670" s="30"/>
+      <c r="C670" s="30"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="A671" s="28"/>
-      <c r="B671" s="28"/>
-      <c r="C671" s="28"/>
+      <c r="A671" s="30"/>
+      <c r="B671" s="30"/>
+      <c r="C671" s="30"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="A672" s="28"/>
-      <c r="B672" s="28"/>
-      <c r="C672" s="28"/>
+      <c r="A672" s="30"/>
+      <c r="B672" s="30"/>
+      <c r="C672" s="30"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="A673" s="28"/>
-      <c r="B673" s="28"/>
-      <c r="C673" s="28"/>
+      <c r="A673" s="30"/>
+      <c r="B673" s="30"/>
+      <c r="C673" s="30"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="A674" s="28"/>
-      <c r="B674" s="28"/>
-      <c r="C674" s="28"/>
+      <c r="A674" s="30"/>
+      <c r="B674" s="30"/>
+      <c r="C674" s="30"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="A675" s="28"/>
-      <c r="B675" s="28"/>
-      <c r="C675" s="28"/>
+      <c r="A675" s="30"/>
+      <c r="B675" s="30"/>
+      <c r="C675" s="30"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="A676" s="28"/>
-      <c r="B676" s="28"/>
-      <c r="C676" s="28"/>
+      <c r="A676" s="30"/>
+      <c r="B676" s="30"/>
+      <c r="C676" s="30"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="A677" s="28"/>
-      <c r="B677" s="28"/>
-      <c r="C677" s="28"/>
+      <c r="A677" s="30"/>
+      <c r="B677" s="30"/>
+      <c r="C677" s="30"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="A678" s="28"/>
-      <c r="B678" s="28"/>
-      <c r="C678" s="28"/>
+      <c r="A678" s="30"/>
+      <c r="B678" s="30"/>
+      <c r="C678" s="30"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="A679" s="28"/>
-      <c r="B679" s="28"/>
-      <c r="C679" s="28"/>
+      <c r="A679" s="30"/>
+      <c r="B679" s="30"/>
+      <c r="C679" s="30"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="A680" s="28"/>
-      <c r="B680" s="28"/>
-      <c r="C680" s="28"/>
+      <c r="A680" s="30"/>
+      <c r="B680" s="30"/>
+      <c r="C680" s="30"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="A681" s="28"/>
-      <c r="B681" s="28"/>
-      <c r="C681" s="28"/>
+      <c r="A681" s="30"/>
+      <c r="B681" s="30"/>
+      <c r="C681" s="30"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="A682" s="28"/>
-      <c r="B682" s="28"/>
-      <c r="C682" s="28"/>
+      <c r="A682" s="30"/>
+      <c r="B682" s="30"/>
+      <c r="C682" s="30"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="A683" s="28"/>
-      <c r="B683" s="28"/>
-      <c r="C683" s="28"/>
+      <c r="A683" s="30"/>
+      <c r="B683" s="30"/>
+      <c r="C683" s="30"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="A684" s="28"/>
-      <c r="B684" s="28"/>
-      <c r="C684" s="28"/>
+      <c r="A684" s="30"/>
+      <c r="B684" s="30"/>
+      <c r="C684" s="30"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="A685" s="28"/>
-      <c r="B685" s="28"/>
-      <c r="C685" s="28"/>
+      <c r="A685" s="30"/>
+      <c r="B685" s="30"/>
+      <c r="C685" s="30"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="A686" s="28"/>
-      <c r="B686" s="28"/>
-      <c r="C686" s="28"/>
+      <c r="A686" s="30"/>
+      <c r="B686" s="30"/>
+      <c r="C686" s="30"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="A687" s="28"/>
-      <c r="B687" s="28"/>
-      <c r="C687" s="28"/>
+      <c r="A687" s="30"/>
+      <c r="B687" s="30"/>
+      <c r="C687" s="30"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="A688" s="28"/>
-      <c r="B688" s="28"/>
-      <c r="C688" s="28"/>
+      <c r="A688" s="30"/>
+      <c r="B688" s="30"/>
+      <c r="C688" s="30"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="A689" s="28"/>
-      <c r="B689" s="28"/>
-      <c r="C689" s="28"/>
+      <c r="A689" s="30"/>
+      <c r="B689" s="30"/>
+      <c r="C689" s="30"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="A690" s="28"/>
-      <c r="B690" s="28"/>
-      <c r="C690" s="28"/>
+      <c r="A690" s="30"/>
+      <c r="B690" s="30"/>
+      <c r="C690" s="30"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="A691" s="28"/>
-      <c r="B691" s="28"/>
-      <c r="C691" s="28"/>
+      <c r="A691" s="30"/>
+      <c r="B691" s="30"/>
+      <c r="C691" s="30"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="A692" s="28"/>
-      <c r="B692" s="28"/>
-      <c r="C692" s="28"/>
+      <c r="A692" s="30"/>
+      <c r="B692" s="30"/>
+      <c r="C692" s="30"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="A693" s="28"/>
-      <c r="B693" s="28"/>
-      <c r="C693" s="28"/>
+      <c r="A693" s="30"/>
+      <c r="B693" s="30"/>
+      <c r="C693" s="30"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="A694" s="28"/>
-      <c r="B694" s="28"/>
-      <c r="C694" s="28"/>
+      <c r="A694" s="30"/>
+      <c r="B694" s="30"/>
+      <c r="C694" s="30"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="A695" s="28"/>
-      <c r="B695" s="28"/>
-      <c r="C695" s="28"/>
+      <c r="A695" s="30"/>
+      <c r="B695" s="30"/>
+      <c r="C695" s="30"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="A696" s="28"/>
-      <c r="B696" s="28"/>
-      <c r="C696" s="28"/>
+      <c r="A696" s="30"/>
+      <c r="B696" s="30"/>
+      <c r="C696" s="30"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="A697" s="28"/>
-      <c r="B697" s="28"/>
-      <c r="C697" s="28"/>
+      <c r="A697" s="30"/>
+      <c r="B697" s="30"/>
+      <c r="C697" s="30"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="A698" s="28"/>
-      <c r="B698" s="28"/>
-      <c r="C698" s="28"/>
+      <c r="A698" s="30"/>
+      <c r="B698" s="30"/>
+      <c r="C698" s="30"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="A699" s="28"/>
-      <c r="B699" s="28"/>
-      <c r="C699" s="28"/>
+      <c r="A699" s="30"/>
+      <c r="B699" s="30"/>
+      <c r="C699" s="30"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="A700" s="28"/>
-      <c r="B700" s="28"/>
-      <c r="C700" s="28"/>
+      <c r="A700" s="30"/>
+      <c r="B700" s="30"/>
+      <c r="C700" s="30"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="A701" s="28"/>
-      <c r="B701" s="28"/>
-      <c r="C701" s="28"/>
+      <c r="A701" s="30"/>
+      <c r="B701" s="30"/>
+      <c r="C701" s="30"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="A702" s="28"/>
-      <c r="B702" s="28"/>
-      <c r="C702" s="28"/>
+      <c r="A702" s="30"/>
+      <c r="B702" s="30"/>
+      <c r="C702" s="30"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="A703" s="28"/>
-      <c r="B703" s="28"/>
-      <c r="C703" s="28"/>
+      <c r="A703" s="30"/>
+      <c r="B703" s="30"/>
+      <c r="C703" s="30"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="A704" s="28"/>
-      <c r="B704" s="28"/>
-      <c r="C704" s="28"/>
+      <c r="A704" s="30"/>
+      <c r="B704" s="30"/>
+      <c r="C704" s="30"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="A705" s="28"/>
-      <c r="B705" s="28"/>
-      <c r="C705" s="28"/>
+      <c r="A705" s="30"/>
+      <c r="B705" s="30"/>
+      <c r="C705" s="30"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="A706" s="28"/>
-      <c r="B706" s="28"/>
-      <c r="C706" s="28"/>
+      <c r="A706" s="30"/>
+      <c r="B706" s="30"/>
+      <c r="C706" s="30"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="A707" s="28"/>
-      <c r="B707" s="28"/>
-      <c r="C707" s="28"/>
+      <c r="A707" s="30"/>
+      <c r="B707" s="30"/>
+      <c r="C707" s="30"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="28"/>
-      <c r="B708" s="28"/>
-      <c r="C708" s="28"/>
+      <c r="A708" s="30"/>
+      <c r="B708" s="30"/>
+      <c r="C708" s="30"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="A709" s="28"/>
-      <c r="B709" s="28"/>
-      <c r="C709" s="28"/>
+      <c r="A709" s="30"/>
+      <c r="B709" s="30"/>
+      <c r="C709" s="30"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="A710" s="28"/>
-      <c r="B710" s="28"/>
-      <c r="C710" s="28"/>
+      <c r="A710" s="30"/>
+      <c r="B710" s="30"/>
+      <c r="C710" s="30"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="A711" s="28"/>
-      <c r="B711" s="28"/>
-      <c r="C711" s="28"/>
+      <c r="A711" s="30"/>
+      <c r="B711" s="30"/>
+      <c r="C711" s="30"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="A712" s="28"/>
-      <c r="B712" s="28"/>
-      <c r="C712" s="28"/>
+      <c r="A712" s="30"/>
+      <c r="B712" s="30"/>
+      <c r="C712" s="30"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="A713" s="28"/>
-      <c r="B713" s="28"/>
-      <c r="C713" s="28"/>
+      <c r="A713" s="30"/>
+      <c r="B713" s="30"/>
+      <c r="C713" s="30"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="A714" s="28"/>
-      <c r="B714" s="28"/>
-      <c r="C714" s="28"/>
+      <c r="A714" s="30"/>
+      <c r="B714" s="30"/>
+      <c r="C714" s="30"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="A715" s="28"/>
-      <c r="B715" s="28"/>
-      <c r="C715" s="28"/>
+      <c r="A715" s="30"/>
+      <c r="B715" s="30"/>
+      <c r="C715" s="30"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="A716" s="28"/>
-      <c r="B716" s="28"/>
-      <c r="C716" s="28"/>
+      <c r="A716" s="30"/>
+      <c r="B716" s="30"/>
+      <c r="C716" s="30"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="A717" s="28"/>
-      <c r="B717" s="28"/>
-      <c r="C717" s="28"/>
+      <c r="A717" s="30"/>
+      <c r="B717" s="30"/>
+      <c r="C717" s="30"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="A718" s="28"/>
-      <c r="B718" s="28"/>
-      <c r="C718" s="28"/>
+      <c r="A718" s="30"/>
+      <c r="B718" s="30"/>
+      <c r="C718" s="30"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="A719" s="28"/>
-      <c r="B719" s="28"/>
-      <c r="C719" s="28"/>
+      <c r="A719" s="30"/>
+      <c r="B719" s="30"/>
+      <c r="C719" s="30"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="A720" s="28"/>
-      <c r="B720" s="28"/>
-      <c r="C720" s="28"/>
+      <c r="A720" s="30"/>
+      <c r="B720" s="30"/>
+      <c r="C720" s="30"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="A721" s="28"/>
-      <c r="B721" s="28"/>
-      <c r="C721" s="28"/>
+      <c r="A721" s="30"/>
+      <c r="B721" s="30"/>
+      <c r="C721" s="30"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="A722" s="28"/>
-      <c r="B722" s="28"/>
-      <c r="C722" s="28"/>
+      <c r="A722" s="30"/>
+      <c r="B722" s="30"/>
+      <c r="C722" s="30"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="A723" s="28"/>
-      <c r="B723" s="28"/>
-      <c r="C723" s="28"/>
+      <c r="A723" s="30"/>
+      <c r="B723" s="30"/>
+      <c r="C723" s="30"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="A724" s="28"/>
-      <c r="B724" s="28"/>
-      <c r="C724" s="28"/>
+      <c r="A724" s="30"/>
+      <c r="B724" s="30"/>
+      <c r="C724" s="30"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="A725" s="28"/>
-      <c r="B725" s="28"/>
-      <c r="C725" s="28"/>
+      <c r="A725" s="30"/>
+      <c r="B725" s="30"/>
+      <c r="C725" s="30"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="A726" s="28"/>
-      <c r="B726" s="28"/>
-      <c r="C726" s="28"/>
+      <c r="A726" s="30"/>
+      <c r="B726" s="30"/>
+      <c r="C726" s="30"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="A727" s="28"/>
-      <c r="B727" s="28"/>
-      <c r="C727" s="28"/>
+      <c r="A727" s="30"/>
+      <c r="B727" s="30"/>
+      <c r="C727" s="30"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="A728" s="28"/>
-      <c r="B728" s="28"/>
-      <c r="C728" s="28"/>
+      <c r="A728" s="30"/>
+      <c r="B728" s="30"/>
+      <c r="C728" s="30"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="A729" s="28"/>
-      <c r="B729" s="28"/>
-      <c r="C729" s="28"/>
+      <c r="A729" s="30"/>
+      <c r="B729" s="30"/>
+      <c r="C729" s="30"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="A730" s="28"/>
-      <c r="B730" s="28"/>
-      <c r="C730" s="28"/>
+      <c r="A730" s="30"/>
+      <c r="B730" s="30"/>
+      <c r="C730" s="30"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="A731" s="28"/>
-      <c r="B731" s="28"/>
-      <c r="C731" s="28"/>
+      <c r="A731" s="30"/>
+      <c r="B731" s="30"/>
+      <c r="C731" s="30"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="A732" s="28"/>
-      <c r="B732" s="28"/>
-      <c r="C732" s="28"/>
+      <c r="A732" s="30"/>
+      <c r="B732" s="30"/>
+      <c r="C732" s="30"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="A733" s="28"/>
-      <c r="B733" s="28"/>
-      <c r="C733" s="28"/>
+      <c r="A733" s="30"/>
+      <c r="B733" s="30"/>
+      <c r="C733" s="30"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="A734" s="28"/>
-      <c r="B734" s="28"/>
-      <c r="C734" s="28"/>
+      <c r="A734" s="30"/>
+      <c r="B734" s="30"/>
+      <c r="C734" s="30"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="A735" s="28"/>
-      <c r="B735" s="28"/>
-      <c r="C735" s="28"/>
+      <c r="A735" s="30"/>
+      <c r="B735" s="30"/>
+      <c r="C735" s="30"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="A736" s="28"/>
-      <c r="B736" s="28"/>
-      <c r="C736" s="28"/>
+      <c r="A736" s="30"/>
+      <c r="B736" s="30"/>
+      <c r="C736" s="30"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="A737" s="28"/>
-      <c r="B737" s="28"/>
-      <c r="C737" s="28"/>
+      <c r="A737" s="30"/>
+      <c r="B737" s="30"/>
+      <c r="C737" s="30"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="A738" s="28"/>
-      <c r="B738" s="28"/>
-      <c r="C738" s="28"/>
+      <c r="A738" s="30"/>
+      <c r="B738" s="30"/>
+      <c r="C738" s="30"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="A739" s="28"/>
-      <c r="B739" s="28"/>
-      <c r="C739" s="28"/>
+      <c r="A739" s="30"/>
+      <c r="B739" s="30"/>
+      <c r="C739" s="30"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="A740" s="28"/>
-      <c r="B740" s="28"/>
-      <c r="C740" s="28"/>
+      <c r="A740" s="30"/>
+      <c r="B740" s="30"/>
+      <c r="C740" s="30"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="A741" s="28"/>
-      <c r="B741" s="28"/>
-      <c r="C741" s="28"/>
+      <c r="A741" s="30"/>
+      <c r="B741" s="30"/>
+      <c r="C741" s="30"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="A742" s="28"/>
-      <c r="B742" s="28"/>
-      <c r="C742" s="28"/>
+      <c r="A742" s="30"/>
+      <c r="B742" s="30"/>
+      <c r="C742" s="30"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="A743" s="28"/>
-      <c r="B743" s="28"/>
-      <c r="C743" s="28"/>
+      <c r="A743" s="30"/>
+      <c r="B743" s="30"/>
+      <c r="C743" s="30"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="A744" s="28"/>
-      <c r="B744" s="28"/>
-      <c r="C744" s="28"/>
+      <c r="A744" s="30"/>
+      <c r="B744" s="30"/>
+      <c r="C744" s="30"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="A745" s="28"/>
-      <c r="B745" s="28"/>
-      <c r="C745" s="28"/>
+      <c r="A745" s="30"/>
+      <c r="B745" s="30"/>
+      <c r="C745" s="30"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="A746" s="28"/>
-      <c r="B746" s="28"/>
-      <c r="C746" s="28"/>
+      <c r="A746" s="30"/>
+      <c r="B746" s="30"/>
+      <c r="C746" s="30"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="A747" s="28"/>
-      <c r="B747" s="28"/>
-      <c r="C747" s="28"/>
+      <c r="A747" s="30"/>
+      <c r="B747" s="30"/>
+      <c r="C747" s="30"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="A748" s="28"/>
-      <c r="B748" s="28"/>
-      <c r="C748" s="28"/>
+      <c r="A748" s="30"/>
+      <c r="B748" s="30"/>
+      <c r="C748" s="30"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="A749" s="28"/>
-      <c r="B749" s="28"/>
-      <c r="C749" s="28"/>
+      <c r="A749" s="30"/>
+      <c r="B749" s="30"/>
+      <c r="C749" s="30"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="A750" s="28"/>
-      <c r="B750" s="28"/>
-      <c r="C750" s="28"/>
+      <c r="A750" s="30"/>
+      <c r="B750" s="30"/>
+      <c r="C750" s="30"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="A751" s="28"/>
-      <c r="B751" s="28"/>
-      <c r="C751" s="28"/>
+      <c r="A751" s="30"/>
+      <c r="B751" s="30"/>
+      <c r="C751" s="30"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="A752" s="28"/>
-      <c r="B752" s="28"/>
-      <c r="C752" s="28"/>
+      <c r="A752" s="30"/>
+      <c r="B752" s="30"/>
+      <c r="C752" s="30"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="A753" s="28"/>
-      <c r="B753" s="28"/>
-      <c r="C753" s="28"/>
+      <c r="A753" s="30"/>
+      <c r="B753" s="30"/>
+      <c r="C753" s="30"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="A754" s="28"/>
-      <c r="B754" s="28"/>
-      <c r="C754" s="28"/>
+      <c r="A754" s="30"/>
+      <c r="B754" s="30"/>
+      <c r="C754" s="30"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="A755" s="28"/>
-      <c r="B755" s="28"/>
-      <c r="C755" s="28"/>
+      <c r="A755" s="30"/>
+      <c r="B755" s="30"/>
+      <c r="C755" s="30"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="A756" s="28"/>
-      <c r="B756" s="28"/>
-      <c r="C756" s="28"/>
+      <c r="A756" s="30"/>
+      <c r="B756" s="30"/>
+      <c r="C756" s="30"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="A757" s="28"/>
-      <c r="B757" s="28"/>
-      <c r="C757" s="28"/>
+      <c r="A757" s="30"/>
+      <c r="B757" s="30"/>
+      <c r="C757" s="30"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="A758" s="28"/>
-      <c r="B758" s="28"/>
-      <c r="C758" s="28"/>
+      <c r="A758" s="30"/>
+      <c r="B758" s="30"/>
+      <c r="C758" s="30"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="A759" s="28"/>
-      <c r="B759" s="28"/>
-      <c r="C759" s="28"/>
+      <c r="A759" s="30"/>
+      <c r="B759" s="30"/>
+      <c r="C759" s="30"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="A760" s="28"/>
-      <c r="B760" s="28"/>
-      <c r="C760" s="28"/>
+      <c r="A760" s="30"/>
+      <c r="B760" s="30"/>
+      <c r="C760" s="30"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="A761" s="28"/>
-      <c r="B761" s="28"/>
-      <c r="C761" s="28"/>
+      <c r="A761" s="30"/>
+      <c r="B761" s="30"/>
+      <c r="C761" s="30"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="A762" s="28"/>
-      <c r="B762" s="28"/>
-      <c r="C762" s="28"/>
+      <c r="A762" s="30"/>
+      <c r="B762" s="30"/>
+      <c r="C762" s="30"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="A763" s="28"/>
-      <c r="B763" s="28"/>
-      <c r="C763" s="28"/>
+      <c r="A763" s="30"/>
+      <c r="B763" s="30"/>
+      <c r="C763" s="30"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="A764" s="28"/>
-      <c r="B764" s="28"/>
-      <c r="C764" s="28"/>
+      <c r="A764" s="30"/>
+      <c r="B764" s="30"/>
+      <c r="C764" s="30"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="A765" s="28"/>
-      <c r="B765" s="28"/>
-      <c r="C765" s="28"/>
+      <c r="A765" s="30"/>
+      <c r="B765" s="30"/>
+      <c r="C765" s="30"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="A766" s="28"/>
-      <c r="B766" s="28"/>
-      <c r="C766" s="28"/>
+      <c r="A766" s="30"/>
+      <c r="B766" s="30"/>
+      <c r="C766" s="30"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="A767" s="28"/>
-      <c r="B767" s="28"/>
-      <c r="C767" s="28"/>
+      <c r="A767" s="30"/>
+      <c r="B767" s="30"/>
+      <c r="C767" s="30"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="A768" s="28"/>
-      <c r="B768" s="28"/>
-      <c r="C768" s="28"/>
+      <c r="A768" s="30"/>
+      <c r="B768" s="30"/>
+      <c r="C768" s="30"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="A769" s="28"/>
-      <c r="B769" s="28"/>
-      <c r="C769" s="28"/>
+      <c r="A769" s="30"/>
+      <c r="B769" s="30"/>
+      <c r="C769" s="30"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="A770" s="28"/>
-      <c r="B770" s="28"/>
-      <c r="C770" s="28"/>
+      <c r="A770" s="30"/>
+      <c r="B770" s="30"/>
+      <c r="C770" s="30"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="A771" s="28"/>
-      <c r="B771" s="28"/>
-      <c r="C771" s="28"/>
+      <c r="A771" s="30"/>
+      <c r="B771" s="30"/>
+      <c r="C771" s="30"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="A772" s="28"/>
-      <c r="B772" s="28"/>
-      <c r="C772" s="28"/>
+      <c r="A772" s="30"/>
+      <c r="B772" s="30"/>
+      <c r="C772" s="30"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="A773" s="28"/>
-      <c r="B773" s="28"/>
-      <c r="C773" s="28"/>
+      <c r="A773" s="30"/>
+      <c r="B773" s="30"/>
+      <c r="C773" s="30"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="A774" s="28"/>
-      <c r="B774" s="28"/>
-      <c r="C774" s="28"/>
+      <c r="A774" s="30"/>
+      <c r="B774" s="30"/>
+      <c r="C774" s="30"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="A775" s="28"/>
-      <c r="B775" s="28"/>
-      <c r="C775" s="28"/>
+      <c r="A775" s="30"/>
+      <c r="B775" s="30"/>
+      <c r="C775" s="30"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="A776" s="28"/>
-      <c r="B776" s="28"/>
-      <c r="C776" s="28"/>
+      <c r="A776" s="30"/>
+      <c r="B776" s="30"/>
+      <c r="C776" s="30"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="A777" s="28"/>
-      <c r="B777" s="28"/>
-      <c r="C777" s="28"/>
+      <c r="A777" s="30"/>
+      <c r="B777" s="30"/>
+      <c r="C777" s="30"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="A778" s="28"/>
-      <c r="B778" s="28"/>
-      <c r="C778" s="28"/>
+      <c r="A778" s="30"/>
+      <c r="B778" s="30"/>
+      <c r="C778" s="30"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="A779" s="28"/>
-      <c r="B779" s="28"/>
-      <c r="C779" s="28"/>
+      <c r="A779" s="30"/>
+      <c r="B779" s="30"/>
+      <c r="C779" s="30"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="A780" s="28"/>
-      <c r="B780" s="28"/>
-      <c r="C780" s="28"/>
+      <c r="A780" s="30"/>
+      <c r="B780" s="30"/>
+      <c r="C780" s="30"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="A781" s="28"/>
-      <c r="B781" s="28"/>
-      <c r="C781" s="28"/>
+      <c r="A781" s="30"/>
+      <c r="B781" s="30"/>
+      <c r="C781" s="30"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="A782" s="28"/>
-      <c r="B782" s="28"/>
-      <c r="C782" s="28"/>
+      <c r="A782" s="30"/>
+      <c r="B782" s="30"/>
+      <c r="C782" s="30"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="A783" s="28"/>
-      <c r="B783" s="28"/>
-      <c r="C783" s="28"/>
+      <c r="A783" s="30"/>
+      <c r="B783" s="30"/>
+      <c r="C783" s="30"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="A784" s="28"/>
-      <c r="B784" s="28"/>
-      <c r="C784" s="28"/>
+      <c r="A784" s="30"/>
+      <c r="B784" s="30"/>
+      <c r="C784" s="30"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="A785" s="28"/>
-      <c r="B785" s="28"/>
-      <c r="C785" s="28"/>
+      <c r="A785" s="30"/>
+      <c r="B785" s="30"/>
+      <c r="C785" s="30"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="A786" s="28"/>
-      <c r="B786" s="28"/>
-      <c r="C786" s="28"/>
+      <c r="A786" s="30"/>
+      <c r="B786" s="30"/>
+      <c r="C786" s="30"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="A787" s="28"/>
-      <c r="B787" s="28"/>
-      <c r="C787" s="28"/>
+      <c r="A787" s="30"/>
+      <c r="B787" s="30"/>
+      <c r="C787" s="30"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="A788" s="28"/>
-      <c r="B788" s="28"/>
-      <c r="C788" s="28"/>
+      <c r="A788" s="30"/>
+      <c r="B788" s="30"/>
+      <c r="C788" s="30"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="A789" s="28"/>
-      <c r="B789" s="28"/>
-      <c r="C789" s="28"/>
+      <c r="A789" s="30"/>
+      <c r="B789" s="30"/>
+      <c r="C789" s="30"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="A790" s="28"/>
-      <c r="B790" s="28"/>
-      <c r="C790" s="28"/>
+      <c r="A790" s="30"/>
+      <c r="B790" s="30"/>
+      <c r="C790" s="30"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="A791" s="28"/>
-      <c r="B791" s="28"/>
-      <c r="C791" s="28"/>
+      <c r="A791" s="30"/>
+      <c r="B791" s="30"/>
+      <c r="C791" s="30"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="A792" s="28"/>
-      <c r="B792" s="28"/>
-      <c r="C792" s="28"/>
+      <c r="A792" s="30"/>
+      <c r="B792" s="30"/>
+      <c r="C792" s="30"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="A793" s="28"/>
-      <c r="B793" s="28"/>
-      <c r="C793" s="28"/>
+      <c r="A793" s="30"/>
+      <c r="B793" s="30"/>
+      <c r="C793" s="30"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="A794" s="28"/>
-      <c r="B794" s="28"/>
-      <c r="C794" s="28"/>
+      <c r="A794" s="30"/>
+      <c r="B794" s="30"/>
+      <c r="C794" s="30"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="A795" s="28"/>
-      <c r="B795" s="28"/>
-      <c r="C795" s="28"/>
+      <c r="A795" s="30"/>
+      <c r="B795" s="30"/>
+      <c r="C795" s="30"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="A796" s="28"/>
-      <c r="B796" s="28"/>
-      <c r="C796" s="28"/>
+      <c r="A796" s="30"/>
+      <c r="B796" s="30"/>
+      <c r="C796" s="30"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="A797" s="28"/>
-      <c r="B797" s="28"/>
-      <c r="C797" s="28"/>
+      <c r="A797" s="30"/>
+      <c r="B797" s="30"/>
+      <c r="C797" s="30"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="A798" s="28"/>
-      <c r="B798" s="28"/>
-      <c r="C798" s="28"/>
+      <c r="A798" s="30"/>
+      <c r="B798" s="30"/>
+      <c r="C798" s="30"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="A799" s="28"/>
-      <c r="B799" s="28"/>
-      <c r="C799" s="28"/>
+      <c r="A799" s="30"/>
+      <c r="B799" s="30"/>
+      <c r="C799" s="30"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="A800" s="28"/>
-      <c r="B800" s="28"/>
-      <c r="C800" s="28"/>
+      <c r="A800" s="30"/>
+      <c r="B800" s="30"/>
+      <c r="C800" s="30"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="A801" s="28"/>
-      <c r="B801" s="28"/>
-      <c r="C801" s="28"/>
+      <c r="A801" s="30"/>
+      <c r="B801" s="30"/>
+      <c r="C801" s="30"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="A802" s="28"/>
-      <c r="B802" s="28"/>
-      <c r="C802" s="28"/>
+      <c r="A802" s="30"/>
+      <c r="B802" s="30"/>
+      <c r="C802" s="30"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="A803" s="28"/>
-      <c r="B803" s="28"/>
-      <c r="C803" s="28"/>
+      <c r="A803" s="30"/>
+      <c r="B803" s="30"/>
+      <c r="C803" s="30"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="A804" s="28"/>
-      <c r="B804" s="28"/>
-      <c r="C804" s="28"/>
+      <c r="A804" s="30"/>
+      <c r="B804" s="30"/>
+      <c r="C804" s="30"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="A805" s="28"/>
-      <c r="B805" s="28"/>
-      <c r="C805" s="28"/>
+      <c r="A805" s="30"/>
+      <c r="B805" s="30"/>
+      <c r="C805" s="30"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="A806" s="28"/>
-      <c r="B806" s="28"/>
-      <c r="C806" s="28"/>
+      <c r="A806" s="30"/>
+      <c r="B806" s="30"/>
+      <c r="C806" s="30"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="A807" s="28"/>
-      <c r="B807" s="28"/>
-      <c r="C807" s="28"/>
+      <c r="A807" s="30"/>
+      <c r="B807" s="30"/>
+      <c r="C807" s="30"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="A808" s="28"/>
-      <c r="B808" s="28"/>
-      <c r="C808" s="28"/>
+      <c r="A808" s="30"/>
+      <c r="B808" s="30"/>
+      <c r="C808" s="30"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="A809" s="28"/>
-      <c r="B809" s="28"/>
-      <c r="C809" s="28"/>
+      <c r="A809" s="30"/>
+      <c r="B809" s="30"/>
+      <c r="C809" s="30"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="A810" s="28"/>
-      <c r="B810" s="28"/>
-      <c r="C810" s="28"/>
+      <c r="A810" s="30"/>
+      <c r="B810" s="30"/>
+      <c r="C810" s="30"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="A811" s="28"/>
-      <c r="B811" s="28"/>
-      <c r="C811" s="28"/>
+      <c r="A811" s="30"/>
+      <c r="B811" s="30"/>
+      <c r="C811" s="30"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="A812" s="28"/>
-      <c r="B812" s="28"/>
-      <c r="C812" s="28"/>
+      <c r="A812" s="30"/>
+      <c r="B812" s="30"/>
+      <c r="C812" s="30"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="A813" s="28"/>
-      <c r="B813" s="28"/>
-      <c r="C813" s="28"/>
+      <c r="A813" s="30"/>
+      <c r="B813" s="30"/>
+      <c r="C813" s="30"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="A814" s="28"/>
-      <c r="B814" s="28"/>
-      <c r="C814" s="28"/>
+      <c r="A814" s="30"/>
+      <c r="B814" s="30"/>
+      <c r="C814" s="30"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="A815" s="28"/>
-      <c r="B815" s="28"/>
-      <c r="C815" s="28"/>
+      <c r="A815" s="30"/>
+      <c r="B815" s="30"/>
+      <c r="C815" s="30"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="A816" s="28"/>
-      <c r="B816" s="28"/>
-      <c r="C816" s="28"/>
+      <c r="A816" s="30"/>
+      <c r="B816" s="30"/>
+      <c r="C816" s="30"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="A817" s="28"/>
-      <c r="B817" s="28"/>
-      <c r="C817" s="28"/>
+      <c r="A817" s="30"/>
+      <c r="B817" s="30"/>
+      <c r="C817" s="30"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="A818" s="28"/>
-      <c r="B818" s="28"/>
-      <c r="C818" s="28"/>
+      <c r="A818" s="30"/>
+      <c r="B818" s="30"/>
+      <c r="C818" s="30"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="A819" s="28"/>
-      <c r="B819" s="28"/>
-      <c r="C819" s="28"/>
+      <c r="A819" s="30"/>
+      <c r="B819" s="30"/>
+      <c r="C819" s="30"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="A820" s="28"/>
-      <c r="B820" s="28"/>
-      <c r="C820" s="28"/>
+      <c r="A820" s="30"/>
+      <c r="B820" s="30"/>
+      <c r="C820" s="30"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="A821" s="28"/>
-      <c r="B821" s="28"/>
-      <c r="C821" s="28"/>
+      <c r="A821" s="30"/>
+      <c r="B821" s="30"/>
+      <c r="C821" s="30"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="A822" s="28"/>
-      <c r="B822" s="28"/>
-      <c r="C822" s="28"/>
+      <c r="A822" s="30"/>
+      <c r="B822" s="30"/>
+      <c r="C822" s="30"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="A823" s="28"/>
-      <c r="B823" s="28"/>
-      <c r="C823" s="28"/>
+      <c r="A823" s="30"/>
+      <c r="B823" s="30"/>
+      <c r="C823" s="30"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="A824" s="28"/>
-      <c r="B824" s="28"/>
-      <c r="C824" s="28"/>
+      <c r="A824" s="30"/>
+      <c r="B824" s="30"/>
+      <c r="C824" s="30"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="A825" s="28"/>
-      <c r="B825" s="28"/>
-      <c r="C825" s="28"/>
+      <c r="A825" s="30"/>
+      <c r="B825" s="30"/>
+      <c r="C825" s="30"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="A826" s="28"/>
-      <c r="B826" s="28"/>
-      <c r="C826" s="28"/>
+      <c r="A826" s="30"/>
+      <c r="B826" s="30"/>
+      <c r="C826" s="30"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="A827" s="28"/>
-      <c r="B827" s="28"/>
-      <c r="C827" s="28"/>
+      <c r="A827" s="30"/>
+      <c r="B827" s="30"/>
+      <c r="C827" s="30"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="A828" s="28"/>
-      <c r="B828" s="28"/>
-      <c r="C828" s="28"/>
+      <c r="A828" s="30"/>
+      <c r="B828" s="30"/>
+      <c r="C828" s="30"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="A829" s="28"/>
-      <c r="B829" s="28"/>
-      <c r="C829" s="28"/>
+      <c r="A829" s="30"/>
+      <c r="B829" s="30"/>
+      <c r="C829" s="30"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="A830" s="28"/>
-      <c r="B830" s="28"/>
-      <c r="C830" s="28"/>
+      <c r="A830" s="30"/>
+      <c r="B830" s="30"/>
+      <c r="C830" s="30"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="A831" s="28"/>
-      <c r="B831" s="28"/>
-      <c r="C831" s="28"/>
+      <c r="A831" s="30"/>
+      <c r="B831" s="30"/>
+      <c r="C831" s="30"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="A832" s="28"/>
-      <c r="B832" s="28"/>
-      <c r="C832" s="28"/>
+      <c r="A832" s="30"/>
+      <c r="B832" s="30"/>
+      <c r="C832" s="30"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="A833" s="28"/>
-      <c r="B833" s="28"/>
-      <c r="C833" s="28"/>
+      <c r="A833" s="30"/>
+      <c r="B833" s="30"/>
+      <c r="C833" s="30"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="A834" s="28"/>
-      <c r="B834" s="28"/>
-      <c r="C834" s="28"/>
+      <c r="A834" s="30"/>
+      <c r="B834" s="30"/>
+      <c r="C834" s="30"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="A835" s="28"/>
-      <c r="B835" s="28"/>
-      <c r="C835" s="28"/>
+      <c r="A835" s="30"/>
+      <c r="B835" s="30"/>
+      <c r="C835" s="30"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="A836" s="28"/>
-      <c r="B836" s="28"/>
-      <c r="C836" s="28"/>
+      <c r="A836" s="30"/>
+      <c r="B836" s="30"/>
+      <c r="C836" s="30"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="A837" s="28"/>
-      <c r="B837" s="28"/>
-      <c r="C837" s="28"/>
+      <c r="A837" s="30"/>
+      <c r="B837" s="30"/>
+      <c r="C837" s="30"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="A838" s="28"/>
-      <c r="B838" s="28"/>
-      <c r="C838" s="28"/>
+      <c r="A838" s="30"/>
+      <c r="B838" s="30"/>
+      <c r="C838" s="30"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="A839" s="28"/>
-      <c r="B839" s="28"/>
-      <c r="C839" s="28"/>
+      <c r="A839" s="30"/>
+      <c r="B839" s="30"/>
+      <c r="C839" s="30"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="A840" s="28"/>
-      <c r="B840" s="28"/>
-      <c r="C840" s="28"/>
+      <c r="A840" s="30"/>
+      <c r="B840" s="30"/>
+      <c r="C840" s="30"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="A841" s="28"/>
-      <c r="B841" s="28"/>
-      <c r="C841" s="28"/>
+      <c r="A841" s="30"/>
+      <c r="B841" s="30"/>
+      <c r="C841" s="30"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="A842" s="28"/>
-      <c r="B842" s="28"/>
-      <c r="C842" s="28"/>
+      <c r="A842" s="30"/>
+      <c r="B842" s="30"/>
+      <c r="C842" s="30"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="A843" s="28"/>
-      <c r="B843" s="28"/>
-      <c r="C843" s="28"/>
+      <c r="A843" s="30"/>
+      <c r="B843" s="30"/>
+      <c r="C843" s="30"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="A844" s="28"/>
-      <c r="B844" s="28"/>
-      <c r="C844" s="28"/>
+      <c r="A844" s="30"/>
+      <c r="B844" s="30"/>
+      <c r="C844" s="30"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="A845" s="28"/>
-      <c r="B845" s="28"/>
-      <c r="C845" s="28"/>
+      <c r="A845" s="30"/>
+      <c r="B845" s="30"/>
+      <c r="C845" s="30"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="A846" s="28"/>
-      <c r="B846" s="28"/>
-      <c r="C846" s="28"/>
+      <c r="A846" s="30"/>
+      <c r="B846" s="30"/>
+      <c r="C846" s="30"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="A847" s="28"/>
-      <c r="B847" s="28"/>
-      <c r="C847" s="28"/>
+      <c r="A847" s="30"/>
+      <c r="B847" s="30"/>
+      <c r="C847" s="30"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="A848" s="28"/>
-      <c r="B848" s="28"/>
-      <c r="C848" s="28"/>
+      <c r="A848" s="30"/>
+      <c r="B848" s="30"/>
+      <c r="C848" s="30"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="A849" s="28"/>
-      <c r="B849" s="28"/>
-      <c r="C849" s="28"/>
+      <c r="A849" s="30"/>
+      <c r="B849" s="30"/>
+      <c r="C849" s="30"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="A850" s="28"/>
-      <c r="B850" s="28"/>
-      <c r="C850" s="28"/>
+      <c r="A850" s="30"/>
+      <c r="B850" s="30"/>
+      <c r="C850" s="30"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="A851" s="28"/>
-      <c r="B851" s="28"/>
-      <c r="C851" s="28"/>
+      <c r="A851" s="30"/>
+      <c r="B851" s="30"/>
+      <c r="C851" s="30"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="A852" s="28"/>
-      <c r="B852" s="28"/>
-      <c r="C852" s="28"/>
+      <c r="A852" s="30"/>
+      <c r="B852" s="30"/>
+      <c r="C852" s="30"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="A853" s="28"/>
-      <c r="B853" s="28"/>
-      <c r="C853" s="28"/>
+      <c r="A853" s="30"/>
+      <c r="B853" s="30"/>
+      <c r="C853" s="30"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="A854" s="28"/>
-      <c r="B854" s="28"/>
-      <c r="C854" s="28"/>
+      <c r="A854" s="30"/>
+      <c r="B854" s="30"/>
+      <c r="C854" s="30"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="A855" s="28"/>
-      <c r="B855" s="28"/>
-      <c r="C855" s="28"/>
+      <c r="A855" s="30"/>
+      <c r="B855" s="30"/>
+      <c r="C855" s="30"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="A856" s="28"/>
-      <c r="B856" s="28"/>
-      <c r="C856" s="28"/>
+      <c r="A856" s="30"/>
+      <c r="B856" s="30"/>
+      <c r="C856" s="30"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="A857" s="28"/>
-      <c r="B857" s="28"/>
-      <c r="C857" s="28"/>
+      <c r="A857" s="30"/>
+      <c r="B857" s="30"/>
+      <c r="C857" s="30"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="A858" s="28"/>
-      <c r="B858" s="28"/>
-      <c r="C858" s="28"/>
+      <c r="A858" s="30"/>
+      <c r="B858" s="30"/>
+      <c r="C858" s="30"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="A859" s="28"/>
-      <c r="B859" s="28"/>
-      <c r="C859" s="28"/>
+      <c r="A859" s="30"/>
+      <c r="B859" s="30"/>
+      <c r="C859" s="30"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="A860" s="28"/>
-      <c r="B860" s="28"/>
-      <c r="C860" s="28"/>
+      <c r="A860" s="30"/>
+      <c r="B860" s="30"/>
+      <c r="C860" s="30"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="A861" s="28"/>
-      <c r="B861" s="28"/>
-      <c r="C861" s="28"/>
+      <c r="A861" s="30"/>
+      <c r="B861" s="30"/>
+      <c r="C861" s="30"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="A862" s="28"/>
-      <c r="B862" s="28"/>
-      <c r="C862" s="28"/>
+      <c r="A862" s="30"/>
+      <c r="B862" s="30"/>
+      <c r="C862" s="30"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="A863" s="28"/>
-      <c r="B863" s="28"/>
-      <c r="C863" s="28"/>
+      <c r="A863" s="30"/>
+      <c r="B863" s="30"/>
+      <c r="C863" s="30"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="A864" s="28"/>
-      <c r="B864" s="28"/>
-      <c r="C864" s="28"/>
+      <c r="A864" s="30"/>
+      <c r="B864" s="30"/>
+      <c r="C864" s="30"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="A865" s="28"/>
-      <c r="B865" s="28"/>
-      <c r="C865" s="28"/>
+      <c r="A865" s="30"/>
+      <c r="B865" s="30"/>
+      <c r="C865" s="30"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="A866" s="28"/>
-      <c r="B866" s="28"/>
-      <c r="C866" s="28"/>
+      <c r="A866" s="30"/>
+      <c r="B866" s="30"/>
+      <c r="C866" s="30"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="A867" s="28"/>
-      <c r="B867" s="28"/>
-      <c r="C867" s="28"/>
+      <c r="A867" s="30"/>
+      <c r="B867" s="30"/>
+      <c r="C867" s="30"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="A868" s="28"/>
-      <c r="B868" s="28"/>
-      <c r="C868" s="28"/>
+      <c r="A868" s="30"/>
+      <c r="B868" s="30"/>
+      <c r="C868" s="30"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="A869" s="28"/>
-      <c r="B869" s="28"/>
-      <c r="C869" s="28"/>
+      <c r="A869" s="30"/>
+      <c r="B869" s="30"/>
+      <c r="C869" s="30"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="A870" s="28"/>
-      <c r="B870" s="28"/>
-      <c r="C870" s="28"/>
+      <c r="A870" s="30"/>
+      <c r="B870" s="30"/>
+      <c r="C870" s="30"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="28"/>
-      <c r="B871" s="28"/>
-      <c r="C871" s="28"/>
+      <c r="A871" s="30"/>
+      <c r="B871" s="30"/>
+      <c r="C871" s="30"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="A872" s="28"/>
-      <c r="B872" s="28"/>
-      <c r="C872" s="28"/>
+      <c r="A872" s="30"/>
+      <c r="B872" s="30"/>
+      <c r="C872" s="30"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="A873" s="28"/>
-      <c r="B873" s="28"/>
-      <c r="C873" s="28"/>
+      <c r="A873" s="30"/>
+      <c r="B873" s="30"/>
+      <c r="C873" s="30"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="A874" s="28"/>
-      <c r="B874" s="28"/>
-      <c r="C874" s="28"/>
+      <c r="A874" s="30"/>
+      <c r="B874" s="30"/>
+      <c r="C874" s="30"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="A875" s="28"/>
-      <c r="B875" s="28"/>
-      <c r="C875" s="28"/>
+      <c r="A875" s="30"/>
+      <c r="B875" s="30"/>
+      <c r="C875" s="30"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="28"/>
-      <c r="B876" s="28"/>
-      <c r="C876" s="28"/>
+      <c r="A876" s="30"/>
+      <c r="B876" s="30"/>
+      <c r="C876" s="30"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="A877" s="28"/>
-      <c r="B877" s="28"/>
-      <c r="C877" s="28"/>
+      <c r="A877" s="30"/>
+      <c r="B877" s="30"/>
+      <c r="C877" s="30"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="A878" s="28"/>
-      <c r="B878" s="28"/>
-      <c r="C878" s="28"/>
+      <c r="A878" s="30"/>
+      <c r="B878" s="30"/>
+      <c r="C878" s="30"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="A879" s="28"/>
-      <c r="B879" s="28"/>
-      <c r="C879" s="28"/>
+      <c r="A879" s="30"/>
+      <c r="B879" s="30"/>
+      <c r="C879" s="30"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="A880" s="28"/>
-      <c r="B880" s="28"/>
-      <c r="C880" s="28"/>
+      <c r="A880" s="30"/>
+      <c r="B880" s="30"/>
+      <c r="C880" s="30"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="A881" s="28"/>
-      <c r="B881" s="28"/>
-      <c r="C881" s="28"/>
+      <c r="A881" s="30"/>
+      <c r="B881" s="30"/>
+      <c r="C881" s="30"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="A882" s="28"/>
-      <c r="B882" s="28"/>
-      <c r="C882" s="28"/>
+      <c r="A882" s="30"/>
+      <c r="B882" s="30"/>
+      <c r="C882" s="30"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="A883" s="28"/>
-      <c r="B883" s="28"/>
-      <c r="C883" s="28"/>
+      <c r="A883" s="30"/>
+      <c r="B883" s="30"/>
+      <c r="C883" s="30"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="A884" s="28"/>
-      <c r="B884" s="28"/>
-      <c r="C884" s="28"/>
+      <c r="A884" s="30"/>
+      <c r="B884" s="30"/>
+      <c r="C884" s="30"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="A885" s="28"/>
-      <c r="B885" s="28"/>
-      <c r="C885" s="28"/>
+      <c r="A885" s="30"/>
+      <c r="B885" s="30"/>
+      <c r="C885" s="30"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="A886" s="28"/>
-      <c r="B886" s="28"/>
-      <c r="C886" s="28"/>
+      <c r="A886" s="30"/>
+      <c r="B886" s="30"/>
+      <c r="C886" s="30"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="A887" s="28"/>
-      <c r="B887" s="28"/>
-      <c r="C887" s="28"/>
+      <c r="A887" s="30"/>
+      <c r="B887" s="30"/>
+      <c r="C887" s="30"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="A888" s="28"/>
-      <c r="B888" s="28"/>
-      <c r="C888" s="28"/>
+      <c r="A888" s="30"/>
+      <c r="B888" s="30"/>
+      <c r="C888" s="30"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="A889" s="28"/>
-      <c r="B889" s="28"/>
-      <c r="C889" s="28"/>
+      <c r="A889" s="30"/>
+      <c r="B889" s="30"/>
+      <c r="C889" s="30"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="A890" s="28"/>
-      <c r="B890" s="28"/>
-      <c r="C890" s="28"/>
+      <c r="A890" s="30"/>
+      <c r="B890" s="30"/>
+      <c r="C890" s="30"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="A891" s="28"/>
-      <c r="B891" s="28"/>
-      <c r="C891" s="28"/>
+      <c r="A891" s="30"/>
+      <c r="B891" s="30"/>
+      <c r="C891" s="30"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="A892" s="28"/>
-      <c r="B892" s="28"/>
-      <c r="C892" s="28"/>
+      <c r="A892" s="30"/>
+      <c r="B892" s="30"/>
+      <c r="C892" s="30"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="A893" s="28"/>
-      <c r="B893" s="28"/>
-      <c r="C893" s="28"/>
+      <c r="A893" s="30"/>
+      <c r="B893" s="30"/>
+      <c r="C893" s="30"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="A894" s="28"/>
-      <c r="B894" s="28"/>
-      <c r="C894" s="28"/>
+      <c r="A894" s="30"/>
+      <c r="B894" s="30"/>
+      <c r="C894" s="30"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="A895" s="28"/>
-      <c r="B895" s="28"/>
-      <c r="C895" s="28"/>
+      <c r="A895" s="30"/>
+      <c r="B895" s="30"/>
+      <c r="C895" s="30"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="A896" s="28"/>
-      <c r="B896" s="28"/>
-      <c r="C896" s="28"/>
+      <c r="A896" s="30"/>
+      <c r="B896" s="30"/>
+      <c r="C896" s="30"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="A897" s="28"/>
-      <c r="B897" s="28"/>
-      <c r="C897" s="28"/>
+      <c r="A897" s="30"/>
+      <c r="B897" s="30"/>
+      <c r="C897" s="30"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="A898" s="28"/>
-      <c r="B898" s="28"/>
-      <c r="C898" s="28"/>
+      <c r="A898" s="30"/>
+      <c r="B898" s="30"/>
+      <c r="C898" s="30"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="A899" s="28"/>
-      <c r="B899" s="28"/>
-      <c r="C899" s="28"/>
+      <c r="A899" s="30"/>
+      <c r="B899" s="30"/>
+      <c r="C899" s="30"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="A900" s="28"/>
-      <c r="B900" s="28"/>
-      <c r="C900" s="28"/>
+      <c r="A900" s="30"/>
+      <c r="B900" s="30"/>
+      <c r="C900" s="30"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="A901" s="28"/>
-      <c r="B901" s="28"/>
-      <c r="C901" s="28"/>
+      <c r="A901" s="30"/>
+      <c r="B901" s="30"/>
+      <c r="C901" s="30"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="A902" s="28"/>
-      <c r="B902" s="28"/>
-      <c r="C902" s="28"/>
+      <c r="A902" s="30"/>
+      <c r="B902" s="30"/>
+      <c r="C902" s="30"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="A903" s="28"/>
-      <c r="B903" s="28"/>
-      <c r="C903" s="28"/>
+      <c r="A903" s="30"/>
+      <c r="B903" s="30"/>
+      <c r="C903" s="30"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="A904" s="28"/>
-      <c r="B904" s="28"/>
-      <c r="C904" s="28"/>
+      <c r="A904" s="30"/>
+      <c r="B904" s="30"/>
+      <c r="C904" s="30"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="A905" s="28"/>
-      <c r="B905" s="28"/>
-      <c r="C905" s="28"/>
+      <c r="A905" s="30"/>
+      <c r="B905" s="30"/>
+      <c r="C905" s="30"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="A906" s="28"/>
-      <c r="B906" s="28"/>
-      <c r="C906" s="28"/>
+      <c r="A906" s="30"/>
+      <c r="B906" s="30"/>
+      <c r="C906" s="30"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="A907" s="28"/>
-      <c r="B907" s="28"/>
-      <c r="C907" s="28"/>
+      <c r="A907" s="30"/>
+      <c r="B907" s="30"/>
+      <c r="C907" s="30"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="A908" s="28"/>
-      <c r="B908" s="28"/>
-      <c r="C908" s="28"/>
+      <c r="A908" s="30"/>
+      <c r="B908" s="30"/>
+      <c r="C908" s="30"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="A909" s="28"/>
-      <c r="B909" s="28"/>
-      <c r="C909" s="28"/>
+      <c r="A909" s="30"/>
+      <c r="B909" s="30"/>
+      <c r="C909" s="30"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="A910" s="28"/>
-      <c r="B910" s="28"/>
-      <c r="C910" s="28"/>
+      <c r="A910" s="30"/>
+      <c r="B910" s="30"/>
+      <c r="C910" s="30"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="A911" s="28"/>
-      <c r="B911" s="28"/>
-      <c r="C911" s="28"/>
+      <c r="A911" s="30"/>
+      <c r="B911" s="30"/>
+      <c r="C911" s="30"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="A912" s="28"/>
-      <c r="B912" s="28"/>
-      <c r="C912" s="28"/>
+      <c r="A912" s="30"/>
+      <c r="B912" s="30"/>
+      <c r="C912" s="30"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="A913" s="28"/>
-      <c r="B913" s="28"/>
-      <c r="C913" s="28"/>
+      <c r="A913" s="30"/>
+      <c r="B913" s="30"/>
+      <c r="C913" s="30"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="A914" s="28"/>
-      <c r="B914" s="28"/>
-      <c r="C914" s="28"/>
+      <c r="A914" s="30"/>
+      <c r="B914" s="30"/>
+      <c r="C914" s="30"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="A915" s="28"/>
-      <c r="B915" s="28"/>
-      <c r="C915" s="28"/>
+      <c r="A915" s="30"/>
+      <c r="B915" s="30"/>
+      <c r="C915" s="30"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="A916" s="28"/>
-      <c r="B916" s="28"/>
-      <c r="C916" s="28"/>
+      <c r="A916" s="30"/>
+      <c r="B916" s="30"/>
+      <c r="C916" s="30"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="A917" s="28"/>
-      <c r="B917" s="28"/>
-      <c r="C917" s="28"/>
+      <c r="A917" s="30"/>
+      <c r="B917" s="30"/>
+      <c r="C917" s="30"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="A918" s="28"/>
-      <c r="B918" s="28"/>
-      <c r="C918" s="28"/>
+      <c r="A918" s="30"/>
+      <c r="B918" s="30"/>
+      <c r="C918" s="30"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="A919" s="28"/>
-      <c r="B919" s="28"/>
-      <c r="C919" s="28"/>
+      <c r="A919" s="30"/>
+      <c r="B919" s="30"/>
+      <c r="C919" s="30"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="A920" s="28"/>
-      <c r="B920" s="28"/>
-      <c r="C920" s="28"/>
+      <c r="A920" s="30"/>
+      <c r="B920" s="30"/>
+      <c r="C920" s="30"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="A921" s="28"/>
-      <c r="B921" s="28"/>
-      <c r="C921" s="28"/>
+      <c r="A921" s="30"/>
+      <c r="B921" s="30"/>
+      <c r="C921" s="30"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="A922" s="28"/>
-      <c r="B922" s="28"/>
-      <c r="C922" s="28"/>
+      <c r="A922" s="30"/>
+      <c r="B922" s="30"/>
+      <c r="C922" s="30"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="A923" s="28"/>
-      <c r="B923" s="28"/>
-      <c r="C923" s="28"/>
+      <c r="A923" s="30"/>
+      <c r="B923" s="30"/>
+      <c r="C923" s="30"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="A924" s="28"/>
-      <c r="B924" s="28"/>
-      <c r="C924" s="28"/>
+      <c r="A924" s="30"/>
+      <c r="B924" s="30"/>
+      <c r="C924" s="30"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="A925" s="28"/>
-      <c r="B925" s="28"/>
-      <c r="C925" s="28"/>
+      <c r="A925" s="30"/>
+      <c r="B925" s="30"/>
+      <c r="C925" s="30"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="A926" s="28"/>
-      <c r="B926" s="28"/>
-      <c r="C926" s="28"/>
+      <c r="A926" s="30"/>
+      <c r="B926" s="30"/>
+      <c r="C926" s="30"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="A927" s="28"/>
-      <c r="B927" s="28"/>
-      <c r="C927" s="28"/>
+      <c r="A927" s="30"/>
+      <c r="B927" s="30"/>
+      <c r="C927" s="30"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="A928" s="28"/>
-      <c r="B928" s="28"/>
-      <c r="C928" s="28"/>
+      <c r="A928" s="30"/>
+      <c r="B928" s="30"/>
+      <c r="C928" s="30"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="A929" s="28"/>
-      <c r="B929" s="28"/>
-      <c r="C929" s="28"/>
+      <c r="A929" s="30"/>
+      <c r="B929" s="30"/>
+      <c r="C929" s="30"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="A930" s="28"/>
-      <c r="B930" s="28"/>
-      <c r="C930" s="28"/>
+      <c r="A930" s="30"/>
+      <c r="B930" s="30"/>
+      <c r="C930" s="30"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="A931" s="28"/>
-      <c r="B931" s="28"/>
-      <c r="C931" s="28"/>
+      <c r="A931" s="30"/>
+      <c r="B931" s="30"/>
+      <c r="C931" s="30"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="A932" s="28"/>
-      <c r="B932" s="28"/>
-      <c r="C932" s="28"/>
+      <c r="A932" s="30"/>
+      <c r="B932" s="30"/>
+      <c r="C932" s="30"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="A933" s="28"/>
-      <c r="B933" s="28"/>
-      <c r="C933" s="28"/>
+      <c r="A933" s="30"/>
+      <c r="B933" s="30"/>
+      <c r="C933" s="30"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="A934" s="28"/>
-      <c r="B934" s="28"/>
-      <c r="C934" s="28"/>
+      <c r="A934" s="30"/>
+      <c r="B934" s="30"/>
+      <c r="C934" s="30"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="A935" s="28"/>
-      <c r="B935" s="28"/>
-      <c r="C935" s="28"/>
+      <c r="A935" s="30"/>
+      <c r="B935" s="30"/>
+      <c r="C935" s="30"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="A936" s="28"/>
-      <c r="B936" s="28"/>
-      <c r="C936" s="28"/>
+      <c r="A936" s="30"/>
+      <c r="B936" s="30"/>
+      <c r="C936" s="30"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="A937" s="28"/>
-      <c r="B937" s="28"/>
-      <c r="C937" s="28"/>
+      <c r="A937" s="30"/>
+      <c r="B937" s="30"/>
+      <c r="C937" s="30"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="A938" s="28"/>
-      <c r="B938" s="28"/>
-      <c r="C938" s="28"/>
+      <c r="A938" s="30"/>
+      <c r="B938" s="30"/>
+      <c r="C938" s="30"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="A939" s="28"/>
-      <c r="B939" s="28"/>
-      <c r="C939" s="28"/>
+      <c r="A939" s="30"/>
+      <c r="B939" s="30"/>
+      <c r="C939" s="30"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="A940" s="28"/>
-      <c r="B940" s="28"/>
-      <c r="C940" s="28"/>
+      <c r="A940" s="30"/>
+      <c r="B940" s="30"/>
+      <c r="C940" s="30"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="A941" s="28"/>
-      <c r="B941" s="28"/>
-      <c r="C941" s="28"/>
+      <c r="A941" s="30"/>
+      <c r="B941" s="30"/>
+      <c r="C941" s="30"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="A942" s="28"/>
-      <c r="B942" s="28"/>
-      <c r="C942" s="28"/>
+      <c r="A942" s="30"/>
+      <c r="B942" s="30"/>
+      <c r="C942" s="30"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="A943" s="28"/>
-      <c r="B943" s="28"/>
-      <c r="C943" s="28"/>
+      <c r="A943" s="30"/>
+      <c r="B943" s="30"/>
+      <c r="C943" s="30"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="A944" s="28"/>
-      <c r="B944" s="28"/>
-      <c r="C944" s="28"/>
+      <c r="A944" s="30"/>
+      <c r="B944" s="30"/>
+      <c r="C944" s="30"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="A945" s="28"/>
-      <c r="B945" s="28"/>
-      <c r="C945" s="28"/>
+      <c r="A945" s="30"/>
+      <c r="B945" s="30"/>
+      <c r="C945" s="30"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="A946" s="28"/>
-      <c r="B946" s="28"/>
-      <c r="C946" s="28"/>
+      <c r="A946" s="30"/>
+      <c r="B946" s="30"/>
+      <c r="C946" s="30"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="A947" s="28"/>
-      <c r="B947" s="28"/>
-      <c r="C947" s="28"/>
+      <c r="A947" s="30"/>
+      <c r="B947" s="30"/>
+      <c r="C947" s="30"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="A948" s="28"/>
-      <c r="B948" s="28"/>
-      <c r="C948" s="28"/>
+      <c r="A948" s="30"/>
+      <c r="B948" s="30"/>
+      <c r="C948" s="30"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="A949" s="28"/>
-      <c r="B949" s="28"/>
-      <c r="C949" s="28"/>
+      <c r="A949" s="30"/>
+      <c r="B949" s="30"/>
+      <c r="C949" s="30"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="A950" s="28"/>
-      <c r="B950" s="28"/>
-      <c r="C950" s="28"/>
+      <c r="A950" s="30"/>
+      <c r="B950" s="30"/>
+      <c r="C950" s="30"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="A951" s="28"/>
-      <c r="B951" s="28"/>
-      <c r="C951" s="28"/>
+      <c r="A951" s="30"/>
+      <c r="B951" s="30"/>
+      <c r="C951" s="30"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="A952" s="28"/>
-      <c r="B952" s="28"/>
-      <c r="C952" s="28"/>
+      <c r="A952" s="30"/>
+      <c r="B952" s="30"/>
+      <c r="C952" s="30"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="A953" s="28"/>
-      <c r="B953" s="28"/>
-      <c r="C953" s="28"/>
+      <c r="A953" s="30"/>
+      <c r="B953" s="30"/>
+      <c r="C953" s="30"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="A954" s="28"/>
-      <c r="B954" s="28"/>
-      <c r="C954" s="28"/>
+      <c r="A954" s="30"/>
+      <c r="B954" s="30"/>
+      <c r="C954" s="30"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="A955" s="28"/>
-      <c r="B955" s="28"/>
-      <c r="C955" s="28"/>
+      <c r="A955" s="30"/>
+      <c r="B955" s="30"/>
+      <c r="C955" s="30"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="A956" s="28"/>
-      <c r="B956" s="28"/>
-      <c r="C956" s="28"/>
+      <c r="A956" s="30"/>
+      <c r="B956" s="30"/>
+      <c r="C956" s="30"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="A957" s="28"/>
-      <c r="B957" s="28"/>
-      <c r="C957" s="28"/>
+      <c r="A957" s="30"/>
+      <c r="B957" s="30"/>
+      <c r="C957" s="30"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="A958" s="28"/>
-      <c r="B958" s="28"/>
-      <c r="C958" s="28"/>
+      <c r="A958" s="30"/>
+      <c r="B958" s="30"/>
+      <c r="C958" s="30"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="A959" s="28"/>
-      <c r="B959" s="28"/>
-      <c r="C959" s="28"/>
+      <c r="A959" s="30"/>
+      <c r="B959" s="30"/>
+      <c r="C959" s="30"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="A960" s="28"/>
-      <c r="B960" s="28"/>
-      <c r="C960" s="28"/>
+      <c r="A960" s="30"/>
+      <c r="B960" s="30"/>
+      <c r="C960" s="30"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="A961" s="28"/>
-      <c r="B961" s="28"/>
-      <c r="C961" s="28"/>
+      <c r="A961" s="30"/>
+      <c r="B961" s="30"/>
+      <c r="C961" s="30"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="A962" s="28"/>
-      <c r="B962" s="28"/>
-      <c r="C962" s="28"/>
+      <c r="A962" s="30"/>
+      <c r="B962" s="30"/>
+      <c r="C962" s="30"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="A963" s="28"/>
-      <c r="B963" s="28"/>
-      <c r="C963" s="28"/>
+      <c r="A963" s="30"/>
+      <c r="B963" s="30"/>
+      <c r="C963" s="30"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="A964" s="28"/>
-      <c r="B964" s="28"/>
-      <c r="C964" s="28"/>
+      <c r="A964" s="30"/>
+      <c r="B964" s="30"/>
+      <c r="C964" s="30"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="A965" s="28"/>
-      <c r="B965" s="28"/>
-      <c r="C965" s="28"/>
+      <c r="A965" s="30"/>
+      <c r="B965" s="30"/>
+      <c r="C965" s="30"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="A966" s="28"/>
-      <c r="B966" s="28"/>
-      <c r="C966" s="28"/>
+      <c r="A966" s="30"/>
+      <c r="B966" s="30"/>
+      <c r="C966" s="30"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="A967" s="28"/>
-      <c r="B967" s="28"/>
-      <c r="C967" s="28"/>
+      <c r="A967" s="30"/>
+      <c r="B967" s="30"/>
+      <c r="C967" s="30"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="A968" s="28"/>
-      <c r="B968" s="28"/>
-      <c r="C968" s="28"/>
+      <c r="A968" s="30"/>
+      <c r="B968" s="30"/>
+      <c r="C968" s="30"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="A969" s="28"/>
-      <c r="B969" s="28"/>
-      <c r="C969" s="28"/>
+      <c r="A969" s="30"/>
+      <c r="B969" s="30"/>
+      <c r="C969" s="30"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="A970" s="28"/>
-      <c r="B970" s="28"/>
-      <c r="C970" s="28"/>
+      <c r="A970" s="30"/>
+      <c r="B970" s="30"/>
+      <c r="C970" s="30"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="A971" s="28"/>
-      <c r="B971" s="28"/>
-      <c r="C971" s="28"/>
+      <c r="A971" s="30"/>
+      <c r="B971" s="30"/>
+      <c r="C971" s="30"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="A972" s="28"/>
-      <c r="B972" s="28"/>
-      <c r="C972" s="28"/>
+      <c r="A972" s="30"/>
+      <c r="B972" s="30"/>
+      <c r="C972" s="30"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="A973" s="28"/>
-      <c r="B973" s="28"/>
-      <c r="C973" s="28"/>
+      <c r="A973" s="30"/>
+      <c r="B973" s="30"/>
+      <c r="C973" s="30"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="A974" s="28"/>
-      <c r="B974" s="28"/>
-      <c r="C974" s="28"/>
+      <c r="A974" s="30"/>
+      <c r="B974" s="30"/>
+      <c r="C974" s="30"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="A975" s="28"/>
-      <c r="B975" s="28"/>
-      <c r="C975" s="28"/>
+      <c r="A975" s="30"/>
+      <c r="B975" s="30"/>
+      <c r="C975" s="30"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="A976" s="28"/>
-      <c r="B976" s="28"/>
-      <c r="C976" s="28"/>
+      <c r="A976" s="30"/>
+      <c r="B976" s="30"/>
+      <c r="C976" s="30"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="A977" s="28"/>
-      <c r="B977" s="28"/>
-      <c r="C977" s="28"/>
+      <c r="A977" s="30"/>
+      <c r="B977" s="30"/>
+      <c r="C977" s="30"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="A978" s="28"/>
-      <c r="B978" s="28"/>
-      <c r="C978" s="28"/>
+      <c r="A978" s="30"/>
+      <c r="B978" s="30"/>
+      <c r="C978" s="30"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="A979" s="28"/>
-      <c r="B979" s="28"/>
-      <c r="C979" s="28"/>
+      <c r="A979" s="30"/>
+      <c r="B979" s="30"/>
+      <c r="C979" s="30"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="A980" s="28"/>
-      <c r="B980" s="28"/>
-      <c r="C980" s="28"/>
+      <c r="A980" s="30"/>
+      <c r="B980" s="30"/>
+      <c r="C980" s="30"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="A981" s="28"/>
-      <c r="B981" s="28"/>
-      <c r="C981" s="28"/>
+      <c r="A981" s="30"/>
+      <c r="B981" s="30"/>
+      <c r="C981" s="30"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="A982" s="28"/>
-      <c r="B982" s="28"/>
-      <c r="C982" s="28"/>
+      <c r="A982" s="30"/>
+      <c r="B982" s="30"/>
+      <c r="C982" s="30"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="A983" s="28"/>
-      <c r="B983" s="28"/>
-      <c r="C983" s="28"/>
+      <c r="A983" s="30"/>
+      <c r="B983" s="30"/>
+      <c r="C983" s="30"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="A984" s="28"/>
-      <c r="B984" s="28"/>
-      <c r="C984" s="28"/>
+      <c r="A984" s="30"/>
+      <c r="B984" s="30"/>
+      <c r="C984" s="30"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="A985" s="28"/>
-      <c r="B985" s="28"/>
-      <c r="C985" s="28"/>
+      <c r="A985" s="30"/>
+      <c r="B985" s="30"/>
+      <c r="C985" s="30"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="A986" s="28"/>
-      <c r="B986" s="28"/>
-      <c r="C986" s="28"/>
+      <c r="A986" s="30"/>
+      <c r="B986" s="30"/>
+      <c r="C986" s="30"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="A987" s="28"/>
-      <c r="B987" s="28"/>
-      <c r="C987" s="28"/>
+      <c r="A987" s="30"/>
+      <c r="B987" s="30"/>
+      <c r="C987" s="30"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="A988" s="28"/>
-      <c r="B988" s="28"/>
-      <c r="C988" s="28"/>
+      <c r="A988" s="30"/>
+      <c r="B988" s="30"/>
+      <c r="C988" s="30"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="A989" s="28"/>
-      <c r="B989" s="28"/>
-      <c r="C989" s="28"/>
+      <c r="A989" s="30"/>
+      <c r="B989" s="30"/>
+      <c r="C989" s="30"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="A990" s="28"/>
-      <c r="B990" s="28"/>
-      <c r="C990" s="28"/>
+      <c r="A990" s="30"/>
+      <c r="B990" s="30"/>
+      <c r="C990" s="30"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="A991" s="28"/>
-      <c r="B991" s="28"/>
-      <c r="C991" s="28"/>
+      <c r="A991" s="30"/>
+      <c r="B991" s="30"/>
+      <c r="C991" s="30"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="A992" s="28"/>
-      <c r="B992" s="28"/>
-      <c r="C992" s="28"/>
+      <c r="A992" s="30"/>
+      <c r="B992" s="30"/>
+      <c r="C992" s="30"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="A993" s="28"/>
-      <c r="B993" s="28"/>
-      <c r="C993" s="28"/>
+      <c r="A993" s="30"/>
+      <c r="B993" s="30"/>
+      <c r="C993" s="30"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="A994" s="28"/>
-      <c r="B994" s="28"/>
-      <c r="C994" s="28"/>
+      <c r="A994" s="30"/>
+      <c r="B994" s="30"/>
+      <c r="C994" s="30"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="A995" s="28"/>
-      <c r="B995" s="28"/>
-      <c r="C995" s="28"/>
+      <c r="A995" s="30"/>
+      <c r="B995" s="30"/>
+      <c r="C995" s="30"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="28"/>
-      <c r="B996" s="28"/>
-      <c r="C996" s="28"/>
+      <c r="A996" s="30"/>
+      <c r="B996" s="30"/>
+      <c r="C996" s="30"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="28"/>
-      <c r="B997" s="28"/>
-      <c r="C997" s="28"/>
+      <c r="A997" s="30"/>
+      <c r="B997" s="30"/>
+      <c r="C997" s="30"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="28"/>
-      <c r="B998" s="28"/>
-      <c r="C998" s="28"/>
+      <c r="A998" s="30"/>
+      <c r="B998" s="30"/>
+      <c r="C998" s="30"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="28"/>
-      <c r="B999" s="28"/>
-      <c r="C999" s="28"/>
+      <c r="A999" s="30"/>
+      <c r="B999" s="30"/>
+      <c r="C999" s="30"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="28"/>
-      <c r="B1000" s="28"/>
-      <c r="C1000" s="28"/>
+      <c r="A1000" s="30"/>
+      <c r="B1000" s="30"/>
+      <c r="C1000" s="30"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="A1001" s="28"/>
-      <c r="B1001" s="28"/>
-      <c r="C1001" s="28"/>
+      <c r="A1001" s="30"/>
+      <c r="B1001" s="30"/>
+      <c r="C1001" s="30"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6889,84 +6905,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="B1" s="29" t="s">
-        <v>102</v>
+      <c r="B1" s="31" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="30" t="s">
-        <v>103</v>
+      <c r="B3" s="32" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="30" t="s">
-        <v>104</v>
+      <c r="B4" s="32" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="30" t="s">
-        <v>105</v>
+      <c r="B5" s="32" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="30" t="s">
-        <v>106</v>
+      <c r="B6" s="32" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="30" t="s">
-        <v>107</v>
+      <c r="B7" s="32" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="30" t="s">
-        <v>108</v>
+      <c r="B8" s="32" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="30" t="s">
-        <v>109</v>
+      <c r="B9" s="32" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="30" t="s">
-        <v>110</v>
+      <c r="B10" s="32" t="s">
+        <v>111</v>
       </c>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="30" t="s">
-        <v>111</v>
+      <c r="B11" s="32" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="30" t="s">
-        <v>112</v>
+      <c r="B12" s="32" t="s">
+        <v>113</v>
       </c>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="30" t="s">
-        <v>113</v>
+      <c r="B13" s="32" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="30" t="s">
-        <v>114</v>
+      <c r="B14" s="32" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="30" t="s">
-        <v>115</v>
+      <c r="B15" s="32" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="30" t="s">
-        <v>116</v>
+      <c r="B16" s="32" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="30" t="s">
-        <v>117</v>
+      <c r="B17" s="32" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7979,237 +7995,237 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="31" t="s">
-        <v>118</v>
-      </c>
-      <c r="B2" s="31"/>
-      <c r="C2" s="31"/>
+      <c r="A2" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="B2" s="33"/>
+      <c r="C2" s="33"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="28"/>
-      <c r="B3" s="32" t="s">
-        <v>119</v>
-      </c>
-      <c r="C3" s="28"/>
+      <c r="A3" s="30"/>
+      <c r="B3" s="34" t="s">
+        <v>120</v>
+      </c>
+      <c r="C3" s="30"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="28"/>
-      <c r="B4" s="33" t="s">
-        <v>120</v>
-      </c>
-      <c r="C4" s="28"/>
+      <c r="A4" s="30"/>
+      <c r="B4" s="35" t="s">
+        <v>121</v>
+      </c>
+      <c r="C4" s="30"/>
     </row>
     <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="34" t="s">
-        <v>121</v>
-      </c>
-      <c r="B5" s="34"/>
-      <c r="C5" s="34"/>
+      <c r="A5" s="36" t="s">
+        <v>122</v>
+      </c>
+      <c r="B5" s="36"/>
+      <c r="C5" s="36"/>
     </row>
     <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
+      <c r="A6" s="30"/>
+      <c r="B6" s="30"/>
+      <c r="C6" s="30"/>
     </row>
     <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="35" t="s">
-        <v>122</v>
-      </c>
-      <c r="B7" s="36" t="s">
+      <c r="A7" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="C7" s="36" t="s">
+      <c r="B7" s="38" t="s">
         <v>124</v>
       </c>
-      <c r="D7" s="35" t="s">
+      <c r="C7" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="E7" s="35" t="s">
+      <c r="D7" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E7" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="F7" s="35" t="s">
-        <v>126</v>
-      </c>
-      <c r="G7" s="35" t="s">
+      <c r="F7" s="37" t="s">
         <v>127</v>
       </c>
+      <c r="G7" s="37" t="s">
+        <v>128</v>
+      </c>
     </row>
     <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="37">
+      <c r="A8" s="39">
         <v>1.0</v>
       </c>
-      <c r="B8" s="38" t="s">
-        <v>128</v>
-      </c>
-      <c r="C8" s="38" t="s">
+      <c r="B8" s="40" t="s">
         <v>129</v>
       </c>
-      <c r="D8" s="39" t="s">
+      <c r="C8" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="E8" s="40" t="s">
+      <c r="D8" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="42"/>
+      <c r="E8" s="42" t="s">
+        <v>132</v>
+      </c>
+      <c r="F8" s="43"/>
+      <c r="G8" s="44"/>
     </row>
     <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="43">
+      <c r="A9" s="45">
         <v>2.0</v>
       </c>
-      <c r="B9" s="44" t="s">
-        <v>128</v>
-      </c>
-      <c r="C9" s="44" t="s">
-        <v>132</v>
-      </c>
-      <c r="D9" s="45" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" s="46" t="s">
+      <c r="B9" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="C9" s="46" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="47"/>
-      <c r="G9" s="42"/>
+      <c r="D9" s="47" t="s">
+        <v>131</v>
+      </c>
+      <c r="E9" s="48" t="s">
+        <v>134</v>
+      </c>
+      <c r="F9" s="49"/>
+      <c r="G9" s="44"/>
     </row>
     <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="48">
+      <c r="A10" s="50">
         <v>3.0</v>
       </c>
-      <c r="B10" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="C10" s="49" t="s">
+      <c r="B10" s="51" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="50" t="s">
+      <c r="C10" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="E10" s="51" t="s">
+      <c r="D10" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="F10" s="52"/>
-      <c r="G10" s="53"/>
+      <c r="E10" s="53" t="s">
+        <v>138</v>
+      </c>
+      <c r="F10" s="54"/>
+      <c r="G10" s="55"/>
     </row>
     <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="37"/>
-      <c r="B11" s="38"/>
-      <c r="C11" s="38"/>
-      <c r="D11" s="39" t="s">
-        <v>138</v>
-      </c>
-      <c r="E11" s="40" t="s">
+      <c r="A11" s="39"/>
+      <c r="B11" s="40"/>
+      <c r="C11" s="40"/>
+      <c r="D11" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="F11" s="54"/>
-      <c r="G11" s="55"/>
+      <c r="E11" s="42" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="56"/>
+      <c r="G11" s="57"/>
     </row>
     <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="56">
+      <c r="A12" s="58">
         <v>4.0</v>
       </c>
-      <c r="B12" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="C12" s="57" t="s">
+      <c r="B12" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="58" t="s">
+      <c r="C12" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="E12" s="59" t="s">
+      <c r="D12" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="F12" s="60"/>
-      <c r="G12" s="61"/>
+      <c r="E12" s="61" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="62"/>
+      <c r="G12" s="63"/>
     </row>
     <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="37"/>
-      <c r="B13" s="38"/>
-      <c r="C13" s="38"/>
-      <c r="D13" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E13" s="40" t="s">
+      <c r="A13" s="39"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="40"/>
+      <c r="D13" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="F13" s="41"/>
-      <c r="G13" s="55"/>
+      <c r="E13" s="42" t="s">
+        <v>146</v>
+      </c>
+      <c r="F13" s="43"/>
+      <c r="G13" s="57"/>
     </row>
     <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="56">
+      <c r="A14" s="58">
         <v>5.0</v>
       </c>
-      <c r="B14" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="C14" s="57" t="s">
-        <v>146</v>
-      </c>
-      <c r="D14" s="58" t="s">
+      <c r="B14" s="59" t="s">
+        <v>141</v>
+      </c>
+      <c r="C14" s="59" t="s">
         <v>147</v>
       </c>
-      <c r="E14" s="59" t="s">
+      <c r="D14" s="60" t="s">
         <v>148</v>
       </c>
-      <c r="F14" s="60"/>
-      <c r="G14" s="61"/>
+      <c r="E14" s="61" t="s">
+        <v>149</v>
+      </c>
+      <c r="F14" s="62"/>
+      <c r="G14" s="63"/>
     </row>
     <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="37"/>
-      <c r="B15" s="38"/>
-      <c r="C15" s="38"/>
-      <c r="D15" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E15" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="F15" s="62" t="s">
+      <c r="A15" s="39"/>
+      <c r="B15" s="40"/>
+      <c r="C15" s="40"/>
+      <c r="D15" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="E15" s="42" t="s">
         <v>150</v>
       </c>
-      <c r="G15" s="55"/>
+      <c r="F15" s="64" t="s">
+        <v>151</v>
+      </c>
+      <c r="G15" s="57"/>
     </row>
     <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="56">
+      <c r="A16" s="58">
         <v>6.0</v>
       </c>
-      <c r="B16" s="57" t="s">
-        <v>140</v>
-      </c>
-      <c r="C16" s="57" t="s">
+      <c r="B16" s="59" t="s">
         <v>141</v>
       </c>
-      <c r="D16" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="E16" s="59" t="s">
+      <c r="C16" s="59" t="s">
+        <v>142</v>
+      </c>
+      <c r="D16" s="60" t="s">
         <v>152</v>
       </c>
-      <c r="F16" s="63"/>
-      <c r="G16" s="61"/>
+      <c r="E16" s="61" t="s">
+        <v>153</v>
+      </c>
+      <c r="F16" s="65"/>
+      <c r="G16" s="63"/>
     </row>
     <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="37"/>
-      <c r="B17" s="38"/>
-      <c r="C17" s="38"/>
-      <c r="D17" s="39" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="40" t="s">
-        <v>149</v>
-      </c>
-      <c r="F17" s="64"/>
-      <c r="G17" s="55"/>
+      <c r="A17" s="39"/>
+      <c r="B17" s="40"/>
+      <c r="C17" s="40"/>
+      <c r="D17" s="41" t="s">
+        <v>145</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>150</v>
+      </c>
+      <c r="F17" s="66"/>
+      <c r="G17" s="57"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="48"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="48"/>
-      <c r="D18" s="65"/>
-      <c r="E18" s="49"/>
-      <c r="F18" s="65"/>
-      <c r="G18" s="65"/>
+      <c r="A18" s="50"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="50"/>
+      <c r="D18" s="67"/>
+      <c r="E18" s="51"/>
+      <c r="F18" s="67"/>
+      <c r="G18" s="67"/>
     </row>
     <row r="19" ht="12.75" customHeight="1"/>
     <row r="20" ht="12.75" customHeight="1"/>

--- a/docs/TestPlan.xlsx
+++ b/docs/TestPlan.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="153">
   <si>
     <t>Test Planner and Tracker</t>
   </si>
@@ -120,9 +120,6 @@
   </si>
   <si>
     <t>Error message shows saying date selected must be current or in the future</t>
-  </si>
-  <si>
-    <t>The room filter still shows the available rooms without the pop up of an error</t>
   </si>
   <si>
     <t>User logged in and IMS connected</t>
@@ -775,7 +772,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="67">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -847,9 +844,6 @@
     <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyFill="1" applyFont="1"/>
     <xf borderId="0" fillId="5" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf borderId="3" fillId="5" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="top" wrapText="1"/>
@@ -1381,11 +1375,9 @@
       <c r="E7" s="20" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="26"/>
-      <c r="G7" s="20" t="s">
-        <v>32</v>
-      </c>
-      <c r="H7" s="27"/>
+      <c r="F7" s="23"/>
+      <c r="G7" s="20"/>
+      <c r="H7" s="26"/>
       <c r="I7" s="22"/>
     </row>
     <row r="8" ht="12.75" customHeight="1">
@@ -1397,13 +1389,13 @@
         <v>26</v>
       </c>
       <c r="C8" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="E8" s="20" t="s">
         <v>34</v>
-      </c>
-      <c r="E8" s="20" t="s">
-        <v>35</v>
       </c>
       <c r="F8" s="22"/>
       <c r="G8" s="22"/>
@@ -1416,16 +1408,16 @@
         <v>7</v>
       </c>
       <c r="B9" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="20" t="s">
+        <v>32</v>
+      </c>
+      <c r="D9" s="20" t="s">
         <v>36</v>
       </c>
-      <c r="C9" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="20" t="s">
+      <c r="E9" s="20" t="s">
         <v>37</v>
-      </c>
-      <c r="E9" s="20" t="s">
-        <v>38</v>
       </c>
       <c r="F9" s="22"/>
       <c r="G9" s="22"/>
@@ -1438,16 +1430,16 @@
         <v>8</v>
       </c>
       <c r="B10" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C10" s="20" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D10" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E10" s="20" t="s">
         <v>39</v>
-      </c>
-      <c r="E10" s="20" t="s">
-        <v>40</v>
       </c>
       <c r="F10" s="22"/>
       <c r="G10" s="22"/>
@@ -1460,16 +1452,16 @@
         <v>9</v>
       </c>
       <c r="B11" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="C11" s="20" t="s">
         <v>41</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="D11" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="E11" s="20" t="s">
         <v>43</v>
-      </c>
-      <c r="E11" s="20" t="s">
-        <v>44</v>
       </c>
       <c r="F11" s="22"/>
       <c r="G11" s="22"/>
@@ -1482,16 +1474,16 @@
         <v>10</v>
       </c>
       <c r="B12" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C12" s="20" t="s">
+        <v>44</v>
+      </c>
+      <c r="D12" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="D12" s="20" t="s">
+      <c r="E12" s="20" t="s">
         <v>46</v>
-      </c>
-      <c r="E12" s="20" t="s">
-        <v>47</v>
       </c>
       <c r="F12" s="22"/>
       <c r="G12" s="22"/>
@@ -1501,16 +1493,16 @@
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="19"/>
       <c r="B13" s="20" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C13" s="20" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="D13" s="20" t="s">
+        <v>47</v>
+      </c>
+      <c r="E13" s="20" t="s">
         <v>48</v>
-      </c>
-      <c r="E13" s="20" t="s">
-        <v>49</v>
       </c>
       <c r="F13" s="22"/>
       <c r="G13" s="22"/>
@@ -1523,16 +1515,16 @@
         <v>11</v>
       </c>
       <c r="B14" s="20" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="20" t="s">
+      <c r="D14" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="E14" s="20" t="s">
         <v>52</v>
-      </c>
-      <c r="E14" s="20" t="s">
-        <v>53</v>
       </c>
       <c r="F14" s="22"/>
       <c r="G14" s="22"/>
@@ -1545,16 +1537,16 @@
         <v>12</v>
       </c>
       <c r="B15" s="20" t="s">
+        <v>53</v>
+      </c>
+      <c r="C15" s="20" t="s">
         <v>54</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="D15" s="20" t="s">
         <v>55</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="E15" s="20" t="s">
         <v>56</v>
-      </c>
-      <c r="E15" s="20" t="s">
-        <v>57</v>
       </c>
       <c r="F15" s="22"/>
       <c r="G15" s="22"/>
@@ -1567,16 +1559,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="20" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C16" s="20" t="s">
+        <v>57</v>
+      </c>
+      <c r="D16" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="E16" s="20" t="s">
         <v>58</v>
-      </c>
-      <c r="D16" s="20" t="s">
-        <v>56</v>
-      </c>
-      <c r="E16" s="20" t="s">
-        <v>59</v>
       </c>
       <c r="F16" s="22"/>
       <c r="G16" s="22"/>
@@ -1589,16 +1581,16 @@
         <v>14</v>
       </c>
       <c r="B17" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C17" s="20" t="s">
+        <v>54</v>
+      </c>
+      <c r="D17" s="20" t="s">
         <v>60</v>
       </c>
-      <c r="C17" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="D17" s="20" t="s">
+      <c r="E17" s="20" t="s">
         <v>61</v>
-      </c>
-      <c r="E17" s="20" t="s">
-        <v>62</v>
       </c>
       <c r="F17" s="22"/>
       <c r="G17" s="22"/>
@@ -1611,16 +1603,16 @@
         <v>15</v>
       </c>
       <c r="B18" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="C18" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="C18" s="20" t="s">
+      <c r="D18" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="E18" s="20" t="s">
         <v>65</v>
-      </c>
-      <c r="E18" s="20" t="s">
-        <v>66</v>
       </c>
       <c r="F18" s="21"/>
       <c r="G18" s="22"/>
@@ -1633,16 +1625,16 @@
         <v>16</v>
       </c>
       <c r="B19" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="C19" s="20" t="s">
+      <c r="D19" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="D19" s="20" t="s">
+      <c r="E19" s="20" t="s">
         <v>69</v>
-      </c>
-      <c r="E19" s="20" t="s">
-        <v>70</v>
       </c>
       <c r="F19" s="22"/>
       <c r="G19" s="22"/>
@@ -1655,16 +1647,16 @@
         <v>17</v>
       </c>
       <c r="B20" s="20" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C20" s="20" t="s">
+        <v>70</v>
+      </c>
+      <c r="D20" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="E20" s="20" t="s">
         <v>71</v>
-      </c>
-      <c r="D20" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="20" t="s">
-        <v>72</v>
       </c>
       <c r="F20" s="22"/>
       <c r="G20" s="22"/>
@@ -1677,16 +1669,16 @@
         <v>18</v>
       </c>
       <c r="B21" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="C21" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="20" t="s">
+      <c r="D21" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="E21" s="20" t="s">
         <v>75</v>
-      </c>
-      <c r="E21" s="20" t="s">
-        <v>76</v>
       </c>
       <c r="F21" s="22"/>
       <c r="G21" s="22"/>
@@ -1699,16 +1691,16 @@
         <v>19</v>
       </c>
       <c r="B22" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="C22" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="D22" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="D22" s="20" t="s">
+      <c r="E22" s="20" t="s">
         <v>79</v>
-      </c>
-      <c r="E22" s="20" t="s">
-        <v>80</v>
       </c>
       <c r="F22" s="22"/>
       <c r="G22" s="22"/>
@@ -1721,16 +1713,16 @@
         <v>20</v>
       </c>
       <c r="B23" s="20" t="s">
+        <v>80</v>
+      </c>
+      <c r="C23" s="20" t="s">
+        <v>50</v>
+      </c>
+      <c r="D23" s="20" t="s">
         <v>81</v>
       </c>
-      <c r="C23" s="20" t="s">
-        <v>51</v>
-      </c>
-      <c r="D23" s="20" t="s">
+      <c r="E23" s="20" t="s">
         <v>82</v>
-      </c>
-      <c r="E23" s="20" t="s">
-        <v>83</v>
       </c>
       <c r="F23" s="22"/>
       <c r="G23" s="22"/>
@@ -1743,16 +1735,16 @@
         <v>21</v>
       </c>
       <c r="B24" s="20" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C24" s="20" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D24" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="E24" s="20" t="s">
         <v>84</v>
-      </c>
-      <c r="E24" s="20" t="s">
-        <v>85</v>
       </c>
       <c r="F24" s="22"/>
       <c r="G24" s="22"/>
@@ -1765,16 +1757,16 @@
         <v>22</v>
       </c>
       <c r="B25" s="20" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C25" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D25" s="20" t="s">
+        <v>86</v>
+      </c>
+      <c r="E25" s="20" t="s">
         <v>87</v>
-      </c>
-      <c r="E25" s="20" t="s">
-        <v>88</v>
       </c>
       <c r="F25" s="22"/>
       <c r="G25" s="22"/>
@@ -1786,17 +1778,17 @@
         <f t="shared" si="2"/>
         <v>23</v>
       </c>
-      <c r="B26" s="28" t="s">
+      <c r="B26" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="C26" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="D26" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="E26" s="20" t="s">
         <v>91</v>
-      </c>
-      <c r="E26" s="20" t="s">
-        <v>92</v>
       </c>
       <c r="F26" s="22"/>
       <c r="G26" s="22"/>
@@ -1809,16 +1801,16 @@
         <v>24</v>
       </c>
       <c r="B27" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C27" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D27" s="20" t="s">
+        <v>92</v>
+      </c>
+      <c r="E27" s="20" t="s">
         <v>93</v>
-      </c>
-      <c r="E27" s="20" t="s">
-        <v>94</v>
       </c>
       <c r="F27" s="22"/>
       <c r="G27" s="22"/>
@@ -1831,16 +1823,16 @@
         <v>25</v>
       </c>
       <c r="B28" s="20" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C28" s="20" t="s">
         <v>27</v>
       </c>
       <c r="D28" s="20" t="s">
+        <v>94</v>
+      </c>
+      <c r="E28" s="20" t="s">
         <v>95</v>
-      </c>
-      <c r="E28" s="20" t="s">
-        <v>96</v>
       </c>
       <c r="F28" s="22"/>
       <c r="G28" s="22"/>
@@ -1867,7 +1859,7 @@
         <v>27</v>
       </c>
       <c r="B30" s="22"/>
-      <c r="C30" s="29"/>
+      <c r="C30" s="28"/>
       <c r="D30" s="22"/>
       <c r="E30" s="22"/>
       <c r="F30" s="22"/>
@@ -1881,7 +1873,7 @@
         <v>28</v>
       </c>
       <c r="B31" s="22"/>
-      <c r="C31" s="29"/>
+      <c r="C31" s="28"/>
       <c r="D31" s="22"/>
       <c r="E31" s="22"/>
       <c r="F31" s="22"/>
@@ -1918,31 +1910,31 @@
       <c r="I33" s="22"/>
     </row>
     <row r="34" ht="12.75" customHeight="1">
-      <c r="A34" s="30"/>
-      <c r="B34" s="30"/>
-      <c r="C34" s="30"/>
+      <c r="A34" s="29"/>
+      <c r="B34" s="29"/>
+      <c r="C34" s="29"/>
     </row>
     <row r="35" ht="12.75" customHeight="1">
-      <c r="A35" s="30"/>
-      <c r="B35" s="30"/>
-      <c r="C35" s="30"/>
+      <c r="A35" s="29"/>
+      <c r="B35" s="29"/>
+      <c r="C35" s="29"/>
     </row>
     <row r="36" ht="12.75" customHeight="1">
-      <c r="A36" s="30"/>
-      <c r="B36" s="30"/>
-      <c r="C36" s="30"/>
+      <c r="A36" s="29"/>
+      <c r="B36" s="29"/>
+      <c r="C36" s="29"/>
     </row>
     <row r="37" ht="12.75" customHeight="1">
-      <c r="A37" s="30"/>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
+      <c r="A37" s="29"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
     </row>
     <row r="38" ht="12.75" customHeight="1">
-      <c r="A38" s="30"/>
-      <c r="B38" s="30"/>
-      <c r="C38" s="30"/>
+      <c r="A38" s="29"/>
+      <c r="B38" s="29"/>
+      <c r="C38" s="29"/>
       <c r="K38" s="4" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="Q38" s="4"/>
       <c r="R38" s="4"/>
@@ -1950,11 +1942,11 @@
       <c r="T38" s="4"/>
     </row>
     <row r="39" ht="12.75" customHeight="1">
-      <c r="A39" s="30"/>
-      <c r="B39" s="30"/>
-      <c r="C39" s="30"/>
+      <c r="A39" s="29"/>
+      <c r="B39" s="29"/>
+      <c r="C39" s="29"/>
       <c r="K39" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="Q39" s="4"/>
       <c r="R39" s="4"/>
@@ -1962,11 +1954,11 @@
       <c r="T39" s="4"/>
     </row>
     <row r="40" ht="12.75" customHeight="1">
-      <c r="A40" s="30"/>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
+      <c r="A40" s="29"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
       <c r="K40" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="Q40" s="4"/>
       <c r="R40" s="4"/>
@@ -1974,11 +1966,11 @@
       <c r="T40" s="4"/>
     </row>
     <row r="41" ht="12.75" customHeight="1">
-      <c r="A41" s="30"/>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
+      <c r="A41" s="29"/>
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
       <c r="K41" s="4" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="Q41" s="4"/>
       <c r="R41" s="4"/>
@@ -1986,11 +1978,11 @@
       <c r="T41" s="4"/>
     </row>
     <row r="42" ht="12.75" customHeight="1">
-      <c r="A42" s="30"/>
-      <c r="B42" s="30"/>
-      <c r="C42" s="30"/>
+      <c r="A42" s="29"/>
+      <c r="B42" s="29"/>
+      <c r="C42" s="29"/>
       <c r="K42" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="Q42" s="4"/>
       <c r="R42" s="4"/>
@@ -1998,11 +1990,11 @@
       <c r="T42" s="4"/>
     </row>
     <row r="43" ht="12.75" customHeight="1">
-      <c r="A43" s="30"/>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
+      <c r="A43" s="29"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
       <c r="K43" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="Q43" s="4"/>
       <c r="R43" s="4"/>
@@ -2010,45 +2002,45 @@
       <c r="T43" s="4"/>
     </row>
     <row r="44" ht="12.75" customHeight="1">
-      <c r="A44" s="30"/>
-      <c r="B44" s="30"/>
-      <c r="C44" s="30"/>
+      <c r="A44" s="29"/>
+      <c r="B44" s="29"/>
+      <c r="C44" s="29"/>
       <c r="K44" s="4"/>
       <c r="R44" s="4"/>
       <c r="S44" s="4"/>
       <c r="T44" s="4"/>
     </row>
     <row r="45" ht="12.75" customHeight="1">
-      <c r="A45" s="30"/>
-      <c r="B45" s="30"/>
-      <c r="C45" s="30"/>
+      <c r="A45" s="29"/>
+      <c r="B45" s="29"/>
+      <c r="C45" s="29"/>
       <c r="K45" s="4"/>
       <c r="R45" s="4"/>
       <c r="S45" s="4"/>
       <c r="T45" s="4"/>
     </row>
     <row r="46" ht="12.75" customHeight="1">
-      <c r="A46" s="30"/>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
+      <c r="A46" s="29"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
       <c r="K46" s="4"/>
       <c r="R46" s="4"/>
       <c r="S46" s="4"/>
       <c r="T46" s="4"/>
     </row>
     <row r="47" ht="12.75" customHeight="1">
-      <c r="A47" s="30"/>
-      <c r="B47" s="30"/>
-      <c r="C47" s="30"/>
+      <c r="A47" s="29"/>
+      <c r="B47" s="29"/>
+      <c r="C47" s="29"/>
       <c r="K47" s="4"/>
       <c r="R47" s="4"/>
       <c r="S47" s="4"/>
       <c r="T47" s="4"/>
     </row>
     <row r="48" ht="12.75" customHeight="1">
-      <c r="A48" s="30"/>
-      <c r="B48" s="30"/>
-      <c r="C48" s="30"/>
+      <c r="A48" s="29"/>
+      <c r="B48" s="29"/>
+      <c r="C48" s="29"/>
       <c r="K48" s="4"/>
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
@@ -2061,9 +2053,9 @@
       <c r="T48" s="4"/>
     </row>
     <row r="49" ht="12.75" customHeight="1">
-      <c r="A49" s="30"/>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
+      <c r="A49" s="29"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
       <c r="K49" s="4"/>
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
@@ -2076,9 +2068,9 @@
       <c r="T49" s="4"/>
     </row>
     <row r="50" ht="12.75" customHeight="1">
-      <c r="A50" s="30"/>
-      <c r="B50" s="30"/>
-      <c r="C50" s="30"/>
+      <c r="A50" s="29"/>
+      <c r="B50" s="29"/>
+      <c r="C50" s="29"/>
       <c r="K50" s="4"/>
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
@@ -2091,9 +2083,9 @@
       <c r="T50" s="4"/>
     </row>
     <row r="51" ht="12.75" customHeight="1">
-      <c r="A51" s="30"/>
-      <c r="B51" s="30"/>
-      <c r="C51" s="30"/>
+      <c r="A51" s="29"/>
+      <c r="B51" s="29"/>
+      <c r="C51" s="29"/>
       <c r="K51" s="4"/>
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
@@ -2106,9 +2098,9 @@
       <c r="T51" s="4"/>
     </row>
     <row r="52" ht="12.75" customHeight="1">
-      <c r="A52" s="30"/>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
+      <c r="A52" s="29"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
       <c r="K52" s="4"/>
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
@@ -2121,4749 +2113,4749 @@
       <c r="T52" s="4"/>
     </row>
     <row r="53" ht="12.75" customHeight="1">
-      <c r="A53" s="30"/>
-      <c r="B53" s="30"/>
-      <c r="C53" s="30"/>
+      <c r="A53" s="29"/>
+      <c r="B53" s="29"/>
+      <c r="C53" s="29"/>
     </row>
     <row r="54" ht="12.75" customHeight="1">
-      <c r="A54" s="30"/>
-      <c r="B54" s="30"/>
-      <c r="C54" s="30"/>
+      <c r="A54" s="29"/>
+      <c r="B54" s="29"/>
+      <c r="C54" s="29"/>
     </row>
     <row r="55" ht="12.75" customHeight="1">
-      <c r="A55" s="30"/>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
+      <c r="A55" s="29"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
     </row>
     <row r="56" ht="12.75" customHeight="1">
-      <c r="A56" s="30"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="30"/>
+      <c r="A56" s="29"/>
+      <c r="B56" s="29"/>
+      <c r="C56" s="29"/>
     </row>
     <row r="57" ht="12.75" customHeight="1">
-      <c r="A57" s="30"/>
-      <c r="B57" s="30"/>
-      <c r="C57" s="30"/>
+      <c r="A57" s="29"/>
+      <c r="B57" s="29"/>
+      <c r="C57" s="29"/>
     </row>
     <row r="58" ht="12.75" customHeight="1">
-      <c r="A58" s="30"/>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
+      <c r="A58" s="29"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
     </row>
     <row r="59" ht="12.75" customHeight="1">
-      <c r="A59" s="30"/>
-      <c r="B59" s="30"/>
-      <c r="C59" s="30"/>
+      <c r="A59" s="29"/>
+      <c r="B59" s="29"/>
+      <c r="C59" s="29"/>
     </row>
     <row r="60" ht="12.75" customHeight="1">
-      <c r="A60" s="30"/>
-      <c r="B60" s="30"/>
-      <c r="C60" s="30"/>
+      <c r="A60" s="29"/>
+      <c r="B60" s="29"/>
+      <c r="C60" s="29"/>
     </row>
     <row r="61" ht="12.75" customHeight="1">
-      <c r="A61" s="30"/>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
+      <c r="A61" s="29"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
     </row>
     <row r="62" ht="12.75" customHeight="1">
-      <c r="A62" s="30"/>
-      <c r="B62" s="30"/>
-      <c r="C62" s="30"/>
+      <c r="A62" s="29"/>
+      <c r="B62" s="29"/>
+      <c r="C62" s="29"/>
     </row>
     <row r="63" ht="12.75" customHeight="1">
-      <c r="A63" s="30"/>
-      <c r="B63" s="30"/>
-      <c r="C63" s="30"/>
+      <c r="A63" s="29"/>
+      <c r="B63" s="29"/>
+      <c r="C63" s="29"/>
     </row>
     <row r="64" ht="12.75" customHeight="1">
-      <c r="A64" s="30"/>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
+      <c r="A64" s="29"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
     </row>
     <row r="65" ht="12.75" customHeight="1">
-      <c r="A65" s="30"/>
-      <c r="B65" s="30"/>
-      <c r="C65" s="30"/>
+      <c r="A65" s="29"/>
+      <c r="B65" s="29"/>
+      <c r="C65" s="29"/>
     </row>
     <row r="66" ht="12.75" customHeight="1">
-      <c r="A66" s="30"/>
-      <c r="B66" s="30"/>
-      <c r="C66" s="30"/>
+      <c r="A66" s="29"/>
+      <c r="B66" s="29"/>
+      <c r="C66" s="29"/>
     </row>
     <row r="67" ht="12.75" customHeight="1">
-      <c r="A67" s="30"/>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
+      <c r="A67" s="29"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
     </row>
     <row r="68" ht="12.75" customHeight="1">
-      <c r="A68" s="30"/>
-      <c r="B68" s="30"/>
-      <c r="C68" s="30"/>
+      <c r="A68" s="29"/>
+      <c r="B68" s="29"/>
+      <c r="C68" s="29"/>
     </row>
     <row r="69" ht="12.75" customHeight="1">
-      <c r="A69" s="30"/>
-      <c r="B69" s="30"/>
-      <c r="C69" s="30"/>
+      <c r="A69" s="29"/>
+      <c r="B69" s="29"/>
+      <c r="C69" s="29"/>
     </row>
     <row r="70" ht="12.75" customHeight="1">
-      <c r="A70" s="30"/>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
+      <c r="A70" s="29"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
     </row>
     <row r="71" ht="12.75" customHeight="1">
-      <c r="A71" s="30"/>
-      <c r="B71" s="30"/>
-      <c r="C71" s="30"/>
+      <c r="A71" s="29"/>
+      <c r="B71" s="29"/>
+      <c r="C71" s="29"/>
     </row>
     <row r="72" ht="12.75" customHeight="1">
-      <c r="A72" s="30"/>
-      <c r="B72" s="30"/>
-      <c r="C72" s="30"/>
+      <c r="A72" s="29"/>
+      <c r="B72" s="29"/>
+      <c r="C72" s="29"/>
     </row>
     <row r="73" ht="12.75" customHeight="1">
-      <c r="A73" s="30"/>
-      <c r="B73" s="30"/>
-      <c r="C73" s="30"/>
+      <c r="A73" s="29"/>
+      <c r="B73" s="29"/>
+      <c r="C73" s="29"/>
     </row>
     <row r="74" ht="12.75" customHeight="1">
-      <c r="A74" s="30"/>
-      <c r="B74" s="30"/>
-      <c r="C74" s="30"/>
+      <c r="A74" s="29"/>
+      <c r="B74" s="29"/>
+      <c r="C74" s="29"/>
     </row>
     <row r="75" ht="12.75" customHeight="1">
-      <c r="A75" s="30"/>
-      <c r="B75" s="30"/>
-      <c r="C75" s="30"/>
+      <c r="A75" s="29"/>
+      <c r="B75" s="29"/>
+      <c r="C75" s="29"/>
     </row>
     <row r="76" ht="12.75" customHeight="1">
-      <c r="A76" s="30"/>
-      <c r="B76" s="30"/>
-      <c r="C76" s="30"/>
+      <c r="A76" s="29"/>
+      <c r="B76" s="29"/>
+      <c r="C76" s="29"/>
     </row>
     <row r="77" ht="12.75" customHeight="1">
-      <c r="A77" s="30"/>
-      <c r="B77" s="30"/>
-      <c r="C77" s="30"/>
+      <c r="A77" s="29"/>
+      <c r="B77" s="29"/>
+      <c r="C77" s="29"/>
     </row>
     <row r="78" ht="12.75" customHeight="1">
-      <c r="A78" s="30"/>
-      <c r="B78" s="30"/>
-      <c r="C78" s="30"/>
+      <c r="A78" s="29"/>
+      <c r="B78" s="29"/>
+      <c r="C78" s="29"/>
     </row>
     <row r="79" ht="12.75" customHeight="1">
-      <c r="A79" s="30"/>
-      <c r="B79" s="30"/>
-      <c r="C79" s="30"/>
+      <c r="A79" s="29"/>
+      <c r="B79" s="29"/>
+      <c r="C79" s="29"/>
     </row>
     <row r="80" ht="12.75" customHeight="1">
-      <c r="A80" s="30"/>
-      <c r="B80" s="30"/>
-      <c r="C80" s="30"/>
+      <c r="A80" s="29"/>
+      <c r="B80" s="29"/>
+      <c r="C80" s="29"/>
     </row>
     <row r="81" ht="12.75" customHeight="1">
-      <c r="A81" s="30"/>
-      <c r="B81" s="30"/>
-      <c r="C81" s="30"/>
+      <c r="A81" s="29"/>
+      <c r="B81" s="29"/>
+      <c r="C81" s="29"/>
     </row>
     <row r="82" ht="12.75" customHeight="1">
-      <c r="A82" s="30"/>
-      <c r="B82" s="30"/>
-      <c r="C82" s="30"/>
+      <c r="A82" s="29"/>
+      <c r="B82" s="29"/>
+      <c r="C82" s="29"/>
     </row>
     <row r="83" ht="12.75" customHeight="1">
-      <c r="A83" s="30"/>
-      <c r="B83" s="30"/>
-      <c r="C83" s="30"/>
+      <c r="A83" s="29"/>
+      <c r="B83" s="29"/>
+      <c r="C83" s="29"/>
     </row>
     <row r="84" ht="12.75" customHeight="1">
-      <c r="A84" s="30"/>
-      <c r="B84" s="30"/>
-      <c r="C84" s="30"/>
+      <c r="A84" s="29"/>
+      <c r="B84" s="29"/>
+      <c r="C84" s="29"/>
     </row>
     <row r="85" ht="12.75" customHeight="1">
-      <c r="A85" s="30"/>
-      <c r="B85" s="30"/>
-      <c r="C85" s="30"/>
+      <c r="A85" s="29"/>
+      <c r="B85" s="29"/>
+      <c r="C85" s="29"/>
     </row>
     <row r="86" ht="12.75" customHeight="1">
-      <c r="A86" s="30"/>
-      <c r="B86" s="30"/>
-      <c r="C86" s="30"/>
+      <c r="A86" s="29"/>
+      <c r="B86" s="29"/>
+      <c r="C86" s="29"/>
     </row>
     <row r="87" ht="12.75" customHeight="1">
-      <c r="A87" s="30"/>
-      <c r="B87" s="30"/>
-      <c r="C87" s="30"/>
+      <c r="A87" s="29"/>
+      <c r="B87" s="29"/>
+      <c r="C87" s="29"/>
     </row>
     <row r="88" ht="12.75" customHeight="1">
-      <c r="A88" s="30"/>
-      <c r="B88" s="30"/>
-      <c r="C88" s="30"/>
+      <c r="A88" s="29"/>
+      <c r="B88" s="29"/>
+      <c r="C88" s="29"/>
     </row>
     <row r="89" ht="12.75" customHeight="1">
-      <c r="A89" s="30"/>
-      <c r="B89" s="30"/>
-      <c r="C89" s="30"/>
+      <c r="A89" s="29"/>
+      <c r="B89" s="29"/>
+      <c r="C89" s="29"/>
     </row>
     <row r="90" ht="12.75" customHeight="1">
-      <c r="A90" s="30"/>
-      <c r="B90" s="30"/>
-      <c r="C90" s="30"/>
+      <c r="A90" s="29"/>
+      <c r="B90" s="29"/>
+      <c r="C90" s="29"/>
     </row>
     <row r="91" ht="12.75" customHeight="1">
-      <c r="A91" s="30"/>
-      <c r="B91" s="30"/>
-      <c r="C91" s="30"/>
+      <c r="A91" s="29"/>
+      <c r="B91" s="29"/>
+      <c r="C91" s="29"/>
     </row>
     <row r="92" ht="12.75" customHeight="1">
-      <c r="A92" s="30"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="30"/>
+      <c r="A92" s="29"/>
+      <c r="B92" s="29"/>
+      <c r="C92" s="29"/>
     </row>
     <row r="93" ht="12.75" customHeight="1">
-      <c r="A93" s="30"/>
-      <c r="B93" s="30"/>
-      <c r="C93" s="30"/>
+      <c r="A93" s="29"/>
+      <c r="B93" s="29"/>
+      <c r="C93" s="29"/>
     </row>
     <row r="94" ht="12.75" customHeight="1">
-      <c r="A94" s="30"/>
-      <c r="B94" s="30"/>
-      <c r="C94" s="30"/>
+      <c r="A94" s="29"/>
+      <c r="B94" s="29"/>
+      <c r="C94" s="29"/>
     </row>
     <row r="95" ht="12.75" customHeight="1">
-      <c r="A95" s="30"/>
-      <c r="B95" s="30"/>
-      <c r="C95" s="30"/>
+      <c r="A95" s="29"/>
+      <c r="B95" s="29"/>
+      <c r="C95" s="29"/>
     </row>
     <row r="96" ht="12.75" customHeight="1">
-      <c r="A96" s="30"/>
-      <c r="B96" s="30"/>
-      <c r="C96" s="30"/>
+      <c r="A96" s="29"/>
+      <c r="B96" s="29"/>
+      <c r="C96" s="29"/>
     </row>
     <row r="97" ht="12.75" customHeight="1">
-      <c r="A97" s="30"/>
-      <c r="B97" s="30"/>
-      <c r="C97" s="30"/>
+      <c r="A97" s="29"/>
+      <c r="B97" s="29"/>
+      <c r="C97" s="29"/>
     </row>
     <row r="98" ht="12.75" customHeight="1">
-      <c r="A98" s="30"/>
-      <c r="B98" s="30"/>
-      <c r="C98" s="30"/>
+      <c r="A98" s="29"/>
+      <c r="B98" s="29"/>
+      <c r="C98" s="29"/>
     </row>
     <row r="99" ht="12.75" customHeight="1">
-      <c r="A99" s="30"/>
-      <c r="B99" s="30"/>
-      <c r="C99" s="30"/>
+      <c r="A99" s="29"/>
+      <c r="B99" s="29"/>
+      <c r="C99" s="29"/>
     </row>
     <row r="100" ht="12.75" customHeight="1">
-      <c r="A100" s="30"/>
-      <c r="B100" s="30"/>
-      <c r="C100" s="30"/>
+      <c r="A100" s="29"/>
+      <c r="B100" s="29"/>
+      <c r="C100" s="29"/>
     </row>
     <row r="101" ht="12.75" customHeight="1">
-      <c r="A101" s="30"/>
-      <c r="B101" s="30"/>
-      <c r="C101" s="30"/>
+      <c r="A101" s="29"/>
+      <c r="B101" s="29"/>
+      <c r="C101" s="29"/>
     </row>
     <row r="102" ht="12.75" customHeight="1">
-      <c r="A102" s="30"/>
-      <c r="B102" s="30"/>
-      <c r="C102" s="30"/>
+      <c r="A102" s="29"/>
+      <c r="B102" s="29"/>
+      <c r="C102" s="29"/>
     </row>
     <row r="103" ht="12.75" customHeight="1">
-      <c r="A103" s="30"/>
-      <c r="B103" s="30"/>
-      <c r="C103" s="30"/>
+      <c r="A103" s="29"/>
+      <c r="B103" s="29"/>
+      <c r="C103" s="29"/>
     </row>
     <row r="104" ht="12.75" customHeight="1">
-      <c r="A104" s="30"/>
-      <c r="B104" s="30"/>
-      <c r="C104" s="30"/>
+      <c r="A104" s="29"/>
+      <c r="B104" s="29"/>
+      <c r="C104" s="29"/>
     </row>
     <row r="105" ht="12.75" customHeight="1">
-      <c r="A105" s="30"/>
-      <c r="B105" s="30"/>
-      <c r="C105" s="30"/>
+      <c r="A105" s="29"/>
+      <c r="B105" s="29"/>
+      <c r="C105" s="29"/>
     </row>
     <row r="106" ht="12.75" customHeight="1">
-      <c r="A106" s="30"/>
-      <c r="B106" s="30"/>
-      <c r="C106" s="30"/>
+      <c r="A106" s="29"/>
+      <c r="B106" s="29"/>
+      <c r="C106" s="29"/>
     </row>
     <row r="107" ht="12.75" customHeight="1">
-      <c r="A107" s="30"/>
-      <c r="B107" s="30"/>
-      <c r="C107" s="30"/>
+      <c r="A107" s="29"/>
+      <c r="B107" s="29"/>
+      <c r="C107" s="29"/>
     </row>
     <row r="108" ht="12.75" customHeight="1">
-      <c r="A108" s="30"/>
-      <c r="B108" s="30"/>
-      <c r="C108" s="30"/>
+      <c r="A108" s="29"/>
+      <c r="B108" s="29"/>
+      <c r="C108" s="29"/>
     </row>
     <row r="109" ht="12.75" customHeight="1">
-      <c r="A109" s="30"/>
-      <c r="B109" s="30"/>
-      <c r="C109" s="30"/>
+      <c r="A109" s="29"/>
+      <c r="B109" s="29"/>
+      <c r="C109" s="29"/>
     </row>
     <row r="110" ht="12.75" customHeight="1">
-      <c r="A110" s="30"/>
-      <c r="B110" s="30"/>
-      <c r="C110" s="30"/>
+      <c r="A110" s="29"/>
+      <c r="B110" s="29"/>
+      <c r="C110" s="29"/>
     </row>
     <row r="111" ht="12.75" customHeight="1">
-      <c r="A111" s="30"/>
-      <c r="B111" s="30"/>
-      <c r="C111" s="30"/>
+      <c r="A111" s="29"/>
+      <c r="B111" s="29"/>
+      <c r="C111" s="29"/>
     </row>
     <row r="112" ht="12.75" customHeight="1">
-      <c r="A112" s="30"/>
-      <c r="B112" s="30"/>
-      <c r="C112" s="30"/>
+      <c r="A112" s="29"/>
+      <c r="B112" s="29"/>
+      <c r="C112" s="29"/>
     </row>
     <row r="113" ht="12.75" customHeight="1">
-      <c r="A113" s="30"/>
-      <c r="B113" s="30"/>
-      <c r="C113" s="30"/>
+      <c r="A113" s="29"/>
+      <c r="B113" s="29"/>
+      <c r="C113" s="29"/>
     </row>
     <row r="114" ht="12.75" customHeight="1">
-      <c r="A114" s="30"/>
-      <c r="B114" s="30"/>
-      <c r="C114" s="30"/>
+      <c r="A114" s="29"/>
+      <c r="B114" s="29"/>
+      <c r="C114" s="29"/>
     </row>
     <row r="115" ht="12.75" customHeight="1">
-      <c r="A115" s="30"/>
-      <c r="B115" s="30"/>
-      <c r="C115" s="30"/>
+      <c r="A115" s="29"/>
+      <c r="B115" s="29"/>
+      <c r="C115" s="29"/>
     </row>
     <row r="116" ht="12.75" customHeight="1">
-      <c r="A116" s="30"/>
-      <c r="B116" s="30"/>
-      <c r="C116" s="30"/>
+      <c r="A116" s="29"/>
+      <c r="B116" s="29"/>
+      <c r="C116" s="29"/>
     </row>
     <row r="117" ht="12.75" customHeight="1">
-      <c r="A117" s="30"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="30"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="29"/>
+      <c r="C117" s="29"/>
     </row>
     <row r="118" ht="12.75" customHeight="1">
-      <c r="A118" s="30"/>
-      <c r="B118" s="30"/>
-      <c r="C118" s="30"/>
+      <c r="A118" s="29"/>
+      <c r="B118" s="29"/>
+      <c r="C118" s="29"/>
     </row>
     <row r="119" ht="12.75" customHeight="1">
-      <c r="A119" s="30"/>
-      <c r="B119" s="30"/>
-      <c r="C119" s="30"/>
+      <c r="A119" s="29"/>
+      <c r="B119" s="29"/>
+      <c r="C119" s="29"/>
     </row>
     <row r="120" ht="12.75" customHeight="1">
-      <c r="A120" s="30"/>
-      <c r="B120" s="30"/>
-      <c r="C120" s="30"/>
+      <c r="A120" s="29"/>
+      <c r="B120" s="29"/>
+      <c r="C120" s="29"/>
     </row>
     <row r="121" ht="12.75" customHeight="1">
-      <c r="A121" s="30"/>
-      <c r="B121" s="30"/>
-      <c r="C121" s="30"/>
+      <c r="A121" s="29"/>
+      <c r="B121" s="29"/>
+      <c r="C121" s="29"/>
     </row>
     <row r="122" ht="12.75" customHeight="1">
-      <c r="A122" s="30"/>
-      <c r="B122" s="30"/>
-      <c r="C122" s="30"/>
+      <c r="A122" s="29"/>
+      <c r="B122" s="29"/>
+      <c r="C122" s="29"/>
     </row>
     <row r="123" ht="12.75" customHeight="1">
-      <c r="A123" s="30"/>
-      <c r="B123" s="30"/>
-      <c r="C123" s="30"/>
+      <c r="A123" s="29"/>
+      <c r="B123" s="29"/>
+      <c r="C123" s="29"/>
     </row>
     <row r="124" ht="12.75" customHeight="1">
-      <c r="A124" s="30"/>
-      <c r="B124" s="30"/>
-      <c r="C124" s="30"/>
+      <c r="A124" s="29"/>
+      <c r="B124" s="29"/>
+      <c r="C124" s="29"/>
     </row>
     <row r="125" ht="12.75" customHeight="1">
-      <c r="A125" s="30"/>
-      <c r="B125" s="30"/>
-      <c r="C125" s="30"/>
+      <c r="A125" s="29"/>
+      <c r="B125" s="29"/>
+      <c r="C125" s="29"/>
     </row>
     <row r="126" ht="12.75" customHeight="1">
-      <c r="A126" s="30"/>
-      <c r="B126" s="30"/>
-      <c r="C126" s="30"/>
+      <c r="A126" s="29"/>
+      <c r="B126" s="29"/>
+      <c r="C126" s="29"/>
     </row>
     <row r="127" ht="12.75" customHeight="1">
-      <c r="A127" s="30"/>
-      <c r="B127" s="30"/>
-      <c r="C127" s="30"/>
+      <c r="A127" s="29"/>
+      <c r="B127" s="29"/>
+      <c r="C127" s="29"/>
     </row>
     <row r="128" ht="12.75" customHeight="1">
-      <c r="A128" s="30"/>
-      <c r="B128" s="30"/>
-      <c r="C128" s="30"/>
+      <c r="A128" s="29"/>
+      <c r="B128" s="29"/>
+      <c r="C128" s="29"/>
     </row>
     <row r="129" ht="12.75" customHeight="1">
-      <c r="A129" s="30"/>
-      <c r="B129" s="30"/>
-      <c r="C129" s="30"/>
+      <c r="A129" s="29"/>
+      <c r="B129" s="29"/>
+      <c r="C129" s="29"/>
     </row>
     <row r="130" ht="12.75" customHeight="1">
-      <c r="A130" s="30"/>
-      <c r="B130" s="30"/>
-      <c r="C130" s="30"/>
+      <c r="A130" s="29"/>
+      <c r="B130" s="29"/>
+      <c r="C130" s="29"/>
     </row>
     <row r="131" ht="12.75" customHeight="1">
-      <c r="A131" s="30"/>
-      <c r="B131" s="30"/>
-      <c r="C131" s="30"/>
+      <c r="A131" s="29"/>
+      <c r="B131" s="29"/>
+      <c r="C131" s="29"/>
     </row>
     <row r="132" ht="12.75" customHeight="1">
-      <c r="A132" s="30"/>
-      <c r="B132" s="30"/>
-      <c r="C132" s="30"/>
+      <c r="A132" s="29"/>
+      <c r="B132" s="29"/>
+      <c r="C132" s="29"/>
     </row>
     <row r="133" ht="12.75" customHeight="1">
-      <c r="A133" s="30"/>
-      <c r="B133" s="30"/>
-      <c r="C133" s="30"/>
+      <c r="A133" s="29"/>
+      <c r="B133" s="29"/>
+      <c r="C133" s="29"/>
     </row>
     <row r="134" ht="12.75" customHeight="1">
-      <c r="A134" s="30"/>
-      <c r="B134" s="30"/>
-      <c r="C134" s="30"/>
+      <c r="A134" s="29"/>
+      <c r="B134" s="29"/>
+      <c r="C134" s="29"/>
     </row>
     <row r="135" ht="12.75" customHeight="1">
-      <c r="A135" s="30"/>
-      <c r="B135" s="30"/>
-      <c r="C135" s="30"/>
+      <c r="A135" s="29"/>
+      <c r="B135" s="29"/>
+      <c r="C135" s="29"/>
     </row>
     <row r="136" ht="12.75" customHeight="1">
-      <c r="A136" s="30"/>
-      <c r="B136" s="30"/>
-      <c r="C136" s="30"/>
+      <c r="A136" s="29"/>
+      <c r="B136" s="29"/>
+      <c r="C136" s="29"/>
     </row>
     <row r="137" ht="12.75" customHeight="1">
-      <c r="A137" s="30"/>
-      <c r="B137" s="30"/>
-      <c r="C137" s="30"/>
+      <c r="A137" s="29"/>
+      <c r="B137" s="29"/>
+      <c r="C137" s="29"/>
     </row>
     <row r="138" ht="12.75" customHeight="1">
-      <c r="A138" s="30"/>
-      <c r="B138" s="30"/>
-      <c r="C138" s="30"/>
+      <c r="A138" s="29"/>
+      <c r="B138" s="29"/>
+      <c r="C138" s="29"/>
     </row>
     <row r="139" ht="12.75" customHeight="1">
-      <c r="A139" s="30"/>
-      <c r="B139" s="30"/>
-      <c r="C139" s="30"/>
+      <c r="A139" s="29"/>
+      <c r="B139" s="29"/>
+      <c r="C139" s="29"/>
     </row>
     <row r="140" ht="12.75" customHeight="1">
-      <c r="A140" s="30"/>
-      <c r="B140" s="30"/>
-      <c r="C140" s="30"/>
+      <c r="A140" s="29"/>
+      <c r="B140" s="29"/>
+      <c r="C140" s="29"/>
     </row>
     <row r="141" ht="12.75" customHeight="1">
-      <c r="A141" s="30"/>
-      <c r="B141" s="30"/>
-      <c r="C141" s="30"/>
+      <c r="A141" s="29"/>
+      <c r="B141" s="29"/>
+      <c r="C141" s="29"/>
     </row>
     <row r="142" ht="12.75" customHeight="1">
-      <c r="A142" s="30"/>
-      <c r="B142" s="30"/>
-      <c r="C142" s="30"/>
+      <c r="A142" s="29"/>
+      <c r="B142" s="29"/>
+      <c r="C142" s="29"/>
     </row>
     <row r="143" ht="12.75" customHeight="1">
-      <c r="A143" s="30"/>
-      <c r="B143" s="30"/>
-      <c r="C143" s="30"/>
+      <c r="A143" s="29"/>
+      <c r="B143" s="29"/>
+      <c r="C143" s="29"/>
     </row>
     <row r="144" ht="12.75" customHeight="1">
-      <c r="A144" s="30"/>
-      <c r="B144" s="30"/>
-      <c r="C144" s="30"/>
+      <c r="A144" s="29"/>
+      <c r="B144" s="29"/>
+      <c r="C144" s="29"/>
     </row>
     <row r="145" ht="12.75" customHeight="1">
-      <c r="A145" s="30"/>
-      <c r="B145" s="30"/>
-      <c r="C145" s="30"/>
+      <c r="A145" s="29"/>
+      <c r="B145" s="29"/>
+      <c r="C145" s="29"/>
     </row>
     <row r="146" ht="12.75" customHeight="1">
-      <c r="A146" s="30"/>
-      <c r="B146" s="30"/>
-      <c r="C146" s="30"/>
+      <c r="A146" s="29"/>
+      <c r="B146" s="29"/>
+      <c r="C146" s="29"/>
     </row>
     <row r="147" ht="12.75" customHeight="1">
-      <c r="A147" s="30"/>
-      <c r="B147" s="30"/>
-      <c r="C147" s="30"/>
+      <c r="A147" s="29"/>
+      <c r="B147" s="29"/>
+      <c r="C147" s="29"/>
     </row>
     <row r="148" ht="12.75" customHeight="1">
-      <c r="A148" s="30"/>
-      <c r="B148" s="30"/>
-      <c r="C148" s="30"/>
+      <c r="A148" s="29"/>
+      <c r="B148" s="29"/>
+      <c r="C148" s="29"/>
     </row>
     <row r="149" ht="12.75" customHeight="1">
-      <c r="A149" s="30"/>
-      <c r="B149" s="30"/>
-      <c r="C149" s="30"/>
+      <c r="A149" s="29"/>
+      <c r="B149" s="29"/>
+      <c r="C149" s="29"/>
     </row>
     <row r="150" ht="12.75" customHeight="1">
-      <c r="A150" s="30"/>
-      <c r="B150" s="30"/>
-      <c r="C150" s="30"/>
+      <c r="A150" s="29"/>
+      <c r="B150" s="29"/>
+      <c r="C150" s="29"/>
     </row>
     <row r="151" ht="12.75" customHeight="1">
-      <c r="A151" s="30"/>
-      <c r="B151" s="30"/>
-      <c r="C151" s="30"/>
+      <c r="A151" s="29"/>
+      <c r="B151" s="29"/>
+      <c r="C151" s="29"/>
     </row>
     <row r="152" ht="12.75" customHeight="1">
-      <c r="A152" s="30"/>
-      <c r="B152" s="30"/>
-      <c r="C152" s="30"/>
+      <c r="A152" s="29"/>
+      <c r="B152" s="29"/>
+      <c r="C152" s="29"/>
     </row>
     <row r="153" ht="12.75" customHeight="1">
-      <c r="A153" s="30"/>
-      <c r="B153" s="30"/>
-      <c r="C153" s="30"/>
+      <c r="A153" s="29"/>
+      <c r="B153" s="29"/>
+      <c r="C153" s="29"/>
     </row>
     <row r="154" ht="12.75" customHeight="1">
-      <c r="A154" s="30"/>
-      <c r="B154" s="30"/>
-      <c r="C154" s="30"/>
+      <c r="A154" s="29"/>
+      <c r="B154" s="29"/>
+      <c r="C154" s="29"/>
     </row>
     <row r="155" ht="12.75" customHeight="1">
-      <c r="A155" s="30"/>
-      <c r="B155" s="30"/>
-      <c r="C155" s="30"/>
+      <c r="A155" s="29"/>
+      <c r="B155" s="29"/>
+      <c r="C155" s="29"/>
     </row>
     <row r="156" ht="12.75" customHeight="1">
-      <c r="A156" s="30"/>
-      <c r="B156" s="30"/>
-      <c r="C156" s="30"/>
+      <c r="A156" s="29"/>
+      <c r="B156" s="29"/>
+      <c r="C156" s="29"/>
     </row>
     <row r="157" ht="12.75" customHeight="1">
-      <c r="A157" s="30"/>
-      <c r="B157" s="30"/>
-      <c r="C157" s="30"/>
+      <c r="A157" s="29"/>
+      <c r="B157" s="29"/>
+      <c r="C157" s="29"/>
     </row>
     <row r="158" ht="12.75" customHeight="1">
-      <c r="A158" s="30"/>
-      <c r="B158" s="30"/>
-      <c r="C158" s="30"/>
+      <c r="A158" s="29"/>
+      <c r="B158" s="29"/>
+      <c r="C158" s="29"/>
     </row>
     <row r="159" ht="12.75" customHeight="1">
-      <c r="A159" s="30"/>
-      <c r="B159" s="30"/>
-      <c r="C159" s="30"/>
+      <c r="A159" s="29"/>
+      <c r="B159" s="29"/>
+      <c r="C159" s="29"/>
     </row>
     <row r="160" ht="12.75" customHeight="1">
-      <c r="A160" s="30"/>
-      <c r="B160" s="30"/>
-      <c r="C160" s="30"/>
+      <c r="A160" s="29"/>
+      <c r="B160" s="29"/>
+      <c r="C160" s="29"/>
     </row>
     <row r="161" ht="12.75" customHeight="1">
-      <c r="A161" s="30"/>
-      <c r="B161" s="30"/>
-      <c r="C161" s="30"/>
+      <c r="A161" s="29"/>
+      <c r="B161" s="29"/>
+      <c r="C161" s="29"/>
     </row>
     <row r="162" ht="12.75" customHeight="1">
-      <c r="A162" s="30"/>
-      <c r="B162" s="30"/>
-      <c r="C162" s="30"/>
+      <c r="A162" s="29"/>
+      <c r="B162" s="29"/>
+      <c r="C162" s="29"/>
     </row>
     <row r="163" ht="12.75" customHeight="1">
-      <c r="A163" s="30"/>
-      <c r="B163" s="30"/>
-      <c r="C163" s="30"/>
+      <c r="A163" s="29"/>
+      <c r="B163" s="29"/>
+      <c r="C163" s="29"/>
     </row>
     <row r="164" ht="12.75" customHeight="1">
-      <c r="A164" s="30"/>
-      <c r="B164" s="30"/>
-      <c r="C164" s="30"/>
+      <c r="A164" s="29"/>
+      <c r="B164" s="29"/>
+      <c r="C164" s="29"/>
     </row>
     <row r="165" ht="12.75" customHeight="1">
-      <c r="A165" s="30"/>
-      <c r="B165" s="30"/>
-      <c r="C165" s="30"/>
+      <c r="A165" s="29"/>
+      <c r="B165" s="29"/>
+      <c r="C165" s="29"/>
     </row>
     <row r="166" ht="12.75" customHeight="1">
-      <c r="A166" s="30"/>
-      <c r="B166" s="30"/>
-      <c r="C166" s="30"/>
+      <c r="A166" s="29"/>
+      <c r="B166" s="29"/>
+      <c r="C166" s="29"/>
     </row>
     <row r="167" ht="12.75" customHeight="1">
-      <c r="A167" s="30"/>
-      <c r="B167" s="30"/>
-      <c r="C167" s="30"/>
+      <c r="A167" s="29"/>
+      <c r="B167" s="29"/>
+      <c r="C167" s="29"/>
     </row>
     <row r="168" ht="12.75" customHeight="1">
-      <c r="A168" s="30"/>
-      <c r="B168" s="30"/>
-      <c r="C168" s="30"/>
+      <c r="A168" s="29"/>
+      <c r="B168" s="29"/>
+      <c r="C168" s="29"/>
     </row>
     <row r="169" ht="12.75" customHeight="1">
-      <c r="A169" s="30"/>
-      <c r="B169" s="30"/>
-      <c r="C169" s="30"/>
+      <c r="A169" s="29"/>
+      <c r="B169" s="29"/>
+      <c r="C169" s="29"/>
     </row>
     <row r="170" ht="12.75" customHeight="1">
-      <c r="A170" s="30"/>
-      <c r="B170" s="30"/>
-      <c r="C170" s="30"/>
+      <c r="A170" s="29"/>
+      <c r="B170" s="29"/>
+      <c r="C170" s="29"/>
     </row>
     <row r="171" ht="12.75" customHeight="1">
-      <c r="A171" s="30"/>
-      <c r="B171" s="30"/>
-      <c r="C171" s="30"/>
+      <c r="A171" s="29"/>
+      <c r="B171" s="29"/>
+      <c r="C171" s="29"/>
     </row>
     <row r="172" ht="12.75" customHeight="1">
-      <c r="A172" s="30"/>
-      <c r="B172" s="30"/>
-      <c r="C172" s="30"/>
+      <c r="A172" s="29"/>
+      <c r="B172" s="29"/>
+      <c r="C172" s="29"/>
     </row>
     <row r="173" ht="12.75" customHeight="1">
-      <c r="A173" s="30"/>
-      <c r="B173" s="30"/>
-      <c r="C173" s="30"/>
+      <c r="A173" s="29"/>
+      <c r="B173" s="29"/>
+      <c r="C173" s="29"/>
     </row>
     <row r="174" ht="12.75" customHeight="1">
-      <c r="A174" s="30"/>
-      <c r="B174" s="30"/>
-      <c r="C174" s="30"/>
+      <c r="A174" s="29"/>
+      <c r="B174" s="29"/>
+      <c r="C174" s="29"/>
     </row>
     <row r="175" ht="12.75" customHeight="1">
-      <c r="A175" s="30"/>
-      <c r="B175" s="30"/>
-      <c r="C175" s="30"/>
+      <c r="A175" s="29"/>
+      <c r="B175" s="29"/>
+      <c r="C175" s="29"/>
     </row>
     <row r="176" ht="12.75" customHeight="1">
-      <c r="A176" s="30"/>
-      <c r="B176" s="30"/>
-      <c r="C176" s="30"/>
+      <c r="A176" s="29"/>
+      <c r="B176" s="29"/>
+      <c r="C176" s="29"/>
     </row>
     <row r="177" ht="12.75" customHeight="1">
-      <c r="A177" s="30"/>
-      <c r="B177" s="30"/>
-      <c r="C177" s="30"/>
+      <c r="A177" s="29"/>
+      <c r="B177" s="29"/>
+      <c r="C177" s="29"/>
     </row>
     <row r="178" ht="12.75" customHeight="1">
-      <c r="A178" s="30"/>
-      <c r="B178" s="30"/>
-      <c r="C178" s="30"/>
+      <c r="A178" s="29"/>
+      <c r="B178" s="29"/>
+      <c r="C178" s="29"/>
     </row>
     <row r="179" ht="12.75" customHeight="1">
-      <c r="A179" s="30"/>
-      <c r="B179" s="30"/>
-      <c r="C179" s="30"/>
+      <c r="A179" s="29"/>
+      <c r="B179" s="29"/>
+      <c r="C179" s="29"/>
     </row>
     <row r="180" ht="12.75" customHeight="1">
-      <c r="A180" s="30"/>
-      <c r="B180" s="30"/>
-      <c r="C180" s="30"/>
+      <c r="A180" s="29"/>
+      <c r="B180" s="29"/>
+      <c r="C180" s="29"/>
     </row>
     <row r="181" ht="12.75" customHeight="1">
-      <c r="A181" s="30"/>
-      <c r="B181" s="30"/>
-      <c r="C181" s="30"/>
+      <c r="A181" s="29"/>
+      <c r="B181" s="29"/>
+      <c r="C181" s="29"/>
     </row>
     <row r="182" ht="12.75" customHeight="1">
-      <c r="A182" s="30"/>
-      <c r="B182" s="30"/>
-      <c r="C182" s="30"/>
+      <c r="A182" s="29"/>
+      <c r="B182" s="29"/>
+      <c r="C182" s="29"/>
     </row>
     <row r="183" ht="12.75" customHeight="1">
-      <c r="A183" s="30"/>
-      <c r="B183" s="30"/>
-      <c r="C183" s="30"/>
+      <c r="A183" s="29"/>
+      <c r="B183" s="29"/>
+      <c r="C183" s="29"/>
     </row>
     <row r="184" ht="12.75" customHeight="1">
-      <c r="A184" s="30"/>
-      <c r="B184" s="30"/>
-      <c r="C184" s="30"/>
+      <c r="A184" s="29"/>
+      <c r="B184" s="29"/>
+      <c r="C184" s="29"/>
     </row>
     <row r="185" ht="12.75" customHeight="1">
-      <c r="A185" s="30"/>
-      <c r="B185" s="30"/>
-      <c r="C185" s="30"/>
+      <c r="A185" s="29"/>
+      <c r="B185" s="29"/>
+      <c r="C185" s="29"/>
     </row>
     <row r="186" ht="12.75" customHeight="1">
-      <c r="A186" s="30"/>
-      <c r="B186" s="30"/>
-      <c r="C186" s="30"/>
+      <c r="A186" s="29"/>
+      <c r="B186" s="29"/>
+      <c r="C186" s="29"/>
     </row>
     <row r="187" ht="12.75" customHeight="1">
-      <c r="A187" s="30"/>
-      <c r="B187" s="30"/>
-      <c r="C187" s="30"/>
+      <c r="A187" s="29"/>
+      <c r="B187" s="29"/>
+      <c r="C187" s="29"/>
     </row>
     <row r="188" ht="12.75" customHeight="1">
-      <c r="A188" s="30"/>
-      <c r="B188" s="30"/>
-      <c r="C188" s="30"/>
+      <c r="A188" s="29"/>
+      <c r="B188" s="29"/>
+      <c r="C188" s="29"/>
     </row>
     <row r="189" ht="12.75" customHeight="1">
-      <c r="A189" s="30"/>
-      <c r="B189" s="30"/>
-      <c r="C189" s="30"/>
+      <c r="A189" s="29"/>
+      <c r="B189" s="29"/>
+      <c r="C189" s="29"/>
     </row>
     <row r="190" ht="12.75" customHeight="1">
-      <c r="A190" s="30"/>
-      <c r="B190" s="30"/>
-      <c r="C190" s="30"/>
+      <c r="A190" s="29"/>
+      <c r="B190" s="29"/>
+      <c r="C190" s="29"/>
     </row>
     <row r="191" ht="12.75" customHeight="1">
-      <c r="A191" s="30"/>
-      <c r="B191" s="30"/>
-      <c r="C191" s="30"/>
+      <c r="A191" s="29"/>
+      <c r="B191" s="29"/>
+      <c r="C191" s="29"/>
     </row>
     <row r="192" ht="12.75" customHeight="1">
-      <c r="A192" s="30"/>
-      <c r="B192" s="30"/>
-      <c r="C192" s="30"/>
+      <c r="A192" s="29"/>
+      <c r="B192" s="29"/>
+      <c r="C192" s="29"/>
     </row>
     <row r="193" ht="12.75" customHeight="1">
-      <c r="A193" s="30"/>
-      <c r="B193" s="30"/>
-      <c r="C193" s="30"/>
+      <c r="A193" s="29"/>
+      <c r="B193" s="29"/>
+      <c r="C193" s="29"/>
     </row>
     <row r="194" ht="12.75" customHeight="1">
-      <c r="A194" s="30"/>
-      <c r="B194" s="30"/>
-      <c r="C194" s="30"/>
+      <c r="A194" s="29"/>
+      <c r="B194" s="29"/>
+      <c r="C194" s="29"/>
     </row>
     <row r="195" ht="12.75" customHeight="1">
-      <c r="A195" s="30"/>
-      <c r="B195" s="30"/>
-      <c r="C195" s="30"/>
+      <c r="A195" s="29"/>
+      <c r="B195" s="29"/>
+      <c r="C195" s="29"/>
     </row>
     <row r="196" ht="12.75" customHeight="1">
-      <c r="A196" s="30"/>
-      <c r="B196" s="30"/>
-      <c r="C196" s="30"/>
+      <c r="A196" s="29"/>
+      <c r="B196" s="29"/>
+      <c r="C196" s="29"/>
     </row>
     <row r="197" ht="12.75" customHeight="1">
-      <c r="A197" s="30"/>
-      <c r="B197" s="30"/>
-      <c r="C197" s="30"/>
+      <c r="A197" s="29"/>
+      <c r="B197" s="29"/>
+      <c r="C197" s="29"/>
     </row>
     <row r="198" ht="12.75" customHeight="1">
-      <c r="A198" s="30"/>
-      <c r="B198" s="30"/>
-      <c r="C198" s="30"/>
+      <c r="A198" s="29"/>
+      <c r="B198" s="29"/>
+      <c r="C198" s="29"/>
     </row>
     <row r="199" ht="12.75" customHeight="1">
-      <c r="A199" s="30"/>
-      <c r="B199" s="30"/>
-      <c r="C199" s="30"/>
+      <c r="A199" s="29"/>
+      <c r="B199" s="29"/>
+      <c r="C199" s="29"/>
     </row>
     <row r="200" ht="12.75" customHeight="1">
-      <c r="A200" s="30"/>
-      <c r="B200" s="30"/>
-      <c r="C200" s="30"/>
+      <c r="A200" s="29"/>
+      <c r="B200" s="29"/>
+      <c r="C200" s="29"/>
     </row>
     <row r="201" ht="12.75" customHeight="1">
-      <c r="A201" s="30"/>
-      <c r="B201" s="30"/>
-      <c r="C201" s="30"/>
+      <c r="A201" s="29"/>
+      <c r="B201" s="29"/>
+      <c r="C201" s="29"/>
     </row>
     <row r="202" ht="12.75" customHeight="1">
-      <c r="A202" s="30"/>
-      <c r="B202" s="30"/>
-      <c r="C202" s="30"/>
+      <c r="A202" s="29"/>
+      <c r="B202" s="29"/>
+      <c r="C202" s="29"/>
     </row>
     <row r="203" ht="12.75" customHeight="1">
-      <c r="A203" s="30"/>
-      <c r="B203" s="30"/>
-      <c r="C203" s="30"/>
+      <c r="A203" s="29"/>
+      <c r="B203" s="29"/>
+      <c r="C203" s="29"/>
     </row>
     <row r="204" ht="12.75" customHeight="1">
-      <c r="A204" s="30"/>
-      <c r="B204" s="30"/>
-      <c r="C204" s="30"/>
+      <c r="A204" s="29"/>
+      <c r="B204" s="29"/>
+      <c r="C204" s="29"/>
     </row>
     <row r="205" ht="12.75" customHeight="1">
-      <c r="A205" s="30"/>
-      <c r="B205" s="30"/>
-      <c r="C205" s="30"/>
+      <c r="A205" s="29"/>
+      <c r="B205" s="29"/>
+      <c r="C205" s="29"/>
     </row>
     <row r="206" ht="12.75" customHeight="1">
-      <c r="A206" s="30"/>
-      <c r="B206" s="30"/>
-      <c r="C206" s="30"/>
+      <c r="A206" s="29"/>
+      <c r="B206" s="29"/>
+      <c r="C206" s="29"/>
     </row>
     <row r="207" ht="12.75" customHeight="1">
-      <c r="A207" s="30"/>
-      <c r="B207" s="30"/>
-      <c r="C207" s="30"/>
+      <c r="A207" s="29"/>
+      <c r="B207" s="29"/>
+      <c r="C207" s="29"/>
     </row>
     <row r="208" ht="12.75" customHeight="1">
-      <c r="A208" s="30"/>
-      <c r="B208" s="30"/>
-      <c r="C208" s="30"/>
+      <c r="A208" s="29"/>
+      <c r="B208" s="29"/>
+      <c r="C208" s="29"/>
     </row>
     <row r="209" ht="12.75" customHeight="1">
-      <c r="A209" s="30"/>
-      <c r="B209" s="30"/>
-      <c r="C209" s="30"/>
+      <c r="A209" s="29"/>
+      <c r="B209" s="29"/>
+      <c r="C209" s="29"/>
     </row>
     <row r="210" ht="12.75" customHeight="1">
-      <c r="A210" s="30"/>
-      <c r="B210" s="30"/>
-      <c r="C210" s="30"/>
+      <c r="A210" s="29"/>
+      <c r="B210" s="29"/>
+      <c r="C210" s="29"/>
     </row>
     <row r="211" ht="12.75" customHeight="1">
-      <c r="A211" s="30"/>
-      <c r="B211" s="30"/>
-      <c r="C211" s="30"/>
+      <c r="A211" s="29"/>
+      <c r="B211" s="29"/>
+      <c r="C211" s="29"/>
     </row>
     <row r="212" ht="12.75" customHeight="1">
-      <c r="A212" s="30"/>
-      <c r="B212" s="30"/>
-      <c r="C212" s="30"/>
+      <c r="A212" s="29"/>
+      <c r="B212" s="29"/>
+      <c r="C212" s="29"/>
     </row>
     <row r="213" ht="12.75" customHeight="1">
-      <c r="A213" s="30"/>
-      <c r="B213" s="30"/>
-      <c r="C213" s="30"/>
+      <c r="A213" s="29"/>
+      <c r="B213" s="29"/>
+      <c r="C213" s="29"/>
     </row>
     <row r="214" ht="12.75" customHeight="1">
-      <c r="A214" s="30"/>
-      <c r="B214" s="30"/>
-      <c r="C214" s="30"/>
+      <c r="A214" s="29"/>
+      <c r="B214" s="29"/>
+      <c r="C214" s="29"/>
     </row>
     <row r="215" ht="12.75" customHeight="1">
-      <c r="A215" s="30"/>
-      <c r="B215" s="30"/>
-      <c r="C215" s="30"/>
+      <c r="A215" s="29"/>
+      <c r="B215" s="29"/>
+      <c r="C215" s="29"/>
     </row>
     <row r="216" ht="12.75" customHeight="1">
-      <c r="A216" s="30"/>
-      <c r="B216" s="30"/>
-      <c r="C216" s="30"/>
+      <c r="A216" s="29"/>
+      <c r="B216" s="29"/>
+      <c r="C216" s="29"/>
     </row>
     <row r="217" ht="12.75" customHeight="1">
-      <c r="A217" s="30"/>
-      <c r="B217" s="30"/>
-      <c r="C217" s="30"/>
+      <c r="A217" s="29"/>
+      <c r="B217" s="29"/>
+      <c r="C217" s="29"/>
     </row>
     <row r="218" ht="12.75" customHeight="1">
-      <c r="A218" s="30"/>
-      <c r="B218" s="30"/>
-      <c r="C218" s="30"/>
+      <c r="A218" s="29"/>
+      <c r="B218" s="29"/>
+      <c r="C218" s="29"/>
     </row>
     <row r="219" ht="12.75" customHeight="1">
-      <c r="A219" s="30"/>
-      <c r="B219" s="30"/>
-      <c r="C219" s="30"/>
+      <c r="A219" s="29"/>
+      <c r="B219" s="29"/>
+      <c r="C219" s="29"/>
     </row>
     <row r="220" ht="12.75" customHeight="1">
-      <c r="A220" s="30"/>
-      <c r="B220" s="30"/>
-      <c r="C220" s="30"/>
+      <c r="A220" s="29"/>
+      <c r="B220" s="29"/>
+      <c r="C220" s="29"/>
     </row>
     <row r="221" ht="12.75" customHeight="1">
-      <c r="A221" s="30"/>
-      <c r="B221" s="30"/>
-      <c r="C221" s="30"/>
+      <c r="A221" s="29"/>
+      <c r="B221" s="29"/>
+      <c r="C221" s="29"/>
     </row>
     <row r="222" ht="12.75" customHeight="1">
-      <c r="A222" s="30"/>
-      <c r="B222" s="30"/>
-      <c r="C222" s="30"/>
+      <c r="A222" s="29"/>
+      <c r="B222" s="29"/>
+      <c r="C222" s="29"/>
     </row>
     <row r="223" ht="12.75" customHeight="1">
-      <c r="A223" s="30"/>
-      <c r="B223" s="30"/>
-      <c r="C223" s="30"/>
+      <c r="A223" s="29"/>
+      <c r="B223" s="29"/>
+      <c r="C223" s="29"/>
     </row>
     <row r="224" ht="12.75" customHeight="1">
-      <c r="A224" s="30"/>
-      <c r="B224" s="30"/>
-      <c r="C224" s="30"/>
+      <c r="A224" s="29"/>
+      <c r="B224" s="29"/>
+      <c r="C224" s="29"/>
     </row>
     <row r="225" ht="12.75" customHeight="1">
-      <c r="A225" s="30"/>
-      <c r="B225" s="30"/>
-      <c r="C225" s="30"/>
+      <c r="A225" s="29"/>
+      <c r="B225" s="29"/>
+      <c r="C225" s="29"/>
     </row>
     <row r="226" ht="12.75" customHeight="1">
-      <c r="A226" s="30"/>
-      <c r="B226" s="30"/>
-      <c r="C226" s="30"/>
+      <c r="A226" s="29"/>
+      <c r="B226" s="29"/>
+      <c r="C226" s="29"/>
     </row>
     <row r="227" ht="12.75" customHeight="1">
-      <c r="A227" s="30"/>
-      <c r="B227" s="30"/>
-      <c r="C227" s="30"/>
+      <c r="A227" s="29"/>
+      <c r="B227" s="29"/>
+      <c r="C227" s="29"/>
     </row>
     <row r="228" ht="12.75" customHeight="1">
-      <c r="A228" s="30"/>
-      <c r="B228" s="30"/>
-      <c r="C228" s="30"/>
+      <c r="A228" s="29"/>
+      <c r="B228" s="29"/>
+      <c r="C228" s="29"/>
     </row>
     <row r="229" ht="12.75" customHeight="1">
-      <c r="A229" s="30"/>
-      <c r="B229" s="30"/>
-      <c r="C229" s="30"/>
+      <c r="A229" s="29"/>
+      <c r="B229" s="29"/>
+      <c r="C229" s="29"/>
     </row>
     <row r="230" ht="12.75" customHeight="1">
-      <c r="A230" s="30"/>
-      <c r="B230" s="30"/>
-      <c r="C230" s="30"/>
+      <c r="A230" s="29"/>
+      <c r="B230" s="29"/>
+      <c r="C230" s="29"/>
     </row>
     <row r="231" ht="12.75" customHeight="1">
-      <c r="A231" s="30"/>
-      <c r="B231" s="30"/>
-      <c r="C231" s="30"/>
+      <c r="A231" s="29"/>
+      <c r="B231" s="29"/>
+      <c r="C231" s="29"/>
     </row>
     <row r="232" ht="12.75" customHeight="1">
-      <c r="A232" s="30"/>
-      <c r="B232" s="30"/>
-      <c r="C232" s="30"/>
+      <c r="A232" s="29"/>
+      <c r="B232" s="29"/>
+      <c r="C232" s="29"/>
     </row>
     <row r="233" ht="12.75" customHeight="1">
-      <c r="A233" s="30"/>
-      <c r="B233" s="30"/>
-      <c r="C233" s="30"/>
+      <c r="A233" s="29"/>
+      <c r="B233" s="29"/>
+      <c r="C233" s="29"/>
     </row>
     <row r="234" ht="12.75" customHeight="1">
-      <c r="A234" s="30"/>
-      <c r="B234" s="30"/>
-      <c r="C234" s="30"/>
+      <c r="A234" s="29"/>
+      <c r="B234" s="29"/>
+      <c r="C234" s="29"/>
     </row>
     <row r="235" ht="12.75" customHeight="1">
-      <c r="A235" s="30"/>
-      <c r="B235" s="30"/>
-      <c r="C235" s="30"/>
+      <c r="A235" s="29"/>
+      <c r="B235" s="29"/>
+      <c r="C235" s="29"/>
     </row>
     <row r="236" ht="12.75" customHeight="1">
-      <c r="A236" s="30"/>
-      <c r="B236" s="30"/>
-      <c r="C236" s="30"/>
+      <c r="A236" s="29"/>
+      <c r="B236" s="29"/>
+      <c r="C236" s="29"/>
     </row>
     <row r="237" ht="12.75" customHeight="1">
-      <c r="A237" s="30"/>
-      <c r="B237" s="30"/>
-      <c r="C237" s="30"/>
+      <c r="A237" s="29"/>
+      <c r="B237" s="29"/>
+      <c r="C237" s="29"/>
     </row>
     <row r="238" ht="12.75" customHeight="1">
-      <c r="A238" s="30"/>
-      <c r="B238" s="30"/>
-      <c r="C238" s="30"/>
+      <c r="A238" s="29"/>
+      <c r="B238" s="29"/>
+      <c r="C238" s="29"/>
     </row>
     <row r="239" ht="12.75" customHeight="1">
-      <c r="A239" s="30"/>
-      <c r="B239" s="30"/>
-      <c r="C239" s="30"/>
+      <c r="A239" s="29"/>
+      <c r="B239" s="29"/>
+      <c r="C239" s="29"/>
     </row>
     <row r="240" ht="12.75" customHeight="1">
-      <c r="A240" s="30"/>
-      <c r="B240" s="30"/>
-      <c r="C240" s="30"/>
+      <c r="A240" s="29"/>
+      <c r="B240" s="29"/>
+      <c r="C240" s="29"/>
     </row>
     <row r="241" ht="12.75" customHeight="1">
-      <c r="A241" s="30"/>
-      <c r="B241" s="30"/>
-      <c r="C241" s="30"/>
+      <c r="A241" s="29"/>
+      <c r="B241" s="29"/>
+      <c r="C241" s="29"/>
     </row>
     <row r="242" ht="12.75" customHeight="1">
-      <c r="A242" s="30"/>
-      <c r="B242" s="30"/>
-      <c r="C242" s="30"/>
+      <c r="A242" s="29"/>
+      <c r="B242" s="29"/>
+      <c r="C242" s="29"/>
     </row>
     <row r="243" ht="12.75" customHeight="1">
-      <c r="A243" s="30"/>
-      <c r="B243" s="30"/>
-      <c r="C243" s="30"/>
+      <c r="A243" s="29"/>
+      <c r="B243" s="29"/>
+      <c r="C243" s="29"/>
     </row>
     <row r="244" ht="12.75" customHeight="1">
-      <c r="A244" s="30"/>
-      <c r="B244" s="30"/>
-      <c r="C244" s="30"/>
+      <c r="A244" s="29"/>
+      <c r="B244" s="29"/>
+      <c r="C244" s="29"/>
     </row>
     <row r="245" ht="12.75" customHeight="1">
-      <c r="A245" s="30"/>
-      <c r="B245" s="30"/>
-      <c r="C245" s="30"/>
+      <c r="A245" s="29"/>
+      <c r="B245" s="29"/>
+      <c r="C245" s="29"/>
     </row>
     <row r="246" ht="12.75" customHeight="1">
-      <c r="A246" s="30"/>
-      <c r="B246" s="30"/>
-      <c r="C246" s="30"/>
+      <c r="A246" s="29"/>
+      <c r="B246" s="29"/>
+      <c r="C246" s="29"/>
     </row>
     <row r="247" ht="12.75" customHeight="1">
-      <c r="A247" s="30"/>
-      <c r="B247" s="30"/>
-      <c r="C247" s="30"/>
+      <c r="A247" s="29"/>
+      <c r="B247" s="29"/>
+      <c r="C247" s="29"/>
     </row>
     <row r="248" ht="12.75" customHeight="1">
-      <c r="A248" s="30"/>
-      <c r="B248" s="30"/>
-      <c r="C248" s="30"/>
+      <c r="A248" s="29"/>
+      <c r="B248" s="29"/>
+      <c r="C248" s="29"/>
     </row>
     <row r="249" ht="12.75" customHeight="1">
-      <c r="A249" s="30"/>
-      <c r="B249" s="30"/>
-      <c r="C249" s="30"/>
+      <c r="A249" s="29"/>
+      <c r="B249" s="29"/>
+      <c r="C249" s="29"/>
     </row>
     <row r="250" ht="12.75" customHeight="1">
-      <c r="A250" s="30"/>
-      <c r="B250" s="30"/>
-      <c r="C250" s="30"/>
+      <c r="A250" s="29"/>
+      <c r="B250" s="29"/>
+      <c r="C250" s="29"/>
     </row>
     <row r="251" ht="12.75" customHeight="1">
-      <c r="A251" s="30"/>
-      <c r="B251" s="30"/>
-      <c r="C251" s="30"/>
+      <c r="A251" s="29"/>
+      <c r="B251" s="29"/>
+      <c r="C251" s="29"/>
     </row>
     <row r="252" ht="12.75" customHeight="1">
-      <c r="A252" s="30"/>
-      <c r="B252" s="30"/>
-      <c r="C252" s="30"/>
+      <c r="A252" s="29"/>
+      <c r="B252" s="29"/>
+      <c r="C252" s="29"/>
     </row>
     <row r="253" ht="12.75" customHeight="1">
-      <c r="A253" s="30"/>
-      <c r="B253" s="30"/>
-      <c r="C253" s="30"/>
+      <c r="A253" s="29"/>
+      <c r="B253" s="29"/>
+      <c r="C253" s="29"/>
     </row>
     <row r="254" ht="12.75" customHeight="1">
-      <c r="A254" s="30"/>
-      <c r="B254" s="30"/>
-      <c r="C254" s="30"/>
+      <c r="A254" s="29"/>
+      <c r="B254" s="29"/>
+      <c r="C254" s="29"/>
     </row>
     <row r="255" ht="12.75" customHeight="1">
-      <c r="A255" s="30"/>
-      <c r="B255" s="30"/>
-      <c r="C255" s="30"/>
+      <c r="A255" s="29"/>
+      <c r="B255" s="29"/>
+      <c r="C255" s="29"/>
     </row>
     <row r="256" ht="12.75" customHeight="1">
-      <c r="A256" s="30"/>
-      <c r="B256" s="30"/>
-      <c r="C256" s="30"/>
+      <c r="A256" s="29"/>
+      <c r="B256" s="29"/>
+      <c r="C256" s="29"/>
     </row>
     <row r="257" ht="12.75" customHeight="1">
-      <c r="A257" s="30"/>
-      <c r="B257" s="30"/>
-      <c r="C257" s="30"/>
+      <c r="A257" s="29"/>
+      <c r="B257" s="29"/>
+      <c r="C257" s="29"/>
     </row>
     <row r="258" ht="12.75" customHeight="1">
-      <c r="A258" s="30"/>
-      <c r="B258" s="30"/>
-      <c r="C258" s="30"/>
+      <c r="A258" s="29"/>
+      <c r="B258" s="29"/>
+      <c r="C258" s="29"/>
     </row>
     <row r="259" ht="12.75" customHeight="1">
-      <c r="A259" s="30"/>
-      <c r="B259" s="30"/>
-      <c r="C259" s="30"/>
+      <c r="A259" s="29"/>
+      <c r="B259" s="29"/>
+      <c r="C259" s="29"/>
     </row>
     <row r="260" ht="12.75" customHeight="1">
-      <c r="A260" s="30"/>
-      <c r="B260" s="30"/>
-      <c r="C260" s="30"/>
+      <c r="A260" s="29"/>
+      <c r="B260" s="29"/>
+      <c r="C260" s="29"/>
     </row>
     <row r="261" ht="12.75" customHeight="1">
-      <c r="A261" s="30"/>
-      <c r="B261" s="30"/>
-      <c r="C261" s="30"/>
+      <c r="A261" s="29"/>
+      <c r="B261" s="29"/>
+      <c r="C261" s="29"/>
     </row>
     <row r="262" ht="12.75" customHeight="1">
-      <c r="A262" s="30"/>
-      <c r="B262" s="30"/>
-      <c r="C262" s="30"/>
+      <c r="A262" s="29"/>
+      <c r="B262" s="29"/>
+      <c r="C262" s="29"/>
     </row>
     <row r="263" ht="12.75" customHeight="1">
-      <c r="A263" s="30"/>
-      <c r="B263" s="30"/>
-      <c r="C263" s="30"/>
+      <c r="A263" s="29"/>
+      <c r="B263" s="29"/>
+      <c r="C263" s="29"/>
     </row>
     <row r="264" ht="12.75" customHeight="1">
-      <c r="A264" s="30"/>
-      <c r="B264" s="30"/>
-      <c r="C264" s="30"/>
+      <c r="A264" s="29"/>
+      <c r="B264" s="29"/>
+      <c r="C264" s="29"/>
     </row>
     <row r="265" ht="12.75" customHeight="1">
-      <c r="A265" s="30"/>
-      <c r="B265" s="30"/>
-      <c r="C265" s="30"/>
+      <c r="A265" s="29"/>
+      <c r="B265" s="29"/>
+      <c r="C265" s="29"/>
     </row>
     <row r="266" ht="12.75" customHeight="1">
-      <c r="A266" s="30"/>
-      <c r="B266" s="30"/>
-      <c r="C266" s="30"/>
+      <c r="A266" s="29"/>
+      <c r="B266" s="29"/>
+      <c r="C266" s="29"/>
     </row>
     <row r="267" ht="12.75" customHeight="1">
-      <c r="A267" s="30"/>
-      <c r="B267" s="30"/>
-      <c r="C267" s="30"/>
+      <c r="A267" s="29"/>
+      <c r="B267" s="29"/>
+      <c r="C267" s="29"/>
     </row>
     <row r="268" ht="12.75" customHeight="1">
-      <c r="A268" s="30"/>
-      <c r="B268" s="30"/>
-      <c r="C268" s="30"/>
+      <c r="A268" s="29"/>
+      <c r="B268" s="29"/>
+      <c r="C268" s="29"/>
     </row>
     <row r="269" ht="12.75" customHeight="1">
-      <c r="A269" s="30"/>
-      <c r="B269" s="30"/>
-      <c r="C269" s="30"/>
+      <c r="A269" s="29"/>
+      <c r="B269" s="29"/>
+      <c r="C269" s="29"/>
     </row>
     <row r="270" ht="12.75" customHeight="1">
-      <c r="A270" s="30"/>
-      <c r="B270" s="30"/>
-      <c r="C270" s="30"/>
+      <c r="A270" s="29"/>
+      <c r="B270" s="29"/>
+      <c r="C270" s="29"/>
     </row>
     <row r="271" ht="12.75" customHeight="1">
-      <c r="A271" s="30"/>
-      <c r="B271" s="30"/>
-      <c r="C271" s="30"/>
+      <c r="A271" s="29"/>
+      <c r="B271" s="29"/>
+      <c r="C271" s="29"/>
     </row>
     <row r="272" ht="12.75" customHeight="1">
-      <c r="A272" s="30"/>
-      <c r="B272" s="30"/>
-      <c r="C272" s="30"/>
+      <c r="A272" s="29"/>
+      <c r="B272" s="29"/>
+      <c r="C272" s="29"/>
     </row>
     <row r="273" ht="12.75" customHeight="1">
-      <c r="A273" s="30"/>
-      <c r="B273" s="30"/>
-      <c r="C273" s="30"/>
+      <c r="A273" s="29"/>
+      <c r="B273" s="29"/>
+      <c r="C273" s="29"/>
     </row>
     <row r="274" ht="12.75" customHeight="1">
-      <c r="A274" s="30"/>
-      <c r="B274" s="30"/>
-      <c r="C274" s="30"/>
+      <c r="A274" s="29"/>
+      <c r="B274" s="29"/>
+      <c r="C274" s="29"/>
     </row>
     <row r="275" ht="12.75" customHeight="1">
-      <c r="A275" s="30"/>
-      <c r="B275" s="30"/>
-      <c r="C275" s="30"/>
+      <c r="A275" s="29"/>
+      <c r="B275" s="29"/>
+      <c r="C275" s="29"/>
     </row>
     <row r="276" ht="12.75" customHeight="1">
-      <c r="A276" s="30"/>
-      <c r="B276" s="30"/>
-      <c r="C276" s="30"/>
+      <c r="A276" s="29"/>
+      <c r="B276" s="29"/>
+      <c r="C276" s="29"/>
     </row>
     <row r="277" ht="12.75" customHeight="1">
-      <c r="A277" s="30"/>
-      <c r="B277" s="30"/>
-      <c r="C277" s="30"/>
+      <c r="A277" s="29"/>
+      <c r="B277" s="29"/>
+      <c r="C277" s="29"/>
     </row>
     <row r="278" ht="12.75" customHeight="1">
-      <c r="A278" s="30"/>
-      <c r="B278" s="30"/>
-      <c r="C278" s="30"/>
+      <c r="A278" s="29"/>
+      <c r="B278" s="29"/>
+      <c r="C278" s="29"/>
     </row>
     <row r="279" ht="12.75" customHeight="1">
-      <c r="A279" s="30"/>
-      <c r="B279" s="30"/>
-      <c r="C279" s="30"/>
+      <c r="A279" s="29"/>
+      <c r="B279" s="29"/>
+      <c r="C279" s="29"/>
     </row>
     <row r="280" ht="12.75" customHeight="1">
-      <c r="A280" s="30"/>
-      <c r="B280" s="30"/>
-      <c r="C280" s="30"/>
+      <c r="A280" s="29"/>
+      <c r="B280" s="29"/>
+      <c r="C280" s="29"/>
     </row>
     <row r="281" ht="12.75" customHeight="1">
-      <c r="A281" s="30"/>
-      <c r="B281" s="30"/>
-      <c r="C281" s="30"/>
+      <c r="A281" s="29"/>
+      <c r="B281" s="29"/>
+      <c r="C281" s="29"/>
     </row>
     <row r="282" ht="12.75" customHeight="1">
-      <c r="A282" s="30"/>
-      <c r="B282" s="30"/>
-      <c r="C282" s="30"/>
+      <c r="A282" s="29"/>
+      <c r="B282" s="29"/>
+      <c r="C282" s="29"/>
     </row>
     <row r="283" ht="12.75" customHeight="1">
-      <c r="A283" s="30"/>
-      <c r="B283" s="30"/>
-      <c r="C283" s="30"/>
+      <c r="A283" s="29"/>
+      <c r="B283" s="29"/>
+      <c r="C283" s="29"/>
     </row>
     <row r="284" ht="12.75" customHeight="1">
-      <c r="A284" s="30"/>
-      <c r="B284" s="30"/>
-      <c r="C284" s="30"/>
+      <c r="A284" s="29"/>
+      <c r="B284" s="29"/>
+      <c r="C284" s="29"/>
     </row>
     <row r="285" ht="12.75" customHeight="1">
-      <c r="A285" s="30"/>
-      <c r="B285" s="30"/>
-      <c r="C285" s="30"/>
+      <c r="A285" s="29"/>
+      <c r="B285" s="29"/>
+      <c r="C285" s="29"/>
     </row>
     <row r="286" ht="12.75" customHeight="1">
-      <c r="A286" s="30"/>
-      <c r="B286" s="30"/>
-      <c r="C286" s="30"/>
+      <c r="A286" s="29"/>
+      <c r="B286" s="29"/>
+      <c r="C286" s="29"/>
     </row>
     <row r="287" ht="12.75" customHeight="1">
-      <c r="A287" s="30"/>
-      <c r="B287" s="30"/>
-      <c r="C287" s="30"/>
+      <c r="A287" s="29"/>
+      <c r="B287" s="29"/>
+      <c r="C287" s="29"/>
     </row>
     <row r="288" ht="12.75" customHeight="1">
-      <c r="A288" s="30"/>
-      <c r="B288" s="30"/>
-      <c r="C288" s="30"/>
+      <c r="A288" s="29"/>
+      <c r="B288" s="29"/>
+      <c r="C288" s="29"/>
     </row>
     <row r="289" ht="12.75" customHeight="1">
-      <c r="A289" s="30"/>
-      <c r="B289" s="30"/>
-      <c r="C289" s="30"/>
+      <c r="A289" s="29"/>
+      <c r="B289" s="29"/>
+      <c r="C289" s="29"/>
     </row>
     <row r="290" ht="12.75" customHeight="1">
-      <c r="A290" s="30"/>
-      <c r="B290" s="30"/>
-      <c r="C290" s="30"/>
+      <c r="A290" s="29"/>
+      <c r="B290" s="29"/>
+      <c r="C290" s="29"/>
     </row>
     <row r="291" ht="12.75" customHeight="1">
-      <c r="A291" s="30"/>
-      <c r="B291" s="30"/>
-      <c r="C291" s="30"/>
+      <c r="A291" s="29"/>
+      <c r="B291" s="29"/>
+      <c r="C291" s="29"/>
     </row>
     <row r="292" ht="12.75" customHeight="1">
-      <c r="A292" s="30"/>
-      <c r="B292" s="30"/>
-      <c r="C292" s="30"/>
+      <c r="A292" s="29"/>
+      <c r="B292" s="29"/>
+      <c r="C292" s="29"/>
     </row>
     <row r="293" ht="12.75" customHeight="1">
-      <c r="A293" s="30"/>
-      <c r="B293" s="30"/>
-      <c r="C293" s="30"/>
+      <c r="A293" s="29"/>
+      <c r="B293" s="29"/>
+      <c r="C293" s="29"/>
     </row>
     <row r="294" ht="12.75" customHeight="1">
-      <c r="A294" s="30"/>
-      <c r="B294" s="30"/>
-      <c r="C294" s="30"/>
+      <c r="A294" s="29"/>
+      <c r="B294" s="29"/>
+      <c r="C294" s="29"/>
     </row>
     <row r="295" ht="12.75" customHeight="1">
-      <c r="A295" s="30"/>
-      <c r="B295" s="30"/>
-      <c r="C295" s="30"/>
+      <c r="A295" s="29"/>
+      <c r="B295" s="29"/>
+      <c r="C295" s="29"/>
     </row>
     <row r="296" ht="12.75" customHeight="1">
-      <c r="A296" s="30"/>
-      <c r="B296" s="30"/>
-      <c r="C296" s="30"/>
+      <c r="A296" s="29"/>
+      <c r="B296" s="29"/>
+      <c r="C296" s="29"/>
     </row>
     <row r="297" ht="12.75" customHeight="1">
-      <c r="A297" s="30"/>
-      <c r="B297" s="30"/>
-      <c r="C297" s="30"/>
+      <c r="A297" s="29"/>
+      <c r="B297" s="29"/>
+      <c r="C297" s="29"/>
     </row>
     <row r="298" ht="12.75" customHeight="1">
-      <c r="A298" s="30"/>
-      <c r="B298" s="30"/>
-      <c r="C298" s="30"/>
+      <c r="A298" s="29"/>
+      <c r="B298" s="29"/>
+      <c r="C298" s="29"/>
     </row>
     <row r="299" ht="12.75" customHeight="1">
-      <c r="A299" s="30"/>
-      <c r="B299" s="30"/>
-      <c r="C299" s="30"/>
+      <c r="A299" s="29"/>
+      <c r="B299" s="29"/>
+      <c r="C299" s="29"/>
     </row>
     <row r="300" ht="12.75" customHeight="1">
-      <c r="A300" s="30"/>
-      <c r="B300" s="30"/>
-      <c r="C300" s="30"/>
+      <c r="A300" s="29"/>
+      <c r="B300" s="29"/>
+      <c r="C300" s="29"/>
     </row>
     <row r="301" ht="12.75" customHeight="1">
-      <c r="A301" s="30"/>
-      <c r="B301" s="30"/>
-      <c r="C301" s="30"/>
+      <c r="A301" s="29"/>
+      <c r="B301" s="29"/>
+      <c r="C301" s="29"/>
     </row>
     <row r="302" ht="12.75" customHeight="1">
-      <c r="A302" s="30"/>
-      <c r="B302" s="30"/>
-      <c r="C302" s="30"/>
+      <c r="A302" s="29"/>
+      <c r="B302" s="29"/>
+      <c r="C302" s="29"/>
     </row>
     <row r="303" ht="12.75" customHeight="1">
-      <c r="A303" s="30"/>
-      <c r="B303" s="30"/>
-      <c r="C303" s="30"/>
+      <c r="A303" s="29"/>
+      <c r="B303" s="29"/>
+      <c r="C303" s="29"/>
     </row>
     <row r="304" ht="12.75" customHeight="1">
-      <c r="A304" s="30"/>
-      <c r="B304" s="30"/>
-      <c r="C304" s="30"/>
+      <c r="A304" s="29"/>
+      <c r="B304" s="29"/>
+      <c r="C304" s="29"/>
     </row>
     <row r="305" ht="12.75" customHeight="1">
-      <c r="A305" s="30"/>
-      <c r="B305" s="30"/>
-      <c r="C305" s="30"/>
+      <c r="A305" s="29"/>
+      <c r="B305" s="29"/>
+      <c r="C305" s="29"/>
     </row>
     <row r="306" ht="12.75" customHeight="1">
-      <c r="A306" s="30"/>
-      <c r="B306" s="30"/>
-      <c r="C306" s="30"/>
+      <c r="A306" s="29"/>
+      <c r="B306" s="29"/>
+      <c r="C306" s="29"/>
     </row>
     <row r="307" ht="12.75" customHeight="1">
-      <c r="A307" s="30"/>
-      <c r="B307" s="30"/>
-      <c r="C307" s="30"/>
+      <c r="A307" s="29"/>
+      <c r="B307" s="29"/>
+      <c r="C307" s="29"/>
     </row>
     <row r="308" ht="12.75" customHeight="1">
-      <c r="A308" s="30"/>
-      <c r="B308" s="30"/>
-      <c r="C308" s="30"/>
+      <c r="A308" s="29"/>
+      <c r="B308" s="29"/>
+      <c r="C308" s="29"/>
     </row>
     <row r="309" ht="12.75" customHeight="1">
-      <c r="A309" s="30"/>
-      <c r="B309" s="30"/>
-      <c r="C309" s="30"/>
+      <c r="A309" s="29"/>
+      <c r="B309" s="29"/>
+      <c r="C309" s="29"/>
     </row>
     <row r="310" ht="12.75" customHeight="1">
-      <c r="A310" s="30"/>
-      <c r="B310" s="30"/>
-      <c r="C310" s="30"/>
+      <c r="A310" s="29"/>
+      <c r="B310" s="29"/>
+      <c r="C310" s="29"/>
     </row>
     <row r="311" ht="12.75" customHeight="1">
-      <c r="A311" s="30"/>
-      <c r="B311" s="30"/>
-      <c r="C311" s="30"/>
+      <c r="A311" s="29"/>
+      <c r="B311" s="29"/>
+      <c r="C311" s="29"/>
     </row>
     <row r="312" ht="12.75" customHeight="1">
-      <c r="A312" s="30"/>
-      <c r="B312" s="30"/>
-      <c r="C312" s="30"/>
+      <c r="A312" s="29"/>
+      <c r="B312" s="29"/>
+      <c r="C312" s="29"/>
     </row>
     <row r="313" ht="12.75" customHeight="1">
-      <c r="A313" s="30"/>
-      <c r="B313" s="30"/>
-      <c r="C313" s="30"/>
+      <c r="A313" s="29"/>
+      <c r="B313" s="29"/>
+      <c r="C313" s="29"/>
     </row>
     <row r="314" ht="12.75" customHeight="1">
-      <c r="A314" s="30"/>
-      <c r="B314" s="30"/>
-      <c r="C314" s="30"/>
+      <c r="A314" s="29"/>
+      <c r="B314" s="29"/>
+      <c r="C314" s="29"/>
     </row>
     <row r="315" ht="12.75" customHeight="1">
-      <c r="A315" s="30"/>
-      <c r="B315" s="30"/>
-      <c r="C315" s="30"/>
+      <c r="A315" s="29"/>
+      <c r="B315" s="29"/>
+      <c r="C315" s="29"/>
     </row>
     <row r="316" ht="12.75" customHeight="1">
-      <c r="A316" s="30"/>
-      <c r="B316" s="30"/>
-      <c r="C316" s="30"/>
+      <c r="A316" s="29"/>
+      <c r="B316" s="29"/>
+      <c r="C316" s="29"/>
     </row>
     <row r="317" ht="12.75" customHeight="1">
-      <c r="A317" s="30"/>
-      <c r="B317" s="30"/>
-      <c r="C317" s="30"/>
+      <c r="A317" s="29"/>
+      <c r="B317" s="29"/>
+      <c r="C317" s="29"/>
     </row>
     <row r="318" ht="12.75" customHeight="1">
-      <c r="A318" s="30"/>
-      <c r="B318" s="30"/>
-      <c r="C318" s="30"/>
+      <c r="A318" s="29"/>
+      <c r="B318" s="29"/>
+      <c r="C318" s="29"/>
     </row>
     <row r="319" ht="12.75" customHeight="1">
-      <c r="A319" s="30"/>
-      <c r="B319" s="30"/>
-      <c r="C319" s="30"/>
+      <c r="A319" s="29"/>
+      <c r="B319" s="29"/>
+      <c r="C319" s="29"/>
     </row>
     <row r="320" ht="12.75" customHeight="1">
-      <c r="A320" s="30"/>
-      <c r="B320" s="30"/>
-      <c r="C320" s="30"/>
+      <c r="A320" s="29"/>
+      <c r="B320" s="29"/>
+      <c r="C320" s="29"/>
     </row>
     <row r="321" ht="12.75" customHeight="1">
-      <c r="A321" s="30"/>
-      <c r="B321" s="30"/>
-      <c r="C321" s="30"/>
+      <c r="A321" s="29"/>
+      <c r="B321" s="29"/>
+      <c r="C321" s="29"/>
     </row>
     <row r="322" ht="12.75" customHeight="1">
-      <c r="A322" s="30"/>
-      <c r="B322" s="30"/>
-      <c r="C322" s="30"/>
+      <c r="A322" s="29"/>
+      <c r="B322" s="29"/>
+      <c r="C322" s="29"/>
     </row>
     <row r="323" ht="12.75" customHeight="1">
-      <c r="A323" s="30"/>
-      <c r="B323" s="30"/>
-      <c r="C323" s="30"/>
+      <c r="A323" s="29"/>
+      <c r="B323" s="29"/>
+      <c r="C323" s="29"/>
     </row>
     <row r="324" ht="12.75" customHeight="1">
-      <c r="A324" s="30"/>
-      <c r="B324" s="30"/>
-      <c r="C324" s="30"/>
+      <c r="A324" s="29"/>
+      <c r="B324" s="29"/>
+      <c r="C324" s="29"/>
     </row>
     <row r="325" ht="12.75" customHeight="1">
-      <c r="A325" s="30"/>
-      <c r="B325" s="30"/>
-      <c r="C325" s="30"/>
+      <c r="A325" s="29"/>
+      <c r="B325" s="29"/>
+      <c r="C325" s="29"/>
     </row>
     <row r="326" ht="12.75" customHeight="1">
-      <c r="A326" s="30"/>
-      <c r="B326" s="30"/>
-      <c r="C326" s="30"/>
+      <c r="A326" s="29"/>
+      <c r="B326" s="29"/>
+      <c r="C326" s="29"/>
     </row>
     <row r="327" ht="12.75" customHeight="1">
-      <c r="A327" s="30"/>
-      <c r="B327" s="30"/>
-      <c r="C327" s="30"/>
+      <c r="A327" s="29"/>
+      <c r="B327" s="29"/>
+      <c r="C327" s="29"/>
     </row>
     <row r="328" ht="12.75" customHeight="1">
-      <c r="A328" s="30"/>
-      <c r="B328" s="30"/>
-      <c r="C328" s="30"/>
+      <c r="A328" s="29"/>
+      <c r="B328" s="29"/>
+      <c r="C328" s="29"/>
     </row>
     <row r="329" ht="12.75" customHeight="1">
-      <c r="A329" s="30"/>
-      <c r="B329" s="30"/>
-      <c r="C329" s="30"/>
+      <c r="A329" s="29"/>
+      <c r="B329" s="29"/>
+      <c r="C329" s="29"/>
     </row>
     <row r="330" ht="12.75" customHeight="1">
-      <c r="A330" s="30"/>
-      <c r="B330" s="30"/>
-      <c r="C330" s="30"/>
+      <c r="A330" s="29"/>
+      <c r="B330" s="29"/>
+      <c r="C330" s="29"/>
     </row>
     <row r="331" ht="12.75" customHeight="1">
-      <c r="A331" s="30"/>
-      <c r="B331" s="30"/>
-      <c r="C331" s="30"/>
+      <c r="A331" s="29"/>
+      <c r="B331" s="29"/>
+      <c r="C331" s="29"/>
     </row>
     <row r="332" ht="12.75" customHeight="1">
-      <c r="A332" s="30"/>
-      <c r="B332" s="30"/>
-      <c r="C332" s="30"/>
+      <c r="A332" s="29"/>
+      <c r="B332" s="29"/>
+      <c r="C332" s="29"/>
     </row>
     <row r="333" ht="12.75" customHeight="1">
-      <c r="A333" s="30"/>
-      <c r="B333" s="30"/>
-      <c r="C333" s="30"/>
+      <c r="A333" s="29"/>
+      <c r="B333" s="29"/>
+      <c r="C333" s="29"/>
     </row>
     <row r="334" ht="12.75" customHeight="1">
-      <c r="A334" s="30"/>
-      <c r="B334" s="30"/>
-      <c r="C334" s="30"/>
+      <c r="A334" s="29"/>
+      <c r="B334" s="29"/>
+      <c r="C334" s="29"/>
     </row>
     <row r="335" ht="12.75" customHeight="1">
-      <c r="A335" s="30"/>
-      <c r="B335" s="30"/>
-      <c r="C335" s="30"/>
+      <c r="A335" s="29"/>
+      <c r="B335" s="29"/>
+      <c r="C335" s="29"/>
     </row>
     <row r="336" ht="12.75" customHeight="1">
-      <c r="A336" s="30"/>
-      <c r="B336" s="30"/>
-      <c r="C336" s="30"/>
+      <c r="A336" s="29"/>
+      <c r="B336" s="29"/>
+      <c r="C336" s="29"/>
     </row>
     <row r="337" ht="12.75" customHeight="1">
-      <c r="A337" s="30"/>
-      <c r="B337" s="30"/>
-      <c r="C337" s="30"/>
+      <c r="A337" s="29"/>
+      <c r="B337" s="29"/>
+      <c r="C337" s="29"/>
     </row>
     <row r="338" ht="12.75" customHeight="1">
-      <c r="A338" s="30"/>
-      <c r="B338" s="30"/>
-      <c r="C338" s="30"/>
+      <c r="A338" s="29"/>
+      <c r="B338" s="29"/>
+      <c r="C338" s="29"/>
     </row>
     <row r="339" ht="12.75" customHeight="1">
-      <c r="A339" s="30"/>
-      <c r="B339" s="30"/>
-      <c r="C339" s="30"/>
+      <c r="A339" s="29"/>
+      <c r="B339" s="29"/>
+      <c r="C339" s="29"/>
     </row>
     <row r="340" ht="12.75" customHeight="1">
-      <c r="A340" s="30"/>
-      <c r="B340" s="30"/>
-      <c r="C340" s="30"/>
+      <c r="A340" s="29"/>
+      <c r="B340" s="29"/>
+      <c r="C340" s="29"/>
     </row>
     <row r="341" ht="12.75" customHeight="1">
-      <c r="A341" s="30"/>
-      <c r="B341" s="30"/>
-      <c r="C341" s="30"/>
+      <c r="A341" s="29"/>
+      <c r="B341" s="29"/>
+      <c r="C341" s="29"/>
     </row>
     <row r="342" ht="12.75" customHeight="1">
-      <c r="A342" s="30"/>
-      <c r="B342" s="30"/>
-      <c r="C342" s="30"/>
+      <c r="A342" s="29"/>
+      <c r="B342" s="29"/>
+      <c r="C342" s="29"/>
     </row>
     <row r="343" ht="12.75" customHeight="1">
-      <c r="A343" s="30"/>
-      <c r="B343" s="30"/>
-      <c r="C343" s="30"/>
+      <c r="A343" s="29"/>
+      <c r="B343" s="29"/>
+      <c r="C343" s="29"/>
     </row>
     <row r="344" ht="12.75" customHeight="1">
-      <c r="A344" s="30"/>
-      <c r="B344" s="30"/>
-      <c r="C344" s="30"/>
+      <c r="A344" s="29"/>
+      <c r="B344" s="29"/>
+      <c r="C344" s="29"/>
     </row>
     <row r="345" ht="12.75" customHeight="1">
-      <c r="A345" s="30"/>
-      <c r="B345" s="30"/>
-      <c r="C345" s="30"/>
+      <c r="A345" s="29"/>
+      <c r="B345" s="29"/>
+      <c r="C345" s="29"/>
     </row>
     <row r="346" ht="12.75" customHeight="1">
-      <c r="A346" s="30"/>
-      <c r="B346" s="30"/>
-      <c r="C346" s="30"/>
+      <c r="A346" s="29"/>
+      <c r="B346" s="29"/>
+      <c r="C346" s="29"/>
     </row>
     <row r="347" ht="12.75" customHeight="1">
-      <c r="A347" s="30"/>
-      <c r="B347" s="30"/>
-      <c r="C347" s="30"/>
+      <c r="A347" s="29"/>
+      <c r="B347" s="29"/>
+      <c r="C347" s="29"/>
     </row>
     <row r="348" ht="12.75" customHeight="1">
-      <c r="A348" s="30"/>
-      <c r="B348" s="30"/>
-      <c r="C348" s="30"/>
+      <c r="A348" s="29"/>
+      <c r="B348" s="29"/>
+      <c r="C348" s="29"/>
     </row>
     <row r="349" ht="12.75" customHeight="1">
-      <c r="A349" s="30"/>
-      <c r="B349" s="30"/>
-      <c r="C349" s="30"/>
+      <c r="A349" s="29"/>
+      <c r="B349" s="29"/>
+      <c r="C349" s="29"/>
     </row>
     <row r="350" ht="12.75" customHeight="1">
-      <c r="A350" s="30"/>
-      <c r="B350" s="30"/>
-      <c r="C350" s="30"/>
+      <c r="A350" s="29"/>
+      <c r="B350" s="29"/>
+      <c r="C350" s="29"/>
     </row>
     <row r="351" ht="12.75" customHeight="1">
-      <c r="A351" s="30"/>
-      <c r="B351" s="30"/>
-      <c r="C351" s="30"/>
+      <c r="A351" s="29"/>
+      <c r="B351" s="29"/>
+      <c r="C351" s="29"/>
     </row>
     <row r="352" ht="12.75" customHeight="1">
-      <c r="A352" s="30"/>
-      <c r="B352" s="30"/>
-      <c r="C352" s="30"/>
+      <c r="A352" s="29"/>
+      <c r="B352" s="29"/>
+      <c r="C352" s="29"/>
     </row>
     <row r="353" ht="12.75" customHeight="1">
-      <c r="A353" s="30"/>
-      <c r="B353" s="30"/>
-      <c r="C353" s="30"/>
+      <c r="A353" s="29"/>
+      <c r="B353" s="29"/>
+      <c r="C353" s="29"/>
     </row>
     <row r="354" ht="12.75" customHeight="1">
-      <c r="A354" s="30"/>
-      <c r="B354" s="30"/>
-      <c r="C354" s="30"/>
+      <c r="A354" s="29"/>
+      <c r="B354" s="29"/>
+      <c r="C354" s="29"/>
     </row>
     <row r="355" ht="12.75" customHeight="1">
-      <c r="A355" s="30"/>
-      <c r="B355" s="30"/>
-      <c r="C355" s="30"/>
+      <c r="A355" s="29"/>
+      <c r="B355" s="29"/>
+      <c r="C355" s="29"/>
     </row>
     <row r="356" ht="12.75" customHeight="1">
-      <c r="A356" s="30"/>
-      <c r="B356" s="30"/>
-      <c r="C356" s="30"/>
+      <c r="A356" s="29"/>
+      <c r="B356" s="29"/>
+      <c r="C356" s="29"/>
     </row>
     <row r="357" ht="12.75" customHeight="1">
-      <c r="A357" s="30"/>
-      <c r="B357" s="30"/>
-      <c r="C357" s="30"/>
+      <c r="A357" s="29"/>
+      <c r="B357" s="29"/>
+      <c r="C357" s="29"/>
     </row>
     <row r="358" ht="12.75" customHeight="1">
-      <c r="A358" s="30"/>
-      <c r="B358" s="30"/>
-      <c r="C358" s="30"/>
+      <c r="A358" s="29"/>
+      <c r="B358" s="29"/>
+      <c r="C358" s="29"/>
     </row>
     <row r="359" ht="12.75" customHeight="1">
-      <c r="A359" s="30"/>
-      <c r="B359" s="30"/>
-      <c r="C359" s="30"/>
+      <c r="A359" s="29"/>
+      <c r="B359" s="29"/>
+      <c r="C359" s="29"/>
     </row>
     <row r="360" ht="12.75" customHeight="1">
-      <c r="A360" s="30"/>
-      <c r="B360" s="30"/>
-      <c r="C360" s="30"/>
+      <c r="A360" s="29"/>
+      <c r="B360" s="29"/>
+      <c r="C360" s="29"/>
     </row>
     <row r="361" ht="12.75" customHeight="1">
-      <c r="A361" s="30"/>
-      <c r="B361" s="30"/>
-      <c r="C361" s="30"/>
+      <c r="A361" s="29"/>
+      <c r="B361" s="29"/>
+      <c r="C361" s="29"/>
     </row>
     <row r="362" ht="12.75" customHeight="1">
-      <c r="A362" s="30"/>
-      <c r="B362" s="30"/>
-      <c r="C362" s="30"/>
+      <c r="A362" s="29"/>
+      <c r="B362" s="29"/>
+      <c r="C362" s="29"/>
     </row>
     <row r="363" ht="12.75" customHeight="1">
-      <c r="A363" s="30"/>
-      <c r="B363" s="30"/>
-      <c r="C363" s="30"/>
+      <c r="A363" s="29"/>
+      <c r="B363" s="29"/>
+      <c r="C363" s="29"/>
     </row>
     <row r="364" ht="12.75" customHeight="1">
-      <c r="A364" s="30"/>
-      <c r="B364" s="30"/>
-      <c r="C364" s="30"/>
+      <c r="A364" s="29"/>
+      <c r="B364" s="29"/>
+      <c r="C364" s="29"/>
     </row>
     <row r="365" ht="12.75" customHeight="1">
-      <c r="A365" s="30"/>
-      <c r="B365" s="30"/>
-      <c r="C365" s="30"/>
+      <c r="A365" s="29"/>
+      <c r="B365" s="29"/>
+      <c r="C365" s="29"/>
     </row>
     <row r="366" ht="12.75" customHeight="1">
-      <c r="A366" s="30"/>
-      <c r="B366" s="30"/>
-      <c r="C366" s="30"/>
+      <c r="A366" s="29"/>
+      <c r="B366" s="29"/>
+      <c r="C366" s="29"/>
     </row>
     <row r="367" ht="12.75" customHeight="1">
-      <c r="A367" s="30"/>
-      <c r="B367" s="30"/>
-      <c r="C367" s="30"/>
+      <c r="A367" s="29"/>
+      <c r="B367" s="29"/>
+      <c r="C367" s="29"/>
     </row>
     <row r="368" ht="12.75" customHeight="1">
-      <c r="A368" s="30"/>
-      <c r="B368" s="30"/>
-      <c r="C368" s="30"/>
+      <c r="A368" s="29"/>
+      <c r="B368" s="29"/>
+      <c r="C368" s="29"/>
     </row>
     <row r="369" ht="12.75" customHeight="1">
-      <c r="A369" s="30"/>
-      <c r="B369" s="30"/>
-      <c r="C369" s="30"/>
+      <c r="A369" s="29"/>
+      <c r="B369" s="29"/>
+      <c r="C369" s="29"/>
     </row>
     <row r="370" ht="12.75" customHeight="1">
-      <c r="A370" s="30"/>
-      <c r="B370" s="30"/>
-      <c r="C370" s="30"/>
+      <c r="A370" s="29"/>
+      <c r="B370" s="29"/>
+      <c r="C370" s="29"/>
     </row>
     <row r="371" ht="12.75" customHeight="1">
-      <c r="A371" s="30"/>
-      <c r="B371" s="30"/>
-      <c r="C371" s="30"/>
+      <c r="A371" s="29"/>
+      <c r="B371" s="29"/>
+      <c r="C371" s="29"/>
     </row>
     <row r="372" ht="12.75" customHeight="1">
-      <c r="A372" s="30"/>
-      <c r="B372" s="30"/>
-      <c r="C372" s="30"/>
+      <c r="A372" s="29"/>
+      <c r="B372" s="29"/>
+      <c r="C372" s="29"/>
     </row>
     <row r="373" ht="12.75" customHeight="1">
-      <c r="A373" s="30"/>
-      <c r="B373" s="30"/>
-      <c r="C373" s="30"/>
+      <c r="A373" s="29"/>
+      <c r="B373" s="29"/>
+      <c r="C373" s="29"/>
     </row>
     <row r="374" ht="12.75" customHeight="1">
-      <c r="A374" s="30"/>
-      <c r="B374" s="30"/>
-      <c r="C374" s="30"/>
+      <c r="A374" s="29"/>
+      <c r="B374" s="29"/>
+      <c r="C374" s="29"/>
     </row>
     <row r="375" ht="12.75" customHeight="1">
-      <c r="A375" s="30"/>
-      <c r="B375" s="30"/>
-      <c r="C375" s="30"/>
+      <c r="A375" s="29"/>
+      <c r="B375" s="29"/>
+      <c r="C375" s="29"/>
     </row>
     <row r="376" ht="12.75" customHeight="1">
-      <c r="A376" s="30"/>
-      <c r="B376" s="30"/>
-      <c r="C376" s="30"/>
+      <c r="A376" s="29"/>
+      <c r="B376" s="29"/>
+      <c r="C376" s="29"/>
     </row>
     <row r="377" ht="12.75" customHeight="1">
-      <c r="A377" s="30"/>
-      <c r="B377" s="30"/>
-      <c r="C377" s="30"/>
+      <c r="A377" s="29"/>
+      <c r="B377" s="29"/>
+      <c r="C377" s="29"/>
     </row>
     <row r="378" ht="12.75" customHeight="1">
-      <c r="A378" s="30"/>
-      <c r="B378" s="30"/>
-      <c r="C378" s="30"/>
+      <c r="A378" s="29"/>
+      <c r="B378" s="29"/>
+      <c r="C378" s="29"/>
     </row>
     <row r="379" ht="12.75" customHeight="1">
-      <c r="A379" s="30"/>
-      <c r="B379" s="30"/>
-      <c r="C379" s="30"/>
+      <c r="A379" s="29"/>
+      <c r="B379" s="29"/>
+      <c r="C379" s="29"/>
     </row>
     <row r="380" ht="12.75" customHeight="1">
-      <c r="A380" s="30"/>
-      <c r="B380" s="30"/>
-      <c r="C380" s="30"/>
+      <c r="A380" s="29"/>
+      <c r="B380" s="29"/>
+      <c r="C380" s="29"/>
     </row>
     <row r="381" ht="12.75" customHeight="1">
-      <c r="A381" s="30"/>
-      <c r="B381" s="30"/>
-      <c r="C381" s="30"/>
+      <c r="A381" s="29"/>
+      <c r="B381" s="29"/>
+      <c r="C381" s="29"/>
     </row>
     <row r="382" ht="12.75" customHeight="1">
-      <c r="A382" s="30"/>
-      <c r="B382" s="30"/>
-      <c r="C382" s="30"/>
+      <c r="A382" s="29"/>
+      <c r="B382" s="29"/>
+      <c r="C382" s="29"/>
     </row>
     <row r="383" ht="12.75" customHeight="1">
-      <c r="A383" s="30"/>
-      <c r="B383" s="30"/>
-      <c r="C383" s="30"/>
+      <c r="A383" s="29"/>
+      <c r="B383" s="29"/>
+      <c r="C383" s="29"/>
     </row>
     <row r="384" ht="12.75" customHeight="1">
-      <c r="A384" s="30"/>
-      <c r="B384" s="30"/>
-      <c r="C384" s="30"/>
+      <c r="A384" s="29"/>
+      <c r="B384" s="29"/>
+      <c r="C384" s="29"/>
     </row>
     <row r="385" ht="12.75" customHeight="1">
-      <c r="A385" s="30"/>
-      <c r="B385" s="30"/>
-      <c r="C385" s="30"/>
+      <c r="A385" s="29"/>
+      <c r="B385" s="29"/>
+      <c r="C385" s="29"/>
     </row>
     <row r="386" ht="12.75" customHeight="1">
-      <c r="A386" s="30"/>
-      <c r="B386" s="30"/>
-      <c r="C386" s="30"/>
+      <c r="A386" s="29"/>
+      <c r="B386" s="29"/>
+      <c r="C386" s="29"/>
     </row>
     <row r="387" ht="12.75" customHeight="1">
-      <c r="A387" s="30"/>
-      <c r="B387" s="30"/>
-      <c r="C387" s="30"/>
+      <c r="A387" s="29"/>
+      <c r="B387" s="29"/>
+      <c r="C387" s="29"/>
     </row>
     <row r="388" ht="12.75" customHeight="1">
-      <c r="A388" s="30"/>
-      <c r="B388" s="30"/>
-      <c r="C388" s="30"/>
+      <c r="A388" s="29"/>
+      <c r="B388" s="29"/>
+      <c r="C388" s="29"/>
     </row>
     <row r="389" ht="12.75" customHeight="1">
-      <c r="A389" s="30"/>
-      <c r="B389" s="30"/>
-      <c r="C389" s="30"/>
+      <c r="A389" s="29"/>
+      <c r="B389" s="29"/>
+      <c r="C389" s="29"/>
     </row>
     <row r="390" ht="12.75" customHeight="1">
-      <c r="A390" s="30"/>
-      <c r="B390" s="30"/>
-      <c r="C390" s="30"/>
+      <c r="A390" s="29"/>
+      <c r="B390" s="29"/>
+      <c r="C390" s="29"/>
     </row>
     <row r="391" ht="12.75" customHeight="1">
-      <c r="A391" s="30"/>
-      <c r="B391" s="30"/>
-      <c r="C391" s="30"/>
+      <c r="A391" s="29"/>
+      <c r="B391" s="29"/>
+      <c r="C391" s="29"/>
     </row>
     <row r="392" ht="12.75" customHeight="1">
-      <c r="A392" s="30"/>
-      <c r="B392" s="30"/>
-      <c r="C392" s="30"/>
+      <c r="A392" s="29"/>
+      <c r="B392" s="29"/>
+      <c r="C392" s="29"/>
     </row>
     <row r="393" ht="12.75" customHeight="1">
-      <c r="A393" s="30"/>
-      <c r="B393" s="30"/>
-      <c r="C393" s="30"/>
+      <c r="A393" s="29"/>
+      <c r="B393" s="29"/>
+      <c r="C393" s="29"/>
     </row>
     <row r="394" ht="12.75" customHeight="1">
-      <c r="A394" s="30"/>
-      <c r="B394" s="30"/>
-      <c r="C394" s="30"/>
+      <c r="A394" s="29"/>
+      <c r="B394" s="29"/>
+      <c r="C394" s="29"/>
     </row>
     <row r="395" ht="12.75" customHeight="1">
-      <c r="A395" s="30"/>
-      <c r="B395" s="30"/>
-      <c r="C395" s="30"/>
+      <c r="A395" s="29"/>
+      <c r="B395" s="29"/>
+      <c r="C395" s="29"/>
     </row>
     <row r="396" ht="12.75" customHeight="1">
-      <c r="A396" s="30"/>
-      <c r="B396" s="30"/>
-      <c r="C396" s="30"/>
+      <c r="A396" s="29"/>
+      <c r="B396" s="29"/>
+      <c r="C396" s="29"/>
     </row>
     <row r="397" ht="12.75" customHeight="1">
-      <c r="A397" s="30"/>
-      <c r="B397" s="30"/>
-      <c r="C397" s="30"/>
+      <c r="A397" s="29"/>
+      <c r="B397" s="29"/>
+      <c r="C397" s="29"/>
     </row>
     <row r="398" ht="12.75" customHeight="1">
-      <c r="A398" s="30"/>
-      <c r="B398" s="30"/>
-      <c r="C398" s="30"/>
+      <c r="A398" s="29"/>
+      <c r="B398" s="29"/>
+      <c r="C398" s="29"/>
     </row>
     <row r="399" ht="12.75" customHeight="1">
-      <c r="A399" s="30"/>
-      <c r="B399" s="30"/>
-      <c r="C399" s="30"/>
+      <c r="A399" s="29"/>
+      <c r="B399" s="29"/>
+      <c r="C399" s="29"/>
     </row>
     <row r="400" ht="12.75" customHeight="1">
-      <c r="A400" s="30"/>
-      <c r="B400" s="30"/>
-      <c r="C400" s="30"/>
+      <c r="A400" s="29"/>
+      <c r="B400" s="29"/>
+      <c r="C400" s="29"/>
     </row>
     <row r="401" ht="12.75" customHeight="1">
-      <c r="A401" s="30"/>
-      <c r="B401" s="30"/>
-      <c r="C401" s="30"/>
+      <c r="A401" s="29"/>
+      <c r="B401" s="29"/>
+      <c r="C401" s="29"/>
     </row>
     <row r="402" ht="12.75" customHeight="1">
-      <c r="A402" s="30"/>
-      <c r="B402" s="30"/>
-      <c r="C402" s="30"/>
+      <c r="A402" s="29"/>
+      <c r="B402" s="29"/>
+      <c r="C402" s="29"/>
     </row>
     <row r="403" ht="12.75" customHeight="1">
-      <c r="A403" s="30"/>
-      <c r="B403" s="30"/>
-      <c r="C403" s="30"/>
+      <c r="A403" s="29"/>
+      <c r="B403" s="29"/>
+      <c r="C403" s="29"/>
     </row>
     <row r="404" ht="12.75" customHeight="1">
-      <c r="A404" s="30"/>
-      <c r="B404" s="30"/>
-      <c r="C404" s="30"/>
+      <c r="A404" s="29"/>
+      <c r="B404" s="29"/>
+      <c r="C404" s="29"/>
     </row>
     <row r="405" ht="12.75" customHeight="1">
-      <c r="A405" s="30"/>
-      <c r="B405" s="30"/>
-      <c r="C405" s="30"/>
+      <c r="A405" s="29"/>
+      <c r="B405" s="29"/>
+      <c r="C405" s="29"/>
     </row>
     <row r="406" ht="12.75" customHeight="1">
-      <c r="A406" s="30"/>
-      <c r="B406" s="30"/>
-      <c r="C406" s="30"/>
+      <c r="A406" s="29"/>
+      <c r="B406" s="29"/>
+      <c r="C406" s="29"/>
     </row>
     <row r="407" ht="12.75" customHeight="1">
-      <c r="A407" s="30"/>
-      <c r="B407" s="30"/>
-      <c r="C407" s="30"/>
+      <c r="A407" s="29"/>
+      <c r="B407" s="29"/>
+      <c r="C407" s="29"/>
     </row>
     <row r="408" ht="12.75" customHeight="1">
-      <c r="A408" s="30"/>
-      <c r="B408" s="30"/>
-      <c r="C408" s="30"/>
+      <c r="A408" s="29"/>
+      <c r="B408" s="29"/>
+      <c r="C408" s="29"/>
     </row>
     <row r="409" ht="12.75" customHeight="1">
-      <c r="A409" s="30"/>
-      <c r="B409" s="30"/>
-      <c r="C409" s="30"/>
+      <c r="A409" s="29"/>
+      <c r="B409" s="29"/>
+      <c r="C409" s="29"/>
     </row>
     <row r="410" ht="12.75" customHeight="1">
-      <c r="A410" s="30"/>
-      <c r="B410" s="30"/>
-      <c r="C410" s="30"/>
+      <c r="A410" s="29"/>
+      <c r="B410" s="29"/>
+      <c r="C410" s="29"/>
     </row>
     <row r="411" ht="12.75" customHeight="1">
-      <c r="A411" s="30"/>
-      <c r="B411" s="30"/>
-      <c r="C411" s="30"/>
+      <c r="A411" s="29"/>
+      <c r="B411" s="29"/>
+      <c r="C411" s="29"/>
     </row>
     <row r="412" ht="12.75" customHeight="1">
-      <c r="A412" s="30"/>
-      <c r="B412" s="30"/>
-      <c r="C412" s="30"/>
+      <c r="A412" s="29"/>
+      <c r="B412" s="29"/>
+      <c r="C412" s="29"/>
     </row>
     <row r="413" ht="12.75" customHeight="1">
-      <c r="A413" s="30"/>
-      <c r="B413" s="30"/>
-      <c r="C413" s="30"/>
+      <c r="A413" s="29"/>
+      <c r="B413" s="29"/>
+      <c r="C413" s="29"/>
     </row>
     <row r="414" ht="12.75" customHeight="1">
-      <c r="A414" s="30"/>
-      <c r="B414" s="30"/>
-      <c r="C414" s="30"/>
+      <c r="A414" s="29"/>
+      <c r="B414" s="29"/>
+      <c r="C414" s="29"/>
     </row>
     <row r="415" ht="12.75" customHeight="1">
-      <c r="A415" s="30"/>
-      <c r="B415" s="30"/>
-      <c r="C415" s="30"/>
+      <c r="A415" s="29"/>
+      <c r="B415" s="29"/>
+      <c r="C415" s="29"/>
     </row>
     <row r="416" ht="12.75" customHeight="1">
-      <c r="A416" s="30"/>
-      <c r="B416" s="30"/>
-      <c r="C416" s="30"/>
+      <c r="A416" s="29"/>
+      <c r="B416" s="29"/>
+      <c r="C416" s="29"/>
     </row>
     <row r="417" ht="12.75" customHeight="1">
-      <c r="A417" s="30"/>
-      <c r="B417" s="30"/>
-      <c r="C417" s="30"/>
+      <c r="A417" s="29"/>
+      <c r="B417" s="29"/>
+      <c r="C417" s="29"/>
     </row>
     <row r="418" ht="12.75" customHeight="1">
-      <c r="A418" s="30"/>
-      <c r="B418" s="30"/>
-      <c r="C418" s="30"/>
+      <c r="A418" s="29"/>
+      <c r="B418" s="29"/>
+      <c r="C418" s="29"/>
     </row>
     <row r="419" ht="12.75" customHeight="1">
-      <c r="A419" s="30"/>
-      <c r="B419" s="30"/>
-      <c r="C419" s="30"/>
+      <c r="A419" s="29"/>
+      <c r="B419" s="29"/>
+      <c r="C419" s="29"/>
     </row>
     <row r="420" ht="12.75" customHeight="1">
-      <c r="A420" s="30"/>
-      <c r="B420" s="30"/>
-      <c r="C420" s="30"/>
+      <c r="A420" s="29"/>
+      <c r="B420" s="29"/>
+      <c r="C420" s="29"/>
     </row>
     <row r="421" ht="12.75" customHeight="1">
-      <c r="A421" s="30"/>
-      <c r="B421" s="30"/>
-      <c r="C421" s="30"/>
+      <c r="A421" s="29"/>
+      <c r="B421" s="29"/>
+      <c r="C421" s="29"/>
     </row>
     <row r="422" ht="12.75" customHeight="1">
-      <c r="A422" s="30"/>
-      <c r="B422" s="30"/>
-      <c r="C422" s="30"/>
+      <c r="A422" s="29"/>
+      <c r="B422" s="29"/>
+      <c r="C422" s="29"/>
     </row>
     <row r="423" ht="12.75" customHeight="1">
-      <c r="A423" s="30"/>
-      <c r="B423" s="30"/>
-      <c r="C423" s="30"/>
+      <c r="A423" s="29"/>
+      <c r="B423" s="29"/>
+      <c r="C423" s="29"/>
     </row>
     <row r="424" ht="12.75" customHeight="1">
-      <c r="A424" s="30"/>
-      <c r="B424" s="30"/>
-      <c r="C424" s="30"/>
+      <c r="A424" s="29"/>
+      <c r="B424" s="29"/>
+      <c r="C424" s="29"/>
     </row>
     <row r="425" ht="12.75" customHeight="1">
-      <c r="A425" s="30"/>
-      <c r="B425" s="30"/>
-      <c r="C425" s="30"/>
+      <c r="A425" s="29"/>
+      <c r="B425" s="29"/>
+      <c r="C425" s="29"/>
     </row>
     <row r="426" ht="12.75" customHeight="1">
-      <c r="A426" s="30"/>
-      <c r="B426" s="30"/>
-      <c r="C426" s="30"/>
+      <c r="A426" s="29"/>
+      <c r="B426" s="29"/>
+      <c r="C426" s="29"/>
     </row>
     <row r="427" ht="12.75" customHeight="1">
-      <c r="A427" s="30"/>
-      <c r="B427" s="30"/>
-      <c r="C427" s="30"/>
+      <c r="A427" s="29"/>
+      <c r="B427" s="29"/>
+      <c r="C427" s="29"/>
     </row>
     <row r="428" ht="12.75" customHeight="1">
-      <c r="A428" s="30"/>
-      <c r="B428" s="30"/>
-      <c r="C428" s="30"/>
+      <c r="A428" s="29"/>
+      <c r="B428" s="29"/>
+      <c r="C428" s="29"/>
     </row>
     <row r="429" ht="12.75" customHeight="1">
-      <c r="A429" s="30"/>
-      <c r="B429" s="30"/>
-      <c r="C429" s="30"/>
+      <c r="A429" s="29"/>
+      <c r="B429" s="29"/>
+      <c r="C429" s="29"/>
     </row>
     <row r="430" ht="12.75" customHeight="1">
-      <c r="A430" s="30"/>
-      <c r="B430" s="30"/>
-      <c r="C430" s="30"/>
+      <c r="A430" s="29"/>
+      <c r="B430" s="29"/>
+      <c r="C430" s="29"/>
     </row>
     <row r="431" ht="12.75" customHeight="1">
-      <c r="A431" s="30"/>
-      <c r="B431" s="30"/>
-      <c r="C431" s="30"/>
+      <c r="A431" s="29"/>
+      <c r="B431" s="29"/>
+      <c r="C431" s="29"/>
     </row>
     <row r="432" ht="12.75" customHeight="1">
-      <c r="A432" s="30"/>
-      <c r="B432" s="30"/>
-      <c r="C432" s="30"/>
+      <c r="A432" s="29"/>
+      <c r="B432" s="29"/>
+      <c r="C432" s="29"/>
     </row>
     <row r="433" ht="12.75" customHeight="1">
-      <c r="A433" s="30"/>
-      <c r="B433" s="30"/>
-      <c r="C433" s="30"/>
+      <c r="A433" s="29"/>
+      <c r="B433" s="29"/>
+      <c r="C433" s="29"/>
     </row>
     <row r="434" ht="12.75" customHeight="1">
-      <c r="A434" s="30"/>
-      <c r="B434" s="30"/>
-      <c r="C434" s="30"/>
+      <c r="A434" s="29"/>
+      <c r="B434" s="29"/>
+      <c r="C434" s="29"/>
     </row>
     <row r="435" ht="12.75" customHeight="1">
-      <c r="A435" s="30"/>
-      <c r="B435" s="30"/>
-      <c r="C435" s="30"/>
+      <c r="A435" s="29"/>
+      <c r="B435" s="29"/>
+      <c r="C435" s="29"/>
     </row>
     <row r="436" ht="12.75" customHeight="1">
-      <c r="A436" s="30"/>
-      <c r="B436" s="30"/>
-      <c r="C436" s="30"/>
+      <c r="A436" s="29"/>
+      <c r="B436" s="29"/>
+      <c r="C436" s="29"/>
     </row>
     <row r="437" ht="12.75" customHeight="1">
-      <c r="A437" s="30"/>
-      <c r="B437" s="30"/>
-      <c r="C437" s="30"/>
+      <c r="A437" s="29"/>
+      <c r="B437" s="29"/>
+      <c r="C437" s="29"/>
     </row>
     <row r="438" ht="12.75" customHeight="1">
-      <c r="A438" s="30"/>
-      <c r="B438" s="30"/>
-      <c r="C438" s="30"/>
+      <c r="A438" s="29"/>
+      <c r="B438" s="29"/>
+      <c r="C438" s="29"/>
     </row>
     <row r="439" ht="12.75" customHeight="1">
-      <c r="A439" s="30"/>
-      <c r="B439" s="30"/>
-      <c r="C439" s="30"/>
+      <c r="A439" s="29"/>
+      <c r="B439" s="29"/>
+      <c r="C439" s="29"/>
     </row>
     <row r="440" ht="12.75" customHeight="1">
-      <c r="A440" s="30"/>
-      <c r="B440" s="30"/>
-      <c r="C440" s="30"/>
+      <c r="A440" s="29"/>
+      <c r="B440" s="29"/>
+      <c r="C440" s="29"/>
     </row>
     <row r="441" ht="12.75" customHeight="1">
-      <c r="A441" s="30"/>
-      <c r="B441" s="30"/>
-      <c r="C441" s="30"/>
+      <c r="A441" s="29"/>
+      <c r="B441" s="29"/>
+      <c r="C441" s="29"/>
     </row>
     <row r="442" ht="12.75" customHeight="1">
-      <c r="A442" s="30"/>
-      <c r="B442" s="30"/>
-      <c r="C442" s="30"/>
+      <c r="A442" s="29"/>
+      <c r="B442" s="29"/>
+      <c r="C442" s="29"/>
     </row>
     <row r="443" ht="12.75" customHeight="1">
-      <c r="A443" s="30"/>
-      <c r="B443" s="30"/>
-      <c r="C443" s="30"/>
+      <c r="A443" s="29"/>
+      <c r="B443" s="29"/>
+      <c r="C443" s="29"/>
     </row>
     <row r="444" ht="12.75" customHeight="1">
-      <c r="A444" s="30"/>
-      <c r="B444" s="30"/>
-      <c r="C444" s="30"/>
+      <c r="A444" s="29"/>
+      <c r="B444" s="29"/>
+      <c r="C444" s="29"/>
     </row>
     <row r="445" ht="12.75" customHeight="1">
-      <c r="A445" s="30"/>
-      <c r="B445" s="30"/>
-      <c r="C445" s="30"/>
+      <c r="A445" s="29"/>
+      <c r="B445" s="29"/>
+      <c r="C445" s="29"/>
     </row>
     <row r="446" ht="12.75" customHeight="1">
-      <c r="A446" s="30"/>
-      <c r="B446" s="30"/>
-      <c r="C446" s="30"/>
+      <c r="A446" s="29"/>
+      <c r="B446" s="29"/>
+      <c r="C446" s="29"/>
     </row>
     <row r="447" ht="12.75" customHeight="1">
-      <c r="A447" s="30"/>
-      <c r="B447" s="30"/>
-      <c r="C447" s="30"/>
+      <c r="A447" s="29"/>
+      <c r="B447" s="29"/>
+      <c r="C447" s="29"/>
     </row>
     <row r="448" ht="12.75" customHeight="1">
-      <c r="A448" s="30"/>
-      <c r="B448" s="30"/>
-      <c r="C448" s="30"/>
+      <c r="A448" s="29"/>
+      <c r="B448" s="29"/>
+      <c r="C448" s="29"/>
     </row>
     <row r="449" ht="12.75" customHeight="1">
-      <c r="A449" s="30"/>
-      <c r="B449" s="30"/>
-      <c r="C449" s="30"/>
+      <c r="A449" s="29"/>
+      <c r="B449" s="29"/>
+      <c r="C449" s="29"/>
     </row>
     <row r="450" ht="12.75" customHeight="1">
-      <c r="A450" s="30"/>
-      <c r="B450" s="30"/>
-      <c r="C450" s="30"/>
+      <c r="A450" s="29"/>
+      <c r="B450" s="29"/>
+      <c r="C450" s="29"/>
     </row>
     <row r="451" ht="12.75" customHeight="1">
-      <c r="A451" s="30"/>
-      <c r="B451" s="30"/>
-      <c r="C451" s="30"/>
+      <c r="A451" s="29"/>
+      <c r="B451" s="29"/>
+      <c r="C451" s="29"/>
     </row>
     <row r="452" ht="12.75" customHeight="1">
-      <c r="A452" s="30"/>
-      <c r="B452" s="30"/>
-      <c r="C452" s="30"/>
+      <c r="A452" s="29"/>
+      <c r="B452" s="29"/>
+      <c r="C452" s="29"/>
     </row>
     <row r="453" ht="12.75" customHeight="1">
-      <c r="A453" s="30"/>
-      <c r="B453" s="30"/>
-      <c r="C453" s="30"/>
+      <c r="A453" s="29"/>
+      <c r="B453" s="29"/>
+      <c r="C453" s="29"/>
     </row>
     <row r="454" ht="12.75" customHeight="1">
-      <c r="A454" s="30"/>
-      <c r="B454" s="30"/>
-      <c r="C454" s="30"/>
+      <c r="A454" s="29"/>
+      <c r="B454" s="29"/>
+      <c r="C454" s="29"/>
     </row>
     <row r="455" ht="12.75" customHeight="1">
-      <c r="A455" s="30"/>
-      <c r="B455" s="30"/>
-      <c r="C455" s="30"/>
+      <c r="A455" s="29"/>
+      <c r="B455" s="29"/>
+      <c r="C455" s="29"/>
     </row>
     <row r="456" ht="12.75" customHeight="1">
-      <c r="A456" s="30"/>
-      <c r="B456" s="30"/>
-      <c r="C456" s="30"/>
+      <c r="A456" s="29"/>
+      <c r="B456" s="29"/>
+      <c r="C456" s="29"/>
     </row>
     <row r="457" ht="12.75" customHeight="1">
-      <c r="A457" s="30"/>
-      <c r="B457" s="30"/>
-      <c r="C457" s="30"/>
+      <c r="A457" s="29"/>
+      <c r="B457" s="29"/>
+      <c r="C457" s="29"/>
     </row>
     <row r="458" ht="12.75" customHeight="1">
-      <c r="A458" s="30"/>
-      <c r="B458" s="30"/>
-      <c r="C458" s="30"/>
+      <c r="A458" s="29"/>
+      <c r="B458" s="29"/>
+      <c r="C458" s="29"/>
     </row>
     <row r="459" ht="12.75" customHeight="1">
-      <c r="A459" s="30"/>
-      <c r="B459" s="30"/>
-      <c r="C459" s="30"/>
+      <c r="A459" s="29"/>
+      <c r="B459" s="29"/>
+      <c r="C459" s="29"/>
     </row>
     <row r="460" ht="12.75" customHeight="1">
-      <c r="A460" s="30"/>
-      <c r="B460" s="30"/>
-      <c r="C460" s="30"/>
+      <c r="A460" s="29"/>
+      <c r="B460" s="29"/>
+      <c r="C460" s="29"/>
     </row>
     <row r="461" ht="12.75" customHeight="1">
-      <c r="A461" s="30"/>
-      <c r="B461" s="30"/>
-      <c r="C461" s="30"/>
+      <c r="A461" s="29"/>
+      <c r="B461" s="29"/>
+      <c r="C461" s="29"/>
     </row>
     <row r="462" ht="12.75" customHeight="1">
-      <c r="A462" s="30"/>
-      <c r="B462" s="30"/>
-      <c r="C462" s="30"/>
+      <c r="A462" s="29"/>
+      <c r="B462" s="29"/>
+      <c r="C462" s="29"/>
     </row>
     <row r="463" ht="12.75" customHeight="1">
-      <c r="A463" s="30"/>
-      <c r="B463" s="30"/>
-      <c r="C463" s="30"/>
+      <c r="A463" s="29"/>
+      <c r="B463" s="29"/>
+      <c r="C463" s="29"/>
     </row>
     <row r="464" ht="12.75" customHeight="1">
-      <c r="A464" s="30"/>
-      <c r="B464" s="30"/>
-      <c r="C464" s="30"/>
+      <c r="A464" s="29"/>
+      <c r="B464" s="29"/>
+      <c r="C464" s="29"/>
     </row>
     <row r="465" ht="12.75" customHeight="1">
-      <c r="A465" s="30"/>
-      <c r="B465" s="30"/>
-      <c r="C465" s="30"/>
+      <c r="A465" s="29"/>
+      <c r="B465" s="29"/>
+      <c r="C465" s="29"/>
     </row>
     <row r="466" ht="12.75" customHeight="1">
-      <c r="A466" s="30"/>
-      <c r="B466" s="30"/>
-      <c r="C466" s="30"/>
+      <c r="A466" s="29"/>
+      <c r="B466" s="29"/>
+      <c r="C466" s="29"/>
     </row>
     <row r="467" ht="12.75" customHeight="1">
-      <c r="A467" s="30"/>
-      <c r="B467" s="30"/>
-      <c r="C467" s="30"/>
+      <c r="A467" s="29"/>
+      <c r="B467" s="29"/>
+      <c r="C467" s="29"/>
     </row>
     <row r="468" ht="12.75" customHeight="1">
-      <c r="A468" s="30"/>
-      <c r="B468" s="30"/>
-      <c r="C468" s="30"/>
+      <c r="A468" s="29"/>
+      <c r="B468" s="29"/>
+      <c r="C468" s="29"/>
     </row>
     <row r="469" ht="12.75" customHeight="1">
-      <c r="A469" s="30"/>
-      <c r="B469" s="30"/>
-      <c r="C469" s="30"/>
+      <c r="A469" s="29"/>
+      <c r="B469" s="29"/>
+      <c r="C469" s="29"/>
     </row>
     <row r="470" ht="12.75" customHeight="1">
-      <c r="A470" s="30"/>
-      <c r="B470" s="30"/>
-      <c r="C470" s="30"/>
+      <c r="A470" s="29"/>
+      <c r="B470" s="29"/>
+      <c r="C470" s="29"/>
     </row>
     <row r="471" ht="12.75" customHeight="1">
-      <c r="A471" s="30"/>
-      <c r="B471" s="30"/>
-      <c r="C471" s="30"/>
+      <c r="A471" s="29"/>
+      <c r="B471" s="29"/>
+      <c r="C471" s="29"/>
     </row>
     <row r="472" ht="12.75" customHeight="1">
-      <c r="A472" s="30"/>
-      <c r="B472" s="30"/>
-      <c r="C472" s="30"/>
+      <c r="A472" s="29"/>
+      <c r="B472" s="29"/>
+      <c r="C472" s="29"/>
     </row>
     <row r="473" ht="12.75" customHeight="1">
-      <c r="A473" s="30"/>
-      <c r="B473" s="30"/>
-      <c r="C473" s="30"/>
+      <c r="A473" s="29"/>
+      <c r="B473" s="29"/>
+      <c r="C473" s="29"/>
     </row>
     <row r="474" ht="12.75" customHeight="1">
-      <c r="A474" s="30"/>
-      <c r="B474" s="30"/>
-      <c r="C474" s="30"/>
+      <c r="A474" s="29"/>
+      <c r="B474" s="29"/>
+      <c r="C474" s="29"/>
     </row>
     <row r="475" ht="12.75" customHeight="1">
-      <c r="A475" s="30"/>
-      <c r="B475" s="30"/>
-      <c r="C475" s="30"/>
+      <c r="A475" s="29"/>
+      <c r="B475" s="29"/>
+      <c r="C475" s="29"/>
     </row>
     <row r="476" ht="12.75" customHeight="1">
-      <c r="A476" s="30"/>
-      <c r="B476" s="30"/>
-      <c r="C476" s="30"/>
+      <c r="A476" s="29"/>
+      <c r="B476" s="29"/>
+      <c r="C476" s="29"/>
     </row>
     <row r="477" ht="12.75" customHeight="1">
-      <c r="A477" s="30"/>
-      <c r="B477" s="30"/>
-      <c r="C477" s="30"/>
+      <c r="A477" s="29"/>
+      <c r="B477" s="29"/>
+      <c r="C477" s="29"/>
     </row>
     <row r="478" ht="12.75" customHeight="1">
-      <c r="A478" s="30"/>
-      <c r="B478" s="30"/>
-      <c r="C478" s="30"/>
+      <c r="A478" s="29"/>
+      <c r="B478" s="29"/>
+      <c r="C478" s="29"/>
     </row>
     <row r="479" ht="12.75" customHeight="1">
-      <c r="A479" s="30"/>
-      <c r="B479" s="30"/>
-      <c r="C479" s="30"/>
+      <c r="A479" s="29"/>
+      <c r="B479" s="29"/>
+      <c r="C479" s="29"/>
     </row>
     <row r="480" ht="12.75" customHeight="1">
-      <c r="A480" s="30"/>
-      <c r="B480" s="30"/>
-      <c r="C480" s="30"/>
+      <c r="A480" s="29"/>
+      <c r="B480" s="29"/>
+      <c r="C480" s="29"/>
     </row>
     <row r="481" ht="12.75" customHeight="1">
-      <c r="A481" s="30"/>
-      <c r="B481" s="30"/>
-      <c r="C481" s="30"/>
+      <c r="A481" s="29"/>
+      <c r="B481" s="29"/>
+      <c r="C481" s="29"/>
     </row>
     <row r="482" ht="12.75" customHeight="1">
-      <c r="A482" s="30"/>
-      <c r="B482" s="30"/>
-      <c r="C482" s="30"/>
+      <c r="A482" s="29"/>
+      <c r="B482" s="29"/>
+      <c r="C482" s="29"/>
     </row>
     <row r="483" ht="12.75" customHeight="1">
-      <c r="A483" s="30"/>
-      <c r="B483" s="30"/>
-      <c r="C483" s="30"/>
+      <c r="A483" s="29"/>
+      <c r="B483" s="29"/>
+      <c r="C483" s="29"/>
     </row>
     <row r="484" ht="12.75" customHeight="1">
-      <c r="A484" s="30"/>
-      <c r="B484" s="30"/>
-      <c r="C484" s="30"/>
+      <c r="A484" s="29"/>
+      <c r="B484" s="29"/>
+      <c r="C484" s="29"/>
     </row>
     <row r="485" ht="12.75" customHeight="1">
-      <c r="A485" s="30"/>
-      <c r="B485" s="30"/>
-      <c r="C485" s="30"/>
+      <c r="A485" s="29"/>
+      <c r="B485" s="29"/>
+      <c r="C485" s="29"/>
     </row>
     <row r="486" ht="12.75" customHeight="1">
-      <c r="A486" s="30"/>
-      <c r="B486" s="30"/>
-      <c r="C486" s="30"/>
+      <c r="A486" s="29"/>
+      <c r="B486" s="29"/>
+      <c r="C486" s="29"/>
     </row>
     <row r="487" ht="12.75" customHeight="1">
-      <c r="A487" s="30"/>
-      <c r="B487" s="30"/>
-      <c r="C487" s="30"/>
+      <c r="A487" s="29"/>
+      <c r="B487" s="29"/>
+      <c r="C487" s="29"/>
     </row>
     <row r="488" ht="12.75" customHeight="1">
-      <c r="A488" s="30"/>
-      <c r="B488" s="30"/>
-      <c r="C488" s="30"/>
+      <c r="A488" s="29"/>
+      <c r="B488" s="29"/>
+      <c r="C488" s="29"/>
     </row>
     <row r="489" ht="12.75" customHeight="1">
-      <c r="A489" s="30"/>
-      <c r="B489" s="30"/>
-      <c r="C489" s="30"/>
+      <c r="A489" s="29"/>
+      <c r="B489" s="29"/>
+      <c r="C489" s="29"/>
     </row>
     <row r="490" ht="12.75" customHeight="1">
-      <c r="A490" s="30"/>
-      <c r="B490" s="30"/>
-      <c r="C490" s="30"/>
+      <c r="A490" s="29"/>
+      <c r="B490" s="29"/>
+      <c r="C490" s="29"/>
     </row>
     <row r="491" ht="12.75" customHeight="1">
-      <c r="A491" s="30"/>
-      <c r="B491" s="30"/>
-      <c r="C491" s="30"/>
+      <c r="A491" s="29"/>
+      <c r="B491" s="29"/>
+      <c r="C491" s="29"/>
     </row>
     <row r="492" ht="12.75" customHeight="1">
-      <c r="A492" s="30"/>
-      <c r="B492" s="30"/>
-      <c r="C492" s="30"/>
+      <c r="A492" s="29"/>
+      <c r="B492" s="29"/>
+      <c r="C492" s="29"/>
     </row>
     <row r="493" ht="12.75" customHeight="1">
-      <c r="A493" s="30"/>
-      <c r="B493" s="30"/>
-      <c r="C493" s="30"/>
+      <c r="A493" s="29"/>
+      <c r="B493" s="29"/>
+      <c r="C493" s="29"/>
     </row>
     <row r="494" ht="12.75" customHeight="1">
-      <c r="A494" s="30"/>
-      <c r="B494" s="30"/>
-      <c r="C494" s="30"/>
+      <c r="A494" s="29"/>
+      <c r="B494" s="29"/>
+      <c r="C494" s="29"/>
     </row>
     <row r="495" ht="12.75" customHeight="1">
-      <c r="A495" s="30"/>
-      <c r="B495" s="30"/>
-      <c r="C495" s="30"/>
+      <c r="A495" s="29"/>
+      <c r="B495" s="29"/>
+      <c r="C495" s="29"/>
     </row>
     <row r="496" ht="12.75" customHeight="1">
-      <c r="A496" s="30"/>
-      <c r="B496" s="30"/>
-      <c r="C496" s="30"/>
+      <c r="A496" s="29"/>
+      <c r="B496" s="29"/>
+      <c r="C496" s="29"/>
     </row>
     <row r="497" ht="12.75" customHeight="1">
-      <c r="A497" s="30"/>
-      <c r="B497" s="30"/>
-      <c r="C497" s="30"/>
+      <c r="A497" s="29"/>
+      <c r="B497" s="29"/>
+      <c r="C497" s="29"/>
     </row>
     <row r="498" ht="12.75" customHeight="1">
-      <c r="A498" s="30"/>
-      <c r="B498" s="30"/>
-      <c r="C498" s="30"/>
+      <c r="A498" s="29"/>
+      <c r="B498" s="29"/>
+      <c r="C498" s="29"/>
     </row>
     <row r="499" ht="12.75" customHeight="1">
-      <c r="A499" s="30"/>
-      <c r="B499" s="30"/>
-      <c r="C499" s="30"/>
+      <c r="A499" s="29"/>
+      <c r="B499" s="29"/>
+      <c r="C499" s="29"/>
     </row>
     <row r="500" ht="12.75" customHeight="1">
-      <c r="A500" s="30"/>
-      <c r="B500" s="30"/>
-      <c r="C500" s="30"/>
+      <c r="A500" s="29"/>
+      <c r="B500" s="29"/>
+      <c r="C500" s="29"/>
     </row>
     <row r="501" ht="12.75" customHeight="1">
-      <c r="A501" s="30"/>
-      <c r="B501" s="30"/>
-      <c r="C501" s="30"/>
+      <c r="A501" s="29"/>
+      <c r="B501" s="29"/>
+      <c r="C501" s="29"/>
     </row>
     <row r="502" ht="12.75" customHeight="1">
-      <c r="A502" s="30"/>
-      <c r="B502" s="30"/>
-      <c r="C502" s="30"/>
+      <c r="A502" s="29"/>
+      <c r="B502" s="29"/>
+      <c r="C502" s="29"/>
     </row>
     <row r="503" ht="12.75" customHeight="1">
-      <c r="A503" s="30"/>
-      <c r="B503" s="30"/>
-      <c r="C503" s="30"/>
+      <c r="A503" s="29"/>
+      <c r="B503" s="29"/>
+      <c r="C503" s="29"/>
     </row>
     <row r="504" ht="12.75" customHeight="1">
-      <c r="A504" s="30"/>
-      <c r="B504" s="30"/>
-      <c r="C504" s="30"/>
+      <c r="A504" s="29"/>
+      <c r="B504" s="29"/>
+      <c r="C504" s="29"/>
     </row>
     <row r="505" ht="12.75" customHeight="1">
-      <c r="A505" s="30"/>
-      <c r="B505" s="30"/>
-      <c r="C505" s="30"/>
+      <c r="A505" s="29"/>
+      <c r="B505" s="29"/>
+      <c r="C505" s="29"/>
     </row>
     <row r="506" ht="12.75" customHeight="1">
-      <c r="A506" s="30"/>
-      <c r="B506" s="30"/>
-      <c r="C506" s="30"/>
+      <c r="A506" s="29"/>
+      <c r="B506" s="29"/>
+      <c r="C506" s="29"/>
     </row>
     <row r="507" ht="12.75" customHeight="1">
-      <c r="A507" s="30"/>
-      <c r="B507" s="30"/>
-      <c r="C507" s="30"/>
+      <c r="A507" s="29"/>
+      <c r="B507" s="29"/>
+      <c r="C507" s="29"/>
     </row>
     <row r="508" ht="12.75" customHeight="1">
-      <c r="A508" s="30"/>
-      <c r="B508" s="30"/>
-      <c r="C508" s="30"/>
+      <c r="A508" s="29"/>
+      <c r="B508" s="29"/>
+      <c r="C508" s="29"/>
     </row>
     <row r="509" ht="12.75" customHeight="1">
-      <c r="A509" s="30"/>
-      <c r="B509" s="30"/>
-      <c r="C509" s="30"/>
+      <c r="A509" s="29"/>
+      <c r="B509" s="29"/>
+      <c r="C509" s="29"/>
     </row>
     <row r="510" ht="12.75" customHeight="1">
-      <c r="A510" s="30"/>
-      <c r="B510" s="30"/>
-      <c r="C510" s="30"/>
+      <c r="A510" s="29"/>
+      <c r="B510" s="29"/>
+      <c r="C510" s="29"/>
     </row>
     <row r="511" ht="12.75" customHeight="1">
-      <c r="A511" s="30"/>
-      <c r="B511" s="30"/>
-      <c r="C511" s="30"/>
+      <c r="A511" s="29"/>
+      <c r="B511" s="29"/>
+      <c r="C511" s="29"/>
     </row>
     <row r="512" ht="12.75" customHeight="1">
-      <c r="A512" s="30"/>
-      <c r="B512" s="30"/>
-      <c r="C512" s="30"/>
+      <c r="A512" s="29"/>
+      <c r="B512" s="29"/>
+      <c r="C512" s="29"/>
     </row>
     <row r="513" ht="12.75" customHeight="1">
-      <c r="A513" s="30"/>
-      <c r="B513" s="30"/>
-      <c r="C513" s="30"/>
+      <c r="A513" s="29"/>
+      <c r="B513" s="29"/>
+      <c r="C513" s="29"/>
     </row>
     <row r="514" ht="12.75" customHeight="1">
-      <c r="A514" s="30"/>
-      <c r="B514" s="30"/>
-      <c r="C514" s="30"/>
+      <c r="A514" s="29"/>
+      <c r="B514" s="29"/>
+      <c r="C514" s="29"/>
     </row>
     <row r="515" ht="12.75" customHeight="1">
-      <c r="A515" s="30"/>
-      <c r="B515" s="30"/>
-      <c r="C515" s="30"/>
+      <c r="A515" s="29"/>
+      <c r="B515" s="29"/>
+      <c r="C515" s="29"/>
     </row>
     <row r="516" ht="12.75" customHeight="1">
-      <c r="A516" s="30"/>
-      <c r="B516" s="30"/>
-      <c r="C516" s="30"/>
+      <c r="A516" s="29"/>
+      <c r="B516" s="29"/>
+      <c r="C516" s="29"/>
     </row>
     <row r="517" ht="12.75" customHeight="1">
-      <c r="A517" s="30"/>
-      <c r="B517" s="30"/>
-      <c r="C517" s="30"/>
+      <c r="A517" s="29"/>
+      <c r="B517" s="29"/>
+      <c r="C517" s="29"/>
     </row>
     <row r="518" ht="12.75" customHeight="1">
-      <c r="A518" s="30"/>
-      <c r="B518" s="30"/>
-      <c r="C518" s="30"/>
+      <c r="A518" s="29"/>
+      <c r="B518" s="29"/>
+      <c r="C518" s="29"/>
     </row>
     <row r="519" ht="12.75" customHeight="1">
-      <c r="A519" s="30"/>
-      <c r="B519" s="30"/>
-      <c r="C519" s="30"/>
+      <c r="A519" s="29"/>
+      <c r="B519" s="29"/>
+      <c r="C519" s="29"/>
     </row>
     <row r="520" ht="12.75" customHeight="1">
-      <c r="A520" s="30"/>
-      <c r="B520" s="30"/>
-      <c r="C520" s="30"/>
+      <c r="A520" s="29"/>
+      <c r="B520" s="29"/>
+      <c r="C520" s="29"/>
     </row>
     <row r="521" ht="12.75" customHeight="1">
-      <c r="A521" s="30"/>
-      <c r="B521" s="30"/>
-      <c r="C521" s="30"/>
+      <c r="A521" s="29"/>
+      <c r="B521" s="29"/>
+      <c r="C521" s="29"/>
     </row>
     <row r="522" ht="12.75" customHeight="1">
-      <c r="A522" s="30"/>
-      <c r="B522" s="30"/>
-      <c r="C522" s="30"/>
+      <c r="A522" s="29"/>
+      <c r="B522" s="29"/>
+      <c r="C522" s="29"/>
     </row>
     <row r="523" ht="12.75" customHeight="1">
-      <c r="A523" s="30"/>
-      <c r="B523" s="30"/>
-      <c r="C523" s="30"/>
+      <c r="A523" s="29"/>
+      <c r="B523" s="29"/>
+      <c r="C523" s="29"/>
     </row>
     <row r="524" ht="12.75" customHeight="1">
-      <c r="A524" s="30"/>
-      <c r="B524" s="30"/>
-      <c r="C524" s="30"/>
+      <c r="A524" s="29"/>
+      <c r="B524" s="29"/>
+      <c r="C524" s="29"/>
     </row>
     <row r="525" ht="12.75" customHeight="1">
-      <c r="A525" s="30"/>
-      <c r="B525" s="30"/>
-      <c r="C525" s="30"/>
+      <c r="A525" s="29"/>
+      <c r="B525" s="29"/>
+      <c r="C525" s="29"/>
     </row>
     <row r="526" ht="12.75" customHeight="1">
-      <c r="A526" s="30"/>
-      <c r="B526" s="30"/>
-      <c r="C526" s="30"/>
+      <c r="A526" s="29"/>
+      <c r="B526" s="29"/>
+      <c r="C526" s="29"/>
     </row>
     <row r="527" ht="12.75" customHeight="1">
-      <c r="A527" s="30"/>
-      <c r="B527" s="30"/>
-      <c r="C527" s="30"/>
+      <c r="A527" s="29"/>
+      <c r="B527" s="29"/>
+      <c r="C527" s="29"/>
     </row>
     <row r="528" ht="12.75" customHeight="1">
-      <c r="A528" s="30"/>
-      <c r="B528" s="30"/>
-      <c r="C528" s="30"/>
+      <c r="A528" s="29"/>
+      <c r="B528" s="29"/>
+      <c r="C528" s="29"/>
     </row>
     <row r="529" ht="12.75" customHeight="1">
-      <c r="A529" s="30"/>
-      <c r="B529" s="30"/>
-      <c r="C529" s="30"/>
+      <c r="A529" s="29"/>
+      <c r="B529" s="29"/>
+      <c r="C529" s="29"/>
     </row>
     <row r="530" ht="12.75" customHeight="1">
-      <c r="A530" s="30"/>
-      <c r="B530" s="30"/>
-      <c r="C530" s="30"/>
+      <c r="A530" s="29"/>
+      <c r="B530" s="29"/>
+      <c r="C530" s="29"/>
     </row>
     <row r="531" ht="12.75" customHeight="1">
-      <c r="A531" s="30"/>
-      <c r="B531" s="30"/>
-      <c r="C531" s="30"/>
+      <c r="A531" s="29"/>
+      <c r="B531" s="29"/>
+      <c r="C531" s="29"/>
     </row>
     <row r="532" ht="12.75" customHeight="1">
-      <c r="A532" s="30"/>
-      <c r="B532" s="30"/>
-      <c r="C532" s="30"/>
+      <c r="A532" s="29"/>
+      <c r="B532" s="29"/>
+      <c r="C532" s="29"/>
     </row>
     <row r="533" ht="12.75" customHeight="1">
-      <c r="A533" s="30"/>
-      <c r="B533" s="30"/>
-      <c r="C533" s="30"/>
+      <c r="A533" s="29"/>
+      <c r="B533" s="29"/>
+      <c r="C533" s="29"/>
     </row>
     <row r="534" ht="12.75" customHeight="1">
-      <c r="A534" s="30"/>
-      <c r="B534" s="30"/>
-      <c r="C534" s="30"/>
+      <c r="A534" s="29"/>
+      <c r="B534" s="29"/>
+      <c r="C534" s="29"/>
     </row>
     <row r="535" ht="12.75" customHeight="1">
-      <c r="A535" s="30"/>
-      <c r="B535" s="30"/>
-      <c r="C535" s="30"/>
+      <c r="A535" s="29"/>
+      <c r="B535" s="29"/>
+      <c r="C535" s="29"/>
     </row>
     <row r="536" ht="12.75" customHeight="1">
-      <c r="A536" s="30"/>
-      <c r="B536" s="30"/>
-      <c r="C536" s="30"/>
+      <c r="A536" s="29"/>
+      <c r="B536" s="29"/>
+      <c r="C536" s="29"/>
     </row>
     <row r="537" ht="12.75" customHeight="1">
-      <c r="A537" s="30"/>
-      <c r="B537" s="30"/>
-      <c r="C537" s="30"/>
+      <c r="A537" s="29"/>
+      <c r="B537" s="29"/>
+      <c r="C537" s="29"/>
     </row>
     <row r="538" ht="12.75" customHeight="1">
-      <c r="A538" s="30"/>
-      <c r="B538" s="30"/>
-      <c r="C538" s="30"/>
+      <c r="A538" s="29"/>
+      <c r="B538" s="29"/>
+      <c r="C538" s="29"/>
     </row>
     <row r="539" ht="12.75" customHeight="1">
-      <c r="A539" s="30"/>
-      <c r="B539" s="30"/>
-      <c r="C539" s="30"/>
+      <c r="A539" s="29"/>
+      <c r="B539" s="29"/>
+      <c r="C539" s="29"/>
     </row>
     <row r="540" ht="12.75" customHeight="1">
-      <c r="A540" s="30"/>
-      <c r="B540" s="30"/>
-      <c r="C540" s="30"/>
+      <c r="A540" s="29"/>
+      <c r="B540" s="29"/>
+      <c r="C540" s="29"/>
     </row>
     <row r="541" ht="12.75" customHeight="1">
-      <c r="A541" s="30"/>
-      <c r="B541" s="30"/>
-      <c r="C541" s="30"/>
+      <c r="A541" s="29"/>
+      <c r="B541" s="29"/>
+      <c r="C541" s="29"/>
     </row>
     <row r="542" ht="12.75" customHeight="1">
-      <c r="A542" s="30"/>
-      <c r="B542" s="30"/>
-      <c r="C542" s="30"/>
+      <c r="A542" s="29"/>
+      <c r="B542" s="29"/>
+      <c r="C542" s="29"/>
     </row>
     <row r="543" ht="12.75" customHeight="1">
-      <c r="A543" s="30"/>
-      <c r="B543" s="30"/>
-      <c r="C543" s="30"/>
+      <c r="A543" s="29"/>
+      <c r="B543" s="29"/>
+      <c r="C543" s="29"/>
     </row>
     <row r="544" ht="12.75" customHeight="1">
-      <c r="A544" s="30"/>
-      <c r="B544" s="30"/>
-      <c r="C544" s="30"/>
+      <c r="A544" s="29"/>
+      <c r="B544" s="29"/>
+      <c r="C544" s="29"/>
     </row>
     <row r="545" ht="12.75" customHeight="1">
-      <c r="A545" s="30"/>
-      <c r="B545" s="30"/>
-      <c r="C545" s="30"/>
+      <c r="A545" s="29"/>
+      <c r="B545" s="29"/>
+      <c r="C545" s="29"/>
     </row>
     <row r="546" ht="12.75" customHeight="1">
-      <c r="A546" s="30"/>
-      <c r="B546" s="30"/>
-      <c r="C546" s="30"/>
+      <c r="A546" s="29"/>
+      <c r="B546" s="29"/>
+      <c r="C546" s="29"/>
     </row>
     <row r="547" ht="12.75" customHeight="1">
-      <c r="A547" s="30"/>
-      <c r="B547" s="30"/>
-      <c r="C547" s="30"/>
+      <c r="A547" s="29"/>
+      <c r="B547" s="29"/>
+      <c r="C547" s="29"/>
     </row>
     <row r="548" ht="12.75" customHeight="1">
-      <c r="A548" s="30"/>
-      <c r="B548" s="30"/>
-      <c r="C548" s="30"/>
+      <c r="A548" s="29"/>
+      <c r="B548" s="29"/>
+      <c r="C548" s="29"/>
     </row>
     <row r="549" ht="12.75" customHeight="1">
-      <c r="A549" s="30"/>
-      <c r="B549" s="30"/>
-      <c r="C549" s="30"/>
+      <c r="A549" s="29"/>
+      <c r="B549" s="29"/>
+      <c r="C549" s="29"/>
     </row>
     <row r="550" ht="12.75" customHeight="1">
-      <c r="A550" s="30"/>
-      <c r="B550" s="30"/>
-      <c r="C550" s="30"/>
+      <c r="A550" s="29"/>
+      <c r="B550" s="29"/>
+      <c r="C550" s="29"/>
     </row>
     <row r="551" ht="12.75" customHeight="1">
-      <c r="A551" s="30"/>
-      <c r="B551" s="30"/>
-      <c r="C551" s="30"/>
+      <c r="A551" s="29"/>
+      <c r="B551" s="29"/>
+      <c r="C551" s="29"/>
     </row>
     <row r="552" ht="12.75" customHeight="1">
-      <c r="A552" s="30"/>
-      <c r="B552" s="30"/>
-      <c r="C552" s="30"/>
+      <c r="A552" s="29"/>
+      <c r="B552" s="29"/>
+      <c r="C552" s="29"/>
     </row>
     <row r="553" ht="12.75" customHeight="1">
-      <c r="A553" s="30"/>
-      <c r="B553" s="30"/>
-      <c r="C553" s="30"/>
+      <c r="A553" s="29"/>
+      <c r="B553" s="29"/>
+      <c r="C553" s="29"/>
     </row>
     <row r="554" ht="12.75" customHeight="1">
-      <c r="A554" s="30"/>
-      <c r="B554" s="30"/>
-      <c r="C554" s="30"/>
+      <c r="A554" s="29"/>
+      <c r="B554" s="29"/>
+      <c r="C554" s="29"/>
     </row>
     <row r="555" ht="12.75" customHeight="1">
-      <c r="A555" s="30"/>
-      <c r="B555" s="30"/>
-      <c r="C555" s="30"/>
+      <c r="A555" s="29"/>
+      <c r="B555" s="29"/>
+      <c r="C555" s="29"/>
     </row>
     <row r="556" ht="12.75" customHeight="1">
-      <c r="A556" s="30"/>
-      <c r="B556" s="30"/>
-      <c r="C556" s="30"/>
+      <c r="A556" s="29"/>
+      <c r="B556" s="29"/>
+      <c r="C556" s="29"/>
     </row>
     <row r="557" ht="12.75" customHeight="1">
-      <c r="A557" s="30"/>
-      <c r="B557" s="30"/>
-      <c r="C557" s="30"/>
+      <c r="A557" s="29"/>
+      <c r="B557" s="29"/>
+      <c r="C557" s="29"/>
     </row>
     <row r="558" ht="12.75" customHeight="1">
-      <c r="A558" s="30"/>
-      <c r="B558" s="30"/>
-      <c r="C558" s="30"/>
+      <c r="A558" s="29"/>
+      <c r="B558" s="29"/>
+      <c r="C558" s="29"/>
     </row>
     <row r="559" ht="12.75" customHeight="1">
-      <c r="A559" s="30"/>
-      <c r="B559" s="30"/>
-      <c r="C559" s="30"/>
+      <c r="A559" s="29"/>
+      <c r="B559" s="29"/>
+      <c r="C559" s="29"/>
     </row>
     <row r="560" ht="12.75" customHeight="1">
-      <c r="A560" s="30"/>
-      <c r="B560" s="30"/>
-      <c r="C560" s="30"/>
+      <c r="A560" s="29"/>
+      <c r="B560" s="29"/>
+      <c r="C560" s="29"/>
     </row>
     <row r="561" ht="12.75" customHeight="1">
-      <c r="A561" s="30"/>
-      <c r="B561" s="30"/>
-      <c r="C561" s="30"/>
+      <c r="A561" s="29"/>
+      <c r="B561" s="29"/>
+      <c r="C561" s="29"/>
     </row>
     <row r="562" ht="12.75" customHeight="1">
-      <c r="A562" s="30"/>
-      <c r="B562" s="30"/>
-      <c r="C562" s="30"/>
+      <c r="A562" s="29"/>
+      <c r="B562" s="29"/>
+      <c r="C562" s="29"/>
     </row>
     <row r="563" ht="12.75" customHeight="1">
-      <c r="A563" s="30"/>
-      <c r="B563" s="30"/>
-      <c r="C563" s="30"/>
+      <c r="A563" s="29"/>
+      <c r="B563" s="29"/>
+      <c r="C563" s="29"/>
     </row>
     <row r="564" ht="12.75" customHeight="1">
-      <c r="A564" s="30"/>
-      <c r="B564" s="30"/>
-      <c r="C564" s="30"/>
+      <c r="A564" s="29"/>
+      <c r="B564" s="29"/>
+      <c r="C564" s="29"/>
     </row>
     <row r="565" ht="12.75" customHeight="1">
-      <c r="A565" s="30"/>
-      <c r="B565" s="30"/>
-      <c r="C565" s="30"/>
+      <c r="A565" s="29"/>
+      <c r="B565" s="29"/>
+      <c r="C565" s="29"/>
     </row>
     <row r="566" ht="12.75" customHeight="1">
-      <c r="A566" s="30"/>
-      <c r="B566" s="30"/>
-      <c r="C566" s="30"/>
+      <c r="A566" s="29"/>
+      <c r="B566" s="29"/>
+      <c r="C566" s="29"/>
     </row>
     <row r="567" ht="12.75" customHeight="1">
-      <c r="A567" s="30"/>
-      <c r="B567" s="30"/>
-      <c r="C567" s="30"/>
+      <c r="A567" s="29"/>
+      <c r="B567" s="29"/>
+      <c r="C567" s="29"/>
     </row>
     <row r="568" ht="12.75" customHeight="1">
-      <c r="A568" s="30"/>
-      <c r="B568" s="30"/>
-      <c r="C568" s="30"/>
+      <c r="A568" s="29"/>
+      <c r="B568" s="29"/>
+      <c r="C568" s="29"/>
     </row>
     <row r="569" ht="12.75" customHeight="1">
-      <c r="A569" s="30"/>
-      <c r="B569" s="30"/>
-      <c r="C569" s="30"/>
+      <c r="A569" s="29"/>
+      <c r="B569" s="29"/>
+      <c r="C569" s="29"/>
     </row>
     <row r="570" ht="12.75" customHeight="1">
-      <c r="A570" s="30"/>
-      <c r="B570" s="30"/>
-      <c r="C570" s="30"/>
+      <c r="A570" s="29"/>
+      <c r="B570" s="29"/>
+      <c r="C570" s="29"/>
     </row>
     <row r="571" ht="12.75" customHeight="1">
-      <c r="A571" s="30"/>
-      <c r="B571" s="30"/>
-      <c r="C571" s="30"/>
+      <c r="A571" s="29"/>
+      <c r="B571" s="29"/>
+      <c r="C571" s="29"/>
     </row>
     <row r="572" ht="12.75" customHeight="1">
-      <c r="A572" s="30"/>
-      <c r="B572" s="30"/>
-      <c r="C572" s="30"/>
+      <c r="A572" s="29"/>
+      <c r="B572" s="29"/>
+      <c r="C572" s="29"/>
     </row>
     <row r="573" ht="12.75" customHeight="1">
-      <c r="A573" s="30"/>
-      <c r="B573" s="30"/>
-      <c r="C573" s="30"/>
+      <c r="A573" s="29"/>
+      <c r="B573" s="29"/>
+      <c r="C573" s="29"/>
     </row>
     <row r="574" ht="12.75" customHeight="1">
-      <c r="A574" s="30"/>
-      <c r="B574" s="30"/>
-      <c r="C574" s="30"/>
+      <c r="A574" s="29"/>
+      <c r="B574" s="29"/>
+      <c r="C574" s="29"/>
     </row>
     <row r="575" ht="12.75" customHeight="1">
-      <c r="A575" s="30"/>
-      <c r="B575" s="30"/>
-      <c r="C575" s="30"/>
+      <c r="A575" s="29"/>
+      <c r="B575" s="29"/>
+      <c r="C575" s="29"/>
     </row>
     <row r="576" ht="12.75" customHeight="1">
-      <c r="A576" s="30"/>
-      <c r="B576" s="30"/>
-      <c r="C576" s="30"/>
+      <c r="A576" s="29"/>
+      <c r="B576" s="29"/>
+      <c r="C576" s="29"/>
     </row>
     <row r="577" ht="12.75" customHeight="1">
-      <c r="A577" s="30"/>
-      <c r="B577" s="30"/>
-      <c r="C577" s="30"/>
+      <c r="A577" s="29"/>
+      <c r="B577" s="29"/>
+      <c r="C577" s="29"/>
     </row>
     <row r="578" ht="12.75" customHeight="1">
-      <c r="A578" s="30"/>
-      <c r="B578" s="30"/>
-      <c r="C578" s="30"/>
+      <c r="A578" s="29"/>
+      <c r="B578" s="29"/>
+      <c r="C578" s="29"/>
     </row>
     <row r="579" ht="12.75" customHeight="1">
-      <c r="A579" s="30"/>
-      <c r="B579" s="30"/>
-      <c r="C579" s="30"/>
+      <c r="A579" s="29"/>
+      <c r="B579" s="29"/>
+      <c r="C579" s="29"/>
     </row>
     <row r="580" ht="12.75" customHeight="1">
-      <c r="A580" s="30"/>
-      <c r="B580" s="30"/>
-      <c r="C580" s="30"/>
+      <c r="A580" s="29"/>
+      <c r="B580" s="29"/>
+      <c r="C580" s="29"/>
     </row>
     <row r="581" ht="12.75" customHeight="1">
-      <c r="A581" s="30"/>
-      <c r="B581" s="30"/>
-      <c r="C581" s="30"/>
+      <c r="A581" s="29"/>
+      <c r="B581" s="29"/>
+      <c r="C581" s="29"/>
     </row>
     <row r="582" ht="12.75" customHeight="1">
-      <c r="A582" s="30"/>
-      <c r="B582" s="30"/>
-      <c r="C582" s="30"/>
+      <c r="A582" s="29"/>
+      <c r="B582" s="29"/>
+      <c r="C582" s="29"/>
     </row>
     <row r="583" ht="12.75" customHeight="1">
-      <c r="A583" s="30"/>
-      <c r="B583" s="30"/>
-      <c r="C583" s="30"/>
+      <c r="A583" s="29"/>
+      <c r="B583" s="29"/>
+      <c r="C583" s="29"/>
     </row>
     <row r="584" ht="12.75" customHeight="1">
-      <c r="A584" s="30"/>
-      <c r="B584" s="30"/>
-      <c r="C584" s="30"/>
+      <c r="A584" s="29"/>
+      <c r="B584" s="29"/>
+      <c r="C584" s="29"/>
     </row>
     <row r="585" ht="12.75" customHeight="1">
-      <c r="A585" s="30"/>
-      <c r="B585" s="30"/>
-      <c r="C585" s="30"/>
+      <c r="A585" s="29"/>
+      <c r="B585" s="29"/>
+      <c r="C585" s="29"/>
     </row>
     <row r="586" ht="12.75" customHeight="1">
-      <c r="A586" s="30"/>
-      <c r="B586" s="30"/>
-      <c r="C586" s="30"/>
+      <c r="A586" s="29"/>
+      <c r="B586" s="29"/>
+      <c r="C586" s="29"/>
     </row>
     <row r="587" ht="12.75" customHeight="1">
-      <c r="A587" s="30"/>
-      <c r="B587" s="30"/>
-      <c r="C587" s="30"/>
+      <c r="A587" s="29"/>
+      <c r="B587" s="29"/>
+      <c r="C587" s="29"/>
     </row>
     <row r="588" ht="12.75" customHeight="1">
-      <c r="A588" s="30"/>
-      <c r="B588" s="30"/>
-      <c r="C588" s="30"/>
+      <c r="A588" s="29"/>
+      <c r="B588" s="29"/>
+      <c r="C588" s="29"/>
     </row>
     <row r="589" ht="12.75" customHeight="1">
-      <c r="A589" s="30"/>
-      <c r="B589" s="30"/>
-      <c r="C589" s="30"/>
+      <c r="A589" s="29"/>
+      <c r="B589" s="29"/>
+      <c r="C589" s="29"/>
     </row>
     <row r="590" ht="12.75" customHeight="1">
-      <c r="A590" s="30"/>
-      <c r="B590" s="30"/>
-      <c r="C590" s="30"/>
+      <c r="A590" s="29"/>
+      <c r="B590" s="29"/>
+      <c r="C590" s="29"/>
     </row>
     <row r="591" ht="12.75" customHeight="1">
-      <c r="A591" s="30"/>
-      <c r="B591" s="30"/>
-      <c r="C591" s="30"/>
+      <c r="A591" s="29"/>
+      <c r="B591" s="29"/>
+      <c r="C591" s="29"/>
     </row>
     <row r="592" ht="12.75" customHeight="1">
-      <c r="A592" s="30"/>
-      <c r="B592" s="30"/>
-      <c r="C592" s="30"/>
+      <c r="A592" s="29"/>
+      <c r="B592" s="29"/>
+      <c r="C592" s="29"/>
     </row>
     <row r="593" ht="12.75" customHeight="1">
-      <c r="A593" s="30"/>
-      <c r="B593" s="30"/>
-      <c r="C593" s="30"/>
+      <c r="A593" s="29"/>
+      <c r="B593" s="29"/>
+      <c r="C593" s="29"/>
     </row>
     <row r="594" ht="12.75" customHeight="1">
-      <c r="A594" s="30"/>
-      <c r="B594" s="30"/>
-      <c r="C594" s="30"/>
+      <c r="A594" s="29"/>
+      <c r="B594" s="29"/>
+      <c r="C594" s="29"/>
     </row>
     <row r="595" ht="12.75" customHeight="1">
-      <c r="A595" s="30"/>
-      <c r="B595" s="30"/>
-      <c r="C595" s="30"/>
+      <c r="A595" s="29"/>
+      <c r="B595" s="29"/>
+      <c r="C595" s="29"/>
     </row>
     <row r="596" ht="12.75" customHeight="1">
-      <c r="A596" s="30"/>
-      <c r="B596" s="30"/>
-      <c r="C596" s="30"/>
+      <c r="A596" s="29"/>
+      <c r="B596" s="29"/>
+      <c r="C596" s="29"/>
     </row>
     <row r="597" ht="12.75" customHeight="1">
-      <c r="A597" s="30"/>
-      <c r="B597" s="30"/>
-      <c r="C597" s="30"/>
+      <c r="A597" s="29"/>
+      <c r="B597" s="29"/>
+      <c r="C597" s="29"/>
     </row>
     <row r="598" ht="12.75" customHeight="1">
-      <c r="A598" s="30"/>
-      <c r="B598" s="30"/>
-      <c r="C598" s="30"/>
+      <c r="A598" s="29"/>
+      <c r="B598" s="29"/>
+      <c r="C598" s="29"/>
     </row>
     <row r="599" ht="12.75" customHeight="1">
-      <c r="A599" s="30"/>
-      <c r="B599" s="30"/>
-      <c r="C599" s="30"/>
+      <c r="A599" s="29"/>
+      <c r="B599" s="29"/>
+      <c r="C599" s="29"/>
     </row>
     <row r="600" ht="12.75" customHeight="1">
-      <c r="A600" s="30"/>
-      <c r="B600" s="30"/>
-      <c r="C600" s="30"/>
+      <c r="A600" s="29"/>
+      <c r="B600" s="29"/>
+      <c r="C600" s="29"/>
     </row>
     <row r="601" ht="12.75" customHeight="1">
-      <c r="A601" s="30"/>
-      <c r="B601" s="30"/>
-      <c r="C601" s="30"/>
+      <c r="A601" s="29"/>
+      <c r="B601" s="29"/>
+      <c r="C601" s="29"/>
     </row>
     <row r="602" ht="12.75" customHeight="1">
-      <c r="A602" s="30"/>
-      <c r="B602" s="30"/>
-      <c r="C602" s="30"/>
+      <c r="A602" s="29"/>
+      <c r="B602" s="29"/>
+      <c r="C602" s="29"/>
     </row>
     <row r="603" ht="12.75" customHeight="1">
-      <c r="A603" s="30"/>
-      <c r="B603" s="30"/>
-      <c r="C603" s="30"/>
+      <c r="A603" s="29"/>
+      <c r="B603" s="29"/>
+      <c r="C603" s="29"/>
     </row>
     <row r="604" ht="12.75" customHeight="1">
-      <c r="A604" s="30"/>
-      <c r="B604" s="30"/>
-      <c r="C604" s="30"/>
+      <c r="A604" s="29"/>
+      <c r="B604" s="29"/>
+      <c r="C604" s="29"/>
     </row>
     <row r="605" ht="12.75" customHeight="1">
-      <c r="A605" s="30"/>
-      <c r="B605" s="30"/>
-      <c r="C605" s="30"/>
+      <c r="A605" s="29"/>
+      <c r="B605" s="29"/>
+      <c r="C605" s="29"/>
     </row>
     <row r="606" ht="12.75" customHeight="1">
-      <c r="A606" s="30"/>
-      <c r="B606" s="30"/>
-      <c r="C606" s="30"/>
+      <c r="A606" s="29"/>
+      <c r="B606" s="29"/>
+      <c r="C606" s="29"/>
     </row>
     <row r="607" ht="12.75" customHeight="1">
-      <c r="A607" s="30"/>
-      <c r="B607" s="30"/>
-      <c r="C607" s="30"/>
+      <c r="A607" s="29"/>
+      <c r="B607" s="29"/>
+      <c r="C607" s="29"/>
     </row>
     <row r="608" ht="12.75" customHeight="1">
-      <c r="A608" s="30"/>
-      <c r="B608" s="30"/>
-      <c r="C608" s="30"/>
+      <c r="A608" s="29"/>
+      <c r="B608" s="29"/>
+      <c r="C608" s="29"/>
     </row>
     <row r="609" ht="12.75" customHeight="1">
-      <c r="A609" s="30"/>
-      <c r="B609" s="30"/>
-      <c r="C609" s="30"/>
+      <c r="A609" s="29"/>
+      <c r="B609" s="29"/>
+      <c r="C609" s="29"/>
     </row>
     <row r="610" ht="12.75" customHeight="1">
-      <c r="A610" s="30"/>
-      <c r="B610" s="30"/>
-      <c r="C610" s="30"/>
+      <c r="A610" s="29"/>
+      <c r="B610" s="29"/>
+      <c r="C610" s="29"/>
     </row>
     <row r="611" ht="12.75" customHeight="1">
-      <c r="A611" s="30"/>
-      <c r="B611" s="30"/>
-      <c r="C611" s="30"/>
+      <c r="A611" s="29"/>
+      <c r="B611" s="29"/>
+      <c r="C611" s="29"/>
     </row>
     <row r="612" ht="12.75" customHeight="1">
-      <c r="A612" s="30"/>
-      <c r="B612" s="30"/>
-      <c r="C612" s="30"/>
+      <c r="A612" s="29"/>
+      <c r="B612" s="29"/>
+      <c r="C612" s="29"/>
     </row>
     <row r="613" ht="12.75" customHeight="1">
-      <c r="A613" s="30"/>
-      <c r="B613" s="30"/>
-      <c r="C613" s="30"/>
+      <c r="A613" s="29"/>
+      <c r="B613" s="29"/>
+      <c r="C613" s="29"/>
     </row>
     <row r="614" ht="12.75" customHeight="1">
-      <c r="A614" s="30"/>
-      <c r="B614" s="30"/>
-      <c r="C614" s="30"/>
+      <c r="A614" s="29"/>
+      <c r="B614" s="29"/>
+      <c r="C614" s="29"/>
     </row>
     <row r="615" ht="12.75" customHeight="1">
-      <c r="A615" s="30"/>
-      <c r="B615" s="30"/>
-      <c r="C615" s="30"/>
+      <c r="A615" s="29"/>
+      <c r="B615" s="29"/>
+      <c r="C615" s="29"/>
     </row>
     <row r="616" ht="12.75" customHeight="1">
-      <c r="A616" s="30"/>
-      <c r="B616" s="30"/>
-      <c r="C616" s="30"/>
+      <c r="A616" s="29"/>
+      <c r="B616" s="29"/>
+      <c r="C616" s="29"/>
     </row>
     <row r="617" ht="12.75" customHeight="1">
-      <c r="A617" s="30"/>
-      <c r="B617" s="30"/>
-      <c r="C617" s="30"/>
+      <c r="A617" s="29"/>
+      <c r="B617" s="29"/>
+      <c r="C617" s="29"/>
     </row>
     <row r="618" ht="12.75" customHeight="1">
-      <c r="A618" s="30"/>
-      <c r="B618" s="30"/>
-      <c r="C618" s="30"/>
+      <c r="A618" s="29"/>
+      <c r="B618" s="29"/>
+      <c r="C618" s="29"/>
     </row>
     <row r="619" ht="12.75" customHeight="1">
-      <c r="A619" s="30"/>
-      <c r="B619" s="30"/>
-      <c r="C619" s="30"/>
+      <c r="A619" s="29"/>
+      <c r="B619" s="29"/>
+      <c r="C619" s="29"/>
     </row>
     <row r="620" ht="12.75" customHeight="1">
-      <c r="A620" s="30"/>
-      <c r="B620" s="30"/>
-      <c r="C620" s="30"/>
+      <c r="A620" s="29"/>
+      <c r="B620" s="29"/>
+      <c r="C620" s="29"/>
     </row>
     <row r="621" ht="12.75" customHeight="1">
-      <c r="A621" s="30"/>
-      <c r="B621" s="30"/>
-      <c r="C621" s="30"/>
+      <c r="A621" s="29"/>
+      <c r="B621" s="29"/>
+      <c r="C621" s="29"/>
     </row>
     <row r="622" ht="12.75" customHeight="1">
-      <c r="A622" s="30"/>
-      <c r="B622" s="30"/>
-      <c r="C622" s="30"/>
+      <c r="A622" s="29"/>
+      <c r="B622" s="29"/>
+      <c r="C622" s="29"/>
     </row>
     <row r="623" ht="12.75" customHeight="1">
-      <c r="A623" s="30"/>
-      <c r="B623" s="30"/>
-      <c r="C623" s="30"/>
+      <c r="A623" s="29"/>
+      <c r="B623" s="29"/>
+      <c r="C623" s="29"/>
     </row>
     <row r="624" ht="12.75" customHeight="1">
-      <c r="A624" s="30"/>
-      <c r="B624" s="30"/>
-      <c r="C624" s="30"/>
+      <c r="A624" s="29"/>
+      <c r="B624" s="29"/>
+      <c r="C624" s="29"/>
     </row>
     <row r="625" ht="12.75" customHeight="1">
-      <c r="A625" s="30"/>
-      <c r="B625" s="30"/>
-      <c r="C625" s="30"/>
+      <c r="A625" s="29"/>
+      <c r="B625" s="29"/>
+      <c r="C625" s="29"/>
     </row>
     <row r="626" ht="12.75" customHeight="1">
-      <c r="A626" s="30"/>
-      <c r="B626" s="30"/>
-      <c r="C626" s="30"/>
+      <c r="A626" s="29"/>
+      <c r="B626" s="29"/>
+      <c r="C626" s="29"/>
     </row>
     <row r="627" ht="12.75" customHeight="1">
-      <c r="A627" s="30"/>
-      <c r="B627" s="30"/>
-      <c r="C627" s="30"/>
+      <c r="A627" s="29"/>
+      <c r="B627" s="29"/>
+      <c r="C627" s="29"/>
     </row>
     <row r="628" ht="12.75" customHeight="1">
-      <c r="A628" s="30"/>
-      <c r="B628" s="30"/>
-      <c r="C628" s="30"/>
+      <c r="A628" s="29"/>
+      <c r="B628" s="29"/>
+      <c r="C628" s="29"/>
     </row>
     <row r="629" ht="12.75" customHeight="1">
-      <c r="A629" s="30"/>
-      <c r="B629" s="30"/>
-      <c r="C629" s="30"/>
+      <c r="A629" s="29"/>
+      <c r="B629" s="29"/>
+      <c r="C629" s="29"/>
     </row>
     <row r="630" ht="12.75" customHeight="1">
-      <c r="A630" s="30"/>
-      <c r="B630" s="30"/>
-      <c r="C630" s="30"/>
+      <c r="A630" s="29"/>
+      <c r="B630" s="29"/>
+      <c r="C630" s="29"/>
     </row>
     <row r="631" ht="12.75" customHeight="1">
-      <c r="A631" s="30"/>
-      <c r="B631" s="30"/>
-      <c r="C631" s="30"/>
+      <c r="A631" s="29"/>
+      <c r="B631" s="29"/>
+      <c r="C631" s="29"/>
     </row>
     <row r="632" ht="12.75" customHeight="1">
-      <c r="A632" s="30"/>
-      <c r="B632" s="30"/>
-      <c r="C632" s="30"/>
+      <c r="A632" s="29"/>
+      <c r="B632" s="29"/>
+      <c r="C632" s="29"/>
     </row>
     <row r="633" ht="12.75" customHeight="1">
-      <c r="A633" s="30"/>
-      <c r="B633" s="30"/>
-      <c r="C633" s="30"/>
+      <c r="A633" s="29"/>
+      <c r="B633" s="29"/>
+      <c r="C633" s="29"/>
     </row>
     <row r="634" ht="12.75" customHeight="1">
-      <c r="A634" s="30"/>
-      <c r="B634" s="30"/>
-      <c r="C634" s="30"/>
+      <c r="A634" s="29"/>
+      <c r="B634" s="29"/>
+      <c r="C634" s="29"/>
     </row>
     <row r="635" ht="12.75" customHeight="1">
-      <c r="A635" s="30"/>
-      <c r="B635" s="30"/>
-      <c r="C635" s="30"/>
+      <c r="A635" s="29"/>
+      <c r="B635" s="29"/>
+      <c r="C635" s="29"/>
     </row>
     <row r="636" ht="12.75" customHeight="1">
-      <c r="A636" s="30"/>
-      <c r="B636" s="30"/>
-      <c r="C636" s="30"/>
+      <c r="A636" s="29"/>
+      <c r="B636" s="29"/>
+      <c r="C636" s="29"/>
     </row>
     <row r="637" ht="12.75" customHeight="1">
-      <c r="A637" s="30"/>
-      <c r="B637" s="30"/>
-      <c r="C637" s="30"/>
+      <c r="A637" s="29"/>
+      <c r="B637" s="29"/>
+      <c r="C637" s="29"/>
     </row>
     <row r="638" ht="12.75" customHeight="1">
-      <c r="A638" s="30"/>
-      <c r="B638" s="30"/>
-      <c r="C638" s="30"/>
+      <c r="A638" s="29"/>
+      <c r="B638" s="29"/>
+      <c r="C638" s="29"/>
     </row>
     <row r="639" ht="12.75" customHeight="1">
-      <c r="A639" s="30"/>
-      <c r="B639" s="30"/>
-      <c r="C639" s="30"/>
+      <c r="A639" s="29"/>
+      <c r="B639" s="29"/>
+      <c r="C639" s="29"/>
     </row>
     <row r="640" ht="12.75" customHeight="1">
-      <c r="A640" s="30"/>
-      <c r="B640" s="30"/>
-      <c r="C640" s="30"/>
+      <c r="A640" s="29"/>
+      <c r="B640" s="29"/>
+      <c r="C640" s="29"/>
     </row>
     <row r="641" ht="12.75" customHeight="1">
-      <c r="A641" s="30"/>
-      <c r="B641" s="30"/>
-      <c r="C641" s="30"/>
+      <c r="A641" s="29"/>
+      <c r="B641" s="29"/>
+      <c r="C641" s="29"/>
     </row>
     <row r="642" ht="12.75" customHeight="1">
-      <c r="A642" s="30"/>
-      <c r="B642" s="30"/>
-      <c r="C642" s="30"/>
+      <c r="A642" s="29"/>
+      <c r="B642" s="29"/>
+      <c r="C642" s="29"/>
     </row>
     <row r="643" ht="12.75" customHeight="1">
-      <c r="A643" s="30"/>
-      <c r="B643" s="30"/>
-      <c r="C643" s="30"/>
+      <c r="A643" s="29"/>
+      <c r="B643" s="29"/>
+      <c r="C643" s="29"/>
     </row>
     <row r="644" ht="12.75" customHeight="1">
-      <c r="A644" s="30"/>
-      <c r="B644" s="30"/>
-      <c r="C644" s="30"/>
+      <c r="A644" s="29"/>
+      <c r="B644" s="29"/>
+      <c r="C644" s="29"/>
     </row>
     <row r="645" ht="12.75" customHeight="1">
-      <c r="A645" s="30"/>
-      <c r="B645" s="30"/>
-      <c r="C645" s="30"/>
+      <c r="A645" s="29"/>
+      <c r="B645" s="29"/>
+      <c r="C645" s="29"/>
     </row>
     <row r="646" ht="12.75" customHeight="1">
-      <c r="A646" s="30"/>
-      <c r="B646" s="30"/>
-      <c r="C646" s="30"/>
+      <c r="A646" s="29"/>
+      <c r="B646" s="29"/>
+      <c r="C646" s="29"/>
     </row>
     <row r="647" ht="12.75" customHeight="1">
-      <c r="A647" s="30"/>
-      <c r="B647" s="30"/>
-      <c r="C647" s="30"/>
+      <c r="A647" s="29"/>
+      <c r="B647" s="29"/>
+      <c r="C647" s="29"/>
     </row>
     <row r="648" ht="12.75" customHeight="1">
-      <c r="A648" s="30"/>
-      <c r="B648" s="30"/>
-      <c r="C648" s="30"/>
+      <c r="A648" s="29"/>
+      <c r="B648" s="29"/>
+      <c r="C648" s="29"/>
     </row>
     <row r="649" ht="12.75" customHeight="1">
-      <c r="A649" s="30"/>
-      <c r="B649" s="30"/>
-      <c r="C649" s="30"/>
+      <c r="A649" s="29"/>
+      <c r="B649" s="29"/>
+      <c r="C649" s="29"/>
     </row>
     <row r="650" ht="12.75" customHeight="1">
-      <c r="A650" s="30"/>
-      <c r="B650" s="30"/>
-      <c r="C650" s="30"/>
+      <c r="A650" s="29"/>
+      <c r="B650" s="29"/>
+      <c r="C650" s="29"/>
     </row>
     <row r="651" ht="12.75" customHeight="1">
-      <c r="A651" s="30"/>
-      <c r="B651" s="30"/>
-      <c r="C651" s="30"/>
+      <c r="A651" s="29"/>
+      <c r="B651" s="29"/>
+      <c r="C651" s="29"/>
     </row>
     <row r="652" ht="12.75" customHeight="1">
-      <c r="A652" s="30"/>
-      <c r="B652" s="30"/>
-      <c r="C652" s="30"/>
+      <c r="A652" s="29"/>
+      <c r="B652" s="29"/>
+      <c r="C652" s="29"/>
     </row>
     <row r="653" ht="12.75" customHeight="1">
-      <c r="A653" s="30"/>
-      <c r="B653" s="30"/>
-      <c r="C653" s="30"/>
+      <c r="A653" s="29"/>
+      <c r="B653" s="29"/>
+      <c r="C653" s="29"/>
     </row>
     <row r="654" ht="12.75" customHeight="1">
-      <c r="A654" s="30"/>
-      <c r="B654" s="30"/>
-      <c r="C654" s="30"/>
+      <c r="A654" s="29"/>
+      <c r="B654" s="29"/>
+      <c r="C654" s="29"/>
     </row>
     <row r="655" ht="12.75" customHeight="1">
-      <c r="A655" s="30"/>
-      <c r="B655" s="30"/>
-      <c r="C655" s="30"/>
+      <c r="A655" s="29"/>
+      <c r="B655" s="29"/>
+      <c r="C655" s="29"/>
     </row>
     <row r="656" ht="12.75" customHeight="1">
-      <c r="A656" s="30"/>
-      <c r="B656" s="30"/>
-      <c r="C656" s="30"/>
+      <c r="A656" s="29"/>
+      <c r="B656" s="29"/>
+      <c r="C656" s="29"/>
     </row>
     <row r="657" ht="12.75" customHeight="1">
-      <c r="A657" s="30"/>
-      <c r="B657" s="30"/>
-      <c r="C657" s="30"/>
+      <c r="A657" s="29"/>
+      <c r="B657" s="29"/>
+      <c r="C657" s="29"/>
     </row>
     <row r="658" ht="12.75" customHeight="1">
-      <c r="A658" s="30"/>
-      <c r="B658" s="30"/>
-      <c r="C658" s="30"/>
+      <c r="A658" s="29"/>
+      <c r="B658" s="29"/>
+      <c r="C658" s="29"/>
     </row>
     <row r="659" ht="12.75" customHeight="1">
-      <c r="A659" s="30"/>
-      <c r="B659" s="30"/>
-      <c r="C659" s="30"/>
+      <c r="A659" s="29"/>
+      <c r="B659" s="29"/>
+      <c r="C659" s="29"/>
     </row>
     <row r="660" ht="12.75" customHeight="1">
-      <c r="A660" s="30"/>
-      <c r="B660" s="30"/>
-      <c r="C660" s="30"/>
+      <c r="A660" s="29"/>
+      <c r="B660" s="29"/>
+      <c r="C660" s="29"/>
     </row>
     <row r="661" ht="12.75" customHeight="1">
-      <c r="A661" s="30"/>
-      <c r="B661" s="30"/>
-      <c r="C661" s="30"/>
+      <c r="A661" s="29"/>
+      <c r="B661" s="29"/>
+      <c r="C661" s="29"/>
     </row>
     <row r="662" ht="12.75" customHeight="1">
-      <c r="A662" s="30"/>
-      <c r="B662" s="30"/>
-      <c r="C662" s="30"/>
+      <c r="A662" s="29"/>
+      <c r="B662" s="29"/>
+      <c r="C662" s="29"/>
     </row>
     <row r="663" ht="12.75" customHeight="1">
-      <c r="A663" s="30"/>
-      <c r="B663" s="30"/>
-      <c r="C663" s="30"/>
+      <c r="A663" s="29"/>
+      <c r="B663" s="29"/>
+      <c r="C663" s="29"/>
     </row>
     <row r="664" ht="12.75" customHeight="1">
-      <c r="A664" s="30"/>
-      <c r="B664" s="30"/>
-      <c r="C664" s="30"/>
+      <c r="A664" s="29"/>
+      <c r="B664" s="29"/>
+      <c r="C664" s="29"/>
     </row>
     <row r="665" ht="12.75" customHeight="1">
-      <c r="A665" s="30"/>
-      <c r="B665" s="30"/>
-      <c r="C665" s="30"/>
+      <c r="A665" s="29"/>
+      <c r="B665" s="29"/>
+      <c r="C665" s="29"/>
     </row>
     <row r="666" ht="12.75" customHeight="1">
-      <c r="A666" s="30"/>
-      <c r="B666" s="30"/>
-      <c r="C666" s="30"/>
+      <c r="A666" s="29"/>
+      <c r="B666" s="29"/>
+      <c r="C666" s="29"/>
     </row>
     <row r="667" ht="12.75" customHeight="1">
-      <c r="A667" s="30"/>
-      <c r="B667" s="30"/>
-      <c r="C667" s="30"/>
+      <c r="A667" s="29"/>
+      <c r="B667" s="29"/>
+      <c r="C667" s="29"/>
     </row>
     <row r="668" ht="12.75" customHeight="1">
-      <c r="A668" s="30"/>
-      <c r="B668" s="30"/>
-      <c r="C668" s="30"/>
+      <c r="A668" s="29"/>
+      <c r="B668" s="29"/>
+      <c r="C668" s="29"/>
     </row>
     <row r="669" ht="12.75" customHeight="1">
-      <c r="A669" s="30"/>
-      <c r="B669" s="30"/>
-      <c r="C669" s="30"/>
+      <c r="A669" s="29"/>
+      <c r="B669" s="29"/>
+      <c r="C669" s="29"/>
     </row>
     <row r="670" ht="12.75" customHeight="1">
-      <c r="A670" s="30"/>
-      <c r="B670" s="30"/>
-      <c r="C670" s="30"/>
+      <c r="A670" s="29"/>
+      <c r="B670" s="29"/>
+      <c r="C670" s="29"/>
     </row>
     <row r="671" ht="12.75" customHeight="1">
-      <c r="A671" s="30"/>
-      <c r="B671" s="30"/>
-      <c r="C671" s="30"/>
+      <c r="A671" s="29"/>
+      <c r="B671" s="29"/>
+      <c r="C671" s="29"/>
     </row>
     <row r="672" ht="12.75" customHeight="1">
-      <c r="A672" s="30"/>
-      <c r="B672" s="30"/>
-      <c r="C672" s="30"/>
+      <c r="A672" s="29"/>
+      <c r="B672" s="29"/>
+      <c r="C672" s="29"/>
     </row>
     <row r="673" ht="12.75" customHeight="1">
-      <c r="A673" s="30"/>
-      <c r="B673" s="30"/>
-      <c r="C673" s="30"/>
+      <c r="A673" s="29"/>
+      <c r="B673" s="29"/>
+      <c r="C673" s="29"/>
     </row>
     <row r="674" ht="12.75" customHeight="1">
-      <c r="A674" s="30"/>
-      <c r="B674" s="30"/>
-      <c r="C674" s="30"/>
+      <c r="A674" s="29"/>
+      <c r="B674" s="29"/>
+      <c r="C674" s="29"/>
     </row>
     <row r="675" ht="12.75" customHeight="1">
-      <c r="A675" s="30"/>
-      <c r="B675" s="30"/>
-      <c r="C675" s="30"/>
+      <c r="A675" s="29"/>
+      <c r="B675" s="29"/>
+      <c r="C675" s="29"/>
     </row>
     <row r="676" ht="12.75" customHeight="1">
-      <c r="A676" s="30"/>
-      <c r="B676" s="30"/>
-      <c r="C676" s="30"/>
+      <c r="A676" s="29"/>
+      <c r="B676" s="29"/>
+      <c r="C676" s="29"/>
     </row>
     <row r="677" ht="12.75" customHeight="1">
-      <c r="A677" s="30"/>
-      <c r="B677" s="30"/>
-      <c r="C677" s="30"/>
+      <c r="A677" s="29"/>
+      <c r="B677" s="29"/>
+      <c r="C677" s="29"/>
     </row>
     <row r="678" ht="12.75" customHeight="1">
-      <c r="A678" s="30"/>
-      <c r="B678" s="30"/>
-      <c r="C678" s="30"/>
+      <c r="A678" s="29"/>
+      <c r="B678" s="29"/>
+      <c r="C678" s="29"/>
     </row>
     <row r="679" ht="12.75" customHeight="1">
-      <c r="A679" s="30"/>
-      <c r="B679" s="30"/>
-      <c r="C679" s="30"/>
+      <c r="A679" s="29"/>
+      <c r="B679" s="29"/>
+      <c r="C679" s="29"/>
     </row>
     <row r="680" ht="12.75" customHeight="1">
-      <c r="A680" s="30"/>
-      <c r="B680" s="30"/>
-      <c r="C680" s="30"/>
+      <c r="A680" s="29"/>
+      <c r="B680" s="29"/>
+      <c r="C680" s="29"/>
     </row>
     <row r="681" ht="12.75" customHeight="1">
-      <c r="A681" s="30"/>
-      <c r="B681" s="30"/>
-      <c r="C681" s="30"/>
+      <c r="A681" s="29"/>
+      <c r="B681" s="29"/>
+      <c r="C681" s="29"/>
     </row>
     <row r="682" ht="12.75" customHeight="1">
-      <c r="A682" s="30"/>
-      <c r="B682" s="30"/>
-      <c r="C682" s="30"/>
+      <c r="A682" s="29"/>
+      <c r="B682" s="29"/>
+      <c r="C682" s="29"/>
     </row>
     <row r="683" ht="12.75" customHeight="1">
-      <c r="A683" s="30"/>
-      <c r="B683" s="30"/>
-      <c r="C683" s="30"/>
+      <c r="A683" s="29"/>
+      <c r="B683" s="29"/>
+      <c r="C683" s="29"/>
     </row>
     <row r="684" ht="12.75" customHeight="1">
-      <c r="A684" s="30"/>
-      <c r="B684" s="30"/>
-      <c r="C684" s="30"/>
+      <c r="A684" s="29"/>
+      <c r="B684" s="29"/>
+      <c r="C684" s="29"/>
     </row>
     <row r="685" ht="12.75" customHeight="1">
-      <c r="A685" s="30"/>
-      <c r="B685" s="30"/>
-      <c r="C685" s="30"/>
+      <c r="A685" s="29"/>
+      <c r="B685" s="29"/>
+      <c r="C685" s="29"/>
     </row>
     <row r="686" ht="12.75" customHeight="1">
-      <c r="A686" s="30"/>
-      <c r="B686" s="30"/>
-      <c r="C686" s="30"/>
+      <c r="A686" s="29"/>
+      <c r="B686" s="29"/>
+      <c r="C686" s="29"/>
     </row>
     <row r="687" ht="12.75" customHeight="1">
-      <c r="A687" s="30"/>
-      <c r="B687" s="30"/>
-      <c r="C687" s="30"/>
+      <c r="A687" s="29"/>
+      <c r="B687" s="29"/>
+      <c r="C687" s="29"/>
     </row>
     <row r="688" ht="12.75" customHeight="1">
-      <c r="A688" s="30"/>
-      <c r="B688" s="30"/>
-      <c r="C688" s="30"/>
+      <c r="A688" s="29"/>
+      <c r="B688" s="29"/>
+      <c r="C688" s="29"/>
     </row>
     <row r="689" ht="12.75" customHeight="1">
-      <c r="A689" s="30"/>
-      <c r="B689" s="30"/>
-      <c r="C689" s="30"/>
+      <c r="A689" s="29"/>
+      <c r="B689" s="29"/>
+      <c r="C689" s="29"/>
     </row>
     <row r="690" ht="12.75" customHeight="1">
-      <c r="A690" s="30"/>
-      <c r="B690" s="30"/>
-      <c r="C690" s="30"/>
+      <c r="A690" s="29"/>
+      <c r="B690" s="29"/>
+      <c r="C690" s="29"/>
     </row>
     <row r="691" ht="12.75" customHeight="1">
-      <c r="A691" s="30"/>
-      <c r="B691" s="30"/>
-      <c r="C691" s="30"/>
+      <c r="A691" s="29"/>
+      <c r="B691" s="29"/>
+      <c r="C691" s="29"/>
     </row>
     <row r="692" ht="12.75" customHeight="1">
-      <c r="A692" s="30"/>
-      <c r="B692" s="30"/>
-      <c r="C692" s="30"/>
+      <c r="A692" s="29"/>
+      <c r="B692" s="29"/>
+      <c r="C692" s="29"/>
     </row>
     <row r="693" ht="12.75" customHeight="1">
-      <c r="A693" s="30"/>
-      <c r="B693" s="30"/>
-      <c r="C693" s="30"/>
+      <c r="A693" s="29"/>
+      <c r="B693" s="29"/>
+      <c r="C693" s="29"/>
     </row>
     <row r="694" ht="12.75" customHeight="1">
-      <c r="A694" s="30"/>
-      <c r="B694" s="30"/>
-      <c r="C694" s="30"/>
+      <c r="A694" s="29"/>
+      <c r="B694" s="29"/>
+      <c r="C694" s="29"/>
     </row>
     <row r="695" ht="12.75" customHeight="1">
-      <c r="A695" s="30"/>
-      <c r="B695" s="30"/>
-      <c r="C695" s="30"/>
+      <c r="A695" s="29"/>
+      <c r="B695" s="29"/>
+      <c r="C695" s="29"/>
     </row>
     <row r="696" ht="12.75" customHeight="1">
-      <c r="A696" s="30"/>
-      <c r="B696" s="30"/>
-      <c r="C696" s="30"/>
+      <c r="A696" s="29"/>
+      <c r="B696" s="29"/>
+      <c r="C696" s="29"/>
     </row>
     <row r="697" ht="12.75" customHeight="1">
-      <c r="A697" s="30"/>
-      <c r="B697" s="30"/>
-      <c r="C697" s="30"/>
+      <c r="A697" s="29"/>
+      <c r="B697" s="29"/>
+      <c r="C697" s="29"/>
     </row>
     <row r="698" ht="12.75" customHeight="1">
-      <c r="A698" s="30"/>
-      <c r="B698" s="30"/>
-      <c r="C698" s="30"/>
+      <c r="A698" s="29"/>
+      <c r="B698" s="29"/>
+      <c r="C698" s="29"/>
     </row>
     <row r="699" ht="12.75" customHeight="1">
-      <c r="A699" s="30"/>
-      <c r="B699" s="30"/>
-      <c r="C699" s="30"/>
+      <c r="A699" s="29"/>
+      <c r="B699" s="29"/>
+      <c r="C699" s="29"/>
     </row>
     <row r="700" ht="12.75" customHeight="1">
-      <c r="A700" s="30"/>
-      <c r="B700" s="30"/>
-      <c r="C700" s="30"/>
+      <c r="A700" s="29"/>
+      <c r="B700" s="29"/>
+      <c r="C700" s="29"/>
     </row>
     <row r="701" ht="12.75" customHeight="1">
-      <c r="A701" s="30"/>
-      <c r="B701" s="30"/>
-      <c r="C701" s="30"/>
+      <c r="A701" s="29"/>
+      <c r="B701" s="29"/>
+      <c r="C701" s="29"/>
     </row>
     <row r="702" ht="12.75" customHeight="1">
-      <c r="A702" s="30"/>
-      <c r="B702" s="30"/>
-      <c r="C702" s="30"/>
+      <c r="A702" s="29"/>
+      <c r="B702" s="29"/>
+      <c r="C702" s="29"/>
     </row>
     <row r="703" ht="12.75" customHeight="1">
-      <c r="A703" s="30"/>
-      <c r="B703" s="30"/>
-      <c r="C703" s="30"/>
+      <c r="A703" s="29"/>
+      <c r="B703" s="29"/>
+      <c r="C703" s="29"/>
     </row>
     <row r="704" ht="12.75" customHeight="1">
-      <c r="A704" s="30"/>
-      <c r="B704" s="30"/>
-      <c r="C704" s="30"/>
+      <c r="A704" s="29"/>
+      <c r="B704" s="29"/>
+      <c r="C704" s="29"/>
     </row>
     <row r="705" ht="12.75" customHeight="1">
-      <c r="A705" s="30"/>
-      <c r="B705" s="30"/>
-      <c r="C705" s="30"/>
+      <c r="A705" s="29"/>
+      <c r="B705" s="29"/>
+      <c r="C705" s="29"/>
     </row>
     <row r="706" ht="12.75" customHeight="1">
-      <c r="A706" s="30"/>
-      <c r="B706" s="30"/>
-      <c r="C706" s="30"/>
+      <c r="A706" s="29"/>
+      <c r="B706" s="29"/>
+      <c r="C706" s="29"/>
     </row>
     <row r="707" ht="12.75" customHeight="1">
-      <c r="A707" s="30"/>
-      <c r="B707" s="30"/>
-      <c r="C707" s="30"/>
+      <c r="A707" s="29"/>
+      <c r="B707" s="29"/>
+      <c r="C707" s="29"/>
     </row>
     <row r="708" ht="12.75" customHeight="1">
-      <c r="A708" s="30"/>
-      <c r="B708" s="30"/>
-      <c r="C708" s="30"/>
+      <c r="A708" s="29"/>
+      <c r="B708" s="29"/>
+      <c r="C708" s="29"/>
     </row>
     <row r="709" ht="12.75" customHeight="1">
-      <c r="A709" s="30"/>
-      <c r="B709" s="30"/>
-      <c r="C709" s="30"/>
+      <c r="A709" s="29"/>
+      <c r="B709" s="29"/>
+      <c r="C709" s="29"/>
     </row>
     <row r="710" ht="12.75" customHeight="1">
-      <c r="A710" s="30"/>
-      <c r="B710" s="30"/>
-      <c r="C710" s="30"/>
+      <c r="A710" s="29"/>
+      <c r="B710" s="29"/>
+      <c r="C710" s="29"/>
     </row>
     <row r="711" ht="12.75" customHeight="1">
-      <c r="A711" s="30"/>
-      <c r="B711" s="30"/>
-      <c r="C711" s="30"/>
+      <c r="A711" s="29"/>
+      <c r="B711" s="29"/>
+      <c r="C711" s="29"/>
     </row>
     <row r="712" ht="12.75" customHeight="1">
-      <c r="A712" s="30"/>
-      <c r="B712" s="30"/>
-      <c r="C712" s="30"/>
+      <c r="A712" s="29"/>
+      <c r="B712" s="29"/>
+      <c r="C712" s="29"/>
     </row>
     <row r="713" ht="12.75" customHeight="1">
-      <c r="A713" s="30"/>
-      <c r="B713" s="30"/>
-      <c r="C713" s="30"/>
+      <c r="A713" s="29"/>
+      <c r="B713" s="29"/>
+      <c r="C713" s="29"/>
     </row>
     <row r="714" ht="12.75" customHeight="1">
-      <c r="A714" s="30"/>
-      <c r="B714" s="30"/>
-      <c r="C714" s="30"/>
+      <c r="A714" s="29"/>
+      <c r="B714" s="29"/>
+      <c r="C714" s="29"/>
     </row>
     <row r="715" ht="12.75" customHeight="1">
-      <c r="A715" s="30"/>
-      <c r="B715" s="30"/>
-      <c r="C715" s="30"/>
+      <c r="A715" s="29"/>
+      <c r="B715" s="29"/>
+      <c r="C715" s="29"/>
     </row>
     <row r="716" ht="12.75" customHeight="1">
-      <c r="A716" s="30"/>
-      <c r="B716" s="30"/>
-      <c r="C716" s="30"/>
+      <c r="A716" s="29"/>
+      <c r="B716" s="29"/>
+      <c r="C716" s="29"/>
     </row>
     <row r="717" ht="12.75" customHeight="1">
-      <c r="A717" s="30"/>
-      <c r="B717" s="30"/>
-      <c r="C717" s="30"/>
+      <c r="A717" s="29"/>
+      <c r="B717" s="29"/>
+      <c r="C717" s="29"/>
     </row>
     <row r="718" ht="12.75" customHeight="1">
-      <c r="A718" s="30"/>
-      <c r="B718" s="30"/>
-      <c r="C718" s="30"/>
+      <c r="A718" s="29"/>
+      <c r="B718" s="29"/>
+      <c r="C718" s="29"/>
     </row>
     <row r="719" ht="12.75" customHeight="1">
-      <c r="A719" s="30"/>
-      <c r="B719" s="30"/>
-      <c r="C719" s="30"/>
+      <c r="A719" s="29"/>
+      <c r="B719" s="29"/>
+      <c r="C719" s="29"/>
     </row>
     <row r="720" ht="12.75" customHeight="1">
-      <c r="A720" s="30"/>
-      <c r="B720" s="30"/>
-      <c r="C720" s="30"/>
+      <c r="A720" s="29"/>
+      <c r="B720" s="29"/>
+      <c r="C720" s="29"/>
     </row>
     <row r="721" ht="12.75" customHeight="1">
-      <c r="A721" s="30"/>
-      <c r="B721" s="30"/>
-      <c r="C721" s="30"/>
+      <c r="A721" s="29"/>
+      <c r="B721" s="29"/>
+      <c r="C721" s="29"/>
     </row>
     <row r="722" ht="12.75" customHeight="1">
-      <c r="A722" s="30"/>
-      <c r="B722" s="30"/>
-      <c r="C722" s="30"/>
+      <c r="A722" s="29"/>
+      <c r="B722" s="29"/>
+      <c r="C722" s="29"/>
     </row>
     <row r="723" ht="12.75" customHeight="1">
-      <c r="A723" s="30"/>
-      <c r="B723" s="30"/>
-      <c r="C723" s="30"/>
+      <c r="A723" s="29"/>
+      <c r="B723" s="29"/>
+      <c r="C723" s="29"/>
     </row>
     <row r="724" ht="12.75" customHeight="1">
-      <c r="A724" s="30"/>
-      <c r="B724" s="30"/>
-      <c r="C724" s="30"/>
+      <c r="A724" s="29"/>
+      <c r="B724" s="29"/>
+      <c r="C724" s="29"/>
     </row>
     <row r="725" ht="12.75" customHeight="1">
-      <c r="A725" s="30"/>
-      <c r="B725" s="30"/>
-      <c r="C725" s="30"/>
+      <c r="A725" s="29"/>
+      <c r="B725" s="29"/>
+      <c r="C725" s="29"/>
     </row>
     <row r="726" ht="12.75" customHeight="1">
-      <c r="A726" s="30"/>
-      <c r="B726" s="30"/>
-      <c r="C726" s="30"/>
+      <c r="A726" s="29"/>
+      <c r="B726" s="29"/>
+      <c r="C726" s="29"/>
     </row>
     <row r="727" ht="12.75" customHeight="1">
-      <c r="A727" s="30"/>
-      <c r="B727" s="30"/>
-      <c r="C727" s="30"/>
+      <c r="A727" s="29"/>
+      <c r="B727" s="29"/>
+      <c r="C727" s="29"/>
     </row>
     <row r="728" ht="12.75" customHeight="1">
-      <c r="A728" s="30"/>
-      <c r="B728" s="30"/>
-      <c r="C728" s="30"/>
+      <c r="A728" s="29"/>
+      <c r="B728" s="29"/>
+      <c r="C728" s="29"/>
     </row>
     <row r="729" ht="12.75" customHeight="1">
-      <c r="A729" s="30"/>
-      <c r="B729" s="30"/>
-      <c r="C729" s="30"/>
+      <c r="A729" s="29"/>
+      <c r="B729" s="29"/>
+      <c r="C729" s="29"/>
     </row>
     <row r="730" ht="12.75" customHeight="1">
-      <c r="A730" s="30"/>
-      <c r="B730" s="30"/>
-      <c r="C730" s="30"/>
+      <c r="A730" s="29"/>
+      <c r="B730" s="29"/>
+      <c r="C730" s="29"/>
     </row>
     <row r="731" ht="12.75" customHeight="1">
-      <c r="A731" s="30"/>
-      <c r="B731" s="30"/>
-      <c r="C731" s="30"/>
+      <c r="A731" s="29"/>
+      <c r="B731" s="29"/>
+      <c r="C731" s="29"/>
     </row>
     <row r="732" ht="12.75" customHeight="1">
-      <c r="A732" s="30"/>
-      <c r="B732" s="30"/>
-      <c r="C732" s="30"/>
+      <c r="A732" s="29"/>
+      <c r="B732" s="29"/>
+      <c r="C732" s="29"/>
     </row>
     <row r="733" ht="12.75" customHeight="1">
-      <c r="A733" s="30"/>
-      <c r="B733" s="30"/>
-      <c r="C733" s="30"/>
+      <c r="A733" s="29"/>
+      <c r="B733" s="29"/>
+      <c r="C733" s="29"/>
     </row>
     <row r="734" ht="12.75" customHeight="1">
-      <c r="A734" s="30"/>
-      <c r="B734" s="30"/>
-      <c r="C734" s="30"/>
+      <c r="A734" s="29"/>
+      <c r="B734" s="29"/>
+      <c r="C734" s="29"/>
     </row>
     <row r="735" ht="12.75" customHeight="1">
-      <c r="A735" s="30"/>
-      <c r="B735" s="30"/>
-      <c r="C735" s="30"/>
+      <c r="A735" s="29"/>
+      <c r="B735" s="29"/>
+      <c r="C735" s="29"/>
     </row>
     <row r="736" ht="12.75" customHeight="1">
-      <c r="A736" s="30"/>
-      <c r="B736" s="30"/>
-      <c r="C736" s="30"/>
+      <c r="A736" s="29"/>
+      <c r="B736" s="29"/>
+      <c r="C736" s="29"/>
     </row>
     <row r="737" ht="12.75" customHeight="1">
-      <c r="A737" s="30"/>
-      <c r="B737" s="30"/>
-      <c r="C737" s="30"/>
+      <c r="A737" s="29"/>
+      <c r="B737" s="29"/>
+      <c r="C737" s="29"/>
     </row>
     <row r="738" ht="12.75" customHeight="1">
-      <c r="A738" s="30"/>
-      <c r="B738" s="30"/>
-      <c r="C738" s="30"/>
+      <c r="A738" s="29"/>
+      <c r="B738" s="29"/>
+      <c r="C738" s="29"/>
     </row>
     <row r="739" ht="12.75" customHeight="1">
-      <c r="A739" s="30"/>
-      <c r="B739" s="30"/>
-      <c r="C739" s="30"/>
+      <c r="A739" s="29"/>
+      <c r="B739" s="29"/>
+      <c r="C739" s="29"/>
     </row>
     <row r="740" ht="12.75" customHeight="1">
-      <c r="A740" s="30"/>
-      <c r="B740" s="30"/>
-      <c r="C740" s="30"/>
+      <c r="A740" s="29"/>
+      <c r="B740" s="29"/>
+      <c r="C740" s="29"/>
     </row>
     <row r="741" ht="12.75" customHeight="1">
-      <c r="A741" s="30"/>
-      <c r="B741" s="30"/>
-      <c r="C741" s="30"/>
+      <c r="A741" s="29"/>
+      <c r="B741" s="29"/>
+      <c r="C741" s="29"/>
     </row>
     <row r="742" ht="12.75" customHeight="1">
-      <c r="A742" s="30"/>
-      <c r="B742" s="30"/>
-      <c r="C742" s="30"/>
+      <c r="A742" s="29"/>
+      <c r="B742" s="29"/>
+      <c r="C742" s="29"/>
     </row>
     <row r="743" ht="12.75" customHeight="1">
-      <c r="A743" s="30"/>
-      <c r="B743" s="30"/>
-      <c r="C743" s="30"/>
+      <c r="A743" s="29"/>
+      <c r="B743" s="29"/>
+      <c r="C743" s="29"/>
     </row>
     <row r="744" ht="12.75" customHeight="1">
-      <c r="A744" s="30"/>
-      <c r="B744" s="30"/>
-      <c r="C744" s="30"/>
+      <c r="A744" s="29"/>
+      <c r="B744" s="29"/>
+      <c r="C744" s="29"/>
     </row>
     <row r="745" ht="12.75" customHeight="1">
-      <c r="A745" s="30"/>
-      <c r="B745" s="30"/>
-      <c r="C745" s="30"/>
+      <c r="A745" s="29"/>
+      <c r="B745" s="29"/>
+      <c r="C745" s="29"/>
     </row>
     <row r="746" ht="12.75" customHeight="1">
-      <c r="A746" s="30"/>
-      <c r="B746" s="30"/>
-      <c r="C746" s="30"/>
+      <c r="A746" s="29"/>
+      <c r="B746" s="29"/>
+      <c r="C746" s="29"/>
     </row>
     <row r="747" ht="12.75" customHeight="1">
-      <c r="A747" s="30"/>
-      <c r="B747" s="30"/>
-      <c r="C747" s="30"/>
+      <c r="A747" s="29"/>
+      <c r="B747" s="29"/>
+      <c r="C747" s="29"/>
     </row>
     <row r="748" ht="12.75" customHeight="1">
-      <c r="A748" s="30"/>
-      <c r="B748" s="30"/>
-      <c r="C748" s="30"/>
+      <c r="A748" s="29"/>
+      <c r="B748" s="29"/>
+      <c r="C748" s="29"/>
     </row>
     <row r="749" ht="12.75" customHeight="1">
-      <c r="A749" s="30"/>
-      <c r="B749" s="30"/>
-      <c r="C749" s="30"/>
+      <c r="A749" s="29"/>
+      <c r="B749" s="29"/>
+      <c r="C749" s="29"/>
     </row>
     <row r="750" ht="12.75" customHeight="1">
-      <c r="A750" s="30"/>
-      <c r="B750" s="30"/>
-      <c r="C750" s="30"/>
+      <c r="A750" s="29"/>
+      <c r="B750" s="29"/>
+      <c r="C750" s="29"/>
     </row>
     <row r="751" ht="12.75" customHeight="1">
-      <c r="A751" s="30"/>
-      <c r="B751" s="30"/>
-      <c r="C751" s="30"/>
+      <c r="A751" s="29"/>
+      <c r="B751" s="29"/>
+      <c r="C751" s="29"/>
     </row>
     <row r="752" ht="12.75" customHeight="1">
-      <c r="A752" s="30"/>
-      <c r="B752" s="30"/>
-      <c r="C752" s="30"/>
+      <c r="A752" s="29"/>
+      <c r="B752" s="29"/>
+      <c r="C752" s="29"/>
     </row>
     <row r="753" ht="12.75" customHeight="1">
-      <c r="A753" s="30"/>
-      <c r="B753" s="30"/>
-      <c r="C753" s="30"/>
+      <c r="A753" s="29"/>
+      <c r="B753" s="29"/>
+      <c r="C753" s="29"/>
     </row>
     <row r="754" ht="12.75" customHeight="1">
-      <c r="A754" s="30"/>
-      <c r="B754" s="30"/>
-      <c r="C754" s="30"/>
+      <c r="A754" s="29"/>
+      <c r="B754" s="29"/>
+      <c r="C754" s="29"/>
     </row>
     <row r="755" ht="12.75" customHeight="1">
-      <c r="A755" s="30"/>
-      <c r="B755" s="30"/>
-      <c r="C755" s="30"/>
+      <c r="A755" s="29"/>
+      <c r="B755" s="29"/>
+      <c r="C755" s="29"/>
     </row>
     <row r="756" ht="12.75" customHeight="1">
-      <c r="A756" s="30"/>
-      <c r="B756" s="30"/>
-      <c r="C756" s="30"/>
+      <c r="A756" s="29"/>
+      <c r="B756" s="29"/>
+      <c r="C756" s="29"/>
     </row>
     <row r="757" ht="12.75" customHeight="1">
-      <c r="A757" s="30"/>
-      <c r="B757" s="30"/>
-      <c r="C757" s="30"/>
+      <c r="A757" s="29"/>
+      <c r="B757" s="29"/>
+      <c r="C757" s="29"/>
     </row>
     <row r="758" ht="12.75" customHeight="1">
-      <c r="A758" s="30"/>
-      <c r="B758" s="30"/>
-      <c r="C758" s="30"/>
+      <c r="A758" s="29"/>
+      <c r="B758" s="29"/>
+      <c r="C758" s="29"/>
     </row>
     <row r="759" ht="12.75" customHeight="1">
-      <c r="A759" s="30"/>
-      <c r="B759" s="30"/>
-      <c r="C759" s="30"/>
+      <c r="A759" s="29"/>
+      <c r="B759" s="29"/>
+      <c r="C759" s="29"/>
     </row>
     <row r="760" ht="12.75" customHeight="1">
-      <c r="A760" s="30"/>
-      <c r="B760" s="30"/>
-      <c r="C760" s="30"/>
+      <c r="A760" s="29"/>
+      <c r="B760" s="29"/>
+      <c r="C760" s="29"/>
     </row>
     <row r="761" ht="12.75" customHeight="1">
-      <c r="A761" s="30"/>
-      <c r="B761" s="30"/>
-      <c r="C761" s="30"/>
+      <c r="A761" s="29"/>
+      <c r="B761" s="29"/>
+      <c r="C761" s="29"/>
     </row>
     <row r="762" ht="12.75" customHeight="1">
-      <c r="A762" s="30"/>
-      <c r="B762" s="30"/>
-      <c r="C762" s="30"/>
+      <c r="A762" s="29"/>
+      <c r="B762" s="29"/>
+      <c r="C762" s="29"/>
     </row>
     <row r="763" ht="12.75" customHeight="1">
-      <c r="A763" s="30"/>
-      <c r="B763" s="30"/>
-      <c r="C763" s="30"/>
+      <c r="A763" s="29"/>
+      <c r="B763" s="29"/>
+      <c r="C763" s="29"/>
     </row>
     <row r="764" ht="12.75" customHeight="1">
-      <c r="A764" s="30"/>
-      <c r="B764" s="30"/>
-      <c r="C764" s="30"/>
+      <c r="A764" s="29"/>
+      <c r="B764" s="29"/>
+      <c r="C764" s="29"/>
     </row>
     <row r="765" ht="12.75" customHeight="1">
-      <c r="A765" s="30"/>
-      <c r="B765" s="30"/>
-      <c r="C765" s="30"/>
+      <c r="A765" s="29"/>
+      <c r="B765" s="29"/>
+      <c r="C765" s="29"/>
     </row>
     <row r="766" ht="12.75" customHeight="1">
-      <c r="A766" s="30"/>
-      <c r="B766" s="30"/>
-      <c r="C766" s="30"/>
+      <c r="A766" s="29"/>
+      <c r="B766" s="29"/>
+      <c r="C766" s="29"/>
     </row>
     <row r="767" ht="12.75" customHeight="1">
-      <c r="A767" s="30"/>
-      <c r="B767" s="30"/>
-      <c r="C767" s="30"/>
+      <c r="A767" s="29"/>
+      <c r="B767" s="29"/>
+      <c r="C767" s="29"/>
     </row>
     <row r="768" ht="12.75" customHeight="1">
-      <c r="A768" s="30"/>
-      <c r="B768" s="30"/>
-      <c r="C768" s="30"/>
+      <c r="A768" s="29"/>
+      <c r="B768" s="29"/>
+      <c r="C768" s="29"/>
     </row>
     <row r="769" ht="12.75" customHeight="1">
-      <c r="A769" s="30"/>
-      <c r="B769" s="30"/>
-      <c r="C769" s="30"/>
+      <c r="A769" s="29"/>
+      <c r="B769" s="29"/>
+      <c r="C769" s="29"/>
     </row>
     <row r="770" ht="12.75" customHeight="1">
-      <c r="A770" s="30"/>
-      <c r="B770" s="30"/>
-      <c r="C770" s="30"/>
+      <c r="A770" s="29"/>
+      <c r="B770" s="29"/>
+      <c r="C770" s="29"/>
     </row>
     <row r="771" ht="12.75" customHeight="1">
-      <c r="A771" s="30"/>
-      <c r="B771" s="30"/>
-      <c r="C771" s="30"/>
+      <c r="A771" s="29"/>
+      <c r="B771" s="29"/>
+      <c r="C771" s="29"/>
     </row>
     <row r="772" ht="12.75" customHeight="1">
-      <c r="A772" s="30"/>
-      <c r="B772" s="30"/>
-      <c r="C772" s="30"/>
+      <c r="A772" s="29"/>
+      <c r="B772" s="29"/>
+      <c r="C772" s="29"/>
     </row>
     <row r="773" ht="12.75" customHeight="1">
-      <c r="A773" s="30"/>
-      <c r="B773" s="30"/>
-      <c r="C773" s="30"/>
+      <c r="A773" s="29"/>
+      <c r="B773" s="29"/>
+      <c r="C773" s="29"/>
     </row>
     <row r="774" ht="12.75" customHeight="1">
-      <c r="A774" s="30"/>
-      <c r="B774" s="30"/>
-      <c r="C774" s="30"/>
+      <c r="A774" s="29"/>
+      <c r="B774" s="29"/>
+      <c r="C774" s="29"/>
     </row>
     <row r="775" ht="12.75" customHeight="1">
-      <c r="A775" s="30"/>
-      <c r="B775" s="30"/>
-      <c r="C775" s="30"/>
+      <c r="A775" s="29"/>
+      <c r="B775" s="29"/>
+      <c r="C775" s="29"/>
     </row>
     <row r="776" ht="12.75" customHeight="1">
-      <c r="A776" s="30"/>
-      <c r="B776" s="30"/>
-      <c r="C776" s="30"/>
+      <c r="A776" s="29"/>
+      <c r="B776" s="29"/>
+      <c r="C776" s="29"/>
     </row>
     <row r="777" ht="12.75" customHeight="1">
-      <c r="A777" s="30"/>
-      <c r="B777" s="30"/>
-      <c r="C777" s="30"/>
+      <c r="A777" s="29"/>
+      <c r="B777" s="29"/>
+      <c r="C777" s="29"/>
     </row>
     <row r="778" ht="12.75" customHeight="1">
-      <c r="A778" s="30"/>
-      <c r="B778" s="30"/>
-      <c r="C778" s="30"/>
+      <c r="A778" s="29"/>
+      <c r="B778" s="29"/>
+      <c r="C778" s="29"/>
     </row>
     <row r="779" ht="12.75" customHeight="1">
-      <c r="A779" s="30"/>
-      <c r="B779" s="30"/>
-      <c r="C779" s="30"/>
+      <c r="A779" s="29"/>
+      <c r="B779" s="29"/>
+      <c r="C779" s="29"/>
     </row>
     <row r="780" ht="12.75" customHeight="1">
-      <c r="A780" s="30"/>
-      <c r="B780" s="30"/>
-      <c r="C780" s="30"/>
+      <c r="A780" s="29"/>
+      <c r="B780" s="29"/>
+      <c r="C780" s="29"/>
     </row>
     <row r="781" ht="12.75" customHeight="1">
-      <c r="A781" s="30"/>
-      <c r="B781" s="30"/>
-      <c r="C781" s="30"/>
+      <c r="A781" s="29"/>
+      <c r="B781" s="29"/>
+      <c r="C781" s="29"/>
     </row>
     <row r="782" ht="12.75" customHeight="1">
-      <c r="A782" s="30"/>
-      <c r="B782" s="30"/>
-      <c r="C782" s="30"/>
+      <c r="A782" s="29"/>
+      <c r="B782" s="29"/>
+      <c r="C782" s="29"/>
     </row>
     <row r="783" ht="12.75" customHeight="1">
-      <c r="A783" s="30"/>
-      <c r="B783" s="30"/>
-      <c r="C783" s="30"/>
+      <c r="A783" s="29"/>
+      <c r="B783" s="29"/>
+      <c r="C783" s="29"/>
     </row>
     <row r="784" ht="12.75" customHeight="1">
-      <c r="A784" s="30"/>
-      <c r="B784" s="30"/>
-      <c r="C784" s="30"/>
+      <c r="A784" s="29"/>
+      <c r="B784" s="29"/>
+      <c r="C784" s="29"/>
     </row>
     <row r="785" ht="12.75" customHeight="1">
-      <c r="A785" s="30"/>
-      <c r="B785" s="30"/>
-      <c r="C785" s="30"/>
+      <c r="A785" s="29"/>
+      <c r="B785" s="29"/>
+      <c r="C785" s="29"/>
     </row>
     <row r="786" ht="12.75" customHeight="1">
-      <c r="A786" s="30"/>
-      <c r="B786" s="30"/>
-      <c r="C786" s="30"/>
+      <c r="A786" s="29"/>
+      <c r="B786" s="29"/>
+      <c r="C786" s="29"/>
     </row>
     <row r="787" ht="12.75" customHeight="1">
-      <c r="A787" s="30"/>
-      <c r="B787" s="30"/>
-      <c r="C787" s="30"/>
+      <c r="A787" s="29"/>
+      <c r="B787" s="29"/>
+      <c r="C787" s="29"/>
     </row>
     <row r="788" ht="12.75" customHeight="1">
-      <c r="A788" s="30"/>
-      <c r="B788" s="30"/>
-      <c r="C788" s="30"/>
+      <c r="A788" s="29"/>
+      <c r="B788" s="29"/>
+      <c r="C788" s="29"/>
     </row>
     <row r="789" ht="12.75" customHeight="1">
-      <c r="A789" s="30"/>
-      <c r="B789" s="30"/>
-      <c r="C789" s="30"/>
+      <c r="A789" s="29"/>
+      <c r="B789" s="29"/>
+      <c r="C789" s="29"/>
     </row>
     <row r="790" ht="12.75" customHeight="1">
-      <c r="A790" s="30"/>
-      <c r="B790" s="30"/>
-      <c r="C790" s="30"/>
+      <c r="A790" s="29"/>
+      <c r="B790" s="29"/>
+      <c r="C790" s="29"/>
     </row>
     <row r="791" ht="12.75" customHeight="1">
-      <c r="A791" s="30"/>
-      <c r="B791" s="30"/>
-      <c r="C791" s="30"/>
+      <c r="A791" s="29"/>
+      <c r="B791" s="29"/>
+      <c r="C791" s="29"/>
     </row>
     <row r="792" ht="12.75" customHeight="1">
-      <c r="A792" s="30"/>
-      <c r="B792" s="30"/>
-      <c r="C792" s="30"/>
+      <c r="A792" s="29"/>
+      <c r="B792" s="29"/>
+      <c r="C792" s="29"/>
     </row>
     <row r="793" ht="12.75" customHeight="1">
-      <c r="A793" s="30"/>
-      <c r="B793" s="30"/>
-      <c r="C793" s="30"/>
+      <c r="A793" s="29"/>
+      <c r="B793" s="29"/>
+      <c r="C793" s="29"/>
     </row>
     <row r="794" ht="12.75" customHeight="1">
-      <c r="A794" s="30"/>
-      <c r="B794" s="30"/>
-      <c r="C794" s="30"/>
+      <c r="A794" s="29"/>
+      <c r="B794" s="29"/>
+      <c r="C794" s="29"/>
     </row>
     <row r="795" ht="12.75" customHeight="1">
-      <c r="A795" s="30"/>
-      <c r="B795" s="30"/>
-      <c r="C795" s="30"/>
+      <c r="A795" s="29"/>
+      <c r="B795" s="29"/>
+      <c r="C795" s="29"/>
     </row>
     <row r="796" ht="12.75" customHeight="1">
-      <c r="A796" s="30"/>
-      <c r="B796" s="30"/>
-      <c r="C796" s="30"/>
+      <c r="A796" s="29"/>
+      <c r="B796" s="29"/>
+      <c r="C796" s="29"/>
     </row>
     <row r="797" ht="12.75" customHeight="1">
-      <c r="A797" s="30"/>
-      <c r="B797" s="30"/>
-      <c r="C797" s="30"/>
+      <c r="A797" s="29"/>
+      <c r="B797" s="29"/>
+      <c r="C797" s="29"/>
     </row>
     <row r="798" ht="12.75" customHeight="1">
-      <c r="A798" s="30"/>
-      <c r="B798" s="30"/>
-      <c r="C798" s="30"/>
+      <c r="A798" s="29"/>
+      <c r="B798" s="29"/>
+      <c r="C798" s="29"/>
     </row>
     <row r="799" ht="12.75" customHeight="1">
-      <c r="A799" s="30"/>
-      <c r="B799" s="30"/>
-      <c r="C799" s="30"/>
+      <c r="A799" s="29"/>
+      <c r="B799" s="29"/>
+      <c r="C799" s="29"/>
     </row>
     <row r="800" ht="12.75" customHeight="1">
-      <c r="A800" s="30"/>
-      <c r="B800" s="30"/>
-      <c r="C800" s="30"/>
+      <c r="A800" s="29"/>
+      <c r="B800" s="29"/>
+      <c r="C800" s="29"/>
     </row>
     <row r="801" ht="12.75" customHeight="1">
-      <c r="A801" s="30"/>
-      <c r="B801" s="30"/>
-      <c r="C801" s="30"/>
+      <c r="A801" s="29"/>
+      <c r="B801" s="29"/>
+      <c r="C801" s="29"/>
     </row>
     <row r="802" ht="12.75" customHeight="1">
-      <c r="A802" s="30"/>
-      <c r="B802" s="30"/>
-      <c r="C802" s="30"/>
+      <c r="A802" s="29"/>
+      <c r="B802" s="29"/>
+      <c r="C802" s="29"/>
     </row>
     <row r="803" ht="12.75" customHeight="1">
-      <c r="A803" s="30"/>
-      <c r="B803" s="30"/>
-      <c r="C803" s="30"/>
+      <c r="A803" s="29"/>
+      <c r="B803" s="29"/>
+      <c r="C803" s="29"/>
     </row>
     <row r="804" ht="12.75" customHeight="1">
-      <c r="A804" s="30"/>
-      <c r="B804" s="30"/>
-      <c r="C804" s="30"/>
+      <c r="A804" s="29"/>
+      <c r="B804" s="29"/>
+      <c r="C804" s="29"/>
     </row>
     <row r="805" ht="12.75" customHeight="1">
-      <c r="A805" s="30"/>
-      <c r="B805" s="30"/>
-      <c r="C805" s="30"/>
+      <c r="A805" s="29"/>
+      <c r="B805" s="29"/>
+      <c r="C805" s="29"/>
     </row>
     <row r="806" ht="12.75" customHeight="1">
-      <c r="A806" s="30"/>
-      <c r="B806" s="30"/>
-      <c r="C806" s="30"/>
+      <c r="A806" s="29"/>
+      <c r="B806" s="29"/>
+      <c r="C806" s="29"/>
     </row>
     <row r="807" ht="12.75" customHeight="1">
-      <c r="A807" s="30"/>
-      <c r="B807" s="30"/>
-      <c r="C807" s="30"/>
+      <c r="A807" s="29"/>
+      <c r="B807" s="29"/>
+      <c r="C807" s="29"/>
     </row>
     <row r="808" ht="12.75" customHeight="1">
-      <c r="A808" s="30"/>
-      <c r="B808" s="30"/>
-      <c r="C808" s="30"/>
+      <c r="A808" s="29"/>
+      <c r="B808" s="29"/>
+      <c r="C808" s="29"/>
     </row>
     <row r="809" ht="12.75" customHeight="1">
-      <c r="A809" s="30"/>
-      <c r="B809" s="30"/>
-      <c r="C809" s="30"/>
+      <c r="A809" s="29"/>
+      <c r="B809" s="29"/>
+      <c r="C809" s="29"/>
     </row>
     <row r="810" ht="12.75" customHeight="1">
-      <c r="A810" s="30"/>
-      <c r="B810" s="30"/>
-      <c r="C810" s="30"/>
+      <c r="A810" s="29"/>
+      <c r="B810" s="29"/>
+      <c r="C810" s="29"/>
     </row>
     <row r="811" ht="12.75" customHeight="1">
-      <c r="A811" s="30"/>
-      <c r="B811" s="30"/>
-      <c r="C811" s="30"/>
+      <c r="A811" s="29"/>
+      <c r="B811" s="29"/>
+      <c r="C811" s="29"/>
     </row>
     <row r="812" ht="12.75" customHeight="1">
-      <c r="A812" s="30"/>
-      <c r="B812" s="30"/>
-      <c r="C812" s="30"/>
+      <c r="A812" s="29"/>
+      <c r="B812" s="29"/>
+      <c r="C812" s="29"/>
     </row>
     <row r="813" ht="12.75" customHeight="1">
-      <c r="A813" s="30"/>
-      <c r="B813" s="30"/>
-      <c r="C813" s="30"/>
+      <c r="A813" s="29"/>
+      <c r="B813" s="29"/>
+      <c r="C813" s="29"/>
     </row>
     <row r="814" ht="12.75" customHeight="1">
-      <c r="A814" s="30"/>
-      <c r="B814" s="30"/>
-      <c r="C814" s="30"/>
+      <c r="A814" s="29"/>
+      <c r="B814" s="29"/>
+      <c r="C814" s="29"/>
     </row>
     <row r="815" ht="12.75" customHeight="1">
-      <c r="A815" s="30"/>
-      <c r="B815" s="30"/>
-      <c r="C815" s="30"/>
+      <c r="A815" s="29"/>
+      <c r="B815" s="29"/>
+      <c r="C815" s="29"/>
     </row>
     <row r="816" ht="12.75" customHeight="1">
-      <c r="A816" s="30"/>
-      <c r="B816" s="30"/>
-      <c r="C816" s="30"/>
+      <c r="A816" s="29"/>
+      <c r="B816" s="29"/>
+      <c r="C816" s="29"/>
     </row>
     <row r="817" ht="12.75" customHeight="1">
-      <c r="A817" s="30"/>
-      <c r="B817" s="30"/>
-      <c r="C817" s="30"/>
+      <c r="A817" s="29"/>
+      <c r="B817" s="29"/>
+      <c r="C817" s="29"/>
     </row>
     <row r="818" ht="12.75" customHeight="1">
-      <c r="A818" s="30"/>
-      <c r="B818" s="30"/>
-      <c r="C818" s="30"/>
+      <c r="A818" s="29"/>
+      <c r="B818" s="29"/>
+      <c r="C818" s="29"/>
     </row>
     <row r="819" ht="12.75" customHeight="1">
-      <c r="A819" s="30"/>
-      <c r="B819" s="30"/>
-      <c r="C819" s="30"/>
+      <c r="A819" s="29"/>
+      <c r="B819" s="29"/>
+      <c r="C819" s="29"/>
     </row>
     <row r="820" ht="12.75" customHeight="1">
-      <c r="A820" s="30"/>
-      <c r="B820" s="30"/>
-      <c r="C820" s="30"/>
+      <c r="A820" s="29"/>
+      <c r="B820" s="29"/>
+      <c r="C820" s="29"/>
     </row>
     <row r="821" ht="12.75" customHeight="1">
-      <c r="A821" s="30"/>
-      <c r="B821" s="30"/>
-      <c r="C821" s="30"/>
+      <c r="A821" s="29"/>
+      <c r="B821" s="29"/>
+      <c r="C821" s="29"/>
     </row>
     <row r="822" ht="12.75" customHeight="1">
-      <c r="A822" s="30"/>
-      <c r="B822" s="30"/>
-      <c r="C822" s="30"/>
+      <c r="A822" s="29"/>
+      <c r="B822" s="29"/>
+      <c r="C822" s="29"/>
     </row>
     <row r="823" ht="12.75" customHeight="1">
-      <c r="A823" s="30"/>
-      <c r="B823" s="30"/>
-      <c r="C823" s="30"/>
+      <c r="A823" s="29"/>
+      <c r="B823" s="29"/>
+      <c r="C823" s="29"/>
     </row>
     <row r="824" ht="12.75" customHeight="1">
-      <c r="A824" s="30"/>
-      <c r="B824" s="30"/>
-      <c r="C824" s="30"/>
+      <c r="A824" s="29"/>
+      <c r="B824" s="29"/>
+      <c r="C824" s="29"/>
     </row>
     <row r="825" ht="12.75" customHeight="1">
-      <c r="A825" s="30"/>
-      <c r="B825" s="30"/>
-      <c r="C825" s="30"/>
+      <c r="A825" s="29"/>
+      <c r="B825" s="29"/>
+      <c r="C825" s="29"/>
     </row>
     <row r="826" ht="12.75" customHeight="1">
-      <c r="A826" s="30"/>
-      <c r="B826" s="30"/>
-      <c r="C826" s="30"/>
+      <c r="A826" s="29"/>
+      <c r="B826" s="29"/>
+      <c r="C826" s="29"/>
     </row>
     <row r="827" ht="12.75" customHeight="1">
-      <c r="A827" s="30"/>
-      <c r="B827" s="30"/>
-      <c r="C827" s="30"/>
+      <c r="A827" s="29"/>
+      <c r="B827" s="29"/>
+      <c r="C827" s="29"/>
     </row>
     <row r="828" ht="12.75" customHeight="1">
-      <c r="A828" s="30"/>
-      <c r="B828" s="30"/>
-      <c r="C828" s="30"/>
+      <c r="A828" s="29"/>
+      <c r="B828" s="29"/>
+      <c r="C828" s="29"/>
     </row>
     <row r="829" ht="12.75" customHeight="1">
-      <c r="A829" s="30"/>
-      <c r="B829" s="30"/>
-      <c r="C829" s="30"/>
+      <c r="A829" s="29"/>
+      <c r="B829" s="29"/>
+      <c r="C829" s="29"/>
     </row>
     <row r="830" ht="12.75" customHeight="1">
-      <c r="A830" s="30"/>
-      <c r="B830" s="30"/>
-      <c r="C830" s="30"/>
+      <c r="A830" s="29"/>
+      <c r="B830" s="29"/>
+      <c r="C830" s="29"/>
     </row>
     <row r="831" ht="12.75" customHeight="1">
-      <c r="A831" s="30"/>
-      <c r="B831" s="30"/>
-      <c r="C831" s="30"/>
+      <c r="A831" s="29"/>
+      <c r="B831" s="29"/>
+      <c r="C831" s="29"/>
     </row>
     <row r="832" ht="12.75" customHeight="1">
-      <c r="A832" s="30"/>
-      <c r="B832" s="30"/>
-      <c r="C832" s="30"/>
+      <c r="A832" s="29"/>
+      <c r="B832" s="29"/>
+      <c r="C832" s="29"/>
     </row>
     <row r="833" ht="12.75" customHeight="1">
-      <c r="A833" s="30"/>
-      <c r="B833" s="30"/>
-      <c r="C833" s="30"/>
+      <c r="A833" s="29"/>
+      <c r="B833" s="29"/>
+      <c r="C833" s="29"/>
     </row>
     <row r="834" ht="12.75" customHeight="1">
-      <c r="A834" s="30"/>
-      <c r="B834" s="30"/>
-      <c r="C834" s="30"/>
+      <c r="A834" s="29"/>
+      <c r="B834" s="29"/>
+      <c r="C834" s="29"/>
     </row>
     <row r="835" ht="12.75" customHeight="1">
-      <c r="A835" s="30"/>
-      <c r="B835" s="30"/>
-      <c r="C835" s="30"/>
+      <c r="A835" s="29"/>
+      <c r="B835" s="29"/>
+      <c r="C835" s="29"/>
     </row>
     <row r="836" ht="12.75" customHeight="1">
-      <c r="A836" s="30"/>
-      <c r="B836" s="30"/>
-      <c r="C836" s="30"/>
+      <c r="A836" s="29"/>
+      <c r="B836" s="29"/>
+      <c r="C836" s="29"/>
     </row>
     <row r="837" ht="12.75" customHeight="1">
-      <c r="A837" s="30"/>
-      <c r="B837" s="30"/>
-      <c r="C837" s="30"/>
+      <c r="A837" s="29"/>
+      <c r="B837" s="29"/>
+      <c r="C837" s="29"/>
     </row>
     <row r="838" ht="12.75" customHeight="1">
-      <c r="A838" s="30"/>
-      <c r="B838" s="30"/>
-      <c r="C838" s="30"/>
+      <c r="A838" s="29"/>
+      <c r="B838" s="29"/>
+      <c r="C838" s="29"/>
     </row>
     <row r="839" ht="12.75" customHeight="1">
-      <c r="A839" s="30"/>
-      <c r="B839" s="30"/>
-      <c r="C839" s="30"/>
+      <c r="A839" s="29"/>
+      <c r="B839" s="29"/>
+      <c r="C839" s="29"/>
     </row>
     <row r="840" ht="12.75" customHeight="1">
-      <c r="A840" s="30"/>
-      <c r="B840" s="30"/>
-      <c r="C840" s="30"/>
+      <c r="A840" s="29"/>
+      <c r="B840" s="29"/>
+      <c r="C840" s="29"/>
     </row>
     <row r="841" ht="12.75" customHeight="1">
-      <c r="A841" s="30"/>
-      <c r="B841" s="30"/>
-      <c r="C841" s="30"/>
+      <c r="A841" s="29"/>
+      <c r="B841" s="29"/>
+      <c r="C841" s="29"/>
     </row>
     <row r="842" ht="12.75" customHeight="1">
-      <c r="A842" s="30"/>
-      <c r="B842" s="30"/>
-      <c r="C842" s="30"/>
+      <c r="A842" s="29"/>
+      <c r="B842" s="29"/>
+      <c r="C842" s="29"/>
     </row>
     <row r="843" ht="12.75" customHeight="1">
-      <c r="A843" s="30"/>
-      <c r="B843" s="30"/>
-      <c r="C843" s="30"/>
+      <c r="A843" s="29"/>
+      <c r="B843" s="29"/>
+      <c r="C843" s="29"/>
     </row>
     <row r="844" ht="12.75" customHeight="1">
-      <c r="A844" s="30"/>
-      <c r="B844" s="30"/>
-      <c r="C844" s="30"/>
+      <c r="A844" s="29"/>
+      <c r="B844" s="29"/>
+      <c r="C844" s="29"/>
     </row>
     <row r="845" ht="12.75" customHeight="1">
-      <c r="A845" s="30"/>
-      <c r="B845" s="30"/>
-      <c r="C845" s="30"/>
+      <c r="A845" s="29"/>
+      <c r="B845" s="29"/>
+      <c r="C845" s="29"/>
     </row>
     <row r="846" ht="12.75" customHeight="1">
-      <c r="A846" s="30"/>
-      <c r="B846" s="30"/>
-      <c r="C846" s="30"/>
+      <c r="A846" s="29"/>
+      <c r="B846" s="29"/>
+      <c r="C846" s="29"/>
     </row>
     <row r="847" ht="12.75" customHeight="1">
-      <c r="A847" s="30"/>
-      <c r="B847" s="30"/>
-      <c r="C847" s="30"/>
+      <c r="A847" s="29"/>
+      <c r="B847" s="29"/>
+      <c r="C847" s="29"/>
     </row>
     <row r="848" ht="12.75" customHeight="1">
-      <c r="A848" s="30"/>
-      <c r="B848" s="30"/>
-      <c r="C848" s="30"/>
+      <c r="A848" s="29"/>
+      <c r="B848" s="29"/>
+      <c r="C848" s="29"/>
     </row>
     <row r="849" ht="12.75" customHeight="1">
-      <c r="A849" s="30"/>
-      <c r="B849" s="30"/>
-      <c r="C849" s="30"/>
+      <c r="A849" s="29"/>
+      <c r="B849" s="29"/>
+      <c r="C849" s="29"/>
     </row>
     <row r="850" ht="12.75" customHeight="1">
-      <c r="A850" s="30"/>
-      <c r="B850" s="30"/>
-      <c r="C850" s="30"/>
+      <c r="A850" s="29"/>
+      <c r="B850" s="29"/>
+      <c r="C850" s="29"/>
     </row>
     <row r="851" ht="12.75" customHeight="1">
-      <c r="A851" s="30"/>
-      <c r="B851" s="30"/>
-      <c r="C851" s="30"/>
+      <c r="A851" s="29"/>
+      <c r="B851" s="29"/>
+      <c r="C851" s="29"/>
     </row>
     <row r="852" ht="12.75" customHeight="1">
-      <c r="A852" s="30"/>
-      <c r="B852" s="30"/>
-      <c r="C852" s="30"/>
+      <c r="A852" s="29"/>
+      <c r="B852" s="29"/>
+      <c r="C852" s="29"/>
     </row>
     <row r="853" ht="12.75" customHeight="1">
-      <c r="A853" s="30"/>
-      <c r="B853" s="30"/>
-      <c r="C853" s="30"/>
+      <c r="A853" s="29"/>
+      <c r="B853" s="29"/>
+      <c r="C853" s="29"/>
     </row>
     <row r="854" ht="12.75" customHeight="1">
-      <c r="A854" s="30"/>
-      <c r="B854" s="30"/>
-      <c r="C854" s="30"/>
+      <c r="A854" s="29"/>
+      <c r="B854" s="29"/>
+      <c r="C854" s="29"/>
     </row>
     <row r="855" ht="12.75" customHeight="1">
-      <c r="A855" s="30"/>
-      <c r="B855" s="30"/>
-      <c r="C855" s="30"/>
+      <c r="A855" s="29"/>
+      <c r="B855" s="29"/>
+      <c r="C855" s="29"/>
     </row>
     <row r="856" ht="12.75" customHeight="1">
-      <c r="A856" s="30"/>
-      <c r="B856" s="30"/>
-      <c r="C856" s="30"/>
+      <c r="A856" s="29"/>
+      <c r="B856" s="29"/>
+      <c r="C856" s="29"/>
     </row>
     <row r="857" ht="12.75" customHeight="1">
-      <c r="A857" s="30"/>
-      <c r="B857" s="30"/>
-      <c r="C857" s="30"/>
+      <c r="A857" s="29"/>
+      <c r="B857" s="29"/>
+      <c r="C857" s="29"/>
     </row>
     <row r="858" ht="12.75" customHeight="1">
-      <c r="A858" s="30"/>
-      <c r="B858" s="30"/>
-      <c r="C858" s="30"/>
+      <c r="A858" s="29"/>
+      <c r="B858" s="29"/>
+      <c r="C858" s="29"/>
     </row>
     <row r="859" ht="12.75" customHeight="1">
-      <c r="A859" s="30"/>
-      <c r="B859" s="30"/>
-      <c r="C859" s="30"/>
+      <c r="A859" s="29"/>
+      <c r="B859" s="29"/>
+      <c r="C859" s="29"/>
     </row>
     <row r="860" ht="12.75" customHeight="1">
-      <c r="A860" s="30"/>
-      <c r="B860" s="30"/>
-      <c r="C860" s="30"/>
+      <c r="A860" s="29"/>
+      <c r="B860" s="29"/>
+      <c r="C860" s="29"/>
     </row>
     <row r="861" ht="12.75" customHeight="1">
-      <c r="A861" s="30"/>
-      <c r="B861" s="30"/>
-      <c r="C861" s="30"/>
+      <c r="A861" s="29"/>
+      <c r="B861" s="29"/>
+      <c r="C861" s="29"/>
     </row>
     <row r="862" ht="12.75" customHeight="1">
-      <c r="A862" s="30"/>
-      <c r="B862" s="30"/>
-      <c r="C862" s="30"/>
+      <c r="A862" s="29"/>
+      <c r="B862" s="29"/>
+      <c r="C862" s="29"/>
     </row>
     <row r="863" ht="12.75" customHeight="1">
-      <c r="A863" s="30"/>
-      <c r="B863" s="30"/>
-      <c r="C863" s="30"/>
+      <c r="A863" s="29"/>
+      <c r="B863" s="29"/>
+      <c r="C863" s="29"/>
     </row>
     <row r="864" ht="12.75" customHeight="1">
-      <c r="A864" s="30"/>
-      <c r="B864" s="30"/>
-      <c r="C864" s="30"/>
+      <c r="A864" s="29"/>
+      <c r="B864" s="29"/>
+      <c r="C864" s="29"/>
     </row>
     <row r="865" ht="12.75" customHeight="1">
-      <c r="A865" s="30"/>
-      <c r="B865" s="30"/>
-      <c r="C865" s="30"/>
+      <c r="A865" s="29"/>
+      <c r="B865" s="29"/>
+      <c r="C865" s="29"/>
     </row>
     <row r="866" ht="12.75" customHeight="1">
-      <c r="A866" s="30"/>
-      <c r="B866" s="30"/>
-      <c r="C866" s="30"/>
+      <c r="A866" s="29"/>
+      <c r="B866" s="29"/>
+      <c r="C866" s="29"/>
     </row>
     <row r="867" ht="12.75" customHeight="1">
-      <c r="A867" s="30"/>
-      <c r="B867" s="30"/>
-      <c r="C867" s="30"/>
+      <c r="A867" s="29"/>
+      <c r="B867" s="29"/>
+      <c r="C867" s="29"/>
     </row>
     <row r="868" ht="12.75" customHeight="1">
-      <c r="A868" s="30"/>
-      <c r="B868" s="30"/>
-      <c r="C868" s="30"/>
+      <c r="A868" s="29"/>
+      <c r="B868" s="29"/>
+      <c r="C868" s="29"/>
     </row>
     <row r="869" ht="12.75" customHeight="1">
-      <c r="A869" s="30"/>
-      <c r="B869" s="30"/>
-      <c r="C869" s="30"/>
+      <c r="A869" s="29"/>
+      <c r="B869" s="29"/>
+      <c r="C869" s="29"/>
     </row>
     <row r="870" ht="12.75" customHeight="1">
-      <c r="A870" s="30"/>
-      <c r="B870" s="30"/>
-      <c r="C870" s="30"/>
+      <c r="A870" s="29"/>
+      <c r="B870" s="29"/>
+      <c r="C870" s="29"/>
     </row>
     <row r="871" ht="12.75" customHeight="1">
-      <c r="A871" s="30"/>
-      <c r="B871" s="30"/>
-      <c r="C871" s="30"/>
+      <c r="A871" s="29"/>
+      <c r="B871" s="29"/>
+      <c r="C871" s="29"/>
     </row>
     <row r="872" ht="12.75" customHeight="1">
-      <c r="A872" s="30"/>
-      <c r="B872" s="30"/>
-      <c r="C872" s="30"/>
+      <c r="A872" s="29"/>
+      <c r="B872" s="29"/>
+      <c r="C872" s="29"/>
     </row>
     <row r="873" ht="12.75" customHeight="1">
-      <c r="A873" s="30"/>
-      <c r="B873" s="30"/>
-      <c r="C873" s="30"/>
+      <c r="A873" s="29"/>
+      <c r="B873" s="29"/>
+      <c r="C873" s="29"/>
     </row>
     <row r="874" ht="12.75" customHeight="1">
-      <c r="A874" s="30"/>
-      <c r="B874" s="30"/>
-      <c r="C874" s="30"/>
+      <c r="A874" s="29"/>
+      <c r="B874" s="29"/>
+      <c r="C874" s="29"/>
     </row>
     <row r="875" ht="12.75" customHeight="1">
-      <c r="A875" s="30"/>
-      <c r="B875" s="30"/>
-      <c r="C875" s="30"/>
+      <c r="A875" s="29"/>
+      <c r="B875" s="29"/>
+      <c r="C875" s="29"/>
     </row>
     <row r="876" ht="12.75" customHeight="1">
-      <c r="A876" s="30"/>
-      <c r="B876" s="30"/>
-      <c r="C876" s="30"/>
+      <c r="A876" s="29"/>
+      <c r="B876" s="29"/>
+      <c r="C876" s="29"/>
     </row>
     <row r="877" ht="12.75" customHeight="1">
-      <c r="A877" s="30"/>
-      <c r="B877" s="30"/>
-      <c r="C877" s="30"/>
+      <c r="A877" s="29"/>
+      <c r="B877" s="29"/>
+      <c r="C877" s="29"/>
     </row>
     <row r="878" ht="12.75" customHeight="1">
-      <c r="A878" s="30"/>
-      <c r="B878" s="30"/>
-      <c r="C878" s="30"/>
+      <c r="A878" s="29"/>
+      <c r="B878" s="29"/>
+      <c r="C878" s="29"/>
     </row>
     <row r="879" ht="12.75" customHeight="1">
-      <c r="A879" s="30"/>
-      <c r="B879" s="30"/>
-      <c r="C879" s="30"/>
+      <c r="A879" s="29"/>
+      <c r="B879" s="29"/>
+      <c r="C879" s="29"/>
     </row>
     <row r="880" ht="12.75" customHeight="1">
-      <c r="A880" s="30"/>
-      <c r="B880" s="30"/>
-      <c r="C880" s="30"/>
+      <c r="A880" s="29"/>
+      <c r="B880" s="29"/>
+      <c r="C880" s="29"/>
     </row>
     <row r="881" ht="12.75" customHeight="1">
-      <c r="A881" s="30"/>
-      <c r="B881" s="30"/>
-      <c r="C881" s="30"/>
+      <c r="A881" s="29"/>
+      <c r="B881" s="29"/>
+      <c r="C881" s="29"/>
     </row>
     <row r="882" ht="12.75" customHeight="1">
-      <c r="A882" s="30"/>
-      <c r="B882" s="30"/>
-      <c r="C882" s="30"/>
+      <c r="A882" s="29"/>
+      <c r="B882" s="29"/>
+      <c r="C882" s="29"/>
     </row>
     <row r="883" ht="12.75" customHeight="1">
-      <c r="A883" s="30"/>
-      <c r="B883" s="30"/>
-      <c r="C883" s="30"/>
+      <c r="A883" s="29"/>
+      <c r="B883" s="29"/>
+      <c r="C883" s="29"/>
     </row>
     <row r="884" ht="12.75" customHeight="1">
-      <c r="A884" s="30"/>
-      <c r="B884" s="30"/>
-      <c r="C884" s="30"/>
+      <c r="A884" s="29"/>
+      <c r="B884" s="29"/>
+      <c r="C884" s="29"/>
     </row>
     <row r="885" ht="12.75" customHeight="1">
-      <c r="A885" s="30"/>
-      <c r="B885" s="30"/>
-      <c r="C885" s="30"/>
+      <c r="A885" s="29"/>
+      <c r="B885" s="29"/>
+      <c r="C885" s="29"/>
     </row>
     <row r="886" ht="12.75" customHeight="1">
-      <c r="A886" s="30"/>
-      <c r="B886" s="30"/>
-      <c r="C886" s="30"/>
+      <c r="A886" s="29"/>
+      <c r="B886" s="29"/>
+      <c r="C886" s="29"/>
     </row>
     <row r="887" ht="12.75" customHeight="1">
-      <c r="A887" s="30"/>
-      <c r="B887" s="30"/>
-      <c r="C887" s="30"/>
+      <c r="A887" s="29"/>
+      <c r="B887" s="29"/>
+      <c r="C887" s="29"/>
     </row>
     <row r="888" ht="12.75" customHeight="1">
-      <c r="A888" s="30"/>
-      <c r="B888" s="30"/>
-      <c r="C888" s="30"/>
+      <c r="A888" s="29"/>
+      <c r="B888" s="29"/>
+      <c r="C888" s="29"/>
     </row>
     <row r="889" ht="12.75" customHeight="1">
-      <c r="A889" s="30"/>
-      <c r="B889" s="30"/>
-      <c r="C889" s="30"/>
+      <c r="A889" s="29"/>
+      <c r="B889" s="29"/>
+      <c r="C889" s="29"/>
     </row>
     <row r="890" ht="12.75" customHeight="1">
-      <c r="A890" s="30"/>
-      <c r="B890" s="30"/>
-      <c r="C890" s="30"/>
+      <c r="A890" s="29"/>
+      <c r="B890" s="29"/>
+      <c r="C890" s="29"/>
     </row>
     <row r="891" ht="12.75" customHeight="1">
-      <c r="A891" s="30"/>
-      <c r="B891" s="30"/>
-      <c r="C891" s="30"/>
+      <c r="A891" s="29"/>
+      <c r="B891" s="29"/>
+      <c r="C891" s="29"/>
     </row>
     <row r="892" ht="12.75" customHeight="1">
-      <c r="A892" s="30"/>
-      <c r="B892" s="30"/>
-      <c r="C892" s="30"/>
+      <c r="A892" s="29"/>
+      <c r="B892" s="29"/>
+      <c r="C892" s="29"/>
     </row>
     <row r="893" ht="12.75" customHeight="1">
-      <c r="A893" s="30"/>
-      <c r="B893" s="30"/>
-      <c r="C893" s="30"/>
+      <c r="A893" s="29"/>
+      <c r="B893" s="29"/>
+      <c r="C893" s="29"/>
     </row>
     <row r="894" ht="12.75" customHeight="1">
-      <c r="A894" s="30"/>
-      <c r="B894" s="30"/>
-      <c r="C894" s="30"/>
+      <c r="A894" s="29"/>
+      <c r="B894" s="29"/>
+      <c r="C894" s="29"/>
     </row>
     <row r="895" ht="12.75" customHeight="1">
-      <c r="A895" s="30"/>
-      <c r="B895" s="30"/>
-      <c r="C895" s="30"/>
+      <c r="A895" s="29"/>
+      <c r="B895" s="29"/>
+      <c r="C895" s="29"/>
     </row>
     <row r="896" ht="12.75" customHeight="1">
-      <c r="A896" s="30"/>
-      <c r="B896" s="30"/>
-      <c r="C896" s="30"/>
+      <c r="A896" s="29"/>
+      <c r="B896" s="29"/>
+      <c r="C896" s="29"/>
     </row>
     <row r="897" ht="12.75" customHeight="1">
-      <c r="A897" s="30"/>
-      <c r="B897" s="30"/>
-      <c r="C897" s="30"/>
+      <c r="A897" s="29"/>
+      <c r="B897" s="29"/>
+      <c r="C897" s="29"/>
     </row>
     <row r="898" ht="12.75" customHeight="1">
-      <c r="A898" s="30"/>
-      <c r="B898" s="30"/>
-      <c r="C898" s="30"/>
+      <c r="A898" s="29"/>
+      <c r="B898" s="29"/>
+      <c r="C898" s="29"/>
     </row>
     <row r="899" ht="12.75" customHeight="1">
-      <c r="A899" s="30"/>
-      <c r="B899" s="30"/>
-      <c r="C899" s="30"/>
+      <c r="A899" s="29"/>
+      <c r="B899" s="29"/>
+      <c r="C899" s="29"/>
     </row>
     <row r="900" ht="12.75" customHeight="1">
-      <c r="A900" s="30"/>
-      <c r="B900" s="30"/>
-      <c r="C900" s="30"/>
+      <c r="A900" s="29"/>
+      <c r="B900" s="29"/>
+      <c r="C900" s="29"/>
     </row>
     <row r="901" ht="12.75" customHeight="1">
-      <c r="A901" s="30"/>
-      <c r="B901" s="30"/>
-      <c r="C901" s="30"/>
+      <c r="A901" s="29"/>
+      <c r="B901" s="29"/>
+      <c r="C901" s="29"/>
     </row>
     <row r="902" ht="12.75" customHeight="1">
-      <c r="A902" s="30"/>
-      <c r="B902" s="30"/>
-      <c r="C902" s="30"/>
+      <c r="A902" s="29"/>
+      <c r="B902" s="29"/>
+      <c r="C902" s="29"/>
     </row>
     <row r="903" ht="12.75" customHeight="1">
-      <c r="A903" s="30"/>
-      <c r="B903" s="30"/>
-      <c r="C903" s="30"/>
+      <c r="A903" s="29"/>
+      <c r="B903" s="29"/>
+      <c r="C903" s="29"/>
     </row>
     <row r="904" ht="12.75" customHeight="1">
-      <c r="A904" s="30"/>
-      <c r="B904" s="30"/>
-      <c r="C904" s="30"/>
+      <c r="A904" s="29"/>
+      <c r="B904" s="29"/>
+      <c r="C904" s="29"/>
     </row>
     <row r="905" ht="12.75" customHeight="1">
-      <c r="A905" s="30"/>
-      <c r="B905" s="30"/>
-      <c r="C905" s="30"/>
+      <c r="A905" s="29"/>
+      <c r="B905" s="29"/>
+      <c r="C905" s="29"/>
     </row>
     <row r="906" ht="12.75" customHeight="1">
-      <c r="A906" s="30"/>
-      <c r="B906" s="30"/>
-      <c r="C906" s="30"/>
+      <c r="A906" s="29"/>
+      <c r="B906" s="29"/>
+      <c r="C906" s="29"/>
     </row>
     <row r="907" ht="12.75" customHeight="1">
-      <c r="A907" s="30"/>
-      <c r="B907" s="30"/>
-      <c r="C907" s="30"/>
+      <c r="A907" s="29"/>
+      <c r="B907" s="29"/>
+      <c r="C907" s="29"/>
     </row>
     <row r="908" ht="12.75" customHeight="1">
-      <c r="A908" s="30"/>
-      <c r="B908" s="30"/>
-      <c r="C908" s="30"/>
+      <c r="A908" s="29"/>
+      <c r="B908" s="29"/>
+      <c r="C908" s="29"/>
     </row>
     <row r="909" ht="12.75" customHeight="1">
-      <c r="A909" s="30"/>
-      <c r="B909" s="30"/>
-      <c r="C909" s="30"/>
+      <c r="A909" s="29"/>
+      <c r="B909" s="29"/>
+      <c r="C909" s="29"/>
     </row>
     <row r="910" ht="12.75" customHeight="1">
-      <c r="A910" s="30"/>
-      <c r="B910" s="30"/>
-      <c r="C910" s="30"/>
+      <c r="A910" s="29"/>
+      <c r="B910" s="29"/>
+      <c r="C910" s="29"/>
     </row>
     <row r="911" ht="12.75" customHeight="1">
-      <c r="A911" s="30"/>
-      <c r="B911" s="30"/>
-      <c r="C911" s="30"/>
+      <c r="A911" s="29"/>
+      <c r="B911" s="29"/>
+      <c r="C911" s="29"/>
     </row>
     <row r="912" ht="12.75" customHeight="1">
-      <c r="A912" s="30"/>
-      <c r="B912" s="30"/>
-      <c r="C912" s="30"/>
+      <c r="A912" s="29"/>
+      <c r="B912" s="29"/>
+      <c r="C912" s="29"/>
     </row>
     <row r="913" ht="12.75" customHeight="1">
-      <c r="A913" s="30"/>
-      <c r="B913" s="30"/>
-      <c r="C913" s="30"/>
+      <c r="A913" s="29"/>
+      <c r="B913" s="29"/>
+      <c r="C913" s="29"/>
     </row>
     <row r="914" ht="12.75" customHeight="1">
-      <c r="A914" s="30"/>
-      <c r="B914" s="30"/>
-      <c r="C914" s="30"/>
+      <c r="A914" s="29"/>
+      <c r="B914" s="29"/>
+      <c r="C914" s="29"/>
     </row>
     <row r="915" ht="12.75" customHeight="1">
-      <c r="A915" s="30"/>
-      <c r="B915" s="30"/>
-      <c r="C915" s="30"/>
+      <c r="A915" s="29"/>
+      <c r="B915" s="29"/>
+      <c r="C915" s="29"/>
     </row>
     <row r="916" ht="12.75" customHeight="1">
-      <c r="A916" s="30"/>
-      <c r="B916" s="30"/>
-      <c r="C916" s="30"/>
+      <c r="A916" s="29"/>
+      <c r="B916" s="29"/>
+      <c r="C916" s="29"/>
     </row>
     <row r="917" ht="12.75" customHeight="1">
-      <c r="A917" s="30"/>
-      <c r="B917" s="30"/>
-      <c r="C917" s="30"/>
+      <c r="A917" s="29"/>
+      <c r="B917" s="29"/>
+      <c r="C917" s="29"/>
     </row>
     <row r="918" ht="12.75" customHeight="1">
-      <c r="A918" s="30"/>
-      <c r="B918" s="30"/>
-      <c r="C918" s="30"/>
+      <c r="A918" s="29"/>
+      <c r="B918" s="29"/>
+      <c r="C918" s="29"/>
     </row>
     <row r="919" ht="12.75" customHeight="1">
-      <c r="A919" s="30"/>
-      <c r="B919" s="30"/>
-      <c r="C919" s="30"/>
+      <c r="A919" s="29"/>
+      <c r="B919" s="29"/>
+      <c r="C919" s="29"/>
     </row>
     <row r="920" ht="12.75" customHeight="1">
-      <c r="A920" s="30"/>
-      <c r="B920" s="30"/>
-      <c r="C920" s="30"/>
+      <c r="A920" s="29"/>
+      <c r="B920" s="29"/>
+      <c r="C920" s="29"/>
     </row>
     <row r="921" ht="12.75" customHeight="1">
-      <c r="A921" s="30"/>
-      <c r="B921" s="30"/>
-      <c r="C921" s="30"/>
+      <c r="A921" s="29"/>
+      <c r="B921" s="29"/>
+      <c r="C921" s="29"/>
     </row>
     <row r="922" ht="12.75" customHeight="1">
-      <c r="A922" s="30"/>
-      <c r="B922" s="30"/>
-      <c r="C922" s="30"/>
+      <c r="A922" s="29"/>
+      <c r="B922" s="29"/>
+      <c r="C922" s="29"/>
     </row>
     <row r="923" ht="12.75" customHeight="1">
-      <c r="A923" s="30"/>
-      <c r="B923" s="30"/>
-      <c r="C923" s="30"/>
+      <c r="A923" s="29"/>
+      <c r="B923" s="29"/>
+      <c r="C923" s="29"/>
     </row>
     <row r="924" ht="12.75" customHeight="1">
-      <c r="A924" s="30"/>
-      <c r="B924" s="30"/>
-      <c r="C924" s="30"/>
+      <c r="A924" s="29"/>
+      <c r="B924" s="29"/>
+      <c r="C924" s="29"/>
     </row>
     <row r="925" ht="12.75" customHeight="1">
-      <c r="A925" s="30"/>
-      <c r="B925" s="30"/>
-      <c r="C925" s="30"/>
+      <c r="A925" s="29"/>
+      <c r="B925" s="29"/>
+      <c r="C925" s="29"/>
     </row>
     <row r="926" ht="12.75" customHeight="1">
-      <c r="A926" s="30"/>
-      <c r="B926" s="30"/>
-      <c r="C926" s="30"/>
+      <c r="A926" s="29"/>
+      <c r="B926" s="29"/>
+      <c r="C926" s="29"/>
     </row>
     <row r="927" ht="12.75" customHeight="1">
-      <c r="A927" s="30"/>
-      <c r="B927" s="30"/>
-      <c r="C927" s="30"/>
+      <c r="A927" s="29"/>
+      <c r="B927" s="29"/>
+      <c r="C927" s="29"/>
     </row>
     <row r="928" ht="12.75" customHeight="1">
-      <c r="A928" s="30"/>
-      <c r="B928" s="30"/>
-      <c r="C928" s="30"/>
+      <c r="A928" s="29"/>
+      <c r="B928" s="29"/>
+      <c r="C928" s="29"/>
     </row>
     <row r="929" ht="12.75" customHeight="1">
-      <c r="A929" s="30"/>
-      <c r="B929" s="30"/>
-      <c r="C929" s="30"/>
+      <c r="A929" s="29"/>
+      <c r="B929" s="29"/>
+      <c r="C929" s="29"/>
     </row>
     <row r="930" ht="12.75" customHeight="1">
-      <c r="A930" s="30"/>
-      <c r="B930" s="30"/>
-      <c r="C930" s="30"/>
+      <c r="A930" s="29"/>
+      <c r="B930" s="29"/>
+      <c r="C930" s="29"/>
     </row>
     <row r="931" ht="12.75" customHeight="1">
-      <c r="A931" s="30"/>
-      <c r="B931" s="30"/>
-      <c r="C931" s="30"/>
+      <c r="A931" s="29"/>
+      <c r="B931" s="29"/>
+      <c r="C931" s="29"/>
     </row>
     <row r="932" ht="12.75" customHeight="1">
-      <c r="A932" s="30"/>
-      <c r="B932" s="30"/>
-      <c r="C932" s="30"/>
+      <c r="A932" s="29"/>
+      <c r="B932" s="29"/>
+      <c r="C932" s="29"/>
     </row>
     <row r="933" ht="12.75" customHeight="1">
-      <c r="A933" s="30"/>
-      <c r="B933" s="30"/>
-      <c r="C933" s="30"/>
+      <c r="A933" s="29"/>
+      <c r="B933" s="29"/>
+      <c r="C933" s="29"/>
     </row>
     <row r="934" ht="12.75" customHeight="1">
-      <c r="A934" s="30"/>
-      <c r="B934" s="30"/>
-      <c r="C934" s="30"/>
+      <c r="A934" s="29"/>
+      <c r="B934" s="29"/>
+      <c r="C934" s="29"/>
     </row>
     <row r="935" ht="12.75" customHeight="1">
-      <c r="A935" s="30"/>
-      <c r="B935" s="30"/>
-      <c r="C935" s="30"/>
+      <c r="A935" s="29"/>
+      <c r="B935" s="29"/>
+      <c r="C935" s="29"/>
     </row>
     <row r="936" ht="12.75" customHeight="1">
-      <c r="A936" s="30"/>
-      <c r="B936" s="30"/>
-      <c r="C936" s="30"/>
+      <c r="A936" s="29"/>
+      <c r="B936" s="29"/>
+      <c r="C936" s="29"/>
     </row>
     <row r="937" ht="12.75" customHeight="1">
-      <c r="A937" s="30"/>
-      <c r="B937" s="30"/>
-      <c r="C937" s="30"/>
+      <c r="A937" s="29"/>
+      <c r="B937" s="29"/>
+      <c r="C937" s="29"/>
     </row>
     <row r="938" ht="12.75" customHeight="1">
-      <c r="A938" s="30"/>
-      <c r="B938" s="30"/>
-      <c r="C938" s="30"/>
+      <c r="A938" s="29"/>
+      <c r="B938" s="29"/>
+      <c r="C938" s="29"/>
     </row>
     <row r="939" ht="12.75" customHeight="1">
-      <c r="A939" s="30"/>
-      <c r="B939" s="30"/>
-      <c r="C939" s="30"/>
+      <c r="A939" s="29"/>
+      <c r="B939" s="29"/>
+      <c r="C939" s="29"/>
     </row>
     <row r="940" ht="12.75" customHeight="1">
-      <c r="A940" s="30"/>
-      <c r="B940" s="30"/>
-      <c r="C940" s="30"/>
+      <c r="A940" s="29"/>
+      <c r="B940" s="29"/>
+      <c r="C940" s="29"/>
     </row>
     <row r="941" ht="12.75" customHeight="1">
-      <c r="A941" s="30"/>
-      <c r="B941" s="30"/>
-      <c r="C941" s="30"/>
+      <c r="A941" s="29"/>
+      <c r="B941" s="29"/>
+      <c r="C941" s="29"/>
     </row>
     <row r="942" ht="12.75" customHeight="1">
-      <c r="A942" s="30"/>
-      <c r="B942" s="30"/>
-      <c r="C942" s="30"/>
+      <c r="A942" s="29"/>
+      <c r="B942" s="29"/>
+      <c r="C942" s="29"/>
     </row>
     <row r="943" ht="12.75" customHeight="1">
-      <c r="A943" s="30"/>
-      <c r="B943" s="30"/>
-      <c r="C943" s="30"/>
+      <c r="A943" s="29"/>
+      <c r="B943" s="29"/>
+      <c r="C943" s="29"/>
     </row>
     <row r="944" ht="12.75" customHeight="1">
-      <c r="A944" s="30"/>
-      <c r="B944" s="30"/>
-      <c r="C944" s="30"/>
+      <c r="A944" s="29"/>
+      <c r="B944" s="29"/>
+      <c r="C944" s="29"/>
     </row>
     <row r="945" ht="12.75" customHeight="1">
-      <c r="A945" s="30"/>
-      <c r="B945" s="30"/>
-      <c r="C945" s="30"/>
+      <c r="A945" s="29"/>
+      <c r="B945" s="29"/>
+      <c r="C945" s="29"/>
     </row>
     <row r="946" ht="12.75" customHeight="1">
-      <c r="A946" s="30"/>
-      <c r="B946" s="30"/>
-      <c r="C946" s="30"/>
+      <c r="A946" s="29"/>
+      <c r="B946" s="29"/>
+      <c r="C946" s="29"/>
     </row>
     <row r="947" ht="12.75" customHeight="1">
-      <c r="A947" s="30"/>
-      <c r="B947" s="30"/>
-      <c r="C947" s="30"/>
+      <c r="A947" s="29"/>
+      <c r="B947" s="29"/>
+      <c r="C947" s="29"/>
     </row>
     <row r="948" ht="12.75" customHeight="1">
-      <c r="A948" s="30"/>
-      <c r="B948" s="30"/>
-      <c r="C948" s="30"/>
+      <c r="A948" s="29"/>
+      <c r="B948" s="29"/>
+      <c r="C948" s="29"/>
     </row>
     <row r="949" ht="12.75" customHeight="1">
-      <c r="A949" s="30"/>
-      <c r="B949" s="30"/>
-      <c r="C949" s="30"/>
+      <c r="A949" s="29"/>
+      <c r="B949" s="29"/>
+      <c r="C949" s="29"/>
     </row>
     <row r="950" ht="12.75" customHeight="1">
-      <c r="A950" s="30"/>
-      <c r="B950" s="30"/>
-      <c r="C950" s="30"/>
+      <c r="A950" s="29"/>
+      <c r="B950" s="29"/>
+      <c r="C950" s="29"/>
     </row>
     <row r="951" ht="12.75" customHeight="1">
-      <c r="A951" s="30"/>
-      <c r="B951" s="30"/>
-      <c r="C951" s="30"/>
+      <c r="A951" s="29"/>
+      <c r="B951" s="29"/>
+      <c r="C951" s="29"/>
     </row>
     <row r="952" ht="12.75" customHeight="1">
-      <c r="A952" s="30"/>
-      <c r="B952" s="30"/>
-      <c r="C952" s="30"/>
+      <c r="A952" s="29"/>
+      <c r="B952" s="29"/>
+      <c r="C952" s="29"/>
     </row>
     <row r="953" ht="12.75" customHeight="1">
-      <c r="A953" s="30"/>
-      <c r="B953" s="30"/>
-      <c r="C953" s="30"/>
+      <c r="A953" s="29"/>
+      <c r="B953" s="29"/>
+      <c r="C953" s="29"/>
     </row>
     <row r="954" ht="12.75" customHeight="1">
-      <c r="A954" s="30"/>
-      <c r="B954" s="30"/>
-      <c r="C954" s="30"/>
+      <c r="A954" s="29"/>
+      <c r="B954" s="29"/>
+      <c r="C954" s="29"/>
     </row>
     <row r="955" ht="12.75" customHeight="1">
-      <c r="A955" s="30"/>
-      <c r="B955" s="30"/>
-      <c r="C955" s="30"/>
+      <c r="A955" s="29"/>
+      <c r="B955" s="29"/>
+      <c r="C955" s="29"/>
     </row>
     <row r="956" ht="12.75" customHeight="1">
-      <c r="A956" s="30"/>
-      <c r="B956" s="30"/>
-      <c r="C956" s="30"/>
+      <c r="A956" s="29"/>
+      <c r="B956" s="29"/>
+      <c r="C956" s="29"/>
     </row>
     <row r="957" ht="12.75" customHeight="1">
-      <c r="A957" s="30"/>
-      <c r="B957" s="30"/>
-      <c r="C957" s="30"/>
+      <c r="A957" s="29"/>
+      <c r="B957" s="29"/>
+      <c r="C957" s="29"/>
     </row>
     <row r="958" ht="12.75" customHeight="1">
-      <c r="A958" s="30"/>
-      <c r="B958" s="30"/>
-      <c r="C958" s="30"/>
+      <c r="A958" s="29"/>
+      <c r="B958" s="29"/>
+      <c r="C958" s="29"/>
     </row>
     <row r="959" ht="12.75" customHeight="1">
-      <c r="A959" s="30"/>
-      <c r="B959" s="30"/>
-      <c r="C959" s="30"/>
+      <c r="A959" s="29"/>
+      <c r="B959" s="29"/>
+      <c r="C959" s="29"/>
     </row>
     <row r="960" ht="12.75" customHeight="1">
-      <c r="A960" s="30"/>
-      <c r="B960" s="30"/>
-      <c r="C960" s="30"/>
+      <c r="A960" s="29"/>
+      <c r="B960" s="29"/>
+      <c r="C960" s="29"/>
     </row>
     <row r="961" ht="12.75" customHeight="1">
-      <c r="A961" s="30"/>
-      <c r="B961" s="30"/>
-      <c r="C961" s="30"/>
+      <c r="A961" s="29"/>
+      <c r="B961" s="29"/>
+      <c r="C961" s="29"/>
     </row>
     <row r="962" ht="12.75" customHeight="1">
-      <c r="A962" s="30"/>
-      <c r="B962" s="30"/>
-      <c r="C962" s="30"/>
+      <c r="A962" s="29"/>
+      <c r="B962" s="29"/>
+      <c r="C962" s="29"/>
     </row>
     <row r="963" ht="12.75" customHeight="1">
-      <c r="A963" s="30"/>
-      <c r="B963" s="30"/>
-      <c r="C963" s="30"/>
+      <c r="A963" s="29"/>
+      <c r="B963" s="29"/>
+      <c r="C963" s="29"/>
     </row>
     <row r="964" ht="12.75" customHeight="1">
-      <c r="A964" s="30"/>
-      <c r="B964" s="30"/>
-      <c r="C964" s="30"/>
+      <c r="A964" s="29"/>
+      <c r="B964" s="29"/>
+      <c r="C964" s="29"/>
     </row>
     <row r="965" ht="12.75" customHeight="1">
-      <c r="A965" s="30"/>
-      <c r="B965" s="30"/>
-      <c r="C965" s="30"/>
+      <c r="A965" s="29"/>
+      <c r="B965" s="29"/>
+      <c r="C965" s="29"/>
     </row>
     <row r="966" ht="12.75" customHeight="1">
-      <c r="A966" s="30"/>
-      <c r="B966" s="30"/>
-      <c r="C966" s="30"/>
+      <c r="A966" s="29"/>
+      <c r="B966" s="29"/>
+      <c r="C966" s="29"/>
     </row>
     <row r="967" ht="12.75" customHeight="1">
-      <c r="A967" s="30"/>
-      <c r="B967" s="30"/>
-      <c r="C967" s="30"/>
+      <c r="A967" s="29"/>
+      <c r="B967" s="29"/>
+      <c r="C967" s="29"/>
     </row>
     <row r="968" ht="12.75" customHeight="1">
-      <c r="A968" s="30"/>
-      <c r="B968" s="30"/>
-      <c r="C968" s="30"/>
+      <c r="A968" s="29"/>
+      <c r="B968" s="29"/>
+      <c r="C968" s="29"/>
     </row>
     <row r="969" ht="12.75" customHeight="1">
-      <c r="A969" s="30"/>
-      <c r="B969" s="30"/>
-      <c r="C969" s="30"/>
+      <c r="A969" s="29"/>
+      <c r="B969" s="29"/>
+      <c r="C969" s="29"/>
     </row>
     <row r="970" ht="12.75" customHeight="1">
-      <c r="A970" s="30"/>
-      <c r="B970" s="30"/>
-      <c r="C970" s="30"/>
+      <c r="A970" s="29"/>
+      <c r="B970" s="29"/>
+      <c r="C970" s="29"/>
     </row>
     <row r="971" ht="12.75" customHeight="1">
-      <c r="A971" s="30"/>
-      <c r="B971" s="30"/>
-      <c r="C971" s="30"/>
+      <c r="A971" s="29"/>
+      <c r="B971" s="29"/>
+      <c r="C971" s="29"/>
     </row>
     <row r="972" ht="12.75" customHeight="1">
-      <c r="A972" s="30"/>
-      <c r="B972" s="30"/>
-      <c r="C972" s="30"/>
+      <c r="A972" s="29"/>
+      <c r="B972" s="29"/>
+      <c r="C972" s="29"/>
     </row>
     <row r="973" ht="12.75" customHeight="1">
-      <c r="A973" s="30"/>
-      <c r="B973" s="30"/>
-      <c r="C973" s="30"/>
+      <c r="A973" s="29"/>
+      <c r="B973" s="29"/>
+      <c r="C973" s="29"/>
     </row>
     <row r="974" ht="12.75" customHeight="1">
-      <c r="A974" s="30"/>
-      <c r="B974" s="30"/>
-      <c r="C974" s="30"/>
+      <c r="A974" s="29"/>
+      <c r="B974" s="29"/>
+      <c r="C974" s="29"/>
     </row>
     <row r="975" ht="12.75" customHeight="1">
-      <c r="A975" s="30"/>
-      <c r="B975" s="30"/>
-      <c r="C975" s="30"/>
+      <c r="A975" s="29"/>
+      <c r="B975" s="29"/>
+      <c r="C975" s="29"/>
     </row>
     <row r="976" ht="12.75" customHeight="1">
-      <c r="A976" s="30"/>
-      <c r="B976" s="30"/>
-      <c r="C976" s="30"/>
+      <c r="A976" s="29"/>
+      <c r="B976" s="29"/>
+      <c r="C976" s="29"/>
     </row>
     <row r="977" ht="12.75" customHeight="1">
-      <c r="A977" s="30"/>
-      <c r="B977" s="30"/>
-      <c r="C977" s="30"/>
+      <c r="A977" s="29"/>
+      <c r="B977" s="29"/>
+      <c r="C977" s="29"/>
     </row>
     <row r="978" ht="12.75" customHeight="1">
-      <c r="A978" s="30"/>
-      <c r="B978" s="30"/>
-      <c r="C978" s="30"/>
+      <c r="A978" s="29"/>
+      <c r="B978" s="29"/>
+      <c r="C978" s="29"/>
     </row>
     <row r="979" ht="12.75" customHeight="1">
-      <c r="A979" s="30"/>
-      <c r="B979" s="30"/>
-      <c r="C979" s="30"/>
+      <c r="A979" s="29"/>
+      <c r="B979" s="29"/>
+      <c r="C979" s="29"/>
     </row>
     <row r="980" ht="12.75" customHeight="1">
-      <c r="A980" s="30"/>
-      <c r="B980" s="30"/>
-      <c r="C980" s="30"/>
+      <c r="A980" s="29"/>
+      <c r="B980" s="29"/>
+      <c r="C980" s="29"/>
     </row>
     <row r="981" ht="12.75" customHeight="1">
-      <c r="A981" s="30"/>
-      <c r="B981" s="30"/>
-      <c r="C981" s="30"/>
+      <c r="A981" s="29"/>
+      <c r="B981" s="29"/>
+      <c r="C981" s="29"/>
     </row>
     <row r="982" ht="12.75" customHeight="1">
-      <c r="A982" s="30"/>
-      <c r="B982" s="30"/>
-      <c r="C982" s="30"/>
+      <c r="A982" s="29"/>
+      <c r="B982" s="29"/>
+      <c r="C982" s="29"/>
     </row>
     <row r="983" ht="12.75" customHeight="1">
-      <c r="A983" s="30"/>
-      <c r="B983" s="30"/>
-      <c r="C983" s="30"/>
+      <c r="A983" s="29"/>
+      <c r="B983" s="29"/>
+      <c r="C983" s="29"/>
     </row>
     <row r="984" ht="12.75" customHeight="1">
-      <c r="A984" s="30"/>
-      <c r="B984" s="30"/>
-      <c r="C984" s="30"/>
+      <c r="A984" s="29"/>
+      <c r="B984" s="29"/>
+      <c r="C984" s="29"/>
     </row>
     <row r="985" ht="12.75" customHeight="1">
-      <c r="A985" s="30"/>
-      <c r="B985" s="30"/>
-      <c r="C985" s="30"/>
+      <c r="A985" s="29"/>
+      <c r="B985" s="29"/>
+      <c r="C985" s="29"/>
     </row>
     <row r="986" ht="12.75" customHeight="1">
-      <c r="A986" s="30"/>
-      <c r="B986" s="30"/>
-      <c r="C986" s="30"/>
+      <c r="A986" s="29"/>
+      <c r="B986" s="29"/>
+      <c r="C986" s="29"/>
     </row>
     <row r="987" ht="12.75" customHeight="1">
-      <c r="A987" s="30"/>
-      <c r="B987" s="30"/>
-      <c r="C987" s="30"/>
+      <c r="A987" s="29"/>
+      <c r="B987" s="29"/>
+      <c r="C987" s="29"/>
     </row>
     <row r="988" ht="12.75" customHeight="1">
-      <c r="A988" s="30"/>
-      <c r="B988" s="30"/>
-      <c r="C988" s="30"/>
+      <c r="A988" s="29"/>
+      <c r="B988" s="29"/>
+      <c r="C988" s="29"/>
     </row>
     <row r="989" ht="12.75" customHeight="1">
-      <c r="A989" s="30"/>
-      <c r="B989" s="30"/>
-      <c r="C989" s="30"/>
+      <c r="A989" s="29"/>
+      <c r="B989" s="29"/>
+      <c r="C989" s="29"/>
     </row>
     <row r="990" ht="12.75" customHeight="1">
-      <c r="A990" s="30"/>
-      <c r="B990" s="30"/>
-      <c r="C990" s="30"/>
+      <c r="A990" s="29"/>
+      <c r="B990" s="29"/>
+      <c r="C990" s="29"/>
     </row>
     <row r="991" ht="12.75" customHeight="1">
-      <c r="A991" s="30"/>
-      <c r="B991" s="30"/>
-      <c r="C991" s="30"/>
+      <c r="A991" s="29"/>
+      <c r="B991" s="29"/>
+      <c r="C991" s="29"/>
     </row>
     <row r="992" ht="12.75" customHeight="1">
-      <c r="A992" s="30"/>
-      <c r="B992" s="30"/>
-      <c r="C992" s="30"/>
+      <c r="A992" s="29"/>
+      <c r="B992" s="29"/>
+      <c r="C992" s="29"/>
     </row>
     <row r="993" ht="12.75" customHeight="1">
-      <c r="A993" s="30"/>
-      <c r="B993" s="30"/>
-      <c r="C993" s="30"/>
+      <c r="A993" s="29"/>
+      <c r="B993" s="29"/>
+      <c r="C993" s="29"/>
     </row>
     <row r="994" ht="12.75" customHeight="1">
-      <c r="A994" s="30"/>
-      <c r="B994" s="30"/>
-      <c r="C994" s="30"/>
+      <c r="A994" s="29"/>
+      <c r="B994" s="29"/>
+      <c r="C994" s="29"/>
     </row>
     <row r="995" ht="12.75" customHeight="1">
-      <c r="A995" s="30"/>
-      <c r="B995" s="30"/>
-      <c r="C995" s="30"/>
+      <c r="A995" s="29"/>
+      <c r="B995" s="29"/>
+      <c r="C995" s="29"/>
     </row>
     <row r="996" ht="12.75" customHeight="1">
-      <c r="A996" s="30"/>
-      <c r="B996" s="30"/>
-      <c r="C996" s="30"/>
+      <c r="A996" s="29"/>
+      <c r="B996" s="29"/>
+      <c r="C996" s="29"/>
     </row>
     <row r="997" ht="12.75" customHeight="1">
-      <c r="A997" s="30"/>
-      <c r="B997" s="30"/>
-      <c r="C997" s="30"/>
+      <c r="A997" s="29"/>
+      <c r="B997" s="29"/>
+      <c r="C997" s="29"/>
     </row>
     <row r="998" ht="12.75" customHeight="1">
-      <c r="A998" s="30"/>
-      <c r="B998" s="30"/>
-      <c r="C998" s="30"/>
+      <c r="A998" s="29"/>
+      <c r="B998" s="29"/>
+      <c r="C998" s="29"/>
     </row>
     <row r="999" ht="12.75" customHeight="1">
-      <c r="A999" s="30"/>
-      <c r="B999" s="30"/>
-      <c r="C999" s="30"/>
+      <c r="A999" s="29"/>
+      <c r="B999" s="29"/>
+      <c r="C999" s="29"/>
     </row>
     <row r="1000" ht="12.75" customHeight="1">
-      <c r="A1000" s="30"/>
-      <c r="B1000" s="30"/>
-      <c r="C1000" s="30"/>
+      <c r="A1000" s="29"/>
+      <c r="B1000" s="29"/>
+      <c r="C1000" s="29"/>
     </row>
     <row r="1001" ht="12.75" customHeight="1">
-      <c r="A1001" s="30"/>
-      <c r="B1001" s="30"/>
-      <c r="C1001" s="30"/>
+      <c r="A1001" s="29"/>
+      <c r="B1001" s="29"/>
+      <c r="C1001" s="29"/>
     </row>
   </sheetData>
   <mergeCells count="12">
@@ -6905,84 +6897,84 @@
   </cols>
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
-      <c r="B1" s="31" t="s">
-        <v>103</v>
+      <c r="B1" s="30" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="2" ht="12.75" customHeight="1"/>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="B4" s="31" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="32" t="s">
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="B5" s="31" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="B5" s="32" t="s">
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="B6" s="31" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="B6" s="32" t="s">
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="B7" s="31" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="B7" s="32" t="s">
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="B8" s="31" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="B8" s="32" t="s">
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="B9" s="31" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="B9" s="32" t="s">
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="B10" s="31" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="B10" s="32" t="s">
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="B11" s="31" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="B11" s="32" t="s">
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="B12" s="31" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="B12" s="32" t="s">
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="B13" s="31" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="B13" s="32" t="s">
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="B14" s="31" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="B14" s="32" t="s">
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="B15" s="31" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="15" ht="12.75" customHeight="1">
-      <c r="B15" s="32" t="s">
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="B16" s="31" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="16" ht="12.75" customHeight="1">
-      <c r="B16" s="32" t="s">
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="B17" s="31" t="s">
         <v>117</v>
-      </c>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="B17" s="32" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="18" ht="12.75" customHeight="1"/>
@@ -7995,237 +7987,237 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1"/>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="32" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" s="32"/>
+      <c r="C2" s="32"/>
+    </row>
+    <row r="3" ht="12.75" customHeight="1">
+      <c r="A3" s="29"/>
+      <c r="B3" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="B2" s="33"/>
-      <c r="C2" s="33"/>
-    </row>
-    <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="30"/>
-      <c r="B3" s="34" t="s">
+      <c r="C3" s="29"/>
+    </row>
+    <row r="4" ht="12.75" customHeight="1">
+      <c r="A4" s="29"/>
+      <c r="B4" s="34" t="s">
         <v>120</v>
       </c>
-      <c r="C3" s="30"/>
-    </row>
-    <row r="4" ht="12.75" customHeight="1">
-      <c r="A4" s="30"/>
-      <c r="B4" s="35" t="s">
+      <c r="C4" s="29"/>
+    </row>
+    <row r="5" ht="12.75" customHeight="1">
+      <c r="A5" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="C4" s="30"/>
-    </row>
-    <row r="5" ht="12.75" customHeight="1">
-      <c r="A5" s="36" t="s">
+      <c r="B5" s="35"/>
+      <c r="C5" s="35"/>
+    </row>
+    <row r="6" ht="12.75" customHeight="1">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+    </row>
+    <row r="7" ht="12.75" customHeight="1">
+      <c r="A7" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="B5" s="36"/>
-      <c r="C5" s="36"/>
-    </row>
-    <row r="6" ht="12.75" customHeight="1">
-      <c r="A6" s="30"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="30"/>
-    </row>
-    <row r="7" ht="12.75" customHeight="1">
-      <c r="A7" s="37" t="s">
+      <c r="B7" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="B7" s="38" t="s">
+      <c r="C7" s="37" t="s">
         <v>124</v>
       </c>
-      <c r="C7" s="38" t="s">
+      <c r="D7" s="36" t="s">
         <v>125</v>
       </c>
-      <c r="D7" s="37" t="s">
+      <c r="E7" s="36" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="36" t="s">
         <v>126</v>
       </c>
-      <c r="E7" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="37" t="s">
+      <c r="G7" s="36" t="s">
         <v>127</v>
       </c>
-      <c r="G7" s="37" t="s">
+    </row>
+    <row r="8" ht="12.75" customHeight="1">
+      <c r="A8" s="38">
+        <v>1.0</v>
+      </c>
+      <c r="B8" s="39" t="s">
         <v>128</v>
       </c>
-    </row>
-    <row r="8" ht="12.75" customHeight="1">
-      <c r="A8" s="39">
-        <v>1.0</v>
-      </c>
-      <c r="B8" s="40" t="s">
+      <c r="C8" s="39" t="s">
         <v>129</v>
       </c>
-      <c r="C8" s="40" t="s">
+      <c r="D8" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="D8" s="41" t="s">
+      <c r="E8" s="41" t="s">
         <v>131</v>
       </c>
-      <c r="E8" s="42" t="s">
+      <c r="F8" s="42"/>
+      <c r="G8" s="43"/>
+    </row>
+    <row r="9" ht="12.75" customHeight="1">
+      <c r="A9" s="44">
+        <v>2.0</v>
+      </c>
+      <c r="B9" s="45" t="s">
+        <v>128</v>
+      </c>
+      <c r="C9" s="45" t="s">
         <v>132</v>
       </c>
-      <c r="F8" s="43"/>
-      <c r="G8" s="44"/>
-    </row>
-    <row r="9" ht="12.75" customHeight="1">
-      <c r="A9" s="45">
-        <v>2.0</v>
-      </c>
-      <c r="B9" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="C9" s="46" t="s">
+      <c r="D9" s="46" t="s">
+        <v>130</v>
+      </c>
+      <c r="E9" s="47" t="s">
         <v>133</v>
       </c>
-      <c r="D9" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="E9" s="48" t="s">
+      <c r="F9" s="48"/>
+      <c r="G9" s="43"/>
+    </row>
+    <row r="10" ht="12.75" customHeight="1">
+      <c r="A10" s="49">
+        <v>3.0</v>
+      </c>
+      <c r="B10" s="50" t="s">
         <v>134</v>
       </c>
-      <c r="F9" s="49"/>
-      <c r="G9" s="44"/>
-    </row>
-    <row r="10" ht="12.75" customHeight="1">
-      <c r="A10" s="50">
-        <v>3.0</v>
-      </c>
-      <c r="B10" s="51" t="s">
+      <c r="C10" s="50" t="s">
         <v>135</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="D10" s="51" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="52" t="s">
+      <c r="E10" s="52" t="s">
         <v>137</v>
       </c>
-      <c r="E10" s="53" t="s">
+      <c r="F10" s="53"/>
+      <c r="G10" s="54"/>
+    </row>
+    <row r="11" ht="12.75" customHeight="1">
+      <c r="A11" s="38"/>
+      <c r="B11" s="39"/>
+      <c r="C11" s="39"/>
+      <c r="D11" s="40" t="s">
         <v>138</v>
       </c>
-      <c r="F10" s="54"/>
-      <c r="G10" s="55"/>
-    </row>
-    <row r="11" ht="12.75" customHeight="1">
-      <c r="A11" s="39"/>
-      <c r="B11" s="40"/>
-      <c r="C11" s="40"/>
-      <c r="D11" s="41" t="s">
+      <c r="E11" s="41" t="s">
         <v>139</v>
       </c>
-      <c r="E11" s="42" t="s">
+      <c r="F11" s="55"/>
+      <c r="G11" s="56"/>
+    </row>
+    <row r="12" ht="12.75" customHeight="1">
+      <c r="A12" s="57">
+        <v>4.0</v>
+      </c>
+      <c r="B12" s="58" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="56"/>
-      <c r="G11" s="57"/>
-    </row>
-    <row r="12" ht="12.75" customHeight="1">
-      <c r="A12" s="58">
-        <v>4.0</v>
-      </c>
-      <c r="B12" s="59" t="s">
+      <c r="C12" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="C12" s="59" t="s">
+      <c r="D12" s="59" t="s">
         <v>142</v>
       </c>
-      <c r="D12" s="60" t="s">
+      <c r="E12" s="60" t="s">
         <v>143</v>
       </c>
-      <c r="E12" s="61" t="s">
+      <c r="F12" s="61"/>
+      <c r="G12" s="62"/>
+    </row>
+    <row r="13" ht="12.75" customHeight="1">
+      <c r="A13" s="38"/>
+      <c r="B13" s="39"/>
+      <c r="C13" s="39"/>
+      <c r="D13" s="40" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="62"/>
-      <c r="G12" s="63"/>
-    </row>
-    <row r="13" ht="12.75" customHeight="1">
-      <c r="A13" s="39"/>
-      <c r="B13" s="40"/>
-      <c r="C13" s="40"/>
-      <c r="D13" s="41" t="s">
+      <c r="E13" s="41" t="s">
         <v>145</v>
       </c>
-      <c r="E13" s="42" t="s">
+      <c r="F13" s="42"/>
+      <c r="G13" s="56"/>
+    </row>
+    <row r="14" ht="12.75" customHeight="1">
+      <c r="A14" s="57">
+        <v>5.0</v>
+      </c>
+      <c r="B14" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="C14" s="58" t="s">
         <v>146</v>
       </c>
-      <c r="F13" s="43"/>
-      <c r="G13" s="57"/>
-    </row>
-    <row r="14" ht="12.75" customHeight="1">
-      <c r="A14" s="58">
-        <v>5.0</v>
-      </c>
-      <c r="B14" s="59" t="s">
+      <c r="D14" s="59" t="s">
+        <v>147</v>
+      </c>
+      <c r="E14" s="60" t="s">
+        <v>148</v>
+      </c>
+      <c r="F14" s="61"/>
+      <c r="G14" s="62"/>
+    </row>
+    <row r="15" ht="12.75" customHeight="1">
+      <c r="A15" s="38"/>
+      <c r="B15" s="39"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>149</v>
+      </c>
+      <c r="F15" s="63" t="s">
+        <v>150</v>
+      </c>
+      <c r="G15" s="56"/>
+    </row>
+    <row r="16" ht="12.75" customHeight="1">
+      <c r="A16" s="57">
+        <v>6.0</v>
+      </c>
+      <c r="B16" s="58" t="s">
+        <v>140</v>
+      </c>
+      <c r="C16" s="58" t="s">
         <v>141</v>
       </c>
-      <c r="C14" s="59" t="s">
-        <v>147</v>
-      </c>
-      <c r="D14" s="60" t="s">
-        <v>148</v>
-      </c>
-      <c r="E14" s="61" t="s">
+      <c r="D16" s="59" t="s">
+        <v>151</v>
+      </c>
+      <c r="E16" s="60" t="s">
+        <v>152</v>
+      </c>
+      <c r="F16" s="64"/>
+      <c r="G16" s="62"/>
+    </row>
+    <row r="17" ht="12.75" customHeight="1">
+      <c r="A17" s="38"/>
+      <c r="B17" s="39"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="40" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="41" t="s">
         <v>149</v>
       </c>
-      <c r="F14" s="62"/>
-      <c r="G14" s="63"/>
-    </row>
-    <row r="15" ht="12.75" customHeight="1">
-      <c r="A15" s="39"/>
-      <c r="B15" s="40"/>
-      <c r="C15" s="40"/>
-      <c r="D15" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="F15" s="64" t="s">
-        <v>151</v>
-      </c>
-      <c r="G15" s="57"/>
-    </row>
-    <row r="16" ht="12.75" customHeight="1">
-      <c r="A16" s="58">
-        <v>6.0</v>
-      </c>
-      <c r="B16" s="59" t="s">
-        <v>141</v>
-      </c>
-      <c r="C16" s="59" t="s">
-        <v>142</v>
-      </c>
-      <c r="D16" s="60" t="s">
-        <v>152</v>
-      </c>
-      <c r="E16" s="61" t="s">
-        <v>153</v>
-      </c>
-      <c r="F16" s="65"/>
-      <c r="G16" s="63"/>
-    </row>
-    <row r="17" ht="12.75" customHeight="1">
-      <c r="A17" s="39"/>
-      <c r="B17" s="40"/>
-      <c r="C17" s="40"/>
-      <c r="D17" s="41" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="F17" s="66"/>
-      <c r="G17" s="57"/>
+      <c r="F17" s="65"/>
+      <c r="G17" s="56"/>
     </row>
     <row r="18" ht="12.75" customHeight="1">
-      <c r="A18" s="50"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
-      <c r="D18" s="67"/>
-      <c r="E18" s="51"/>
-      <c r="F18" s="67"/>
-      <c r="G18" s="67"/>
+      <c r="A18" s="49"/>
+      <c r="B18" s="49"/>
+      <c r="C18" s="49"/>
+      <c r="D18" s="66"/>
+      <c r="E18" s="50"/>
+      <c r="F18" s="66"/>
+      <c r="G18" s="66"/>
     </row>
     <row r="19" ht="12.75" customHeight="1"/>
     <row r="20" ht="12.75" customHeight="1"/>
